--- a/on_the_way.xlsx
+++ b/on_the_way.xlsx
@@ -16,33 +16,84 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
-  <si>
-    <t>YT8854192398132</t>
-  </si>
-  <si>
-    <t>YT8854024401676</t>
-  </si>
-  <si>
-    <t>JT0022634442173</t>
-  </si>
-  <si>
-    <t>JT0022631852425</t>
-  </si>
-  <si>
-    <t>YT8853824117110</t>
-  </si>
-  <si>
-    <t>YT8854353173859</t>
-  </si>
-  <si>
-    <t>JT5470674116182</t>
-  </si>
-  <si>
-    <t>YT8854146688355</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="26">
   <si>
     <t>Track</t>
+  </si>
+  <si>
+    <t>Yusuf 501250707</t>
+  </si>
+  <si>
+    <t>15.06.2026</t>
+  </si>
+  <si>
+    <t>JT5496410411821</t>
+  </si>
+  <si>
+    <t>Alisher0004-777016333</t>
+  </si>
+  <si>
+    <t>Anvar 977205225</t>
+  </si>
+  <si>
+    <t>JT5496392281486</t>
+  </si>
+  <si>
+    <t>Fayyoz0888-927080406</t>
+  </si>
+  <si>
+    <t>YT8877225732475</t>
+  </si>
+  <si>
+    <t>JT5495399331306</t>
+  </si>
+  <si>
+    <t>YT8877267471668</t>
+  </si>
+  <si>
+    <t>JT5496376810838</t>
+  </si>
+  <si>
+    <t>JT5496270516915</t>
+  </si>
+  <si>
+    <t>JT5495394393083</t>
+  </si>
+  <si>
+    <t>JT5496376872907</t>
+  </si>
+  <si>
+    <t>JT5496389040454</t>
+  </si>
+  <si>
+    <t>JT5495342616032</t>
+  </si>
+  <si>
+    <t>JT5495433647705</t>
+  </si>
+  <si>
+    <t>JT5496380854606</t>
+  </si>
+  <si>
+    <t>JT5495899178526</t>
+  </si>
+  <si>
+    <t>JT5495806308084</t>
+  </si>
+  <si>
+    <t>YT8878190975603</t>
+  </si>
+  <si>
+    <t>YT8878256195196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DATE </t>
+  </si>
+  <si>
+    <t>18.06.26</t>
+  </si>
+  <si>
+    <t>рохба буромад</t>
   </si>
 </sst>
 </file>
@@ -384,165 +435,677 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="20.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>79114287730818</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>79113721261163</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>79114199400506</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>79114203887940</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>777418407164674</v>
+      </c>
+      <c r="C9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>79114287731046</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>79114114585570</v>
+      </c>
+      <c r="C11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>9817311547938</v>
+      </c>
+      <c r="C12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>777418210107128</v>
+      </c>
+      <c r="C13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>777418540098081</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>79114008929258</v>
+      </c>
+      <c r="C16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>79114123496019</v>
+      </c>
+      <c r="C17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>79011910916564</v>
+      </c>
+      <c r="C18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>79114056552890</v>
+      </c>
+      <c r="C20" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>79011810156917</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>79114129226699</v>
+      </c>
+      <c r="C24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" t="s">
+        <v>2</v>
+      </c>
+      <c r="D25" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>79114119950813</v>
+      </c>
+      <c r="C26" t="s">
+        <v>2</v>
+      </c>
+      <c r="D26" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>79113831226396</v>
+      </c>
+      <c r="C27" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>79114249344806</v>
+      </c>
+      <c r="C29" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>9817286636034</v>
+      </c>
+      <c r="C30" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" t="s">
+        <v>2</v>
+      </c>
+      <c r="D31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>9817306833974</v>
+      </c>
+      <c r="C32" t="s">
+        <v>2</v>
+      </c>
+      <c r="D32" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D33" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>9817266811309</v>
+      </c>
+      <c r="C34" t="s">
+        <v>2</v>
+      </c>
+      <c r="D34" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>79114119952579</v>
+      </c>
+      <c r="C35" t="s">
+        <v>2</v>
+      </c>
+      <c r="D35" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" t="s">
+        <v>2</v>
+      </c>
+      <c r="D36" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>79113859937536</v>
+      </c>
+      <c r="C37" t="s">
+        <v>2</v>
+      </c>
+      <c r="D37" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>9817310662063</v>
+      </c>
+      <c r="C38" t="s">
+        <v>2</v>
+      </c>
+      <c r="D38" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>79113826114819</v>
+      </c>
+      <c r="C39" t="s">
+        <v>2</v>
+      </c>
+      <c r="D39" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>79114123512156</v>
+      </c>
+      <c r="C40" t="s">
+        <v>2</v>
+      </c>
+      <c r="D40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>9817293577073</v>
+      </c>
+      <c r="C41" t="s">
+        <v>2</v>
+      </c>
+      <c r="D41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>79114123473093</v>
+      </c>
+      <c r="C42" t="s">
+        <v>2</v>
+      </c>
+      <c r="D42" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" t="s">
+        <v>2</v>
+      </c>
+      <c r="D43" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>79114114546115</v>
+      </c>
+      <c r="C44" t="s">
+        <v>2</v>
+      </c>
+      <c r="D44" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>465426010024137</v>
+      </c>
+      <c r="C45" t="s">
+        <v>2</v>
+      </c>
+      <c r="D45" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>9817293845966</v>
+      </c>
+      <c r="C46" t="s">
+        <v>2</v>
+      </c>
+      <c r="D46" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>9</v>
+      </c>
+      <c r="C47" t="s">
+        <v>2</v>
+      </c>
+      <c r="D47" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>79114224672451</v>
+      </c>
+      <c r="C48" t="s">
+        <v>2</v>
+      </c>
+      <c r="D48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>9817310661010</v>
+      </c>
+      <c r="C49" t="s">
+        <v>2</v>
+      </c>
+      <c r="D49" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>78590946320856</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
-        <v>777395872957833</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>9815040285428</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
-        <v>9815041606309</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <v>465206723405076</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
-        <v>9815106710951</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
-        <v>465212977190580</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
-        <v>78590261371754</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
-        <v>78991601969677</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="C50" t="s">
+        <v>2</v>
+      </c>
+      <c r="D50" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" t="s">
+        <v>2</v>
+      </c>
+      <c r="D51" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>79114096392960</v>
+      </c>
+      <c r="C52" t="s">
+        <v>2</v>
+      </c>
+      <c r="D52" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>777417680528740</v>
+      </c>
+      <c r="C53" t="s">
+        <v>2</v>
+      </c>
+      <c r="D53" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>79114114545731</v>
+      </c>
+      <c r="C54" t="s">
+        <v>2</v>
+      </c>
+      <c r="D54" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>79114123470502</v>
+      </c>
+      <c r="C55" t="s">
+        <v>2</v>
+      </c>
+      <c r="D55" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>79114158480850</v>
+      </c>
+      <c r="C56" t="s">
+        <v>2</v>
+      </c>
+      <c r="D56" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>79114287730634</v>
+      </c>
+      <c r="C57" t="s">
+        <v>2</v>
+      </c>
+      <c r="D57" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>79011815866016</v>
+      </c>
+      <c r="C58" t="s">
+        <v>2</v>
+      </c>
+      <c r="D58" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>777418512271860</v>
+      </c>
+      <c r="C59" t="s">
+        <v>2</v>
+      </c>
+      <c r="D59" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
-        <v>78590344958183</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
-        <v>465207044287168</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
-        <v>777395656342166</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
-        <v>465207251332983</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
-        <v>78590930125150</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
-        <v>465211063196648</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="1">
-        <v>78590814134280</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
-        <v>777395640477337</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
-        <v>9815139666088</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
-        <v>777395796170254</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
-        <v>777394834611460</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" s="1">
-        <v>465206521408152</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" s="1">
-        <v>465212373853512</v>
+      <c r="C60" t="s">
+        <v>2</v>
+      </c>
+      <c r="D60" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C61" t="s">
+        <v>24</v>
+      </c>
+      <c r="D61" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/on_the_way.xlsx
+++ b/on_the_way.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="35">
   <si>
     <t>Track</t>
   </si>
@@ -94,15 +94,49 @@
   </si>
   <si>
     <t>рохба буромад</t>
+  </si>
+  <si>
+    <t>SF5197155647582</t>
+  </si>
+  <si>
+    <t>YT8878636869808</t>
+  </si>
+  <si>
+    <t>SF5197162197328</t>
+  </si>
+  <si>
+    <t>YT8878955638123</t>
+  </si>
+  <si>
+    <t>YT8878964260562</t>
+  </si>
+  <si>
+    <t>JT5496184190660</t>
+  </si>
+  <si>
+    <t>YT8879052026024</t>
+  </si>
+  <si>
+    <t>JT5497157488381</t>
+  </si>
+  <si>
+    <t>BAHTIGUL 875266000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -129,9 +163,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -435,681 +472,869 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D61"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D83"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.33203125" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="20.77734375" customWidth="1"/>
+    <col min="1" max="1" width="19.77734375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" style="1"/>
+    <col min="3" max="3" width="12" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.77734375" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
+      <c r="A4" s="2">
         <v>79114287730818</v>
       </c>
-      <c r="C4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
+      <c r="A5" s="2">
         <v>79113721261163</v>
       </c>
-      <c r="C5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
+      <c r="A6" s="2">
         <v>79114199400506</v>
       </c>
-      <c r="C6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="C7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
+      <c r="A8" s="2">
         <v>79114203887940</v>
       </c>
-      <c r="C8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="C8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
+      <c r="A9" s="2">
         <v>777418407164674</v>
       </c>
-      <c r="C9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="C9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
+      <c r="A10" s="2">
         <v>79114287731046</v>
       </c>
-      <c r="C10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="C10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
+      <c r="A11" s="2">
         <v>79114114585570</v>
       </c>
-      <c r="C11" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="C11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
+      <c r="A12" s="2">
         <v>9817311547938</v>
       </c>
-      <c r="C12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="C12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
+      <c r="A13" s="2">
         <v>777418210107128</v>
       </c>
-      <c r="C13" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="C13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C14" t="s">
-        <v>2</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="C14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
+      <c r="A15" s="2">
         <v>777418540098081</v>
       </c>
-      <c r="C15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="C15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
+      <c r="A16" s="2">
         <v>79114008929258</v>
       </c>
-      <c r="C16" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="C16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
+      <c r="A17" s="2">
         <v>79114123496019</v>
       </c>
-      <c r="C17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="C17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
+      <c r="A18" s="2">
         <v>79011910916564</v>
       </c>
-      <c r="C18" t="s">
-        <v>2</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="C18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C19" t="s">
-        <v>2</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="C19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
+      <c r="A20" s="2">
         <v>79114056552890</v>
       </c>
-      <c r="C20" t="s">
-        <v>2</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="C20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C21" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="C21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
+      <c r="A22" s="2">
         <v>79011810156917</v>
       </c>
-      <c r="C22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="C22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C23" t="s">
-        <v>2</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="C23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
+      <c r="A24" s="2">
         <v>79114129226699</v>
       </c>
-      <c r="C24" t="s">
-        <v>2</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="C24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C25" t="s">
-        <v>2</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="C25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
+      <c r="A26" s="2">
         <v>79114119950813</v>
       </c>
-      <c r="C26" t="s">
-        <v>2</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="C26" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
+      <c r="A27" s="2">
         <v>79113831226396</v>
       </c>
-      <c r="C27" t="s">
-        <v>2</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="C27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C28" t="s">
-        <v>2</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="C28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="1">
+      <c r="A29" s="2">
         <v>79114249344806</v>
       </c>
-      <c r="C29" t="s">
-        <v>2</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="C29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="1">
+      <c r="A30" s="2">
         <v>9817286636034</v>
       </c>
-      <c r="C30" t="s">
-        <v>2</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="C30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C31" t="s">
-        <v>2</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="C31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="1">
+      <c r="A32" s="2">
         <v>9817306833974</v>
       </c>
-      <c r="C32" t="s">
-        <v>2</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="C32" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C33" t="s">
-        <v>2</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="C33" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="1">
+      <c r="A34" s="2">
         <v>9817266811309</v>
       </c>
-      <c r="C34" t="s">
-        <v>2</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="C34" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="1">
+      <c r="A35" s="2">
         <v>79114119952579</v>
       </c>
-      <c r="C35" t="s">
-        <v>2</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="C35" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C36" t="s">
-        <v>2</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="C36" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="1">
+      <c r="A37" s="2">
         <v>79113859937536</v>
       </c>
-      <c r="C37" t="s">
-        <v>2</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="C37" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="1">
+      <c r="A38" s="2">
         <v>9817310662063</v>
       </c>
-      <c r="C38" t="s">
-        <v>2</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="C38" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="1">
+      <c r="A39" s="2">
         <v>79113826114819</v>
       </c>
-      <c r="C39" t="s">
-        <v>2</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="C39" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="1">
+      <c r="A40" s="2">
         <v>79114123512156</v>
       </c>
-      <c r="C40" t="s">
-        <v>2</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="C40" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="1">
+      <c r="A41" s="2">
         <v>9817293577073</v>
       </c>
-      <c r="C41" t="s">
-        <v>2</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="C41" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="1">
+      <c r="A42" s="2">
         <v>79114123473093</v>
       </c>
-      <c r="C42" t="s">
-        <v>2</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="C42" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+      <c r="A43" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C43" t="s">
-        <v>2</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="C43" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="1">
+      <c r="A44" s="2">
         <v>79114114546115</v>
       </c>
-      <c r="C44" t="s">
-        <v>2</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="C44" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="1">
+      <c r="A45" s="2">
         <v>465426010024137</v>
       </c>
-      <c r="C45" t="s">
-        <v>2</v>
-      </c>
-      <c r="D45" t="s">
+      <c r="C45" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="1">
+      <c r="A46" s="2">
         <v>9817293845966</v>
       </c>
-      <c r="C46" t="s">
-        <v>2</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="C46" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+      <c r="A47" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C47" t="s">
-        <v>2</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="C47" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="1">
+      <c r="A48" s="2">
         <v>79114224672451</v>
       </c>
-      <c r="C48" t="s">
-        <v>2</v>
-      </c>
-      <c r="D48" t="s">
+      <c r="C48" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="1">
+      <c r="A49" s="2">
         <v>9817310661010</v>
       </c>
-      <c r="C49" t="s">
-        <v>2</v>
-      </c>
-      <c r="D49" t="s">
+      <c r="C49" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+      <c r="A50" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C50" t="s">
-        <v>2</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="C50" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+      <c r="A51" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C51" t="s">
-        <v>2</v>
-      </c>
-      <c r="D51" t="s">
+      <c r="C51" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="1">
+      <c r="A52" s="2">
         <v>79114096392960</v>
       </c>
-      <c r="C52" t="s">
-        <v>2</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="C52" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="1">
+      <c r="A53" s="2">
         <v>777417680528740</v>
       </c>
-      <c r="C53" t="s">
-        <v>2</v>
-      </c>
-      <c r="D53" t="s">
+      <c r="C53" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="1">
+      <c r="A54" s="2">
         <v>79114114545731</v>
       </c>
-      <c r="C54" t="s">
-        <v>2</v>
-      </c>
-      <c r="D54" t="s">
+      <c r="C54" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="1">
+      <c r="A55" s="2">
         <v>79114123470502</v>
       </c>
-      <c r="C55" t="s">
-        <v>2</v>
-      </c>
-      <c r="D55" t="s">
+      <c r="C55" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="1">
+      <c r="A56" s="2">
         <v>79114158480850</v>
       </c>
-      <c r="C56" t="s">
-        <v>2</v>
-      </c>
-      <c r="D56" t="s">
+      <c r="C56" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="1">
+      <c r="A57" s="2">
         <v>79114287730634</v>
       </c>
-      <c r="C57" t="s">
-        <v>2</v>
-      </c>
-      <c r="D57" t="s">
+      <c r="C57" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="1">
+      <c r="A58" s="2">
         <v>79011815866016</v>
       </c>
-      <c r="C58" t="s">
-        <v>2</v>
-      </c>
-      <c r="D58" t="s">
+      <c r="C58" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="1">
+      <c r="A59" s="2">
         <v>777418512271860</v>
       </c>
-      <c r="C59" t="s">
-        <v>2</v>
-      </c>
-      <c r="D59" t="s">
+      <c r="C59" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+      <c r="A60" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C60" t="s">
-        <v>2</v>
-      </c>
-      <c r="D60" t="s">
+      <c r="C60" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C61" t="s">
+      <c r="C61" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D61" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C62" s="1">
+        <v>20.0626</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" s="2">
+        <v>77419047733484</v>
+      </c>
+      <c r="C63" s="1">
+        <v>20.0626</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" s="2">
+        <v>465430383814609</v>
+      </c>
+      <c r="C64" s="1">
+        <v>20.0626</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" s="2">
+        <v>777419015424748</v>
+      </c>
+      <c r="C65" s="1">
+        <v>20.0626</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" s="2">
+        <v>465429582994887</v>
+      </c>
+      <c r="C66" s="1">
+        <v>20.0626</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" s="2">
+        <v>79114917851687</v>
+      </c>
+      <c r="C67" s="1">
+        <v>20.0626</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C68" s="1">
+        <v>20.0626</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C69" s="1">
+        <v>20.0626</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" s="2">
+        <v>79114362617905</v>
+      </c>
+      <c r="C70" s="1">
+        <v>20.0626</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" s="2">
+        <v>79114362826221</v>
+      </c>
+      <c r="C71" s="1">
+        <v>20.0626</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" s="2">
+        <v>79114362855049</v>
+      </c>
+      <c r="C72" s="1">
+        <v>20.0626</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C73" s="1">
+        <v>20.0626</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" s="2">
+        <v>79114716195683</v>
+      </c>
+      <c r="C74" s="1">
+        <v>20.0626</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" s="2">
+        <v>465432952519118</v>
+      </c>
+      <c r="C75" s="1">
+        <v>20.0626</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C76" s="1">
+        <v>20.0626</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="1">
+        <v>20.0626</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C78" s="1">
+        <v>20.0626</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C79" s="1">
+        <v>20.0626</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80" s="2">
+        <v>79114362617905</v>
+      </c>
+      <c r="C80" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" s="2">
+        <v>777419015424748</v>
+      </c>
+      <c r="C81" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" s="2">
+        <v>79114302102362</v>
+      </c>
+      <c r="C82" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C83" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>25</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
 </file>
 

--- a/on_the_way.xlsx
+++ b/on_the_way.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="61">
   <si>
     <t>Track</t>
   </si>
@@ -121,6 +121,84 @@
   </si>
   <si>
     <t>BAHTIGUL 875266000</t>
+  </si>
+  <si>
+    <t>YT8877953717504</t>
+  </si>
+  <si>
+    <t>YT8878376042259</t>
+  </si>
+  <si>
+    <t>JT5496562912088</t>
+  </si>
+  <si>
+    <t>Hasanjon 9283135944</t>
+  </si>
+  <si>
+    <t>JT5495975576123</t>
+  </si>
+  <si>
+    <t>JT5496426856472</t>
+  </si>
+  <si>
+    <t>YT8877978258660</t>
+  </si>
+  <si>
+    <t>JT5496083260646</t>
+  </si>
+  <si>
+    <t>JT5496555809498</t>
+  </si>
+  <si>
+    <t>YT8878489431799</t>
+  </si>
+  <si>
+    <t>YT8878924839212</t>
+  </si>
+  <si>
+    <t>YT8877954257843</t>
+  </si>
+  <si>
+    <t>JT5496397100619</t>
+  </si>
+  <si>
+    <t>JT5496532028174</t>
+  </si>
+  <si>
+    <t>YT8877957922382</t>
+  </si>
+  <si>
+    <t>YT8878892869002</t>
+  </si>
+  <si>
+    <t>YT8878973794278</t>
+  </si>
+  <si>
+    <t>JT5496426439535</t>
+  </si>
+  <si>
+    <t>YT8878013142445</t>
+  </si>
+  <si>
+    <t>Islombek 783349009</t>
+  </si>
+  <si>
+    <t>YT8878891266189</t>
+  </si>
+  <si>
+    <t>YT8878364185573</t>
+  </si>
+  <si>
+    <t>YT8878433846646</t>
+  </si>
+  <si>
+    <t>YT8878373344697</t>
+  </si>
+  <si>
+    <t>JT5496397081847</t>
+  </si>
+  <si>
+    <t>Hilola 555572809</t>
   </si>
 </sst>
 </file>
@@ -163,13 +241,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -472,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D83"/>
+  <dimension ref="A1:D129"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.77734375" style="2" customWidth="1"/>
@@ -1324,11 +1405,563 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A83" s="1">
+        <v>79114218356055</v>
+      </c>
+      <c r="B83"/>
       <c r="C83" s="1">
         <v>20.0626</v>
       </c>
-      <c r="D83" s="1" t="s">
+      <c r="D83" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A84" s="1">
+        <v>79012581856167</v>
+      </c>
+      <c r="B84"/>
+      <c r="C84" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D84" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A85" s="1">
+        <v>79114409063138</v>
+      </c>
+      <c r="B85"/>
+      <c r="C85" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D85" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A86" s="1">
+        <v>79114218396909</v>
+      </c>
+      <c r="B86"/>
+      <c r="C86" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D86" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A87" s="1">
+        <v>9817337232960</v>
+      </c>
+      <c r="B87"/>
+      <c r="C87" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D87" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A88" s="1">
+        <v>465426605460787</v>
+      </c>
+      <c r="B88"/>
+      <c r="C88" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D88" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A89" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B89"/>
+      <c r="C89" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D89" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A90" s="1">
+        <v>79114347075820</v>
+      </c>
+      <c r="B90"/>
+      <c r="C90" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D90" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A91" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B91"/>
+      <c r="C91" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D91" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A92" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B92"/>
+      <c r="C92" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D92" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A93" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B93"/>
+      <c r="C93" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D93" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A94" s="1">
+        <v>79114641590826</v>
+      </c>
+      <c r="B94"/>
+      <c r="C94" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D94" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B95"/>
+      <c r="C95" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D95" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A96" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B96"/>
+      <c r="C96" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D96" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A97" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B97"/>
+      <c r="C97" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D97" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A98" s="1">
+        <v>777419080528783</v>
+      </c>
+      <c r="B98"/>
+      <c r="C98" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D98" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A99" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B99"/>
+      <c r="C99" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D99" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A100" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B100"/>
+      <c r="C100" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D100" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A101" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B101"/>
+      <c r="C101" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D101" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A102" s="1">
+        <v>9817298550257</v>
+      </c>
+      <c r="B102"/>
+      <c r="C102" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D102" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A103" s="1">
+        <v>9817338834087</v>
+      </c>
+      <c r="B103"/>
+      <c r="C103" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D103" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A104" s="1">
+        <v>79114351420184</v>
+      </c>
+      <c r="B104"/>
+      <c r="C104" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D104" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A105" s="1">
+        <v>79114523941757</v>
+      </c>
+      <c r="B105"/>
+      <c r="C105" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D105" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A106" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B106"/>
+      <c r="C106" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D106" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A107" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B107"/>
+      <c r="C107" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D107" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A108" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B108"/>
+      <c r="C108" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D108" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A109" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B109"/>
+      <c r="C109" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D109" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A110" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B110"/>
+      <c r="C110" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D110" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A111" s="1">
+        <v>465425273153619</v>
+      </c>
+      <c r="B111"/>
+      <c r="C111" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D111" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A112" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B112"/>
+      <c r="C112" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D112" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A113" s="1">
+        <v>79114272667800</v>
+      </c>
+      <c r="B113"/>
+      <c r="C113" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D113" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A114" s="1">
+        <v>79114445687079</v>
+      </c>
+      <c r="B114"/>
+      <c r="C114" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D114" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A115" s="1">
+        <v>777419340694859</v>
+      </c>
+      <c r="B115"/>
+      <c r="C115" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D115" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A116" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B116"/>
+      <c r="C116" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D116" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A117" s="1">
+        <v>777419197107227</v>
+      </c>
+      <c r="B117"/>
+      <c r="C117" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D117" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A118" s="1">
+        <v>777419193134582</v>
+      </c>
+      <c r="B118"/>
+      <c r="C118" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D118" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A119" s="1">
+        <v>777419149591288</v>
+      </c>
+      <c r="B119"/>
+      <c r="C119" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D119" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A120" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B120"/>
+      <c r="C120" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D120" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A121" s="1">
+        <v>465427544369324</v>
+      </c>
+      <c r="B121"/>
+      <c r="C121" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D121" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A122" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B122"/>
+      <c r="C122" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D122" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A123" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B123"/>
+      <c r="C123" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D123" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A124" s="1">
+        <v>435227038851000</v>
+      </c>
+      <c r="B124"/>
+      <c r="C124" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D124" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A125" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B125"/>
+      <c r="C125" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D125" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A126" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B126"/>
+      <c r="C126" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D126" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A127" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B127"/>
+      <c r="C127" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D127" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A128" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B128"/>
+      <c r="C128" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D128" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C129" s="1">
+        <v>20.0626</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>25</v>
       </c>
     </row>

--- a/on_the_way.xlsx
+++ b/on_the_way.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="192">
   <si>
     <t>Track</t>
   </si>
@@ -199,13 +199,406 @@
   </si>
   <si>
     <t>Hilola 555572809</t>
+  </si>
+  <si>
+    <t>777421190698415</t>
+  </si>
+  <si>
+    <t>777420190077415</t>
+  </si>
+  <si>
+    <t>_x000D_777420148088605</t>
+  </si>
+  <si>
+    <t>777420320755106</t>
+  </si>
+  <si>
+    <t>JT5498515169938</t>
+  </si>
+  <si>
+    <t>777420415699128</t>
+  </si>
+  <si>
+    <t>9817455768664</t>
+  </si>
+  <si>
+    <t>465445838248752</t>
+  </si>
+  <si>
+    <t>79115916921709</t>
+  </si>
+  <si>
+    <t>465445620423811</t>
+  </si>
+  <si>
+    <t>79116064173156</t>
+  </si>
+  <si>
+    <t>9817475375924</t>
+  </si>
+  <si>
+    <t>777420209995112</t>
+  </si>
+  <si>
+    <t>9817494430164</t>
+  </si>
+  <si>
+    <t>777420107395099</t>
+  </si>
+  <si>
+    <t>9817479807223</t>
+  </si>
+  <si>
+    <t>JT5498130519084</t>
+  </si>
+  <si>
+    <t>YT8880292978538</t>
+  </si>
+  <si>
+    <t>9817512182414</t>
+  </si>
+  <si>
+    <t>777420364234201</t>
+  </si>
+  <si>
+    <t>JT5498262384603</t>
+  </si>
+  <si>
+    <t>JT5498044681933</t>
+  </si>
+  <si>
+    <t>YT8879925973530</t>
+  </si>
+  <si>
+    <t>79013823518038</t>
+  </si>
+  <si>
+    <t>777421046930615</t>
+  </si>
+  <si>
+    <t>777421365313677</t>
+  </si>
+  <si>
+    <t>465444445672611</t>
+  </si>
+  <si>
+    <t>465448988108738</t>
+  </si>
+  <si>
+    <t>YT8879882443578</t>
+  </si>
+  <si>
+    <t>9817450914859</t>
+  </si>
+  <si>
+    <t>9817508074958</t>
+  </si>
+  <si>
+    <t>79116252056460</t>
+  </si>
+  <si>
+    <t>777421232224929</t>
+  </si>
+  <si>
+    <t>YT7628954567668</t>
+  </si>
+  <si>
+    <t>465447154216665</t>
+  </si>
+  <si>
+    <t>JT5498880650303</t>
+  </si>
+  <si>
+    <t>JT5498569535322</t>
+  </si>
+  <si>
+    <t>JT9001972082680</t>
+  </si>
+  <si>
+    <t>9817528972077</t>
+  </si>
+  <si>
+    <t>465447506810494</t>
+  </si>
+  <si>
+    <t>777421365892035</t>
+  </si>
+  <si>
+    <t>YT8880510987456</t>
+  </si>
+  <si>
+    <t>YT8879913736413</t>
+  </si>
+  <si>
+    <t>777421096212600</t>
+  </si>
+  <si>
+    <t>JT5498684503822</t>
+  </si>
+  <si>
+    <t>465443036459439</t>
+  </si>
+  <si>
+    <t>773428109156580</t>
+  </si>
+  <si>
+    <t>777420362773842</t>
+  </si>
+  <si>
+    <t>465431595916185</t>
+  </si>
+  <si>
+    <t>79115778829822</t>
+  </si>
+  <si>
+    <t>773427894002509</t>
+  </si>
+  <si>
+    <t>9817488472301</t>
+  </si>
+  <si>
+    <t>JT5497902864629</t>
+  </si>
+  <si>
+    <t>79115217530969</t>
+  </si>
+  <si>
+    <t>465438148003260</t>
+  </si>
+  <si>
+    <t>9817400004337</t>
+  </si>
+  <si>
+    <t>JT5497309265696</t>
+  </si>
+  <si>
+    <t>465440833112815</t>
+  </si>
+  <si>
+    <t>465443562685094</t>
+  </si>
+  <si>
+    <t>777420761036545</t>
+  </si>
+  <si>
+    <t>9817406887127</t>
+  </si>
+  <si>
+    <t>79115160935146</t>
+  </si>
+  <si>
+    <t>465438121549440</t>
+  </si>
+  <si>
+    <t>777419598365458</t>
+  </si>
+  <si>
+    <t>JT3167641128678</t>
+  </si>
+  <si>
+    <t>777419937761545</t>
+  </si>
+  <si>
+    <t>JT5498008554176</t>
+  </si>
+  <si>
+    <t>79115423942776</t>
+  </si>
+  <si>
+    <t>777420736117016</t>
+  </si>
+  <si>
+    <t>9817515911466</t>
+  </si>
+  <si>
+    <t>YT8878768954500</t>
+  </si>
+  <si>
+    <t>JT5497412193995</t>
+  </si>
+  <si>
+    <t>465436556503490</t>
+  </si>
+  <si>
+    <t>777420344786652</t>
+  </si>
+  <si>
+    <t>465436248025772</t>
+  </si>
+  <si>
+    <t>777420036266214</t>
+  </si>
+  <si>
+    <t>YT8879801289410</t>
+  </si>
+  <si>
+    <t>JT5496862334701</t>
+  </si>
+  <si>
+    <t>YT8879664256136</t>
+  </si>
+  <si>
+    <t>9817390894601</t>
+  </si>
+  <si>
+    <t>YT8878968394212</t>
+  </si>
+  <si>
+    <t>79115259676892</t>
+  </si>
+  <si>
+    <t>79115339142391</t>
+  </si>
+  <si>
+    <t>79115778018962</t>
+  </si>
+  <si>
+    <t>79115562559722</t>
+  </si>
+  <si>
+    <t>YT8879654833161</t>
+  </si>
+  <si>
+    <t>79115875475609</t>
+  </si>
+  <si>
+    <t>YT8880224877818</t>
+  </si>
+  <si>
+    <t>79115618203299</t>
+  </si>
+  <si>
+    <t>YT8879492297615</t>
+  </si>
+  <si>
+    <t>9817413373378</t>
+  </si>
+  <si>
+    <t>777420502615652</t>
+  </si>
+  <si>
+    <t>465442166542045</t>
+  </si>
+  <si>
+    <t>9817444225906</t>
+  </si>
+  <si>
+    <t>777420511746482</t>
+  </si>
+  <si>
+    <t>JT5498240151291</t>
+  </si>
+  <si>
+    <t>465439549581166</t>
+  </si>
+  <si>
+    <t>YT8880516144853</t>
+  </si>
+  <si>
+    <t>JT5497763940837</t>
+  </si>
+  <si>
+    <t>YT8879719599548</t>
+  </si>
+  <si>
+    <t>9817507329843</t>
+  </si>
+  <si>
+    <t>YT8879250061555</t>
+  </si>
+  <si>
+    <t>JT5497935900101</t>
+  </si>
+  <si>
+    <t>777419489090424</t>
+  </si>
+  <si>
+    <t>777419981445223</t>
+  </si>
+  <si>
+    <t>777419765655499</t>
+  </si>
+  <si>
+    <t>YT8879455407277</t>
+  </si>
+  <si>
+    <t>9817409543990</t>
+  </si>
+  <si>
+    <t>9817405916045</t>
+  </si>
+  <si>
+    <t>JT5497337398636</t>
+  </si>
+  <si>
+    <t>JT5496612105825</t>
+  </si>
+  <si>
+    <t>465431628056949</t>
+  </si>
+  <si>
+    <t>465437677907712</t>
+  </si>
+  <si>
+    <t>79115529526722</t>
+  </si>
+  <si>
+    <t>9817416839635</t>
+  </si>
+  <si>
+    <t>9817420692647</t>
+  </si>
+  <si>
+    <t>79115132996630</t>
+  </si>
+  <si>
+    <t>9817455368726</t>
+  </si>
+  <si>
+    <t>465443092240324</t>
+  </si>
+  <si>
+    <t>YT8879556055276</t>
+  </si>
+  <si>
+    <t>79115622195645</t>
+  </si>
+  <si>
+    <t>9822575422831</t>
+  </si>
+  <si>
+    <t>9817439413482</t>
+  </si>
+  <si>
+    <t>YT8879522724737</t>
+  </si>
+  <si>
+    <t>9817417696535</t>
+  </si>
+  <si>
+    <t>9817424014641</t>
+  </si>
+  <si>
+    <t>465434996040715</t>
+  </si>
+  <si>
+    <t>9817411332059</t>
+  </si>
+  <si>
+    <t>JT5496867306346</t>
+  </si>
+  <si>
+    <t>77420713856011</t>
+  </si>
+  <si>
+    <t>26.06.26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -220,6 +613,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -229,7 +629,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -237,11 +637,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyBorder="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -252,9 +670,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -553,8 +990,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D129"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D260"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="19.77734375" style="2" customWidth="1"/>
     <col min="2" max="2" width="8.88671875" style="1"/>
@@ -563,7 +1000,7 @@
     <col min="5" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -571,7 +1008,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>22</v>
       </c>
@@ -582,7 +1019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
         <v>21</v>
       </c>
@@ -593,7 +1030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" s="2">
         <v>79114287730818</v>
       </c>
@@ -604,7 +1041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5" s="2">
         <v>79113721261163</v>
       </c>
@@ -615,7 +1052,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" s="2">
         <v>79114199400506</v>
       </c>
@@ -626,7 +1063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
         <v>20</v>
       </c>
@@ -637,7 +1074,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8" s="2">
         <v>79114203887940</v>
       </c>
@@ -648,7 +1085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="A9" s="2">
         <v>777418407164674</v>
       </c>
@@ -659,7 +1096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="A10" s="2">
         <v>79114287731046</v>
       </c>
@@ -670,7 +1107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4">
       <c r="A11" s="2">
         <v>79114114585570</v>
       </c>
@@ -681,7 +1118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="A12" s="2">
         <v>9817311547938</v>
       </c>
@@ -692,7 +1129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4">
       <c r="A13" s="2">
         <v>777418210107128</v>
       </c>
@@ -703,7 +1140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
         <v>19</v>
       </c>
@@ -714,7 +1151,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4">
       <c r="A15" s="2">
         <v>777418540098081</v>
       </c>
@@ -725,7 +1162,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4">
       <c r="A16" s="2">
         <v>79114008929258</v>
       </c>
@@ -736,7 +1173,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4">
       <c r="A17" s="2">
         <v>79114123496019</v>
       </c>
@@ -747,7 +1184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4">
       <c r="A18" s="2">
         <v>79011910916564</v>
       </c>
@@ -758,7 +1195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
@@ -769,7 +1206,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4">
       <c r="A20" s="2">
         <v>79114056552890</v>
       </c>
@@ -780,7 +1217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
         <v>17</v>
       </c>
@@ -791,7 +1228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4">
       <c r="A22" s="2">
         <v>79011810156917</v>
       </c>
@@ -802,7 +1239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
         <v>16</v>
       </c>
@@ -813,7 +1250,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4">
       <c r="A24" s="2">
         <v>79114129226699</v>
       </c>
@@ -824,7 +1261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
         <v>15</v>
       </c>
@@ -835,7 +1272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4">
       <c r="A26" s="2">
         <v>79114119950813</v>
       </c>
@@ -846,7 +1283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4">
       <c r="A27" s="2">
         <v>79113831226396</v>
       </c>
@@ -857,7 +1294,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
         <v>14</v>
       </c>
@@ -868,7 +1305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4">
       <c r="A29" s="2">
         <v>79114249344806</v>
       </c>
@@ -879,7 +1316,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4">
       <c r="A30" s="2">
         <v>9817286636034</v>
       </c>
@@ -890,7 +1327,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4">
       <c r="A31" s="2" t="s">
         <v>13</v>
       </c>
@@ -901,7 +1338,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4">
       <c r="A32" s="2">
         <v>9817306833974</v>
       </c>
@@ -912,7 +1349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4">
       <c r="A33" s="2" t="s">
         <v>12</v>
       </c>
@@ -923,7 +1360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4">
       <c r="A34" s="2">
         <v>9817266811309</v>
       </c>
@@ -934,7 +1371,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4">
       <c r="A35" s="2">
         <v>79114119952579</v>
       </c>
@@ -945,7 +1382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4">
       <c r="A36" s="2" t="s">
         <v>11</v>
       </c>
@@ -956,7 +1393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4">
       <c r="A37" s="2">
         <v>79113859937536</v>
       </c>
@@ -967,7 +1404,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4">
       <c r="A38" s="2">
         <v>9817310662063</v>
       </c>
@@ -978,7 +1415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4">
       <c r="A39" s="2">
         <v>79113826114819</v>
       </c>
@@ -989,7 +1426,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4">
       <c r="A40" s="2">
         <v>79114123512156</v>
       </c>
@@ -1000,7 +1437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4">
       <c r="A41" s="2">
         <v>9817293577073</v>
       </c>
@@ -1011,7 +1448,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4">
       <c r="A42" s="2">
         <v>79114123473093</v>
       </c>
@@ -1022,7 +1459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4">
       <c r="A43" s="2" t="s">
         <v>10</v>
       </c>
@@ -1033,7 +1470,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4">
       <c r="A44" s="2">
         <v>79114114546115</v>
       </c>
@@ -1044,7 +1481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4">
       <c r="A45" s="2">
         <v>465426010024137</v>
       </c>
@@ -1055,7 +1492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4">
       <c r="A46" s="2">
         <v>9817293845966</v>
       </c>
@@ -1066,7 +1503,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4">
       <c r="A47" s="2" t="s">
         <v>9</v>
       </c>
@@ -1077,7 +1514,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4">
       <c r="A48" s="2">
         <v>79114224672451</v>
       </c>
@@ -1088,7 +1525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4">
       <c r="A49" s="2">
         <v>9817310661010</v>
       </c>
@@ -1099,7 +1536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4">
       <c r="A50" s="2" t="s">
         <v>8</v>
       </c>
@@ -1110,7 +1547,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4">
       <c r="A51" s="2" t="s">
         <v>6</v>
       </c>
@@ -1121,7 +1558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4">
       <c r="A52" s="2">
         <v>79114096392960</v>
       </c>
@@ -1132,7 +1569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4">
       <c r="A53" s="2">
         <v>777417680528740</v>
       </c>
@@ -1143,7 +1580,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4">
       <c r="A54" s="2">
         <v>79114114545731</v>
       </c>
@@ -1154,7 +1591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4">
       <c r="A55" s="2">
         <v>79114123470502</v>
       </c>
@@ -1165,7 +1602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4">
       <c r="A56" s="2">
         <v>79114158480850</v>
       </c>
@@ -1176,7 +1613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4">
       <c r="A57" s="2">
         <v>79114287730634</v>
       </c>
@@ -1187,7 +1624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4">
       <c r="A58" s="2">
         <v>79011815866016</v>
       </c>
@@ -1198,7 +1635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4">
       <c r="A59" s="2">
         <v>777418512271860</v>
       </c>
@@ -1209,7 +1646,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4">
       <c r="A60" s="2" t="s">
         <v>3</v>
       </c>
@@ -1220,7 +1657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4">
       <c r="C61" s="1" t="s">
         <v>24</v>
       </c>
@@ -1228,7 +1665,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4">
       <c r="A62" s="2" t="s">
         <v>26</v>
       </c>
@@ -1236,7 +1673,7 @@
         <v>20.0626</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4">
       <c r="A63" s="2">
         <v>77419047733484</v>
       </c>
@@ -1244,7 +1681,7 @@
         <v>20.0626</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4">
       <c r="A64" s="2">
         <v>465430383814609</v>
       </c>
@@ -1252,7 +1689,7 @@
         <v>20.0626</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4">
       <c r="A65" s="2">
         <v>777419015424748</v>
       </c>
@@ -1260,7 +1697,7 @@
         <v>20.0626</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4">
       <c r="A66" s="2">
         <v>465429582994887</v>
       </c>
@@ -1268,7 +1705,7 @@
         <v>20.0626</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4">
       <c r="A67" s="2">
         <v>79114917851687</v>
       </c>
@@ -1276,7 +1713,7 @@
         <v>20.0626</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4">
       <c r="A68" s="2" t="s">
         <v>27</v>
       </c>
@@ -1284,7 +1721,7 @@
         <v>20.0626</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4">
       <c r="A69" s="2" t="s">
         <v>28</v>
       </c>
@@ -1292,7 +1729,7 @@
         <v>20.0626</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4">
       <c r="A70" s="2">
         <v>79114362617905</v>
       </c>
@@ -1300,7 +1737,7 @@
         <v>20.0626</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4">
       <c r="A71" s="2">
         <v>79114362826221</v>
       </c>
@@ -1308,7 +1745,7 @@
         <v>20.0626</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4">
       <c r="A72" s="2">
         <v>79114362855049</v>
       </c>
@@ -1316,7 +1753,7 @@
         <v>20.0626</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4">
       <c r="A73" s="2" t="s">
         <v>29</v>
       </c>
@@ -1324,7 +1761,7 @@
         <v>20.0626</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4">
       <c r="A74" s="2">
         <v>79114716195683</v>
       </c>
@@ -1332,7 +1769,7 @@
         <v>20.0626</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4">
       <c r="A75" s="2">
         <v>465432952519118</v>
       </c>
@@ -1340,7 +1777,7 @@
         <v>20.0626</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4">
       <c r="A76" s="2" t="s">
         <v>30</v>
       </c>
@@ -1348,7 +1785,7 @@
         <v>20.0626</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4">
       <c r="A77" s="2" t="s">
         <v>31</v>
       </c>
@@ -1356,7 +1793,7 @@
         <v>20.0626</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4">
       <c r="A78" s="2" t="s">
         <v>32</v>
       </c>
@@ -1364,7 +1801,7 @@
         <v>20.0626</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4">
       <c r="A79" s="2" t="s">
         <v>33</v>
       </c>
@@ -1372,7 +1809,7 @@
         <v>20.0626</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4">
       <c r="A80" s="2">
         <v>79114362617905</v>
       </c>
@@ -1383,7 +1820,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4">
       <c r="A81" s="2">
         <v>777419015424748</v>
       </c>
@@ -1394,7 +1831,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4">
       <c r="A82" s="2">
         <v>79114302102362</v>
       </c>
@@ -1405,7 +1842,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" ht="14.4">
       <c r="A83" s="1">
         <v>79114218356055</v>
       </c>
@@ -1417,7 +1854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" ht="14.4">
       <c r="A84" s="1">
         <v>79012581856167</v>
       </c>
@@ -1429,7 +1866,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" ht="14.4">
       <c r="A85" s="1">
         <v>79114409063138</v>
       </c>
@@ -1441,7 +1878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" ht="14.4">
       <c r="A86" s="1">
         <v>79114218396909</v>
       </c>
@@ -1453,7 +1890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" ht="14.4">
       <c r="A87" s="1">
         <v>9817337232960</v>
       </c>
@@ -1465,7 +1902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" ht="14.4">
       <c r="A88" s="1">
         <v>465426605460787</v>
       </c>
@@ -1477,7 +1914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" ht="14.4">
       <c r="A89" s="3" t="s">
         <v>59</v>
       </c>
@@ -1489,7 +1926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" ht="14.4">
       <c r="A90" s="1">
         <v>79114347075820</v>
       </c>
@@ -1501,7 +1938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" ht="14.4">
       <c r="A91" s="1" t="s">
         <v>58</v>
       </c>
@@ -1513,7 +1950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" ht="14.4">
       <c r="A92" s="1" t="s">
         <v>57</v>
       </c>
@@ -1525,7 +1962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" ht="14.4">
       <c r="A93" s="1" t="s">
         <v>56</v>
       </c>
@@ -1537,7 +1974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" ht="14.4">
       <c r="A94" s="1">
         <v>79114641590826</v>
       </c>
@@ -1549,7 +1986,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" ht="14.4">
       <c r="A95" s="1" t="s">
         <v>55</v>
       </c>
@@ -1561,7 +1998,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" ht="14.4">
       <c r="A96" s="1" t="s">
         <v>53</v>
       </c>
@@ -1573,7 +2010,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" ht="14.4">
       <c r="A97" s="1" t="s">
         <v>52</v>
       </c>
@@ -1585,7 +2022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" ht="14.4">
       <c r="A98" s="1">
         <v>777419080528783</v>
       </c>
@@ -1597,7 +2034,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" ht="14.4">
       <c r="A99" s="1" t="s">
         <v>51</v>
       </c>
@@ -1609,7 +2046,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" ht="14.4">
       <c r="A100" s="1" t="s">
         <v>50</v>
       </c>
@@ -1621,7 +2058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" ht="14.4">
       <c r="A101" s="1" t="s">
         <v>49</v>
       </c>
@@ -1633,7 +2070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" ht="14.4">
       <c r="A102" s="1">
         <v>9817298550257</v>
       </c>
@@ -1645,7 +2082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" ht="14.4">
       <c r="A103" s="1">
         <v>9817338834087</v>
       </c>
@@ -1657,7 +2094,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" ht="14.4">
       <c r="A104" s="1">
         <v>79114351420184</v>
       </c>
@@ -1669,7 +2106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" ht="14.4">
       <c r="A105" s="1">
         <v>79114523941757</v>
       </c>
@@ -1681,7 +2118,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" ht="14.4">
       <c r="A106" s="1" t="s">
         <v>48</v>
       </c>
@@ -1693,7 +2130,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" ht="14.4">
       <c r="A107" s="1" t="s">
         <v>47</v>
       </c>
@@ -1705,7 +2142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" ht="14.4">
       <c r="A108" s="1" t="s">
         <v>46</v>
       </c>
@@ -1717,7 +2154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" ht="14.4">
       <c r="A109" s="1" t="s">
         <v>45</v>
       </c>
@@ -1729,7 +2166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" ht="14.4">
       <c r="A110" s="1" t="s">
         <v>44</v>
       </c>
@@ -1741,7 +2178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" ht="14.4">
       <c r="A111" s="1">
         <v>465425273153619</v>
       </c>
@@ -1753,7 +2190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" ht="14.4">
       <c r="A112" s="1" t="s">
         <v>43</v>
       </c>
@@ -1765,7 +2202,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="113" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" ht="14.4">
       <c r="A113" s="1">
         <v>79114272667800</v>
       </c>
@@ -1777,7 +2214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" ht="14.4">
       <c r="A114" s="1">
         <v>79114445687079</v>
       </c>
@@ -1789,7 +2226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" ht="14.4">
       <c r="A115" s="1">
         <v>777419340694859</v>
       </c>
@@ -1801,7 +2238,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" ht="14.4">
       <c r="A116" s="1" t="s">
         <v>42</v>
       </c>
@@ -1813,7 +2250,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" ht="14.4">
       <c r="A117" s="1">
         <v>777419197107227</v>
       </c>
@@ -1825,7 +2262,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" ht="14.4">
       <c r="A118" s="1">
         <v>777419193134582</v>
       </c>
@@ -1837,7 +2274,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" ht="14.4">
       <c r="A119" s="1">
         <v>777419149591288</v>
       </c>
@@ -1849,7 +2286,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" ht="14.4">
       <c r="A120" s="1" t="s">
         <v>41</v>
       </c>
@@ -1861,7 +2298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" ht="14.4">
       <c r="A121" s="1">
         <v>465427544369324</v>
       </c>
@@ -1873,7 +2310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" ht="14.4">
       <c r="A122" s="1" t="s">
         <v>41</v>
       </c>
@@ -1885,7 +2322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" ht="14.4">
       <c r="A123" s="1" t="s">
         <v>40</v>
       </c>
@@ -1897,7 +2334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" ht="14.4">
       <c r="A124" s="1">
         <v>435227038851000</v>
       </c>
@@ -1909,7 +2346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" ht="14.4">
       <c r="A125" s="1" t="s">
         <v>39</v>
       </c>
@@ -1921,7 +2358,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" ht="14.4">
       <c r="A126" s="1" t="s">
         <v>37</v>
       </c>
@@ -1933,7 +2370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" ht="14.4">
       <c r="A127" s="1" t="s">
         <v>36</v>
       </c>
@@ -1945,7 +2382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" ht="14.4">
       <c r="A128" s="1" t="s">
         <v>35</v>
       </c>
@@ -1957,12 +2394,667 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4">
       <c r="C129" s="1">
         <v>20.0626</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" ht="14.4">
+      <c r="A130" s="8" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" ht="14.4">
+      <c r="A131" s="9" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" ht="14.4">
+      <c r="A132" s="8" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" ht="14.4">
+      <c r="A133" s="8" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" ht="14.4">
+      <c r="A134" s="8" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" ht="14.4">
+      <c r="A135" s="8" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" ht="14.4">
+      <c r="A136" s="9" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" ht="14.4">
+      <c r="A137" s="8" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" ht="14.4">
+      <c r="A138" s="8" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" ht="14.4">
+      <c r="A139" s="8" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" ht="14.4">
+      <c r="A140" s="9" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" ht="14.4">
+      <c r="A141" s="8" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" ht="14.4">
+      <c r="A142" s="8" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" ht="14.4">
+      <c r="A143" s="8" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="14.4">
+      <c r="A144" s="8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" ht="14.4">
+      <c r="A145" s="8" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" ht="14.4">
+      <c r="A146" s="8" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" ht="14.4">
+      <c r="A147" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" ht="14.4">
+      <c r="A148" s="8" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" ht="14.4">
+      <c r="A149" s="9" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" ht="14.4">
+      <c r="A150" s="9" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" ht="14.4">
+      <c r="A151" s="8" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" ht="14.4">
+      <c r="A152" s="8" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" ht="14.4">
+      <c r="A153" s="9" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" ht="14.4">
+      <c r="A154" s="8" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" ht="14.4">
+      <c r="A155" s="8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" ht="14.4">
+      <c r="A156" s="8" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" ht="14.4">
+      <c r="A157" s="9" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" ht="14.4">
+      <c r="A158" s="9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" ht="14.4">
+      <c r="A159" s="8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" ht="14.4">
+      <c r="A160" s="9" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" ht="14.4">
+      <c r="A161" s="9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" ht="14.4">
+      <c r="A162" s="9" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" ht="14.4">
+      <c r="A163" s="8" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" ht="14.4">
+      <c r="A164" s="9" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" ht="14.4">
+      <c r="A165" s="8" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" ht="14.4">
+      <c r="A166" s="8" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" ht="14.4">
+      <c r="A167" s="8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" ht="14.4">
+      <c r="A168" s="8" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" ht="14.4">
+      <c r="A169" s="8" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" ht="14.4">
+      <c r="A170" s="9" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" ht="14.4">
+      <c r="A171" s="8" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" ht="14.4">
+      <c r="A172" s="9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" ht="14.4">
+      <c r="A173" s="8" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" ht="14.4">
+      <c r="A174" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" ht="14.4">
+      <c r="A175" s="8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" ht="14.4">
+      <c r="A176" s="8" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" ht="14.4">
+      <c r="A177" s="8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" ht="14.4">
+      <c r="A178" s="8" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" ht="14.4">
+      <c r="A179" s="9" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" ht="14.4">
+      <c r="A180" s="8" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" ht="14.4">
+      <c r="A181" s="9" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" ht="14.4">
+      <c r="A182" s="9" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" ht="14.4">
+      <c r="A183" s="9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" ht="14.4">
+      <c r="A184" s="8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" ht="14.4">
+      <c r="A185" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" ht="14.4">
+      <c r="A186" s="8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" ht="14.4">
+      <c r="A187" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" ht="14.4">
+      <c r="A188" s="9" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" ht="14.4">
+      <c r="A189" s="9" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" ht="14.4">
+      <c r="A190" s="8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" ht="14.4">
+      <c r="A191" s="8" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" ht="14.4">
+      <c r="A192" s="8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" ht="14.4">
+      <c r="A193" s="9" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" ht="14.4">
+      <c r="A194" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" ht="14.4">
+      <c r="A195" s="9" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" ht="14.4">
+      <c r="A196" s="8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" ht="14.4">
+      <c r="A197" s="8" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" ht="14.4">
+      <c r="A198" s="8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" ht="14.4">
+      <c r="A199" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" ht="14.4">
+      <c r="A200" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" ht="14.4">
+      <c r="A201" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" ht="14.4">
+      <c r="A202" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" ht="14.4">
+      <c r="A203" s="9" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" ht="14.4">
+      <c r="A204" s="8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" ht="14.4">
+      <c r="A205" s="8" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" ht="14.4">
+      <c r="A206" s="8" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" ht="14.4">
+      <c r="A207" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" ht="14.4">
+      <c r="A208" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" ht="14.4">
+      <c r="A209" s="8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" ht="14.4">
+      <c r="A210" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" ht="14.4">
+      <c r="A211" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" ht="14.4">
+      <c r="A212" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" ht="14.4">
+      <c r="A213" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" ht="14.4">
+      <c r="A214" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" ht="14.4">
+      <c r="A215" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" ht="14.4">
+      <c r="A216" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" ht="14.4">
+      <c r="A217" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" ht="14.4">
+      <c r="A218" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" ht="14.4">
+      <c r="A219" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" ht="14.4">
+      <c r="A220" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" ht="14.4">
+      <c r="A221" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" ht="14.4">
+      <c r="A222" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" ht="14.4">
+      <c r="A223" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" ht="14.4">
+      <c r="A224" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" ht="14.4">
+      <c r="A225" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" ht="14.4">
+      <c r="A226" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" ht="14.4">
+      <c r="A227" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" ht="14.4">
+      <c r="A228" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" ht="14.4">
+      <c r="A229" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" ht="14.4">
+      <c r="A230" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" ht="14.4">
+      <c r="A231" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" ht="14.4">
+      <c r="A232" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" ht="14.4">
+      <c r="A233" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" ht="14.4">
+      <c r="A234" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" ht="14.4">
+      <c r="A235" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" ht="14.4">
+      <c r="A236" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" ht="14.4">
+      <c r="A237" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" ht="14.4">
+      <c r="A238" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" ht="14.4">
+      <c r="A239" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" ht="14.4">
+      <c r="A240" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" ht="14.4">
+      <c r="A241" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" ht="14.4">
+      <c r="A242" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1" ht="14.4">
+      <c r="A243" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1" ht="14.4">
+      <c r="A244" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1" ht="14.4">
+      <c r="A245" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1" ht="14.4">
+      <c r="A246" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1" ht="14.4">
+      <c r="A247" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1" ht="14.4">
+      <c r="A248" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1" ht="14.4">
+      <c r="A249" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1" ht="14.4">
+      <c r="A250" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1" ht="14.4">
+      <c r="A251" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1" ht="14.4">
+      <c r="A252" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1" ht="14.4">
+      <c r="A253" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1" ht="14.4">
+      <c r="A254" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1" ht="14.4">
+      <c r="A255" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1" ht="14.4">
+      <c r="A256" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" ht="14.4">
+      <c r="A257" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" ht="14.4">
+      <c r="A258" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" ht="14.4">
+      <c r="A259" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3">
+      <c r="C260" s="1" t="s">
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -1974,7 +3066,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1983,7 +3075,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/on_the_way.xlsx
+++ b/on_the_way.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="274">
   <si>
     <t>Track</t>
   </si>
@@ -592,6 +592,252 @@
   </si>
   <si>
     <t>26.06.26</t>
+  </si>
+  <si>
+    <t>777422227310805</t>
+  </si>
+  <si>
+    <t>9817572476799</t>
+  </si>
+  <si>
+    <t>79117465527523</t>
+  </si>
+  <si>
+    <t>79117696250946</t>
+  </si>
+  <si>
+    <t>777421616975217</t>
+  </si>
+  <si>
+    <t>JT5499505166782</t>
+  </si>
+  <si>
+    <t>9817577879969</t>
+  </si>
+  <si>
+    <t>79117509710669</t>
+  </si>
+  <si>
+    <t>9817606613366</t>
+  </si>
+  <si>
+    <t>79117415228084</t>
+  </si>
+  <si>
+    <t>JT5499708160992</t>
+  </si>
+  <si>
+    <t>YT8881256136317</t>
+  </si>
+  <si>
+    <t>777421939569475</t>
+  </si>
+  <si>
+    <t>465450172258904</t>
+  </si>
+  <si>
+    <t>9817607428330</t>
+  </si>
+  <si>
+    <t>79117774445858</t>
+  </si>
+  <si>
+    <t>777421855554896</t>
+  </si>
+  <si>
+    <t>777422224291867</t>
+  </si>
+  <si>
+    <t>JT5499555318372</t>
+  </si>
+  <si>
+    <t>YT8881710489346</t>
+  </si>
+  <si>
+    <t>YT8881203079304</t>
+  </si>
+  <si>
+    <t>435243081637711</t>
+  </si>
+  <si>
+    <t>465459149313511</t>
+  </si>
+  <si>
+    <t>9817583571857</t>
+  </si>
+  <si>
+    <t>JT5499357097713</t>
+  </si>
+  <si>
+    <t>777422279578535</t>
+  </si>
+  <si>
+    <t>777422057138983</t>
+  </si>
+  <si>
+    <t>YT8881713805039</t>
+  </si>
+  <si>
+    <t>YT8881205713280</t>
+  </si>
+  <si>
+    <t>JT5499474471835</t>
+  </si>
+  <si>
+    <t>9817611933106</t>
+  </si>
+  <si>
+    <t>YT8881264556325</t>
+  </si>
+  <si>
+    <t>79014648854833</t>
+  </si>
+  <si>
+    <t>79117070893183</t>
+  </si>
+  <si>
+    <t>9817587676356</t>
+  </si>
+  <si>
+    <t>465459292330949</t>
+  </si>
+  <si>
+    <t>777422232180626</t>
+  </si>
+  <si>
+    <t>79117436311943</t>
+  </si>
+  <si>
+    <t>9817599918493</t>
+  </si>
+  <si>
+    <t>465457764900348</t>
+  </si>
+  <si>
+    <t>YT8881827269921</t>
+  </si>
+  <si>
+    <t>465454450241432</t>
+  </si>
+  <si>
+    <t>8258794480420</t>
+  </si>
+  <si>
+    <t>9817587706895</t>
+  </si>
+  <si>
+    <t>465451760956911</t>
+  </si>
+  <si>
+    <t>777421979396975</t>
+  </si>
+  <si>
+    <t>JT5499459270971</t>
+  </si>
+  <si>
+    <t>9817601310341</t>
+  </si>
+  <si>
+    <t>JT5499593076310</t>
+  </si>
+  <si>
+    <t>JT5499557335871</t>
+  </si>
+  <si>
+    <t>777422249209050</t>
+  </si>
+  <si>
+    <t>79117395794341</t>
+  </si>
+  <si>
+    <t>777422098989110</t>
+  </si>
+  <si>
+    <t>777421947371815</t>
+  </si>
+  <si>
+    <t>465456795812468</t>
+  </si>
+  <si>
+    <t>JT5499420492228</t>
+  </si>
+  <si>
+    <t>777422047937564</t>
+  </si>
+  <si>
+    <t>777422086167392</t>
+  </si>
+  <si>
+    <t>9817585314171</t>
+  </si>
+  <si>
+    <t>9817590201640</t>
+  </si>
+  <si>
+    <t>777422365205500</t>
+  </si>
+  <si>
+    <t>JT5499581951689</t>
+  </si>
+  <si>
+    <t>YT8881016845806</t>
+  </si>
+  <si>
+    <t>465453390178582</t>
+  </si>
+  <si>
+    <t>777421102032945</t>
+  </si>
+  <si>
+    <t>777420974852832</t>
+  </si>
+  <si>
+    <t>JT5499254571451</t>
+  </si>
+  <si>
+    <t>YT8881014957527</t>
+  </si>
+  <si>
+    <t>465448606440063</t>
+  </si>
+  <si>
+    <t>JT5499824273016</t>
+  </si>
+  <si>
+    <t>465455321353258</t>
+  </si>
+  <si>
+    <t>79116352158884</t>
+  </si>
+  <si>
+    <t>79117054093610</t>
+  </si>
+  <si>
+    <t>YT8881001428247</t>
+  </si>
+  <si>
+    <t>465453312175650</t>
+  </si>
+  <si>
+    <t>79116860524513</t>
+  </si>
+  <si>
+    <t>9817597042198</t>
+  </si>
+  <si>
+    <t>9817561906196</t>
+  </si>
+  <si>
+    <t>9817598337810</t>
+  </si>
+  <si>
+    <t>JT5498633122296</t>
+  </si>
+  <si>
+    <t>YT8880982299813</t>
+  </si>
+  <si>
+    <t>30.06.26</t>
   </si>
 </sst>
 </file>
@@ -990,7 +1236,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D260"/>
+  <dimension ref="A1:D342"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="19.77734375" style="2" customWidth="1"/>
@@ -3055,6 +3301,416 @@
     <row r="260" spans="1:3">
       <c r="C260" s="1" t="s">
         <v>191</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" ht="14.4">
+      <c r="A261" s="6" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" ht="14.4">
+      <c r="A262" s="6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" ht="14.4">
+      <c r="A263" s="4" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" ht="14.4">
+      <c r="A264" s="4" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" ht="14.4">
+      <c r="A265" s="4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" ht="14.4">
+      <c r="A266" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" ht="14.4">
+      <c r="A267" s="4" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" ht="14.4">
+      <c r="A268" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" ht="14.4">
+      <c r="A269" s="4" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" ht="14.4">
+      <c r="A270" s="4" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" ht="14.4">
+      <c r="A271" s="4" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" ht="14.4">
+      <c r="A272" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1" ht="14.4">
+      <c r="A273" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1" ht="14.4">
+      <c r="A274" s="6" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1" ht="14.4">
+      <c r="A275" s="6" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1" ht="14.4">
+      <c r="A276" s="4" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1" ht="14.4">
+      <c r="A277" s="4" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1" ht="14.4">
+      <c r="A278" s="4" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1" ht="14.4">
+      <c r="A279" s="6" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1" ht="14.4">
+      <c r="A280" s="6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1" ht="14.4">
+      <c r="A281" s="4" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1" ht="14.4">
+      <c r="A282" s="4" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1" ht="14.4">
+      <c r="A283" s="4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1" ht="14.4">
+      <c r="A284" s="4" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1" ht="14.4">
+      <c r="A285" s="4" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1" ht="14.4">
+      <c r="A286" s="6" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1" ht="14.4">
+      <c r="A287" s="4" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1" ht="14.4">
+      <c r="A288" s="4" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1" ht="14.4">
+      <c r="A289" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1" ht="14.4">
+      <c r="A290" s="4" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1" ht="14.4">
+      <c r="A291" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1" ht="14.4">
+      <c r="A292" s="6" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1" ht="14.4">
+      <c r="A293" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1" ht="14.4">
+      <c r="A294" s="4" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1" ht="14.4">
+      <c r="A295" s="6" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1" ht="14.4">
+      <c r="A296" s="4" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1" ht="14.4">
+      <c r="A297" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1" ht="14.4">
+      <c r="A298" s="4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1" ht="14.4">
+      <c r="A299" s="4" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1" ht="14.4">
+      <c r="A300" s="4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1" ht="14.4">
+      <c r="A301" s="6" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1" ht="14.4">
+      <c r="A302" s="4" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1" ht="14.4">
+      <c r="A303" s="4" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1" ht="14.4">
+      <c r="A304" s="4" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1" ht="14.4">
+      <c r="A305" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1" ht="14.4">
+      <c r="A306" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1" ht="14.4">
+      <c r="A307" s="4" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1" ht="14.4">
+      <c r="A308" s="4" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1" ht="14.4">
+      <c r="A309" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1" ht="14.4">
+      <c r="A310" s="6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1" ht="14.4">
+      <c r="A311" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1" ht="14.4">
+      <c r="A312" s="6" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1" ht="14.4">
+      <c r="A313" s="6" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1" ht="14.4">
+      <c r="A314" s="6" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1" ht="14.4">
+      <c r="A315" s="4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1" ht="14.4">
+      <c r="A316" s="4" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1" ht="14.4">
+      <c r="A317" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1" ht="14.4">
+      <c r="A318" s="4" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1" ht="14.4">
+      <c r="A319" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1" ht="14.4">
+      <c r="A320" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1" ht="14.4">
+      <c r="A321" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1" ht="14.4">
+      <c r="A322" s="6" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1" ht="14.4">
+      <c r="A323" s="6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1" ht="14.4">
+      <c r="A324" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1" ht="14.4">
+      <c r="A325" s="4" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1" ht="14.4">
+      <c r="A326" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1" ht="14.4">
+      <c r="A327" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1" ht="14.4">
+      <c r="A328" s="4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1" ht="14.4">
+      <c r="A329" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1" ht="14.4">
+      <c r="A330" s="6" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1" ht="14.4">
+      <c r="A331" s="6" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1" ht="14.4">
+      <c r="A332" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1" ht="14.4">
+      <c r="A333" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1" ht="14.4">
+      <c r="A334" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1" ht="14.4">
+      <c r="A335" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1" ht="14.4">
+      <c r="A336" s="6" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" ht="14.4">
+      <c r="A337" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" ht="14.4">
+      <c r="A338" s="4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" ht="14.4">
+      <c r="A339" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" ht="14.4">
+      <c r="A340" s="4" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" ht="14.4">
+      <c r="A341" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="B342" s="1" t="s">
+        <v>273</v>
       </c>
     </row>
   </sheetData>

--- a/on_the_way.xlsx
+++ b/on_the_way.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="309">
   <si>
     <t>Track</t>
   </si>
@@ -838,6 +838,111 @@
   </si>
   <si>
     <t>30.06.26</t>
+  </si>
+  <si>
+    <t>YT8881595284182</t>
+  </si>
+  <si>
+    <t>YT8882260952847</t>
+  </si>
+  <si>
+    <t>YT8882494776859</t>
+  </si>
+  <si>
+    <t>YT8881755208728</t>
+  </si>
+  <si>
+    <t>YT8881657240525</t>
+  </si>
+  <si>
+    <t>YT8882144681960</t>
+  </si>
+  <si>
+    <t>JT5500131975712</t>
+  </si>
+  <si>
+    <t>YT8881755210383</t>
+  </si>
+  <si>
+    <t>YT8881755208849</t>
+  </si>
+  <si>
+    <t>YT8882396047152</t>
+  </si>
+  <si>
+    <t>JT5499595952076</t>
+  </si>
+  <si>
+    <t>YT8882309071744</t>
+  </si>
+  <si>
+    <t>JT5500220106336</t>
+  </si>
+  <si>
+    <t>YT8882440004894</t>
+  </si>
+  <si>
+    <t>JT5499973731091</t>
+  </si>
+  <si>
+    <t>JT5500042212292</t>
+  </si>
+  <si>
+    <t>JT5500386588411</t>
+  </si>
+  <si>
+    <t>JT5500705303808</t>
+  </si>
+  <si>
+    <t>YT8881664761417</t>
+  </si>
+  <si>
+    <t>YT8882023690124</t>
+  </si>
+  <si>
+    <t>YT8881965706708</t>
+  </si>
+  <si>
+    <t>YT8882049235336</t>
+  </si>
+  <si>
+    <t>JT5500085421454</t>
+  </si>
+  <si>
+    <t>YT8881981266714</t>
+  </si>
+  <si>
+    <t>YT8882084279009</t>
+  </si>
+  <si>
+    <t>JT5500709369606</t>
+  </si>
+  <si>
+    <t>YT8882331018326</t>
+  </si>
+  <si>
+    <t>YT8881923064217</t>
+  </si>
+  <si>
+    <t>JT5500171686135</t>
+  </si>
+  <si>
+    <t>JT5500642188425</t>
+  </si>
+  <si>
+    <t>YT8882082598760</t>
+  </si>
+  <si>
+    <t>YT8882105763850</t>
+  </si>
+  <si>
+    <t>SF5112110102446</t>
+  </si>
+  <si>
+    <t>YT8881876085352</t>
+  </si>
+  <si>
+    <t>2.07.26</t>
   </si>
 </sst>
 </file>
@@ -1236,7 +1341,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D342"/>
+  <dimension ref="A1:D435"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="19.77734375" style="2" customWidth="1"/>
@@ -3711,6 +3816,471 @@
     <row r="342" spans="1:2">
       <c r="B342" s="1" t="s">
         <v>273</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" ht="14.4">
+      <c r="A343" s="1">
+        <v>777421971309997</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" ht="14.4">
+      <c r="A344" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" ht="14.4">
+      <c r="A345" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" ht="14.4">
+      <c r="A346" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" ht="14.4">
+      <c r="A347" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" ht="14.4">
+      <c r="A348" s="1">
+        <v>79117952924235</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" ht="14.4">
+      <c r="A349" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" ht="14.4">
+      <c r="A350" s="1">
+        <v>465458300612210</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" ht="14.4">
+      <c r="A351" s="1">
+        <v>465462997566968</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" ht="14.4">
+      <c r="A352" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1" ht="14.4">
+      <c r="A353" s="1">
+        <v>9817637752976</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1" ht="14.4">
+      <c r="A354" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1" ht="14.4">
+      <c r="A355" s="1">
+        <v>777422386231741</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1" ht="14.4">
+      <c r="A356" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1" ht="14.4">
+      <c r="A357" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1" ht="14.4">
+      <c r="A358" s="1">
+        <v>777422549883964</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1" ht="14.4">
+      <c r="A359" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1" ht="14.4">
+      <c r="A360" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1" ht="14.4">
+      <c r="A361" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1" ht="14.4">
+      <c r="A362" s="1">
+        <v>777422741197359</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1" ht="14.4">
+      <c r="A363" s="1" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1" ht="14.4">
+      <c r="A364" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1" ht="14.4">
+      <c r="A365" s="1">
+        <v>79117641603383</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1" ht="14.4">
+      <c r="A366" s="1">
+        <v>777422423684474</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1" ht="14.4">
+      <c r="A367" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1" ht="14.4">
+      <c r="A368" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1" ht="14.4">
+      <c r="A369" s="1">
+        <v>79117947325687</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1" ht="14.4">
+      <c r="A370" s="1">
+        <v>777422657466151</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1" ht="14.4">
+      <c r="A371" s="1">
+        <v>79118115286962</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1" ht="14.4">
+      <c r="A372" s="1">
+        <v>465458348367580</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1" ht="14.4">
+      <c r="A373" s="1">
+        <v>465464907314970</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1" ht="14.4">
+      <c r="A374" s="1">
+        <v>777422134424763</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1" ht="14.4">
+      <c r="A375" s="1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="376" spans="1:1" ht="14.4">
+      <c r="A376" s="1">
+        <v>9817706152080</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1" ht="14.4">
+      <c r="A377" s="1">
+        <v>9817641420345</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1" ht="14.4">
+      <c r="A378" s="1">
+        <v>9817618218214</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1" ht="14.4">
+      <c r="A379" s="1">
+        <v>777422513725104</v>
+      </c>
+    </row>
+    <row r="380" spans="1:1" ht="14.4">
+      <c r="A380" s="1">
+        <v>79118024749653</v>
+      </c>
+    </row>
+    <row r="381" spans="1:1" ht="14.4">
+      <c r="A381" s="1">
+        <v>777422657905926</v>
+      </c>
+    </row>
+    <row r="382" spans="1:1" ht="14.4">
+      <c r="A382" s="1">
+        <v>777423203000463</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1" ht="14.4">
+      <c r="A383" s="1">
+        <v>777422413035587</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1" ht="14.4">
+      <c r="A384" s="1">
+        <v>79117818077517</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1" ht="14.4">
+      <c r="A385" s="1">
+        <v>777422517419094</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1" ht="14.4">
+      <c r="A386" s="1">
+        <v>9817699670146</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1" ht="14.4">
+      <c r="A387" s="1">
+        <v>9817626176674</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1" ht="14.4">
+      <c r="A388" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="389" spans="1:1" ht="14.4">
+      <c r="A389" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1" ht="14.4">
+      <c r="A390" s="1">
+        <v>465464033007149</v>
+      </c>
+    </row>
+    <row r="391" spans="1:1" ht="14.4">
+      <c r="A391" s="1">
+        <v>9817684175880</v>
+      </c>
+    </row>
+    <row r="392" spans="1:1" ht="14.4">
+      <c r="A392" s="1">
+        <v>9817638532752</v>
+      </c>
+    </row>
+    <row r="393" spans="1:1" ht="14.4">
+      <c r="A393" s="1">
+        <v>79117975994426</v>
+      </c>
+    </row>
+    <row r="394" spans="1:1" ht="14.4">
+      <c r="A394" s="1">
+        <v>777422279037036</v>
+      </c>
+    </row>
+    <row r="395" spans="1:1" ht="14.4">
+      <c r="A395" s="1">
+        <v>465460191668107</v>
+      </c>
+    </row>
+    <row r="396" spans="1:1" ht="14.4">
+      <c r="A396" s="1">
+        <v>465458538755029</v>
+      </c>
+    </row>
+    <row r="397" spans="1:1" ht="14.4">
+      <c r="A397" s="1">
+        <v>9817633727498</v>
+      </c>
+    </row>
+    <row r="398" spans="1:1" ht="14.4">
+      <c r="A398" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="399" spans="1:1" ht="14.4">
+      <c r="A399" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="400" spans="1:1" ht="14.4">
+      <c r="A400" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="401" spans="1:1" ht="14.4">
+      <c r="A401" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="402" spans="1:1" ht="14.4">
+      <c r="A402" s="1">
+        <v>79118367685893</v>
+      </c>
+    </row>
+    <row r="403" spans="1:1" ht="14.4">
+      <c r="A403" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="404" spans="1:1" ht="14.4">
+      <c r="A404" s="1">
+        <v>9817700621226</v>
+      </c>
+    </row>
+    <row r="405" spans="1:1" ht="14.4">
+      <c r="A405" s="1">
+        <v>79117796071346</v>
+      </c>
+    </row>
+    <row r="406" spans="1:1" ht="14.4">
+      <c r="A406" s="1">
+        <v>465457962486311</v>
+      </c>
+    </row>
+    <row r="407" spans="1:1" ht="14.4">
+      <c r="A407" s="1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="408" spans="1:1" ht="14.4">
+      <c r="A408" s="1">
+        <v>777422731528745</v>
+      </c>
+    </row>
+    <row r="409" spans="1:1" ht="14.4">
+      <c r="A409" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="410" spans="1:1" ht="14.4">
+      <c r="A410" s="1">
+        <v>465462045052132</v>
+      </c>
+    </row>
+    <row r="411" spans="1:1" ht="14.4">
+      <c r="A411" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="412" spans="1:1" ht="14.4">
+      <c r="A412" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="413" spans="1:1" ht="14.4">
+      <c r="A413" s="1">
+        <v>777422556482984</v>
+      </c>
+    </row>
+    <row r="414" spans="1:1" ht="14.4">
+      <c r="A414" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="415" spans="1:1" ht="14.4">
+      <c r="A415" s="1">
+        <v>465464224986141</v>
+      </c>
+    </row>
+    <row r="416" spans="1:1" ht="14.4">
+      <c r="A416" s="1">
+        <v>465461539296139</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1" ht="14.4">
+      <c r="A417" s="1">
+        <v>777422770801355</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1" ht="14.4">
+      <c r="A418" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="419" spans="1:1" ht="14.4">
+      <c r="A419" s="1">
+        <v>777423239248503</v>
+      </c>
+    </row>
+    <row r="420" spans="1:1" ht="14.4">
+      <c r="A420" s="1">
+        <v>79117651536910</v>
+      </c>
+    </row>
+    <row r="421" spans="1:1" ht="14.4">
+      <c r="A421" s="1">
+        <v>79117933681198</v>
+      </c>
+    </row>
+    <row r="422" spans="1:1" ht="14.4">
+      <c r="A422" s="1">
+        <v>9817627085660</v>
+      </c>
+    </row>
+    <row r="423" spans="1:1" ht="14.4">
+      <c r="A423" s="1">
+        <v>777422282995768</v>
+      </c>
+    </row>
+    <row r="424" spans="1:1" ht="14.4">
+      <c r="A424" s="1" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="425" spans="1:1" ht="14.4">
+      <c r="A425" s="1">
+        <v>777423239698605</v>
+      </c>
+    </row>
+    <row r="426" spans="1:1" ht="14.4">
+      <c r="A426" s="1">
+        <v>465465103750961</v>
+      </c>
+    </row>
+    <row r="427" spans="1:1" ht="14.4">
+      <c r="A427" s="1">
+        <v>9817620085910</v>
+      </c>
+    </row>
+    <row r="428" spans="1:1" ht="14.4">
+      <c r="A428" s="1">
+        <v>465457413048475</v>
+      </c>
+    </row>
+    <row r="429" spans="1:1" ht="14.4">
+      <c r="A429" s="1">
+        <v>465456211470405</v>
+      </c>
+    </row>
+    <row r="430" spans="1:1" ht="14.4">
+      <c r="A430" s="1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="431" spans="1:1" ht="14.4">
+      <c r="A431" s="1">
+        <v>465464532957747</v>
+      </c>
+    </row>
+    <row r="432" spans="1:1" ht="14.4">
+      <c r="A432" s="1">
+        <v>777423140486346</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2" ht="14.4">
+      <c r="A433" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2" ht="14.4">
+      <c r="A434" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2">
+      <c r="B435" s="1" t="s">
+        <v>308</v>
       </c>
     </row>
   </sheetData>

--- a/on_the_way.xlsx
+++ b/on_the_way.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="514">
   <si>
     <t>Track</t>
   </si>
@@ -1024,6 +1024,540 @@
   </si>
   <si>
     <t>777423269005541</t>
+  </si>
+  <si>
+    <t>777424220162412</t>
+  </si>
+  <si>
+    <t>465479229384518</t>
+  </si>
+  <si>
+    <t>9817874570506</t>
+  </si>
+  <si>
+    <t>777424361174079</t>
+  </si>
+  <si>
+    <t>465476500993347</t>
+  </si>
+  <si>
+    <t>777424993812033</t>
+  </si>
+  <si>
+    <t>79119513045156</t>
+  </si>
+  <si>
+    <t>YT8883447163830</t>
+  </si>
+  <si>
+    <t>JT5502797492566</t>
+  </si>
+  <si>
+    <t>79120018634046</t>
+  </si>
+  <si>
+    <t>79120328238119</t>
+  </si>
+  <si>
+    <t>9817726240838</t>
+  </si>
+  <si>
+    <t>777424168124852</t>
+  </si>
+  <si>
+    <t>JT3169425015783</t>
+  </si>
+  <si>
+    <t>YT8884258229922</t>
+  </si>
+  <si>
+    <t>YT8884120626190</t>
+  </si>
+  <si>
+    <t>465482477918590</t>
+  </si>
+  <si>
+    <t>777424241079598</t>
+  </si>
+  <si>
+    <t>79016630818351</t>
+  </si>
+  <si>
+    <t>79120061484942</t>
+  </si>
+  <si>
+    <t>465478784045939</t>
+  </si>
+  <si>
+    <t>YT8884426509513</t>
+  </si>
+  <si>
+    <t>9817842086178</t>
+  </si>
+  <si>
+    <t>9817824222503</t>
+  </si>
+  <si>
+    <t>9817744360683</t>
+  </si>
+  <si>
+    <t>9817833357257</t>
+  </si>
+  <si>
+    <t>79119680373126</t>
+  </si>
+  <si>
+    <t>777424953542826</t>
+  </si>
+  <si>
+    <t>JT5502038877683</t>
+  </si>
+  <si>
+    <t>JT5502586459458</t>
+  </si>
+  <si>
+    <t>777424563328445</t>
+  </si>
+  <si>
+    <t>9817783262947</t>
+  </si>
+  <si>
+    <t>JT5501949529727</t>
+  </si>
+  <si>
+    <t>YT8883889378511</t>
+  </si>
+  <si>
+    <t>465480494417993</t>
+  </si>
+  <si>
+    <t>JT5502803401712</t>
+  </si>
+  <si>
+    <t>YT8884389671506</t>
+  </si>
+  <si>
+    <t>9817802550951</t>
+  </si>
+  <si>
+    <t>JT9001357075546</t>
+  </si>
+  <si>
+    <t>9817817233388</t>
+  </si>
+  <si>
+    <t>79119353172438</t>
+  </si>
+  <si>
+    <t>79120038283526</t>
+  </si>
+  <si>
+    <t>79119416390403</t>
+  </si>
+  <si>
+    <t>JT5502063985498</t>
+  </si>
+  <si>
+    <t>9817817261348</t>
+  </si>
+  <si>
+    <t>777424230198347</t>
+  </si>
+  <si>
+    <t>79120384923273</t>
+  </si>
+  <si>
+    <t>9817814907148</t>
+  </si>
+  <si>
+    <t>79119699371877</t>
+  </si>
+  <si>
+    <t>79119373863903</t>
+  </si>
+  <si>
+    <t>79016454897614</t>
+  </si>
+  <si>
+    <t>465478907911956</t>
+  </si>
+  <si>
+    <t>79119682173315</t>
+  </si>
+  <si>
+    <t>9817833727780</t>
+  </si>
+  <si>
+    <t>YT8883932774068</t>
+  </si>
+  <si>
+    <t>79119364223825</t>
+  </si>
+  <si>
+    <t>JT5502750696507</t>
+  </si>
+  <si>
+    <t>JT5502253986072</t>
+  </si>
+  <si>
+    <t>79119623086735</t>
+  </si>
+  <si>
+    <t>JT5502741718081</t>
+  </si>
+  <si>
+    <t>777424342650506</t>
+  </si>
+  <si>
+    <t>465481632912782</t>
+  </si>
+  <si>
+    <t>79119333092366</t>
+  </si>
+  <si>
+    <t>9817844495105</t>
+  </si>
+  <si>
+    <t>79119902597646</t>
+  </si>
+  <si>
+    <t>79119935578123</t>
+  </si>
+  <si>
+    <t>YT8884336503775</t>
+  </si>
+  <si>
+    <t>79120061027112</t>
+  </si>
+  <si>
+    <t>465478890570558</t>
+  </si>
+  <si>
+    <t>JT5502695633268</t>
+  </si>
+  <si>
+    <t>YT8883878678840</t>
+  </si>
+  <si>
+    <t>465470049614367</t>
+  </si>
+  <si>
+    <t>465473534442564</t>
+  </si>
+  <si>
+    <t>79120332036445</t>
+  </si>
+  <si>
+    <t>JT5503266812933</t>
+  </si>
+  <si>
+    <t>465480645383240</t>
+  </si>
+  <si>
+    <t>777423826557941</t>
+  </si>
+  <si>
+    <t>JT5502515695069</t>
+  </si>
+  <si>
+    <t>777424752557155</t>
+  </si>
+  <si>
+    <t>465471994471730</t>
+  </si>
+  <si>
+    <t>JT5502070896573</t>
+  </si>
+  <si>
+    <t>YT8884117072986</t>
+  </si>
+  <si>
+    <t>JT5502298396291</t>
+  </si>
+  <si>
+    <t>777424713674098</t>
+  </si>
+  <si>
+    <t>777423993882325</t>
+  </si>
+  <si>
+    <t>YT8883878440548</t>
+  </si>
+  <si>
+    <t>JT5502242836349</t>
+  </si>
+  <si>
+    <t>YT8884489615042</t>
+  </si>
+  <si>
+    <t>JT5502396965926</t>
+  </si>
+  <si>
+    <t>JT5502578278301</t>
+  </si>
+  <si>
+    <t>JT5502224005826</t>
+  </si>
+  <si>
+    <t>465469564298701</t>
+  </si>
+  <si>
+    <t>465476542484994</t>
+  </si>
+  <si>
+    <t>777424019456798</t>
+  </si>
+  <si>
+    <t>465478695635802</t>
+  </si>
+  <si>
+    <t>79119334943698</t>
+  </si>
+  <si>
+    <t>YT8883891190132</t>
+  </si>
+  <si>
+    <t>777423915519907</t>
+  </si>
+  <si>
+    <t>777424450392984</t>
+  </si>
+  <si>
+    <t>JT5502579705752</t>
+  </si>
+  <si>
+    <t>YT8883903450609</t>
+  </si>
+  <si>
+    <t>465478836046637</t>
+  </si>
+  <si>
+    <t>YT8883595470376</t>
+  </si>
+  <si>
+    <t>465475481375138</t>
+  </si>
+  <si>
+    <t>777423955269542</t>
+  </si>
+  <si>
+    <t>79118705036709</t>
+  </si>
+  <si>
+    <t>YT8883410575516</t>
+  </si>
+  <si>
+    <t>9817726965432</t>
+  </si>
+  <si>
+    <t>79119122374228</t>
+  </si>
+  <si>
+    <t>79119161828030</t>
+  </si>
+  <si>
+    <t>777423648422955</t>
+  </si>
+  <si>
+    <t>777423009363641</t>
+  </si>
+  <si>
+    <t>JT5501372942277</t>
+  </si>
+  <si>
+    <t>JT5501532764591</t>
+  </si>
+  <si>
+    <t>777423677128532</t>
+  </si>
+  <si>
+    <t>465472391693106</t>
+  </si>
+  <si>
+    <t>777422996731755</t>
+  </si>
+  <si>
+    <t>JT5501532535801</t>
+  </si>
+  <si>
+    <t>777423745466795</t>
+  </si>
+  <si>
+    <t>777423767375582</t>
+  </si>
+  <si>
+    <t>465472002832188</t>
+  </si>
+  <si>
+    <t>YT8883674598074</t>
+  </si>
+  <si>
+    <t>465471732331470</t>
+  </si>
+  <si>
+    <t>YT8882580605650</t>
+  </si>
+  <si>
+    <t>465472312616126</t>
+  </si>
+  <si>
+    <t>YT8883239639732</t>
+  </si>
+  <si>
+    <t>JT5501302513659</t>
+  </si>
+  <si>
+    <t>777422837209675</t>
+  </si>
+  <si>
+    <t>777424099932425</t>
+  </si>
+  <si>
+    <t>YT8882970307102</t>
+  </si>
+  <si>
+    <t>JT5501077523127</t>
+  </si>
+  <si>
+    <t>9817736381529</t>
+  </si>
+  <si>
+    <t>777423571387306</t>
+  </si>
+  <si>
+    <t>YT8882892016005</t>
+  </si>
+  <si>
+    <t>777424007430464</t>
+  </si>
+  <si>
+    <t>777423875081346</t>
+  </si>
+  <si>
+    <t>465473412612728</t>
+  </si>
+  <si>
+    <t>777423532876975</t>
+  </si>
+  <si>
+    <t>777424092833669</t>
+  </si>
+  <si>
+    <t>YT8883742931987</t>
+  </si>
+  <si>
+    <t>79119299656526</t>
+  </si>
+  <si>
+    <t>9817780091264</t>
+  </si>
+  <si>
+    <t>YT8883626255907</t>
+  </si>
+  <si>
+    <t>465475448112441</t>
+  </si>
+  <si>
+    <t>JT5501299359983</t>
+  </si>
+  <si>
+    <t>79119137632359</t>
+  </si>
+  <si>
+    <t>777424114810896</t>
+  </si>
+  <si>
+    <t>9817653521677</t>
+  </si>
+  <si>
+    <t>777424572515165</t>
+  </si>
+  <si>
+    <t>JT5502597241614</t>
+  </si>
+  <si>
+    <t>79118979425089</t>
+  </si>
+  <si>
+    <t>79118833080186</t>
+  </si>
+  <si>
+    <t>YT8882874480068</t>
+  </si>
+  <si>
+    <t>JT5501535601748</t>
+  </si>
+  <si>
+    <t>9817769911867</t>
+  </si>
+  <si>
+    <t>9817753460786</t>
+  </si>
+  <si>
+    <t>YT8883849849679</t>
+  </si>
+  <si>
+    <t>9817784576370</t>
+  </si>
+  <si>
+    <t>9817605081138</t>
+  </si>
+  <si>
+    <t>YT8883723028714</t>
+  </si>
+  <si>
+    <t>79119050833173</t>
+  </si>
+  <si>
+    <t>79119471430708</t>
+  </si>
+  <si>
+    <t>9817751874305</t>
+  </si>
+  <si>
+    <t>79119089277103</t>
+  </si>
+  <si>
+    <t>9817718946799</t>
+  </si>
+  <si>
+    <t>79119327158321</t>
+  </si>
+  <si>
+    <t>79119040950183</t>
+  </si>
+  <si>
+    <t>YT8883182286722</t>
+  </si>
+  <si>
+    <t>79118908516350</t>
+  </si>
+  <si>
+    <t>465475730266001</t>
+  </si>
+  <si>
+    <t>79119115957783</t>
+  </si>
+  <si>
+    <t>YT8883049444988</t>
+  </si>
+  <si>
+    <t>465460557466698</t>
+  </si>
+  <si>
+    <t>777423791434285</t>
+  </si>
+  <si>
+    <t>777423766456070</t>
+  </si>
+  <si>
+    <t>JT5501371556169</t>
+  </si>
+  <si>
+    <t>465472981439634</t>
+  </si>
+  <si>
+    <t>79118824420191</t>
   </si>
 </sst>
 </file>
@@ -1638,7 +2172,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D513"/>
+  <dimension ref="A1:D771"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="19.77734375" style="2" customWidth="1"/>
@@ -4590,6 +5124,1296 @@
     <row r="513" spans="1:1" ht="14.4">
       <c r="A513" s="10" t="s">
         <v>288</v>
+      </c>
+    </row>
+    <row r="514" spans="1:1" ht="14.4">
+      <c r="A514" s="10" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="515" spans="1:1" ht="14.4">
+      <c r="A515" s="9" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="516" spans="1:1" ht="14.4">
+      <c r="A516" s="9" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="517" spans="1:1" ht="14.4">
+      <c r="A517" s="9" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="518" spans="1:1" ht="14.4">
+      <c r="A518" s="10" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="519" spans="1:1" ht="14.4">
+      <c r="A519" s="10" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="520" spans="1:1" ht="14.4">
+      <c r="A520" s="10" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="521" spans="1:1" ht="14.4">
+      <c r="A521" s="10" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="522" spans="1:1" ht="14.4">
+      <c r="A522" s="10" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="523" spans="1:1" ht="14.4">
+      <c r="A523" s="10" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="524" spans="1:1" ht="14.4">
+      <c r="A524" s="9" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="525" spans="1:1" ht="14.4">
+      <c r="A525" s="10" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="526" spans="1:1" ht="14.4">
+      <c r="A526" s="10" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="527" spans="1:1" ht="14.4">
+      <c r="A527" s="10" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="528" spans="1:1" ht="14.4">
+      <c r="A528" s="10" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="529" spans="1:1" ht="14.4">
+      <c r="A529" s="10" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="530" spans="1:1" ht="14.4">
+      <c r="A530" s="9" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="531" spans="1:1" ht="14.4">
+      <c r="A531" s="10" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="532" spans="1:1" ht="14.4">
+      <c r="A532" s="9" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="533" spans="1:1" ht="14.4">
+      <c r="A533" s="9" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="534" spans="1:1" ht="14.4">
+      <c r="A534" s="10" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="535" spans="1:1" ht="14.4">
+      <c r="A535" s="10" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="536" spans="1:1" ht="14.4">
+      <c r="A536" s="9" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="537" spans="1:1" ht="14.4">
+      <c r="A537" s="9" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="538" spans="1:1" ht="14.4">
+      <c r="A538" s="10" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="539" spans="1:1" ht="14.4">
+      <c r="A539" s="9" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="540" spans="1:1" ht="14.4">
+      <c r="A540" s="9" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="541" spans="1:1" ht="14.4">
+      <c r="A541" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="542" spans="1:1" ht="14.4">
+      <c r="A542" s="9" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="543" spans="1:1" ht="14.4">
+      <c r="A543" s="10" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="544" spans="1:1" ht="14.4">
+      <c r="A544" s="9" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="545" spans="1:1" ht="14.4">
+      <c r="A545" s="10" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="546" spans="1:1" ht="14.4">
+      <c r="A546" s="10" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="547" spans="1:1" ht="14.4">
+      <c r="A547" s="10" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="548" spans="1:1" ht="14.4">
+      <c r="A548" s="10" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="549" spans="1:1" ht="14.4">
+      <c r="A549" s="10" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="550" spans="1:1" ht="14.4">
+      <c r="A550" s="10" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="551" spans="1:1" ht="14.4">
+      <c r="A551" s="10" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="552" spans="1:1" ht="14.4">
+      <c r="A552" s="10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="553" spans="1:1" ht="14.4">
+      <c r="A553" s="10" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="554" spans="1:1" ht="14.4">
+      <c r="A554" s="10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="555" spans="1:1" ht="14.4">
+      <c r="A555" s="10" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="556" spans="1:1" ht="14.4">
+      <c r="A556" s="10" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="557" spans="1:1" ht="14.4">
+      <c r="A557" s="10" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="558" spans="1:1" ht="14.4">
+      <c r="A558" s="10" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="559" spans="1:1" ht="14.4">
+      <c r="A559" s="10" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="560" spans="1:1" ht="14.4">
+      <c r="A560" s="10" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="561" spans="1:1" ht="14.4">
+      <c r="A561" s="10" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="562" spans="1:1" ht="14.4">
+      <c r="A562" s="9" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="563" spans="1:1" ht="14.4">
+      <c r="A563" s="9" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="564" spans="1:1" ht="14.4">
+      <c r="A564" s="10" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="565" spans="1:1" ht="14.4">
+      <c r="A565" s="10" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="566" spans="1:1" ht="14.4">
+      <c r="A566" s="9" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="567" spans="1:1" ht="14.4">
+      <c r="A567" s="10" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="568" spans="1:1" ht="14.4">
+      <c r="A568" s="9" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="569" spans="1:1" ht="14.4">
+      <c r="A569" s="9" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="570" spans="1:1" ht="14.4">
+      <c r="A570" s="10" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="571" spans="1:1" ht="14.4">
+      <c r="A571" s="9" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="572" spans="1:1" ht="14.4">
+      <c r="A572" s="10" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="573" spans="1:1" ht="14.4">
+      <c r="A573" s="9" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="574" spans="1:1" ht="14.4">
+      <c r="A574" s="9" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="575" spans="1:1" ht="14.4">
+      <c r="A575" s="9" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="576" spans="1:1" ht="14.4">
+      <c r="A576" s="9" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="577" spans="1:1" ht="14.4">
+      <c r="A577" s="10" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="578" spans="1:1" ht="14.4">
+      <c r="A578" s="9" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="579" spans="1:1" ht="14.4">
+      <c r="A579" s="10" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="580" spans="1:1" ht="14.4">
+      <c r="A580" s="10" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="581" spans="1:1" ht="14.4">
+      <c r="A581" s="10" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="582" spans="1:1" ht="14.4">
+      <c r="A582" s="10" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="583" spans="1:1" ht="14.4">
+      <c r="A583" s="10" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="584" spans="1:1" ht="14.4">
+      <c r="A584" s="10" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="585" spans="1:1" ht="14.4">
+      <c r="A585" s="10" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="586" spans="1:1" ht="14.4">
+      <c r="A586" s="10" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="587" spans="1:1" ht="14.4">
+      <c r="A587" s="10" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="588" spans="1:1" ht="14.4">
+      <c r="A588" s="9" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="589" spans="1:1" ht="14.4">
+      <c r="A589" s="10" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="590" spans="1:1" ht="14.4">
+      <c r="A590" s="10" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="591" spans="1:1" ht="14.4">
+      <c r="A591" s="10" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="592" spans="1:1" ht="14.4">
+      <c r="A592" s="10" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="593" spans="1:1" ht="14.4">
+      <c r="A593" s="10" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="594" spans="1:1" ht="14.4">
+      <c r="A594" s="9" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="595" spans="1:1" ht="14.4">
+      <c r="A595" s="10" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="596" spans="1:1" ht="14.4">
+      <c r="A596" s="10" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="597" spans="1:1" ht="14.4">
+      <c r="A597" s="10" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="598" spans="1:1" ht="14.4">
+      <c r="A598" s="9" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="599" spans="1:1" ht="14.4">
+      <c r="A599" s="10" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="600" spans="1:1" ht="14.4">
+      <c r="A600" s="10" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="601" spans="1:1" ht="14.4">
+      <c r="A601" s="10" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="602" spans="1:1" ht="14.4">
+      <c r="A602" s="9" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="603" spans="1:1" ht="14.4">
+      <c r="A603" s="10" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="604" spans="1:1" ht="14.4">
+      <c r="A604" s="10" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="605" spans="1:1" ht="14.4">
+      <c r="A605" s="10" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="606" spans="1:1" ht="14.4">
+      <c r="A606" s="10" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="607" spans="1:1" ht="14.4">
+      <c r="A607" s="10" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="608" spans="1:1" ht="14.4">
+      <c r="A608" s="10" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="609" spans="1:1" ht="14.4">
+      <c r="A609" s="10" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="610" spans="1:1" ht="14.4">
+      <c r="A610" s="9" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="611" spans="1:1" ht="14.4">
+      <c r="A611" s="10" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="612" spans="1:1" ht="14.4">
+      <c r="A612" s="10" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="613" spans="1:1" ht="14.4">
+      <c r="A613" s="9" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="614" spans="1:1" ht="14.4">
+      <c r="A614" s="10" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="615" spans="1:1" ht="14.4">
+      <c r="A615" s="10" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="616" spans="1:1" ht="14.4">
+      <c r="A616" s="9" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="617" spans="1:1" ht="14.4">
+      <c r="A617" s="9" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="618" spans="1:1" ht="14.4">
+      <c r="A618" s="10" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="619" spans="1:1" ht="14.4">
+      <c r="A619" s="10" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="620" spans="1:1" ht="14.4">
+      <c r="A620" s="9" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="621" spans="1:1" ht="14.4">
+      <c r="A621" s="10" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="622" spans="1:1" ht="14.4">
+      <c r="A622" s="10" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="623" spans="1:1" ht="14.4">
+      <c r="A623" s="10" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="624" spans="1:1" ht="14.4">
+      <c r="A624" s="10" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="625" spans="1:1" ht="14.4">
+      <c r="A625" s="9" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="626" spans="1:1" ht="14.4">
+      <c r="A626" s="10" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="627" spans="1:1" ht="14.4">
+      <c r="A627" s="9" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="628" spans="1:1" ht="14.4">
+      <c r="A628" s="10" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="629" spans="1:1" ht="14.4">
+      <c r="A629" s="10" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="630" spans="1:1" ht="14.4">
+      <c r="A630" s="9" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="631" spans="1:1" ht="14.4">
+      <c r="A631" s="10" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="632" spans="1:1" ht="14.4">
+      <c r="A632" s="10" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="633" spans="1:1" ht="14.4">
+      <c r="A633" s="10" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="634" spans="1:1" ht="14.4">
+      <c r="A634" s="10" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="635" spans="1:1" ht="14.4">
+      <c r="A635" s="10" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="636" spans="1:1" ht="14.4">
+      <c r="A636" s="9" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="637" spans="1:1" ht="14.4">
+      <c r="A637" s="10" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="638" spans="1:1" ht="14.4">
+      <c r="A638" s="10" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="639" spans="1:1" ht="14.4">
+      <c r="A639" s="9" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="640" spans="1:1" ht="14.4">
+      <c r="A640" s="9" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="641" spans="1:1" ht="14.4">
+      <c r="A641" s="10" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="642" spans="1:1" ht="14.4">
+      <c r="A642" s="10" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="643" spans="1:1" ht="14.4">
+      <c r="A643" s="9" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="644" spans="1:1" ht="14.4">
+      <c r="A644" s="9" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="645" spans="1:1" ht="14.4">
+      <c r="A645" s="10" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="646" spans="1:1" ht="14.4">
+      <c r="A646" s="9" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="647" spans="1:1" ht="14.4">
+      <c r="A647" s="10" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="648" spans="1:1" ht="14.4">
+      <c r="A648" s="9" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="649" spans="1:1" ht="14.4">
+      <c r="A649" s="10" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="650" spans="1:1" ht="14.4">
+      <c r="A650" s="10" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="651" spans="1:1" ht="14.4">
+      <c r="A651" s="10" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="652" spans="1:1" ht="14.4">
+      <c r="A652" s="9" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="653" spans="1:1" ht="14.4">
+      <c r="A653" s="10" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="654" spans="1:1" ht="14.4">
+      <c r="A654" s="10" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="655" spans="1:1" ht="14.4">
+      <c r="A655" s="10" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="656" spans="1:1" ht="14.4">
+      <c r="A656" s="9" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="657" spans="1:1" ht="14.4">
+      <c r="A657" s="9" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="658" spans="1:1" ht="14.4">
+      <c r="A658" s="10" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="659" spans="1:1" ht="14.4">
+      <c r="A659" s="10" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="660" spans="1:1" ht="14.4">
+      <c r="A660" s="10" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="661" spans="1:1" ht="14.4">
+      <c r="A661" s="10" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="662" spans="1:1" ht="14.4">
+      <c r="A662" s="10" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="663" spans="1:1" ht="14.4">
+      <c r="A663" s="9" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="664" spans="1:1" ht="14.4">
+      <c r="A664" s="10" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="665" spans="1:1" ht="14.4">
+      <c r="A665" s="10" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="666" spans="1:1" ht="14.4">
+      <c r="A666" s="10" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="667" spans="1:1" ht="14.4">
+      <c r="A667" s="9" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="668" spans="1:1" ht="14.4">
+      <c r="A668" s="10" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="669" spans="1:1" ht="14.4">
+      <c r="A669" s="10" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="670" spans="1:1" ht="14.4">
+      <c r="A670" s="10" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="671" spans="1:1" ht="14.4">
+      <c r="A671" s="9" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="672" spans="1:1" ht="14.4">
+      <c r="A672" s="9" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="673" spans="1:1" ht="14.4">
+      <c r="A673" s="10" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="674" spans="1:1" ht="14.4">
+      <c r="A674" s="10" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="675" spans="1:1" ht="14.4">
+      <c r="A675" s="9" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="676" spans="1:1" ht="14.4">
+      <c r="A676" s="10" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="677" spans="1:1" ht="14.4">
+      <c r="A677" s="10" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="678" spans="1:1" ht="14.4">
+      <c r="A678" s="10" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="679" spans="1:1" ht="14.4">
+      <c r="A679" s="10" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="680" spans="1:1" ht="14.4">
+      <c r="A680" s="10" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="681" spans="1:1" ht="14.4">
+      <c r="A681" s="9" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="682" spans="1:1" ht="14.4">
+      <c r="A682" s="9" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="683" spans="1:1" ht="14.4">
+      <c r="A683" s="9" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="684" spans="1:1" ht="14.4">
+      <c r="A684" s="9" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="685" spans="1:1" ht="14.4">
+      <c r="A685" s="9" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="686" spans="1:1" ht="14.4">
+      <c r="A686" s="9" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="687" spans="1:1" ht="14.4">
+      <c r="A687" s="10" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="688" spans="1:1" ht="14.4">
+      <c r="A688" s="10" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="689" spans="1:1" ht="14.4">
+      <c r="A689" s="9" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="690" spans="1:1" ht="14.4">
+      <c r="A690" s="9" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="691" spans="1:1" ht="14.4">
+      <c r="A691" s="9" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="692" spans="1:1" ht="14.4">
+      <c r="A692" s="10" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="693" spans="1:1" ht="14.4">
+      <c r="A693" s="10" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="694" spans="1:1" ht="14.4">
+      <c r="A694" s="9" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="695" spans="1:1" ht="14.4">
+      <c r="A695" s="10" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="696" spans="1:1" ht="14.4">
+      <c r="A696" s="10" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="697" spans="1:1" ht="14.4">
+      <c r="A697" s="9" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="698" spans="1:1" ht="14.4">
+      <c r="A698" s="10" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="699" spans="1:1" ht="14.4">
+      <c r="A699" s="10" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="700" spans="1:1" ht="14.4">
+      <c r="A700" s="10" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="701" spans="1:1" ht="14.4">
+      <c r="A701" s="9" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="702" spans="1:1" ht="14.4">
+      <c r="A702" s="9" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="703" spans="1:1" ht="14.4">
+      <c r="A703" s="10" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="704" spans="1:1" ht="14.4">
+      <c r="A704" s="10" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="705" spans="1:1" ht="14.4">
+      <c r="A705" s="9" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="706" spans="1:1" ht="14.4">
+      <c r="A706" s="10" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="707" spans="1:1" ht="14.4">
+      <c r="A707" s="10" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="708" spans="1:1" ht="14.4">
+      <c r="A708" s="10" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="709" spans="1:1" ht="14.4">
+      <c r="A709" s="10" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="710" spans="1:1" ht="14.4">
+      <c r="A710" s="10" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="711" spans="1:1" ht="14.4">
+      <c r="A711" s="10" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="712" spans="1:1" ht="14.4">
+      <c r="A712" s="9" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="713" spans="1:1" ht="14.4">
+      <c r="A713" s="10" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="714" spans="1:1" ht="14.4">
+      <c r="A714" s="9" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="715" spans="1:1" ht="14.4">
+      <c r="A715" s="9" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="716" spans="1:1" ht="14.4">
+      <c r="A716" s="10" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="717" spans="1:1" ht="14.4">
+      <c r="A717" s="9" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="718" spans="1:1" ht="14.4">
+      <c r="A718" s="10" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="719" spans="1:1" ht="14.4">
+      <c r="A719" s="10" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="720" spans="1:1" ht="14.4">
+      <c r="A720" s="10" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="721" spans="1:1" ht="14.4">
+      <c r="A721" s="10" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="722" spans="1:1" ht="14.4">
+      <c r="A722" s="10" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="723" spans="1:1" ht="14.4">
+      <c r="A723" s="10" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="724" spans="1:1" ht="14.4">
+      <c r="A724" s="10" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="725" spans="1:1" ht="14.4">
+      <c r="A725" s="10" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="726" spans="1:1" ht="14.4">
+      <c r="A726" s="10" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="727" spans="1:1" ht="14.4">
+      <c r="A727" s="10" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="728" spans="1:1" ht="14.4">
+      <c r="A728" s="9" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="729" spans="1:1" ht="14.4">
+      <c r="A729" s="10" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="730" spans="1:1" ht="14.4">
+      <c r="A730" s="10" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="731" spans="1:1" ht="14.4">
+      <c r="A731" s="10" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="732" spans="1:1" ht="14.4">
+      <c r="A732" s="10" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="733" spans="1:1" ht="14.4">
+      <c r="A733" s="9" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="734" spans="1:1" ht="14.4">
+      <c r="A734" s="10" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="735" spans="1:1" ht="14.4">
+      <c r="A735" s="9" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="736" spans="1:1" ht="14.4">
+      <c r="A736" s="9" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="737" spans="1:1" ht="14.4">
+      <c r="A737" s="10" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="738" spans="1:1" ht="14.4">
+      <c r="A738" s="9" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="739" spans="1:1" ht="14.4">
+      <c r="A739" s="9" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="740" spans="1:1" ht="14.4">
+      <c r="A740" s="10" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="741" spans="1:1" ht="14.4">
+      <c r="A741" s="10" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="742" spans="1:1" ht="14.4">
+      <c r="A742" s="9" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="743" spans="1:1" ht="14.4">
+      <c r="A743" s="9" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="744" spans="1:1" ht="14.4">
+      <c r="A744" s="10" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="745" spans="1:1" ht="14.4">
+      <c r="A745" s="10" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="746" spans="1:1" ht="14.4">
+      <c r="A746" s="10" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="747" spans="1:1" ht="14.4">
+      <c r="A747" s="10" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="748" spans="1:1" ht="14.4">
+      <c r="A748" s="10" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="749" spans="1:1" ht="14.4">
+      <c r="A749" s="10" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="750" spans="1:1" ht="14.4">
+      <c r="A750" s="9" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="751" spans="1:1" ht="14.4">
+      <c r="A751" s="10" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="752" spans="1:1" ht="14.4">
+      <c r="A752" s="10" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="753" spans="1:1" ht="14.4">
+      <c r="A753" s="10" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="754" spans="1:1" ht="14.4">
+      <c r="A754" s="10" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="755" spans="1:1" ht="14.4">
+      <c r="A755" s="10" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="756" spans="1:1" ht="14.4">
+      <c r="A756" s="9" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="757" spans="1:1" ht="14.4">
+      <c r="A757" s="9" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="758" spans="1:1" ht="14.4">
+      <c r="A758" s="9" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="759" spans="1:1" ht="14.4">
+      <c r="A759" s="10" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="760" spans="1:1" ht="14.4">
+      <c r="A760" s="10" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="761" spans="1:1" ht="14.4">
+      <c r="A761" s="10" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="762" spans="1:1" ht="14.4">
+      <c r="A762" s="10" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="763" spans="1:1" ht="14.4">
+      <c r="A763" s="9" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="764" spans="1:1" ht="14.4">
+      <c r="A764" s="9" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="765" spans="1:1" ht="14.4">
+      <c r="A765" s="10" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="766" spans="1:1" ht="14.4">
+      <c r="A766" s="10" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="767" spans="1:1" ht="14.4">
+      <c r="A767" s="10" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="768" spans="1:1" ht="14.4">
+      <c r="A768" s="10" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="769" spans="1:1" ht="14.4">
+      <c r="A769" s="10" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="770" spans="1:1" ht="14.4">
+      <c r="A770" s="10" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="771" spans="1:1" ht="14.4">
+      <c r="A771" s="10" t="s">
+        <v>336</v>
       </c>
     </row>
   </sheetData>

--- a/on_the_way.xlsx
+++ b/on_the_way.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="634">
   <si>
     <t>Track</t>
   </si>
@@ -1558,6 +1558,366 @@
   </si>
   <si>
     <t>79118824420191</t>
+  </si>
+  <si>
+    <t>YT8884755194668</t>
+  </si>
+  <si>
+    <t>79120571661088</t>
+  </si>
+  <si>
+    <t>73716426051276</t>
+  </si>
+  <si>
+    <t>777425552263142</t>
+  </si>
+  <si>
+    <t>773430169099707</t>
+  </si>
+  <si>
+    <t>777425497747169</t>
+  </si>
+  <si>
+    <t>79120492216951</t>
+  </si>
+  <si>
+    <t>JT5503909880771</t>
+  </si>
+  <si>
+    <t>777425406799771</t>
+  </si>
+  <si>
+    <t>YT8884929245680</t>
+  </si>
+  <si>
+    <t>JT5503756413585</t>
+  </si>
+  <si>
+    <t>79120273943032</t>
+  </si>
+  <si>
+    <t>777425512853696</t>
+  </si>
+  <si>
+    <t>465494472191076</t>
+  </si>
+  <si>
+    <t>465485363226456</t>
+  </si>
+  <si>
+    <t>465486045639866</t>
+  </si>
+  <si>
+    <t>YT8884901508329</t>
+  </si>
+  <si>
+    <t>465485289856256</t>
+  </si>
+  <si>
+    <t>465485672986262</t>
+  </si>
+  <si>
+    <t>YT8884756076626</t>
+  </si>
+  <si>
+    <t>777425538961039</t>
+  </si>
+  <si>
+    <t>777425492400505</t>
+  </si>
+  <si>
+    <t>777425376893025</t>
+  </si>
+  <si>
+    <t>YT8885713972711</t>
+  </si>
+  <si>
+    <t>465493047946239</t>
+  </si>
+  <si>
+    <t>YT8884852002725</t>
+  </si>
+  <si>
+    <t>JT5503934267516</t>
+  </si>
+  <si>
+    <t>JT5503723040860</t>
+  </si>
+  <si>
+    <t>777425217523315</t>
+  </si>
+  <si>
+    <t>YT8884777619042</t>
+  </si>
+  <si>
+    <t>JT5503980623746</t>
+  </si>
+  <si>
+    <t>YT8885213220312</t>
+  </si>
+  <si>
+    <t>777425614036297</t>
+  </si>
+  <si>
+    <t>YT8884804050635</t>
+  </si>
+  <si>
+    <t>JT9001470362258</t>
+  </si>
+  <si>
+    <t>465484039936407</t>
+  </si>
+  <si>
+    <t>JT5503943390671</t>
+  </si>
+  <si>
+    <t>YT8884779828624</t>
+  </si>
+  <si>
+    <t>79120994662956</t>
+  </si>
+  <si>
+    <t>9817903095048</t>
+  </si>
+  <si>
+    <t>79120926941206</t>
+  </si>
+  <si>
+    <t>YT7631927398745</t>
+  </si>
+  <si>
+    <t>JT5503946278929</t>
+  </si>
+  <si>
+    <t>YT8884674366823</t>
+  </si>
+  <si>
+    <t>465484052406977</t>
+  </si>
+  <si>
+    <t>777425075185916</t>
+  </si>
+  <si>
+    <t>777424952193652</t>
+  </si>
+  <si>
+    <t>YT8884549928833</t>
+  </si>
+  <si>
+    <t>777425532295679</t>
+  </si>
+  <si>
+    <t>777425292337950</t>
+  </si>
+  <si>
+    <t>777425561922513</t>
+  </si>
+  <si>
+    <t>465483864393112</t>
+  </si>
+  <si>
+    <t>79121420106957</t>
+  </si>
+  <si>
+    <t>9817900423455</t>
+  </si>
+  <si>
+    <t>JT5503614888010</t>
+  </si>
+  <si>
+    <t>JDAP03199174222</t>
+  </si>
+  <si>
+    <t>9817858283449</t>
+  </si>
+  <si>
+    <t>YT8884867106797</t>
+  </si>
+  <si>
+    <t>777425029418984</t>
+  </si>
+  <si>
+    <t>777424939805614</t>
+  </si>
+  <si>
+    <t>79120583583816</t>
+  </si>
+  <si>
+    <t>777425556295308</t>
+  </si>
+  <si>
+    <t>YT7631737508840</t>
+  </si>
+  <si>
+    <t>YT8884855694613</t>
+  </si>
+  <si>
+    <t>JT5503622166402</t>
+  </si>
+  <si>
+    <t>79121035460932</t>
+  </si>
+  <si>
+    <t>YT8884665198192</t>
+  </si>
+  <si>
+    <t>79120737015066</t>
+  </si>
+  <si>
+    <t>773430615417672</t>
+  </si>
+  <si>
+    <t>9817911190682</t>
+  </si>
+  <si>
+    <t>YT8885608190598</t>
+  </si>
+  <si>
+    <t>YT8884560989732</t>
+  </si>
+  <si>
+    <t>JT5503598011345</t>
+  </si>
+  <si>
+    <t>465493030554901</t>
+  </si>
+  <si>
+    <t>JT5503312311887</t>
+  </si>
+  <si>
+    <t>JT5503788424481</t>
+  </si>
+  <si>
+    <t>773430619143253</t>
+  </si>
+  <si>
+    <t>465483610812509</t>
+  </si>
+  <si>
+    <t>777424986197449</t>
+  </si>
+  <si>
+    <t>YT8884843406758</t>
+  </si>
+  <si>
+    <t>465485939540824</t>
+  </si>
+  <si>
+    <t>777425442675982</t>
+  </si>
+  <si>
+    <t>777425354589800</t>
+  </si>
+  <si>
+    <t>777425328442133</t>
+  </si>
+  <si>
+    <t>JT5503665519773</t>
+  </si>
+  <si>
+    <t>JT5503356984126</t>
+  </si>
+  <si>
+    <t>777424952568763</t>
+  </si>
+  <si>
+    <t>YT8884280552889</t>
+  </si>
+  <si>
+    <t>79121004489806</t>
+  </si>
+  <si>
+    <t>465484249602894</t>
+  </si>
+  <si>
+    <t>465493029458794</t>
+  </si>
+  <si>
+    <t>9817904648526</t>
+  </si>
+  <si>
+    <t>465486424671792</t>
+  </si>
+  <si>
+    <t>79120513891281</t>
+  </si>
+  <si>
+    <t>777425078148667</t>
+  </si>
+  <si>
+    <t>JT5503731539655</t>
+  </si>
+  <si>
+    <t>773430488632225</t>
+  </si>
+  <si>
+    <t>9817883876957</t>
+  </si>
+  <si>
+    <t>79120771222043</t>
+  </si>
+  <si>
+    <t>465494207464740</t>
+  </si>
+  <si>
+    <t>79120859994050</t>
+  </si>
+  <si>
+    <t>9817857282681</t>
+  </si>
+  <si>
+    <t>YT2544888435581</t>
+  </si>
+  <si>
+    <t>465494671170125</t>
+  </si>
+  <si>
+    <t>777425635070207</t>
+  </si>
+  <si>
+    <t>9817917146012</t>
+  </si>
+  <si>
+    <t>777425437843233</t>
+  </si>
+  <si>
+    <t>465495973466450</t>
+  </si>
+  <si>
+    <t>9817914931482</t>
+  </si>
+  <si>
+    <t>YT8885720429350</t>
+  </si>
+  <si>
+    <t>79121247992132</t>
+  </si>
+  <si>
+    <t>9817855386753</t>
+  </si>
+  <si>
+    <t>79120808394858</t>
+  </si>
+  <si>
+    <t>9817907816815</t>
+  </si>
+  <si>
+    <t>9817914022790</t>
+  </si>
+  <si>
+    <t>79120925438667</t>
+  </si>
+  <si>
+    <t>9817886341964</t>
+  </si>
+  <si>
+    <t>777425644089342</t>
+  </si>
+  <si>
+    <t>465483971196465</t>
+  </si>
+  <si>
+    <t>9817917440595</t>
   </si>
 </sst>
 </file>
@@ -2190,7 +2550,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" ht="14.4">
+      <c r="A2" s="9" t="s">
+        <v>514</v>
+      </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
@@ -2198,7 +2561,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" ht="14.4">
+      <c r="A3" s="10" t="s">
+        <v>515</v>
+      </c>
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
@@ -2206,7 +2572,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" ht="14.4">
+      <c r="A4" s="10" t="s">
+        <v>516</v>
+      </c>
       <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
@@ -2214,7 +2583,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" ht="14.4">
+      <c r="A5" s="10" t="s">
+        <v>517</v>
+      </c>
       <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
@@ -2222,7 +2594,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" ht="14.4">
+      <c r="A6" s="10" t="s">
+        <v>518</v>
+      </c>
       <c r="C6" s="1" t="s">
         <v>2</v>
       </c>
@@ -2230,7 +2605,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" ht="14.4">
+      <c r="A7" s="10" t="s">
+        <v>519</v>
+      </c>
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
@@ -2238,7 +2616,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" ht="14.4">
+      <c r="A8" s="10" t="s">
+        <v>520</v>
+      </c>
       <c r="C8" s="1" t="s">
         <v>2</v>
       </c>
@@ -2246,7 +2627,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" ht="14.4">
+      <c r="A9" s="9" t="s">
+        <v>521</v>
+      </c>
       <c r="C9" s="1" t="s">
         <v>2</v>
       </c>
@@ -2254,7 +2638,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" ht="14.4">
+      <c r="A10" s="10" t="s">
+        <v>522</v>
+      </c>
       <c r="C10" s="1" t="s">
         <v>2</v>
       </c>
@@ -2262,7 +2649,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" ht="14.4">
+      <c r="A11" s="9" t="s">
+        <v>523</v>
+      </c>
       <c r="C11" s="1" t="s">
         <v>2</v>
       </c>
@@ -2270,7 +2660,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" ht="14.4">
+      <c r="A12" s="9" t="s">
+        <v>524</v>
+      </c>
       <c r="C12" s="1" t="s">
         <v>2</v>
       </c>
@@ -2278,7 +2671,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" ht="14.4">
+      <c r="A13" s="10" t="s">
+        <v>525</v>
+      </c>
       <c r="C13" s="1" t="s">
         <v>2</v>
       </c>
@@ -2286,7 +2682,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" ht="14.4">
+      <c r="A14" s="10" t="s">
+        <v>526</v>
+      </c>
       <c r="C14" s="1" t="s">
         <v>2</v>
       </c>
@@ -2294,7 +2693,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" ht="14.4">
+      <c r="A15" s="10" t="s">
+        <v>527</v>
+      </c>
       <c r="C15" s="1" t="s">
         <v>2</v>
       </c>
@@ -2302,7 +2704,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" ht="14.4">
+      <c r="A16" s="10" t="s">
+        <v>528</v>
+      </c>
       <c r="C16" s="1" t="s">
         <v>2</v>
       </c>
@@ -2310,7 +2715,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="3:4">
+    <row r="17" spans="1:4" ht="14.4">
+      <c r="A17" s="10" t="s">
+        <v>529</v>
+      </c>
       <c r="C17" s="1" t="s">
         <v>2</v>
       </c>
@@ -2318,7 +2726,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="3:4">
+    <row r="18" spans="1:4" ht="14.4">
+      <c r="A18" s="9" t="s">
+        <v>530</v>
+      </c>
       <c r="C18" s="1" t="s">
         <v>2</v>
       </c>
@@ -2326,7 +2737,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="3:4">
+    <row r="19" spans="1:4" ht="14.4">
+      <c r="A19" s="10" t="s">
+        <v>531</v>
+      </c>
       <c r="C19" s="1" t="s">
         <v>2</v>
       </c>
@@ -2334,7 +2748,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="3:4">
+    <row r="20" spans="1:4" ht="14.4">
+      <c r="A20" s="10" t="s">
+        <v>532</v>
+      </c>
       <c r="C20" s="1" t="s">
         <v>2</v>
       </c>
@@ -2342,7 +2759,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="3:4">
+    <row r="21" spans="1:4" ht="14.4">
+      <c r="A21" s="9" t="s">
+        <v>533</v>
+      </c>
       <c r="C21" s="1" t="s">
         <v>2</v>
       </c>
@@ -2350,7 +2770,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="3:4">
+    <row r="22" spans="1:4" ht="14.4">
+      <c r="A22" s="10" t="s">
+        <v>534</v>
+      </c>
       <c r="C22" s="1" t="s">
         <v>2</v>
       </c>
@@ -2358,7 +2781,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="3:4">
+    <row r="23" spans="1:4" ht="14.4">
+      <c r="A23" s="10" t="s">
+        <v>535</v>
+      </c>
       <c r="C23" s="1" t="s">
         <v>2</v>
       </c>
@@ -2366,7 +2792,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="3:4">
+    <row r="24" spans="1:4" ht="14.4">
+      <c r="A24" s="10" t="s">
+        <v>536</v>
+      </c>
       <c r="C24" s="1" t="s">
         <v>2</v>
       </c>
@@ -2374,7 +2803,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="3:4">
+    <row r="25" spans="1:4" ht="14.4">
+      <c r="A25" s="9" t="s">
+        <v>537</v>
+      </c>
       <c r="C25" s="1" t="s">
         <v>2</v>
       </c>
@@ -2382,7 +2814,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="3:4">
+    <row r="26" spans="1:4" ht="14.4">
+      <c r="A26" s="10" t="s">
+        <v>538</v>
+      </c>
       <c r="C26" s="1" t="s">
         <v>2</v>
       </c>
@@ -2390,7 +2825,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="3:4">
+    <row r="27" spans="1:4" ht="14.4">
+      <c r="A27" s="9" t="s">
+        <v>539</v>
+      </c>
       <c r="C27" s="1" t="s">
         <v>2</v>
       </c>
@@ -2398,7 +2836,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="3:4">
+    <row r="28" spans="1:4" ht="14.4">
+      <c r="A28" s="9" t="s">
+        <v>540</v>
+      </c>
       <c r="C28" s="1" t="s">
         <v>2</v>
       </c>
@@ -2406,7 +2847,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="3:4">
+    <row r="29" spans="1:4" ht="14.4">
+      <c r="A29" s="9" t="s">
+        <v>541</v>
+      </c>
       <c r="C29" s="1" t="s">
         <v>2</v>
       </c>
@@ -2414,7 +2858,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="3:4">
+    <row r="30" spans="1:4" ht="14.4">
+      <c r="A30" s="10" t="s">
+        <v>542</v>
+      </c>
       <c r="C30" s="1" t="s">
         <v>2</v>
       </c>
@@ -2422,7 +2869,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="3:4">
+    <row r="31" spans="1:4" ht="14.4">
+      <c r="A31" s="9" t="s">
+        <v>543</v>
+      </c>
       <c r="C31" s="1" t="s">
         <v>2</v>
       </c>
@@ -2430,7 +2880,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="3:4">
+    <row r="32" spans="1:4" ht="14.4">
+      <c r="A32" s="9" t="s">
+        <v>544</v>
+      </c>
       <c r="C32" s="1" t="s">
         <v>2</v>
       </c>
@@ -2438,7 +2891,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="3:4">
+    <row r="33" spans="1:4" ht="14.4">
+      <c r="A33" s="9" t="s">
+        <v>545</v>
+      </c>
       <c r="C33" s="1" t="s">
         <v>2</v>
       </c>
@@ -2446,7 +2902,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="3:4">
+    <row r="34" spans="1:4" ht="14.4">
+      <c r="A34" s="10" t="s">
+        <v>546</v>
+      </c>
       <c r="C34" s="1" t="s">
         <v>2</v>
       </c>
@@ -2454,7 +2913,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="3:4">
+    <row r="35" spans="1:4" ht="14.4">
+      <c r="A35" s="9" t="s">
+        <v>547</v>
+      </c>
       <c r="C35" s="1" t="s">
         <v>2</v>
       </c>
@@ -2462,7 +2924,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="3:4">
+    <row r="36" spans="1:4" ht="14.4">
+      <c r="A36" s="9" t="s">
+        <v>548</v>
+      </c>
       <c r="C36" s="1" t="s">
         <v>2</v>
       </c>
@@ -2470,7 +2935,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="3:4">
+    <row r="37" spans="1:4" ht="14.4">
+      <c r="A37" s="10" t="s">
+        <v>549</v>
+      </c>
       <c r="C37" s="1" t="s">
         <v>2</v>
       </c>
@@ -2478,7 +2946,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="3:4">
+    <row r="38" spans="1:4" ht="14.4">
+      <c r="A38" s="9" t="s">
+        <v>550</v>
+      </c>
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
@@ -2486,7 +2957,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="3:4">
+    <row r="39" spans="1:4" ht="14.4">
+      <c r="A39" s="9" t="s">
+        <v>551</v>
+      </c>
       <c r="C39" s="1" t="s">
         <v>2</v>
       </c>
@@ -2494,7 +2968,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="3:4">
+    <row r="40" spans="1:4" ht="14.4">
+      <c r="A40" s="10" t="s">
+        <v>552</v>
+      </c>
       <c r="C40" s="1" t="s">
         <v>2</v>
       </c>
@@ -2502,7 +2979,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="3:4">
+    <row r="41" spans="1:4" ht="14.4">
+      <c r="A41" s="10" t="s">
+        <v>553</v>
+      </c>
       <c r="C41" s="1" t="s">
         <v>2</v>
       </c>
@@ -2510,7 +2990,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="3:4">
+    <row r="42" spans="1:4" ht="14.4">
+      <c r="A42" s="10" t="s">
+        <v>554</v>
+      </c>
       <c r="C42" s="1" t="s">
         <v>2</v>
       </c>
@@ -2518,7 +3001,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="3:4">
+    <row r="43" spans="1:4" ht="14.4">
+      <c r="A43" s="9" t="s">
+        <v>555</v>
+      </c>
       <c r="C43" s="1" t="s">
         <v>2</v>
       </c>
@@ -2526,7 +3012,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="3:4">
+    <row r="44" spans="1:4" ht="14.4">
+      <c r="A44" s="9" t="s">
+        <v>556</v>
+      </c>
       <c r="C44" s="1" t="s">
         <v>2</v>
       </c>
@@ -2534,7 +3023,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="3:4">
+    <row r="45" spans="1:4" ht="14.4">
+      <c r="A45" s="9" t="s">
+        <v>557</v>
+      </c>
       <c r="C45" s="1" t="s">
         <v>2</v>
       </c>
@@ -2542,7 +3034,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="3:4">
+    <row r="46" spans="1:4" ht="14.4">
+      <c r="A46" s="10" t="s">
+        <v>558</v>
+      </c>
       <c r="C46" s="1" t="s">
         <v>2</v>
       </c>
@@ -2550,7 +3045,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="3:4">
+    <row r="47" spans="1:4" ht="14.4">
+      <c r="A47" s="10" t="s">
+        <v>559</v>
+      </c>
       <c r="C47" s="1" t="s">
         <v>2</v>
       </c>
@@ -2558,7 +3056,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="3:4">
+    <row r="48" spans="1:4" ht="14.4">
+      <c r="A48" s="10" t="s">
+        <v>560</v>
+      </c>
       <c r="C48" s="1" t="s">
         <v>2</v>
       </c>
@@ -2566,7 +3067,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="3:4">
+    <row r="49" spans="1:4" ht="14.4">
+      <c r="A49" s="9" t="s">
+        <v>561</v>
+      </c>
       <c r="C49" s="1" t="s">
         <v>2</v>
       </c>
@@ -2574,7 +3078,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="3:4">
+    <row r="50" spans="1:4" ht="14.4">
+      <c r="A50" s="10" t="s">
+        <v>562</v>
+      </c>
       <c r="C50" s="1" t="s">
         <v>2</v>
       </c>
@@ -2582,7 +3089,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="3:4">
+    <row r="51" spans="1:4" ht="14.4">
+      <c r="A51" s="10" t="s">
+        <v>563</v>
+      </c>
       <c r="C51" s="1" t="s">
         <v>2</v>
       </c>
@@ -2590,7 +3100,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="3:4">
+    <row r="52" spans="1:4" ht="14.4">
+      <c r="A52" s="10" t="s">
+        <v>564</v>
+      </c>
       <c r="C52" s="1" t="s">
         <v>2</v>
       </c>
@@ -2598,7 +3111,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="3:4">
+    <row r="53" spans="1:4" ht="14.4">
+      <c r="A53" s="10" t="s">
+        <v>565</v>
+      </c>
       <c r="C53" s="1" t="s">
         <v>2</v>
       </c>
@@ -2606,7 +3122,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="3:4">
+    <row r="54" spans="1:4" ht="14.4">
+      <c r="A54" s="10" t="s">
+        <v>566</v>
+      </c>
       <c r="C54" s="1" t="s">
         <v>2</v>
       </c>
@@ -2614,7 +3133,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="3:4">
+    <row r="55" spans="1:4" ht="14.4">
+      <c r="A55" s="10" t="s">
+        <v>567</v>
+      </c>
       <c r="C55" s="1" t="s">
         <v>2</v>
       </c>
@@ -2622,7 +3144,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="3:4">
+    <row r="56" spans="1:4" ht="14.4">
+      <c r="A56" s="9" t="s">
+        <v>568</v>
+      </c>
       <c r="C56" s="1" t="s">
         <v>2</v>
       </c>
@@ -2630,7 +3155,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="3:4">
+    <row r="57" spans="1:4" ht="14.4">
+      <c r="A57" s="9" t="s">
+        <v>569</v>
+      </c>
       <c r="C57" s="1" t="s">
         <v>2</v>
       </c>
@@ -2638,7 +3166,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="3:4">
+    <row r="58" spans="1:4" ht="14.4">
+      <c r="A58" s="10" t="s">
+        <v>570</v>
+      </c>
       <c r="C58" s="1" t="s">
         <v>2</v>
       </c>
@@ -2646,7 +3177,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="3:4">
+    <row r="59" spans="1:4" ht="14.4">
+      <c r="A59" s="9" t="s">
+        <v>571</v>
+      </c>
       <c r="C59" s="1" t="s">
         <v>2</v>
       </c>
@@ -2654,7 +3188,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="3:4">
+    <row r="60" spans="1:4" ht="14.4">
+      <c r="A60" s="10" t="s">
+        <v>572</v>
+      </c>
       <c r="C60" s="1" t="s">
         <v>2</v>
       </c>
@@ -2662,7 +3199,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="3:4">
+    <row r="61" spans="1:4" ht="14.4">
+      <c r="A61" s="10" t="s">
+        <v>573</v>
+      </c>
       <c r="C61" s="1" t="s">
         <v>7</v>
       </c>
@@ -2670,97 +3210,154 @@
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="3:4">
+    <row r="62" spans="1:4" ht="14.4">
+      <c r="A62" s="10" t="s">
+        <v>574</v>
+      </c>
       <c r="C62" s="1">
         <v>20.0626</v>
       </c>
     </row>
-    <row r="63" spans="3:4">
+    <row r="63" spans="1:4" ht="14.4">
+      <c r="A63" s="10" t="s">
+        <v>575</v>
+      </c>
       <c r="C63" s="1">
         <v>20.0626</v>
       </c>
     </row>
-    <row r="64" spans="3:4">
+    <row r="64" spans="1:4" ht="14.4">
+      <c r="A64" s="9" t="s">
+        <v>576</v>
+      </c>
       <c r="C64" s="1">
         <v>20.0626</v>
       </c>
     </row>
-    <row r="65" spans="3:4">
+    <row r="65" spans="1:4" ht="14.4">
+      <c r="A65" s="9" t="s">
+        <v>577</v>
+      </c>
       <c r="C65" s="1">
         <v>20.0626</v>
       </c>
     </row>
-    <row r="66" spans="3:4">
+    <row r="66" spans="1:4" ht="14.4">
+      <c r="A66" s="9" t="s">
+        <v>578</v>
+      </c>
       <c r="C66" s="1">
         <v>20.0626</v>
       </c>
     </row>
-    <row r="67" spans="3:4">
+    <row r="67" spans="1:4" ht="14.4">
+      <c r="A67" s="10" t="s">
+        <v>579</v>
+      </c>
       <c r="C67" s="1">
         <v>20.0626</v>
       </c>
     </row>
-    <row r="68" spans="3:4">
+    <row r="68" spans="1:4" ht="14.4">
+      <c r="A68" s="9" t="s">
+        <v>580</v>
+      </c>
       <c r="C68" s="1">
         <v>20.0626</v>
       </c>
     </row>
-    <row r="69" spans="3:4">
+    <row r="69" spans="1:4" ht="14.4">
+      <c r="A69" s="10" t="s">
+        <v>581</v>
+      </c>
       <c r="C69" s="1">
         <v>20.0626</v>
       </c>
     </row>
-    <row r="70" spans="3:4">
+    <row r="70" spans="1:4" ht="14.4">
+      <c r="A70" s="10" t="s">
+        <v>582</v>
+      </c>
       <c r="C70" s="1">
         <v>20.0626</v>
       </c>
     </row>
-    <row r="71" spans="3:4">
+    <row r="71" spans="1:4" ht="14.4">
+      <c r="A71" s="10" t="s">
+        <v>583</v>
+      </c>
       <c r="C71" s="1">
         <v>20.0626</v>
       </c>
     </row>
-    <row r="72" spans="3:4">
+    <row r="72" spans="1:4" ht="14.4">
+      <c r="A72" s="9" t="s">
+        <v>584</v>
+      </c>
       <c r="C72" s="1">
         <v>20.0626</v>
       </c>
     </row>
-    <row r="73" spans="3:4">
+    <row r="73" spans="1:4" ht="14.4">
+      <c r="A73" s="9" t="s">
+        <v>585</v>
+      </c>
       <c r="C73" s="1">
         <v>20.0626</v>
       </c>
     </row>
-    <row r="74" spans="3:4">
+    <row r="74" spans="1:4" ht="14.4">
+      <c r="A74" s="9" t="s">
+        <v>586</v>
+      </c>
       <c r="C74" s="1">
         <v>20.0626</v>
       </c>
     </row>
-    <row r="75" spans="3:4">
+    <row r="75" spans="1:4" ht="14.4">
+      <c r="A75" s="10" t="s">
+        <v>587</v>
+      </c>
       <c r="C75" s="1">
         <v>20.0626</v>
       </c>
     </row>
-    <row r="76" spans="3:4">
+    <row r="76" spans="1:4" ht="14.4">
+      <c r="A76" s="9" t="s">
+        <v>588</v>
+      </c>
       <c r="C76" s="1">
         <v>20.0626</v>
       </c>
     </row>
-    <row r="77" spans="3:4">
+    <row r="77" spans="1:4" ht="14.4">
+      <c r="A77" s="9" t="s">
+        <v>589</v>
+      </c>
       <c r="C77" s="1">
         <v>20.0626</v>
       </c>
     </row>
-    <row r="78" spans="3:4">
+    <row r="78" spans="1:4" ht="14.4">
+      <c r="A78" s="10" t="s">
+        <v>590</v>
+      </c>
       <c r="C78" s="1">
         <v>20.0626</v>
       </c>
     </row>
-    <row r="79" spans="3:4">
+    <row r="79" spans="1:4" ht="14.4">
+      <c r="A79" s="10" t="s">
+        <v>591</v>
+      </c>
       <c r="C79" s="1">
         <v>20.0626</v>
       </c>
     </row>
-    <row r="80" spans="3:4">
+    <row r="80" spans="1:4" ht="14.4">
+      <c r="A80" s="10" t="s">
+        <v>592</v>
+      </c>
       <c r="C80" s="1">
         <v>20.0626</v>
       </c>
@@ -2768,7 +3365,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="2:4">
+    <row r="81" spans="1:4" ht="14.4">
+      <c r="A81" s="9" t="s">
+        <v>593</v>
+      </c>
       <c r="C81" s="1">
         <v>20.0626</v>
       </c>
@@ -2776,7 +3376,10 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="2:4">
+    <row r="82" spans="1:4" ht="14.4">
+      <c r="A82" s="10" t="s">
+        <v>594</v>
+      </c>
       <c r="C82" s="1">
         <v>20.0626</v>
       </c>
@@ -2784,7 +3387,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="2:4">
+    <row r="83" spans="1:4" ht="14.4">
+      <c r="A83" s="10" t="s">
+        <v>595</v>
+      </c>
       <c r="B83"/>
       <c r="C83" s="1">
         <v>20.0626</v>
@@ -2793,7 +3399,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="2:4">
+    <row r="84" spans="1:4" ht="14.4">
+      <c r="A84" s="10" t="s">
+        <v>596</v>
+      </c>
       <c r="B84"/>
       <c r="C84" s="1">
         <v>20.0626</v>
@@ -2802,7 +3411,10 @@
         <v>12</v>
       </c>
     </row>
-    <row r="85" spans="2:4">
+    <row r="85" spans="1:4" ht="14.4">
+      <c r="A85" s="10" t="s">
+        <v>597</v>
+      </c>
       <c r="B85"/>
       <c r="C85" s="1">
         <v>20.0626</v>
@@ -2811,7 +3423,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="2:4">
+    <row r="86" spans="1:4" ht="14.4">
+      <c r="A86" s="9" t="s">
+        <v>598</v>
+      </c>
       <c r="B86"/>
       <c r="C86" s="1">
         <v>20.0626</v>
@@ -2820,7 +3435,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="2:4">
+    <row r="87" spans="1:4" ht="14.4">
+      <c r="A87" s="9" t="s">
+        <v>599</v>
+      </c>
       <c r="B87"/>
       <c r="C87" s="1">
         <v>20.0626</v>
@@ -2829,7 +3447,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="2:4">
+    <row r="88" spans="1:4" ht="14.4">
+      <c r="A88" s="10" t="s">
+        <v>600</v>
+      </c>
       <c r="B88"/>
       <c r="C88" s="1">
         <v>20.0626</v>
@@ -2838,7 +3459,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="2:4">
+    <row r="89" spans="1:4" ht="14.4">
+      <c r="A89" s="9" t="s">
+        <v>601</v>
+      </c>
       <c r="B89"/>
       <c r="C89" s="1">
         <v>20.0626</v>
@@ -2847,7 +3471,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="2:4">
+    <row r="90" spans="1:4" ht="14.4">
+      <c r="A90" s="10" t="s">
+        <v>602</v>
+      </c>
       <c r="B90"/>
       <c r="C90" s="1">
         <v>20.0626</v>
@@ -2856,7 +3483,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="2:4">
+    <row r="91" spans="1:4" ht="14.4">
+      <c r="A91" s="10" t="s">
+        <v>603</v>
+      </c>
       <c r="B91"/>
       <c r="C91" s="1">
         <v>20.0626</v>
@@ -2865,7 +3495,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="2:4">
+    <row r="92" spans="1:4" ht="14.4">
+      <c r="A92" s="10" t="s">
+        <v>604</v>
+      </c>
       <c r="B92"/>
       <c r="C92" s="1">
         <v>20.0626</v>
@@ -2874,7 +3507,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="2:4">
+    <row r="93" spans="1:4" ht="14.4">
+      <c r="A93" s="10" t="s">
+        <v>605</v>
+      </c>
       <c r="B93"/>
       <c r="C93" s="1">
         <v>20.0626</v>
@@ -2883,7 +3519,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="2:4">
+    <row r="94" spans="1:4" ht="14.4">
+      <c r="A94" s="10" t="s">
+        <v>606</v>
+      </c>
       <c r="B94"/>
       <c r="C94" s="1">
         <v>20.0626</v>
@@ -2892,7 +3531,10 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="2:4">
+    <row r="95" spans="1:4" ht="14.4">
+      <c r="A95" s="10" t="s">
+        <v>607</v>
+      </c>
       <c r="B95"/>
       <c r="C95" s="1">
         <v>20.0626</v>
@@ -2901,7 +3543,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="96" spans="2:4">
+    <row r="96" spans="1:4" ht="14.4">
+      <c r="A96" s="10" t="s">
+        <v>608</v>
+      </c>
       <c r="B96"/>
       <c r="C96" s="1">
         <v>20.0626</v>
@@ -2910,7 +3555,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="2:4">
+    <row r="97" spans="1:4" ht="14.4">
+      <c r="A97" s="9" t="s">
+        <v>609</v>
+      </c>
       <c r="B97"/>
       <c r="C97" s="1">
         <v>20.0626</v>
@@ -2919,7 +3567,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="2:4">
+    <row r="98" spans="1:4" ht="14.4">
+      <c r="A98" s="10" t="s">
+        <v>610</v>
+      </c>
       <c r="B98"/>
       <c r="C98" s="1">
         <v>20.0626</v>
@@ -2928,7 +3579,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="2:4">
+    <row r="99" spans="1:4" ht="14.4">
+      <c r="A99" s="10" t="s">
+        <v>611</v>
+      </c>
       <c r="B99"/>
       <c r="C99" s="1">
         <v>20.0626</v>
@@ -2937,7 +3591,10 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="2:4">
+    <row r="100" spans="1:4" ht="14.4">
+      <c r="A100" s="10" t="s">
+        <v>612</v>
+      </c>
       <c r="B100"/>
       <c r="C100" s="1">
         <v>20.0626</v>
@@ -2946,7 +3603,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="2:4">
+    <row r="101" spans="1:4" ht="14.4">
+      <c r="A101" s="10" t="s">
+        <v>613</v>
+      </c>
       <c r="B101"/>
       <c r="C101" s="1">
         <v>20.0626</v>
@@ -2955,7 +3615,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="2:4">
+    <row r="102" spans="1:4" ht="14.4">
+      <c r="A102" s="10" t="s">
+        <v>614</v>
+      </c>
       <c r="B102"/>
       <c r="C102" s="1">
         <v>20.0626</v>
@@ -2964,7 +3627,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="2:4">
+    <row r="103" spans="1:4" ht="14.4">
+      <c r="A103" s="10" t="s">
+        <v>615</v>
+      </c>
       <c r="B103"/>
       <c r="C103" s="1">
         <v>20.0626</v>
@@ -2973,7 +3639,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="2:4">
+    <row r="104" spans="1:4" ht="14.4">
+      <c r="A104" s="9" t="s">
+        <v>616</v>
+      </c>
       <c r="B104"/>
       <c r="C104" s="1">
         <v>20.0626</v>
@@ -2982,7 +3651,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="2:4">
+    <row r="105" spans="1:4" ht="14.4">
+      <c r="A105" s="10" t="s">
+        <v>617</v>
+      </c>
       <c r="B105"/>
       <c r="C105" s="1">
         <v>20.0626</v>
@@ -2991,7 +3663,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="106" spans="2:4">
+    <row r="106" spans="1:4" ht="14.4">
+      <c r="A106" s="10" t="s">
+        <v>618</v>
+      </c>
       <c r="B106"/>
       <c r="C106" s="1">
         <v>20.0626</v>
@@ -3000,7 +3675,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="107" spans="2:4">
+    <row r="107" spans="1:4" ht="14.4">
+      <c r="A107" s="10" t="s">
+        <v>619</v>
+      </c>
       <c r="B107"/>
       <c r="C107" s="1">
         <v>20.0626</v>
@@ -3009,7 +3687,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="2:4">
+    <row r="108" spans="1:4" ht="14.4">
+      <c r="A108" s="10" t="s">
+        <v>620</v>
+      </c>
       <c r="B108"/>
       <c r="C108" s="1">
         <v>20.0626</v>
@@ -3018,7 +3699,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="2:4">
+    <row r="109" spans="1:4" ht="14.4">
+      <c r="A109" s="10" t="s">
+        <v>621</v>
+      </c>
       <c r="B109"/>
       <c r="C109" s="1">
         <v>20.0626</v>
@@ -3027,7 +3711,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="2:4">
+    <row r="110" spans="1:4" ht="14.4">
+      <c r="A110" s="10" t="s">
+        <v>622</v>
+      </c>
       <c r="B110"/>
       <c r="C110" s="1">
         <v>20.0626</v>
@@ -3036,7 +3723,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="2:4">
+    <row r="111" spans="1:4" ht="14.4">
+      <c r="A111" s="9" t="s">
+        <v>623</v>
+      </c>
       <c r="B111"/>
       <c r="C111" s="1">
         <v>20.0626</v>
@@ -3045,7 +3735,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="2:4">
+    <row r="112" spans="1:4" ht="14.4">
+      <c r="A112" s="10" t="s">
+        <v>624</v>
+      </c>
       <c r="B112"/>
       <c r="C112" s="1">
         <v>20.0626</v>
@@ -3054,7 +3747,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="113" spans="2:4">
+    <row r="113" spans="1:4" ht="14.4">
+      <c r="A113" s="10" t="s">
+        <v>625</v>
+      </c>
       <c r="B113"/>
       <c r="C113" s="1">
         <v>20.0626</v>
@@ -3063,7 +3759,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="2:4">
+    <row r="114" spans="1:4" ht="14.4">
+      <c r="A114" s="10" t="s">
+        <v>626</v>
+      </c>
       <c r="B114"/>
       <c r="C114" s="1">
         <v>20.0626</v>
@@ -3072,7 +3771,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="2:4">
+    <row r="115" spans="1:4" ht="14.4">
+      <c r="A115" s="10" t="s">
+        <v>627</v>
+      </c>
       <c r="B115"/>
       <c r="C115" s="1">
         <v>20.0626</v>
@@ -3081,7 +3783,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="2:4">
+    <row r="116" spans="1:4" ht="14.4">
+      <c r="A116" s="10" t="s">
+        <v>628</v>
+      </c>
       <c r="B116"/>
       <c r="C116" s="1">
         <v>20.0626</v>
@@ -3090,7 +3795,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="117" spans="2:4">
+    <row r="117" spans="1:4" ht="14.4">
+      <c r="A117" s="10" t="s">
+        <v>629</v>
+      </c>
       <c r="B117"/>
       <c r="C117" s="1">
         <v>20.0626</v>
@@ -3099,7 +3807,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="118" spans="2:4">
+    <row r="118" spans="1:4" ht="14.4">
+      <c r="A118" s="10" t="s">
+        <v>630</v>
+      </c>
       <c r="B118"/>
       <c r="C118" s="1">
         <v>20.0626</v>
@@ -3108,7 +3819,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="119" spans="2:4">
+    <row r="119" spans="1:4" ht="14.4">
+      <c r="A119" s="10" t="s">
+        <v>631</v>
+      </c>
       <c r="B119"/>
       <c r="C119" s="1">
         <v>20.0626</v>
@@ -3117,7 +3831,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="120" spans="2:4">
+    <row r="120" spans="1:4" ht="14.4">
+      <c r="A120" s="10" t="s">
+        <v>632</v>
+      </c>
       <c r="B120"/>
       <c r="C120" s="1">
         <v>20.0626</v>
@@ -3126,7 +3843,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="2:4">
+    <row r="121" spans="1:4" ht="14.4">
+      <c r="A121" s="10" t="s">
+        <v>633</v>
+      </c>
       <c r="B121"/>
       <c r="C121" s="1">
         <v>20.0626</v>
@@ -3135,7 +3855,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="2:4">
+    <row r="122" spans="1:4" ht="14.4">
+      <c r="A122" s="10" t="s">
+        <v>516</v>
+      </c>
       <c r="B122"/>
       <c r="C122" s="1">
         <v>20.0626</v>
@@ -3144,7 +3867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="2:4">
+    <row r="123" spans="1:4">
       <c r="B123"/>
       <c r="C123" s="1">
         <v>20.0626</v>
@@ -3153,7 +3876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="2:4">
+    <row r="124" spans="1:4">
       <c r="B124"/>
       <c r="C124" s="1">
         <v>20.0626</v>
@@ -3162,7 +3885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="2:4">
+    <row r="125" spans="1:4">
       <c r="B125"/>
       <c r="C125" s="1">
         <v>20.0626</v>
@@ -3171,7 +3894,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="126" spans="2:4">
+    <row r="126" spans="1:4">
       <c r="B126"/>
       <c r="C126" s="1">
         <v>20.0626</v>
@@ -3180,7 +3903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="2:4">
+    <row r="127" spans="1:4">
       <c r="B127"/>
       <c r="C127" s="1">
         <v>20.0626</v>
@@ -3189,7 +3912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="2:4">
+    <row r="128" spans="1:4">
       <c r="B128"/>
       <c r="C128" s="1">
         <v>20.0626</v>

--- a/on_the_way.xlsx
+++ b/on_the_way.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="672">
   <si>
     <t>Track</t>
   </si>
@@ -1918,6 +1918,120 @@
   </si>
   <si>
     <t>9817917440595</t>
+  </si>
+  <si>
+    <t>JT5505255975481</t>
+  </si>
+  <si>
+    <t>JT5504825809292</t>
+  </si>
+  <si>
+    <t>79121618345607</t>
+  </si>
+  <si>
+    <t>9817949573418</t>
+  </si>
+  <si>
+    <t>JT5504998948258</t>
+  </si>
+  <si>
+    <t>465501199601972</t>
+  </si>
+  <si>
+    <t>79121636735126</t>
+  </si>
+  <si>
+    <t>777426502141976</t>
+  </si>
+  <si>
+    <t>79121800010852</t>
+  </si>
+  <si>
+    <t>JT5505282889514</t>
+  </si>
+  <si>
+    <t>465500678686356</t>
+  </si>
+  <si>
+    <t>777426457494875</t>
+  </si>
+  <si>
+    <t>465502104232434</t>
+  </si>
+  <si>
+    <t>9817951581468</t>
+  </si>
+  <si>
+    <t>777426778488134</t>
+  </si>
+  <si>
+    <t>YT8885969781930</t>
+  </si>
+  <si>
+    <t>79121667178404</t>
+  </si>
+  <si>
+    <t>YT8886196738528</t>
+  </si>
+  <si>
+    <t>9817954030235</t>
+  </si>
+  <si>
+    <t>9817943793166</t>
+  </si>
+  <si>
+    <t>9817966084147</t>
+  </si>
+  <si>
+    <t>79121727019157</t>
+  </si>
+  <si>
+    <t>79121981513759</t>
+  </si>
+  <si>
+    <t>JT5505201778852</t>
+  </si>
+  <si>
+    <t>9817958820639</t>
+  </si>
+  <si>
+    <t>9817956925032</t>
+  </si>
+  <si>
+    <t>465501494935518</t>
+  </si>
+  <si>
+    <t>79121527527448</t>
+  </si>
+  <si>
+    <t>79121608498840</t>
+  </si>
+  <si>
+    <t>9817971903882</t>
+  </si>
+  <si>
+    <t>79121799191425</t>
+  </si>
+  <si>
+    <t>777426806685057</t>
+  </si>
+  <si>
+    <t>YT8885905743570</t>
+  </si>
+  <si>
+    <t>9817966082788</t>
+  </si>
+  <si>
+    <t>9817955045050</t>
+  </si>
+  <si>
+    <t>YT7632675835236</t>
+  </si>
+  <si>
+    <t>JT3169788112207</t>
+  </si>
+  <si>
+    <t>17.07.26</t>
   </si>
 </sst>
 </file>
@@ -2532,7 +2646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D771"/>
+  <dimension ref="A1:D811"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="19.77734375" style="2" customWidth="1"/>
@@ -7137,6 +7251,201 @@
     <row r="771" spans="1:1" ht="14.4">
       <c r="A771" s="10" t="s">
         <v>336</v>
+      </c>
+    </row>
+    <row r="773" spans="1:1" ht="14.4">
+      <c r="A773" s="10">
+        <v>777425546939086</v>
+      </c>
+    </row>
+    <row r="774" spans="1:1" ht="14.4">
+      <c r="A774" s="10" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="775" spans="1:1" ht="14.4">
+      <c r="A775" s="9" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="776" spans="1:1" ht="14.4">
+      <c r="A776" s="10" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="777" spans="1:1" ht="14.4">
+      <c r="A777" s="10" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="778" spans="1:1" ht="14.4">
+      <c r="A778" s="9" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="779" spans="1:1" ht="14.4">
+      <c r="A779" s="10" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="780" spans="1:1" ht="14.4">
+      <c r="A780" s="10" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="781" spans="1:1" ht="14.4">
+      <c r="A781" s="10" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="782" spans="1:1" ht="14.4">
+      <c r="A782" s="10" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="783" spans="1:1" ht="14.4">
+      <c r="A783" s="10" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="784" spans="1:1" ht="14.4">
+      <c r="A784" s="10" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="785" spans="1:1" ht="14.4">
+      <c r="A785" s="10" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="786" spans="1:1" ht="14.4">
+      <c r="A786" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="787" spans="1:1" ht="14.4">
+      <c r="A787" s="9" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="788" spans="1:1" ht="14.4">
+      <c r="A788" s="10" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="789" spans="1:1" ht="14.4">
+      <c r="A789" s="10" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="790" spans="1:1" ht="14.4">
+      <c r="A790" s="10" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="791" spans="1:1" ht="14.4">
+      <c r="A791" s="10" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="792" spans="1:1" ht="14.4">
+      <c r="A792" s="10" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="793" spans="1:1" ht="14.4">
+      <c r="A793" s="9" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="794" spans="1:1" ht="14.4">
+      <c r="A794" s="10" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="795" spans="1:1" ht="14.4">
+      <c r="A795" s="9" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="796" spans="1:1" ht="14.4">
+      <c r="A796" s="10" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="797" spans="1:1" ht="14.4">
+      <c r="A797" s="10" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="798" spans="1:1" ht="14.4">
+      <c r="A798" s="10" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="799" spans="1:1" ht="14.4">
+      <c r="A799" s="10" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="800" spans="1:1" ht="14.4">
+      <c r="A800" s="10" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="801" spans="1:2" ht="14.4">
+      <c r="A801" s="9" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="802" spans="1:2" ht="14.4">
+      <c r="A802" s="10" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="803" spans="1:2" ht="14.4">
+      <c r="A803" s="10" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="804" spans="1:2" ht="14.4">
+      <c r="A804" s="10" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="805" spans="1:2" ht="14.4">
+      <c r="A805" s="10" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="806" spans="1:2" ht="14.4">
+      <c r="A806" s="9" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="807" spans="1:2" ht="14.4">
+      <c r="A807" s="10" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="808" spans="1:2" ht="14.4">
+      <c r="A808" s="10" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="809" spans="1:2" ht="14.4">
+      <c r="A809" s="9" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="810" spans="1:2" ht="14.4">
+      <c r="A810" s="9" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="811" spans="1:2">
+      <c r="B811" s="1" t="s">
+        <v>671</v>
       </c>
     </row>
   </sheetData>

--- a/on_the_way.xlsx
+++ b/on_the_way.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="625">
   <si>
     <t>Track</t>
   </si>
@@ -57,148 +57,7 @@
     <t>Hilola 555572809</t>
   </si>
   <si>
-    <t>777421190698415</t>
-  </si>
-  <si>
-    <t>777420190077415</t>
-  </si>
-  <si>
-    <t>_x000D_777420148088605</t>
-  </si>
-  <si>
-    <t>777420320755106</t>
-  </si>
-  <si>
-    <t>JT5498515169938</t>
-  </si>
-  <si>
-    <t>777420415699128</t>
-  </si>
-  <si>
-    <t>9817455768664</t>
-  </si>
-  <si>
-    <t>465445838248752</t>
-  </si>
-  <si>
-    <t>79115916921709</t>
-  </si>
-  <si>
-    <t>465445620423811</t>
-  </si>
-  <si>
-    <t>79116064173156</t>
-  </si>
-  <si>
-    <t>9817475375924</t>
-  </si>
-  <si>
-    <t>777420209995112</t>
-  </si>
-  <si>
-    <t>9817494430164</t>
-  </si>
-  <si>
-    <t>777420107395099</t>
-  </si>
-  <si>
-    <t>9817479807223</t>
-  </si>
-  <si>
-    <t>JT5498130519084</t>
-  </si>
-  <si>
-    <t>YT8880292978538</t>
-  </si>
-  <si>
-    <t>9817512182414</t>
-  </si>
-  <si>
-    <t>777420364234201</t>
-  </si>
-  <si>
-    <t>JT5498262384603</t>
-  </si>
-  <si>
-    <t>JT5498044681933</t>
-  </si>
-  <si>
-    <t>YT8879925973530</t>
-  </si>
-  <si>
-    <t>79013823518038</t>
-  </si>
-  <si>
-    <t>777421046930615</t>
-  </si>
-  <si>
-    <t>777421365313677</t>
-  </si>
-  <si>
-    <t>465444445672611</t>
-  </si>
-  <si>
     <t>465448988108738</t>
-  </si>
-  <si>
-    <t>YT8879882443578</t>
-  </si>
-  <si>
-    <t>9817450914859</t>
-  </si>
-  <si>
-    <t>9817508074958</t>
-  </si>
-  <si>
-    <t>79116252056460</t>
-  </si>
-  <si>
-    <t>777421232224929</t>
-  </si>
-  <si>
-    <t>YT7628954567668</t>
-  </si>
-  <si>
-    <t>465447154216665</t>
-  </si>
-  <si>
-    <t>JT5498880650303</t>
-  </si>
-  <si>
-    <t>JT5498569535322</t>
-  </si>
-  <si>
-    <t>JT9001972082680</t>
-  </si>
-  <si>
-    <t>9817528972077</t>
-  </si>
-  <si>
-    <t>465447506810494</t>
-  </si>
-  <si>
-    <t>777421365892035</t>
-  </si>
-  <si>
-    <t>YT8880510987456</t>
-  </si>
-  <si>
-    <t>YT8879913736413</t>
-  </si>
-  <si>
-    <t>777421096212600</t>
-  </si>
-  <si>
-    <t>JT5498684503822</t>
-  </si>
-  <si>
-    <t>465443036459439</t>
-  </si>
-  <si>
-    <t>773428109156580</t>
-  </si>
-  <si>
-    <t>777420362773842</t>
   </si>
   <si>
     <t>465431595916185</t>
@@ -2666,7 +2525,7 @@
     </row>
     <row r="2" spans="1:4" ht="14.4">
       <c r="A2" s="9" t="s">
-        <v>514</v>
+        <v>467</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
@@ -2677,7 +2536,7 @@
     </row>
     <row r="3" spans="1:4" ht="14.4">
       <c r="A3" s="10" t="s">
-        <v>515</v>
+        <v>468</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>2</v>
@@ -2688,7 +2547,7 @@
     </row>
     <row r="4" spans="1:4" ht="14.4">
       <c r="A4" s="10" t="s">
-        <v>516</v>
+        <v>469</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>2</v>
@@ -2699,7 +2558,7 @@
     </row>
     <row r="5" spans="1:4" ht="14.4">
       <c r="A5" s="10" t="s">
-        <v>517</v>
+        <v>470</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>2</v>
@@ -2710,7 +2569,7 @@
     </row>
     <row r="6" spans="1:4" ht="14.4">
       <c r="A6" s="10" t="s">
-        <v>518</v>
+        <v>471</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>2</v>
@@ -2721,7 +2580,7 @@
     </row>
     <row r="7" spans="1:4" ht="14.4">
       <c r="A7" s="10" t="s">
-        <v>519</v>
+        <v>472</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>2</v>
@@ -2732,7 +2591,7 @@
     </row>
     <row r="8" spans="1:4" ht="14.4">
       <c r="A8" s="10" t="s">
-        <v>520</v>
+        <v>473</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>2</v>
@@ -2743,7 +2602,7 @@
     </row>
     <row r="9" spans="1:4" ht="14.4">
       <c r="A9" s="9" t="s">
-        <v>521</v>
+        <v>474</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>2</v>
@@ -2754,7 +2613,7 @@
     </row>
     <row r="10" spans="1:4" ht="14.4">
       <c r="A10" s="10" t="s">
-        <v>522</v>
+        <v>475</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>2</v>
@@ -2765,7 +2624,7 @@
     </row>
     <row r="11" spans="1:4" ht="14.4">
       <c r="A11" s="9" t="s">
-        <v>523</v>
+        <v>476</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>2</v>
@@ -2776,7 +2635,7 @@
     </row>
     <row r="12" spans="1:4" ht="14.4">
       <c r="A12" s="9" t="s">
-        <v>524</v>
+        <v>477</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>2</v>
@@ -2787,7 +2646,7 @@
     </row>
     <row r="13" spans="1:4" ht="14.4">
       <c r="A13" s="10" t="s">
-        <v>525</v>
+        <v>478</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>2</v>
@@ -2798,7 +2657,7 @@
     </row>
     <row r="14" spans="1:4" ht="14.4">
       <c r="A14" s="10" t="s">
-        <v>526</v>
+        <v>479</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>2</v>
@@ -2809,7 +2668,7 @@
     </row>
     <row r="15" spans="1:4" ht="14.4">
       <c r="A15" s="10" t="s">
-        <v>527</v>
+        <v>480</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>2</v>
@@ -2820,7 +2679,7 @@
     </row>
     <row r="16" spans="1:4" ht="14.4">
       <c r="A16" s="10" t="s">
-        <v>528</v>
+        <v>481</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>2</v>
@@ -2831,7 +2690,7 @@
     </row>
     <row r="17" spans="1:4" ht="14.4">
       <c r="A17" s="10" t="s">
-        <v>529</v>
+        <v>482</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>2</v>
@@ -2842,7 +2701,7 @@
     </row>
     <row r="18" spans="1:4" ht="14.4">
       <c r="A18" s="9" t="s">
-        <v>530</v>
+        <v>483</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>2</v>
@@ -2853,7 +2712,7 @@
     </row>
     <row r="19" spans="1:4" ht="14.4">
       <c r="A19" s="10" t="s">
-        <v>531</v>
+        <v>484</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>2</v>
@@ -2864,7 +2723,7 @@
     </row>
     <row r="20" spans="1:4" ht="14.4">
       <c r="A20" s="10" t="s">
-        <v>532</v>
+        <v>485</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>2</v>
@@ -2875,7 +2734,7 @@
     </row>
     <row r="21" spans="1:4" ht="14.4">
       <c r="A21" s="9" t="s">
-        <v>533</v>
+        <v>486</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>2</v>
@@ -2886,7 +2745,7 @@
     </row>
     <row r="22" spans="1:4" ht="14.4">
       <c r="A22" s="10" t="s">
-        <v>534</v>
+        <v>487</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>2</v>
@@ -2897,7 +2756,7 @@
     </row>
     <row r="23" spans="1:4" ht="14.4">
       <c r="A23" s="10" t="s">
-        <v>535</v>
+        <v>488</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>2</v>
@@ -2908,7 +2767,7 @@
     </row>
     <row r="24" spans="1:4" ht="14.4">
       <c r="A24" s="10" t="s">
-        <v>536</v>
+        <v>489</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>2</v>
@@ -2919,7 +2778,7 @@
     </row>
     <row r="25" spans="1:4" ht="14.4">
       <c r="A25" s="9" t="s">
-        <v>537</v>
+        <v>490</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>2</v>
@@ -2930,7 +2789,7 @@
     </row>
     <row r="26" spans="1:4" ht="14.4">
       <c r="A26" s="10" t="s">
-        <v>538</v>
+        <v>491</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>2</v>
@@ -2941,7 +2800,7 @@
     </row>
     <row r="27" spans="1:4" ht="14.4">
       <c r="A27" s="9" t="s">
-        <v>539</v>
+        <v>492</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>2</v>
@@ -2952,7 +2811,7 @@
     </row>
     <row r="28" spans="1:4" ht="14.4">
       <c r="A28" s="9" t="s">
-        <v>540</v>
+        <v>493</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>2</v>
@@ -2963,7 +2822,7 @@
     </row>
     <row r="29" spans="1:4" ht="14.4">
       <c r="A29" s="9" t="s">
-        <v>541</v>
+        <v>494</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>2</v>
@@ -2974,7 +2833,7 @@
     </row>
     <row r="30" spans="1:4" ht="14.4">
       <c r="A30" s="10" t="s">
-        <v>542</v>
+        <v>495</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>2</v>
@@ -2985,7 +2844,7 @@
     </row>
     <row r="31" spans="1:4" ht="14.4">
       <c r="A31" s="9" t="s">
-        <v>543</v>
+        <v>496</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>2</v>
@@ -2996,7 +2855,7 @@
     </row>
     <row r="32" spans="1:4" ht="14.4">
       <c r="A32" s="9" t="s">
-        <v>544</v>
+        <v>497</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>2</v>
@@ -3007,7 +2866,7 @@
     </row>
     <row r="33" spans="1:4" ht="14.4">
       <c r="A33" s="9" t="s">
-        <v>545</v>
+        <v>498</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>2</v>
@@ -3018,7 +2877,7 @@
     </row>
     <row r="34" spans="1:4" ht="14.4">
       <c r="A34" s="10" t="s">
-        <v>546</v>
+        <v>499</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>2</v>
@@ -3029,7 +2888,7 @@
     </row>
     <row r="35" spans="1:4" ht="14.4">
       <c r="A35" s="9" t="s">
-        <v>547</v>
+        <v>500</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>2</v>
@@ -3040,7 +2899,7 @@
     </row>
     <row r="36" spans="1:4" ht="14.4">
       <c r="A36" s="9" t="s">
-        <v>548</v>
+        <v>501</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>2</v>
@@ -3051,7 +2910,7 @@
     </row>
     <row r="37" spans="1:4" ht="14.4">
       <c r="A37" s="10" t="s">
-        <v>549</v>
+        <v>502</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>2</v>
@@ -3062,7 +2921,7 @@
     </row>
     <row r="38" spans="1:4" ht="14.4">
       <c r="A38" s="9" t="s">
-        <v>550</v>
+        <v>503</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>2</v>
@@ -3073,7 +2932,7 @@
     </row>
     <row r="39" spans="1:4" ht="14.4">
       <c r="A39" s="9" t="s">
-        <v>551</v>
+        <v>504</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>2</v>
@@ -3084,7 +2943,7 @@
     </row>
     <row r="40" spans="1:4" ht="14.4">
       <c r="A40" s="10" t="s">
-        <v>552</v>
+        <v>505</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>2</v>
@@ -3095,7 +2954,7 @@
     </row>
     <row r="41" spans="1:4" ht="14.4">
       <c r="A41" s="10" t="s">
-        <v>553</v>
+        <v>506</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>2</v>
@@ -3106,7 +2965,7 @@
     </row>
     <row r="42" spans="1:4" ht="14.4">
       <c r="A42" s="10" t="s">
-        <v>554</v>
+        <v>507</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>2</v>
@@ -3117,7 +2976,7 @@
     </row>
     <row r="43" spans="1:4" ht="14.4">
       <c r="A43" s="9" t="s">
-        <v>555</v>
+        <v>508</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>2</v>
@@ -3128,7 +2987,7 @@
     </row>
     <row r="44" spans="1:4" ht="14.4">
       <c r="A44" s="9" t="s">
-        <v>556</v>
+        <v>509</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>2</v>
@@ -3139,7 +2998,7 @@
     </row>
     <row r="45" spans="1:4" ht="14.4">
       <c r="A45" s="9" t="s">
-        <v>557</v>
+        <v>510</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>2</v>
@@ -3150,7 +3009,7 @@
     </row>
     <row r="46" spans="1:4" ht="14.4">
       <c r="A46" s="10" t="s">
-        <v>558</v>
+        <v>511</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>2</v>
@@ -3161,7 +3020,7 @@
     </row>
     <row r="47" spans="1:4" ht="14.4">
       <c r="A47" s="10" t="s">
-        <v>559</v>
+        <v>512</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>2</v>
@@ -3172,7 +3031,7 @@
     </row>
     <row r="48" spans="1:4" ht="14.4">
       <c r="A48" s="10" t="s">
-        <v>560</v>
+        <v>513</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>2</v>
@@ -3183,7 +3042,7 @@
     </row>
     <row r="49" spans="1:4" ht="14.4">
       <c r="A49" s="9" t="s">
-        <v>561</v>
+        <v>514</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>2</v>
@@ -3194,7 +3053,7 @@
     </row>
     <row r="50" spans="1:4" ht="14.4">
       <c r="A50" s="10" t="s">
-        <v>562</v>
+        <v>515</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>2</v>
@@ -3205,7 +3064,7 @@
     </row>
     <row r="51" spans="1:4" ht="14.4">
       <c r="A51" s="10" t="s">
-        <v>563</v>
+        <v>516</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>2</v>
@@ -3216,7 +3075,7 @@
     </row>
     <row r="52" spans="1:4" ht="14.4">
       <c r="A52" s="10" t="s">
-        <v>564</v>
+        <v>517</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>2</v>
@@ -3227,7 +3086,7 @@
     </row>
     <row r="53" spans="1:4" ht="14.4">
       <c r="A53" s="10" t="s">
-        <v>565</v>
+        <v>518</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>2</v>
@@ -3238,7 +3097,7 @@
     </row>
     <row r="54" spans="1:4" ht="14.4">
       <c r="A54" s="10" t="s">
-        <v>566</v>
+        <v>519</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>2</v>
@@ -3249,7 +3108,7 @@
     </row>
     <row r="55" spans="1:4" ht="14.4">
       <c r="A55" s="10" t="s">
-        <v>567</v>
+        <v>520</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>2</v>
@@ -3260,7 +3119,7 @@
     </row>
     <row r="56" spans="1:4" ht="14.4">
       <c r="A56" s="9" t="s">
-        <v>568</v>
+        <v>521</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>2</v>
@@ -3271,7 +3130,7 @@
     </row>
     <row r="57" spans="1:4" ht="14.4">
       <c r="A57" s="9" t="s">
-        <v>569</v>
+        <v>522</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>2</v>
@@ -3282,7 +3141,7 @@
     </row>
     <row r="58" spans="1:4" ht="14.4">
       <c r="A58" s="10" t="s">
-        <v>570</v>
+        <v>523</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>2</v>
@@ -3293,7 +3152,7 @@
     </row>
     <row r="59" spans="1:4" ht="14.4">
       <c r="A59" s="9" t="s">
-        <v>571</v>
+        <v>524</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>2</v>
@@ -3304,7 +3163,7 @@
     </row>
     <row r="60" spans="1:4" ht="14.4">
       <c r="A60" s="10" t="s">
-        <v>572</v>
+        <v>525</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>2</v>
@@ -3315,7 +3174,7 @@
     </row>
     <row r="61" spans="1:4" ht="14.4">
       <c r="A61" s="10" t="s">
-        <v>573</v>
+        <v>526</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>7</v>
@@ -3326,7 +3185,7 @@
     </row>
     <row r="62" spans="1:4" ht="14.4">
       <c r="A62" s="10" t="s">
-        <v>574</v>
+        <v>527</v>
       </c>
       <c r="C62" s="1">
         <v>20.0626</v>
@@ -3334,7 +3193,7 @@
     </row>
     <row r="63" spans="1:4" ht="14.4">
       <c r="A63" s="10" t="s">
-        <v>575</v>
+        <v>528</v>
       </c>
       <c r="C63" s="1">
         <v>20.0626</v>
@@ -3342,7 +3201,7 @@
     </row>
     <row r="64" spans="1:4" ht="14.4">
       <c r="A64" s="9" t="s">
-        <v>576</v>
+        <v>529</v>
       </c>
       <c r="C64" s="1">
         <v>20.0626</v>
@@ -3350,7 +3209,7 @@
     </row>
     <row r="65" spans="1:4" ht="14.4">
       <c r="A65" s="9" t="s">
-        <v>577</v>
+        <v>530</v>
       </c>
       <c r="C65" s="1">
         <v>20.0626</v>
@@ -3358,7 +3217,7 @@
     </row>
     <row r="66" spans="1:4" ht="14.4">
       <c r="A66" s="9" t="s">
-        <v>578</v>
+        <v>531</v>
       </c>
       <c r="C66" s="1">
         <v>20.0626</v>
@@ -3366,7 +3225,7 @@
     </row>
     <row r="67" spans="1:4" ht="14.4">
       <c r="A67" s="10" t="s">
-        <v>579</v>
+        <v>532</v>
       </c>
       <c r="C67" s="1">
         <v>20.0626</v>
@@ -3374,7 +3233,7 @@
     </row>
     <row r="68" spans="1:4" ht="14.4">
       <c r="A68" s="9" t="s">
-        <v>580</v>
+        <v>533</v>
       </c>
       <c r="C68" s="1">
         <v>20.0626</v>
@@ -3382,7 +3241,7 @@
     </row>
     <row r="69" spans="1:4" ht="14.4">
       <c r="A69" s="10" t="s">
-        <v>581</v>
+        <v>534</v>
       </c>
       <c r="C69" s="1">
         <v>20.0626</v>
@@ -3390,7 +3249,7 @@
     </row>
     <row r="70" spans="1:4" ht="14.4">
       <c r="A70" s="10" t="s">
-        <v>582</v>
+        <v>535</v>
       </c>
       <c r="C70" s="1">
         <v>20.0626</v>
@@ -3398,7 +3257,7 @@
     </row>
     <row r="71" spans="1:4" ht="14.4">
       <c r="A71" s="10" t="s">
-        <v>583</v>
+        <v>536</v>
       </c>
       <c r="C71" s="1">
         <v>20.0626</v>
@@ -3406,7 +3265,7 @@
     </row>
     <row r="72" spans="1:4" ht="14.4">
       <c r="A72" s="9" t="s">
-        <v>584</v>
+        <v>537</v>
       </c>
       <c r="C72" s="1">
         <v>20.0626</v>
@@ -3414,7 +3273,7 @@
     </row>
     <row r="73" spans="1:4" ht="14.4">
       <c r="A73" s="9" t="s">
-        <v>585</v>
+        <v>538</v>
       </c>
       <c r="C73" s="1">
         <v>20.0626</v>
@@ -3422,7 +3281,7 @@
     </row>
     <row r="74" spans="1:4" ht="14.4">
       <c r="A74" s="9" t="s">
-        <v>586</v>
+        <v>539</v>
       </c>
       <c r="C74" s="1">
         <v>20.0626</v>
@@ -3430,7 +3289,7 @@
     </row>
     <row r="75" spans="1:4" ht="14.4">
       <c r="A75" s="10" t="s">
-        <v>587</v>
+        <v>540</v>
       </c>
       <c r="C75" s="1">
         <v>20.0626</v>
@@ -3438,7 +3297,7 @@
     </row>
     <row r="76" spans="1:4" ht="14.4">
       <c r="A76" s="9" t="s">
-        <v>588</v>
+        <v>541</v>
       </c>
       <c r="C76" s="1">
         <v>20.0626</v>
@@ -3446,7 +3305,7 @@
     </row>
     <row r="77" spans="1:4" ht="14.4">
       <c r="A77" s="9" t="s">
-        <v>589</v>
+        <v>542</v>
       </c>
       <c r="C77" s="1">
         <v>20.0626</v>
@@ -3454,7 +3313,7 @@
     </row>
     <row r="78" spans="1:4" ht="14.4">
       <c r="A78" s="10" t="s">
-        <v>590</v>
+        <v>543</v>
       </c>
       <c r="C78" s="1">
         <v>20.0626</v>
@@ -3462,7 +3321,7 @@
     </row>
     <row r="79" spans="1:4" ht="14.4">
       <c r="A79" s="10" t="s">
-        <v>591</v>
+        <v>544</v>
       </c>
       <c r="C79" s="1">
         <v>20.0626</v>
@@ -3470,7 +3329,7 @@
     </row>
     <row r="80" spans="1:4" ht="14.4">
       <c r="A80" s="10" t="s">
-        <v>592</v>
+        <v>545</v>
       </c>
       <c r="C80" s="1">
         <v>20.0626</v>
@@ -3481,7 +3340,7 @@
     </row>
     <row r="81" spans="1:4" ht="14.4">
       <c r="A81" s="9" t="s">
-        <v>593</v>
+        <v>546</v>
       </c>
       <c r="C81" s="1">
         <v>20.0626</v>
@@ -3492,7 +3351,7 @@
     </row>
     <row r="82" spans="1:4" ht="14.4">
       <c r="A82" s="10" t="s">
-        <v>594</v>
+        <v>547</v>
       </c>
       <c r="C82" s="1">
         <v>20.0626</v>
@@ -3503,7 +3362,7 @@
     </row>
     <row r="83" spans="1:4" ht="14.4">
       <c r="A83" s="10" t="s">
-        <v>595</v>
+        <v>548</v>
       </c>
       <c r="B83"/>
       <c r="C83" s="1">
@@ -3515,7 +3374,7 @@
     </row>
     <row r="84" spans="1:4" ht="14.4">
       <c r="A84" s="10" t="s">
-        <v>596</v>
+        <v>549</v>
       </c>
       <c r="B84"/>
       <c r="C84" s="1">
@@ -3527,7 +3386,7 @@
     </row>
     <row r="85" spans="1:4" ht="14.4">
       <c r="A85" s="10" t="s">
-        <v>597</v>
+        <v>550</v>
       </c>
       <c r="B85"/>
       <c r="C85" s="1">
@@ -3539,7 +3398,7 @@
     </row>
     <row r="86" spans="1:4" ht="14.4">
       <c r="A86" s="9" t="s">
-        <v>598</v>
+        <v>551</v>
       </c>
       <c r="B86"/>
       <c r="C86" s="1">
@@ -3551,7 +3410,7 @@
     </row>
     <row r="87" spans="1:4" ht="14.4">
       <c r="A87" s="9" t="s">
-        <v>599</v>
+        <v>552</v>
       </c>
       <c r="B87"/>
       <c r="C87" s="1">
@@ -3563,7 +3422,7 @@
     </row>
     <row r="88" spans="1:4" ht="14.4">
       <c r="A88" s="10" t="s">
-        <v>600</v>
+        <v>553</v>
       </c>
       <c r="B88"/>
       <c r="C88" s="1">
@@ -3575,7 +3434,7 @@
     </row>
     <row r="89" spans="1:4" ht="14.4">
       <c r="A89" s="9" t="s">
-        <v>601</v>
+        <v>554</v>
       </c>
       <c r="B89"/>
       <c r="C89" s="1">
@@ -3587,7 +3446,7 @@
     </row>
     <row r="90" spans="1:4" ht="14.4">
       <c r="A90" s="10" t="s">
-        <v>602</v>
+        <v>555</v>
       </c>
       <c r="B90"/>
       <c r="C90" s="1">
@@ -3599,7 +3458,7 @@
     </row>
     <row r="91" spans="1:4" ht="14.4">
       <c r="A91" s="10" t="s">
-        <v>603</v>
+        <v>556</v>
       </c>
       <c r="B91"/>
       <c r="C91" s="1">
@@ -3611,7 +3470,7 @@
     </row>
     <row r="92" spans="1:4" ht="14.4">
       <c r="A92" s="10" t="s">
-        <v>604</v>
+        <v>557</v>
       </c>
       <c r="B92"/>
       <c r="C92" s="1">
@@ -3623,7 +3482,7 @@
     </row>
     <row r="93" spans="1:4" ht="14.4">
       <c r="A93" s="10" t="s">
-        <v>605</v>
+        <v>558</v>
       </c>
       <c r="B93"/>
       <c r="C93" s="1">
@@ -3635,7 +3494,7 @@
     </row>
     <row r="94" spans="1:4" ht="14.4">
       <c r="A94" s="10" t="s">
-        <v>606</v>
+        <v>559</v>
       </c>
       <c r="B94"/>
       <c r="C94" s="1">
@@ -3647,7 +3506,7 @@
     </row>
     <row r="95" spans="1:4" ht="14.4">
       <c r="A95" s="10" t="s">
-        <v>607</v>
+        <v>560</v>
       </c>
       <c r="B95"/>
       <c r="C95" s="1">
@@ -3659,7 +3518,7 @@
     </row>
     <row r="96" spans="1:4" ht="14.4">
       <c r="A96" s="10" t="s">
-        <v>608</v>
+        <v>561</v>
       </c>
       <c r="B96"/>
       <c r="C96" s="1">
@@ -3671,7 +3530,7 @@
     </row>
     <row r="97" spans="1:4" ht="14.4">
       <c r="A97" s="9" t="s">
-        <v>609</v>
+        <v>562</v>
       </c>
       <c r="B97"/>
       <c r="C97" s="1">
@@ -3683,7 +3542,7 @@
     </row>
     <row r="98" spans="1:4" ht="14.4">
       <c r="A98" s="10" t="s">
-        <v>610</v>
+        <v>563</v>
       </c>
       <c r="B98"/>
       <c r="C98" s="1">
@@ -3695,7 +3554,7 @@
     </row>
     <row r="99" spans="1:4" ht="14.4">
       <c r="A99" s="10" t="s">
-        <v>611</v>
+        <v>564</v>
       </c>
       <c r="B99"/>
       <c r="C99" s="1">
@@ -3707,7 +3566,7 @@
     </row>
     <row r="100" spans="1:4" ht="14.4">
       <c r="A100" s="10" t="s">
-        <v>612</v>
+        <v>565</v>
       </c>
       <c r="B100"/>
       <c r="C100" s="1">
@@ -3719,7 +3578,7 @@
     </row>
     <row r="101" spans="1:4" ht="14.4">
       <c r="A101" s="10" t="s">
-        <v>613</v>
+        <v>566</v>
       </c>
       <c r="B101"/>
       <c r="C101" s="1">
@@ -3731,7 +3590,7 @@
     </row>
     <row r="102" spans="1:4" ht="14.4">
       <c r="A102" s="10" t="s">
-        <v>614</v>
+        <v>567</v>
       </c>
       <c r="B102"/>
       <c r="C102" s="1">
@@ -3743,7 +3602,7 @@
     </row>
     <row r="103" spans="1:4" ht="14.4">
       <c r="A103" s="10" t="s">
-        <v>615</v>
+        <v>568</v>
       </c>
       <c r="B103"/>
       <c r="C103" s="1">
@@ -3755,7 +3614,7 @@
     </row>
     <row r="104" spans="1:4" ht="14.4">
       <c r="A104" s="9" t="s">
-        <v>616</v>
+        <v>569</v>
       </c>
       <c r="B104"/>
       <c r="C104" s="1">
@@ -3767,7 +3626,7 @@
     </row>
     <row r="105" spans="1:4" ht="14.4">
       <c r="A105" s="10" t="s">
-        <v>617</v>
+        <v>570</v>
       </c>
       <c r="B105"/>
       <c r="C105" s="1">
@@ -3779,7 +3638,7 @@
     </row>
     <row r="106" spans="1:4" ht="14.4">
       <c r="A106" s="10" t="s">
-        <v>618</v>
+        <v>571</v>
       </c>
       <c r="B106"/>
       <c r="C106" s="1">
@@ -3791,7 +3650,7 @@
     </row>
     <row r="107" spans="1:4" ht="14.4">
       <c r="A107" s="10" t="s">
-        <v>619</v>
+        <v>572</v>
       </c>
       <c r="B107"/>
       <c r="C107" s="1">
@@ -3803,7 +3662,7 @@
     </row>
     <row r="108" spans="1:4" ht="14.4">
       <c r="A108" s="10" t="s">
-        <v>620</v>
+        <v>573</v>
       </c>
       <c r="B108"/>
       <c r="C108" s="1">
@@ -3815,7 +3674,7 @@
     </row>
     <row r="109" spans="1:4" ht="14.4">
       <c r="A109" s="10" t="s">
-        <v>621</v>
+        <v>574</v>
       </c>
       <c r="B109"/>
       <c r="C109" s="1">
@@ -3827,7 +3686,7 @@
     </row>
     <row r="110" spans="1:4" ht="14.4">
       <c r="A110" s="10" t="s">
-        <v>622</v>
+        <v>575</v>
       </c>
       <c r="B110"/>
       <c r="C110" s="1">
@@ -3839,7 +3698,7 @@
     </row>
     <row r="111" spans="1:4" ht="14.4">
       <c r="A111" s="9" t="s">
-        <v>623</v>
+        <v>576</v>
       </c>
       <c r="B111"/>
       <c r="C111" s="1">
@@ -3851,7 +3710,7 @@
     </row>
     <row r="112" spans="1:4" ht="14.4">
       <c r="A112" s="10" t="s">
-        <v>624</v>
+        <v>577</v>
       </c>
       <c r="B112"/>
       <c r="C112" s="1">
@@ -3863,7 +3722,7 @@
     </row>
     <row r="113" spans="1:4" ht="14.4">
       <c r="A113" s="10" t="s">
-        <v>625</v>
+        <v>578</v>
       </c>
       <c r="B113"/>
       <c r="C113" s="1">
@@ -3875,7 +3734,7 @@
     </row>
     <row r="114" spans="1:4" ht="14.4">
       <c r="A114" s="10" t="s">
-        <v>626</v>
+        <v>579</v>
       </c>
       <c r="B114"/>
       <c r="C114" s="1">
@@ -3887,7 +3746,7 @@
     </row>
     <row r="115" spans="1:4" ht="14.4">
       <c r="A115" s="10" t="s">
-        <v>627</v>
+        <v>580</v>
       </c>
       <c r="B115"/>
       <c r="C115" s="1">
@@ -3899,7 +3758,7 @@
     </row>
     <row r="116" spans="1:4" ht="14.4">
       <c r="A116" s="10" t="s">
-        <v>628</v>
+        <v>581</v>
       </c>
       <c r="B116"/>
       <c r="C116" s="1">
@@ -3911,7 +3770,7 @@
     </row>
     <row r="117" spans="1:4" ht="14.4">
       <c r="A117" s="10" t="s">
-        <v>629</v>
+        <v>582</v>
       </c>
       <c r="B117"/>
       <c r="C117" s="1">
@@ -3923,7 +3782,7 @@
     </row>
     <row r="118" spans="1:4" ht="14.4">
       <c r="A118" s="10" t="s">
-        <v>630</v>
+        <v>583</v>
       </c>
       <c r="B118"/>
       <c r="C118" s="1">
@@ -3935,7 +3794,7 @@
     </row>
     <row r="119" spans="1:4" ht="14.4">
       <c r="A119" s="10" t="s">
-        <v>631</v>
+        <v>584</v>
       </c>
       <c r="B119"/>
       <c r="C119" s="1">
@@ -3947,7 +3806,7 @@
     </row>
     <row r="120" spans="1:4" ht="14.4">
       <c r="A120" s="10" t="s">
-        <v>632</v>
+        <v>585</v>
       </c>
       <c r="B120"/>
       <c r="C120" s="1">
@@ -3959,7 +3818,7 @@
     </row>
     <row r="121" spans="1:4" ht="14.4">
       <c r="A121" s="10" t="s">
-        <v>633</v>
+        <v>586</v>
       </c>
       <c r="B121"/>
       <c r="C121" s="1">
@@ -3971,7 +3830,7 @@
     </row>
     <row r="122" spans="1:4" ht="14.4">
       <c r="A122" s="10" t="s">
-        <v>516</v>
+        <v>469</v>
       </c>
       <c r="B122"/>
       <c r="C122" s="1">
@@ -4045,1067 +3904,973 @@
     </row>
     <row r="130" spans="1:4" ht="14.4">
       <c r="A130" s="7" t="s">
-        <v>142</v>
+        <v>95</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="14.4">
       <c r="A131" s="8" t="s">
-        <v>141</v>
+        <v>94</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="14.4">
       <c r="A132" s="7" t="s">
-        <v>140</v>
+        <v>93</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="14.4">
       <c r="A133" s="7" t="s">
-        <v>139</v>
+        <v>92</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="14.4">
       <c r="A134" s="7" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="14.4">
       <c r="A135" s="7" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="14.4">
       <c r="A136" s="8" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="14.4">
       <c r="A137" s="7" t="s">
-        <v>135</v>
+        <v>88</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="14.4">
       <c r="A138" s="7" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="14.4">
       <c r="A139" s="7" t="s">
-        <v>133</v>
+        <v>86</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="14.4">
       <c r="A140" s="8" t="s">
-        <v>132</v>
+        <v>85</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="14.4">
       <c r="A141" s="7" t="s">
-        <v>131</v>
+        <v>84</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="14.4">
       <c r="A142" s="7" t="s">
-        <v>130</v>
+        <v>83</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="14.4">
       <c r="A143" s="7" t="s">
-        <v>129</v>
+        <v>82</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="14.4">
       <c r="A144" s="7" t="s">
-        <v>128</v>
+        <v>81</v>
       </c>
     </row>
     <row r="145" spans="1:1" ht="14.4">
       <c r="A145" s="7" t="s">
-        <v>127</v>
+        <v>80</v>
       </c>
     </row>
     <row r="146" spans="1:1" ht="14.4">
       <c r="A146" s="7" t="s">
-        <v>126</v>
+        <v>79</v>
       </c>
     </row>
     <row r="147" spans="1:1" ht="14.4">
       <c r="A147" s="7" t="s">
-        <v>125</v>
+        <v>78</v>
       </c>
     </row>
     <row r="148" spans="1:1" ht="14.4">
       <c r="A148" s="7" t="s">
-        <v>124</v>
+        <v>77</v>
       </c>
     </row>
     <row r="149" spans="1:1" ht="14.4">
       <c r="A149" s="8" t="s">
-        <v>123</v>
+        <v>76</v>
       </c>
     </row>
     <row r="150" spans="1:1" ht="14.4">
       <c r="A150" s="8" t="s">
-        <v>122</v>
+        <v>75</v>
       </c>
     </row>
     <row r="151" spans="1:1" ht="14.4">
       <c r="A151" s="7" t="s">
-        <v>121</v>
+        <v>74</v>
       </c>
     </row>
     <row r="152" spans="1:1" ht="14.4">
       <c r="A152" s="7" t="s">
-        <v>120</v>
+        <v>73</v>
       </c>
     </row>
     <row r="153" spans="1:1" ht="14.4">
       <c r="A153" s="8" t="s">
-        <v>119</v>
+        <v>72</v>
       </c>
     </row>
     <row r="154" spans="1:1" ht="14.4">
       <c r="A154" s="7" t="s">
-        <v>118</v>
+        <v>71</v>
       </c>
     </row>
     <row r="155" spans="1:1" ht="14.4">
       <c r="A155" s="7" t="s">
-        <v>117</v>
+        <v>70</v>
       </c>
     </row>
     <row r="156" spans="1:1" ht="14.4">
       <c r="A156" s="7" t="s">
-        <v>116</v>
+        <v>69</v>
       </c>
     </row>
     <row r="157" spans="1:1" ht="14.4">
       <c r="A157" s="8" t="s">
-        <v>115</v>
+        <v>68</v>
       </c>
     </row>
     <row r="158" spans="1:1" ht="14.4">
       <c r="A158" s="8" t="s">
-        <v>114</v>
+        <v>67</v>
       </c>
     </row>
     <row r="159" spans="1:1" ht="14.4">
       <c r="A159" s="7" t="s">
-        <v>113</v>
+        <v>66</v>
       </c>
     </row>
     <row r="160" spans="1:1" ht="14.4">
       <c r="A160" s="8" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
     </row>
     <row r="161" spans="1:1" ht="14.4">
       <c r="A161" s="8" t="s">
-        <v>111</v>
+        <v>64</v>
       </c>
     </row>
     <row r="162" spans="1:1" ht="14.4">
       <c r="A162" s="8" t="s">
-        <v>110</v>
+        <v>63</v>
       </c>
     </row>
     <row r="163" spans="1:1" ht="14.4">
       <c r="A163" s="7" t="s">
-        <v>109</v>
+        <v>62</v>
       </c>
     </row>
     <row r="164" spans="1:1" ht="14.4">
       <c r="A164" s="8" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
     </row>
     <row r="165" spans="1:1" ht="14.4">
       <c r="A165" s="7" t="s">
-        <v>107</v>
+        <v>60</v>
       </c>
     </row>
     <row r="166" spans="1:1" ht="14.4">
       <c r="A166" s="7" t="s">
-        <v>106</v>
+        <v>59</v>
       </c>
     </row>
     <row r="167" spans="1:1" ht="14.4">
       <c r="A167" s="7" t="s">
-        <v>105</v>
+        <v>58</v>
       </c>
     </row>
     <row r="168" spans="1:1" ht="14.4">
       <c r="A168" s="7" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
     </row>
     <row r="169" spans="1:1" ht="14.4">
       <c r="A169" s="7" t="s">
-        <v>103</v>
+        <v>56</v>
       </c>
     </row>
     <row r="170" spans="1:1" ht="14.4">
       <c r="A170" s="8" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
     </row>
     <row r="171" spans="1:1" ht="14.4">
       <c r="A171" s="7" t="s">
-        <v>101</v>
+        <v>54</v>
       </c>
     </row>
     <row r="172" spans="1:1" ht="14.4">
       <c r="A172" s="8" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
     </row>
     <row r="173" spans="1:1" ht="14.4">
       <c r="A173" s="7" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
     </row>
     <row r="174" spans="1:1" ht="14.4">
       <c r="A174" s="8" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
     </row>
     <row r="175" spans="1:1" ht="14.4">
       <c r="A175" s="7" t="s">
-        <v>97</v>
+        <v>50</v>
       </c>
     </row>
     <row r="176" spans="1:1" ht="14.4">
       <c r="A176" s="7" t="s">
-        <v>96</v>
+        <v>49</v>
       </c>
     </row>
     <row r="177" spans="1:1" ht="14.4">
       <c r="A177" s="7" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
     </row>
     <row r="178" spans="1:1" ht="14.4">
       <c r="A178" s="7" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
     </row>
     <row r="179" spans="1:1" ht="14.4">
       <c r="A179" s="8" t="s">
-        <v>93</v>
+        <v>46</v>
       </c>
     </row>
     <row r="180" spans="1:1" ht="14.4">
       <c r="A180" s="7" t="s">
-        <v>92</v>
+        <v>45</v>
       </c>
     </row>
     <row r="181" spans="1:1" ht="14.4">
       <c r="A181" s="8" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
     </row>
     <row r="182" spans="1:1" ht="14.4">
       <c r="A182" s="8" t="s">
-        <v>90</v>
+        <v>43</v>
       </c>
     </row>
     <row r="183" spans="1:1" ht="14.4">
       <c r="A183" s="8" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
     </row>
     <row r="184" spans="1:1" ht="14.4">
       <c r="A184" s="7" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
     </row>
     <row r="185" spans="1:1" ht="14.4">
       <c r="A185" s="7" t="s">
-        <v>87</v>
+        <v>40</v>
       </c>
     </row>
     <row r="186" spans="1:1" ht="14.4">
       <c r="A186" s="7" t="s">
-        <v>86</v>
+        <v>39</v>
       </c>
     </row>
     <row r="187" spans="1:1" ht="14.4">
       <c r="A187" s="7" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
     </row>
     <row r="188" spans="1:1" ht="14.4">
       <c r="A188" s="8" t="s">
-        <v>84</v>
+        <v>37</v>
       </c>
     </row>
     <row r="189" spans="1:1" ht="14.4">
       <c r="A189" s="8" t="s">
-        <v>83</v>
+        <v>36</v>
       </c>
     </row>
     <row r="190" spans="1:1" ht="14.4">
       <c r="A190" s="7" t="s">
-        <v>82</v>
+        <v>35</v>
       </c>
     </row>
     <row r="191" spans="1:1" ht="14.4">
       <c r="A191" s="7" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
     </row>
     <row r="192" spans="1:1" ht="14.4">
       <c r="A192" s="7" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
     </row>
     <row r="193" spans="1:1" ht="14.4">
       <c r="A193" s="8" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
     </row>
     <row r="194" spans="1:1" ht="14.4">
       <c r="A194" s="7" t="s">
-        <v>78</v>
+        <v>31</v>
       </c>
     </row>
     <row r="195" spans="1:1" ht="14.4">
       <c r="A195" s="8" t="s">
-        <v>77</v>
+        <v>30</v>
       </c>
     </row>
     <row r="196" spans="1:1" ht="14.4">
       <c r="A196" s="7" t="s">
-        <v>76</v>
+        <v>29</v>
       </c>
     </row>
     <row r="197" spans="1:1" ht="14.4">
       <c r="A197" s="7" t="s">
-        <v>75</v>
+        <v>28</v>
       </c>
     </row>
     <row r="198" spans="1:1" ht="14.4">
       <c r="A198" s="7" t="s">
-        <v>74</v>
+        <v>27</v>
       </c>
     </row>
     <row r="199" spans="1:1" ht="14.4">
       <c r="A199" s="7" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
     </row>
     <row r="200" spans="1:1" ht="14.4">
       <c r="A200" s="7" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
     </row>
     <row r="201" spans="1:1" ht="14.4">
       <c r="A201" s="7" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
     </row>
     <row r="202" spans="1:1" ht="14.4">
       <c r="A202" s="7" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
     </row>
     <row r="203" spans="1:1" ht="14.4">
       <c r="A203" s="8" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
     </row>
     <row r="204" spans="1:1" ht="14.4">
       <c r="A204" s="7" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
     </row>
     <row r="205" spans="1:1" ht="14.4">
       <c r="A205" s="7" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
     </row>
     <row r="206" spans="1:1" ht="14.4">
       <c r="A206" s="7" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
     </row>
     <row r="207" spans="1:1" ht="14.4">
       <c r="A207" s="8" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
     </row>
     <row r="208" spans="1:1" ht="14.4">
       <c r="A208" s="7" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
     </row>
     <row r="209" spans="1:1" ht="14.4">
       <c r="A209" s="7" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
     </row>
     <row r="210" spans="1:1" ht="14.4">
       <c r="A210" s="7" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
     </row>
     <row r="211" spans="1:1" ht="14.4">
       <c r="A211" s="6" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
     </row>
     <row r="212" spans="1:1" ht="14.4">
-      <c r="A212" s="3" t="s">
-        <v>60</v>
-      </c>
+      <c r="A212" s="3"/>
     </row>
     <row r="213" spans="1:1" ht="14.4">
-      <c r="A213" s="3" t="s">
-        <v>59</v>
-      </c>
+      <c r="A213" s="3"/>
     </row>
     <row r="214" spans="1:1" ht="14.4">
-      <c r="A214" s="3" t="s">
-        <v>58</v>
-      </c>
+      <c r="A214" s="3"/>
     </row>
     <row r="215" spans="1:1" ht="14.4">
-      <c r="A215" s="5" t="s">
-        <v>57</v>
-      </c>
+      <c r="A215" s="5"/>
     </row>
     <row r="216" spans="1:1" ht="14.4">
-      <c r="A216" s="3" t="s">
-        <v>56</v>
-      </c>
+      <c r="A216" s="3"/>
     </row>
     <row r="217" spans="1:1" ht="14.4">
-      <c r="A217" s="5" t="s">
-        <v>55</v>
-      </c>
+      <c r="A217" s="5"/>
     </row>
     <row r="218" spans="1:1" ht="14.4">
-      <c r="A218" s="5" t="s">
-        <v>54</v>
-      </c>
+      <c r="A218" s="5"/>
     </row>
     <row r="219" spans="1:1" ht="14.4">
-      <c r="A219" s="3" t="s">
-        <v>53</v>
-      </c>
+      <c r="A219" s="3"/>
     </row>
     <row r="220" spans="1:1" ht="14.4">
-      <c r="A220" s="3" t="s">
-        <v>52</v>
-      </c>
+      <c r="A220" s="3"/>
     </row>
     <row r="221" spans="1:1" ht="14.4">
-      <c r="A221" s="3" t="s">
-        <v>51</v>
-      </c>
+      <c r="A221" s="3"/>
     </row>
     <row r="222" spans="1:1" ht="14.4">
-      <c r="A222" s="5" t="s">
-        <v>50</v>
-      </c>
+      <c r="A222" s="5"/>
     </row>
     <row r="223" spans="1:1" ht="14.4">
-      <c r="A223" s="5" t="s">
-        <v>49</v>
-      </c>
+      <c r="A223" s="5"/>
     </row>
     <row r="224" spans="1:1" ht="14.4">
-      <c r="A224" s="5" t="s">
-        <v>48</v>
-      </c>
+      <c r="A224" s="5"/>
     </row>
     <row r="225" spans="1:1" ht="14.4">
-      <c r="A225" s="3" t="s">
-        <v>47</v>
-      </c>
+      <c r="A225" s="3"/>
     </row>
     <row r="226" spans="1:1" ht="14.4">
-      <c r="A226" s="5" t="s">
-        <v>46</v>
-      </c>
+      <c r="A226" s="5"/>
     </row>
     <row r="227" spans="1:1" ht="14.4">
-      <c r="A227" s="3" t="s">
-        <v>45</v>
-      </c>
+      <c r="A227" s="3"/>
     </row>
     <row r="228" spans="1:1" ht="14.4">
-      <c r="A228" s="3" t="s">
-        <v>44</v>
-      </c>
+      <c r="A228" s="3"/>
     </row>
     <row r="229" spans="1:1" ht="14.4">
-      <c r="A229" s="3" t="s">
-        <v>43</v>
-      </c>
+      <c r="A229" s="3"/>
     </row>
     <row r="230" spans="1:1" ht="14.4">
-      <c r="A230" s="3" t="s">
-        <v>42</v>
-      </c>
+      <c r="A230" s="3"/>
     </row>
     <row r="231" spans="1:1" ht="14.4">
-      <c r="A231" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="A231" s="5"/>
     </row>
     <row r="232" spans="1:1" ht="14.4">
-      <c r="A232" s="3" t="s">
-        <v>40</v>
+      <c r="A232" s="10" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="233" spans="1:1" ht="14.4">
-      <c r="A233" s="3" t="s">
-        <v>39</v>
-      </c>
+      <c r="A233" s="3"/>
     </row>
     <row r="234" spans="1:1" ht="14.4">
-      <c r="A234" s="3" t="s">
-        <v>38</v>
-      </c>
+      <c r="A234" s="3"/>
     </row>
     <row r="235" spans="1:1" ht="14.4">
-      <c r="A235" s="3" t="s">
-        <v>37</v>
-      </c>
+      <c r="A235" s="3"/>
     </row>
     <row r="236" spans="1:1" ht="14.4">
-      <c r="A236" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="A236" s="3"/>
     </row>
     <row r="237" spans="1:1" ht="14.4">
-      <c r="A237" s="5" t="s">
-        <v>35</v>
-      </c>
+      <c r="A237" s="5"/>
     </row>
     <row r="238" spans="1:1" ht="14.4">
-      <c r="A238" s="5" t="s">
-        <v>34</v>
-      </c>
+      <c r="A238" s="5"/>
     </row>
     <row r="239" spans="1:1" ht="14.4">
-      <c r="A239" s="5" t="s">
-        <v>33</v>
-      </c>
+      <c r="A239" s="5"/>
     </row>
     <row r="240" spans="1:1" ht="14.4">
-      <c r="A240" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="A240" s="3"/>
     </row>
     <row r="241" spans="1:1" ht="14.4">
-      <c r="A241" s="3" t="s">
-        <v>31</v>
-      </c>
+      <c r="A241" s="3"/>
     </row>
     <row r="242" spans="1:1" ht="14.4">
-      <c r="A242" s="5" t="s">
-        <v>30</v>
-      </c>
+      <c r="A242" s="5"/>
     </row>
     <row r="243" spans="1:1" ht="14.4">
-      <c r="A243" s="5" t="s">
-        <v>29</v>
-      </c>
+      <c r="A243" s="5"/>
     </row>
     <row r="244" spans="1:1" ht="14.4">
-      <c r="A244" s="3" t="s">
-        <v>28</v>
-      </c>
+      <c r="A244" s="3"/>
     </row>
     <row r="245" spans="1:1" ht="14.4">
-      <c r="A245" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="A245" s="3"/>
     </row>
     <row r="246" spans="1:1" ht="14.4">
-      <c r="A246" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="A246" s="3"/>
     </row>
     <row r="247" spans="1:1" ht="14.4">
-      <c r="A247" s="3" t="s">
-        <v>25</v>
-      </c>
+      <c r="A247" s="3"/>
     </row>
     <row r="248" spans="1:1" ht="14.4">
-      <c r="A248" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="A248" s="3"/>
     </row>
     <row r="249" spans="1:1" ht="14.4">
-      <c r="A249" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="A249" s="3"/>
     </row>
     <row r="250" spans="1:1" ht="14.4">
-      <c r="A250" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="A250" s="3"/>
     </row>
     <row r="251" spans="1:1" ht="14.4">
-      <c r="A251" s="3" t="s">
-        <v>21</v>
-      </c>
+      <c r="A251" s="3"/>
     </row>
     <row r="252" spans="1:1" ht="14.4">
-      <c r="A252" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="A252" s="3"/>
     </row>
     <row r="253" spans="1:1" ht="14.4">
-      <c r="A253" s="3" t="s">
-        <v>19</v>
-      </c>
+      <c r="A253" s="3"/>
     </row>
     <row r="254" spans="1:1" ht="14.4">
-      <c r="A254" s="3" t="s">
-        <v>18</v>
-      </c>
+      <c r="A254" s="3"/>
     </row>
     <row r="255" spans="1:1" ht="14.4">
-      <c r="A255" s="5" t="s">
-        <v>17</v>
-      </c>
+      <c r="A255" s="5"/>
     </row>
     <row r="256" spans="1:1" ht="14.4">
-      <c r="A256" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="A256" s="3"/>
     </row>
     <row r="257" spans="1:3" ht="14.4">
-      <c r="A257" s="4" t="s">
-        <v>15</v>
-      </c>
+      <c r="A257" s="4"/>
     </row>
     <row r="258" spans="1:3" ht="14.4">
-      <c r="A258" s="3" t="s">
-        <v>14</v>
-      </c>
+      <c r="A258" s="3"/>
     </row>
     <row r="259" spans="1:3" ht="14.4">
-      <c r="A259" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="A259" s="3"/>
     </row>
     <row r="260" spans="1:3">
       <c r="C260" s="1" t="s">
-        <v>143</v>
+        <v>96</v>
       </c>
     </row>
     <row r="261" spans="1:3" ht="14.4">
       <c r="A261" s="5" t="s">
-        <v>224</v>
+        <v>177</v>
       </c>
     </row>
     <row r="262" spans="1:3" ht="14.4">
       <c r="A262" s="5" t="s">
-        <v>223</v>
+        <v>176</v>
       </c>
     </row>
     <row r="263" spans="1:3" ht="14.4">
       <c r="A263" s="3" t="s">
-        <v>222</v>
+        <v>175</v>
       </c>
     </row>
     <row r="264" spans="1:3" ht="14.4">
       <c r="A264" s="3" t="s">
-        <v>221</v>
+        <v>174</v>
       </c>
     </row>
     <row r="265" spans="1:3" ht="14.4">
       <c r="A265" s="3" t="s">
-        <v>220</v>
+        <v>173</v>
       </c>
     </row>
     <row r="266" spans="1:3" ht="14.4">
       <c r="A266" s="3" t="s">
-        <v>219</v>
+        <v>172</v>
       </c>
     </row>
     <row r="267" spans="1:3" ht="14.4">
       <c r="A267" s="3" t="s">
-        <v>218</v>
+        <v>171</v>
       </c>
     </row>
     <row r="268" spans="1:3" ht="14.4">
       <c r="A268" s="5" t="s">
-        <v>217</v>
+        <v>170</v>
       </c>
     </row>
     <row r="269" spans="1:3" ht="14.4">
       <c r="A269" s="3" t="s">
-        <v>216</v>
+        <v>169</v>
       </c>
     </row>
     <row r="270" spans="1:3" ht="14.4">
       <c r="A270" s="3" t="s">
-        <v>215</v>
+        <v>168</v>
       </c>
     </row>
     <row r="271" spans="1:3" ht="14.4">
       <c r="A271" s="3" t="s">
-        <v>214</v>
+        <v>167</v>
       </c>
     </row>
     <row r="272" spans="1:3" ht="14.4">
       <c r="A272" s="5" t="s">
-        <v>213</v>
+        <v>166</v>
       </c>
     </row>
     <row r="273" spans="1:1" ht="14.4">
       <c r="A273" s="3" t="s">
-        <v>212</v>
+        <v>165</v>
       </c>
     </row>
     <row r="274" spans="1:1" ht="14.4">
       <c r="A274" s="5" t="s">
-        <v>211</v>
+        <v>164</v>
       </c>
     </row>
     <row r="275" spans="1:1" ht="14.4">
       <c r="A275" s="5" t="s">
-        <v>210</v>
+        <v>163</v>
       </c>
     </row>
     <row r="276" spans="1:1" ht="14.4">
       <c r="A276" s="3" t="s">
-        <v>209</v>
+        <v>162</v>
       </c>
     </row>
     <row r="277" spans="1:1" ht="14.4">
       <c r="A277" s="3" t="s">
-        <v>208</v>
+        <v>161</v>
       </c>
     </row>
     <row r="278" spans="1:1" ht="14.4">
       <c r="A278" s="3" t="s">
-        <v>207</v>
+        <v>160</v>
       </c>
     </row>
     <row r="279" spans="1:1" ht="14.4">
       <c r="A279" s="5" t="s">
-        <v>206</v>
+        <v>159</v>
       </c>
     </row>
     <row r="280" spans="1:1" ht="14.4">
       <c r="A280" s="5" t="s">
-        <v>205</v>
+        <v>158</v>
       </c>
     </row>
     <row r="281" spans="1:1" ht="14.4">
       <c r="A281" s="3" t="s">
-        <v>204</v>
+        <v>157</v>
       </c>
     </row>
     <row r="282" spans="1:1" ht="14.4">
       <c r="A282" s="3" t="s">
-        <v>203</v>
+        <v>156</v>
       </c>
     </row>
     <row r="283" spans="1:1" ht="14.4">
       <c r="A283" s="3" t="s">
-        <v>202</v>
+        <v>155</v>
       </c>
     </row>
     <row r="284" spans="1:1" ht="14.4">
       <c r="A284" s="3" t="s">
-        <v>201</v>
+        <v>154</v>
       </c>
     </row>
     <row r="285" spans="1:1" ht="14.4">
       <c r="A285" s="3" t="s">
-        <v>200</v>
+        <v>153</v>
       </c>
     </row>
     <row r="286" spans="1:1" ht="14.4">
       <c r="A286" s="5" t="s">
-        <v>199</v>
+        <v>152</v>
       </c>
     </row>
     <row r="287" spans="1:1" ht="14.4">
       <c r="A287" s="3" t="s">
-        <v>198</v>
+        <v>151</v>
       </c>
     </row>
     <row r="288" spans="1:1" ht="14.4">
       <c r="A288" s="3" t="s">
-        <v>197</v>
+        <v>150</v>
       </c>
     </row>
     <row r="289" spans="1:1" ht="14.4">
       <c r="A289" s="3" t="s">
-        <v>196</v>
+        <v>149</v>
       </c>
     </row>
     <row r="290" spans="1:1" ht="14.4">
       <c r="A290" s="3" t="s">
-        <v>195</v>
+        <v>148</v>
       </c>
     </row>
     <row r="291" spans="1:1" ht="14.4">
       <c r="A291" s="3" t="s">
-        <v>194</v>
+        <v>147</v>
       </c>
     </row>
     <row r="292" spans="1:1" ht="14.4">
       <c r="A292" s="5" t="s">
-        <v>193</v>
+        <v>146</v>
       </c>
     </row>
     <row r="293" spans="1:1" ht="14.4">
       <c r="A293" s="5" t="s">
-        <v>192</v>
+        <v>145</v>
       </c>
     </row>
     <row r="294" spans="1:1" ht="14.4">
       <c r="A294" s="3" t="s">
-        <v>191</v>
+        <v>144</v>
       </c>
     </row>
     <row r="295" spans="1:1" ht="14.4">
       <c r="A295" s="5" t="s">
-        <v>190</v>
+        <v>143</v>
       </c>
     </row>
     <row r="296" spans="1:1" ht="14.4">
       <c r="A296" s="3" t="s">
-        <v>189</v>
+        <v>142</v>
       </c>
     </row>
     <row r="297" spans="1:1" ht="14.4">
       <c r="A297" s="3" t="s">
-        <v>188</v>
+        <v>141</v>
       </c>
     </row>
     <row r="298" spans="1:1" ht="14.4">
       <c r="A298" s="3" t="s">
-        <v>187</v>
+        <v>140</v>
       </c>
     </row>
     <row r="299" spans="1:1" ht="14.4">
       <c r="A299" s="3" t="s">
-        <v>186</v>
+        <v>139</v>
       </c>
     </row>
     <row r="300" spans="1:1" ht="14.4">
       <c r="A300" s="3" t="s">
-        <v>185</v>
+        <v>138</v>
       </c>
     </row>
     <row r="301" spans="1:1" ht="14.4">
       <c r="A301" s="5" t="s">
-        <v>184</v>
+        <v>137</v>
       </c>
     </row>
     <row r="302" spans="1:1" ht="14.4">
       <c r="A302" s="3" t="s">
-        <v>183</v>
+        <v>136</v>
       </c>
     </row>
     <row r="303" spans="1:1" ht="14.4">
       <c r="A303" s="3" t="s">
-        <v>182</v>
+        <v>135</v>
       </c>
     </row>
     <row r="304" spans="1:1" ht="14.4">
       <c r="A304" s="3" t="s">
-        <v>181</v>
+        <v>134</v>
       </c>
     </row>
     <row r="305" spans="1:1" ht="14.4">
       <c r="A305" s="3" t="s">
-        <v>180</v>
+        <v>133</v>
       </c>
     </row>
     <row r="306" spans="1:1" ht="14.4">
       <c r="A306" s="3" t="s">
-        <v>179</v>
+        <v>132</v>
       </c>
     </row>
     <row r="307" spans="1:1" ht="14.4">
       <c r="A307" s="3" t="s">
-        <v>178</v>
+        <v>131</v>
       </c>
     </row>
     <row r="308" spans="1:1" ht="14.4">
       <c r="A308" s="3" t="s">
-        <v>177</v>
+        <v>130</v>
       </c>
     </row>
     <row r="309" spans="1:1" ht="14.4">
       <c r="A309" s="3" t="s">
-        <v>176</v>
+        <v>129</v>
       </c>
     </row>
     <row r="310" spans="1:1" ht="14.4">
       <c r="A310" s="5" t="s">
-        <v>175</v>
+        <v>128</v>
       </c>
     </row>
     <row r="311" spans="1:1" ht="14.4">
       <c r="A311" s="3" t="s">
-        <v>174</v>
+        <v>127</v>
       </c>
     </row>
     <row r="312" spans="1:1" ht="14.4">
       <c r="A312" s="5" t="s">
-        <v>173</v>
+        <v>126</v>
       </c>
     </row>
     <row r="313" spans="1:1" ht="14.4">
       <c r="A313" s="5" t="s">
-        <v>172</v>
+        <v>125</v>
       </c>
     </row>
     <row r="314" spans="1:1" ht="14.4">
       <c r="A314" s="5" t="s">
-        <v>171</v>
+        <v>124</v>
       </c>
     </row>
     <row r="315" spans="1:1" ht="14.4">
       <c r="A315" s="3" t="s">
-        <v>170</v>
+        <v>123</v>
       </c>
     </row>
     <row r="316" spans="1:1" ht="14.4">
       <c r="A316" s="3" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
     </row>
     <row r="317" spans="1:1" ht="14.4">
       <c r="A317" s="5" t="s">
-        <v>168</v>
+        <v>121</v>
       </c>
     </row>
     <row r="318" spans="1:1" ht="14.4">
       <c r="A318" s="3" t="s">
-        <v>167</v>
+        <v>120</v>
       </c>
     </row>
     <row r="319" spans="1:1" ht="14.4">
       <c r="A319" s="3" t="s">
-        <v>166</v>
+        <v>119</v>
       </c>
     </row>
     <row r="320" spans="1:1" ht="14.4">
       <c r="A320" s="3" t="s">
-        <v>165</v>
+        <v>118</v>
       </c>
     </row>
     <row r="321" spans="1:1" ht="14.4">
       <c r="A321" s="5" t="s">
-        <v>164</v>
+        <v>117</v>
       </c>
     </row>
     <row r="322" spans="1:1" ht="14.4">
       <c r="A322" s="5" t="s">
-        <v>163</v>
+        <v>116</v>
       </c>
     </row>
     <row r="323" spans="1:1" ht="14.4">
       <c r="A323" s="5" t="s">
-        <v>162</v>
+        <v>115</v>
       </c>
     </row>
     <row r="324" spans="1:1" ht="14.4">
       <c r="A324" s="3" t="s">
-        <v>161</v>
+        <v>114</v>
       </c>
     </row>
     <row r="325" spans="1:1" ht="14.4">
       <c r="A325" s="3" t="s">
-        <v>160</v>
+        <v>113</v>
       </c>
     </row>
     <row r="326" spans="1:1" ht="14.4">
       <c r="A326" s="3" t="s">
-        <v>159</v>
+        <v>112</v>
       </c>
     </row>
     <row r="327" spans="1:1" ht="14.4">
       <c r="A327" s="3" t="s">
-        <v>158</v>
+        <v>111</v>
       </c>
     </row>
     <row r="328" spans="1:1" ht="14.4">
       <c r="A328" s="3" t="s">
-        <v>157</v>
+        <v>110</v>
       </c>
     </row>
     <row r="329" spans="1:1" ht="14.4">
       <c r="A329" s="3" t="s">
-        <v>156</v>
+        <v>109</v>
       </c>
     </row>
     <row r="330" spans="1:1" ht="14.4">
       <c r="A330" s="5" t="s">
-        <v>155</v>
+        <v>108</v>
       </c>
     </row>
     <row r="331" spans="1:1" ht="14.4">
       <c r="A331" s="5" t="s">
-        <v>154</v>
+        <v>107</v>
       </c>
     </row>
     <row r="332" spans="1:1" ht="14.4">
       <c r="A332" s="3" t="s">
-        <v>153</v>
+        <v>106</v>
       </c>
     </row>
     <row r="333" spans="1:1" ht="14.4">
       <c r="A333" s="3" t="s">
-        <v>152</v>
+        <v>105</v>
       </c>
     </row>
     <row r="334" spans="1:1" ht="14.4">
       <c r="A334" s="3" t="s">
-        <v>151</v>
+        <v>104</v>
       </c>
     </row>
     <row r="335" spans="1:1" ht="14.4">
       <c r="A335" s="3" t="s">
-        <v>150</v>
+        <v>103</v>
       </c>
     </row>
     <row r="336" spans="1:1" ht="14.4">
       <c r="A336" s="5" t="s">
-        <v>149</v>
+        <v>102</v>
       </c>
     </row>
     <row r="337" spans="1:2" ht="14.4">
       <c r="A337" s="3" t="s">
-        <v>148</v>
+        <v>101</v>
       </c>
     </row>
     <row r="338" spans="1:2" ht="14.4">
       <c r="A338" s="3" t="s">
-        <v>147</v>
+        <v>100</v>
       </c>
     </row>
     <row r="339" spans="1:2" ht="14.4">
       <c r="A339" s="3" t="s">
-        <v>146</v>
+        <v>99</v>
       </c>
     </row>
     <row r="340" spans="1:2" ht="14.4">
       <c r="A340" s="3" t="s">
-        <v>145</v>
+        <v>98</v>
       </c>
     </row>
     <row r="341" spans="1:2" ht="14.4">
       <c r="A341" s="3" t="s">
-        <v>144</v>
+        <v>97</v>
       </c>
     </row>
     <row r="342" spans="1:2">
       <c r="B342" s="1" t="s">
-        <v>225</v>
+        <v>178</v>
       </c>
     </row>
     <row r="343" spans="1:2" ht="14.4">
@@ -5115,22 +4880,22 @@
     </row>
     <row r="344" spans="1:2" ht="14.4">
       <c r="A344" s="1" t="s">
-        <v>226</v>
+        <v>179</v>
       </c>
     </row>
     <row r="345" spans="1:2" ht="14.4">
       <c r="A345" s="1" t="s">
-        <v>227</v>
+        <v>180</v>
       </c>
     </row>
     <row r="346" spans="1:2" ht="14.4">
       <c r="A346" s="1" t="s">
-        <v>228</v>
+        <v>181</v>
       </c>
     </row>
     <row r="347" spans="1:2" ht="14.4">
       <c r="A347" s="1" t="s">
-        <v>229</v>
+        <v>182</v>
       </c>
     </row>
     <row r="348" spans="1:2" ht="14.4">
@@ -5140,7 +4905,7 @@
     </row>
     <row r="349" spans="1:2" ht="14.4">
       <c r="A349" s="1" t="s">
-        <v>230</v>
+        <v>183</v>
       </c>
     </row>
     <row r="350" spans="1:2" ht="14.4">
@@ -5155,7 +4920,7 @@
     </row>
     <row r="352" spans="1:2" ht="14.4">
       <c r="A352" s="1" t="s">
-        <v>231</v>
+        <v>184</v>
       </c>
     </row>
     <row r="353" spans="1:1" ht="14.4">
@@ -5165,7 +4930,7 @@
     </row>
     <row r="354" spans="1:1" ht="14.4">
       <c r="A354" s="1" t="s">
-        <v>232</v>
+        <v>185</v>
       </c>
     </row>
     <row r="355" spans="1:1" ht="14.4">
@@ -5175,12 +4940,12 @@
     </row>
     <row r="356" spans="1:1" ht="14.4">
       <c r="A356" s="1" t="s">
-        <v>233</v>
+        <v>186</v>
       </c>
     </row>
     <row r="357" spans="1:1" ht="14.4">
       <c r="A357" s="1" t="s">
-        <v>234</v>
+        <v>187</v>
       </c>
     </row>
     <row r="358" spans="1:1" ht="14.4">
@@ -5190,17 +4955,17 @@
     </row>
     <row r="359" spans="1:1" ht="14.4">
       <c r="A359" s="1" t="s">
-        <v>235</v>
+        <v>188</v>
       </c>
     </row>
     <row r="360" spans="1:1" ht="14.4">
       <c r="A360" s="1" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
     </row>
     <row r="361" spans="1:1" ht="14.4">
       <c r="A361" s="1" t="s">
-        <v>237</v>
+        <v>190</v>
       </c>
     </row>
     <row r="362" spans="1:1" ht="14.4">
@@ -5210,12 +4975,12 @@
     </row>
     <row r="363" spans="1:1" ht="14.4">
       <c r="A363" s="1" t="s">
-        <v>238</v>
+        <v>191</v>
       </c>
     </row>
     <row r="364" spans="1:1" ht="14.4">
       <c r="A364" s="1" t="s">
-        <v>239</v>
+        <v>192</v>
       </c>
     </row>
     <row r="365" spans="1:1" ht="14.4">
@@ -5230,12 +4995,12 @@
     </row>
     <row r="367" spans="1:1" ht="14.4">
       <c r="A367" s="1" t="s">
-        <v>240</v>
+        <v>193</v>
       </c>
     </row>
     <row r="368" spans="1:1" ht="14.4">
       <c r="A368" s="1" t="s">
-        <v>241</v>
+        <v>194</v>
       </c>
     </row>
     <row r="369" spans="1:1" ht="14.4">
@@ -5270,7 +5035,7 @@
     </row>
     <row r="375" spans="1:1" ht="14.4">
       <c r="A375" s="1" t="s">
-        <v>242</v>
+        <v>195</v>
       </c>
     </row>
     <row r="376" spans="1:1" ht="14.4">
@@ -5335,12 +5100,12 @@
     </row>
     <row r="388" spans="1:1" ht="14.4">
       <c r="A388" s="1" t="s">
-        <v>243</v>
+        <v>196</v>
       </c>
     </row>
     <row r="389" spans="1:1" ht="14.4">
       <c r="A389" s="1" t="s">
-        <v>244</v>
+        <v>197</v>
       </c>
     </row>
     <row r="390" spans="1:1" ht="14.4">
@@ -5385,22 +5150,22 @@
     </row>
     <row r="398" spans="1:1" ht="14.4">
       <c r="A398" s="1" t="s">
-        <v>245</v>
+        <v>198</v>
       </c>
     </row>
     <row r="399" spans="1:1" ht="14.4">
       <c r="A399" s="1" t="s">
-        <v>246</v>
+        <v>199</v>
       </c>
     </row>
     <row r="400" spans="1:1" ht="14.4">
       <c r="A400" s="1" t="s">
-        <v>247</v>
+        <v>200</v>
       </c>
     </row>
     <row r="401" spans="1:1" ht="14.4">
       <c r="A401" s="1" t="s">
-        <v>248</v>
+        <v>201</v>
       </c>
     </row>
     <row r="402" spans="1:1" ht="14.4">
@@ -5410,7 +5175,7 @@
     </row>
     <row r="403" spans="1:1" ht="14.4">
       <c r="A403" s="1" t="s">
-        <v>249</v>
+        <v>202</v>
       </c>
     </row>
     <row r="404" spans="1:1" ht="14.4">
@@ -5430,7 +5195,7 @@
     </row>
     <row r="407" spans="1:1" ht="14.4">
       <c r="A407" s="1" t="s">
-        <v>250</v>
+        <v>203</v>
       </c>
     </row>
     <row r="408" spans="1:1" ht="14.4">
@@ -5440,7 +5205,7 @@
     </row>
     <row r="409" spans="1:1" ht="14.4">
       <c r="A409" s="1" t="s">
-        <v>251</v>
+        <v>204</v>
       </c>
     </row>
     <row r="410" spans="1:1" ht="14.4">
@@ -5450,12 +5215,12 @@
     </row>
     <row r="411" spans="1:1" ht="14.4">
       <c r="A411" s="1" t="s">
-        <v>252</v>
+        <v>205</v>
       </c>
     </row>
     <row r="412" spans="1:1" ht="14.4">
       <c r="A412" s="1" t="s">
-        <v>253</v>
+        <v>206</v>
       </c>
     </row>
     <row r="413" spans="1:1" ht="14.4">
@@ -5465,7 +5230,7 @@
     </row>
     <row r="414" spans="1:1" ht="14.4">
       <c r="A414" s="1" t="s">
-        <v>254</v>
+        <v>207</v>
       </c>
     </row>
     <row r="415" spans="1:1" ht="14.4">
@@ -5485,7 +5250,7 @@
     </row>
     <row r="418" spans="1:1" ht="14.4">
       <c r="A418" s="1" t="s">
-        <v>255</v>
+        <v>208</v>
       </c>
     </row>
     <row r="419" spans="1:1" ht="14.4">
@@ -5515,7 +5280,7 @@
     </row>
     <row r="424" spans="1:1" ht="14.4">
       <c r="A424" s="1" t="s">
-        <v>256</v>
+        <v>209</v>
       </c>
     </row>
     <row r="425" spans="1:1" ht="14.4">
@@ -5545,7 +5310,7 @@
     </row>
     <row r="430" spans="1:1" ht="14.4">
       <c r="A430" s="1" t="s">
-        <v>257</v>
+        <v>210</v>
       </c>
     </row>
     <row r="431" spans="1:1" ht="14.4">
@@ -5560,1697 +5325,1697 @@
     </row>
     <row r="433" spans="1:2" ht="14.4">
       <c r="A433" s="1" t="s">
-        <v>258</v>
+        <v>211</v>
       </c>
     </row>
     <row r="434" spans="1:2" ht="14.4">
       <c r="A434" s="1" t="s">
-        <v>259</v>
+        <v>212</v>
       </c>
     </row>
     <row r="435" spans="1:2">
       <c r="B435" s="1" t="s">
-        <v>260</v>
+        <v>213</v>
       </c>
     </row>
     <row r="436" spans="1:2" ht="14.4">
       <c r="A436" s="10" t="s">
-        <v>261</v>
+        <v>214</v>
       </c>
     </row>
     <row r="437" spans="1:2" ht="14.4">
       <c r="A437" s="9" t="s">
-        <v>262</v>
+        <v>215</v>
       </c>
     </row>
     <row r="438" spans="1:2" ht="14.4">
       <c r="A438" s="9" t="s">
-        <v>263</v>
+        <v>216</v>
       </c>
     </row>
     <row r="439" spans="1:2" ht="14.4">
       <c r="A439" s="9" t="s">
-        <v>264</v>
+        <v>217</v>
       </c>
     </row>
     <row r="440" spans="1:2" ht="14.4">
       <c r="A440" s="10" t="s">
-        <v>265</v>
+        <v>218</v>
       </c>
     </row>
     <row r="441" spans="1:2" ht="14.4">
       <c r="A441" s="10" t="s">
-        <v>266</v>
+        <v>219</v>
       </c>
     </row>
     <row r="442" spans="1:2" ht="14.4">
       <c r="A442" s="10" t="s">
-        <v>267</v>
+        <v>220</v>
       </c>
     </row>
     <row r="443" spans="1:2" ht="14.4">
       <c r="A443" s="10" t="s">
-        <v>268</v>
+        <v>221</v>
       </c>
     </row>
     <row r="444" spans="1:2" ht="14.4">
       <c r="A444" s="10" t="s">
-        <v>265</v>
+        <v>218</v>
       </c>
     </row>
     <row r="445" spans="1:2" ht="14.4">
       <c r="A445" s="10" t="s">
-        <v>269</v>
+        <v>222</v>
       </c>
     </row>
     <row r="446" spans="1:2" ht="14.4">
       <c r="A446" s="9" t="s">
-        <v>270</v>
+        <v>223</v>
       </c>
     </row>
     <row r="447" spans="1:2" ht="14.4">
       <c r="A447" s="10" t="s">
-        <v>271</v>
+        <v>224</v>
       </c>
     </row>
     <row r="448" spans="1:2" ht="14.4">
       <c r="A448" s="10" t="s">
-        <v>271</v>
+        <v>224</v>
       </c>
     </row>
     <row r="449" spans="1:1" ht="14.4">
       <c r="A449" s="10" t="s">
-        <v>272</v>
+        <v>225</v>
       </c>
     </row>
     <row r="450" spans="1:1" ht="14.4">
       <c r="A450" s="10" t="s">
-        <v>273</v>
+        <v>226</v>
       </c>
     </row>
     <row r="451" spans="1:1" ht="14.4">
       <c r="A451" s="10" t="s">
-        <v>274</v>
+        <v>227</v>
       </c>
     </row>
     <row r="452" spans="1:1" ht="14.4">
       <c r="A452" s="9" t="s">
-        <v>275</v>
+        <v>228</v>
       </c>
     </row>
     <row r="453" spans="1:1" ht="14.4">
       <c r="A453" s="10" t="s">
-        <v>276</v>
+        <v>229</v>
       </c>
     </row>
     <row r="454" spans="1:1" ht="14.4">
       <c r="A454" s="9" t="s">
-        <v>277</v>
+        <v>230</v>
       </c>
     </row>
     <row r="455" spans="1:1" ht="14.4">
       <c r="A455" s="9" t="s">
-        <v>278</v>
+        <v>231</v>
       </c>
     </row>
     <row r="456" spans="1:1" ht="14.4">
       <c r="A456" s="10" t="s">
-        <v>279</v>
+        <v>232</v>
       </c>
     </row>
     <row r="457" spans="1:1" ht="14.4">
       <c r="A457" s="10" t="s">
-        <v>280</v>
+        <v>233</v>
       </c>
     </row>
     <row r="458" spans="1:1" ht="14.4">
       <c r="A458" s="9" t="s">
-        <v>281</v>
+        <v>234</v>
       </c>
     </row>
     <row r="459" spans="1:1" ht="14.4">
       <c r="A459" s="9" t="s">
-        <v>282</v>
+        <v>235</v>
       </c>
     </row>
     <row r="460" spans="1:1" ht="14.4">
       <c r="A460" s="10" t="s">
-        <v>283</v>
+        <v>236</v>
       </c>
     </row>
     <row r="461" spans="1:1" ht="14.4">
       <c r="A461" s="9" t="s">
-        <v>284</v>
+        <v>237</v>
       </c>
     </row>
     <row r="462" spans="1:1" ht="14.4">
       <c r="A462" s="9" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
     </row>
     <row r="463" spans="1:1" ht="14.4">
       <c r="A463" s="9" t="s">
-        <v>286</v>
+        <v>239</v>
       </c>
     </row>
     <row r="464" spans="1:1" ht="14.4">
       <c r="A464" s="9" t="s">
-        <v>287</v>
+        <v>240</v>
       </c>
     </row>
     <row r="465" spans="1:1" ht="14.4">
       <c r="A465" s="10" t="s">
-        <v>288</v>
+        <v>241</v>
       </c>
     </row>
     <row r="466" spans="1:1" ht="14.4">
       <c r="A466" s="9" t="s">
-        <v>289</v>
+        <v>242</v>
       </c>
     </row>
     <row r="467" spans="1:1" ht="14.4">
       <c r="A467" s="10" t="s">
-        <v>290</v>
+        <v>243</v>
       </c>
     </row>
     <row r="468" spans="1:1" ht="14.4">
       <c r="A468" s="10" t="s">
-        <v>291</v>
+        <v>244</v>
       </c>
     </row>
     <row r="469" spans="1:1" ht="14.4">
       <c r="A469" s="10" t="s">
-        <v>292</v>
+        <v>245</v>
       </c>
     </row>
     <row r="470" spans="1:1" ht="14.4">
       <c r="A470" s="10" t="s">
-        <v>293</v>
+        <v>246</v>
       </c>
     </row>
     <row r="471" spans="1:1" ht="14.4">
       <c r="A471" s="10" t="s">
-        <v>294</v>
+        <v>247</v>
       </c>
     </row>
     <row r="472" spans="1:1" ht="14.4">
       <c r="A472" s="10" t="s">
-        <v>295</v>
+        <v>248</v>
       </c>
     </row>
     <row r="473" spans="1:1" ht="14.4">
       <c r="A473" s="10" t="s">
-        <v>296</v>
+        <v>249</v>
       </c>
     </row>
     <row r="474" spans="1:1" ht="14.4">
       <c r="A474" s="10" t="s">
-        <v>297</v>
+        <v>250</v>
       </c>
     </row>
     <row r="475" spans="1:1" ht="14.4">
       <c r="A475" s="10" t="s">
-        <v>298</v>
+        <v>251</v>
       </c>
     </row>
     <row r="476" spans="1:1" ht="14.4">
       <c r="A476" s="10" t="s">
-        <v>299</v>
+        <v>252</v>
       </c>
     </row>
     <row r="477" spans="1:1" ht="14.4">
       <c r="A477" s="10" t="s">
-        <v>300</v>
+        <v>253</v>
       </c>
     </row>
     <row r="478" spans="1:1" ht="14.4">
       <c r="A478" s="10" t="s">
-        <v>301</v>
+        <v>254</v>
       </c>
     </row>
     <row r="479" spans="1:1" ht="14.4">
       <c r="A479" s="10" t="s">
-        <v>302</v>
+        <v>255</v>
       </c>
     </row>
     <row r="480" spans="1:1" ht="14.4">
       <c r="A480" s="10" t="s">
-        <v>303</v>
+        <v>256</v>
       </c>
     </row>
     <row r="481" spans="1:1" ht="14.4">
       <c r="A481" s="10" t="s">
-        <v>304</v>
+        <v>257</v>
       </c>
     </row>
     <row r="482" spans="1:1" ht="14.4">
       <c r="A482" s="10" t="s">
-        <v>305</v>
+        <v>258</v>
       </c>
     </row>
     <row r="483" spans="1:1" ht="14.4">
       <c r="A483" s="10" t="s">
-        <v>306</v>
+        <v>259</v>
       </c>
     </row>
     <row r="484" spans="1:1" ht="14.4">
       <c r="A484" s="9" t="s">
-        <v>307</v>
+        <v>260</v>
       </c>
     </row>
     <row r="485" spans="1:1" ht="14.4">
       <c r="A485" s="9" t="s">
-        <v>308</v>
+        <v>261</v>
       </c>
     </row>
     <row r="486" spans="1:1" ht="14.4">
       <c r="A486" s="10" t="s">
-        <v>309</v>
+        <v>262</v>
       </c>
     </row>
     <row r="487" spans="1:1" ht="14.4">
       <c r="A487" s="10" t="s">
-        <v>310</v>
+        <v>263</v>
       </c>
     </row>
     <row r="488" spans="1:1" ht="14.4">
       <c r="A488" s="9" t="s">
-        <v>311</v>
+        <v>264</v>
       </c>
     </row>
     <row r="489" spans="1:1" ht="14.4">
       <c r="A489" s="10" t="s">
-        <v>312</v>
+        <v>265</v>
       </c>
     </row>
     <row r="490" spans="1:1" ht="14.4">
       <c r="A490" s="9" t="s">
-        <v>313</v>
+        <v>266</v>
       </c>
     </row>
     <row r="491" spans="1:1" ht="14.4">
       <c r="A491" s="9" t="s">
-        <v>314</v>
+        <v>267</v>
       </c>
     </row>
     <row r="492" spans="1:1" ht="14.4">
       <c r="A492" s="10" t="s">
-        <v>315</v>
+        <v>268</v>
       </c>
     </row>
     <row r="493" spans="1:1" ht="14.4">
       <c r="A493" s="9" t="s">
-        <v>316</v>
+        <v>269</v>
       </c>
     </row>
     <row r="494" spans="1:1" ht="14.4">
       <c r="A494" s="10" t="s">
-        <v>317</v>
+        <v>270</v>
       </c>
     </row>
     <row r="495" spans="1:1" ht="14.4">
       <c r="A495" s="9" t="s">
-        <v>318</v>
+        <v>271</v>
       </c>
     </row>
     <row r="496" spans="1:1" ht="14.4">
       <c r="A496" s="9" t="s">
-        <v>319</v>
+        <v>272</v>
       </c>
     </row>
     <row r="497" spans="1:1" ht="14.4">
       <c r="A497" s="9" t="s">
-        <v>320</v>
+        <v>273</v>
       </c>
     </row>
     <row r="498" spans="1:1" ht="14.4">
       <c r="A498" s="9" t="s">
-        <v>321</v>
+        <v>274</v>
       </c>
     </row>
     <row r="499" spans="1:1" ht="14.4">
       <c r="A499" s="10" t="s">
-        <v>322</v>
+        <v>275</v>
       </c>
     </row>
     <row r="500" spans="1:1" ht="14.4">
       <c r="A500" s="9" t="s">
-        <v>323</v>
+        <v>276</v>
       </c>
     </row>
     <row r="501" spans="1:1" ht="14.4">
       <c r="A501" s="10" t="s">
-        <v>324</v>
+        <v>277</v>
       </c>
     </row>
     <row r="502" spans="1:1" ht="14.4">
       <c r="A502" s="10" t="s">
-        <v>325</v>
+        <v>278</v>
       </c>
     </row>
     <row r="503" spans="1:1" ht="14.4">
       <c r="A503" s="10" t="s">
-        <v>326</v>
+        <v>279</v>
       </c>
     </row>
     <row r="504" spans="1:1" ht="14.4">
       <c r="A504" s="10" t="s">
-        <v>327</v>
+        <v>280</v>
       </c>
     </row>
     <row r="505" spans="1:1" ht="14.4">
       <c r="A505" s="10" t="s">
-        <v>328</v>
+        <v>281</v>
       </c>
     </row>
     <row r="506" spans="1:1" ht="14.4">
       <c r="A506" s="10" t="s">
-        <v>329</v>
+        <v>282</v>
       </c>
     </row>
     <row r="507" spans="1:1" ht="14.4">
       <c r="A507" s="10" t="s">
-        <v>330</v>
+        <v>283</v>
       </c>
     </row>
     <row r="508" spans="1:1" ht="14.4">
       <c r="A508" s="10" t="s">
-        <v>331</v>
+        <v>284</v>
       </c>
     </row>
     <row r="509" spans="1:1" ht="14.4">
       <c r="A509" s="10" t="s">
-        <v>332</v>
+        <v>285</v>
       </c>
     </row>
     <row r="510" spans="1:1" ht="14.4">
       <c r="A510" s="9" t="s">
-        <v>333</v>
+        <v>286</v>
       </c>
     </row>
     <row r="511" spans="1:1" ht="14.4">
       <c r="A511" s="10" t="s">
-        <v>334</v>
+        <v>287</v>
       </c>
     </row>
     <row r="512" spans="1:1" ht="14.4">
       <c r="A512" s="10" t="s">
-        <v>335</v>
+        <v>288</v>
       </c>
     </row>
     <row r="513" spans="1:1" ht="14.4">
       <c r="A513" s="10" t="s">
-        <v>288</v>
+        <v>241</v>
       </c>
     </row>
     <row r="514" spans="1:1" ht="14.4">
       <c r="A514" s="10" t="s">
-        <v>261</v>
+        <v>214</v>
       </c>
     </row>
     <row r="515" spans="1:1" ht="14.4">
       <c r="A515" s="9" t="s">
-        <v>262</v>
+        <v>215</v>
       </c>
     </row>
     <row r="516" spans="1:1" ht="14.4">
       <c r="A516" s="9" t="s">
-        <v>263</v>
+        <v>216</v>
       </c>
     </row>
     <row r="517" spans="1:1" ht="14.4">
       <c r="A517" s="9" t="s">
-        <v>264</v>
+        <v>217</v>
       </c>
     </row>
     <row r="518" spans="1:1" ht="14.4">
       <c r="A518" s="10" t="s">
-        <v>265</v>
+        <v>218</v>
       </c>
     </row>
     <row r="519" spans="1:1" ht="14.4">
       <c r="A519" s="10" t="s">
-        <v>266</v>
+        <v>219</v>
       </c>
     </row>
     <row r="520" spans="1:1" ht="14.4">
       <c r="A520" s="10" t="s">
-        <v>267</v>
+        <v>220</v>
       </c>
     </row>
     <row r="521" spans="1:1" ht="14.4">
       <c r="A521" s="10" t="s">
-        <v>268</v>
+        <v>221</v>
       </c>
     </row>
     <row r="522" spans="1:1" ht="14.4">
       <c r="A522" s="10" t="s">
-        <v>265</v>
+        <v>218</v>
       </c>
     </row>
     <row r="523" spans="1:1" ht="14.4">
       <c r="A523" s="10" t="s">
-        <v>269</v>
+        <v>222</v>
       </c>
     </row>
     <row r="524" spans="1:1" ht="14.4">
       <c r="A524" s="9" t="s">
-        <v>270</v>
+        <v>223</v>
       </c>
     </row>
     <row r="525" spans="1:1" ht="14.4">
       <c r="A525" s="10" t="s">
-        <v>271</v>
+        <v>224</v>
       </c>
     </row>
     <row r="526" spans="1:1" ht="14.4">
       <c r="A526" s="10" t="s">
-        <v>271</v>
+        <v>224</v>
       </c>
     </row>
     <row r="527" spans="1:1" ht="14.4">
       <c r="A527" s="10" t="s">
-        <v>272</v>
+        <v>225</v>
       </c>
     </row>
     <row r="528" spans="1:1" ht="14.4">
       <c r="A528" s="10" t="s">
-        <v>273</v>
+        <v>226</v>
       </c>
     </row>
     <row r="529" spans="1:1" ht="14.4">
       <c r="A529" s="10" t="s">
-        <v>274</v>
+        <v>227</v>
       </c>
     </row>
     <row r="530" spans="1:1" ht="14.4">
       <c r="A530" s="9" t="s">
-        <v>275</v>
+        <v>228</v>
       </c>
     </row>
     <row r="531" spans="1:1" ht="14.4">
       <c r="A531" s="10" t="s">
-        <v>276</v>
+        <v>229</v>
       </c>
     </row>
     <row r="532" spans="1:1" ht="14.4">
       <c r="A532" s="9" t="s">
-        <v>277</v>
+        <v>230</v>
       </c>
     </row>
     <row r="533" spans="1:1" ht="14.4">
       <c r="A533" s="9" t="s">
-        <v>278</v>
+        <v>231</v>
       </c>
     </row>
     <row r="534" spans="1:1" ht="14.4">
       <c r="A534" s="10" t="s">
-        <v>279</v>
+        <v>232</v>
       </c>
     </row>
     <row r="535" spans="1:1" ht="14.4">
       <c r="A535" s="10" t="s">
-        <v>280</v>
+        <v>233</v>
       </c>
     </row>
     <row r="536" spans="1:1" ht="14.4">
       <c r="A536" s="9" t="s">
-        <v>281</v>
+        <v>234</v>
       </c>
     </row>
     <row r="537" spans="1:1" ht="14.4">
       <c r="A537" s="9" t="s">
-        <v>282</v>
+        <v>235</v>
       </c>
     </row>
     <row r="538" spans="1:1" ht="14.4">
       <c r="A538" s="10" t="s">
-        <v>283</v>
+        <v>236</v>
       </c>
     </row>
     <row r="539" spans="1:1" ht="14.4">
       <c r="A539" s="9" t="s">
-        <v>284</v>
+        <v>237</v>
       </c>
     </row>
     <row r="540" spans="1:1" ht="14.4">
       <c r="A540" s="9" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
     </row>
     <row r="541" spans="1:1" ht="14.4">
       <c r="A541" s="9" t="s">
-        <v>286</v>
+        <v>239</v>
       </c>
     </row>
     <row r="542" spans="1:1" ht="14.4">
       <c r="A542" s="9" t="s">
-        <v>287</v>
+        <v>240</v>
       </c>
     </row>
     <row r="543" spans="1:1" ht="14.4">
       <c r="A543" s="10" t="s">
-        <v>288</v>
+        <v>241</v>
       </c>
     </row>
     <row r="544" spans="1:1" ht="14.4">
       <c r="A544" s="9" t="s">
-        <v>289</v>
+        <v>242</v>
       </c>
     </row>
     <row r="545" spans="1:1" ht="14.4">
       <c r="A545" s="10" t="s">
-        <v>290</v>
+        <v>243</v>
       </c>
     </row>
     <row r="546" spans="1:1" ht="14.4">
       <c r="A546" s="10" t="s">
-        <v>291</v>
+        <v>244</v>
       </c>
     </row>
     <row r="547" spans="1:1" ht="14.4">
       <c r="A547" s="10" t="s">
-        <v>292</v>
+        <v>245</v>
       </c>
     </row>
     <row r="548" spans="1:1" ht="14.4">
       <c r="A548" s="10" t="s">
-        <v>293</v>
+        <v>246</v>
       </c>
     </row>
     <row r="549" spans="1:1" ht="14.4">
       <c r="A549" s="10" t="s">
-        <v>294</v>
+        <v>247</v>
       </c>
     </row>
     <row r="550" spans="1:1" ht="14.4">
       <c r="A550" s="10" t="s">
-        <v>295</v>
+        <v>248</v>
       </c>
     </row>
     <row r="551" spans="1:1" ht="14.4">
       <c r="A551" s="10" t="s">
-        <v>296</v>
+        <v>249</v>
       </c>
     </row>
     <row r="552" spans="1:1" ht="14.4">
       <c r="A552" s="10" t="s">
-        <v>297</v>
+        <v>250</v>
       </c>
     </row>
     <row r="553" spans="1:1" ht="14.4">
       <c r="A553" s="10" t="s">
-        <v>298</v>
+        <v>251</v>
       </c>
     </row>
     <row r="554" spans="1:1" ht="14.4">
       <c r="A554" s="10" t="s">
-        <v>299</v>
+        <v>252</v>
       </c>
     </row>
     <row r="555" spans="1:1" ht="14.4">
       <c r="A555" s="10" t="s">
-        <v>300</v>
+        <v>253</v>
       </c>
     </row>
     <row r="556" spans="1:1" ht="14.4">
       <c r="A556" s="10" t="s">
-        <v>301</v>
+        <v>254</v>
       </c>
     </row>
     <row r="557" spans="1:1" ht="14.4">
       <c r="A557" s="10" t="s">
-        <v>302</v>
+        <v>255</v>
       </c>
     </row>
     <row r="558" spans="1:1" ht="14.4">
       <c r="A558" s="10" t="s">
-        <v>303</v>
+        <v>256</v>
       </c>
     </row>
     <row r="559" spans="1:1" ht="14.4">
       <c r="A559" s="10" t="s">
-        <v>304</v>
+        <v>257</v>
       </c>
     </row>
     <row r="560" spans="1:1" ht="14.4">
       <c r="A560" s="10" t="s">
-        <v>305</v>
+        <v>258</v>
       </c>
     </row>
     <row r="561" spans="1:1" ht="14.4">
       <c r="A561" s="10" t="s">
-        <v>306</v>
+        <v>259</v>
       </c>
     </row>
     <row r="562" spans="1:1" ht="14.4">
       <c r="A562" s="9" t="s">
-        <v>307</v>
+        <v>260</v>
       </c>
     </row>
     <row r="563" spans="1:1" ht="14.4">
       <c r="A563" s="9" t="s">
-        <v>308</v>
+        <v>261</v>
       </c>
     </row>
     <row r="564" spans="1:1" ht="14.4">
       <c r="A564" s="10" t="s">
-        <v>309</v>
+        <v>262</v>
       </c>
     </row>
     <row r="565" spans="1:1" ht="14.4">
       <c r="A565" s="10" t="s">
-        <v>310</v>
+        <v>263</v>
       </c>
     </row>
     <row r="566" spans="1:1" ht="14.4">
       <c r="A566" s="9" t="s">
-        <v>311</v>
+        <v>264</v>
       </c>
     </row>
     <row r="567" spans="1:1" ht="14.4">
       <c r="A567" s="10" t="s">
-        <v>312</v>
+        <v>265</v>
       </c>
     </row>
     <row r="568" spans="1:1" ht="14.4">
       <c r="A568" s="9" t="s">
-        <v>313</v>
+        <v>266</v>
       </c>
     </row>
     <row r="569" spans="1:1" ht="14.4">
       <c r="A569" s="9" t="s">
-        <v>314</v>
+        <v>267</v>
       </c>
     </row>
     <row r="570" spans="1:1" ht="14.4">
       <c r="A570" s="10" t="s">
-        <v>315</v>
+        <v>268</v>
       </c>
     </row>
     <row r="571" spans="1:1" ht="14.4">
       <c r="A571" s="9" t="s">
-        <v>316</v>
+        <v>269</v>
       </c>
     </row>
     <row r="572" spans="1:1" ht="14.4">
       <c r="A572" s="10" t="s">
-        <v>317</v>
+        <v>270</v>
       </c>
     </row>
     <row r="573" spans="1:1" ht="14.4">
       <c r="A573" s="9" t="s">
-        <v>318</v>
+        <v>271</v>
       </c>
     </row>
     <row r="574" spans="1:1" ht="14.4">
       <c r="A574" s="9" t="s">
-        <v>319</v>
+        <v>272</v>
       </c>
     </row>
     <row r="575" spans="1:1" ht="14.4">
       <c r="A575" s="9" t="s">
-        <v>320</v>
+        <v>273</v>
       </c>
     </row>
     <row r="576" spans="1:1" ht="14.4">
       <c r="A576" s="9" t="s">
-        <v>321</v>
+        <v>274</v>
       </c>
     </row>
     <row r="577" spans="1:1" ht="14.4">
       <c r="A577" s="10" t="s">
-        <v>322</v>
+        <v>275</v>
       </c>
     </row>
     <row r="578" spans="1:1" ht="14.4">
       <c r="A578" s="9" t="s">
-        <v>323</v>
+        <v>276</v>
       </c>
     </row>
     <row r="579" spans="1:1" ht="14.4">
       <c r="A579" s="10" t="s">
-        <v>324</v>
+        <v>277</v>
       </c>
     </row>
     <row r="580" spans="1:1" ht="14.4">
       <c r="A580" s="10" t="s">
-        <v>325</v>
+        <v>278</v>
       </c>
     </row>
     <row r="581" spans="1:1" ht="14.4">
       <c r="A581" s="10" t="s">
-        <v>326</v>
+        <v>279</v>
       </c>
     </row>
     <row r="582" spans="1:1" ht="14.4">
       <c r="A582" s="10" t="s">
-        <v>327</v>
+        <v>280</v>
       </c>
     </row>
     <row r="583" spans="1:1" ht="14.4">
       <c r="A583" s="10" t="s">
-        <v>328</v>
+        <v>281</v>
       </c>
     </row>
     <row r="584" spans="1:1" ht="14.4">
       <c r="A584" s="10" t="s">
-        <v>329</v>
+        <v>282</v>
       </c>
     </row>
     <row r="585" spans="1:1" ht="14.4">
       <c r="A585" s="10" t="s">
-        <v>330</v>
+        <v>283</v>
       </c>
     </row>
     <row r="586" spans="1:1" ht="14.4">
       <c r="A586" s="10" t="s">
-        <v>331</v>
+        <v>284</v>
       </c>
     </row>
     <row r="587" spans="1:1" ht="14.4">
       <c r="A587" s="10" t="s">
-        <v>332</v>
+        <v>285</v>
       </c>
     </row>
     <row r="588" spans="1:1" ht="14.4">
       <c r="A588" s="9" t="s">
-        <v>333</v>
+        <v>286</v>
       </c>
     </row>
     <row r="589" spans="1:1" ht="14.4">
       <c r="A589" s="10" t="s">
-        <v>334</v>
+        <v>287</v>
       </c>
     </row>
     <row r="590" spans="1:1" ht="14.4">
       <c r="A590" s="10" t="s">
-        <v>335</v>
+        <v>288</v>
       </c>
     </row>
     <row r="591" spans="1:1" ht="14.4">
       <c r="A591" s="10" t="s">
-        <v>288</v>
+        <v>241</v>
       </c>
     </row>
     <row r="592" spans="1:1" ht="14.4">
       <c r="A592" s="10" t="s">
-        <v>513</v>
+        <v>466</v>
       </c>
     </row>
     <row r="593" spans="1:1" ht="14.4">
       <c r="A593" s="10" t="s">
-        <v>512</v>
+        <v>465</v>
       </c>
     </row>
     <row r="594" spans="1:1" ht="14.4">
       <c r="A594" s="9" t="s">
-        <v>511</v>
+        <v>464</v>
       </c>
     </row>
     <row r="595" spans="1:1" ht="14.4">
       <c r="A595" s="10" t="s">
-        <v>510</v>
+        <v>463</v>
       </c>
     </row>
     <row r="596" spans="1:1" ht="14.4">
       <c r="A596" s="10" t="s">
-        <v>509</v>
+        <v>462</v>
       </c>
     </row>
     <row r="597" spans="1:1" ht="14.4">
       <c r="A597" s="10" t="s">
-        <v>508</v>
+        <v>461</v>
       </c>
     </row>
     <row r="598" spans="1:1" ht="14.4">
       <c r="A598" s="9" t="s">
-        <v>507</v>
+        <v>460</v>
       </c>
     </row>
     <row r="599" spans="1:1" ht="14.4">
       <c r="A599" s="10" t="s">
-        <v>506</v>
+        <v>459</v>
       </c>
     </row>
     <row r="600" spans="1:1" ht="14.4">
       <c r="A600" s="10" t="s">
-        <v>505</v>
+        <v>458</v>
       </c>
     </row>
     <row r="601" spans="1:1" ht="14.4">
       <c r="A601" s="10" t="s">
-        <v>504</v>
+        <v>457</v>
       </c>
     </row>
     <row r="602" spans="1:1" ht="14.4">
       <c r="A602" s="9" t="s">
-        <v>503</v>
+        <v>456</v>
       </c>
     </row>
     <row r="603" spans="1:1" ht="14.4">
       <c r="A603" s="10" t="s">
-        <v>502</v>
+        <v>455</v>
       </c>
     </row>
     <row r="604" spans="1:1" ht="14.4">
       <c r="A604" s="10" t="s">
-        <v>501</v>
+        <v>454</v>
       </c>
     </row>
     <row r="605" spans="1:1" ht="14.4">
       <c r="A605" s="10" t="s">
-        <v>500</v>
+        <v>453</v>
       </c>
     </row>
     <row r="606" spans="1:1" ht="14.4">
       <c r="A606" s="10" t="s">
-        <v>499</v>
+        <v>452</v>
       </c>
     </row>
     <row r="607" spans="1:1" ht="14.4">
       <c r="A607" s="10" t="s">
-        <v>498</v>
+        <v>451</v>
       </c>
     </row>
     <row r="608" spans="1:1" ht="14.4">
       <c r="A608" s="10" t="s">
-        <v>497</v>
+        <v>450</v>
       </c>
     </row>
     <row r="609" spans="1:1" ht="14.4">
       <c r="A609" s="10" t="s">
-        <v>496</v>
+        <v>449</v>
       </c>
     </row>
     <row r="610" spans="1:1" ht="14.4">
       <c r="A610" s="9" t="s">
-        <v>495</v>
+        <v>448</v>
       </c>
     </row>
     <row r="611" spans="1:1" ht="14.4">
       <c r="A611" s="10" t="s">
-        <v>494</v>
+        <v>447</v>
       </c>
     </row>
     <row r="612" spans="1:1" ht="14.4">
       <c r="A612" s="10" t="s">
-        <v>493</v>
+        <v>446</v>
       </c>
     </row>
     <row r="613" spans="1:1" ht="14.4">
       <c r="A613" s="9" t="s">
-        <v>492</v>
+        <v>445</v>
       </c>
     </row>
     <row r="614" spans="1:1" ht="14.4">
       <c r="A614" s="10" t="s">
-        <v>491</v>
+        <v>444</v>
       </c>
     </row>
     <row r="615" spans="1:1" ht="14.4">
       <c r="A615" s="10" t="s">
-        <v>490</v>
+        <v>443</v>
       </c>
     </row>
     <row r="616" spans="1:1" ht="14.4">
       <c r="A616" s="9" t="s">
-        <v>489</v>
+        <v>442</v>
       </c>
     </row>
     <row r="617" spans="1:1" ht="14.4">
       <c r="A617" s="9" t="s">
-        <v>488</v>
+        <v>441</v>
       </c>
     </row>
     <row r="618" spans="1:1" ht="14.4">
       <c r="A618" s="10" t="s">
-        <v>487</v>
+        <v>440</v>
       </c>
     </row>
     <row r="619" spans="1:1" ht="14.4">
       <c r="A619" s="10" t="s">
-        <v>486</v>
+        <v>439</v>
       </c>
     </row>
     <row r="620" spans="1:1" ht="14.4">
       <c r="A620" s="9" t="s">
-        <v>485</v>
+        <v>438</v>
       </c>
     </row>
     <row r="621" spans="1:1" ht="14.4">
       <c r="A621" s="10" t="s">
-        <v>484</v>
+        <v>437</v>
       </c>
     </row>
     <row r="622" spans="1:1" ht="14.4">
       <c r="A622" s="10" t="s">
-        <v>483</v>
+        <v>436</v>
       </c>
     </row>
     <row r="623" spans="1:1" ht="14.4">
       <c r="A623" s="10" t="s">
-        <v>482</v>
+        <v>435</v>
       </c>
     </row>
     <row r="624" spans="1:1" ht="14.4">
       <c r="A624" s="10" t="s">
-        <v>481</v>
+        <v>434</v>
       </c>
     </row>
     <row r="625" spans="1:1" ht="14.4">
       <c r="A625" s="9" t="s">
-        <v>480</v>
+        <v>433</v>
       </c>
     </row>
     <row r="626" spans="1:1" ht="14.4">
       <c r="A626" s="10" t="s">
-        <v>479</v>
+        <v>432</v>
       </c>
     </row>
     <row r="627" spans="1:1" ht="14.4">
       <c r="A627" s="9" t="s">
-        <v>478</v>
+        <v>431</v>
       </c>
     </row>
     <row r="628" spans="1:1" ht="14.4">
       <c r="A628" s="10" t="s">
-        <v>477</v>
+        <v>430</v>
       </c>
     </row>
     <row r="629" spans="1:1" ht="14.4">
       <c r="A629" s="10" t="s">
-        <v>476</v>
+        <v>429</v>
       </c>
     </row>
     <row r="630" spans="1:1" ht="14.4">
       <c r="A630" s="9" t="s">
-        <v>475</v>
+        <v>428</v>
       </c>
     </row>
     <row r="631" spans="1:1" ht="14.4">
       <c r="A631" s="10" t="s">
-        <v>474</v>
+        <v>427</v>
       </c>
     </row>
     <row r="632" spans="1:1" ht="14.4">
       <c r="A632" s="10" t="s">
-        <v>473</v>
+        <v>426</v>
       </c>
     </row>
     <row r="633" spans="1:1" ht="14.4">
       <c r="A633" s="10" t="s">
-        <v>472</v>
+        <v>425</v>
       </c>
     </row>
     <row r="634" spans="1:1" ht="14.4">
       <c r="A634" s="10" t="s">
-        <v>471</v>
+        <v>424</v>
       </c>
     </row>
     <row r="635" spans="1:1" ht="14.4">
       <c r="A635" s="10" t="s">
-        <v>470</v>
+        <v>423</v>
       </c>
     </row>
     <row r="636" spans="1:1" ht="14.4">
       <c r="A636" s="9" t="s">
-        <v>469</v>
+        <v>422</v>
       </c>
     </row>
     <row r="637" spans="1:1" ht="14.4">
       <c r="A637" s="10" t="s">
-        <v>468</v>
+        <v>421</v>
       </c>
     </row>
     <row r="638" spans="1:1" ht="14.4">
       <c r="A638" s="10" t="s">
-        <v>467</v>
+        <v>420</v>
       </c>
     </row>
     <row r="639" spans="1:1" ht="14.4">
       <c r="A639" s="9" t="s">
-        <v>466</v>
+        <v>419</v>
       </c>
     </row>
     <row r="640" spans="1:1" ht="14.4">
       <c r="A640" s="9" t="s">
-        <v>465</v>
+        <v>418</v>
       </c>
     </row>
     <row r="641" spans="1:1" ht="14.4">
       <c r="A641" s="10" t="s">
-        <v>464</v>
+        <v>417</v>
       </c>
     </row>
     <row r="642" spans="1:1" ht="14.4">
       <c r="A642" s="10" t="s">
-        <v>463</v>
+        <v>416</v>
       </c>
     </row>
     <row r="643" spans="1:1" ht="14.4">
       <c r="A643" s="9" t="s">
-        <v>462</v>
+        <v>415</v>
       </c>
     </row>
     <row r="644" spans="1:1" ht="14.4">
       <c r="A644" s="9" t="s">
-        <v>461</v>
+        <v>414</v>
       </c>
     </row>
     <row r="645" spans="1:1" ht="14.4">
       <c r="A645" s="10" t="s">
-        <v>460</v>
+        <v>413</v>
       </c>
     </row>
     <row r="646" spans="1:1" ht="14.4">
       <c r="A646" s="9" t="s">
-        <v>459</v>
+        <v>412</v>
       </c>
     </row>
     <row r="647" spans="1:1" ht="14.4">
       <c r="A647" s="10" t="s">
-        <v>458</v>
+        <v>411</v>
       </c>
     </row>
     <row r="648" spans="1:1" ht="14.4">
       <c r="A648" s="9" t="s">
-        <v>457</v>
+        <v>410</v>
       </c>
     </row>
     <row r="649" spans="1:1" ht="14.4">
       <c r="A649" s="10" t="s">
-        <v>456</v>
+        <v>409</v>
       </c>
     </row>
     <row r="650" spans="1:1" ht="14.4">
       <c r="A650" s="10" t="s">
-        <v>455</v>
+        <v>408</v>
       </c>
     </row>
     <row r="651" spans="1:1" ht="14.4">
       <c r="A651" s="10" t="s">
-        <v>454</v>
+        <v>407</v>
       </c>
     </row>
     <row r="652" spans="1:1" ht="14.4">
       <c r="A652" s="9" t="s">
-        <v>453</v>
+        <v>406</v>
       </c>
     </row>
     <row r="653" spans="1:1" ht="14.4">
       <c r="A653" s="10" t="s">
-        <v>452</v>
+        <v>405</v>
       </c>
     </row>
     <row r="654" spans="1:1" ht="14.4">
       <c r="A654" s="10" t="s">
-        <v>451</v>
+        <v>404</v>
       </c>
     </row>
     <row r="655" spans="1:1" ht="14.4">
       <c r="A655" s="10" t="s">
-        <v>450</v>
+        <v>403</v>
       </c>
     </row>
     <row r="656" spans="1:1" ht="14.4">
       <c r="A656" s="9" t="s">
-        <v>449</v>
+        <v>402</v>
       </c>
     </row>
     <row r="657" spans="1:1" ht="14.4">
       <c r="A657" s="9" t="s">
-        <v>448</v>
+        <v>401</v>
       </c>
     </row>
     <row r="658" spans="1:1" ht="14.4">
       <c r="A658" s="10" t="s">
-        <v>447</v>
+        <v>400</v>
       </c>
     </row>
     <row r="659" spans="1:1" ht="14.4">
       <c r="A659" s="10" t="s">
-        <v>446</v>
+        <v>399</v>
       </c>
     </row>
     <row r="660" spans="1:1" ht="14.4">
       <c r="A660" s="10" t="s">
-        <v>445</v>
+        <v>398</v>
       </c>
     </row>
     <row r="661" spans="1:1" ht="14.4">
       <c r="A661" s="10" t="s">
-        <v>444</v>
+        <v>397</v>
       </c>
     </row>
     <row r="662" spans="1:1" ht="14.4">
       <c r="A662" s="10" t="s">
-        <v>443</v>
+        <v>396</v>
       </c>
     </row>
     <row r="663" spans="1:1" ht="14.4">
       <c r="A663" s="9" t="s">
-        <v>442</v>
+        <v>395</v>
       </c>
     </row>
     <row r="664" spans="1:1" ht="14.4">
       <c r="A664" s="10" t="s">
-        <v>441</v>
+        <v>394</v>
       </c>
     </row>
     <row r="665" spans="1:1" ht="14.4">
       <c r="A665" s="10" t="s">
-        <v>440</v>
+        <v>393</v>
       </c>
     </row>
     <row r="666" spans="1:1" ht="14.4">
       <c r="A666" s="10" t="s">
-        <v>439</v>
+        <v>392</v>
       </c>
     </row>
     <row r="667" spans="1:1" ht="14.4">
       <c r="A667" s="9" t="s">
-        <v>438</v>
+        <v>391</v>
       </c>
     </row>
     <row r="668" spans="1:1" ht="14.4">
       <c r="A668" s="10" t="s">
-        <v>336</v>
+        <v>289</v>
       </c>
     </row>
     <row r="669" spans="1:1" ht="14.4">
       <c r="A669" s="10" t="s">
-        <v>404</v>
+        <v>357</v>
       </c>
     </row>
     <row r="670" spans="1:1" ht="14.4">
       <c r="A670" s="10" t="s">
-        <v>437</v>
+        <v>390</v>
       </c>
     </row>
     <row r="671" spans="1:1" ht="14.4">
       <c r="A671" s="9" t="s">
-        <v>436</v>
+        <v>389</v>
       </c>
     </row>
     <row r="672" spans="1:1" ht="14.4">
       <c r="A672" s="9" t="s">
-        <v>435</v>
+        <v>388</v>
       </c>
     </row>
     <row r="673" spans="1:1" ht="14.4">
       <c r="A673" s="10" t="s">
-        <v>434</v>
+        <v>387</v>
       </c>
     </row>
     <row r="674" spans="1:1" ht="14.4">
       <c r="A674" s="10" t="s">
-        <v>433</v>
+        <v>386</v>
       </c>
     </row>
     <row r="675" spans="1:1" ht="14.4">
       <c r="A675" s="9" t="s">
-        <v>432</v>
+        <v>385</v>
       </c>
     </row>
     <row r="676" spans="1:1" ht="14.4">
       <c r="A676" s="10" t="s">
-        <v>431</v>
+        <v>384</v>
       </c>
     </row>
     <row r="677" spans="1:1" ht="14.4">
       <c r="A677" s="10" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
     </row>
     <row r="678" spans="1:1" ht="14.4">
       <c r="A678" s="10" t="s">
-        <v>429</v>
+        <v>382</v>
       </c>
     </row>
     <row r="679" spans="1:1" ht="14.4">
       <c r="A679" s="10" t="s">
-        <v>428</v>
+        <v>381</v>
       </c>
     </row>
     <row r="680" spans="1:1" ht="14.4">
       <c r="A680" s="10" t="s">
-        <v>427</v>
+        <v>380</v>
       </c>
     </row>
     <row r="681" spans="1:1" ht="14.4">
       <c r="A681" s="9" t="s">
-        <v>426</v>
+        <v>379</v>
       </c>
     </row>
     <row r="682" spans="1:1" ht="14.4">
       <c r="A682" s="9" t="s">
-        <v>425</v>
+        <v>378</v>
       </c>
     </row>
     <row r="683" spans="1:1" ht="14.4">
       <c r="A683" s="9" t="s">
-        <v>424</v>
+        <v>377</v>
       </c>
     </row>
     <row r="684" spans="1:1" ht="14.4">
       <c r="A684" s="9" t="s">
-        <v>423</v>
+        <v>376</v>
       </c>
     </row>
     <row r="685" spans="1:1" ht="14.4">
       <c r="A685" s="9" t="s">
-        <v>422</v>
+        <v>375</v>
       </c>
     </row>
     <row r="686" spans="1:1" ht="14.4">
       <c r="A686" s="9" t="s">
-        <v>421</v>
+        <v>374</v>
       </c>
     </row>
     <row r="687" spans="1:1" ht="14.4">
       <c r="A687" s="10" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
     </row>
     <row r="688" spans="1:1" ht="14.4">
       <c r="A688" s="10" t="s">
-        <v>419</v>
+        <v>372</v>
       </c>
     </row>
     <row r="689" spans="1:1" ht="14.4">
       <c r="A689" s="9" t="s">
-        <v>418</v>
+        <v>371</v>
       </c>
     </row>
     <row r="690" spans="1:1" ht="14.4">
       <c r="A690" s="9" t="s">
-        <v>417</v>
+        <v>370</v>
       </c>
     </row>
     <row r="691" spans="1:1" ht="14.4">
       <c r="A691" s="9" t="s">
-        <v>416</v>
+        <v>369</v>
       </c>
     </row>
     <row r="692" spans="1:1" ht="14.4">
       <c r="A692" s="10" t="s">
-        <v>415</v>
+        <v>368</v>
       </c>
     </row>
     <row r="693" spans="1:1" ht="14.4">
       <c r="A693" s="10" t="s">
-        <v>414</v>
+        <v>367</v>
       </c>
     </row>
     <row r="694" spans="1:1" ht="14.4">
       <c r="A694" s="9" t="s">
-        <v>413</v>
+        <v>366</v>
       </c>
     </row>
     <row r="695" spans="1:1" ht="14.4">
       <c r="A695" s="10" t="s">
-        <v>412</v>
+        <v>365</v>
       </c>
     </row>
     <row r="696" spans="1:1" ht="14.4">
       <c r="A696" s="10" t="s">
-        <v>411</v>
+        <v>364</v>
       </c>
     </row>
     <row r="697" spans="1:1" ht="14.4">
       <c r="A697" s="9" t="s">
-        <v>410</v>
+        <v>363</v>
       </c>
     </row>
     <row r="698" spans="1:1" ht="14.4">
       <c r="A698" s="10" t="s">
-        <v>409</v>
+        <v>362</v>
       </c>
     </row>
     <row r="699" spans="1:1" ht="14.4">
       <c r="A699" s="10" t="s">
-        <v>408</v>
+        <v>361</v>
       </c>
     </row>
     <row r="700" spans="1:1" ht="14.4">
       <c r="A700" s="10" t="s">
-        <v>407</v>
+        <v>360</v>
       </c>
     </row>
     <row r="701" spans="1:1" ht="14.4">
       <c r="A701" s="9" t="s">
-        <v>406</v>
+        <v>359</v>
       </c>
     </row>
     <row r="702" spans="1:1" ht="14.4">
       <c r="A702" s="9" t="s">
-        <v>405</v>
+        <v>358</v>
       </c>
     </row>
     <row r="703" spans="1:1" ht="14.4">
       <c r="A703" s="10" t="s">
-        <v>404</v>
+        <v>357</v>
       </c>
     </row>
     <row r="704" spans="1:1" ht="14.4">
       <c r="A704" s="10" t="s">
-        <v>403</v>
+        <v>356</v>
       </c>
     </row>
     <row r="705" spans="1:1" ht="14.4">
       <c r="A705" s="9" t="s">
-        <v>402</v>
+        <v>355</v>
       </c>
     </row>
     <row r="706" spans="1:1" ht="14.4">
       <c r="A706" s="10" t="s">
-        <v>401</v>
+        <v>354</v>
       </c>
     </row>
     <row r="707" spans="1:1" ht="14.4">
       <c r="A707" s="10" t="s">
-        <v>400</v>
+        <v>353</v>
       </c>
     </row>
     <row r="708" spans="1:1" ht="14.4">
       <c r="A708" s="10" t="s">
-        <v>399</v>
+        <v>352</v>
       </c>
     </row>
     <row r="709" spans="1:1" ht="14.4">
       <c r="A709" s="10" t="s">
-        <v>398</v>
+        <v>351</v>
       </c>
     </row>
     <row r="710" spans="1:1" ht="14.4">
       <c r="A710" s="10" t="s">
-        <v>397</v>
+        <v>350</v>
       </c>
     </row>
     <row r="711" spans="1:1" ht="14.4">
       <c r="A711" s="10" t="s">
-        <v>396</v>
+        <v>349</v>
       </c>
     </row>
     <row r="712" spans="1:1" ht="14.4">
       <c r="A712" s="9" t="s">
-        <v>395</v>
+        <v>348</v>
       </c>
     </row>
     <row r="713" spans="1:1" ht="14.4">
       <c r="A713" s="10" t="s">
-        <v>394</v>
+        <v>347</v>
       </c>
     </row>
     <row r="714" spans="1:1" ht="14.4">
       <c r="A714" s="9" t="s">
-        <v>393</v>
+        <v>346</v>
       </c>
     </row>
     <row r="715" spans="1:1" ht="14.4">
       <c r="A715" s="9" t="s">
-        <v>392</v>
+        <v>345</v>
       </c>
     </row>
     <row r="716" spans="1:1" ht="14.4">
       <c r="A716" s="10" t="s">
-        <v>391</v>
+        <v>344</v>
       </c>
     </row>
     <row r="717" spans="1:1" ht="14.4">
       <c r="A717" s="9" t="s">
-        <v>390</v>
+        <v>343</v>
       </c>
     </row>
     <row r="718" spans="1:1" ht="14.4">
       <c r="A718" s="10" t="s">
-        <v>389</v>
+        <v>342</v>
       </c>
     </row>
     <row r="719" spans="1:1" ht="14.4">
       <c r="A719" s="10" t="s">
-        <v>388</v>
+        <v>341</v>
       </c>
     </row>
     <row r="720" spans="1:1" ht="14.4">
       <c r="A720" s="10" t="s">
-        <v>387</v>
+        <v>340</v>
       </c>
     </row>
     <row r="721" spans="1:1" ht="14.4">
       <c r="A721" s="10" t="s">
-        <v>386</v>
+        <v>339</v>
       </c>
     </row>
     <row r="722" spans="1:1" ht="14.4">
       <c r="A722" s="10" t="s">
-        <v>385</v>
+        <v>338</v>
       </c>
     </row>
     <row r="723" spans="1:1" ht="14.4">
       <c r="A723" s="10" t="s">
-        <v>384</v>
+        <v>337</v>
       </c>
     </row>
     <row r="724" spans="1:1" ht="14.4">
       <c r="A724" s="10" t="s">
-        <v>383</v>
+        <v>336</v>
       </c>
     </row>
     <row r="725" spans="1:1" ht="14.4">
       <c r="A725" s="10" t="s">
-        <v>382</v>
+        <v>335</v>
       </c>
     </row>
     <row r="726" spans="1:1" ht="14.4">
       <c r="A726" s="10" t="s">
-        <v>381</v>
+        <v>334</v>
       </c>
     </row>
     <row r="727" spans="1:1" ht="14.4">
       <c r="A727" s="10" t="s">
-        <v>380</v>
+        <v>333</v>
       </c>
     </row>
     <row r="728" spans="1:1" ht="14.4">
       <c r="A728" s="9" t="s">
-        <v>379</v>
+        <v>332</v>
       </c>
     </row>
     <row r="729" spans="1:1" ht="14.4">
       <c r="A729" s="10" t="s">
-        <v>378</v>
+        <v>331</v>
       </c>
     </row>
     <row r="730" spans="1:1" ht="14.4">
       <c r="A730" s="10" t="s">
-        <v>377</v>
+        <v>330</v>
       </c>
     </row>
     <row r="731" spans="1:1" ht="14.4">
       <c r="A731" s="10" t="s">
-        <v>376</v>
+        <v>329</v>
       </c>
     </row>
     <row r="732" spans="1:1" ht="14.4">
       <c r="A732" s="10" t="s">
-        <v>375</v>
+        <v>328</v>
       </c>
     </row>
     <row r="733" spans="1:1" ht="14.4">
       <c r="A733" s="9" t="s">
-        <v>374</v>
+        <v>327</v>
       </c>
     </row>
     <row r="734" spans="1:1" ht="14.4">
       <c r="A734" s="10" t="s">
-        <v>373</v>
+        <v>326</v>
       </c>
     </row>
     <row r="735" spans="1:1" ht="14.4">
       <c r="A735" s="9" t="s">
-        <v>372</v>
+        <v>325</v>
       </c>
     </row>
     <row r="736" spans="1:1" ht="14.4">
       <c r="A736" s="9" t="s">
-        <v>371</v>
+        <v>324</v>
       </c>
     </row>
     <row r="737" spans="1:1" ht="14.4">
       <c r="A737" s="10" t="s">
-        <v>370</v>
+        <v>323</v>
       </c>
     </row>
     <row r="738" spans="1:1" ht="14.4">
       <c r="A738" s="9" t="s">
-        <v>369</v>
+        <v>322</v>
       </c>
     </row>
     <row r="739" spans="1:1" ht="14.4">
       <c r="A739" s="9" t="s">
-        <v>368</v>
+        <v>321</v>
       </c>
     </row>
     <row r="740" spans="1:1" ht="14.4">
       <c r="A740" s="10" t="s">
-        <v>367</v>
+        <v>320</v>
       </c>
     </row>
     <row r="741" spans="1:1" ht="14.4">
       <c r="A741" s="10" t="s">
-        <v>366</v>
+        <v>319</v>
       </c>
     </row>
     <row r="742" spans="1:1" ht="14.4">
       <c r="A742" s="9" t="s">
-        <v>365</v>
+        <v>318</v>
       </c>
     </row>
     <row r="743" spans="1:1" ht="14.4">
       <c r="A743" s="9" t="s">
-        <v>364</v>
+        <v>317</v>
       </c>
     </row>
     <row r="744" spans="1:1" ht="14.4">
       <c r="A744" s="10" t="s">
-        <v>363</v>
+        <v>316</v>
       </c>
     </row>
     <row r="745" spans="1:1" ht="14.4">
       <c r="A745" s="10" t="s">
-        <v>362</v>
+        <v>315</v>
       </c>
     </row>
     <row r="746" spans="1:1" ht="14.4">
       <c r="A746" s="10" t="s">
-        <v>361</v>
+        <v>314</v>
       </c>
     </row>
     <row r="747" spans="1:1" ht="14.4">
       <c r="A747" s="10" t="s">
-        <v>360</v>
+        <v>313</v>
       </c>
     </row>
     <row r="748" spans="1:1" ht="14.4">
       <c r="A748" s="10" t="s">
-        <v>359</v>
+        <v>312</v>
       </c>
     </row>
     <row r="749" spans="1:1" ht="14.4">
       <c r="A749" s="10" t="s">
-        <v>358</v>
+        <v>311</v>
       </c>
     </row>
     <row r="750" spans="1:1" ht="14.4">
       <c r="A750" s="9" t="s">
-        <v>357</v>
+        <v>310</v>
       </c>
     </row>
     <row r="751" spans="1:1" ht="14.4">
       <c r="A751" s="10" t="s">
-        <v>356</v>
+        <v>309</v>
       </c>
     </row>
     <row r="752" spans="1:1" ht="14.4">
       <c r="A752" s="10" t="s">
-        <v>355</v>
+        <v>308</v>
       </c>
     </row>
     <row r="753" spans="1:1" ht="14.4">
       <c r="A753" s="10" t="s">
-        <v>354</v>
+        <v>307</v>
       </c>
     </row>
     <row r="754" spans="1:1" ht="14.4">
       <c r="A754" s="10" t="s">
-        <v>353</v>
+        <v>306</v>
       </c>
     </row>
     <row r="755" spans="1:1" ht="14.4">
       <c r="A755" s="10" t="s">
-        <v>352</v>
+        <v>305</v>
       </c>
     </row>
     <row r="756" spans="1:1" ht="14.4">
       <c r="A756" s="9" t="s">
-        <v>351</v>
+        <v>304</v>
       </c>
     </row>
     <row r="757" spans="1:1" ht="14.4">
       <c r="A757" s="9" t="s">
-        <v>350</v>
+        <v>303</v>
       </c>
     </row>
     <row r="758" spans="1:1" ht="14.4">
       <c r="A758" s="9" t="s">
-        <v>349</v>
+        <v>302</v>
       </c>
     </row>
     <row r="759" spans="1:1" ht="14.4">
       <c r="A759" s="10" t="s">
-        <v>348</v>
+        <v>301</v>
       </c>
     </row>
     <row r="760" spans="1:1" ht="14.4">
       <c r="A760" s="10" t="s">
-        <v>347</v>
+        <v>300</v>
       </c>
     </row>
     <row r="761" spans="1:1" ht="14.4">
       <c r="A761" s="10" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="762" spans="1:1" ht="14.4">
       <c r="A762" s="10" t="s">
-        <v>345</v>
+        <v>298</v>
       </c>
     </row>
     <row r="763" spans="1:1" ht="14.4">
       <c r="A763" s="9" t="s">
-        <v>344</v>
+        <v>297</v>
       </c>
     </row>
     <row r="764" spans="1:1" ht="14.4">
       <c r="A764" s="9" t="s">
-        <v>343</v>
+        <v>296</v>
       </c>
     </row>
     <row r="765" spans="1:1" ht="14.4">
       <c r="A765" s="10" t="s">
-        <v>342</v>
+        <v>295</v>
       </c>
     </row>
     <row r="766" spans="1:1" ht="14.4">
       <c r="A766" s="10" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
     </row>
     <row r="767" spans="1:1" ht="14.4">
       <c r="A767" s="10" t="s">
-        <v>340</v>
+        <v>293</v>
       </c>
     </row>
     <row r="768" spans="1:1" ht="14.4">
       <c r="A768" s="10" t="s">
-        <v>339</v>
+        <v>292</v>
       </c>
     </row>
     <row r="769" spans="1:1" ht="14.4">
       <c r="A769" s="10" t="s">
-        <v>338</v>
+        <v>291</v>
       </c>
     </row>
     <row r="770" spans="1:1" ht="14.4">
       <c r="A770" s="10" t="s">
-        <v>337</v>
+        <v>290</v>
       </c>
     </row>
     <row r="771" spans="1:1" ht="14.4">
       <c r="A771" s="10" t="s">
-        <v>336</v>
+        <v>289</v>
       </c>
     </row>
     <row r="773" spans="1:1" ht="14.4">
@@ -7260,192 +7025,192 @@
     </row>
     <row r="774" spans="1:1" ht="14.4">
       <c r="A774" s="10" t="s">
-        <v>670</v>
+        <v>623</v>
       </c>
     </row>
     <row r="775" spans="1:1" ht="14.4">
       <c r="A775" s="9" t="s">
-        <v>669</v>
+        <v>622</v>
       </c>
     </row>
     <row r="776" spans="1:1" ht="14.4">
       <c r="A776" s="10" t="s">
-        <v>668</v>
+        <v>621</v>
       </c>
     </row>
     <row r="777" spans="1:1" ht="14.4">
       <c r="A777" s="10" t="s">
-        <v>667</v>
+        <v>620</v>
       </c>
     </row>
     <row r="778" spans="1:1" ht="14.4">
       <c r="A778" s="9" t="s">
-        <v>666</v>
+        <v>619</v>
       </c>
     </row>
     <row r="779" spans="1:1" ht="14.4">
       <c r="A779" s="10" t="s">
-        <v>665</v>
+        <v>618</v>
       </c>
     </row>
     <row r="780" spans="1:1" ht="14.4">
       <c r="A780" s="10" t="s">
-        <v>664</v>
+        <v>617</v>
       </c>
     </row>
     <row r="781" spans="1:1" ht="14.4">
       <c r="A781" s="10" t="s">
-        <v>663</v>
+        <v>616</v>
       </c>
     </row>
     <row r="782" spans="1:1" ht="14.4">
       <c r="A782" s="10" t="s">
-        <v>662</v>
+        <v>615</v>
       </c>
     </row>
     <row r="783" spans="1:1" ht="14.4">
       <c r="A783" s="10" t="s">
-        <v>661</v>
+        <v>614</v>
       </c>
     </row>
     <row r="784" spans="1:1" ht="14.4">
       <c r="A784" s="10" t="s">
-        <v>660</v>
+        <v>613</v>
       </c>
     </row>
     <row r="785" spans="1:1" ht="14.4">
       <c r="A785" s="10" t="s">
-        <v>659</v>
+        <v>612</v>
       </c>
     </row>
     <row r="786" spans="1:1" ht="14.4">
       <c r="A786" s="10" t="s">
-        <v>658</v>
+        <v>611</v>
       </c>
     </row>
     <row r="787" spans="1:1" ht="14.4">
       <c r="A787" s="9" t="s">
-        <v>657</v>
+        <v>610</v>
       </c>
     </row>
     <row r="788" spans="1:1" ht="14.4">
       <c r="A788" s="10" t="s">
-        <v>656</v>
+        <v>609</v>
       </c>
     </row>
     <row r="789" spans="1:1" ht="14.4">
       <c r="A789" s="10" t="s">
-        <v>655</v>
+        <v>608</v>
       </c>
     </row>
     <row r="790" spans="1:1" ht="14.4">
       <c r="A790" s="10" t="s">
-        <v>654</v>
+        <v>607</v>
       </c>
     </row>
     <row r="791" spans="1:1" ht="14.4">
       <c r="A791" s="10" t="s">
-        <v>653</v>
+        <v>606</v>
       </c>
     </row>
     <row r="792" spans="1:1" ht="14.4">
       <c r="A792" s="10" t="s">
-        <v>652</v>
+        <v>605</v>
       </c>
     </row>
     <row r="793" spans="1:1" ht="14.4">
       <c r="A793" s="9" t="s">
-        <v>651</v>
+        <v>604</v>
       </c>
     </row>
     <row r="794" spans="1:1" ht="14.4">
       <c r="A794" s="10" t="s">
-        <v>650</v>
+        <v>603</v>
       </c>
     </row>
     <row r="795" spans="1:1" ht="14.4">
       <c r="A795" s="9" t="s">
-        <v>649</v>
+        <v>602</v>
       </c>
     </row>
     <row r="796" spans="1:1" ht="14.4">
       <c r="A796" s="10" t="s">
-        <v>648</v>
+        <v>601</v>
       </c>
     </row>
     <row r="797" spans="1:1" ht="14.4">
       <c r="A797" s="10" t="s">
-        <v>647</v>
+        <v>600</v>
       </c>
     </row>
     <row r="798" spans="1:1" ht="14.4">
       <c r="A798" s="10" t="s">
-        <v>646</v>
+        <v>599</v>
       </c>
     </row>
     <row r="799" spans="1:1" ht="14.4">
       <c r="A799" s="10" t="s">
-        <v>645</v>
+        <v>598</v>
       </c>
     </row>
     <row r="800" spans="1:1" ht="14.4">
       <c r="A800" s="10" t="s">
-        <v>644</v>
+        <v>597</v>
       </c>
     </row>
     <row r="801" spans="1:2" ht="14.4">
       <c r="A801" s="9" t="s">
-        <v>643</v>
+        <v>596</v>
       </c>
     </row>
     <row r="802" spans="1:2" ht="14.4">
       <c r="A802" s="10" t="s">
-        <v>642</v>
+        <v>595</v>
       </c>
     </row>
     <row r="803" spans="1:2" ht="14.4">
       <c r="A803" s="10" t="s">
-        <v>641</v>
+        <v>594</v>
       </c>
     </row>
     <row r="804" spans="1:2" ht="14.4">
       <c r="A804" s="10" t="s">
-        <v>640</v>
+        <v>593</v>
       </c>
     </row>
     <row r="805" spans="1:2" ht="14.4">
       <c r="A805" s="10" t="s">
-        <v>639</v>
+        <v>592</v>
       </c>
     </row>
     <row r="806" spans="1:2" ht="14.4">
       <c r="A806" s="9" t="s">
-        <v>638</v>
+        <v>591</v>
       </c>
     </row>
     <row r="807" spans="1:2" ht="14.4">
       <c r="A807" s="10" t="s">
-        <v>637</v>
+        <v>590</v>
       </c>
     </row>
     <row r="808" spans="1:2" ht="14.4">
       <c r="A808" s="10" t="s">
-        <v>636</v>
+        <v>589</v>
       </c>
     </row>
     <row r="809" spans="1:2" ht="14.4">
       <c r="A809" s="9" t="s">
-        <v>635</v>
+        <v>588</v>
       </c>
     </row>
     <row r="810" spans="1:2" ht="14.4">
       <c r="A810" s="9" t="s">
-        <v>634</v>
+        <v>587</v>
       </c>
     </row>
     <row r="811" spans="1:2">
       <c r="B811" s="1" t="s">
-        <v>671</v>
+        <v>624</v>
       </c>
     </row>
   </sheetData>

--- a/on_the_way.xlsx
+++ b/on_the_way.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="733">
   <si>
     <t>Track</t>
   </si>
@@ -1891,6 +1891,330 @@
   </si>
   <si>
     <t>17.07.26</t>
+  </si>
+  <si>
+    <t>79018771858616</t>
+  </si>
+  <si>
+    <t>JT3170316758166</t>
+  </si>
+  <si>
+    <t>JT5505579885426</t>
+  </si>
+  <si>
+    <t>YT8887110380694</t>
+  </si>
+  <si>
+    <t>777427404579120</t>
+  </si>
+  <si>
+    <t>YT8886995204480</t>
+  </si>
+  <si>
+    <t>465509132293841</t>
+  </si>
+  <si>
+    <t>465509360373029</t>
+  </si>
+  <si>
+    <t>9817995428423</t>
+  </si>
+  <si>
+    <t>YT8887233456818</t>
+  </si>
+  <si>
+    <t>79122903499256</t>
+  </si>
+  <si>
+    <t>465496611398797</t>
+  </si>
+  <si>
+    <t>465508083387532</t>
+  </si>
+  <si>
+    <t>435270971367024</t>
+  </si>
+  <si>
+    <t>JT5504985858847</t>
+  </si>
+  <si>
+    <t>777426918928394</t>
+  </si>
+  <si>
+    <t>465499311973338</t>
+  </si>
+  <si>
+    <t>465506538373629</t>
+  </si>
+  <si>
+    <t>JT5505554534455</t>
+  </si>
+  <si>
+    <t>JT5504948709547</t>
+  </si>
+  <si>
+    <t>777427144833852</t>
+  </si>
+  <si>
+    <t>465507898194276</t>
+  </si>
+  <si>
+    <t>8244401142220</t>
+  </si>
+  <si>
+    <t>465514247899696</t>
+  </si>
+  <si>
+    <t>79122602798414</t>
+  </si>
+  <si>
+    <t>JT5504898039627</t>
+  </si>
+  <si>
+    <t>YT8886672643157</t>
+  </si>
+  <si>
+    <t>465506370218522</t>
+  </si>
+  <si>
+    <t>JT5504948725054</t>
+  </si>
+  <si>
+    <t>465503371714135</t>
+  </si>
+  <si>
+    <t>777426933997095</t>
+  </si>
+  <si>
+    <t>79122847348936</t>
+  </si>
+  <si>
+    <t>JT5505044125581</t>
+  </si>
+  <si>
+    <t>YT8887499234380</t>
+  </si>
+  <si>
+    <t>777427186380345</t>
+  </si>
+  <si>
+    <t>79122687747282</t>
+  </si>
+  <si>
+    <t>79122934811109</t>
+  </si>
+  <si>
+    <t>9818058273226</t>
+  </si>
+  <si>
+    <t>9818049917828</t>
+  </si>
+  <si>
+    <t>JT5505842113414</t>
+  </si>
+  <si>
+    <t>777426842208139</t>
+  </si>
+  <si>
+    <t>9818042527494</t>
+  </si>
+  <si>
+    <t>YT8887474259342</t>
+  </si>
+  <si>
+    <t>79122173802535</t>
+  </si>
+  <si>
+    <t>465507914083094</t>
+  </si>
+  <si>
+    <t>777427085931458</t>
+  </si>
+  <si>
+    <t>465514489030346</t>
+  </si>
+  <si>
+    <t>YT7632865575296</t>
+  </si>
+  <si>
+    <t>YT7632553701941</t>
+  </si>
+  <si>
+    <t>YT8886715622217</t>
+  </si>
+  <si>
+    <t>465502961247710</t>
+  </si>
+  <si>
+    <t>9817961258666</t>
+  </si>
+  <si>
+    <t>JT5505607338561</t>
+  </si>
+  <si>
+    <t>465514633151567</t>
+  </si>
+  <si>
+    <t>79122909191923</t>
+  </si>
+  <si>
+    <t>JT5505661002107</t>
+  </si>
+  <si>
+    <t>465506506662766</t>
+  </si>
+  <si>
+    <t>JT5505595034152</t>
+  </si>
+  <si>
+    <t>YT8886915531472</t>
+  </si>
+  <si>
+    <t>777426896912398</t>
+  </si>
+  <si>
+    <t>9818049060949</t>
+  </si>
+  <si>
+    <t>465506921261332</t>
+  </si>
+  <si>
+    <t>YT8886635357071</t>
+  </si>
+  <si>
+    <t>YT8887180283699</t>
+  </si>
+  <si>
+    <t>JT5505896621144</t>
+  </si>
+  <si>
+    <t>79122191195930</t>
+  </si>
+  <si>
+    <t>73717328976746</t>
+  </si>
+  <si>
+    <t>YT7632865500214</t>
+  </si>
+  <si>
+    <t>465492724651609</t>
+  </si>
+  <si>
+    <t>YT7633058282366</t>
+  </si>
+  <si>
+    <t>YT7632094972824</t>
+  </si>
+  <si>
+    <t>YT8885333846328</t>
+  </si>
+  <si>
+    <t>79122258818446</t>
+  </si>
+  <si>
+    <t>JT5505589725403</t>
+  </si>
+  <si>
+    <t>465508782347677</t>
+  </si>
+  <si>
+    <t>465507254476899</t>
+  </si>
+  <si>
+    <t>JT5505149288184</t>
+  </si>
+  <si>
+    <t>JT5505709983398</t>
+  </si>
+  <si>
+    <t>777427358319738</t>
+  </si>
+  <si>
+    <t>9817997645724</t>
+  </si>
+  <si>
+    <t>465500863123295</t>
+  </si>
+  <si>
+    <t>JT5504307726856</t>
+  </si>
+  <si>
+    <t>JT5504307209131</t>
+  </si>
+  <si>
+    <t>79122539705596</t>
+  </si>
+  <si>
+    <t>YT8886581615609</t>
+  </si>
+  <si>
+    <t>777426587500268</t>
+  </si>
+  <si>
+    <t>79122143971445</t>
+  </si>
+  <si>
+    <t>79122940553887</t>
+  </si>
+  <si>
+    <t>465509754781473</t>
+  </si>
+  <si>
+    <t>777427087637042</t>
+  </si>
+  <si>
+    <t>YT8885952562674</t>
+  </si>
+  <si>
+    <t>9818062333520</t>
+  </si>
+  <si>
+    <t>JT5506545455404</t>
+  </si>
+  <si>
+    <t>465509376161976</t>
+  </si>
+  <si>
+    <t>777427346837197</t>
+  </si>
+  <si>
+    <t>JT5505439599036</t>
+  </si>
+  <si>
+    <t>79122531626386</t>
+  </si>
+  <si>
+    <t>465502154312880</t>
+  </si>
+  <si>
+    <t>79122239505024</t>
+  </si>
+  <si>
+    <t>YT8886765884971</t>
+  </si>
+  <si>
+    <t>465508194640408</t>
+  </si>
+  <si>
+    <t>777426672106640</t>
+  </si>
+  <si>
+    <t>YT8886384406516</t>
+  </si>
+  <si>
+    <t>465503689108873</t>
+  </si>
+  <si>
+    <t>JT5504942213349</t>
+  </si>
+  <si>
+    <t>79122824512889</t>
+  </si>
+  <si>
+    <t>79122498404692</t>
+  </si>
+  <si>
+    <t>19.07.26</t>
   </si>
 </sst>
 </file>
@@ -2505,7 +2829,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D811"/>
+  <dimension ref="A1:D922"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="19.77734375" style="2" customWidth="1"/>
@@ -7211,6 +7535,561 @@
     <row r="811" spans="1:2">
       <c r="B811" s="1" t="s">
         <v>624</v>
+      </c>
+    </row>
+    <row r="812" spans="1:2" ht="14.4">
+      <c r="A812" s="10" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="813" spans="1:2" ht="14.4">
+      <c r="A813" s="10" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="814" spans="1:2" ht="14.4">
+      <c r="A814" s="9" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="815" spans="1:2" ht="14.4">
+      <c r="A815" s="10" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="816" spans="1:2" ht="14.4">
+      <c r="A816" s="9" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="817" spans="1:1" ht="14.4">
+      <c r="A817" s="10" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="818" spans="1:1" ht="14.4">
+      <c r="A818" s="10" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="819" spans="1:1" ht="14.4">
+      <c r="A819" s="9" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="820" spans="1:1" ht="14.4">
+      <c r="A820" s="9" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="821" spans="1:1" ht="14.4">
+      <c r="A821" s="10" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="822" spans="1:1" ht="14.4">
+      <c r="A822" s="10" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="823" spans="1:1" ht="14.4">
+      <c r="A823" s="10" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="824" spans="1:1" ht="14.4">
+      <c r="A824" s="9" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="825" spans="1:1" ht="14.4">
+      <c r="A825" s="10" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="826" spans="1:1" ht="14.4">
+      <c r="A826" s="10" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="827" spans="1:1" ht="14.4">
+      <c r="A827" s="9" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="828" spans="1:1" ht="14.4">
+      <c r="A828" s="10" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="829" spans="1:1" ht="14.4">
+      <c r="A829" s="9" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="830" spans="1:1" ht="14.4">
+      <c r="A830" s="10" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="831" spans="1:1" ht="14.4">
+      <c r="A831" s="10" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="832" spans="1:1" ht="14.4">
+      <c r="A832" s="10" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="833" spans="1:1" ht="14.4">
+      <c r="A833" s="10" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="834" spans="1:1" ht="14.4">
+      <c r="A834" s="10" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="835" spans="1:1" ht="14.4">
+      <c r="A835" s="9" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="836" spans="1:1" ht="14.4">
+      <c r="A836" s="10" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="837" spans="1:1" ht="14.4">
+      <c r="A837" s="9" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="838" spans="1:1" ht="14.4">
+      <c r="A838" s="9" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="839" spans="1:1" ht="14.4">
+      <c r="A839" s="10" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="840" spans="1:1" ht="14.4">
+      <c r="A840" s="10" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="841" spans="1:1" ht="14.4">
+      <c r="A841" s="10" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="842" spans="1:1" ht="14.4">
+      <c r="A842" s="9" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="843" spans="1:1" ht="14.4">
+      <c r="A843" s="9" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="844" spans="1:1" ht="14.4">
+      <c r="A844" s="10" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="845" spans="1:1" ht="14.4">
+      <c r="A845" s="10" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="846" spans="1:1" ht="14.4">
+      <c r="A846" s="9" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="847" spans="1:1" ht="14.4">
+      <c r="A847" s="10" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="848" spans="1:1" ht="14.4">
+      <c r="A848" s="9" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="849" spans="1:1" ht="14.4">
+      <c r="A849" s="9" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="850" spans="1:1" ht="14.4">
+      <c r="A850" s="9" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="851" spans="1:1" ht="14.4">
+      <c r="A851" s="10" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="852" spans="1:1" ht="14.4">
+      <c r="A852" s="9" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="853" spans="1:1" ht="14.4">
+      <c r="A853" s="10" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="854" spans="1:1" ht="14.4">
+      <c r="A854" s="10" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="855" spans="1:1" ht="14.4">
+      <c r="A855" s="9" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="856" spans="1:1" ht="14.4">
+      <c r="A856" s="9" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="857" spans="1:1" ht="14.4">
+      <c r="A857" s="9" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="858" spans="1:1" ht="14.4">
+      <c r="A858" s="10" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="859" spans="1:1" ht="14.4">
+      <c r="A859" s="10" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="860" spans="1:1" ht="14.4">
+      <c r="A860" s="10" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="861" spans="1:1" ht="14.4">
+      <c r="A861" s="9" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="862" spans="1:1" ht="14.4">
+      <c r="A862" s="9" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="863" spans="1:1" ht="14.4">
+      <c r="A863" s="10" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="864" spans="1:1" ht="14.4">
+      <c r="A864" s="9" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="865" spans="1:1" ht="14.4">
+      <c r="A865" s="10" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="866" spans="1:1" ht="14.4">
+      <c r="A866" s="10" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="867" spans="1:1" ht="14.4">
+      <c r="A867" s="9" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="868" spans="1:1" ht="14.4">
+      <c r="A868" s="10" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="869" spans="1:1" ht="14.4">
+      <c r="A869" s="10" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="870" spans="1:1" ht="14.4">
+      <c r="A870" s="9" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="871" spans="1:1" ht="14.4">
+      <c r="A871" s="9" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="872" spans="1:1" ht="14.4">
+      <c r="A872" s="9" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="873" spans="1:1" ht="14.4">
+      <c r="A873" s="10" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="874" spans="1:1" ht="14.4">
+      <c r="A874" s="10" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="875" spans="1:1" ht="14.4">
+      <c r="A875" s="10" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="876" spans="1:1" ht="14.4">
+      <c r="A876" s="10" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="877" spans="1:1" ht="14.4">
+      <c r="A877" s="9" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="878" spans="1:1" ht="14.4">
+      <c r="A878" s="10" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="879" spans="1:1" ht="14.4">
+      <c r="A879" s="10" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="880" spans="1:1" ht="14.4">
+      <c r="A880" s="9" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="881" spans="1:1" ht="14.4">
+      <c r="A881" s="10" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="882" spans="1:1" ht="14.4">
+      <c r="A882" s="10" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="883" spans="1:1" ht="14.4">
+      <c r="A883" s="10" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="884" spans="1:1" ht="14.4">
+      <c r="A884" s="10" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="885" spans="1:1" ht="14.4">
+      <c r="A885" s="10" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="886" spans="1:1" ht="14.4">
+      <c r="A886" s="10" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="887" spans="1:1" ht="14.4">
+      <c r="A887" s="9" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="888" spans="1:1" ht="14.4">
+      <c r="A888" s="9" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="889" spans="1:1" ht="14.4">
+      <c r="A889" s="10" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="890" spans="1:1" ht="14.4">
+      <c r="A890" s="10" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="891" spans="1:1" ht="14.4">
+      <c r="A891" s="10" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="892" spans="1:1" ht="14.4">
+      <c r="A892" s="9" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="893" spans="1:1" ht="14.4">
+      <c r="A893" s="10" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="894" spans="1:1" ht="14.4">
+      <c r="A894" s="10" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="895" spans="1:1" ht="14.4">
+      <c r="A895" s="9" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="896" spans="1:1" ht="14.4">
+      <c r="A896" s="9" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="897" spans="1:1" ht="14.4">
+      <c r="A897" s="10" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="898" spans="1:1" ht="14.4">
+      <c r="A898" s="10" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="899" spans="1:1" ht="14.4">
+      <c r="A899" s="10" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="900" spans="1:1" ht="14.4">
+      <c r="A900" s="10" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="901" spans="1:1" ht="14.4">
+      <c r="A901" s="10" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="902" spans="1:1" ht="14.4">
+      <c r="A902" s="9" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="903" spans="1:1" ht="14.4">
+      <c r="A903" s="9" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="904" spans="1:1" ht="14.4">
+      <c r="A904" s="10" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="905" spans="1:1" ht="14.4">
+      <c r="A905" s="10" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="906" spans="1:1" ht="14.4">
+      <c r="A906" s="10" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="907" spans="1:1" ht="14.4">
+      <c r="A907" s="9" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="908" spans="1:1" ht="14.4">
+      <c r="A908" s="10" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="909" spans="1:1" ht="14.4">
+      <c r="A909" s="10" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="910" spans="1:1" ht="14.4">
+      <c r="A910" s="10" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="911" spans="1:1" ht="14.4">
+      <c r="A911" s="10" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="912" spans="1:1" ht="14.4">
+      <c r="A912" s="9" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="913" spans="1:2" ht="14.4">
+      <c r="A913" s="10" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="914" spans="1:2" ht="14.4">
+      <c r="A914" s="10" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="915" spans="1:2" ht="14.4">
+      <c r="A915" s="10" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="916" spans="1:2" ht="14.4">
+      <c r="A916" s="9" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="917" spans="1:2" ht="14.4">
+      <c r="A917" s="10" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="918" spans="1:2" ht="14.4">
+      <c r="A918" s="9" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="919" spans="1:2" ht="14.4">
+      <c r="A919" s="9" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="920" spans="1:2" ht="14.4">
+      <c r="A920" s="9" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="921" spans="1:2" ht="14.4">
+      <c r="A921" s="10" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="922" spans="1:2">
+      <c r="B922" s="1" t="s">
+        <v>732</v>
       </c>
     </row>
   </sheetData>

--- a/on_the_way.xlsx
+++ b/on_the_way.xlsx
@@ -16,261 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="643">
   <si>
     <t>Track</t>
   </si>
   <si>
     <t>465448988108738</t>
-  </si>
-  <si>
-    <t>465431595916185</t>
-  </si>
-  <si>
-    <t>79115778829822</t>
-  </si>
-  <si>
-    <t>773427894002509</t>
-  </si>
-  <si>
-    <t>9817488472301</t>
-  </si>
-  <si>
-    <t>JT5497902864629</t>
-  </si>
-  <si>
-    <t>79115217530969</t>
-  </si>
-  <si>
-    <t>465438148003260</t>
-  </si>
-  <si>
-    <t>9817400004337</t>
-  </si>
-  <si>
-    <t>JT5497309265696</t>
-  </si>
-  <si>
-    <t>465440833112815</t>
-  </si>
-  <si>
-    <t>465443562685094</t>
-  </si>
-  <si>
-    <t>777420761036545</t>
-  </si>
-  <si>
-    <t>9817406887127</t>
-  </si>
-  <si>
-    <t>79115160935146</t>
-  </si>
-  <si>
-    <t>465438121549440</t>
-  </si>
-  <si>
-    <t>777419598365458</t>
-  </si>
-  <si>
-    <t>JT3167641128678</t>
-  </si>
-  <si>
-    <t>777419937761545</t>
-  </si>
-  <si>
-    <t>JT5498008554176</t>
-  </si>
-  <si>
-    <t>79115423942776</t>
-  </si>
-  <si>
-    <t>777420736117016</t>
-  </si>
-  <si>
-    <t>9817515911466</t>
-  </si>
-  <si>
-    <t>YT8878768954500</t>
-  </si>
-  <si>
-    <t>JT5497412193995</t>
-  </si>
-  <si>
-    <t>465436556503490</t>
-  </si>
-  <si>
-    <t>777420344786652</t>
-  </si>
-  <si>
-    <t>465436248025772</t>
-  </si>
-  <si>
-    <t>777420036266214</t>
-  </si>
-  <si>
-    <t>YT8879801289410</t>
-  </si>
-  <si>
-    <t>JT5496862334701</t>
-  </si>
-  <si>
-    <t>YT8879664256136</t>
-  </si>
-  <si>
-    <t>9817390894601</t>
-  </si>
-  <si>
-    <t>YT8878968394212</t>
-  </si>
-  <si>
-    <t>79115259676892</t>
-  </si>
-  <si>
-    <t>79115339142391</t>
-  </si>
-  <si>
-    <t>79115778018962</t>
-  </si>
-  <si>
-    <t>79115562559722</t>
-  </si>
-  <si>
-    <t>YT8879654833161</t>
-  </si>
-  <si>
-    <t>79115875475609</t>
-  </si>
-  <si>
-    <t>YT8880224877818</t>
-  </si>
-  <si>
-    <t>79115618203299</t>
-  </si>
-  <si>
-    <t>YT8879492297615</t>
-  </si>
-  <si>
-    <t>9817413373378</t>
-  </si>
-  <si>
-    <t>777420502615652</t>
-  </si>
-  <si>
-    <t>465442166542045</t>
-  </si>
-  <si>
-    <t>9817444225906</t>
-  </si>
-  <si>
-    <t>777420511746482</t>
-  </si>
-  <si>
-    <t>JT5498240151291</t>
-  </si>
-  <si>
-    <t>465439549581166</t>
-  </si>
-  <si>
-    <t>YT8880516144853</t>
-  </si>
-  <si>
-    <t>JT5497763940837</t>
-  </si>
-  <si>
-    <t>YT8879719599548</t>
-  </si>
-  <si>
-    <t>9817507329843</t>
-  </si>
-  <si>
-    <t>YT8879250061555</t>
-  </si>
-  <si>
-    <t>JT5497935900101</t>
-  </si>
-  <si>
-    <t>777419489090424</t>
-  </si>
-  <si>
-    <t>777419981445223</t>
-  </si>
-  <si>
-    <t>777419765655499</t>
-  </si>
-  <si>
-    <t>YT8879455407277</t>
-  </si>
-  <si>
-    <t>9817409543990</t>
-  </si>
-  <si>
-    <t>9817405916045</t>
-  </si>
-  <si>
-    <t>JT5497337398636</t>
-  </si>
-  <si>
-    <t>JT5496612105825</t>
-  </si>
-  <si>
-    <t>465431628056949</t>
-  </si>
-  <si>
-    <t>465437677907712</t>
-  </si>
-  <si>
-    <t>79115529526722</t>
-  </si>
-  <si>
-    <t>9817416839635</t>
-  </si>
-  <si>
-    <t>9817420692647</t>
-  </si>
-  <si>
-    <t>79115132996630</t>
-  </si>
-  <si>
-    <t>9817455368726</t>
-  </si>
-  <si>
-    <t>465443092240324</t>
-  </si>
-  <si>
-    <t>YT8879556055276</t>
-  </si>
-  <si>
-    <t>79115622195645</t>
-  </si>
-  <si>
-    <t>9822575422831</t>
-  </si>
-  <si>
-    <t>9817439413482</t>
-  </si>
-  <si>
-    <t>YT8879522724737</t>
-  </si>
-  <si>
-    <t>9817417696535</t>
-  </si>
-  <si>
-    <t>9817424014641</t>
-  </si>
-  <si>
-    <t>465434996040715</t>
-  </si>
-  <si>
-    <t>9817411332059</t>
-  </si>
-  <si>
-    <t>JT5496867306346</t>
-  </si>
-  <si>
-    <t>77420713856011</t>
-  </si>
-  <si>
-    <t>26.06.26</t>
   </si>
   <si>
     <t>777422227310805</t>
@@ -2823,1014 +2574,1014 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>719</v>
+        <v>636</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="14.4">
       <c r="A2" s="9" t="s">
-        <v>453</v>
+        <v>370</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.4">
       <c r="A3" s="10" t="s">
-        <v>454</v>
+        <v>371</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="14.4">
       <c r="A4" s="10" t="s">
-        <v>455</v>
+        <v>372</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="14.4">
       <c r="A5" s="10" t="s">
-        <v>456</v>
+        <v>373</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="14.4">
       <c r="A6" s="10" t="s">
-        <v>457</v>
+        <v>374</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="14.4">
       <c r="A7" s="10" t="s">
-        <v>458</v>
+        <v>375</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="14.4">
       <c r="A8" s="10" t="s">
-        <v>459</v>
+        <v>376</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="14.4">
       <c r="A9" s="9" t="s">
-        <v>460</v>
+        <v>377</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="14.4">
       <c r="A10" s="10" t="s">
-        <v>461</v>
+        <v>378</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="14.4">
       <c r="A11" s="9" t="s">
-        <v>462</v>
+        <v>379</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="14.4">
       <c r="A12" s="9" t="s">
-        <v>463</v>
+        <v>380</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="14.4">
       <c r="A13" s="10" t="s">
-        <v>464</v>
+        <v>381</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="14.4">
       <c r="A14" s="10" t="s">
-        <v>465</v>
+        <v>382</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="14.4">
       <c r="A15" s="10" t="s">
-        <v>466</v>
+        <v>383</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="14.4">
       <c r="A16" s="10" t="s">
-        <v>467</v>
+        <v>384</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.4">
       <c r="A17" s="10" t="s">
-        <v>468</v>
+        <v>385</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="14.4">
       <c r="A18" s="9" t="s">
-        <v>469</v>
+        <v>386</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="14.4">
       <c r="A19" s="10" t="s">
-        <v>470</v>
+        <v>387</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="14.4">
       <c r="A20" s="10" t="s">
-        <v>471</v>
+        <v>388</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="14.4">
       <c r="A21" s="9" t="s">
-        <v>472</v>
+        <v>389</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="14.4">
       <c r="A22" s="10" t="s">
-        <v>473</v>
+        <v>390</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="14.4">
       <c r="A23" s="10" t="s">
-        <v>474</v>
+        <v>391</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="14.4">
       <c r="A24" s="10" t="s">
-        <v>475</v>
+        <v>392</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="14.4">
       <c r="A25" s="9" t="s">
-        <v>476</v>
+        <v>393</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="14.4">
       <c r="A26" s="10" t="s">
-        <v>477</v>
+        <v>394</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="14.4">
       <c r="A27" s="9" t="s">
-        <v>478</v>
+        <v>395</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="14.4">
       <c r="A28" s="9" t="s">
-        <v>479</v>
+        <v>396</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="14.4">
       <c r="A29" s="9" t="s">
-        <v>480</v>
+        <v>397</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="14.4">
       <c r="A30" s="10" t="s">
-        <v>481</v>
+        <v>398</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="14.4">
       <c r="A31" s="9" t="s">
-        <v>482</v>
+        <v>399</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="14.4">
       <c r="A32" s="9" t="s">
-        <v>483</v>
+        <v>400</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="14.4">
       <c r="A33" s="9" t="s">
-        <v>484</v>
+        <v>401</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="14.4">
       <c r="A34" s="10" t="s">
-        <v>485</v>
+        <v>402</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="14.4">
       <c r="A35" s="9" t="s">
-        <v>486</v>
+        <v>403</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="14.4">
       <c r="A36" s="9" t="s">
-        <v>487</v>
+        <v>404</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="14.4">
       <c r="A37" s="10" t="s">
-        <v>488</v>
+        <v>405</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="14.4">
       <c r="A38" s="9" t="s">
-        <v>489</v>
+        <v>406</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="14.4">
       <c r="A39" s="9" t="s">
-        <v>490</v>
+        <v>407</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="14.4">
       <c r="A40" s="10" t="s">
-        <v>491</v>
+        <v>408</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="14.4">
       <c r="A41" s="10" t="s">
-        <v>492</v>
+        <v>409</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="14.4">
       <c r="A42" s="10" t="s">
-        <v>493</v>
+        <v>410</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="14.4">
       <c r="A43" s="9" t="s">
-        <v>494</v>
+        <v>411</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="14.4">
       <c r="A44" s="9" t="s">
-        <v>495</v>
+        <v>412</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="14.4">
       <c r="A45" s="9" t="s">
-        <v>496</v>
+        <v>413</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="14.4">
       <c r="A46" s="10" t="s">
-        <v>497</v>
+        <v>414</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="14.4">
       <c r="A47" s="10" t="s">
-        <v>498</v>
+        <v>415</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="14.4">
       <c r="A48" s="10" t="s">
-        <v>499</v>
+        <v>416</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="14.4">
       <c r="A49" s="9" t="s">
-        <v>500</v>
+        <v>417</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="14.4">
       <c r="A50" s="10" t="s">
-        <v>501</v>
+        <v>418</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="14.4">
       <c r="A51" s="10" t="s">
-        <v>502</v>
+        <v>419</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="14.4">
       <c r="A52" s="10" t="s">
-        <v>503</v>
+        <v>420</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="14.4">
       <c r="A53" s="10" t="s">
-        <v>504</v>
+        <v>421</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="14.4">
       <c r="A54" s="10" t="s">
-        <v>505</v>
+        <v>422</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="14.4">
       <c r="A55" s="10" t="s">
-        <v>506</v>
+        <v>423</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="14.4">
       <c r="A56" s="9" t="s">
-        <v>507</v>
+        <v>424</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="14.4">
       <c r="A57" s="9" t="s">
-        <v>508</v>
+        <v>425</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="14.4">
       <c r="A58" s="10" t="s">
-        <v>509</v>
+        <v>426</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="14.4">
       <c r="A59" s="9" t="s">
-        <v>510</v>
+        <v>427</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="14.4">
       <c r="A60" s="10" t="s">
-        <v>511</v>
+        <v>428</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="14.4">
       <c r="A61" s="10" t="s">
-        <v>512</v>
+        <v>429</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="14.4">
       <c r="A62" s="10" t="s">
-        <v>513</v>
+        <v>430</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="63" spans="1:2" ht="14.4">
       <c r="A63" s="10" t="s">
-        <v>514</v>
+        <v>431</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="64" spans="1:2" ht="14.4">
       <c r="A64" s="9" t="s">
-        <v>515</v>
+        <v>432</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="14.4">
       <c r="A65" s="9" t="s">
-        <v>516</v>
+        <v>433</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="14.4">
       <c r="A66" s="9" t="s">
-        <v>517</v>
+        <v>434</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="67" spans="1:2" ht="14.4">
       <c r="A67" s="10" t="s">
-        <v>518</v>
+        <v>435</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="14.4">
       <c r="A68" s="9" t="s">
-        <v>519</v>
+        <v>436</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="14.4">
       <c r="A69" s="10" t="s">
-        <v>520</v>
+        <v>437</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="14.4">
       <c r="A70" s="10" t="s">
-        <v>521</v>
+        <v>438</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="14.4">
       <c r="A71" s="10" t="s">
-        <v>522</v>
+        <v>439</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="72" spans="1:2" ht="14.4">
       <c r="A72" s="9" t="s">
-        <v>523</v>
+        <v>440</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="73" spans="1:2" ht="14.4">
       <c r="A73" s="9" t="s">
-        <v>524</v>
+        <v>441</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="74" spans="1:2" ht="14.4">
       <c r="A74" s="9" t="s">
-        <v>525</v>
+        <v>442</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="75" spans="1:2" ht="14.4">
       <c r="A75" s="10" t="s">
-        <v>526</v>
+        <v>443</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="14.4">
       <c r="A76" s="9" t="s">
-        <v>527</v>
+        <v>444</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="14.4">
       <c r="A77" s="9" t="s">
-        <v>528</v>
+        <v>445</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="78" spans="1:2" ht="14.4">
       <c r="A78" s="10" t="s">
-        <v>529</v>
+        <v>446</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="79" spans="1:2" ht="14.4">
       <c r="A79" s="10" t="s">
-        <v>530</v>
+        <v>447</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="80" spans="1:2" ht="14.4">
       <c r="A80" s="10" t="s">
-        <v>531</v>
+        <v>448</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="14.4">
       <c r="A81" s="9" t="s">
-        <v>532</v>
+        <v>449</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="14.4">
       <c r="A82" s="10" t="s">
-        <v>533</v>
+        <v>450</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="14.4">
       <c r="A83" s="10" t="s">
-        <v>534</v>
+        <v>451</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D83"/>
     </row>
     <row r="84" spans="1:4" ht="14.4">
       <c r="A84" s="10" t="s">
-        <v>535</v>
+        <v>452</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D84"/>
     </row>
     <row r="85" spans="1:4" ht="14.4">
       <c r="A85" s="10" t="s">
-        <v>536</v>
+        <v>453</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D85"/>
     </row>
     <row r="86" spans="1:4" ht="14.4">
       <c r="A86" s="9" t="s">
-        <v>537</v>
+        <v>454</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D86"/>
     </row>
     <row r="87" spans="1:4" ht="14.4">
       <c r="A87" s="9" t="s">
-        <v>538</v>
+        <v>455</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D87"/>
     </row>
     <row r="88" spans="1:4" ht="14.4">
       <c r="A88" s="10" t="s">
-        <v>539</v>
+        <v>456</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D88"/>
     </row>
     <row r="89" spans="1:4" ht="14.4">
       <c r="A89" s="9" t="s">
-        <v>540</v>
+        <v>457</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D89"/>
     </row>
     <row r="90" spans="1:4" ht="14.4">
       <c r="A90" s="10" t="s">
-        <v>541</v>
+        <v>458</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D90"/>
     </row>
     <row r="91" spans="1:4" ht="14.4">
       <c r="A91" s="10" t="s">
-        <v>542</v>
+        <v>459</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D91"/>
     </row>
     <row r="92" spans="1:4" ht="14.4">
       <c r="A92" s="10" t="s">
-        <v>543</v>
+        <v>460</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D92"/>
     </row>
     <row r="93" spans="1:4" ht="14.4">
       <c r="A93" s="10" t="s">
-        <v>544</v>
+        <v>461</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D93"/>
     </row>
     <row r="94" spans="1:4" ht="14.4">
       <c r="A94" s="10" t="s">
-        <v>545</v>
+        <v>462</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D94"/>
     </row>
     <row r="95" spans="1:4" ht="14.4">
       <c r="A95" s="10" t="s">
-        <v>546</v>
+        <v>463</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D95"/>
     </row>
     <row r="96" spans="1:4" ht="14.4">
       <c r="A96" s="10" t="s">
-        <v>547</v>
+        <v>464</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D96"/>
     </row>
     <row r="97" spans="1:4" ht="14.4">
       <c r="A97" s="9" t="s">
-        <v>548</v>
+        <v>465</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D97"/>
     </row>
     <row r="98" spans="1:4" ht="14.4">
       <c r="A98" s="10" t="s">
-        <v>549</v>
+        <v>466</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D98"/>
     </row>
     <row r="99" spans="1:4" ht="14.4">
       <c r="A99" s="10" t="s">
-        <v>550</v>
+        <v>467</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D99"/>
     </row>
     <row r="100" spans="1:4" ht="14.4">
       <c r="A100" s="10" t="s">
-        <v>551</v>
+        <v>468</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D100"/>
     </row>
     <row r="101" spans="1:4" ht="14.4">
       <c r="A101" s="10" t="s">
-        <v>552</v>
+        <v>469</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D101"/>
     </row>
     <row r="102" spans="1:4" ht="14.4">
       <c r="A102" s="10" t="s">
-        <v>553</v>
+        <v>470</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D102"/>
     </row>
     <row r="103" spans="1:4" ht="14.4">
       <c r="A103" s="10" t="s">
-        <v>554</v>
+        <v>471</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D103"/>
     </row>
     <row r="104" spans="1:4" ht="14.4">
       <c r="A104" s="9" t="s">
-        <v>555</v>
+        <v>472</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D104"/>
     </row>
     <row r="105" spans="1:4" ht="14.4">
       <c r="A105" s="10" t="s">
-        <v>556</v>
+        <v>473</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D105"/>
     </row>
     <row r="106" spans="1:4" ht="14.4">
       <c r="A106" s="10" t="s">
-        <v>557</v>
+        <v>474</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D106"/>
     </row>
     <row r="107" spans="1:4" ht="14.4">
       <c r="A107" s="10" t="s">
-        <v>558</v>
+        <v>475</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D107"/>
     </row>
     <row r="108" spans="1:4" ht="14.4">
       <c r="A108" s="10" t="s">
-        <v>559</v>
+        <v>476</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D108"/>
     </row>
     <row r="109" spans="1:4" ht="14.4">
       <c r="A109" s="10" t="s">
-        <v>560</v>
+        <v>477</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D109"/>
     </row>
     <row r="110" spans="1:4" ht="14.4">
       <c r="A110" s="10" t="s">
-        <v>561</v>
+        <v>478</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D110"/>
     </row>
     <row r="111" spans="1:4" ht="14.4">
       <c r="A111" s="9" t="s">
-        <v>562</v>
+        <v>479</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D111"/>
     </row>
     <row r="112" spans="1:4" ht="14.4">
       <c r="A112" s="10" t="s">
-        <v>563</v>
+        <v>480</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D112"/>
     </row>
     <row r="113" spans="1:4" ht="14.4">
       <c r="A113" s="10" t="s">
-        <v>564</v>
+        <v>481</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D113"/>
     </row>
     <row r="114" spans="1:4" ht="14.4">
       <c r="A114" s="10" t="s">
-        <v>565</v>
+        <v>482</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D114"/>
     </row>
     <row r="115" spans="1:4" ht="14.4">
       <c r="A115" s="10" t="s">
-        <v>566</v>
+        <v>483</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D115"/>
     </row>
     <row r="116" spans="1:4" ht="14.4">
       <c r="A116" s="10" t="s">
-        <v>567</v>
+        <v>484</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D116"/>
     </row>
     <row r="117" spans="1:4" ht="14.4">
       <c r="A117" s="10" t="s">
-        <v>568</v>
+        <v>485</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D117"/>
     </row>
     <row r="118" spans="1:4" ht="14.4">
       <c r="A118" s="10" t="s">
-        <v>569</v>
+        <v>486</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D118"/>
     </row>
     <row r="119" spans="1:4" ht="14.4">
       <c r="A119" s="10" t="s">
-        <v>570</v>
+        <v>487</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D119"/>
     </row>
     <row r="120" spans="1:4" ht="14.4">
       <c r="A120" s="10" t="s">
-        <v>571</v>
+        <v>488</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D120"/>
     </row>
     <row r="121" spans="1:4" ht="14.4">
       <c r="A121" s="10" t="s">
-        <v>572</v>
+        <v>489</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D121"/>
     </row>
     <row r="122" spans="1:4" ht="14.4">
       <c r="A122" s="10" t="s">
-        <v>455</v>
+        <v>372</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>718</v>
+        <v>635</v>
       </c>
       <c r="D122"/>
     </row>
@@ -3858,699 +3609,289 @@
       <c r="B128"/>
       <c r="D128"/>
     </row>
-    <row r="130" spans="1:2" ht="14.4">
-      <c r="A130" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" ht="14.4">
-      <c r="A131" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" ht="14.4">
-      <c r="A132" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" ht="14.4">
-      <c r="A133" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" ht="14.4">
-      <c r="A134" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" ht="14.4">
-      <c r="A135" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" ht="14.4">
-      <c r="A136" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" ht="14.4">
-      <c r="A137" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" ht="14.4">
-      <c r="A138" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" ht="14.4">
-      <c r="A139" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" ht="14.4">
-      <c r="A140" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" ht="14.4">
-      <c r="A141" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" ht="14.4">
-      <c r="A142" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" ht="14.4">
-      <c r="A143" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" ht="14.4">
-      <c r="A144" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" ht="14.4">
-      <c r="A145" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" ht="14.4">
-      <c r="A146" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" ht="14.4">
-      <c r="A147" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" ht="14.4">
-      <c r="A148" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" ht="14.4">
-      <c r="A149" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" ht="14.4">
-      <c r="A150" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" ht="14.4">
-      <c r="A151" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" ht="14.4">
-      <c r="A152" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" ht="14.4">
-      <c r="A153" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" ht="14.4">
-      <c r="A154" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" ht="14.4">
-      <c r="A155" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B155" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" ht="14.4">
-      <c r="A156" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" ht="14.4">
-      <c r="A157" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" ht="14.4">
-      <c r="A158" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" ht="14.4">
-      <c r="A159" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" ht="14.4">
-      <c r="A160" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" ht="14.4">
-      <c r="A161" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" ht="14.4">
-      <c r="A162" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" ht="14.4">
-      <c r="A163" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" ht="14.4">
-      <c r="A164" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" ht="14.4">
-      <c r="A165" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" ht="14.4">
-      <c r="A166" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B166" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2" ht="14.4">
-      <c r="A167" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" ht="14.4">
-      <c r="A168" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2" ht="14.4">
-      <c r="A169" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2" ht="14.4">
-      <c r="A170" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2" ht="14.4">
-      <c r="A171" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2" ht="14.4">
-      <c r="A172" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2" ht="14.4">
-      <c r="A173" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B173" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2" ht="14.4">
-      <c r="A174" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B174" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2" ht="14.4">
-      <c r="A175" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B175" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2" ht="14.4">
-      <c r="A176" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B176" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2" ht="14.4">
-      <c r="A177" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B177" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2" ht="14.4">
-      <c r="A178" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B178" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2" ht="14.4">
-      <c r="A179" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2" ht="14.4">
-      <c r="A180" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B180" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2" ht="14.4">
-      <c r="A181" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B181" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2" ht="14.4">
-      <c r="A182" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B182" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2" ht="14.4">
-      <c r="A183" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B183" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2" ht="14.4">
-      <c r="A184" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B184" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2" ht="14.4">
-      <c r="A185" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B185" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2" ht="14.4">
-      <c r="A186" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2" ht="14.4">
-      <c r="A187" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2" ht="14.4">
-      <c r="A188" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2" ht="14.4">
-      <c r="A189" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2" ht="14.4">
-      <c r="A190" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B190" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2" ht="14.4">
-      <c r="A191" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B191" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2" ht="14.4">
-      <c r="A192" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B192" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2" ht="14.4">
-      <c r="A193" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B193" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="194" spans="1:2" ht="14.4">
-      <c r="A194" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B194" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="195" spans="1:2" ht="14.4">
-      <c r="A195" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B195" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="196" spans="1:2" ht="14.4">
-      <c r="A196" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B196" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="197" spans="1:2" ht="14.4">
-      <c r="A197" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B197" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="198" spans="1:2" ht="14.4">
-      <c r="A198" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2" ht="14.4">
-      <c r="A199" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B199" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2" ht="14.4">
-      <c r="A200" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B200" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2" ht="14.4">
-      <c r="A201" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B201" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="202" spans="1:2" ht="14.4">
-      <c r="A202" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B202" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="203" spans="1:2" ht="14.4">
-      <c r="A203" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B203" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="204" spans="1:2" ht="14.4">
-      <c r="A204" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="205" spans="1:2" ht="14.4">
-      <c r="A205" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B205" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="206" spans="1:2" ht="14.4">
-      <c r="A206" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B206" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="207" spans="1:2" ht="14.4">
-      <c r="A207" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B207" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="208" spans="1:2" ht="14.4">
-      <c r="A208" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B208" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="209" spans="1:2" ht="14.4">
-      <c r="A209" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B209" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="210" spans="1:2" ht="14.4">
-      <c r="A210" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B210" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="211" spans="1:2" ht="14.4">
-      <c r="A211" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B211" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2" ht="14.4">
+    <row r="130" spans="1:1" ht="14.4">
+      <c r="A130" s="7"/>
+    </row>
+    <row r="131" spans="1:1" ht="14.4">
+      <c r="A131" s="8"/>
+    </row>
+    <row r="132" spans="1:1" ht="14.4">
+      <c r="A132" s="7"/>
+    </row>
+    <row r="133" spans="1:1" ht="14.4">
+      <c r="A133" s="7"/>
+    </row>
+    <row r="134" spans="1:1" ht="14.4">
+      <c r="A134" s="7"/>
+    </row>
+    <row r="135" spans="1:1" ht="14.4">
+      <c r="A135" s="7"/>
+    </row>
+    <row r="136" spans="1:1" ht="14.4">
+      <c r="A136" s="8"/>
+    </row>
+    <row r="137" spans="1:1" ht="14.4">
+      <c r="A137" s="7"/>
+    </row>
+    <row r="138" spans="1:1" ht="14.4">
+      <c r="A138" s="7"/>
+    </row>
+    <row r="139" spans="1:1" ht="14.4">
+      <c r="A139" s="7"/>
+    </row>
+    <row r="140" spans="1:1" ht="14.4">
+      <c r="A140" s="8"/>
+    </row>
+    <row r="141" spans="1:1" ht="14.4">
+      <c r="A141" s="7"/>
+    </row>
+    <row r="142" spans="1:1" ht="14.4">
+      <c r="A142" s="7"/>
+    </row>
+    <row r="143" spans="1:1" ht="14.4">
+      <c r="A143" s="7"/>
+    </row>
+    <row r="144" spans="1:1" ht="14.4">
+      <c r="A144" s="7"/>
+    </row>
+    <row r="145" spans="1:1" ht="14.4">
+      <c r="A145" s="7"/>
+    </row>
+    <row r="146" spans="1:1" ht="14.4">
+      <c r="A146" s="7"/>
+    </row>
+    <row r="147" spans="1:1" ht="14.4">
+      <c r="A147" s="7"/>
+    </row>
+    <row r="148" spans="1:1" ht="14.4">
+      <c r="A148" s="7"/>
+    </row>
+    <row r="149" spans="1:1" ht="14.4">
+      <c r="A149" s="8"/>
+    </row>
+    <row r="150" spans="1:1" ht="14.4">
+      <c r="A150" s="8"/>
+    </row>
+    <row r="151" spans="1:1" ht="14.4">
+      <c r="A151" s="7"/>
+    </row>
+    <row r="152" spans="1:1" ht="14.4">
+      <c r="A152" s="7"/>
+    </row>
+    <row r="153" spans="1:1" ht="14.4">
+      <c r="A153" s="8"/>
+    </row>
+    <row r="154" spans="1:1" ht="14.4">
+      <c r="A154" s="7"/>
+    </row>
+    <row r="155" spans="1:1" ht="14.4">
+      <c r="A155" s="7"/>
+    </row>
+    <row r="156" spans="1:1" ht="14.4">
+      <c r="A156" s="7"/>
+    </row>
+    <row r="157" spans="1:1" ht="14.4">
+      <c r="A157" s="8"/>
+    </row>
+    <row r="158" spans="1:1" ht="14.4">
+      <c r="A158" s="8"/>
+    </row>
+    <row r="159" spans="1:1" ht="14.4">
+      <c r="A159" s="7"/>
+    </row>
+    <row r="160" spans="1:1" ht="14.4">
+      <c r="A160" s="8"/>
+    </row>
+    <row r="161" spans="1:1" ht="14.4">
+      <c r="A161" s="8"/>
+    </row>
+    <row r="162" spans="1:1" ht="14.4">
+      <c r="A162" s="8"/>
+    </row>
+    <row r="163" spans="1:1" ht="14.4">
+      <c r="A163" s="7"/>
+    </row>
+    <row r="164" spans="1:1" ht="14.4">
+      <c r="A164" s="8"/>
+    </row>
+    <row r="165" spans="1:1" ht="14.4">
+      <c r="A165" s="7"/>
+    </row>
+    <row r="166" spans="1:1" ht="14.4">
+      <c r="A166" s="7"/>
+    </row>
+    <row r="167" spans="1:1" ht="14.4">
+      <c r="A167" s="7"/>
+    </row>
+    <row r="168" spans="1:1" ht="14.4">
+      <c r="A168" s="7"/>
+    </row>
+    <row r="169" spans="1:1" ht="14.4">
+      <c r="A169" s="7"/>
+    </row>
+    <row r="170" spans="1:1" ht="14.4">
+      <c r="A170" s="8"/>
+    </row>
+    <row r="171" spans="1:1" ht="14.4">
+      <c r="A171" s="7"/>
+    </row>
+    <row r="172" spans="1:1" ht="14.4">
+      <c r="A172" s="8"/>
+    </row>
+    <row r="173" spans="1:1" ht="14.4">
+      <c r="A173" s="7"/>
+    </row>
+    <row r="174" spans="1:1" ht="14.4">
+      <c r="A174" s="8"/>
+    </row>
+    <row r="175" spans="1:1" ht="14.4">
+      <c r="A175" s="7"/>
+    </row>
+    <row r="176" spans="1:1" ht="14.4">
+      <c r="A176" s="7"/>
+    </row>
+    <row r="177" spans="1:1" ht="14.4">
+      <c r="A177" s="7"/>
+    </row>
+    <row r="178" spans="1:1" ht="14.4">
+      <c r="A178" s="7"/>
+    </row>
+    <row r="179" spans="1:1" ht="14.4">
+      <c r="A179" s="8"/>
+    </row>
+    <row r="180" spans="1:1" ht="14.4">
+      <c r="A180" s="7"/>
+    </row>
+    <row r="181" spans="1:1" ht="14.4">
+      <c r="A181" s="8"/>
+    </row>
+    <row r="182" spans="1:1" ht="14.4">
+      <c r="A182" s="8"/>
+    </row>
+    <row r="183" spans="1:1" ht="14.4">
+      <c r="A183" s="8"/>
+    </row>
+    <row r="184" spans="1:1" ht="14.4">
+      <c r="A184" s="7"/>
+    </row>
+    <row r="185" spans="1:1" ht="14.4">
+      <c r="A185" s="7"/>
+    </row>
+    <row r="186" spans="1:1" ht="14.4">
+      <c r="A186" s="7"/>
+    </row>
+    <row r="187" spans="1:1" ht="14.4">
+      <c r="A187" s="7"/>
+    </row>
+    <row r="188" spans="1:1" ht="14.4">
+      <c r="A188" s="8"/>
+    </row>
+    <row r="189" spans="1:1" ht="14.4">
+      <c r="A189" s="8"/>
+    </row>
+    <row r="190" spans="1:1" ht="14.4">
+      <c r="A190" s="7"/>
+    </row>
+    <row r="191" spans="1:1" ht="14.4">
+      <c r="A191" s="7"/>
+    </row>
+    <row r="192" spans="1:1" ht="14.4">
+      <c r="A192" s="7"/>
+    </row>
+    <row r="193" spans="1:1" ht="14.4">
+      <c r="A193" s="8"/>
+    </row>
+    <row r="194" spans="1:1" ht="14.4">
+      <c r="A194" s="7"/>
+    </row>
+    <row r="195" spans="1:1" ht="14.4">
+      <c r="A195" s="8"/>
+    </row>
+    <row r="196" spans="1:1" ht="14.4">
+      <c r="A196" s="7"/>
+    </row>
+    <row r="197" spans="1:1" ht="14.4">
+      <c r="A197" s="7"/>
+    </row>
+    <row r="198" spans="1:1" ht="14.4">
+      <c r="A198" s="7"/>
+    </row>
+    <row r="199" spans="1:1" ht="14.4">
+      <c r="A199" s="7"/>
+    </row>
+    <row r="200" spans="1:1" ht="14.4">
+      <c r="A200" s="7"/>
+    </row>
+    <row r="201" spans="1:1" ht="14.4">
+      <c r="A201" s="7"/>
+    </row>
+    <row r="202" spans="1:1" ht="14.4">
+      <c r="A202" s="7"/>
+    </row>
+    <row r="203" spans="1:1" ht="14.4">
+      <c r="A203" s="8"/>
+    </row>
+    <row r="204" spans="1:1" ht="14.4">
+      <c r="A204" s="7"/>
+    </row>
+    <row r="205" spans="1:1" ht="14.4">
+      <c r="A205" s="7"/>
+    </row>
+    <row r="206" spans="1:1" ht="14.4">
+      <c r="A206" s="7"/>
+    </row>
+    <row r="207" spans="1:1" ht="14.4">
+      <c r="A207" s="8"/>
+    </row>
+    <row r="208" spans="1:1" ht="14.4">
+      <c r="A208" s="7"/>
+    </row>
+    <row r="209" spans="1:1" ht="14.4">
+      <c r="A209" s="7"/>
+    </row>
+    <row r="210" spans="1:1" ht="14.4">
+      <c r="A210" s="7"/>
+    </row>
+    <row r="211" spans="1:1" ht="14.4">
+      <c r="A211" s="6"/>
+    </row>
+    <row r="212" spans="1:1" ht="14.4">
       <c r="A212" s="3"/>
     </row>
-    <row r="213" spans="1:2" ht="14.4">
+    <row r="213" spans="1:1" ht="14.4">
       <c r="A213" s="3"/>
     </row>
-    <row r="214" spans="1:2" ht="14.4">
+    <row r="214" spans="1:1" ht="14.4">
       <c r="A214" s="3"/>
     </row>
-    <row r="215" spans="1:2" ht="14.4">
+    <row r="215" spans="1:1" ht="14.4">
       <c r="A215" s="5"/>
     </row>
-    <row r="216" spans="1:2" ht="14.4">
+    <row r="216" spans="1:1" ht="14.4">
       <c r="A216" s="3"/>
     </row>
-    <row r="217" spans="1:2" ht="14.4">
+    <row r="217" spans="1:1" ht="14.4">
       <c r="A217" s="5"/>
     </row>
-    <row r="218" spans="1:2" ht="14.4">
+    <row r="218" spans="1:1" ht="14.4">
       <c r="A218" s="5"/>
     </row>
-    <row r="219" spans="1:2" ht="14.4">
+    <row r="219" spans="1:1" ht="14.4">
       <c r="A219" s="3"/>
     </row>
-    <row r="220" spans="1:2" ht="14.4">
+    <row r="220" spans="1:1" ht="14.4">
       <c r="A220" s="3"/>
     </row>
-    <row r="221" spans="1:2" ht="14.4">
+    <row r="221" spans="1:1" ht="14.4">
       <c r="A221" s="3"/>
     </row>
-    <row r="222" spans="1:2" ht="14.4">
+    <row r="222" spans="1:1" ht="14.4">
       <c r="A222" s="5"/>
     </row>
-    <row r="223" spans="1:2" ht="14.4">
+    <row r="223" spans="1:1" ht="14.4">
       <c r="A223" s="5"/>
     </row>
-    <row r="224" spans="1:2" ht="14.4">
+    <row r="224" spans="1:1" ht="14.4">
       <c r="A224" s="5"/>
     </row>
     <row r="225" spans="1:1" ht="14.4">
@@ -4662,650 +4003,650 @@
     </row>
     <row r="261" spans="1:2" ht="14.4">
       <c r="A261" s="5" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="262" spans="1:2" ht="14.4">
       <c r="A262" s="5" t="s">
-        <v>164</v>
+        <v>81</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="263" spans="1:2" ht="14.4">
       <c r="A263" s="3" t="s">
-        <v>163</v>
+        <v>80</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="264" spans="1:2" ht="14.4">
       <c r="A264" s="3" t="s">
-        <v>162</v>
+        <v>79</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="265" spans="1:2" ht="14.4">
       <c r="A265" s="3" t="s">
-        <v>161</v>
+        <v>78</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="266" spans="1:2" ht="14.4">
       <c r="A266" s="3" t="s">
-        <v>160</v>
+        <v>77</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="267" spans="1:2" ht="14.4">
       <c r="A267" s="3" t="s">
-        <v>159</v>
+        <v>76</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="268" spans="1:2" ht="14.4">
       <c r="A268" s="5" t="s">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="269" spans="1:2" ht="14.4">
       <c r="A269" s="3" t="s">
-        <v>157</v>
+        <v>74</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="270" spans="1:2" ht="14.4">
       <c r="A270" s="3" t="s">
-        <v>156</v>
+        <v>73</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="271" spans="1:2" ht="14.4">
       <c r="A271" s="3" t="s">
-        <v>155</v>
+        <v>72</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="272" spans="1:2" ht="14.4">
       <c r="A272" s="5" t="s">
-        <v>154</v>
+        <v>71</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="273" spans="1:2" ht="14.4">
       <c r="A273" s="3" t="s">
-        <v>153</v>
+        <v>70</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="274" spans="1:2" ht="14.4">
       <c r="A274" s="5" t="s">
-        <v>152</v>
+        <v>69</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="275" spans="1:2" ht="14.4">
       <c r="A275" s="5" t="s">
-        <v>151</v>
+        <v>68</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="276" spans="1:2" ht="14.4">
       <c r="A276" s="3" t="s">
-        <v>150</v>
+        <v>67</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="277" spans="1:2" ht="14.4">
       <c r="A277" s="3" t="s">
-        <v>149</v>
+        <v>66</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="278" spans="1:2" ht="14.4">
       <c r="A278" s="3" t="s">
-        <v>148</v>
+        <v>65</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="279" spans="1:2" ht="14.4">
       <c r="A279" s="5" t="s">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="280" spans="1:2" ht="14.4">
       <c r="A280" s="5" t="s">
-        <v>146</v>
+        <v>63</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="281" spans="1:2" ht="14.4">
       <c r="A281" s="3" t="s">
-        <v>145</v>
+        <v>62</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="282" spans="1:2" ht="14.4">
       <c r="A282" s="3" t="s">
-        <v>144</v>
+        <v>61</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="283" spans="1:2" ht="14.4">
       <c r="A283" s="3" t="s">
-        <v>143</v>
+        <v>60</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="284" spans="1:2" ht="14.4">
       <c r="A284" s="3" t="s">
-        <v>142</v>
+        <v>59</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="285" spans="1:2" ht="14.4">
       <c r="A285" s="3" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="286" spans="1:2" ht="14.4">
       <c r="A286" s="5" t="s">
-        <v>140</v>
+        <v>57</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="287" spans="1:2" ht="14.4">
       <c r="A287" s="3" t="s">
-        <v>139</v>
+        <v>56</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="288" spans="1:2" ht="14.4">
       <c r="A288" s="3" t="s">
-        <v>138</v>
+        <v>55</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="289" spans="1:2" ht="14.4">
       <c r="A289" s="3" t="s">
-        <v>137</v>
+        <v>54</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="290" spans="1:2" ht="14.4">
       <c r="A290" s="3" t="s">
-        <v>136</v>
+        <v>53</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="291" spans="1:2" ht="14.4">
       <c r="A291" s="3" t="s">
-        <v>135</v>
+        <v>52</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="292" spans="1:2" ht="14.4">
       <c r="A292" s="5" t="s">
-        <v>134</v>
+        <v>51</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="293" spans="1:2" ht="14.4">
       <c r="A293" s="5" t="s">
-        <v>133</v>
+        <v>50</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="294" spans="1:2" ht="14.4">
       <c r="A294" s="3" t="s">
-        <v>132</v>
+        <v>49</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="295" spans="1:2" ht="14.4">
       <c r="A295" s="5" t="s">
-        <v>131</v>
+        <v>48</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="296" spans="1:2" ht="14.4">
       <c r="A296" s="3" t="s">
-        <v>130</v>
+        <v>47</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="297" spans="1:2" ht="14.4">
       <c r="A297" s="3" t="s">
-        <v>129</v>
+        <v>46</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="298" spans="1:2" ht="14.4">
       <c r="A298" s="3" t="s">
-        <v>128</v>
+        <v>45</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="299" spans="1:2" ht="14.4">
       <c r="A299" s="3" t="s">
-        <v>127</v>
+        <v>44</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="300" spans="1:2" ht="14.4">
       <c r="A300" s="3" t="s">
-        <v>126</v>
+        <v>43</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="301" spans="1:2" ht="14.4">
       <c r="A301" s="5" t="s">
-        <v>125</v>
+        <v>42</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="302" spans="1:2" ht="14.4">
       <c r="A302" s="3" t="s">
-        <v>124</v>
+        <v>41</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="303" spans="1:2" ht="14.4">
       <c r="A303" s="3" t="s">
-        <v>123</v>
+        <v>40</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="304" spans="1:2" ht="14.4">
       <c r="A304" s="3" t="s">
-        <v>122</v>
+        <v>39</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="305" spans="1:2" ht="14.4">
       <c r="A305" s="3" t="s">
-        <v>121</v>
+        <v>38</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="306" spans="1:2" ht="14.4">
       <c r="A306" s="3" t="s">
-        <v>120</v>
+        <v>37</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="307" spans="1:2" ht="14.4">
       <c r="A307" s="3" t="s">
-        <v>119</v>
+        <v>36</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="308" spans="1:2" ht="14.4">
       <c r="A308" s="3" t="s">
-        <v>118</v>
+        <v>35</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="309" spans="1:2" ht="14.4">
       <c r="A309" s="3" t="s">
-        <v>117</v>
+        <v>34</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="310" spans="1:2" ht="14.4">
       <c r="A310" s="5" t="s">
-        <v>116</v>
+        <v>33</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="311" spans="1:2" ht="14.4">
       <c r="A311" s="3" t="s">
-        <v>115</v>
+        <v>32</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="312" spans="1:2" ht="14.4">
       <c r="A312" s="5" t="s">
-        <v>114</v>
+        <v>31</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="313" spans="1:2" ht="14.4">
       <c r="A313" s="5" t="s">
-        <v>113</v>
+        <v>30</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="314" spans="1:2" ht="14.4">
       <c r="A314" s="5" t="s">
-        <v>112</v>
+        <v>29</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="315" spans="1:2" ht="14.4">
       <c r="A315" s="3" t="s">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="316" spans="1:2" ht="14.4">
       <c r="A316" s="3" t="s">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="317" spans="1:2" ht="14.4">
       <c r="A317" s="5" t="s">
-        <v>109</v>
+        <v>26</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="318" spans="1:2" ht="14.4">
       <c r="A318" s="3" t="s">
-        <v>108</v>
+        <v>25</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="319" spans="1:2" ht="14.4">
       <c r="A319" s="3" t="s">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="320" spans="1:2" ht="14.4">
       <c r="A320" s="3" t="s">
-        <v>106</v>
+        <v>23</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="321" spans="1:2" ht="14.4">
       <c r="A321" s="5" t="s">
-        <v>105</v>
+        <v>22</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="322" spans="1:2" ht="14.4">
       <c r="A322" s="5" t="s">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="323" spans="1:2" ht="14.4">
       <c r="A323" s="5" t="s">
-        <v>103</v>
+        <v>20</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="324" spans="1:2" ht="14.4">
       <c r="A324" s="3" t="s">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="325" spans="1:2" ht="14.4">
       <c r="A325" s="3" t="s">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="326" spans="1:2" ht="14.4">
       <c r="A326" s="3" t="s">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="327" spans="1:2" ht="14.4">
       <c r="A327" s="3" t="s">
-        <v>99</v>
+        <v>16</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="328" spans="1:2" ht="14.4">
       <c r="A328" s="3" t="s">
-        <v>98</v>
+        <v>15</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="329" spans="1:2" ht="14.4">
       <c r="A329" s="3" t="s">
-        <v>97</v>
+        <v>14</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="330" spans="1:2" ht="14.4">
       <c r="A330" s="5" t="s">
-        <v>96</v>
+        <v>13</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="331" spans="1:2" ht="14.4">
       <c r="A331" s="5" t="s">
-        <v>95</v>
+        <v>12</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="332" spans="1:2" ht="14.4">
       <c r="A332" s="3" t="s">
-        <v>94</v>
+        <v>11</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="333" spans="1:2" ht="14.4">
       <c r="A333" s="3" t="s">
-        <v>93</v>
+        <v>10</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="334" spans="1:2" ht="14.4">
       <c r="A334" s="3" t="s">
-        <v>92</v>
+        <v>9</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="335" spans="1:2" ht="14.4">
       <c r="A335" s="3" t="s">
-        <v>91</v>
+        <v>8</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="336" spans="1:2" ht="14.4">
       <c r="A336" s="5" t="s">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="337" spans="1:2" ht="14.4">
       <c r="A337" s="3" t="s">
-        <v>89</v>
+        <v>6</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="338" spans="1:2" ht="14.4">
       <c r="A338" s="3" t="s">
-        <v>88</v>
+        <v>5</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="339" spans="1:2" ht="14.4">
       <c r="A339" s="3" t="s">
-        <v>87</v>
+        <v>4</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="340" spans="1:2" ht="14.4">
       <c r="A340" s="3" t="s">
-        <v>86</v>
+        <v>3</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="341" spans="1:2" ht="14.4">
       <c r="A341" s="3" t="s">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>720</v>
+        <v>637</v>
       </c>
     </row>
     <row r="343" spans="1:2" ht="14.4">
@@ -5313,39 +4654,39 @@
         <v>777421971309997</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="344" spans="1:2" ht="14.4">
       <c r="A344" s="1" t="s">
-        <v>166</v>
+        <v>83</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="345" spans="1:2" ht="14.4">
       <c r="A345" s="1" t="s">
-        <v>167</v>
+        <v>84</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="346" spans="1:2" ht="14.4">
       <c r="A346" s="1" t="s">
-        <v>168</v>
+        <v>85</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="347" spans="1:2" ht="14.4">
       <c r="A347" s="1" t="s">
-        <v>169</v>
+        <v>86</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="348" spans="1:2" ht="14.4">
@@ -5353,15 +4694,15 @@
         <v>79117952924235</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="349" spans="1:2" ht="14.4">
       <c r="A349" s="1" t="s">
-        <v>170</v>
+        <v>87</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="350" spans="1:2" ht="14.4">
@@ -5369,7 +4710,7 @@
         <v>465458300612210</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="351" spans="1:2" ht="14.4">
@@ -5377,15 +4718,15 @@
         <v>465462997566968</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="352" spans="1:2" ht="14.4">
       <c r="A352" s="1" t="s">
-        <v>171</v>
+        <v>88</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="353" spans="1:2" ht="14.4">
@@ -5393,15 +4734,15 @@
         <v>9817637752976</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="354" spans="1:2" ht="14.4">
       <c r="A354" s="1" t="s">
-        <v>172</v>
+        <v>89</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="355" spans="1:2" ht="14.4">
@@ -5409,23 +4750,23 @@
         <v>777422386231741</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="356" spans="1:2" ht="14.4">
       <c r="A356" s="1" t="s">
-        <v>173</v>
+        <v>90</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="357" spans="1:2" ht="14.4">
       <c r="A357" s="1" t="s">
-        <v>174</v>
+        <v>91</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="358" spans="1:2" ht="14.4">
@@ -5433,31 +4774,31 @@
         <v>777422549883964</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="359" spans="1:2" ht="14.4">
       <c r="A359" s="1" t="s">
-        <v>175</v>
+        <v>92</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="360" spans="1:2" ht="14.4">
       <c r="A360" s="1" t="s">
-        <v>176</v>
+        <v>93</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="361" spans="1:2" ht="14.4">
       <c r="A361" s="1" t="s">
-        <v>177</v>
+        <v>94</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="362" spans="1:2" ht="14.4">
@@ -5465,23 +4806,23 @@
         <v>777422741197359</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="363" spans="1:2" ht="14.4">
       <c r="A363" s="1" t="s">
-        <v>178</v>
+        <v>95</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="364" spans="1:2" ht="14.4">
       <c r="A364" s="1" t="s">
-        <v>179</v>
+        <v>96</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="365" spans="1:2" ht="14.4">
@@ -5489,7 +4830,7 @@
         <v>79117641603383</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="366" spans="1:2" ht="14.4">
@@ -5497,23 +4838,23 @@
         <v>777422423684474</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="367" spans="1:2" ht="14.4">
       <c r="A367" s="1" t="s">
-        <v>180</v>
+        <v>97</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="368" spans="1:2" ht="14.4">
       <c r="A368" s="1" t="s">
-        <v>181</v>
+        <v>98</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="369" spans="1:2" ht="14.4">
@@ -5521,7 +4862,7 @@
         <v>79117947325687</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="370" spans="1:2" ht="14.4">
@@ -5529,7 +4870,7 @@
         <v>777422657466151</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="371" spans="1:2" ht="14.4">
@@ -5537,7 +4878,7 @@
         <v>79118115286962</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="372" spans="1:2" ht="14.4">
@@ -5545,7 +4886,7 @@
         <v>465458348367580</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="373" spans="1:2" ht="14.4">
@@ -5553,7 +4894,7 @@
         <v>465464907314970</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="374" spans="1:2" ht="14.4">
@@ -5561,15 +4902,15 @@
         <v>777422134424763</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="375" spans="1:2" ht="14.4">
       <c r="A375" s="1" t="s">
-        <v>182</v>
+        <v>99</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="376" spans="1:2" ht="14.4">
@@ -5577,7 +4918,7 @@
         <v>9817706152080</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="377" spans="1:2" ht="14.4">
@@ -5585,7 +4926,7 @@
         <v>9817641420345</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="378" spans="1:2" ht="14.4">
@@ -5593,7 +4934,7 @@
         <v>9817618218214</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="379" spans="1:2" ht="14.4">
@@ -5601,7 +4942,7 @@
         <v>777422513725104</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="380" spans="1:2" ht="14.4">
@@ -5609,7 +4950,7 @@
         <v>79118024749653</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="381" spans="1:2" ht="14.4">
@@ -5617,7 +4958,7 @@
         <v>777422657905926</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="382" spans="1:2" ht="14.4">
@@ -5625,7 +4966,7 @@
         <v>777423203000463</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="383" spans="1:2" ht="14.4">
@@ -5633,7 +4974,7 @@
         <v>777422413035587</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="384" spans="1:2" ht="14.4">
@@ -5641,7 +4982,7 @@
         <v>79117818077517</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="385" spans="1:2" ht="14.4">
@@ -5649,7 +4990,7 @@
         <v>777422517419094</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="386" spans="1:2" ht="14.4">
@@ -5657,7 +4998,7 @@
         <v>9817699670146</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="387" spans="1:2" ht="14.4">
@@ -5665,23 +5006,23 @@
         <v>9817626176674</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="388" spans="1:2" ht="14.4">
       <c r="A388" s="1" t="s">
-        <v>183</v>
+        <v>100</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="389" spans="1:2" ht="14.4">
       <c r="A389" s="1" t="s">
-        <v>184</v>
+        <v>101</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="390" spans="1:2" ht="14.4">
@@ -5689,7 +5030,7 @@
         <v>465464033007149</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="391" spans="1:2" ht="14.4">
@@ -5697,7 +5038,7 @@
         <v>9817684175880</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="392" spans="1:2" ht="14.4">
@@ -5705,7 +5046,7 @@
         <v>9817638532752</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="393" spans="1:2" ht="14.4">
@@ -5713,7 +5054,7 @@
         <v>79117975994426</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="394" spans="1:2" ht="14.4">
@@ -5721,7 +5062,7 @@
         <v>777422279037036</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="395" spans="1:2" ht="14.4">
@@ -5729,7 +5070,7 @@
         <v>465460191668107</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="396" spans="1:2" ht="14.4">
@@ -5737,7 +5078,7 @@
         <v>465458538755029</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="397" spans="1:2" ht="14.4">
@@ -5745,39 +5086,39 @@
         <v>9817633727498</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="398" spans="1:2" ht="14.4">
       <c r="A398" s="1" t="s">
-        <v>185</v>
+        <v>102</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="399" spans="1:2" ht="14.4">
       <c r="A399" s="1" t="s">
-        <v>186</v>
+        <v>103</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="400" spans="1:2" ht="14.4">
       <c r="A400" s="1" t="s">
-        <v>187</v>
+        <v>104</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="401" spans="1:2" ht="14.4">
       <c r="A401" s="1" t="s">
-        <v>188</v>
+        <v>105</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="402" spans="1:2" ht="14.4">
@@ -5785,15 +5126,15 @@
         <v>79118367685893</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="403" spans="1:2" ht="14.4">
       <c r="A403" s="1" t="s">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="404" spans="1:2" ht="14.4">
@@ -5801,7 +5142,7 @@
         <v>9817700621226</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="405" spans="1:2" ht="14.4">
@@ -5809,7 +5150,7 @@
         <v>79117796071346</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="406" spans="1:2" ht="14.4">
@@ -5817,15 +5158,15 @@
         <v>465457962486311</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="407" spans="1:2" ht="14.4">
       <c r="A407" s="1" t="s">
-        <v>190</v>
+        <v>107</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="408" spans="1:2" ht="14.4">
@@ -5833,15 +5174,15 @@
         <v>777422731528745</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="409" spans="1:2" ht="14.4">
       <c r="A409" s="1" t="s">
-        <v>191</v>
+        <v>108</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="410" spans="1:2" ht="14.4">
@@ -5849,23 +5190,23 @@
         <v>465462045052132</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="411" spans="1:2" ht="14.4">
       <c r="A411" s="1" t="s">
-        <v>192</v>
+        <v>109</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="412" spans="1:2" ht="14.4">
       <c r="A412" s="1" t="s">
-        <v>193</v>
+        <v>110</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="413" spans="1:2" ht="14.4">
@@ -5873,15 +5214,15 @@
         <v>777422556482984</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="414" spans="1:2" ht="14.4">
       <c r="A414" s="1" t="s">
-        <v>194</v>
+        <v>111</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="415" spans="1:2" ht="14.4">
@@ -5889,7 +5230,7 @@
         <v>465464224986141</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="416" spans="1:2" ht="14.4">
@@ -5897,7 +5238,7 @@
         <v>465461539296139</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="417" spans="1:2" ht="14.4">
@@ -5905,15 +5246,15 @@
         <v>777422770801355</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="418" spans="1:2" ht="14.4">
       <c r="A418" s="1" t="s">
-        <v>195</v>
+        <v>112</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="419" spans="1:2" ht="14.4">
@@ -5921,7 +5262,7 @@
         <v>777423239248503</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="420" spans="1:2" ht="14.4">
@@ -5929,7 +5270,7 @@
         <v>79117651536910</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="421" spans="1:2" ht="14.4">
@@ -5937,7 +5278,7 @@
         <v>79117933681198</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="422" spans="1:2" ht="14.4">
@@ -5945,7 +5286,7 @@
         <v>9817627085660</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="423" spans="1:2" ht="14.4">
@@ -5953,15 +5294,15 @@
         <v>777422282995768</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="424" spans="1:2" ht="14.4">
       <c r="A424" s="1" t="s">
-        <v>196</v>
+        <v>113</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="425" spans="1:2" ht="14.4">
@@ -5969,7 +5310,7 @@
         <v>777423239698605</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="426" spans="1:2" ht="14.4">
@@ -5977,7 +5318,7 @@
         <v>465465103750961</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="427" spans="1:2" ht="14.4">
@@ -5985,7 +5326,7 @@
         <v>9817620085910</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="428" spans="1:2" ht="14.4">
@@ -5993,7 +5334,7 @@
         <v>465457413048475</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="429" spans="1:2" ht="14.4">
@@ -6001,15 +5342,15 @@
         <v>465456211470405</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="430" spans="1:2" ht="14.4">
       <c r="A430" s="1" t="s">
-        <v>197</v>
+        <v>114</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="431" spans="1:2" ht="14.4">
@@ -6017,7 +5358,7 @@
         <v>465464532957747</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="432" spans="1:2" ht="14.4">
@@ -6025,647 +5366,647 @@
         <v>777423140486346</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="433" spans="1:2" ht="14.4">
       <c r="A433" s="1" t="s">
-        <v>198</v>
+        <v>115</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="434" spans="1:2" ht="14.4">
       <c r="A434" s="1" t="s">
-        <v>199</v>
+        <v>116</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>721</v>
+        <v>638</v>
       </c>
     </row>
     <row r="436" spans="1:2" ht="14.4">
       <c r="A436" s="10" t="s">
-        <v>200</v>
+        <v>117</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="437" spans="1:2" ht="14.4">
       <c r="A437" s="9" t="s">
-        <v>201</v>
+        <v>118</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="438" spans="1:2" ht="14.4">
       <c r="A438" s="9" t="s">
-        <v>202</v>
+        <v>119</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="439" spans="1:2" ht="14.4">
       <c r="A439" s="9" t="s">
-        <v>203</v>
+        <v>120</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="440" spans="1:2" ht="14.4">
       <c r="A440" s="10" t="s">
-        <v>204</v>
+        <v>121</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="441" spans="1:2" ht="14.4">
       <c r="A441" s="10" t="s">
-        <v>205</v>
+        <v>122</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="442" spans="1:2" ht="14.4">
       <c r="A442" s="10" t="s">
-        <v>206</v>
+        <v>123</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="443" spans="1:2" ht="14.4">
       <c r="A443" s="10" t="s">
-        <v>207</v>
+        <v>124</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="444" spans="1:2" ht="14.4">
       <c r="A444" s="10" t="s">
-        <v>204</v>
+        <v>121</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="445" spans="1:2" ht="14.4">
       <c r="A445" s="10" t="s">
-        <v>208</v>
+        <v>125</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="446" spans="1:2" ht="14.4">
       <c r="A446" s="9" t="s">
-        <v>209</v>
+        <v>126</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="447" spans="1:2" ht="14.4">
       <c r="A447" s="10" t="s">
-        <v>210</v>
+        <v>127</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="448" spans="1:2" ht="14.4">
       <c r="A448" s="10" t="s">
-        <v>210</v>
+        <v>127</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="449" spans="1:2" ht="14.4">
       <c r="A449" s="10" t="s">
-        <v>211</v>
+        <v>128</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="450" spans="1:2" ht="14.4">
       <c r="A450" s="10" t="s">
-        <v>212</v>
+        <v>129</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="451" spans="1:2" ht="14.4">
       <c r="A451" s="10" t="s">
-        <v>213</v>
+        <v>130</v>
       </c>
       <c r="B451" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="452" spans="1:2" ht="14.4">
       <c r="A452" s="9" t="s">
-        <v>214</v>
+        <v>131</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="453" spans="1:2" ht="14.4">
       <c r="A453" s="10" t="s">
-        <v>215</v>
+        <v>132</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="454" spans="1:2" ht="14.4">
       <c r="A454" s="9" t="s">
-        <v>216</v>
+        <v>133</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="455" spans="1:2" ht="14.4">
       <c r="A455" s="9" t="s">
-        <v>217</v>
+        <v>134</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="456" spans="1:2" ht="14.4">
       <c r="A456" s="10" t="s">
-        <v>218</v>
+        <v>135</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="457" spans="1:2" ht="14.4">
       <c r="A457" s="10" t="s">
-        <v>219</v>
+        <v>136</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="458" spans="1:2" ht="14.4">
       <c r="A458" s="9" t="s">
-        <v>220</v>
+        <v>137</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="459" spans="1:2" ht="14.4">
       <c r="A459" s="9" t="s">
-        <v>221</v>
+        <v>138</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="460" spans="1:2" ht="14.4">
       <c r="A460" s="10" t="s">
-        <v>222</v>
+        <v>139</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="461" spans="1:2" ht="14.4">
       <c r="A461" s="9" t="s">
-        <v>223</v>
+        <v>140</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="462" spans="1:2" ht="14.4">
       <c r="A462" s="9" t="s">
-        <v>224</v>
+        <v>141</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="463" spans="1:2" ht="14.4">
       <c r="A463" s="9" t="s">
-        <v>225</v>
+        <v>142</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="464" spans="1:2" ht="14.4">
       <c r="A464" s="9" t="s">
-        <v>226</v>
+        <v>143</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="465" spans="1:2" ht="14.4">
       <c r="A465" s="10" t="s">
-        <v>227</v>
+        <v>144</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="466" spans="1:2" ht="14.4">
       <c r="A466" s="9" t="s">
-        <v>228</v>
+        <v>145</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="467" spans="1:2" ht="14.4">
       <c r="A467" s="10" t="s">
-        <v>229</v>
+        <v>146</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="468" spans="1:2" ht="14.4">
       <c r="A468" s="10" t="s">
-        <v>230</v>
+        <v>147</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="469" spans="1:2" ht="14.4">
       <c r="A469" s="10" t="s">
-        <v>231</v>
+        <v>148</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="470" spans="1:2" ht="14.4">
       <c r="A470" s="10" t="s">
-        <v>232</v>
+        <v>149</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="471" spans="1:2" ht="14.4">
       <c r="A471" s="10" t="s">
-        <v>233</v>
+        <v>150</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="472" spans="1:2" ht="14.4">
       <c r="A472" s="10" t="s">
-        <v>234</v>
+        <v>151</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="473" spans="1:2" ht="14.4">
       <c r="A473" s="10" t="s">
-        <v>235</v>
+        <v>152</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="474" spans="1:2" ht="14.4">
       <c r="A474" s="10" t="s">
-        <v>236</v>
+        <v>153</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="475" spans="1:2" ht="14.4">
       <c r="A475" s="10" t="s">
-        <v>237</v>
+        <v>154</v>
       </c>
       <c r="B475" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="476" spans="1:2" ht="14.4">
       <c r="A476" s="10" t="s">
-        <v>238</v>
+        <v>155</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="477" spans="1:2" ht="14.4">
       <c r="A477" s="10" t="s">
-        <v>239</v>
+        <v>156</v>
       </c>
       <c r="B477" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="478" spans="1:2" ht="14.4">
       <c r="A478" s="10" t="s">
-        <v>240</v>
+        <v>157</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="479" spans="1:2" ht="14.4">
       <c r="A479" s="10" t="s">
-        <v>241</v>
+        <v>158</v>
       </c>
       <c r="B479" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="480" spans="1:2" ht="14.4">
       <c r="A480" s="10" t="s">
-        <v>242</v>
+        <v>159</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="481" spans="1:2" ht="14.4">
       <c r="A481" s="10" t="s">
-        <v>243</v>
+        <v>160</v>
       </c>
       <c r="B481" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="482" spans="1:2" ht="14.4">
       <c r="A482" s="10" t="s">
-        <v>244</v>
+        <v>161</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="483" spans="1:2" ht="14.4">
       <c r="A483" s="10" t="s">
-        <v>245</v>
+        <v>162</v>
       </c>
       <c r="B483" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="484" spans="1:2" ht="14.4">
       <c r="A484" s="9" t="s">
-        <v>246</v>
+        <v>163</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="485" spans="1:2" ht="14.4">
       <c r="A485" s="9" t="s">
-        <v>247</v>
+        <v>164</v>
       </c>
       <c r="B485" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="486" spans="1:2" ht="14.4">
       <c r="A486" s="10" t="s">
-        <v>248</v>
+        <v>165</v>
       </c>
       <c r="B486" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="487" spans="1:2" ht="14.4">
       <c r="A487" s="10" t="s">
-        <v>249</v>
+        <v>166</v>
       </c>
       <c r="B487" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="488" spans="1:2" ht="14.4">
       <c r="A488" s="9" t="s">
-        <v>250</v>
+        <v>167</v>
       </c>
       <c r="B488" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="489" spans="1:2" ht="14.4">
       <c r="A489" s="10" t="s">
-        <v>251</v>
+        <v>168</v>
       </c>
       <c r="B489" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="490" spans="1:2" ht="14.4">
       <c r="A490" s="9" t="s">
-        <v>252</v>
+        <v>169</v>
       </c>
       <c r="B490" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="491" spans="1:2" ht="14.4">
       <c r="A491" s="9" t="s">
-        <v>253</v>
+        <v>170</v>
       </c>
       <c r="B491" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="492" spans="1:2" ht="14.4">
       <c r="A492" s="10" t="s">
-        <v>254</v>
+        <v>171</v>
       </c>
       <c r="B492" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="493" spans="1:2" ht="14.4">
       <c r="A493" s="9" t="s">
-        <v>255</v>
+        <v>172</v>
       </c>
       <c r="B493" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="494" spans="1:2" ht="14.4">
       <c r="A494" s="10" t="s">
-        <v>256</v>
+        <v>173</v>
       </c>
       <c r="B494" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="495" spans="1:2" ht="14.4">
       <c r="A495" s="9" t="s">
-        <v>257</v>
+        <v>174</v>
       </c>
       <c r="B495" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="496" spans="1:2" ht="14.4">
       <c r="A496" s="9" t="s">
-        <v>258</v>
+        <v>175</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="497" spans="1:2" ht="14.4">
       <c r="A497" s="9" t="s">
-        <v>259</v>
+        <v>176</v>
       </c>
       <c r="B497" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="498" spans="1:2" ht="14.4">
       <c r="A498" s="9" t="s">
-        <v>260</v>
+        <v>177</v>
       </c>
       <c r="B498" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="499" spans="1:2" ht="14.4">
       <c r="A499" s="10" t="s">
-        <v>261</v>
+        <v>178</v>
       </c>
       <c r="B499" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="500" spans="1:2" ht="14.4">
       <c r="A500" s="9" t="s">
-        <v>262</v>
+        <v>179</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="501" spans="1:2" ht="14.4">
       <c r="A501" s="10" t="s">
-        <v>263</v>
+        <v>180</v>
       </c>
       <c r="B501" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="502" spans="1:2" ht="14.4">
       <c r="A502" s="10" t="s">
-        <v>264</v>
+        <v>181</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="503" spans="1:2" ht="14.4">
       <c r="A503" s="10" t="s">
-        <v>265</v>
+        <v>182</v>
       </c>
       <c r="B503" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="504" spans="1:2" ht="14.4">
       <c r="A504" s="10" t="s">
-        <v>266</v>
+        <v>183</v>
       </c>
       <c r="B504" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="505" spans="1:2" ht="14.4">
       <c r="A505" s="10" t="s">
-        <v>267</v>
+        <v>184</v>
       </c>
       <c r="B505" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="506" spans="1:2" ht="14.4">
       <c r="A506" s="10" t="s">
-        <v>268</v>
+        <v>185</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="507" spans="1:2" ht="14.4">
       <c r="A507" s="10" t="s">
-        <v>269</v>
+        <v>186</v>
       </c>
       <c r="B507" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="508" spans="1:2" ht="14.4">
       <c r="A508" s="10" t="s">
-        <v>270</v>
+        <v>187</v>
       </c>
       <c r="B508" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="509" spans="1:2" ht="14.4">
       <c r="A509" s="10" t="s">
-        <v>271</v>
+        <v>188</v>
       </c>
       <c r="B509" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="510" spans="1:2" ht="14.4">
       <c r="A510" s="9" t="s">
-        <v>272</v>
+        <v>189</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="511" spans="1:2" ht="14.4">
       <c r="A511" s="10" t="s">
-        <v>273</v>
+        <v>190</v>
       </c>
       <c r="B511" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="512" spans="1:2" ht="14.4">
       <c r="A512" s="10" t="s">
-        <v>274</v>
+        <v>191</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="513" spans="1:2" ht="14.4">
       <c r="A513" s="10" t="s">
-        <v>227</v>
+        <v>144</v>
       </c>
       <c r="B513" s="1" t="s">
-        <v>722</v>
+        <v>639</v>
       </c>
     </row>
     <row r="515" spans="1:2" ht="14.4">
@@ -6904,610 +6245,610 @@
     </row>
     <row r="593" spans="1:2" ht="14.4">
       <c r="A593" s="10" t="s">
-        <v>452</v>
+        <v>369</v>
       </c>
       <c r="B593" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="594" spans="1:2" ht="14.4">
       <c r="A594" s="10" t="s">
-        <v>451</v>
+        <v>368</v>
       </c>
       <c r="B594" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="595" spans="1:2" ht="14.4">
       <c r="A595" s="9" t="s">
-        <v>450</v>
+        <v>367</v>
       </c>
       <c r="B595" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="596" spans="1:2" ht="14.4">
       <c r="A596" s="10" t="s">
-        <v>449</v>
+        <v>366</v>
       </c>
       <c r="B596" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="597" spans="1:2" ht="14.4">
       <c r="A597" s="10" t="s">
-        <v>448</v>
+        <v>365</v>
       </c>
       <c r="B597" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="598" spans="1:2" ht="14.4">
       <c r="A598" s="10" t="s">
-        <v>447</v>
+        <v>364</v>
       </c>
       <c r="B598" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="599" spans="1:2" ht="14.4">
       <c r="A599" s="9" t="s">
-        <v>446</v>
+        <v>363</v>
       </c>
       <c r="B599" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="600" spans="1:2" ht="14.4">
       <c r="A600" s="10" t="s">
-        <v>445</v>
+        <v>362</v>
       </c>
       <c r="B600" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="601" spans="1:2" ht="14.4">
       <c r="A601" s="10" t="s">
-        <v>444</v>
+        <v>361</v>
       </c>
       <c r="B601" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="602" spans="1:2" ht="14.4">
       <c r="A602" s="10" t="s">
-        <v>443</v>
+        <v>360</v>
       </c>
       <c r="B602" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="603" spans="1:2" ht="14.4">
       <c r="A603" s="9" t="s">
-        <v>442</v>
+        <v>359</v>
       </c>
       <c r="B603" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="604" spans="1:2" ht="14.4">
       <c r="A604" s="10" t="s">
-        <v>441</v>
+        <v>358</v>
       </c>
       <c r="B604" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="605" spans="1:2" ht="14.4">
       <c r="A605" s="10" t="s">
-        <v>440</v>
+        <v>357</v>
       </c>
       <c r="B605" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="606" spans="1:2" ht="14.4">
       <c r="A606" s="10" t="s">
-        <v>439</v>
+        <v>356</v>
       </c>
       <c r="B606" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="607" spans="1:2" ht="14.4">
       <c r="A607" s="10" t="s">
-        <v>438</v>
+        <v>355</v>
       </c>
       <c r="B607" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="608" spans="1:2" ht="14.4">
       <c r="A608" s="10" t="s">
-        <v>437</v>
+        <v>354</v>
       </c>
       <c r="B608" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="609" spans="1:2" ht="14.4">
       <c r="A609" s="10" t="s">
-        <v>436</v>
+        <v>353</v>
       </c>
       <c r="B609" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="610" spans="1:2" ht="14.4">
       <c r="A610" s="10" t="s">
-        <v>435</v>
+        <v>352</v>
       </c>
       <c r="B610" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="611" spans="1:2" ht="14.4">
       <c r="A611" s="9" t="s">
-        <v>434</v>
+        <v>351</v>
       </c>
       <c r="B611" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="612" spans="1:2" ht="14.4">
       <c r="A612" s="10" t="s">
-        <v>433</v>
+        <v>350</v>
       </c>
       <c r="B612" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="613" spans="1:2" ht="14.4">
       <c r="A613" s="10" t="s">
-        <v>432</v>
+        <v>349</v>
       </c>
       <c r="B613" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="614" spans="1:2" ht="14.4">
       <c r="A614" s="9" t="s">
-        <v>431</v>
+        <v>348</v>
       </c>
       <c r="B614" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="615" spans="1:2" ht="14.4">
       <c r="A615" s="10" t="s">
-        <v>430</v>
+        <v>347</v>
       </c>
       <c r="B615" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="616" spans="1:2" ht="14.4">
       <c r="A616" s="10" t="s">
-        <v>429</v>
+        <v>346</v>
       </c>
       <c r="B616" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="617" spans="1:2" ht="14.4">
       <c r="A617" s="9" t="s">
-        <v>428</v>
+        <v>345</v>
       </c>
       <c r="B617" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="618" spans="1:2" ht="14.4">
       <c r="A618" s="9" t="s">
-        <v>427</v>
+        <v>344</v>
       </c>
       <c r="B618" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="619" spans="1:2" ht="14.4">
       <c r="A619" s="10" t="s">
-        <v>426</v>
+        <v>343</v>
       </c>
       <c r="B619" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="620" spans="1:2" ht="14.4">
       <c r="A620" s="10" t="s">
-        <v>425</v>
+        <v>342</v>
       </c>
       <c r="B620" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="621" spans="1:2" ht="14.4">
       <c r="A621" s="9" t="s">
-        <v>424</v>
+        <v>341</v>
       </c>
       <c r="B621" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="622" spans="1:2" ht="14.4">
       <c r="A622" s="10" t="s">
-        <v>423</v>
+        <v>340</v>
       </c>
       <c r="B622" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="623" spans="1:2" ht="14.4">
       <c r="A623" s="10" t="s">
-        <v>422</v>
+        <v>339</v>
       </c>
       <c r="B623" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="624" spans="1:2" ht="14.4">
       <c r="A624" s="10" t="s">
-        <v>421</v>
+        <v>338</v>
       </c>
       <c r="B624" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="625" spans="1:2" ht="14.4">
       <c r="A625" s="10" t="s">
-        <v>420</v>
+        <v>337</v>
       </c>
       <c r="B625" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="626" spans="1:2" ht="14.4">
       <c r="A626" s="9" t="s">
-        <v>419</v>
+        <v>336</v>
       </c>
       <c r="B626" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="627" spans="1:2" ht="14.4">
       <c r="A627" s="10" t="s">
-        <v>418</v>
+        <v>335</v>
       </c>
       <c r="B627" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="628" spans="1:2" ht="14.4">
       <c r="A628" s="9" t="s">
-        <v>417</v>
+        <v>334</v>
       </c>
       <c r="B628" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="629" spans="1:2" ht="14.4">
       <c r="A629" s="10" t="s">
-        <v>416</v>
+        <v>333</v>
       </c>
       <c r="B629" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="630" spans="1:2" ht="14.4">
       <c r="A630" s="10" t="s">
-        <v>415</v>
+        <v>332</v>
       </c>
       <c r="B630" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="631" spans="1:2" ht="14.4">
       <c r="A631" s="9" t="s">
-        <v>414</v>
+        <v>331</v>
       </c>
       <c r="B631" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="632" spans="1:2" ht="14.4">
       <c r="A632" s="10" t="s">
-        <v>413</v>
+        <v>330</v>
       </c>
       <c r="B632" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="633" spans="1:2" ht="14.4">
       <c r="A633" s="10" t="s">
-        <v>412</v>
+        <v>329</v>
       </c>
       <c r="B633" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="634" spans="1:2" ht="14.4">
       <c r="A634" s="10" t="s">
-        <v>411</v>
+        <v>328</v>
       </c>
       <c r="B634" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="635" spans="1:2" ht="14.4">
       <c r="A635" s="10" t="s">
-        <v>410</v>
+        <v>327</v>
       </c>
       <c r="B635" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="636" spans="1:2" ht="14.4">
       <c r="A636" s="10" t="s">
-        <v>409</v>
+        <v>326</v>
       </c>
       <c r="B636" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="637" spans="1:2" ht="14.4">
       <c r="A637" s="9" t="s">
-        <v>408</v>
+        <v>325</v>
       </c>
       <c r="B637" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="638" spans="1:2" ht="14.4">
       <c r="A638" s="10" t="s">
-        <v>407</v>
+        <v>324</v>
       </c>
       <c r="B638" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="639" spans="1:2" ht="14.4">
       <c r="A639" s="10" t="s">
-        <v>406</v>
+        <v>323</v>
       </c>
       <c r="B639" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="640" spans="1:2" ht="14.4">
       <c r="A640" s="9" t="s">
-        <v>405</v>
+        <v>322</v>
       </c>
       <c r="B640" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="641" spans="1:2" ht="14.4">
       <c r="A641" s="9" t="s">
-        <v>404</v>
+        <v>321</v>
       </c>
       <c r="B641" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="642" spans="1:2" ht="14.4">
       <c r="A642" s="10" t="s">
-        <v>403</v>
+        <v>320</v>
       </c>
       <c r="B642" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="643" spans="1:2" ht="14.4">
       <c r="A643" s="10" t="s">
-        <v>402</v>
+        <v>319</v>
       </c>
       <c r="B643" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="644" spans="1:2" ht="14.4">
       <c r="A644" s="9" t="s">
-        <v>401</v>
+        <v>318</v>
       </c>
       <c r="B644" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="645" spans="1:2" ht="14.4">
       <c r="A645" s="9" t="s">
-        <v>400</v>
+        <v>317</v>
       </c>
       <c r="B645" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="646" spans="1:2" ht="14.4">
       <c r="A646" s="10" t="s">
-        <v>399</v>
+        <v>316</v>
       </c>
       <c r="B646" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="647" spans="1:2" ht="14.4">
       <c r="A647" s="9" t="s">
-        <v>398</v>
+        <v>315</v>
       </c>
       <c r="B647" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="648" spans="1:2" ht="14.4">
       <c r="A648" s="10" t="s">
-        <v>397</v>
+        <v>314</v>
       </c>
       <c r="B648" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="649" spans="1:2" ht="14.4">
       <c r="A649" s="9" t="s">
-        <v>396</v>
+        <v>313</v>
       </c>
       <c r="B649" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="650" spans="1:2" ht="14.4">
       <c r="A650" s="10" t="s">
-        <v>395</v>
+        <v>312</v>
       </c>
       <c r="B650" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="651" spans="1:2" ht="14.4">
       <c r="A651" s="10" t="s">
-        <v>394</v>
+        <v>311</v>
       </c>
       <c r="B651" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="652" spans="1:2" ht="14.4">
       <c r="A652" s="10" t="s">
-        <v>393</v>
+        <v>310</v>
       </c>
       <c r="B652" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="653" spans="1:2" ht="14.4">
       <c r="A653" s="9" t="s">
-        <v>392</v>
+        <v>309</v>
       </c>
       <c r="B653" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="654" spans="1:2" ht="14.4">
       <c r="A654" s="10" t="s">
-        <v>391</v>
+        <v>308</v>
       </c>
       <c r="B654" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="655" spans="1:2" ht="14.4">
       <c r="A655" s="10" t="s">
-        <v>390</v>
+        <v>307</v>
       </c>
       <c r="B655" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="656" spans="1:2" ht="14.4">
       <c r="A656" s="10" t="s">
-        <v>389</v>
+        <v>306</v>
       </c>
       <c r="B656" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="657" spans="1:2" ht="14.4">
       <c r="A657" s="9" t="s">
-        <v>388</v>
+        <v>305</v>
       </c>
       <c r="B657" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="658" spans="1:2" ht="14.4">
       <c r="A658" s="9" t="s">
-        <v>387</v>
+        <v>304</v>
       </c>
       <c r="B658" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="659" spans="1:2" ht="14.4">
       <c r="A659" s="10" t="s">
-        <v>386</v>
+        <v>303</v>
       </c>
       <c r="B659" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="660" spans="1:2" ht="14.4">
       <c r="A660" s="10" t="s">
-        <v>385</v>
+        <v>302</v>
       </c>
       <c r="B660" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="661" spans="1:2" ht="14.4">
       <c r="A661" s="10" t="s">
-        <v>384</v>
+        <v>301</v>
       </c>
       <c r="B661" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="662" spans="1:2" ht="14.4">
       <c r="A662" s="10" t="s">
-        <v>383</v>
+        <v>300</v>
       </c>
       <c r="B662" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="663" spans="1:2" ht="14.4">
       <c r="A663" s="10" t="s">
-        <v>382</v>
+        <v>299</v>
       </c>
       <c r="B663" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="664" spans="1:2" ht="14.4">
       <c r="A664" s="9" t="s">
-        <v>381</v>
+        <v>298</v>
       </c>
       <c r="B664" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="665" spans="1:2" ht="14.4">
       <c r="A665" s="10" t="s">
-        <v>380</v>
+        <v>297</v>
       </c>
       <c r="B665" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="666" spans="1:2" ht="14.4">
       <c r="A666" s="10" t="s">
-        <v>379</v>
+        <v>296</v>
       </c>
       <c r="B666" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="667" spans="1:2" ht="14.4">
       <c r="A667" s="10" t="s">
-        <v>378</v>
+        <v>295</v>
       </c>
       <c r="B667" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="668" spans="1:2" ht="14.4">
       <c r="A668" s="9" t="s">
-        <v>377</v>
+        <v>294</v>
       </c>
       <c r="B668" s="1" t="s">
-        <v>723</v>
+        <v>640</v>
       </c>
     </row>
     <row r="669" spans="1:2" ht="14.4">
@@ -7515,834 +6856,834 @@
     </row>
     <row r="670" spans="1:2" ht="14.4">
       <c r="A670" s="10" t="s">
-        <v>275</v>
+        <v>192</v>
       </c>
       <c r="B670" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="671" spans="1:2" ht="14.4">
       <c r="A671" s="10" t="s">
-        <v>343</v>
+        <v>260</v>
       </c>
       <c r="B671" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="672" spans="1:2" ht="14.4">
       <c r="A672" s="10" t="s">
-        <v>376</v>
+        <v>293</v>
       </c>
       <c r="B672" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="673" spans="1:2" ht="14.4">
       <c r="A673" s="9" t="s">
-        <v>375</v>
+        <v>292</v>
       </c>
       <c r="B673" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="674" spans="1:2" ht="14.4">
       <c r="A674" s="9" t="s">
-        <v>374</v>
+        <v>291</v>
       </c>
       <c r="B674" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="675" spans="1:2" ht="14.4">
       <c r="A675" s="10" t="s">
-        <v>373</v>
+        <v>290</v>
       </c>
       <c r="B675" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="676" spans="1:2" ht="14.4">
       <c r="A676" s="10" t="s">
-        <v>372</v>
+        <v>289</v>
       </c>
       <c r="B676" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="677" spans="1:2" ht="14.4">
       <c r="A677" s="9" t="s">
-        <v>371</v>
+        <v>288</v>
       </c>
       <c r="B677" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="678" spans="1:2" ht="14.4">
       <c r="A678" s="10" t="s">
-        <v>370</v>
+        <v>287</v>
       </c>
       <c r="B678" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="679" spans="1:2" ht="14.4">
       <c r="A679" s="10" t="s">
-        <v>369</v>
+        <v>286</v>
       </c>
       <c r="B679" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="680" spans="1:2" ht="14.4">
       <c r="A680" s="10" t="s">
-        <v>368</v>
+        <v>285</v>
       </c>
       <c r="B680" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="681" spans="1:2" ht="14.4">
       <c r="A681" s="10" t="s">
-        <v>367</v>
+        <v>284</v>
       </c>
       <c r="B681" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="682" spans="1:2" ht="14.4">
       <c r="A682" s="10" t="s">
-        <v>366</v>
+        <v>283</v>
       </c>
       <c r="B682" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="683" spans="1:2" ht="14.4">
       <c r="A683" s="9" t="s">
-        <v>365</v>
+        <v>282</v>
       </c>
       <c r="B683" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="684" spans="1:2" ht="14.4">
       <c r="A684" s="9" t="s">
-        <v>364</v>
+        <v>281</v>
       </c>
       <c r="B684" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="685" spans="1:2" ht="14.4">
       <c r="A685" s="9" t="s">
-        <v>363</v>
+        <v>280</v>
       </c>
       <c r="B685" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="686" spans="1:2" ht="14.4">
       <c r="A686" s="9" t="s">
-        <v>362</v>
+        <v>279</v>
       </c>
       <c r="B686" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="687" spans="1:2" ht="14.4">
       <c r="A687" s="9" t="s">
-        <v>361</v>
+        <v>278</v>
       </c>
       <c r="B687" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="688" spans="1:2" ht="14.4">
       <c r="A688" s="9" t="s">
-        <v>360</v>
+        <v>277</v>
       </c>
       <c r="B688" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="689" spans="1:2" ht="14.4">
       <c r="A689" s="10" t="s">
-        <v>359</v>
+        <v>276</v>
       </c>
       <c r="B689" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="690" spans="1:2" ht="14.4">
       <c r="A690" s="10" t="s">
-        <v>358</v>
+        <v>275</v>
       </c>
       <c r="B690" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="691" spans="1:2" ht="14.4">
       <c r="A691" s="9" t="s">
-        <v>357</v>
+        <v>274</v>
       </c>
       <c r="B691" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="692" spans="1:2" ht="14.4">
       <c r="A692" s="9" t="s">
-        <v>356</v>
+        <v>273</v>
       </c>
       <c r="B692" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="693" spans="1:2" ht="14.4">
       <c r="A693" s="9" t="s">
-        <v>355</v>
+        <v>272</v>
       </c>
       <c r="B693" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="694" spans="1:2" ht="14.4">
       <c r="A694" s="10" t="s">
-        <v>354</v>
+        <v>271</v>
       </c>
       <c r="B694" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="695" spans="1:2" ht="14.4">
       <c r="A695" s="10" t="s">
-        <v>353</v>
+        <v>270</v>
       </c>
       <c r="B695" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="696" spans="1:2" ht="14.4">
       <c r="A696" s="9" t="s">
-        <v>352</v>
+        <v>269</v>
       </c>
       <c r="B696" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="697" spans="1:2" ht="14.4">
       <c r="A697" s="10" t="s">
-        <v>351</v>
+        <v>268</v>
       </c>
       <c r="B697" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="698" spans="1:2" ht="14.4">
       <c r="A698" s="10" t="s">
-        <v>350</v>
+        <v>267</v>
       </c>
       <c r="B698" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="699" spans="1:2" ht="14.4">
       <c r="A699" s="9" t="s">
-        <v>349</v>
+        <v>266</v>
       </c>
       <c r="B699" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="700" spans="1:2" ht="14.4">
       <c r="A700" s="10" t="s">
-        <v>348</v>
+        <v>265</v>
       </c>
       <c r="B700" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="701" spans="1:2" ht="14.4">
       <c r="A701" s="10" t="s">
-        <v>347</v>
+        <v>264</v>
       </c>
       <c r="B701" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="702" spans="1:2" ht="14.4">
       <c r="A702" s="10" t="s">
-        <v>346</v>
+        <v>263</v>
       </c>
       <c r="B702" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="703" spans="1:2" ht="14.4">
       <c r="A703" s="9" t="s">
-        <v>345</v>
+        <v>262</v>
       </c>
       <c r="B703" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="704" spans="1:2" ht="14.4">
       <c r="A704" s="9" t="s">
-        <v>344</v>
+        <v>261</v>
       </c>
       <c r="B704" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="705" spans="1:2" ht="14.4">
       <c r="A705" s="10" t="s">
-        <v>343</v>
+        <v>260</v>
       </c>
       <c r="B705" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="706" spans="1:2" ht="14.4">
       <c r="A706" s="10" t="s">
-        <v>342</v>
+        <v>259</v>
       </c>
       <c r="B706" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="707" spans="1:2" ht="14.4">
       <c r="A707" s="9" t="s">
-        <v>341</v>
+        <v>258</v>
       </c>
       <c r="B707" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="708" spans="1:2" ht="14.4">
       <c r="A708" s="10" t="s">
-        <v>340</v>
+        <v>257</v>
       </c>
       <c r="B708" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="709" spans="1:2" ht="14.4">
       <c r="A709" s="10" t="s">
-        <v>339</v>
+        <v>256</v>
       </c>
       <c r="B709" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="710" spans="1:2" ht="14.4">
       <c r="A710" s="10" t="s">
-        <v>338</v>
+        <v>255</v>
       </c>
       <c r="B710" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="711" spans="1:2" ht="14.4">
       <c r="A711" s="10" t="s">
-        <v>337</v>
+        <v>254</v>
       </c>
       <c r="B711" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="712" spans="1:2" ht="14.4">
       <c r="A712" s="10" t="s">
-        <v>336</v>
+        <v>253</v>
       </c>
       <c r="B712" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="713" spans="1:2" ht="14.4">
       <c r="A713" s="10" t="s">
-        <v>335</v>
+        <v>252</v>
       </c>
       <c r="B713" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="714" spans="1:2" ht="14.4">
       <c r="A714" s="9" t="s">
-        <v>334</v>
+        <v>251</v>
       </c>
       <c r="B714" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="715" spans="1:2" ht="14.4">
       <c r="A715" s="10" t="s">
-        <v>333</v>
+        <v>250</v>
       </c>
       <c r="B715" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="716" spans="1:2" ht="14.4">
       <c r="A716" s="9" t="s">
-        <v>332</v>
+        <v>249</v>
       </c>
       <c r="B716" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="717" spans="1:2" ht="14.4">
       <c r="A717" s="9" t="s">
-        <v>331</v>
+        <v>248</v>
       </c>
       <c r="B717" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="718" spans="1:2" ht="14.4">
       <c r="A718" s="10" t="s">
-        <v>330</v>
+        <v>247</v>
       </c>
       <c r="B718" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="719" spans="1:2" ht="14.4">
       <c r="A719" s="9" t="s">
-        <v>329</v>
+        <v>246</v>
       </c>
       <c r="B719" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="720" spans="1:2" ht="14.4">
       <c r="A720" s="10" t="s">
-        <v>328</v>
+        <v>245</v>
       </c>
       <c r="B720" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="721" spans="1:2" ht="14.4">
       <c r="A721" s="10" t="s">
-        <v>327</v>
+        <v>244</v>
       </c>
       <c r="B721" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="722" spans="1:2" ht="14.4">
       <c r="A722" s="10" t="s">
-        <v>326</v>
+        <v>243</v>
       </c>
       <c r="B722" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="723" spans="1:2" ht="14.4">
       <c r="A723" s="10" t="s">
-        <v>325</v>
+        <v>242</v>
       </c>
       <c r="B723" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="724" spans="1:2" ht="14.4">
       <c r="A724" s="10" t="s">
-        <v>324</v>
+        <v>241</v>
       </c>
       <c r="B724" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="725" spans="1:2" ht="14.4">
       <c r="A725" s="10" t="s">
-        <v>323</v>
+        <v>240</v>
       </c>
       <c r="B725" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="726" spans="1:2" ht="14.4">
       <c r="A726" s="10" t="s">
-        <v>322</v>
+        <v>239</v>
       </c>
       <c r="B726" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="727" spans="1:2" ht="14.4">
       <c r="A727" s="10" t="s">
-        <v>321</v>
+        <v>238</v>
       </c>
       <c r="B727" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="728" spans="1:2" ht="14.4">
       <c r="A728" s="10" t="s">
-        <v>320</v>
+        <v>237</v>
       </c>
       <c r="B728" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="729" spans="1:2" ht="14.4">
       <c r="A729" s="10" t="s">
-        <v>319</v>
+        <v>236</v>
       </c>
       <c r="B729" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="730" spans="1:2" ht="14.4">
       <c r="A730" s="9" t="s">
-        <v>318</v>
+        <v>235</v>
       </c>
       <c r="B730" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="731" spans="1:2" ht="14.4">
       <c r="A731" s="10" t="s">
-        <v>317</v>
+        <v>234</v>
       </c>
       <c r="B731" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="732" spans="1:2" ht="14.4">
       <c r="A732" s="10" t="s">
-        <v>316</v>
+        <v>233</v>
       </c>
       <c r="B732" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="733" spans="1:2" ht="14.4">
       <c r="A733" s="10" t="s">
-        <v>315</v>
+        <v>232</v>
       </c>
       <c r="B733" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="734" spans="1:2" ht="14.4">
       <c r="A734" s="10" t="s">
-        <v>314</v>
+        <v>231</v>
       </c>
       <c r="B734" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="735" spans="1:2" ht="14.4">
       <c r="A735" s="9" t="s">
-        <v>313</v>
+        <v>230</v>
       </c>
       <c r="B735" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="736" spans="1:2" ht="14.4">
       <c r="A736" s="10" t="s">
-        <v>312</v>
+        <v>229</v>
       </c>
       <c r="B736" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="737" spans="1:2" ht="14.4">
       <c r="A737" s="9" t="s">
-        <v>311</v>
+        <v>228</v>
       </c>
       <c r="B737" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="738" spans="1:2" ht="14.4">
       <c r="A738" s="9" t="s">
-        <v>310</v>
+        <v>227</v>
       </c>
       <c r="B738" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="739" spans="1:2" ht="14.4">
       <c r="A739" s="10" t="s">
-        <v>309</v>
+        <v>226</v>
       </c>
       <c r="B739" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="740" spans="1:2" ht="14.4">
       <c r="A740" s="9" t="s">
-        <v>308</v>
+        <v>225</v>
       </c>
       <c r="B740" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="741" spans="1:2" ht="14.4">
       <c r="A741" s="9" t="s">
-        <v>307</v>
+        <v>224</v>
       </c>
       <c r="B741" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="742" spans="1:2" ht="14.4">
       <c r="A742" s="10" t="s">
-        <v>306</v>
+        <v>223</v>
       </c>
       <c r="B742" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="743" spans="1:2" ht="14.4">
       <c r="A743" s="10" t="s">
-        <v>305</v>
+        <v>222</v>
       </c>
       <c r="B743" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="744" spans="1:2" ht="14.4">
       <c r="A744" s="9" t="s">
-        <v>304</v>
+        <v>221</v>
       </c>
       <c r="B744" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="745" spans="1:2" ht="14.4">
       <c r="A745" s="9" t="s">
-        <v>303</v>
+        <v>220</v>
       </c>
       <c r="B745" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="746" spans="1:2" ht="14.4">
       <c r="A746" s="10" t="s">
-        <v>302</v>
+        <v>219</v>
       </c>
       <c r="B746" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="747" spans="1:2" ht="14.4">
       <c r="A747" s="10" t="s">
-        <v>301</v>
+        <v>218</v>
       </c>
       <c r="B747" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="748" spans="1:2" ht="14.4">
       <c r="A748" s="10" t="s">
-        <v>300</v>
+        <v>217</v>
       </c>
       <c r="B748" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="749" spans="1:2" ht="14.4">
       <c r="A749" s="10" t="s">
-        <v>299</v>
+        <v>216</v>
       </c>
       <c r="B749" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="750" spans="1:2" ht="14.4">
       <c r="A750" s="10" t="s">
-        <v>298</v>
+        <v>215</v>
       </c>
       <c r="B750" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="751" spans="1:2" ht="14.4">
       <c r="A751" s="10" t="s">
-        <v>297</v>
+        <v>214</v>
       </c>
       <c r="B751" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="752" spans="1:2" ht="14.4">
       <c r="A752" s="9" t="s">
-        <v>296</v>
+        <v>213</v>
       </c>
       <c r="B752" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="753" spans="1:2" ht="14.4">
       <c r="A753" s="10" t="s">
-        <v>295</v>
+        <v>212</v>
       </c>
       <c r="B753" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="754" spans="1:2" ht="14.4">
       <c r="A754" s="10" t="s">
-        <v>294</v>
+        <v>211</v>
       </c>
       <c r="B754" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="755" spans="1:2" ht="14.4">
       <c r="A755" s="10" t="s">
-        <v>293</v>
+        <v>210</v>
       </c>
       <c r="B755" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="756" spans="1:2" ht="14.4">
       <c r="A756" s="10" t="s">
-        <v>292</v>
+        <v>209</v>
       </c>
       <c r="B756" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="757" spans="1:2" ht="14.4">
       <c r="A757" s="10" t="s">
-        <v>291</v>
+        <v>208</v>
       </c>
       <c r="B757" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="758" spans="1:2" ht="14.4">
       <c r="A758" s="9" t="s">
-        <v>290</v>
+        <v>207</v>
       </c>
       <c r="B758" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="759" spans="1:2" ht="14.4">
       <c r="A759" s="9" t="s">
-        <v>289</v>
+        <v>206</v>
       </c>
       <c r="B759" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="760" spans="1:2" ht="14.4">
       <c r="A760" s="9" t="s">
-        <v>288</v>
+        <v>205</v>
       </c>
       <c r="B760" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="761" spans="1:2" ht="14.4">
       <c r="A761" s="10" t="s">
-        <v>287</v>
+        <v>204</v>
       </c>
       <c r="B761" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="762" spans="1:2" ht="14.4">
       <c r="A762" s="10" t="s">
-        <v>286</v>
+        <v>203</v>
       </c>
       <c r="B762" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="763" spans="1:2" ht="14.4">
       <c r="A763" s="10" t="s">
-        <v>285</v>
+        <v>202</v>
       </c>
       <c r="B763" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="764" spans="1:2" ht="14.4">
       <c r="A764" s="10" t="s">
-        <v>284</v>
+        <v>201</v>
       </c>
       <c r="B764" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="765" spans="1:2" ht="14.4">
       <c r="A765" s="9" t="s">
-        <v>283</v>
+        <v>200</v>
       </c>
       <c r="B765" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="766" spans="1:2" ht="14.4">
       <c r="A766" s="9" t="s">
-        <v>282</v>
+        <v>199</v>
       </c>
       <c r="B766" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="767" spans="1:2" ht="14.4">
       <c r="A767" s="10" t="s">
-        <v>281</v>
+        <v>198</v>
       </c>
       <c r="B767" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="768" spans="1:2" ht="14.4">
       <c r="A768" s="10" t="s">
-        <v>280</v>
+        <v>197</v>
       </c>
       <c r="B768" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="769" spans="1:2" ht="14.4">
       <c r="A769" s="10" t="s">
-        <v>279</v>
+        <v>196</v>
       </c>
       <c r="B769" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="770" spans="1:2" ht="14.4">
       <c r="A770" s="10" t="s">
-        <v>278</v>
+        <v>195</v>
       </c>
       <c r="B770" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="771" spans="1:2" ht="14.4">
       <c r="A771" s="10" t="s">
-        <v>277</v>
+        <v>194</v>
       </c>
       <c r="B771" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="772" spans="1:2" ht="14.4">
       <c r="A772" s="10" t="s">
-        <v>276</v>
+        <v>193</v>
       </c>
       <c r="B772" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="773" spans="1:2" ht="14.4">
       <c r="A773" s="10" t="s">
-        <v>275</v>
+        <v>192</v>
       </c>
       <c r="B773" s="1" t="s">
-        <v>724</v>
+        <v>641</v>
       </c>
     </row>
     <row r="775" spans="1:2" ht="14.4">
@@ -8350,1183 +7691,1183 @@
         <v>777425546939086</v>
       </c>
       <c r="B775" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="776" spans="1:2" ht="14.4">
       <c r="A776" s="10" t="s">
-        <v>609</v>
+        <v>526</v>
       </c>
       <c r="B776" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="777" spans="1:2" ht="14.4">
       <c r="A777" s="9" t="s">
-        <v>608</v>
+        <v>525</v>
       </c>
       <c r="B777" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="778" spans="1:2" ht="14.4">
       <c r="A778" s="10" t="s">
-        <v>607</v>
+        <v>524</v>
       </c>
       <c r="B778" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="779" spans="1:2" ht="14.4">
       <c r="A779" s="10" t="s">
-        <v>606</v>
+        <v>523</v>
       </c>
       <c r="B779" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="780" spans="1:2" ht="14.4">
       <c r="A780" s="9" t="s">
-        <v>605</v>
+        <v>522</v>
       </c>
       <c r="B780" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="781" spans="1:2" ht="14.4">
       <c r="A781" s="10" t="s">
-        <v>604</v>
+        <v>521</v>
       </c>
       <c r="B781" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="782" spans="1:2" ht="14.4">
       <c r="A782" s="10" t="s">
-        <v>603</v>
+        <v>520</v>
       </c>
       <c r="B782" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="783" spans="1:2" ht="14.4">
       <c r="A783" s="10" t="s">
-        <v>602</v>
+        <v>519</v>
       </c>
       <c r="B783" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="784" spans="1:2" ht="14.4">
       <c r="A784" s="10" t="s">
-        <v>601</v>
+        <v>518</v>
       </c>
       <c r="B784" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="785" spans="1:2" ht="14.4">
       <c r="A785" s="10" t="s">
-        <v>600</v>
+        <v>517</v>
       </c>
       <c r="B785" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="786" spans="1:2" ht="14.4">
       <c r="A786" s="10" t="s">
-        <v>599</v>
+        <v>516</v>
       </c>
       <c r="B786" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="787" spans="1:2" ht="14.4">
       <c r="A787" s="10" t="s">
-        <v>598</v>
+        <v>515</v>
       </c>
       <c r="B787" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="788" spans="1:2" ht="14.4">
       <c r="A788" s="10" t="s">
-        <v>597</v>
+        <v>514</v>
       </c>
       <c r="B788" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="789" spans="1:2" ht="14.4">
       <c r="A789" s="9" t="s">
-        <v>596</v>
+        <v>513</v>
       </c>
       <c r="B789" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="790" spans="1:2" ht="14.4">
       <c r="A790" s="10" t="s">
-        <v>595</v>
+        <v>512</v>
       </c>
       <c r="B790" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="791" spans="1:2" ht="14.4">
       <c r="A791" s="10" t="s">
-        <v>594</v>
+        <v>511</v>
       </c>
       <c r="B791" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="792" spans="1:2" ht="14.4">
       <c r="A792" s="10" t="s">
-        <v>593</v>
+        <v>510</v>
       </c>
       <c r="B792" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="793" spans="1:2" ht="14.4">
       <c r="A793" s="10" t="s">
-        <v>592</v>
+        <v>509</v>
       </c>
       <c r="B793" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="794" spans="1:2" ht="14.4">
       <c r="A794" s="10" t="s">
-        <v>591</v>
+        <v>508</v>
       </c>
       <c r="B794" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="795" spans="1:2" ht="14.4">
       <c r="A795" s="9" t="s">
-        <v>590</v>
+        <v>507</v>
       </c>
       <c r="B795" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="796" spans="1:2" ht="14.4">
       <c r="A796" s="10" t="s">
-        <v>589</v>
+        <v>506</v>
       </c>
       <c r="B796" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="797" spans="1:2" ht="14.4">
       <c r="A797" s="9" t="s">
-        <v>588</v>
+        <v>505</v>
       </c>
       <c r="B797" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="798" spans="1:2" ht="14.4">
       <c r="A798" s="10" t="s">
-        <v>587</v>
+        <v>504</v>
       </c>
       <c r="B798" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="799" spans="1:2" ht="14.4">
       <c r="A799" s="10" t="s">
-        <v>586</v>
+        <v>503</v>
       </c>
       <c r="B799" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="800" spans="1:2" ht="14.4">
       <c r="A800" s="10" t="s">
-        <v>585</v>
+        <v>502</v>
       </c>
       <c r="B800" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="801" spans="1:2" ht="14.4">
       <c r="A801" s="10" t="s">
-        <v>584</v>
+        <v>501</v>
       </c>
       <c r="B801" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="802" spans="1:2" ht="14.4">
       <c r="A802" s="10" t="s">
-        <v>583</v>
+        <v>500</v>
       </c>
       <c r="B802" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="803" spans="1:2" ht="14.4">
       <c r="A803" s="9" t="s">
-        <v>582</v>
+        <v>499</v>
       </c>
       <c r="B803" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="804" spans="1:2" ht="14.4">
       <c r="A804" s="10" t="s">
-        <v>581</v>
+        <v>498</v>
       </c>
       <c r="B804" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="805" spans="1:2" ht="14.4">
       <c r="A805" s="10" t="s">
-        <v>580</v>
+        <v>497</v>
       </c>
       <c r="B805" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="806" spans="1:2" ht="14.4">
       <c r="A806" s="10" t="s">
-        <v>579</v>
+        <v>496</v>
       </c>
       <c r="B806" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="807" spans="1:2" ht="14.4">
       <c r="A807" s="10" t="s">
-        <v>578</v>
+        <v>495</v>
       </c>
       <c r="B807" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="808" spans="1:2" ht="14.4">
       <c r="A808" s="9" t="s">
-        <v>577</v>
+        <v>494</v>
       </c>
       <c r="B808" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="809" spans="1:2" ht="14.4">
       <c r="A809" s="10" t="s">
-        <v>576</v>
+        <v>493</v>
       </c>
       <c r="B809" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="810" spans="1:2" ht="14.4">
       <c r="A810" s="10" t="s">
-        <v>575</v>
+        <v>492</v>
       </c>
       <c r="B810" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="811" spans="1:2" ht="14.4">
       <c r="A811" s="9" t="s">
-        <v>574</v>
+        <v>491</v>
       </c>
       <c r="B811" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="812" spans="1:2" ht="14.4">
       <c r="A812" s="9" t="s">
-        <v>573</v>
+        <v>490</v>
       </c>
       <c r="B812" s="1" t="s">
-        <v>610</v>
+        <v>527</v>
       </c>
     </row>
     <row r="814" spans="1:2" ht="14.4">
       <c r="A814" s="10" t="s">
-        <v>717</v>
+        <v>634</v>
       </c>
       <c r="B814" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="815" spans="1:2" ht="14.4">
       <c r="A815" s="10" t="s">
-        <v>716</v>
+        <v>633</v>
       </c>
       <c r="B815" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="816" spans="1:2" ht="14.4">
       <c r="A816" s="9" t="s">
-        <v>715</v>
+        <v>632</v>
       </c>
       <c r="B816" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="817" spans="1:2" ht="14.4">
       <c r="A817" s="10" t="s">
-        <v>714</v>
+        <v>631</v>
       </c>
       <c r="B817" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="818" spans="1:2" ht="14.4">
       <c r="A818" s="9" t="s">
-        <v>713</v>
+        <v>630</v>
       </c>
       <c r="B818" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="819" spans="1:2" ht="14.4">
       <c r="A819" s="10" t="s">
-        <v>712</v>
+        <v>629</v>
       </c>
       <c r="B819" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="820" spans="1:2" ht="14.4">
       <c r="A820" s="10" t="s">
-        <v>711</v>
+        <v>628</v>
       </c>
       <c r="B820" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="821" spans="1:2" ht="14.4">
       <c r="A821" s="9" t="s">
-        <v>637</v>
+        <v>554</v>
       </c>
       <c r="B821" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="822" spans="1:2" ht="14.4">
       <c r="A822" s="9" t="s">
-        <v>710</v>
+        <v>627</v>
       </c>
       <c r="B822" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="823" spans="1:2" ht="14.4">
       <c r="A823" s="10" t="s">
-        <v>709</v>
+        <v>626</v>
       </c>
       <c r="B823" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="824" spans="1:2" ht="14.4">
       <c r="A824" s="10" t="s">
-        <v>708</v>
+        <v>625</v>
       </c>
       <c r="B824" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="825" spans="1:2" ht="14.4">
       <c r="A825" s="10" t="s">
-        <v>707</v>
+        <v>624</v>
       </c>
       <c r="B825" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="826" spans="1:2" ht="14.4">
       <c r="A826" s="9" t="s">
-        <v>706</v>
+        <v>623</v>
       </c>
       <c r="B826" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="827" spans="1:2" ht="14.4">
       <c r="A827" s="10" t="s">
-        <v>705</v>
+        <v>622</v>
       </c>
       <c r="B827" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="828" spans="1:2" ht="14.4">
       <c r="A828" s="10" t="s">
-        <v>704</v>
+        <v>621</v>
       </c>
       <c r="B828" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="829" spans="1:2" ht="14.4">
       <c r="A829" s="9" t="s">
-        <v>703</v>
+        <v>620</v>
       </c>
       <c r="B829" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="830" spans="1:2" ht="14.4">
       <c r="A830" s="10" t="s">
-        <v>702</v>
+        <v>619</v>
       </c>
       <c r="B830" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="831" spans="1:2" ht="14.4">
       <c r="A831" s="9" t="s">
-        <v>701</v>
+        <v>618</v>
       </c>
       <c r="B831" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="832" spans="1:2" ht="14.4">
       <c r="A832" s="10" t="s">
-        <v>700</v>
+        <v>617</v>
       </c>
       <c r="B832" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="833" spans="1:2" ht="14.4">
       <c r="A833" s="10" t="s">
-        <v>699</v>
+        <v>616</v>
       </c>
       <c r="B833" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="834" spans="1:2" ht="14.4">
       <c r="A834" s="10" t="s">
-        <v>698</v>
+        <v>615</v>
       </c>
       <c r="B834" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="835" spans="1:2" ht="14.4">
       <c r="A835" s="10" t="s">
-        <v>697</v>
+        <v>614</v>
       </c>
       <c r="B835" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="836" spans="1:2" ht="14.4">
       <c r="A836" s="10" t="s">
-        <v>696</v>
+        <v>613</v>
       </c>
       <c r="B836" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="837" spans="1:2" ht="14.4">
       <c r="A837" s="9" t="s">
-        <v>695</v>
+        <v>612</v>
       </c>
       <c r="B837" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="838" spans="1:2" ht="14.4">
       <c r="A838" s="10" t="s">
-        <v>694</v>
+        <v>611</v>
       </c>
       <c r="B838" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="839" spans="1:2" ht="14.4">
       <c r="A839" s="9" t="s">
-        <v>693</v>
+        <v>610</v>
       </c>
       <c r="B839" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="840" spans="1:2" ht="14.4">
       <c r="A840" s="9" t="s">
-        <v>692</v>
+        <v>609</v>
       </c>
       <c r="B840" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="841" spans="1:2" ht="14.4">
       <c r="A841" s="10" t="s">
-        <v>691</v>
+        <v>608</v>
       </c>
       <c r="B841" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="842" spans="1:2" ht="14.4">
       <c r="A842" s="10" t="s">
-        <v>690</v>
+        <v>607</v>
       </c>
       <c r="B842" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="843" spans="1:2" ht="14.4">
       <c r="A843" s="10" t="s">
-        <v>689</v>
+        <v>606</v>
       </c>
       <c r="B843" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="844" spans="1:2" ht="14.4">
       <c r="A844" s="9" t="s">
-        <v>688</v>
+        <v>605</v>
       </c>
       <c r="B844" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="845" spans="1:2" ht="14.4">
       <c r="A845" s="9" t="s">
-        <v>687</v>
+        <v>604</v>
       </c>
       <c r="B845" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="846" spans="1:2" ht="14.4">
       <c r="A846" s="10" t="s">
-        <v>686</v>
+        <v>603</v>
       </c>
       <c r="B846" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="847" spans="1:2" ht="14.4">
       <c r="A847" s="10" t="s">
-        <v>685</v>
+        <v>602</v>
       </c>
       <c r="B847" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="848" spans="1:2" ht="14.4">
       <c r="A848" s="9" t="s">
-        <v>684</v>
+        <v>601</v>
       </c>
       <c r="B848" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="849" spans="1:2" ht="14.4">
       <c r="A849" s="10" t="s">
-        <v>683</v>
+        <v>600</v>
       </c>
       <c r="B849" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="850" spans="1:2" ht="14.4">
       <c r="A850" s="9" t="s">
-        <v>682</v>
+        <v>599</v>
       </c>
       <c r="B850" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="851" spans="1:2" ht="14.4">
       <c r="A851" s="9" t="s">
-        <v>681</v>
+        <v>598</v>
       </c>
       <c r="B851" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="852" spans="1:2" ht="14.4">
       <c r="A852" s="9" t="s">
-        <v>680</v>
+        <v>597</v>
       </c>
       <c r="B852" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="853" spans="1:2" ht="14.4">
       <c r="A853" s="10" t="s">
-        <v>679</v>
+        <v>596</v>
       </c>
       <c r="B853" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="854" spans="1:2" ht="14.4">
       <c r="A854" s="9" t="s">
-        <v>678</v>
+        <v>595</v>
       </c>
       <c r="B854" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="855" spans="1:2" ht="14.4">
       <c r="A855" s="10" t="s">
-        <v>677</v>
+        <v>594</v>
       </c>
       <c r="B855" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="856" spans="1:2" ht="14.4">
       <c r="A856" s="10" t="s">
-        <v>676</v>
+        <v>593</v>
       </c>
       <c r="B856" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="857" spans="1:2" ht="14.4">
       <c r="A857" s="9" t="s">
-        <v>675</v>
+        <v>592</v>
       </c>
       <c r="B857" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="858" spans="1:2" ht="14.4">
       <c r="A858" s="9" t="s">
-        <v>674</v>
+        <v>591</v>
       </c>
       <c r="B858" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="859" spans="1:2" ht="14.4">
       <c r="A859" s="9" t="s">
-        <v>673</v>
+        <v>590</v>
       </c>
       <c r="B859" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="860" spans="1:2" ht="14.4">
       <c r="A860" s="10" t="s">
-        <v>672</v>
+        <v>589</v>
       </c>
       <c r="B860" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="861" spans="1:2" ht="14.4">
       <c r="A861" s="10" t="s">
-        <v>671</v>
+        <v>588</v>
       </c>
       <c r="B861" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="862" spans="1:2" ht="14.4">
       <c r="A862" s="10" t="s">
-        <v>670</v>
+        <v>587</v>
       </c>
       <c r="B862" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="863" spans="1:2" ht="14.4">
       <c r="A863" s="9" t="s">
-        <v>669</v>
+        <v>586</v>
       </c>
       <c r="B863" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="864" spans="1:2" ht="14.4">
       <c r="A864" s="9" t="s">
-        <v>668</v>
+        <v>585</v>
       </c>
       <c r="B864" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="865" spans="1:2" ht="14.4">
       <c r="A865" s="10" t="s">
-        <v>667</v>
+        <v>584</v>
       </c>
       <c r="B865" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="866" spans="1:2" ht="14.4">
       <c r="A866" s="9" t="s">
-        <v>666</v>
+        <v>583</v>
       </c>
       <c r="B866" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="867" spans="1:2" ht="14.4">
       <c r="A867" s="10" t="s">
-        <v>665</v>
+        <v>582</v>
       </c>
       <c r="B867" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="868" spans="1:2" ht="14.4">
       <c r="A868" s="10" t="s">
-        <v>664</v>
+        <v>581</v>
       </c>
       <c r="B868" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="869" spans="1:2" ht="14.4">
       <c r="A869" s="9" t="s">
-        <v>663</v>
+        <v>580</v>
       </c>
       <c r="B869" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="870" spans="1:2" ht="14.4">
       <c r="A870" s="10" t="s">
-        <v>662</v>
+        <v>579</v>
       </c>
       <c r="B870" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="871" spans="1:2" ht="14.4">
       <c r="A871" s="10" t="s">
-        <v>661</v>
+        <v>578</v>
       </c>
       <c r="B871" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="872" spans="1:2" ht="14.4">
       <c r="A872" s="9" t="s">
-        <v>660</v>
+        <v>577</v>
       </c>
       <c r="B872" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="873" spans="1:2" ht="14.4">
       <c r="A873" s="9" t="s">
-        <v>659</v>
+        <v>576</v>
       </c>
       <c r="B873" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="874" spans="1:2" ht="14.4">
       <c r="A874" s="9" t="s">
-        <v>658</v>
+        <v>575</v>
       </c>
       <c r="B874" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="875" spans="1:2" ht="14.4">
       <c r="A875" s="10" t="s">
-        <v>657</v>
+        <v>574</v>
       </c>
       <c r="B875" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="876" spans="1:2" ht="14.4">
       <c r="A876" s="10" t="s">
-        <v>656</v>
+        <v>573</v>
       </c>
       <c r="B876" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="877" spans="1:2" ht="14.4">
       <c r="A877" s="10" t="s">
-        <v>655</v>
+        <v>572</v>
       </c>
       <c r="B877" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="878" spans="1:2" ht="14.4">
       <c r="A878" s="10" t="s">
-        <v>654</v>
+        <v>571</v>
       </c>
       <c r="B878" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="879" spans="1:2" ht="14.4">
       <c r="A879" s="9" t="s">
-        <v>653</v>
+        <v>570</v>
       </c>
       <c r="B879" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="880" spans="1:2" ht="14.4">
       <c r="A880" s="10" t="s">
-        <v>652</v>
+        <v>569</v>
       </c>
       <c r="B880" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="881" spans="1:2" ht="14.4">
       <c r="A881" s="10" t="s">
-        <v>651</v>
+        <v>568</v>
       </c>
       <c r="B881" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="882" spans="1:2" ht="14.4">
       <c r="A882" s="9" t="s">
-        <v>650</v>
+        <v>567</v>
       </c>
       <c r="B882" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="883" spans="1:2" ht="14.4">
       <c r="A883" s="10" t="s">
-        <v>649</v>
+        <v>566</v>
       </c>
       <c r="B883" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="884" spans="1:2" ht="14.4">
       <c r="A884" s="10" t="s">
-        <v>648</v>
+        <v>565</v>
       </c>
       <c r="B884" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="885" spans="1:2" ht="14.4">
       <c r="A885" s="10" t="s">
-        <v>647</v>
+        <v>564</v>
       </c>
       <c r="B885" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="886" spans="1:2" ht="14.4">
       <c r="A886" s="10" t="s">
-        <v>646</v>
+        <v>563</v>
       </c>
       <c r="B886" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="887" spans="1:2" ht="14.4">
       <c r="A887" s="10" t="s">
-        <v>634</v>
+        <v>551</v>
       </c>
       <c r="B887" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="888" spans="1:2" ht="14.4">
       <c r="A888" s="10" t="s">
-        <v>645</v>
+        <v>562</v>
       </c>
       <c r="B888" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="889" spans="1:2" ht="14.4">
       <c r="A889" s="9" t="s">
-        <v>644</v>
+        <v>561</v>
       </c>
       <c r="B889" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="890" spans="1:2" ht="14.4">
       <c r="A890" s="9" t="s">
-        <v>643</v>
+        <v>560</v>
       </c>
       <c r="B890" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="891" spans="1:2" ht="14.4">
       <c r="A891" s="10" t="s">
-        <v>642</v>
+        <v>559</v>
       </c>
       <c r="B891" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="892" spans="1:2" ht="14.4">
       <c r="A892" s="10" t="s">
-        <v>641</v>
+        <v>558</v>
       </c>
       <c r="B892" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="893" spans="1:2" ht="14.4">
       <c r="A893" s="10" t="s">
-        <v>640</v>
+        <v>557</v>
       </c>
       <c r="B893" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="894" spans="1:2" ht="14.4">
       <c r="A894" s="9" t="s">
-        <v>639</v>
+        <v>556</v>
       </c>
       <c r="B894" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="895" spans="1:2" ht="14.4">
       <c r="A895" s="10" t="s">
-        <v>635</v>
+        <v>552</v>
       </c>
       <c r="B895" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="896" spans="1:2" ht="14.4">
       <c r="A896" s="10" t="s">
-        <v>638</v>
+        <v>555</v>
       </c>
       <c r="B896" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="897" spans="1:2" ht="14.4">
       <c r="A897" s="9" t="s">
-        <v>637</v>
+        <v>554</v>
       </c>
       <c r="B897" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="898" spans="1:2" ht="14.4">
       <c r="A898" s="9" t="s">
-        <v>636</v>
+        <v>553</v>
       </c>
       <c r="B898" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="899" spans="1:2" ht="14.4">
       <c r="A899" s="10" t="s">
-        <v>635</v>
+        <v>552</v>
       </c>
       <c r="B899" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="900" spans="1:2" ht="14.4">
       <c r="A900" s="10" t="s">
-        <v>634</v>
+        <v>551</v>
       </c>
       <c r="B900" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="901" spans="1:2" ht="14.4">
       <c r="A901" s="10" t="s">
-        <v>633</v>
+        <v>550</v>
       </c>
       <c r="B901" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="902" spans="1:2" ht="14.4">
       <c r="A902" s="10" t="s">
-        <v>632</v>
+        <v>549</v>
       </c>
       <c r="B902" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="903" spans="1:2" ht="14.4">
       <c r="A903" s="10" t="s">
-        <v>631</v>
+        <v>548</v>
       </c>
       <c r="B903" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="904" spans="1:2" ht="14.4">
       <c r="A904" s="9" t="s">
-        <v>630</v>
+        <v>547</v>
       </c>
       <c r="B904" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="905" spans="1:2" ht="14.4">
       <c r="A905" s="9" t="s">
-        <v>629</v>
+        <v>546</v>
       </c>
       <c r="B905" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="906" spans="1:2" ht="14.4">
       <c r="A906" s="10" t="s">
-        <v>628</v>
+        <v>545</v>
       </c>
       <c r="B906" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="907" spans="1:2" ht="14.4">
       <c r="A907" s="10" t="s">
-        <v>627</v>
+        <v>544</v>
       </c>
       <c r="B907" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="908" spans="1:2" ht="14.4">
       <c r="A908" s="10" t="s">
-        <v>626</v>
+        <v>543</v>
       </c>
       <c r="B908" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="909" spans="1:2" ht="14.4">
       <c r="A909" s="9" t="s">
-        <v>625</v>
+        <v>542</v>
       </c>
       <c r="B909" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="910" spans="1:2" ht="14.4">
       <c r="A910" s="10" t="s">
-        <v>624</v>
+        <v>541</v>
       </c>
       <c r="B910" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="911" spans="1:2" ht="14.4">
       <c r="A911" s="10" t="s">
-        <v>623</v>
+        <v>540</v>
       </c>
       <c r="B911" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="912" spans="1:2" ht="14.4">
       <c r="A912" s="10" t="s">
-        <v>622</v>
+        <v>539</v>
       </c>
       <c r="B912" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="913" spans="1:2" ht="14.4">
       <c r="A913" s="10" t="s">
-        <v>621</v>
+        <v>538</v>
       </c>
       <c r="B913" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="914" spans="1:2" ht="14.4">
       <c r="A914" s="9" t="s">
-        <v>620</v>
+        <v>537</v>
       </c>
       <c r="B914" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="915" spans="1:2" ht="14.4">
       <c r="A915" s="10" t="s">
-        <v>619</v>
+        <v>536</v>
       </c>
       <c r="B915" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="916" spans="1:2" ht="14.4">
       <c r="A916" s="10" t="s">
-        <v>618</v>
+        <v>535</v>
       </c>
       <c r="B916" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="917" spans="1:2" ht="14.4">
       <c r="A917" s="10" t="s">
-        <v>617</v>
+        <v>534</v>
       </c>
       <c r="B917" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="918" spans="1:2" ht="14.4">
       <c r="A918" s="9" t="s">
-        <v>616</v>
+        <v>533</v>
       </c>
       <c r="B918" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="919" spans="1:2" ht="14.4">
       <c r="A919" s="10" t="s">
-        <v>615</v>
+        <v>532</v>
       </c>
       <c r="B919" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="920" spans="1:2" ht="14.4">
       <c r="A920" s="9" t="s">
-        <v>614</v>
+        <v>531</v>
       </c>
       <c r="B920" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="921" spans="1:2" ht="14.4">
       <c r="A921" s="9" t="s">
-        <v>613</v>
+        <v>530</v>
       </c>
       <c r="B921" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="922" spans="1:2" ht="14.4">
       <c r="A922" s="9" t="s">
-        <v>612</v>
+        <v>529</v>
       </c>
       <c r="B922" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
     <row r="923" spans="1:2" ht="14.4">
       <c r="A923" s="10" t="s">
-        <v>611</v>
+        <v>528</v>
       </c>
       <c r="B923" s="1" t="s">
-        <v>725</v>
+        <v>642</v>
       </c>
     </row>
   </sheetData>

--- a/on_the_way.xlsx
+++ b/on_the_way.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="643">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="867">
   <si>
     <t>Track</t>
   </si>
@@ -1945,6 +1945,678 @@
   </si>
   <si>
     <t>20.07.26</t>
+  </si>
+  <si>
+    <t>465510460307851</t>
+  </si>
+  <si>
+    <t>JT5507337898487</t>
+  </si>
+  <si>
+    <t>79019435474422</t>
+  </si>
+  <si>
+    <t>777428265484423</t>
+  </si>
+  <si>
+    <t>465515646672564</t>
+  </si>
+  <si>
+    <t>79123166392831</t>
+  </si>
+  <si>
+    <t>777427635693095</t>
+  </si>
+  <si>
+    <t>JT5507276114172</t>
+  </si>
+  <si>
+    <t>777428182458625</t>
+  </si>
+  <si>
+    <t>79123239816408</t>
+  </si>
+  <si>
+    <t>777427612934180</t>
+  </si>
+  <si>
+    <t>JT5507203669617</t>
+  </si>
+  <si>
+    <t>79123106747998</t>
+  </si>
+  <si>
+    <t>JT5506186308031</t>
+  </si>
+  <si>
+    <t>79123252656006</t>
+  </si>
+  <si>
+    <t>435274435411742</t>
+  </si>
+  <si>
+    <t>79123570328412</t>
+  </si>
+  <si>
+    <t>YT8887716104052</t>
+  </si>
+  <si>
+    <t>79123114287214</t>
+  </si>
+  <si>
+    <t>YT8887865004609</t>
+  </si>
+  <si>
+    <t>777427958247663</t>
+  </si>
+  <si>
+    <t>465514479319672</t>
+  </si>
+  <si>
+    <t>777427962413779</t>
+  </si>
+  <si>
+    <t>79123098652802</t>
+  </si>
+  <si>
+    <t>YT8888105378643</t>
+  </si>
+  <si>
+    <t>JT5506307113595</t>
+  </si>
+  <si>
+    <t>JT5507237177763</t>
+  </si>
+  <si>
+    <t>JT5506626995922</t>
+  </si>
+  <si>
+    <t>79123085410794</t>
+  </si>
+  <si>
+    <t>JT5507324542496</t>
+  </si>
+  <si>
+    <t>JT5506232592542</t>
+  </si>
+  <si>
+    <t>JT5506221766106</t>
+  </si>
+  <si>
+    <t>773432034780670</t>
+  </si>
+  <si>
+    <t>777428024999640</t>
+  </si>
+  <si>
+    <t>YT8887564921339</t>
+  </si>
+  <si>
+    <t>465514648477851</t>
+  </si>
+  <si>
+    <t>YT8887415841436</t>
+  </si>
+  <si>
+    <t>JT5506173436073</t>
+  </si>
+  <si>
+    <t>465505833882627</t>
+  </si>
+  <si>
+    <t>JT5506461519158</t>
+  </si>
+  <si>
+    <t>79123182559533</t>
+  </si>
+  <si>
+    <t>YT8887558230557</t>
+  </si>
+  <si>
+    <t>465513976759928</t>
+  </si>
+  <si>
+    <t>777427933079050</t>
+  </si>
+  <si>
+    <t>JT5506658558624</t>
+  </si>
+  <si>
+    <t>777427938573474</t>
+  </si>
+  <si>
+    <t>465510240057912</t>
+  </si>
+  <si>
+    <t>JT5506179560811</t>
+  </si>
+  <si>
+    <t>JT5506336304725</t>
+  </si>
+  <si>
+    <t>YT8887501949475</t>
+  </si>
+  <si>
+    <t>JT5506418660495</t>
+  </si>
+  <si>
+    <t>465504078480174</t>
+  </si>
+  <si>
+    <t>JT9001576894302</t>
+  </si>
+  <si>
+    <t>JT5505794604522</t>
+  </si>
+  <si>
+    <t>777427923003751</t>
+  </si>
+  <si>
+    <t>465516060265840</t>
+  </si>
+  <si>
+    <t>465505840210088</t>
+  </si>
+  <si>
+    <t>465514444026213</t>
+  </si>
+  <si>
+    <t>YT8887562635203</t>
+  </si>
+  <si>
+    <t>777427584520146</t>
+  </si>
+  <si>
+    <t>465514871468417</t>
+  </si>
+  <si>
+    <t>777427997167390</t>
+  </si>
+  <si>
+    <t>777427562006041</t>
+  </si>
+  <si>
+    <t>777427548979794</t>
+  </si>
+  <si>
+    <t>JT9001570009876</t>
+  </si>
+  <si>
+    <t>JT5507244554173</t>
+  </si>
+  <si>
+    <t>465510505044154</t>
+  </si>
+  <si>
+    <t>777428378951961</t>
+  </si>
+  <si>
+    <t>777428637814555</t>
+  </si>
+  <si>
+    <t>YT8888515293154</t>
+  </si>
+  <si>
+    <t>777427507401185</t>
+  </si>
+  <si>
+    <t>YT8888537584100</t>
+  </si>
+  <si>
+    <t>YT8887569556680</t>
+  </si>
+  <si>
+    <t>465511136676140</t>
+  </si>
+  <si>
+    <t>22.07.26</t>
+  </si>
+  <si>
+    <t>9818093692863</t>
+  </si>
+  <si>
+    <t>777428444129030</t>
+  </si>
+  <si>
+    <t>9818072983732</t>
+  </si>
+  <si>
+    <t>465522915619192</t>
+  </si>
+  <si>
+    <t>79019659011425</t>
+  </si>
+  <si>
+    <t>79123798032324</t>
+  </si>
+  <si>
+    <t>9818180581994</t>
+  </si>
+  <si>
+    <t>9818138761106</t>
+  </si>
+  <si>
+    <t>JT5507144076361</t>
+  </si>
+  <si>
+    <t>9818172123217</t>
+  </si>
+  <si>
+    <t>9818111039401</t>
+  </si>
+  <si>
+    <t>9818180980604</t>
+  </si>
+  <si>
+    <t>9818122486430</t>
+  </si>
+  <si>
+    <t>773432223697761</t>
+  </si>
+  <si>
+    <t>777427625098257</t>
+  </si>
+  <si>
+    <t>79123488727326</t>
+  </si>
+  <si>
+    <t>9818116933963</t>
+  </si>
+  <si>
+    <t>9818070555800</t>
+  </si>
+  <si>
+    <t>9818082414629</t>
+  </si>
+  <si>
+    <t>777428489819234</t>
+  </si>
+  <si>
+    <t>79123665608643</t>
+  </si>
+  <si>
+    <t>9818091703204</t>
+  </si>
+  <si>
+    <t>465520446419119</t>
+  </si>
+  <si>
+    <t>9818093298447</t>
+  </si>
+  <si>
+    <t>79123395536493</t>
+  </si>
+  <si>
+    <t>777428218867597</t>
+  </si>
+  <si>
+    <t>YT8888308339274</t>
+  </si>
+  <si>
+    <t>9818187182439</t>
+  </si>
+  <si>
+    <t>9818127090526</t>
+  </si>
+  <si>
+    <t>9818106766725</t>
+  </si>
+  <si>
+    <t>9818138403691</t>
+  </si>
+  <si>
+    <t>777428534262087</t>
+  </si>
+  <si>
+    <t>YT8888324621641</t>
+  </si>
+  <si>
+    <t>9818143746867</t>
+  </si>
+  <si>
+    <t>9818114512539</t>
+  </si>
+  <si>
+    <t>465521357894421</t>
+  </si>
+  <si>
+    <t>JT5506823984702</t>
+  </si>
+  <si>
+    <t>9818110603935</t>
+  </si>
+  <si>
+    <t>9818122256458</t>
+  </si>
+  <si>
+    <t>777428509196955</t>
+  </si>
+  <si>
+    <t>465521950123855</t>
+  </si>
+  <si>
+    <t>YT8889172189248</t>
+  </si>
+  <si>
+    <t>YT8888253835016</t>
+  </si>
+  <si>
+    <t>465517769716193</t>
+  </si>
+  <si>
+    <t>9818139113611</t>
+  </si>
+  <si>
+    <t>9818141869938</t>
+  </si>
+  <si>
+    <t>79123535621138</t>
+  </si>
+  <si>
+    <t>79123707154281</t>
+  </si>
+  <si>
+    <t>YT8888426812721</t>
+  </si>
+  <si>
+    <t>465517949919201</t>
+  </si>
+  <si>
+    <t>777428636239359</t>
+  </si>
+  <si>
+    <t>JT5507113656781</t>
+  </si>
+  <si>
+    <t>465520579629016</t>
+  </si>
+  <si>
+    <t>777428482644970</t>
+  </si>
+  <si>
+    <t>YT8887969967981</t>
+  </si>
+  <si>
+    <t>JT5506803649727</t>
+  </si>
+  <si>
+    <t>777428624964212</t>
+  </si>
+  <si>
+    <t>YT8888060085600</t>
+  </si>
+  <si>
+    <t>9818135183313</t>
+  </si>
+  <si>
+    <t>23.07.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   </t>
+  </si>
+  <si>
+    <t>JT5507810272778</t>
+  </si>
+  <si>
+    <t>JT5507404645358</t>
+  </si>
+  <si>
+    <t>777429103658216</t>
+  </si>
+  <si>
+    <t>YT8889111284942</t>
+  </si>
+  <si>
+    <t>JT5507404683676</t>
+  </si>
+  <si>
+    <t>79123988777582</t>
+  </si>
+  <si>
+    <t>777428968829152</t>
+  </si>
+  <si>
+    <t>JT5506903391720</t>
+  </si>
+  <si>
+    <t>465522096178285</t>
+  </si>
+  <si>
+    <t>79122927323997</t>
+  </si>
+  <si>
+    <t>465522164948717</t>
+  </si>
+  <si>
+    <t>YT8889131620540</t>
+  </si>
+  <si>
+    <t>777428816310939</t>
+  </si>
+  <si>
+    <t>YT8889143234360</t>
+  </si>
+  <si>
+    <t>JT5506686036938</t>
+  </si>
+  <si>
+    <t>YT8888941019542</t>
+  </si>
+  <si>
+    <t>465522009355527</t>
+  </si>
+  <si>
+    <t>JT5507648674820</t>
+  </si>
+  <si>
+    <t>777428778700486</t>
+  </si>
+  <si>
+    <t>YT8888764144757</t>
+  </si>
+  <si>
+    <t>777429018415064</t>
+  </si>
+  <si>
+    <t>465521895381574</t>
+  </si>
+  <si>
+    <t>79124072521556</t>
+  </si>
+  <si>
+    <t>YT7634106006439</t>
+  </si>
+  <si>
+    <t>79124177130815</t>
+  </si>
+  <si>
+    <t>JT5507540885564</t>
+  </si>
+  <si>
+    <t>465521852388801</t>
+  </si>
+  <si>
+    <t>YT8889229566330</t>
+  </si>
+  <si>
+    <t>777428809958638</t>
+  </si>
+  <si>
+    <t>79123908503229</t>
+  </si>
+  <si>
+    <t>79124089149990</t>
+  </si>
+  <si>
+    <t>YT8889196281665</t>
+  </si>
+  <si>
+    <t>777428772503247</t>
+  </si>
+  <si>
+    <t>777429080653565</t>
+  </si>
+  <si>
+    <t>YT8889229407323</t>
+  </si>
+  <si>
+    <t>JT5507734587401</t>
+  </si>
+  <si>
+    <t>777428781524849</t>
+  </si>
+  <si>
+    <t>777428495030249</t>
+  </si>
+  <si>
+    <t>JT5507551803751</t>
+  </si>
+  <si>
+    <t>JT5506781522812</t>
+  </si>
+  <si>
+    <t>79124036277998</t>
+  </si>
+  <si>
+    <t>79124052917179</t>
+  </si>
+  <si>
+    <t>YT7633834106110</t>
+  </si>
+  <si>
+    <t>9818088835384</t>
+  </si>
+  <si>
+    <t>465521705851554</t>
+  </si>
+  <si>
+    <t>465523480801307</t>
+  </si>
+  <si>
+    <t>465520406310173</t>
+  </si>
+  <si>
+    <t>465523662773323</t>
+  </si>
+  <si>
+    <t>465518484009777</t>
+  </si>
+  <si>
+    <t>465518884606813</t>
+  </si>
+  <si>
+    <t>79124653204855</t>
+  </si>
+  <si>
+    <t>79124573214025</t>
+  </si>
+  <si>
+    <t>9818155773148</t>
+  </si>
+  <si>
+    <t>YT8889465925728</t>
+  </si>
+  <si>
+    <t>YT8888939712837</t>
+  </si>
+  <si>
+    <t>9818184952568</t>
+  </si>
+  <si>
+    <t>777428863470145</t>
+  </si>
+  <si>
+    <t>9818173914565</t>
+  </si>
+  <si>
+    <t>9818183115232</t>
+  </si>
+  <si>
+    <t>465525303220879</t>
+  </si>
+  <si>
+    <t>YT8889141925701</t>
+  </si>
+  <si>
+    <t>9818252184495</t>
+  </si>
+  <si>
+    <t>79124748390613</t>
+  </si>
+  <si>
+    <t>9818182643860</t>
+  </si>
+  <si>
+    <t>777429436706722</t>
+  </si>
+  <si>
+    <t>79124416679017</t>
+  </si>
+  <si>
+    <t>YT8888782931933</t>
+  </si>
+  <si>
+    <t>9818167340729</t>
+  </si>
+  <si>
+    <t>YT8888630251251</t>
+  </si>
+  <si>
+    <t>465524366147784</t>
+  </si>
+  <si>
+    <t>465524297566156</t>
+  </si>
+  <si>
+    <t>YT8888799114833</t>
+  </si>
+  <si>
+    <t>JT5507822263796</t>
+  </si>
+  <si>
+    <t>79020567707826</t>
+  </si>
+  <si>
+    <t>465519105482735</t>
+  </si>
+  <si>
+    <t>9818185643870</t>
+  </si>
+  <si>
+    <t>YT8888897177879</t>
+  </si>
+  <si>
+    <t>773432769198473</t>
+  </si>
+  <si>
+    <t>79124599535574</t>
+  </si>
+  <si>
+    <t>JT5507807289884</t>
+  </si>
+  <si>
+    <t>79124630340018</t>
+  </si>
+  <si>
+    <t>YT8888766963183</t>
+  </si>
+  <si>
+    <t>JT5507722000398</t>
+  </si>
+  <si>
+    <t>JT5507671659050</t>
+  </si>
+  <si>
+    <t>JT5504976138805</t>
+  </si>
+  <si>
+    <t>JT5507767387001</t>
+  </si>
+  <si>
+    <t>777429098540797</t>
+  </si>
+  <si>
+    <t>25.07.26</t>
   </si>
 </sst>
 </file>
@@ -2012,7 +2684,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2037,6 +2709,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -2559,7 +3237,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D923"/>
+  <dimension ref="A1:D1073"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="27.44140625" style="2" customWidth="1"/>
@@ -6010,237 +6688,612 @@
       </c>
     </row>
     <row r="515" spans="1:2" ht="14.4">
-      <c r="A515" s="10"/>
+      <c r="A515" s="10" t="s">
+        <v>716</v>
+      </c>
+      <c r="B515" s="1" t="s">
+        <v>717</v>
+      </c>
     </row>
     <row r="516" spans="1:2" ht="14.4">
-      <c r="A516" s="9"/>
+      <c r="A516" s="9" t="s">
+        <v>715</v>
+      </c>
+      <c r="B516" s="1" t="s">
+        <v>717</v>
+      </c>
     </row>
     <row r="517" spans="1:2" ht="14.4">
-      <c r="A517" s="9"/>
+      <c r="A517" s="9" t="s">
+        <v>714</v>
+      </c>
+      <c r="B517" s="1" t="s">
+        <v>717</v>
+      </c>
     </row>
     <row r="518" spans="1:2" ht="14.4">
-      <c r="A518" s="9"/>
+      <c r="A518" s="10" t="s">
+        <v>713</v>
+      </c>
+      <c r="B518" s="1" t="s">
+        <v>717</v>
+      </c>
     </row>
     <row r="519" spans="1:2" ht="14.4">
-      <c r="A519" s="10"/>
+      <c r="A519" s="9" t="s">
+        <v>712</v>
+      </c>
+      <c r="B519" s="1" t="s">
+        <v>717</v>
+      </c>
     </row>
     <row r="520" spans="1:2" ht="14.4">
-      <c r="A520" s="10"/>
+      <c r="A520" s="10" t="s">
+        <v>711</v>
+      </c>
+      <c r="B520" s="1" t="s">
+        <v>717</v>
+      </c>
     </row>
     <row r="521" spans="1:2" ht="14.4">
-      <c r="A521" s="10"/>
+      <c r="A521" s="10" t="s">
+        <v>710</v>
+      </c>
+      <c r="B521" s="1" t="s">
+        <v>717</v>
+      </c>
     </row>
     <row r="522" spans="1:2" ht="14.4">
-      <c r="A522" s="10"/>
+      <c r="A522" s="10" t="s">
+        <v>709</v>
+      </c>
+      <c r="B522" s="1" t="s">
+        <v>717</v>
+      </c>
     </row>
     <row r="523" spans="1:2" ht="14.4">
-      <c r="A523" s="10"/>
+      <c r="A523" s="9" t="s">
+        <v>708</v>
+      </c>
+      <c r="B523" s="1" t="s">
+        <v>717</v>
+      </c>
     </row>
     <row r="524" spans="1:2" ht="14.4">
-      <c r="A524" s="10"/>
+      <c r="A524" s="9" t="s">
+        <v>707</v>
+      </c>
+      <c r="B524" s="1" t="s">
+        <v>717</v>
+      </c>
     </row>
     <row r="525" spans="1:2" ht="14.4">
-      <c r="A525" s="9"/>
+      <c r="A525" s="10" t="s">
+        <v>706</v>
+      </c>
+      <c r="B525" s="1" t="s">
+        <v>717</v>
+      </c>
     </row>
     <row r="526" spans="1:2" ht="14.4">
-      <c r="A526" s="10"/>
+      <c r="A526" s="10" t="s">
+        <v>705</v>
+      </c>
+      <c r="B526" s="1" t="s">
+        <v>717</v>
+      </c>
     </row>
     <row r="527" spans="1:2" ht="14.4">
-      <c r="A527" s="10"/>
+      <c r="A527" s="10" t="s">
+        <v>704</v>
+      </c>
+      <c r="B527" s="1" t="s">
+        <v>717</v>
+      </c>
     </row>
     <row r="528" spans="1:2" ht="14.4">
-      <c r="A528" s="10"/>
-    </row>
-    <row r="529" spans="1:1" ht="14.4">
-      <c r="A529" s="10"/>
-    </row>
-    <row r="530" spans="1:1" ht="14.4">
-      <c r="A530" s="10"/>
-    </row>
-    <row r="531" spans="1:1" ht="14.4">
-      <c r="A531" s="9"/>
-    </row>
-    <row r="532" spans="1:1" ht="14.4">
-      <c r="A532" s="10"/>
-    </row>
-    <row r="533" spans="1:1" ht="14.4">
-      <c r="A533" s="9"/>
-    </row>
-    <row r="534" spans="1:1" ht="14.4">
-      <c r="A534" s="9"/>
-    </row>
-    <row r="535" spans="1:1" ht="14.4">
-      <c r="A535" s="10"/>
-    </row>
-    <row r="536" spans="1:1" ht="14.4">
-      <c r="A536" s="10"/>
-    </row>
-    <row r="537" spans="1:1" ht="14.4">
-      <c r="A537" s="9"/>
-    </row>
-    <row r="538" spans="1:1" ht="14.4">
-      <c r="A538" s="9"/>
-    </row>
-    <row r="539" spans="1:1" ht="14.4">
-      <c r="A539" s="10"/>
-    </row>
-    <row r="540" spans="1:1" ht="14.4">
-      <c r="A540" s="9"/>
-    </row>
-    <row r="541" spans="1:1" ht="14.4">
-      <c r="A541" s="9"/>
-    </row>
-    <row r="542" spans="1:1" ht="14.4">
-      <c r="A542" s="9"/>
-    </row>
-    <row r="543" spans="1:1" ht="14.4">
-      <c r="A543" s="9"/>
-    </row>
-    <row r="544" spans="1:1" ht="14.4">
-      <c r="A544" s="10"/>
-    </row>
-    <row r="545" spans="1:1" ht="14.4">
-      <c r="A545" s="9"/>
-    </row>
-    <row r="546" spans="1:1" ht="14.4">
-      <c r="A546" s="10"/>
-    </row>
-    <row r="547" spans="1:1" ht="14.4">
-      <c r="A547" s="10"/>
-    </row>
-    <row r="548" spans="1:1" ht="14.4">
-      <c r="A548" s="10"/>
-    </row>
-    <row r="549" spans="1:1" ht="14.4">
-      <c r="A549" s="10"/>
-    </row>
-    <row r="550" spans="1:1" ht="14.4">
-      <c r="A550" s="10"/>
-    </row>
-    <row r="551" spans="1:1" ht="14.4">
-      <c r="A551" s="10"/>
-    </row>
-    <row r="552" spans="1:1" ht="14.4">
-      <c r="A552" s="10"/>
-    </row>
-    <row r="553" spans="1:1" ht="14.4">
-      <c r="A553" s="10"/>
-    </row>
-    <row r="554" spans="1:1" ht="14.4">
-      <c r="A554" s="10"/>
-    </row>
-    <row r="555" spans="1:1" ht="14.4">
-      <c r="A555" s="10"/>
-    </row>
-    <row r="556" spans="1:1" ht="14.4">
-      <c r="A556" s="10"/>
-    </row>
-    <row r="557" spans="1:1" ht="14.4">
-      <c r="A557" s="10"/>
-    </row>
-    <row r="558" spans="1:1" ht="14.4">
-      <c r="A558" s="10"/>
-    </row>
-    <row r="559" spans="1:1" ht="14.4">
-      <c r="A559" s="10"/>
-    </row>
-    <row r="560" spans="1:1" ht="14.4">
-      <c r="A560" s="10"/>
-    </row>
-    <row r="561" spans="1:1" ht="14.4">
-      <c r="A561" s="10"/>
-    </row>
-    <row r="562" spans="1:1" ht="14.4">
-      <c r="A562" s="10"/>
-    </row>
-    <row r="563" spans="1:1" ht="14.4">
-      <c r="A563" s="9"/>
-    </row>
-    <row r="564" spans="1:1" ht="14.4">
-      <c r="A564" s="9"/>
-    </row>
-    <row r="565" spans="1:1" ht="14.4">
-      <c r="A565" s="10"/>
-    </row>
-    <row r="566" spans="1:1" ht="14.4">
-      <c r="A566" s="10"/>
-    </row>
-    <row r="567" spans="1:1" ht="14.4">
-      <c r="A567" s="9"/>
-    </row>
-    <row r="568" spans="1:1" ht="14.4">
-      <c r="A568" s="10"/>
-    </row>
-    <row r="569" spans="1:1" ht="14.4">
-      <c r="A569" s="9"/>
-    </row>
-    <row r="570" spans="1:1" ht="14.4">
-      <c r="A570" s="9"/>
-    </row>
-    <row r="571" spans="1:1" ht="14.4">
-      <c r="A571" s="10"/>
-    </row>
-    <row r="572" spans="1:1" ht="14.4">
-      <c r="A572" s="9"/>
-    </row>
-    <row r="573" spans="1:1" ht="14.4">
-      <c r="A573" s="10"/>
-    </row>
-    <row r="574" spans="1:1" ht="14.4">
-      <c r="A574" s="9"/>
-    </row>
-    <row r="575" spans="1:1" ht="14.4">
-      <c r="A575" s="9"/>
-    </row>
-    <row r="576" spans="1:1" ht="14.4">
-      <c r="A576" s="9"/>
-    </row>
-    <row r="577" spans="1:1" ht="14.4">
-      <c r="A577" s="9"/>
-    </row>
-    <row r="578" spans="1:1" ht="14.4">
-      <c r="A578" s="10"/>
-    </row>
-    <row r="579" spans="1:1" ht="14.4">
-      <c r="A579" s="9"/>
-    </row>
-    <row r="580" spans="1:1" ht="14.4">
-      <c r="A580" s="10"/>
-    </row>
-    <row r="581" spans="1:1" ht="14.4">
-      <c r="A581" s="10"/>
-    </row>
-    <row r="582" spans="1:1" ht="14.4">
-      <c r="A582" s="10"/>
-    </row>
-    <row r="583" spans="1:1" ht="14.4">
-      <c r="A583" s="10"/>
-    </row>
-    <row r="584" spans="1:1" ht="14.4">
-      <c r="A584" s="10"/>
-    </row>
-    <row r="585" spans="1:1" ht="14.4">
-      <c r="A585" s="10"/>
-    </row>
-    <row r="586" spans="1:1" ht="14.4">
-      <c r="A586" s="10"/>
-    </row>
-    <row r="587" spans="1:1" ht="14.4">
-      <c r="A587" s="10"/>
-    </row>
-    <row r="588" spans="1:1" ht="14.4">
-      <c r="A588" s="10"/>
-    </row>
-    <row r="589" spans="1:1" ht="14.4">
-      <c r="A589" s="9"/>
-    </row>
-    <row r="590" spans="1:1" ht="14.4">
+      <c r="A528" s="10" t="s">
+        <v>703</v>
+      </c>
+      <c r="B528" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2" ht="14.4">
+      <c r="A529" s="10" t="s">
+        <v>702</v>
+      </c>
+      <c r="B529" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2" ht="14.4">
+      <c r="A530" s="9" t="s">
+        <v>701</v>
+      </c>
+      <c r="B530" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2" ht="14.4">
+      <c r="A531" s="10" t="s">
+        <v>700</v>
+      </c>
+      <c r="B531" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2" ht="14.4">
+      <c r="A532" s="10" t="s">
+        <v>699</v>
+      </c>
+      <c r="B532" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2" ht="14.4">
+      <c r="A533" s="10" t="s">
+        <v>698</v>
+      </c>
+      <c r="B533" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2" ht="14.4">
+      <c r="A534" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="B534" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2" ht="14.4">
+      <c r="A535" s="9" t="s">
+        <v>696</v>
+      </c>
+      <c r="B535" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2" ht="14.4">
+      <c r="A536" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="B536" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2" ht="14.4">
+      <c r="A537" s="10" t="s">
+        <v>694</v>
+      </c>
+      <c r="B537" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2" ht="14.4">
+      <c r="A538" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="B538" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2" ht="14.4">
+      <c r="A539" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="B539" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2" ht="14.4">
+      <c r="A540" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="B540" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2" ht="14.4">
+      <c r="A541" s="9" t="s">
+        <v>690</v>
+      </c>
+      <c r="B541" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2" ht="14.4">
+      <c r="A542" s="10" t="s">
+        <v>689</v>
+      </c>
+      <c r="B542" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2" ht="14.4">
+      <c r="A543" s="10" t="s">
+        <v>688</v>
+      </c>
+      <c r="B543" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2" ht="14.4">
+      <c r="A544" s="9" t="s">
+        <v>687</v>
+      </c>
+      <c r="B544" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2" ht="14.4">
+      <c r="A545" s="10" t="s">
+        <v>686</v>
+      </c>
+      <c r="B545" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2" ht="14.4">
+      <c r="A546" s="10" t="s">
+        <v>685</v>
+      </c>
+      <c r="B546" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2" ht="14.4">
+      <c r="A547" s="9" t="s">
+        <v>660</v>
+      </c>
+      <c r="B547" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2" ht="14.4">
+      <c r="A548" s="9" t="s">
+        <v>684</v>
+      </c>
+      <c r="B548" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2" ht="14.4">
+      <c r="A549" s="10" t="s">
+        <v>683</v>
+      </c>
+      <c r="B549" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2" ht="14.4">
+      <c r="A550" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="B550" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2" ht="14.4">
+      <c r="A551" s="10" t="s">
+        <v>681</v>
+      </c>
+      <c r="B551" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2" ht="14.4">
+      <c r="A552" s="9" t="s">
+        <v>680</v>
+      </c>
+      <c r="B552" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2" ht="14.4">
+      <c r="A553" s="9" t="s">
+        <v>679</v>
+      </c>
+      <c r="B553" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2" ht="14.4">
+      <c r="A554" s="10" t="s">
+        <v>678</v>
+      </c>
+      <c r="B554" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2" ht="14.4">
+      <c r="A555" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="B555" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2" ht="14.4">
+      <c r="A556" s="10" t="s">
+        <v>676</v>
+      </c>
+      <c r="B556" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2" ht="14.4">
+      <c r="A557" s="10" t="s">
+        <v>675</v>
+      </c>
+      <c r="B557" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2" ht="14.4">
+      <c r="A558" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="B558" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2" ht="14.4">
+      <c r="A559" s="9" t="s">
+        <v>673</v>
+      </c>
+      <c r="B559" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2" ht="14.4">
+      <c r="A560" s="9" t="s">
+        <v>672</v>
+      </c>
+      <c r="B560" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2" ht="14.4">
+      <c r="A561" s="10" t="s">
+        <v>671</v>
+      </c>
+      <c r="B561" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2" ht="14.4">
+      <c r="A562" s="9" t="s">
+        <v>670</v>
+      </c>
+      <c r="B562" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2" ht="14.4">
+      <c r="A563" s="9" t="s">
+        <v>669</v>
+      </c>
+      <c r="B563" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2" ht="14.4">
+      <c r="A564" s="9" t="s">
+        <v>668</v>
+      </c>
+      <c r="B564" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2" ht="14.4">
+      <c r="A565" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="B565" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2" ht="14.4">
+      <c r="A566" s="10" t="s">
+        <v>666</v>
+      </c>
+      <c r="B566" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2" ht="14.4">
+      <c r="A567" s="10" t="s">
+        <v>665</v>
+      </c>
+      <c r="B567" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2" ht="14.4">
+      <c r="A568" s="10" t="s">
+        <v>664</v>
+      </c>
+      <c r="B568" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2" ht="14.4">
+      <c r="A569" s="10" t="s">
+        <v>663</v>
+      </c>
+      <c r="B569" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2" ht="14.4">
+      <c r="A570" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="B570" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2" ht="14.4">
+      <c r="A571" s="10" t="s">
+        <v>661</v>
+      </c>
+      <c r="B571" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2" ht="14.4">
+      <c r="A572" s="9" t="s">
+        <v>660</v>
+      </c>
+      <c r="B572" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2" ht="14.4">
+      <c r="A573" s="10" t="s">
+        <v>659</v>
+      </c>
+      <c r="B573" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2" ht="14.4">
+      <c r="A574" s="10" t="s">
+        <v>658</v>
+      </c>
+      <c r="B574" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2" ht="14.4">
+      <c r="A575" s="10" t="s">
+        <v>657</v>
+      </c>
+      <c r="B575" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2" ht="14.4">
+      <c r="A576" s="9" t="s">
+        <v>656</v>
+      </c>
+      <c r="B576" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2" ht="14.4">
+      <c r="A577" s="10" t="s">
+        <v>655</v>
+      </c>
+      <c r="B577" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="578" spans="1:2" ht="14.4">
+      <c r="A578" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="B578" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="579" spans="1:2" ht="14.4">
+      <c r="A579" s="10" t="s">
+        <v>653</v>
+      </c>
+      <c r="B579" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="580" spans="1:2" ht="14.4">
+      <c r="A580" s="10" t="s">
+        <v>652</v>
+      </c>
+      <c r="B580" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="581" spans="1:2" ht="14.4">
+      <c r="A581" s="10" t="s">
+        <v>651</v>
+      </c>
+      <c r="B581" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="582" spans="1:2" ht="14.4">
+      <c r="A582" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="B582" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="583" spans="1:2" ht="14.4">
+      <c r="A583" s="10" t="s">
+        <v>649</v>
+      </c>
+      <c r="B583" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="584" spans="1:2" ht="14.4">
+      <c r="A584" s="10" t="s">
+        <v>648</v>
+      </c>
+      <c r="B584" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="585" spans="1:2" ht="14.4">
+      <c r="A585" s="10" t="s">
+        <v>647</v>
+      </c>
+      <c r="B585" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="586" spans="1:2" ht="14.4">
+      <c r="A586" s="10" t="s">
+        <v>646</v>
+      </c>
+      <c r="B586" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2" ht="14.4">
+      <c r="A587" s="10" t="s">
+        <v>645</v>
+      </c>
+      <c r="B587" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="588" spans="1:2" ht="14.4">
+      <c r="A588" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="B588" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="589" spans="1:2" ht="14.4">
+      <c r="A589" s="10" t="s">
+        <v>643</v>
+      </c>
+      <c r="B589" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="590" spans="1:2" ht="14.4">
       <c r="A590" s="10"/>
     </row>
-    <row r="591" spans="1:1" ht="14.4">
+    <row r="591" spans="1:2" ht="14.4">
       <c r="A591" s="10"/>
     </row>
-    <row r="592" spans="1:1" ht="14.4">
+    <row r="592" spans="1:2" ht="14.4">
       <c r="A592" s="10"/>
     </row>
     <row r="593" spans="1:2" ht="14.4">
@@ -8868,6 +9921,1193 @@
       </c>
       <c r="B923" s="1" t="s">
         <v>642</v>
+      </c>
+    </row>
+    <row r="925" spans="1:2" ht="14.4">
+      <c r="A925" s="10" t="s">
+        <v>776</v>
+      </c>
+      <c r="B925" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="926" spans="1:2" ht="14.4">
+      <c r="A926" s="9" t="s">
+        <v>775</v>
+      </c>
+      <c r="B926" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="927" spans="1:2" ht="14.4">
+      <c r="A927" s="10" t="s">
+        <v>774</v>
+      </c>
+      <c r="B927" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="928" spans="1:2" ht="14.4">
+      <c r="A928" s="9" t="s">
+        <v>773</v>
+      </c>
+      <c r="B928" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="929" spans="1:2" ht="14.4">
+      <c r="A929" s="9" t="s">
+        <v>772</v>
+      </c>
+      <c r="B929" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="930" spans="1:2" ht="14.4">
+      <c r="A930" s="10" t="s">
+        <v>771</v>
+      </c>
+      <c r="B930" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="931" spans="1:2" ht="14.4">
+      <c r="A931" s="10" t="s">
+        <v>770</v>
+      </c>
+      <c r="B931" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="932" spans="1:2" ht="14.4">
+      <c r="A932" s="9" t="s">
+        <v>769</v>
+      </c>
+      <c r="B932" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="933" spans="1:2" ht="14.4">
+      <c r="A933" s="10" t="s">
+        <v>768</v>
+      </c>
+      <c r="B933" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="934" spans="1:2" ht="14.4">
+      <c r="A934" s="10" t="s">
+        <v>767</v>
+      </c>
+      <c r="B934" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="935" spans="1:2" ht="14.4">
+      <c r="A935" s="9" t="s">
+        <v>766</v>
+      </c>
+      <c r="B935" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="936" spans="1:2" ht="14.4">
+      <c r="A936" s="10" t="s">
+        <v>765</v>
+      </c>
+      <c r="B936" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="937" spans="1:2" ht="14.4">
+      <c r="A937" s="10" t="s">
+        <v>764</v>
+      </c>
+      <c r="B937" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="938" spans="1:2" ht="14.4">
+      <c r="A938" s="10" t="s">
+        <v>763</v>
+      </c>
+      <c r="B938" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="939" spans="1:2" ht="14.4">
+      <c r="A939" s="10" t="s">
+        <v>762</v>
+      </c>
+      <c r="B939" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="940" spans="1:2" ht="14.4">
+      <c r="A940" s="10" t="s">
+        <v>761</v>
+      </c>
+      <c r="B940" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="941" spans="1:2" ht="14.4">
+      <c r="A941" s="9" t="s">
+        <v>760</v>
+      </c>
+      <c r="B941" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="942" spans="1:2" ht="14.4">
+      <c r="A942" s="9" t="s">
+        <v>759</v>
+      </c>
+      <c r="B942" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="943" spans="1:2" ht="14.4">
+      <c r="A943" s="10" t="s">
+        <v>758</v>
+      </c>
+      <c r="B943" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="944" spans="1:2" ht="14.4">
+      <c r="A944" s="10" t="s">
+        <v>757</v>
+      </c>
+      <c r="B944" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="945" spans="1:2" ht="14.4">
+      <c r="A945" s="10" t="s">
+        <v>756</v>
+      </c>
+      <c r="B945" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="946" spans="1:2" ht="14.4">
+      <c r="A946" s="10" t="s">
+        <v>755</v>
+      </c>
+      <c r="B946" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="947" spans="1:2" ht="14.4">
+      <c r="A947" s="9" t="s">
+        <v>754</v>
+      </c>
+      <c r="B947" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="948" spans="1:2" ht="14.4">
+      <c r="A948" s="10" t="s">
+        <v>753</v>
+      </c>
+      <c r="B948" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="949" spans="1:2" ht="14.4">
+      <c r="A949" s="10" t="s">
+        <v>752</v>
+      </c>
+      <c r="B949" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="950" spans="1:2" ht="14.4">
+      <c r="A950" s="10" t="s">
+        <v>751</v>
+      </c>
+      <c r="B950" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="951" spans="1:2" ht="14.4">
+      <c r="A951" s="9" t="s">
+        <v>750</v>
+      </c>
+      <c r="B951" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="952" spans="1:2" ht="14.4">
+      <c r="A952" s="10" t="s">
+        <v>749</v>
+      </c>
+      <c r="B952" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="953" spans="1:2" ht="14.4">
+      <c r="A953" s="10" t="s">
+        <v>748</v>
+      </c>
+      <c r="B953" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="954" spans="1:2" ht="14.4">
+      <c r="A954" s="10" t="s">
+        <v>747</v>
+      </c>
+      <c r="B954" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="955" spans="1:2" ht="14.4">
+      <c r="A955" s="10" t="s">
+        <v>746</v>
+      </c>
+      <c r="B955" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="956" spans="1:2" ht="14.4">
+      <c r="A956" s="10" t="s">
+        <v>745</v>
+      </c>
+      <c r="B956" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="957" spans="1:2" ht="14.4">
+      <c r="A957" s="9" t="s">
+        <v>744</v>
+      </c>
+      <c r="B957" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="958" spans="1:2" ht="14.4">
+      <c r="A958" s="10" t="s">
+        <v>743</v>
+      </c>
+      <c r="B958" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="959" spans="1:2" ht="14.4">
+      <c r="A959" s="10" t="s">
+        <v>742</v>
+      </c>
+      <c r="B959" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="960" spans="1:2" ht="14.4">
+      <c r="A960" s="10" t="s">
+        <v>741</v>
+      </c>
+      <c r="B960" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="961" spans="1:2" ht="14.4">
+      <c r="A961" s="10" t="s">
+        <v>740</v>
+      </c>
+      <c r="B961" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="962" spans="1:2" ht="14.4">
+      <c r="A962" s="10" t="s">
+        <v>739</v>
+      </c>
+      <c r="B962" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="963" spans="1:2" ht="14.4">
+      <c r="A963" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="B963" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="964" spans="1:2" ht="14.4">
+      <c r="A964" s="10" t="s">
+        <v>737</v>
+      </c>
+      <c r="B964" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="965" spans="1:2" ht="14.4">
+      <c r="A965" s="10" t="s">
+        <v>736</v>
+      </c>
+      <c r="B965" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="966" spans="1:2" ht="14.4">
+      <c r="A966" s="10" t="s">
+        <v>735</v>
+      </c>
+      <c r="B966" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="967" spans="1:2" ht="14.4">
+      <c r="A967" s="10" t="s">
+        <v>734</v>
+      </c>
+      <c r="B967" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="968" spans="1:2" ht="14.4">
+      <c r="A968" s="10" t="s">
+        <v>733</v>
+      </c>
+      <c r="B968" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="969" spans="1:2" ht="14.4">
+      <c r="A969" s="10" t="s">
+        <v>732</v>
+      </c>
+      <c r="B969" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="970" spans="1:2" ht="14.4">
+      <c r="A970" s="10" t="s">
+        <v>731</v>
+      </c>
+      <c r="B970" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="971" spans="1:2" ht="14.4">
+      <c r="A971" s="10" t="s">
+        <v>730</v>
+      </c>
+      <c r="B971" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="972" spans="1:2" ht="14.4">
+      <c r="A972" s="10" t="s">
+        <v>729</v>
+      </c>
+      <c r="B972" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="973" spans="1:2" ht="14.4">
+      <c r="A973" s="10" t="s">
+        <v>728</v>
+      </c>
+      <c r="B973" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="974" spans="1:2" ht="14.4">
+      <c r="A974" s="10" t="s">
+        <v>727</v>
+      </c>
+      <c r="B974" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="975" spans="1:2" ht="14.4">
+      <c r="A975" s="9" t="s">
+        <v>726</v>
+      </c>
+      <c r="B975" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="976" spans="1:2" ht="14.4">
+      <c r="A976" s="10" t="s">
+        <v>725</v>
+      </c>
+      <c r="B976" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="977" spans="1:4" ht="14.4">
+      <c r="A977" s="10" t="s">
+        <v>724</v>
+      </c>
+      <c r="B977" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="978" spans="1:4" ht="14.4">
+      <c r="A978" s="10" t="s">
+        <v>723</v>
+      </c>
+      <c r="B978" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="D978" s="1" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="979" spans="1:4" ht="14.4">
+      <c r="A979" s="10" t="s">
+        <v>722</v>
+      </c>
+      <c r="B979" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="980" spans="1:4" ht="14.4">
+      <c r="A980" s="10" t="s">
+        <v>721</v>
+      </c>
+      <c r="B980" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="981" spans="1:4" ht="14.4">
+      <c r="A981" s="10" t="s">
+        <v>720</v>
+      </c>
+      <c r="B981" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="982" spans="1:4" ht="14.4">
+      <c r="A982" s="10" t="s">
+        <v>719</v>
+      </c>
+      <c r="B982" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="983" spans="1:4" ht="14.4">
+      <c r="A983" s="10" t="s">
+        <v>718</v>
+      </c>
+      <c r="B983" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="985" spans="1:4" ht="14.4">
+      <c r="A985" s="11" t="s">
+        <v>779</v>
+      </c>
+      <c r="B985" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="986" spans="1:4" ht="14.4">
+      <c r="A986" s="11" t="s">
+        <v>780</v>
+      </c>
+      <c r="B986" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="987" spans="1:4" ht="14.4">
+      <c r="A987" s="12" t="s">
+        <v>781</v>
+      </c>
+      <c r="B987" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="988" spans="1:4" ht="14.4">
+      <c r="A988" s="11" t="s">
+        <v>782</v>
+      </c>
+      <c r="B988" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="989" spans="1:4" ht="14.4">
+      <c r="A989" s="11" t="s">
+        <v>783</v>
+      </c>
+      <c r="B989" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="990" spans="1:4" ht="14.4">
+      <c r="A990" s="12" t="s">
+        <v>784</v>
+      </c>
+      <c r="B990" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="991" spans="1:4" ht="14.4">
+      <c r="A991" s="12" t="s">
+        <v>785</v>
+      </c>
+      <c r="B991" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="992" spans="1:4" ht="14.4">
+      <c r="A992" s="11" t="s">
+        <v>786</v>
+      </c>
+      <c r="B992" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="993" spans="1:2" ht="14.4">
+      <c r="A993" s="12" t="s">
+        <v>787</v>
+      </c>
+      <c r="B993" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="994" spans="1:2" ht="14.4">
+      <c r="A994" s="12" t="s">
+        <v>788</v>
+      </c>
+      <c r="B994" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="995" spans="1:2" ht="14.4">
+      <c r="A995" s="12" t="s">
+        <v>789</v>
+      </c>
+      <c r="B995" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="996" spans="1:2" ht="14.4">
+      <c r="A996" s="11" t="s">
+        <v>790</v>
+      </c>
+      <c r="B996" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="997" spans="1:2" ht="14.4">
+      <c r="A997" s="12" t="s">
+        <v>791</v>
+      </c>
+      <c r="B997" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="998" spans="1:2" ht="14.4">
+      <c r="A998" s="11" t="s">
+        <v>792</v>
+      </c>
+      <c r="B998" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="999" spans="1:2" ht="14.4">
+      <c r="A999" s="11" t="s">
+        <v>793</v>
+      </c>
+      <c r="B999" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:2" ht="14.4">
+      <c r="A1000" s="11" t="s">
+        <v>794</v>
+      </c>
+      <c r="B1000" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:2" ht="14.4">
+      <c r="A1001" s="12" t="s">
+        <v>795</v>
+      </c>
+      <c r="B1001" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:2" ht="14.4">
+      <c r="A1002" s="11" t="s">
+        <v>796</v>
+      </c>
+      <c r="B1002" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:2" ht="14.4">
+      <c r="A1003" s="12" t="s">
+        <v>797</v>
+      </c>
+      <c r="B1003" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:2" ht="14.4">
+      <c r="A1004" s="11" t="s">
+        <v>798</v>
+      </c>
+      <c r="B1004" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:2" ht="14.4">
+      <c r="A1005" s="12" t="s">
+        <v>799</v>
+      </c>
+      <c r="B1005" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:2" ht="14.4">
+      <c r="A1006" s="12" t="s">
+        <v>800</v>
+      </c>
+      <c r="B1006" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:2" ht="14.4">
+      <c r="A1007" s="12" t="s">
+        <v>801</v>
+      </c>
+      <c r="B1007" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:2" ht="14.4">
+      <c r="A1008" s="11" t="s">
+        <v>802</v>
+      </c>
+      <c r="B1008" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:2" ht="14.4">
+      <c r="A1009" s="12" t="s">
+        <v>803</v>
+      </c>
+      <c r="B1009" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:2" ht="14.4">
+      <c r="A1010" s="11" t="s">
+        <v>804</v>
+      </c>
+      <c r="B1010" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:2" ht="14.4">
+      <c r="A1011" s="12" t="s">
+        <v>805</v>
+      </c>
+      <c r="B1011" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:2" ht="14.4">
+      <c r="A1012" s="11" t="s">
+        <v>806</v>
+      </c>
+      <c r="B1012" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:2" ht="14.4">
+      <c r="A1013" s="12" t="s">
+        <v>807</v>
+      </c>
+      <c r="B1013" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:2" ht="14.4">
+      <c r="A1014" s="12" t="s">
+        <v>808</v>
+      </c>
+      <c r="B1014" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:2" ht="14.4">
+      <c r="A1015" s="12" t="s">
+        <v>809</v>
+      </c>
+      <c r="B1015" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:2" ht="14.4">
+      <c r="A1016" s="11" t="s">
+        <v>810</v>
+      </c>
+      <c r="B1016" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:2" ht="14.4">
+      <c r="A1017" s="12" t="s">
+        <v>811</v>
+      </c>
+      <c r="B1017" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:2" ht="14.4">
+      <c r="A1018" s="12" t="s">
+        <v>812</v>
+      </c>
+      <c r="B1018" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:2" ht="14.4">
+      <c r="A1019" s="11" t="s">
+        <v>813</v>
+      </c>
+      <c r="B1019" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:2" ht="14.4">
+      <c r="A1020" s="11" t="s">
+        <v>814</v>
+      </c>
+      <c r="B1020" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:2" ht="14.4">
+      <c r="A1021" s="12" t="s">
+        <v>815</v>
+      </c>
+      <c r="B1021" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:2" ht="14.4">
+      <c r="A1022" s="12" t="s">
+        <v>816</v>
+      </c>
+      <c r="B1022" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:2" ht="14.4">
+      <c r="A1023" s="11" t="s">
+        <v>817</v>
+      </c>
+      <c r="B1023" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:2" ht="14.4">
+      <c r="A1024" s="11" t="s">
+        <v>818</v>
+      </c>
+      <c r="B1024" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:2" ht="14.4">
+      <c r="A1025" s="12" t="s">
+        <v>819</v>
+      </c>
+      <c r="B1025" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:2" ht="14.4">
+      <c r="A1026" s="12" t="s">
+        <v>820</v>
+      </c>
+      <c r="B1026" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:2" ht="14.4">
+      <c r="A1027" s="11" t="s">
+        <v>821</v>
+      </c>
+      <c r="B1027" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:2" ht="14.4">
+      <c r="A1028" s="12" t="s">
+        <v>822</v>
+      </c>
+      <c r="B1028" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:2" ht="14.4">
+      <c r="A1029" s="12" t="s">
+        <v>823</v>
+      </c>
+      <c r="B1029" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:2" ht="14.4">
+      <c r="A1030" s="12" t="s">
+        <v>824</v>
+      </c>
+      <c r="B1030" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:2" ht="14.4">
+      <c r="A1031" s="12" t="s">
+        <v>825</v>
+      </c>
+      <c r="B1031" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:2" ht="14.4">
+      <c r="A1032" s="12" t="s">
+        <v>826</v>
+      </c>
+      <c r="B1032" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:2" ht="14.4">
+      <c r="A1033" s="12" t="s">
+        <v>827</v>
+      </c>
+      <c r="B1033" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:2" ht="14.4">
+      <c r="A1034" s="12" t="s">
+        <v>828</v>
+      </c>
+      <c r="B1034" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:2" ht="14.4">
+      <c r="A1035" s="12" t="s">
+        <v>829</v>
+      </c>
+      <c r="B1035" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:2" ht="14.4">
+      <c r="A1036" s="12" t="s">
+        <v>830</v>
+      </c>
+      <c r="B1036" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:2" ht="14.4">
+      <c r="A1037" s="12" t="s">
+        <v>831</v>
+      </c>
+      <c r="B1037" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:2" ht="14.4">
+      <c r="A1038" s="11" t="s">
+        <v>832</v>
+      </c>
+      <c r="B1038" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:2" ht="14.4">
+      <c r="A1039" s="11" t="s">
+        <v>833</v>
+      </c>
+      <c r="B1039" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:2" ht="14.4">
+      <c r="A1040" s="12" t="s">
+        <v>834</v>
+      </c>
+      <c r="B1040" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:2" ht="14.4">
+      <c r="A1041" s="12" t="s">
+        <v>835</v>
+      </c>
+      <c r="B1041" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:2" ht="14.4">
+      <c r="A1042" s="12" t="s">
+        <v>836</v>
+      </c>
+      <c r="B1042" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:2" ht="14.4">
+      <c r="A1043" s="12" t="s">
+        <v>837</v>
+      </c>
+      <c r="B1043" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:2" ht="14.4">
+      <c r="A1044" s="12" t="s">
+        <v>837</v>
+      </c>
+      <c r="B1044" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:2" ht="14.4">
+      <c r="A1045" s="12" t="s">
+        <v>838</v>
+      </c>
+      <c r="B1045" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:2" ht="14.4">
+      <c r="A1046" s="11" t="s">
+        <v>839</v>
+      </c>
+      <c r="B1046" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:2" ht="14.4">
+      <c r="A1047" s="12" t="s">
+        <v>840</v>
+      </c>
+      <c r="B1047" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:2" ht="14.4">
+      <c r="A1048" s="12" t="s">
+        <v>841</v>
+      </c>
+      <c r="B1048" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:2" ht="14.4">
+      <c r="A1049" s="12" t="s">
+        <v>842</v>
+      </c>
+      <c r="B1049" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:2" ht="14.4">
+      <c r="A1050" s="12" t="s">
+        <v>843</v>
+      </c>
+      <c r="B1050" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:2" ht="14.4">
+      <c r="A1051" s="12" t="s">
+        <v>844</v>
+      </c>
+      <c r="B1051" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:2" ht="14.4">
+      <c r="A1052" s="11" t="s">
+        <v>845</v>
+      </c>
+      <c r="B1052" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:2" ht="14.4">
+      <c r="A1053" s="12" t="s">
+        <v>846</v>
+      </c>
+      <c r="B1053" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:2" ht="14.4">
+      <c r="A1054" s="11" t="s">
+        <v>847</v>
+      </c>
+      <c r="B1054" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:2" ht="14.4">
+      <c r="A1055" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="B1055" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:2" ht="14.4">
+      <c r="A1056" s="12" t="s">
+        <v>849</v>
+      </c>
+      <c r="B1056" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:2" ht="14.4">
+      <c r="A1057" s="11" t="s">
+        <v>850</v>
+      </c>
+      <c r="B1057" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:2" ht="14.4">
+      <c r="A1058" s="11" t="s">
+        <v>851</v>
+      </c>
+      <c r="B1058" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:2" ht="14.4">
+      <c r="A1059" s="12" t="s">
+        <v>852</v>
+      </c>
+      <c r="B1059" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:2" ht="14.4">
+      <c r="A1060" s="12" t="s">
+        <v>853</v>
+      </c>
+      <c r="B1060" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:2" ht="14.4">
+      <c r="A1061" s="12" t="s">
+        <v>854</v>
+      </c>
+      <c r="B1061" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:2" ht="14.4">
+      <c r="A1062" s="11" t="s">
+        <v>855</v>
+      </c>
+      <c r="B1062" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:2" ht="14.4">
+      <c r="A1063" s="12" t="s">
+        <v>856</v>
+      </c>
+      <c r="B1063" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:2" ht="14.4">
+      <c r="A1064" s="12" t="s">
+        <v>857</v>
+      </c>
+      <c r="B1064" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:2" ht="14.4">
+      <c r="A1065" s="11" t="s">
+        <v>858</v>
+      </c>
+      <c r="B1065" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:2" ht="14.4">
+      <c r="A1066" s="12" t="s">
+        <v>859</v>
+      </c>
+      <c r="B1066" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:2" ht="14.4">
+      <c r="A1067" s="11" t="s">
+        <v>860</v>
+      </c>
+      <c r="B1067" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:2" ht="14.4">
+      <c r="A1068" s="11" t="s">
+        <v>861</v>
+      </c>
+      <c r="B1068" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:2" ht="14.4">
+      <c r="A1069" s="11" t="s">
+        <v>862</v>
+      </c>
+      <c r="B1069" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:2" ht="14.4">
+      <c r="A1070" s="11" t="s">
+        <v>863</v>
+      </c>
+      <c r="B1070" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:2" ht="14.4">
+      <c r="A1071" s="11" t="s">
+        <v>864</v>
+      </c>
+      <c r="B1071" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:2" ht="14.4">
+      <c r="A1072" s="12" t="s">
+        <v>865</v>
+      </c>
+      <c r="B1072" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:2" ht="14.4">
+      <c r="A1073" s="12" t="s">
+        <v>825</v>
+      </c>
+      <c r="B1073" s="1" t="s">
+        <v>866</v>
       </c>
     </row>
   </sheetData>

--- a/on_the_way.xlsx
+++ b/on_the_way.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="888">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1933" uniqueCount="889">
   <si>
     <t>Track</t>
   </si>
@@ -2680,13 +2680,16 @@
   </si>
   <si>
     <t>30.07.26</t>
+  </si>
+  <si>
+    <t>28.07.26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2705,7 +2708,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2747,7 +2750,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2796,6 +2799,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3313,7 +3319,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D1214"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.44140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="8.88671875" style="1"/>
@@ -3322,7 +3328,7 @@
     <col min="5" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3330,7 +3336,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="14.4">
+    <row r="2" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>255</v>
       </c>
@@ -3338,7 +3344,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="14.4">
+    <row r="3" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>256</v>
       </c>
@@ -3346,7 +3352,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="14.4">
+    <row r="4" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>257</v>
       </c>
@@ -3354,7 +3360,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="14.4">
+    <row r="5" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>258</v>
       </c>
@@ -3362,7 +3368,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="14.4">
+    <row r="6" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>259</v>
       </c>
@@ -3370,7 +3376,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="14.4">
+    <row r="7" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>260</v>
       </c>
@@ -3378,7 +3384,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="14.4">
+    <row r="8" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
         <v>261</v>
       </c>
@@ -3386,7 +3392,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="14.4">
+    <row r="9" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>262</v>
       </c>
@@ -3394,7 +3400,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="14.4">
+    <row r="10" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
         <v>263</v>
       </c>
@@ -3402,7 +3408,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="14.4">
+    <row r="11" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
         <v>264</v>
       </c>
@@ -3410,7 +3416,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="14.4">
+    <row r="12" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>265</v>
       </c>
@@ -3418,7 +3424,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="14.4">
+    <row r="13" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
         <v>266</v>
       </c>
@@ -3426,7 +3432,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="14.4">
+    <row r="14" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
         <v>267</v>
       </c>
@@ -3434,7 +3440,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="14.4">
+    <row r="15" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
         <v>268</v>
       </c>
@@ -3442,7 +3448,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="14.4">
+    <row r="16" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
         <v>269</v>
       </c>
@@ -3450,7 +3456,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="14.4">
+    <row r="17" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>270</v>
       </c>
@@ -3458,7 +3464,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="14.4">
+    <row r="18" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>271</v>
       </c>
@@ -3466,7 +3472,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="14.4">
+    <row r="19" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>272</v>
       </c>
@@ -3474,7 +3480,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="14.4">
+    <row r="20" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
         <v>273</v>
       </c>
@@ -3482,7 +3488,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="14.4">
+    <row r="21" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
         <v>274</v>
       </c>
@@ -3490,7 +3496,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="14.4">
+    <row r="22" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
         <v>275</v>
       </c>
@@ -3498,7 +3504,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="14.4">
+    <row r="23" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>276</v>
       </c>
@@ -3506,7 +3512,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="14.4">
+    <row r="24" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="10" t="s">
         <v>277</v>
       </c>
@@ -3514,7 +3520,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="14.4">
+    <row r="25" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
         <v>278</v>
       </c>
@@ -3522,7 +3528,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="14.4">
+    <row r="26" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
         <v>279</v>
       </c>
@@ -3530,7 +3536,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="14.4">
+    <row r="27" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
         <v>280</v>
       </c>
@@ -3538,7 +3544,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="14.4">
+    <row r="28" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>281</v>
       </c>
@@ -3546,7 +3552,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="14.4">
+    <row r="29" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
         <v>282</v>
       </c>
@@ -3554,7 +3560,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="14.4">
+    <row r="30" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
         <v>283</v>
       </c>
@@ -3562,7 +3568,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="14.4">
+    <row r="31" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
         <v>284</v>
       </c>
@@ -3570,7 +3576,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="14.4">
+    <row r="32" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>285</v>
       </c>
@@ -3578,7 +3584,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="14.4">
+    <row r="33" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
         <v>286</v>
       </c>
@@ -3586,7 +3592,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="14.4">
+    <row r="34" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
         <v>287</v>
       </c>
@@ -3594,7 +3600,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="14.4">
+    <row r="35" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
         <v>288</v>
       </c>
@@ -3602,7 +3608,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="14.4">
+    <row r="36" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>289</v>
       </c>
@@ -3610,7 +3616,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="14.4">
+    <row r="37" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>290</v>
       </c>
@@ -3618,7 +3624,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="14.4">
+    <row r="38" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>291</v>
       </c>
@@ -3626,7 +3632,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="14.4">
+    <row r="39" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
         <v>292</v>
       </c>
@@ -3634,7 +3640,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="14.4">
+    <row r="40" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="10" t="s">
         <v>293</v>
       </c>
@@ -3642,7 +3648,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="14.4">
+    <row r="41" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="10" t="s">
         <v>294</v>
       </c>
@@ -3650,7 +3656,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="14.4">
+    <row r="42" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="10" t="s">
         <v>295</v>
       </c>
@@ -3658,7 +3664,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="14.4">
+    <row r="43" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
         <v>296</v>
       </c>
@@ -3666,7 +3672,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="14.4">
+    <row r="44" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>297</v>
       </c>
@@ -3674,7 +3680,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="14.4">
+    <row r="45" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
         <v>298</v>
       </c>
@@ -3682,7 +3688,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="14.4">
+    <row r="46" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="10" t="s">
         <v>299</v>
       </c>
@@ -3690,7 +3696,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="14.4">
+    <row r="47" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>300</v>
       </c>
@@ -3698,7 +3704,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="14.4">
+    <row r="48" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="10" t="s">
         <v>301</v>
       </c>
@@ -3706,7 +3712,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="14.4">
+    <row r="49" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="9" t="s">
         <v>302</v>
       </c>
@@ -3714,7 +3720,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="14.4">
+    <row r="50" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="10" t="s">
         <v>303</v>
       </c>
@@ -3722,7 +3728,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="14.4">
+    <row r="51" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>304</v>
       </c>
@@ -3730,7 +3736,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="14.4">
+    <row r="52" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="10" t="s">
         <v>305</v>
       </c>
@@ -3738,7 +3744,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="14.4">
+    <row r="53" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>306</v>
       </c>
@@ -3746,7 +3752,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="14.4">
+    <row r="54" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="10" t="s">
         <v>307</v>
       </c>
@@ -3754,7 +3760,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="14.4">
+    <row r="55" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>308</v>
       </c>
@@ -3762,7 +3768,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="14.4">
+    <row r="56" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
         <v>309</v>
       </c>
@@ -3770,7 +3776,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="14.4">
+    <row r="57" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
         <v>310</v>
       </c>
@@ -3778,7 +3784,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="14.4">
+    <row r="58" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="10" t="s">
         <v>311</v>
       </c>
@@ -3786,7 +3792,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="14.4">
+    <row r="59" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
         <v>312</v>
       </c>
@@ -3794,7 +3800,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="14.4">
+    <row r="60" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="10" t="s">
         <v>313</v>
       </c>
@@ -3802,7 +3808,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="14.4">
+    <row r="61" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="10" t="s">
         <v>314</v>
       </c>
@@ -3810,7 +3816,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="14.4">
+    <row r="62" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="10" t="s">
         <v>315</v>
       </c>
@@ -3818,7 +3824,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="14.4">
+    <row r="63" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="10" t="s">
         <v>316</v>
       </c>
@@ -3826,7 +3832,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="14.4">
+    <row r="64" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
         <v>317</v>
       </c>
@@ -3834,7 +3840,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="14.4">
+    <row r="65" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="9" t="s">
         <v>318</v>
       </c>
@@ -3842,7 +3848,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="14.4">
+    <row r="66" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="9" t="s">
         <v>319</v>
       </c>
@@ -3850,7 +3856,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="14.4">
+    <row r="67" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="10" t="s">
         <v>320</v>
       </c>
@@ -3858,7 +3864,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="14.4">
+    <row r="68" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="9" t="s">
         <v>321</v>
       </c>
@@ -3866,7 +3872,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="14.4">
+    <row r="69" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="10" t="s">
         <v>322</v>
       </c>
@@ -3874,7 +3880,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="14.4">
+    <row r="70" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="10" t="s">
         <v>323</v>
       </c>
@@ -3882,7 +3888,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="14.4">
+    <row r="71" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="10" t="s">
         <v>324</v>
       </c>
@@ -3890,7 +3896,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="14.4">
+    <row r="72" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="9" t="s">
         <v>325</v>
       </c>
@@ -3898,7 +3904,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="14.4">
+    <row r="73" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73" s="9" t="s">
         <v>326</v>
       </c>
@@ -3906,7 +3912,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="14.4">
+    <row r="74" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="9" t="s">
         <v>327</v>
       </c>
@@ -3914,7 +3920,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="14.4">
+    <row r="75" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" s="10" t="s">
         <v>328</v>
       </c>
@@ -3922,7 +3928,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="14.4">
+    <row r="76" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76" s="9" t="s">
         <v>329</v>
       </c>
@@ -3930,7 +3936,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="14.4">
+    <row r="77" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="9" t="s">
         <v>330</v>
       </c>
@@ -3938,7 +3944,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="14.4">
+    <row r="78" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="10" t="s">
         <v>331</v>
       </c>
@@ -3946,7 +3952,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="14.4">
+    <row r="79" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" s="10" t="s">
         <v>332</v>
       </c>
@@ -3954,7 +3960,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="14.4">
+    <row r="80" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" s="10" t="s">
         <v>333</v>
       </c>
@@ -3962,7 +3968,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="14.4">
+    <row r="81" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A81" s="9" t="s">
         <v>334</v>
       </c>
@@ -3970,7 +3976,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="14.4">
+    <row r="82" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A82" s="10" t="s">
         <v>335</v>
       </c>
@@ -3978,7 +3984,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="14.4">
+    <row r="83" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A83" s="10" t="s">
         <v>336</v>
       </c>
@@ -3987,7 +3993,7 @@
       </c>
       <c r="D83"/>
     </row>
-    <row r="84" spans="1:4" ht="14.4">
+    <row r="84" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A84" s="10" t="s">
         <v>337</v>
       </c>
@@ -3996,7 +4002,7 @@
       </c>
       <c r="D84"/>
     </row>
-    <row r="85" spans="1:4" ht="14.4">
+    <row r="85" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A85" s="10" t="s">
         <v>338</v>
       </c>
@@ -4005,7 +4011,7 @@
       </c>
       <c r="D85"/>
     </row>
-    <row r="86" spans="1:4" ht="14.4">
+    <row r="86" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" s="9" t="s">
         <v>339</v>
       </c>
@@ -4014,7 +4020,7 @@
       </c>
       <c r="D86"/>
     </row>
-    <row r="87" spans="1:4" ht="14.4">
+    <row r="87" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A87" s="9" t="s">
         <v>340</v>
       </c>
@@ -4023,7 +4029,7 @@
       </c>
       <c r="D87"/>
     </row>
-    <row r="88" spans="1:4" ht="14.4">
+    <row r="88" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A88" s="10" t="s">
         <v>341</v>
       </c>
@@ -4032,7 +4038,7 @@
       </c>
       <c r="D88"/>
     </row>
-    <row r="89" spans="1:4" ht="14.4">
+    <row r="89" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A89" s="9" t="s">
         <v>342</v>
       </c>
@@ -4041,7 +4047,7 @@
       </c>
       <c r="D89"/>
     </row>
-    <row r="90" spans="1:4" ht="14.4">
+    <row r="90" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A90" s="10" t="s">
         <v>343</v>
       </c>
@@ -4050,7 +4056,7 @@
       </c>
       <c r="D90"/>
     </row>
-    <row r="91" spans="1:4" ht="14.4">
+    <row r="91" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A91" s="10" t="s">
         <v>344</v>
       </c>
@@ -4059,7 +4065,7 @@
       </c>
       <c r="D91"/>
     </row>
-    <row r="92" spans="1:4" ht="14.4">
+    <row r="92" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A92" s="10" t="s">
         <v>345</v>
       </c>
@@ -4068,7 +4074,7 @@
       </c>
       <c r="D92"/>
     </row>
-    <row r="93" spans="1:4" ht="14.4">
+    <row r="93" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A93" s="10" t="s">
         <v>346</v>
       </c>
@@ -4077,7 +4083,7 @@
       </c>
       <c r="D93"/>
     </row>
-    <row r="94" spans="1:4" ht="14.4">
+    <row r="94" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A94" s="10" t="s">
         <v>347</v>
       </c>
@@ -4086,7 +4092,7 @@
       </c>
       <c r="D94"/>
     </row>
-    <row r="95" spans="1:4" ht="14.4">
+    <row r="95" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A95" s="10" t="s">
         <v>348</v>
       </c>
@@ -4095,7 +4101,7 @@
       </c>
       <c r="D95"/>
     </row>
-    <row r="96" spans="1:4" ht="14.4">
+    <row r="96" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A96" s="10" t="s">
         <v>349</v>
       </c>
@@ -4104,7 +4110,7 @@
       </c>
       <c r="D96"/>
     </row>
-    <row r="97" spans="1:4" ht="14.4">
+    <row r="97" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A97" s="9" t="s">
         <v>350</v>
       </c>
@@ -4113,7 +4119,7 @@
       </c>
       <c r="D97"/>
     </row>
-    <row r="98" spans="1:4" ht="14.4">
+    <row r="98" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A98" s="10" t="s">
         <v>351</v>
       </c>
@@ -4122,7 +4128,7 @@
       </c>
       <c r="D98"/>
     </row>
-    <row r="99" spans="1:4" ht="14.4">
+    <row r="99" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A99" s="10" t="s">
         <v>352</v>
       </c>
@@ -4131,7 +4137,7 @@
       </c>
       <c r="D99"/>
     </row>
-    <row r="100" spans="1:4" ht="14.4">
+    <row r="100" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A100" s="10" t="s">
         <v>353</v>
       </c>
@@ -4140,7 +4146,7 @@
       </c>
       <c r="D100"/>
     </row>
-    <row r="101" spans="1:4" ht="14.4">
+    <row r="101" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A101" s="10" t="s">
         <v>354</v>
       </c>
@@ -4149,7 +4155,7 @@
       </c>
       <c r="D101"/>
     </row>
-    <row r="102" spans="1:4" ht="14.4">
+    <row r="102" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A102" s="10" t="s">
         <v>355</v>
       </c>
@@ -4158,7 +4164,7 @@
       </c>
       <c r="D102"/>
     </row>
-    <row r="103" spans="1:4" ht="14.4">
+    <row r="103" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A103" s="10" t="s">
         <v>356</v>
       </c>
@@ -4167,7 +4173,7 @@
       </c>
       <c r="D103"/>
     </row>
-    <row r="104" spans="1:4" ht="14.4">
+    <row r="104" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A104" s="9" t="s">
         <v>357</v>
       </c>
@@ -4176,7 +4182,7 @@
       </c>
       <c r="D104"/>
     </row>
-    <row r="105" spans="1:4" ht="14.4">
+    <row r="105" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A105" s="10" t="s">
         <v>358</v>
       </c>
@@ -4185,7 +4191,7 @@
       </c>
       <c r="D105"/>
     </row>
-    <row r="106" spans="1:4" ht="14.4">
+    <row r="106" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A106" s="10" t="s">
         <v>359</v>
       </c>
@@ -4194,7 +4200,7 @@
       </c>
       <c r="D106"/>
     </row>
-    <row r="107" spans="1:4" ht="14.4">
+    <row r="107" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A107" s="10" t="s">
         <v>360</v>
       </c>
@@ -4203,7 +4209,7 @@
       </c>
       <c r="D107"/>
     </row>
-    <row r="108" spans="1:4" ht="14.4">
+    <row r="108" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A108" s="10" t="s">
         <v>361</v>
       </c>
@@ -4212,7 +4218,7 @@
       </c>
       <c r="D108"/>
     </row>
-    <row r="109" spans="1:4" ht="14.4">
+    <row r="109" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A109" s="10" t="s">
         <v>362</v>
       </c>
@@ -4221,7 +4227,7 @@
       </c>
       <c r="D109"/>
     </row>
-    <row r="110" spans="1:4" ht="14.4">
+    <row r="110" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A110" s="10" t="s">
         <v>363</v>
       </c>
@@ -4230,7 +4236,7 @@
       </c>
       <c r="D110"/>
     </row>
-    <row r="111" spans="1:4" ht="14.4">
+    <row r="111" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A111" s="9" t="s">
         <v>364</v>
       </c>
@@ -4239,7 +4245,7 @@
       </c>
       <c r="D111"/>
     </row>
-    <row r="112" spans="1:4" ht="14.4">
+    <row r="112" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A112" s="10" t="s">
         <v>365</v>
       </c>
@@ -4248,7 +4254,7 @@
       </c>
       <c r="D112"/>
     </row>
-    <row r="113" spans="1:4" ht="14.4">
+    <row r="113" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A113" s="10" t="s">
         <v>366</v>
       </c>
@@ -4257,7 +4263,7 @@
       </c>
       <c r="D113"/>
     </row>
-    <row r="114" spans="1:4" ht="14.4">
+    <row r="114" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A114" s="10" t="s">
         <v>367</v>
       </c>
@@ -4266,7 +4272,7 @@
       </c>
       <c r="D114"/>
     </row>
-    <row r="115" spans="1:4" ht="14.4">
+    <row r="115" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A115" s="10" t="s">
         <v>368</v>
       </c>
@@ -4275,7 +4281,7 @@
       </c>
       <c r="D115"/>
     </row>
-    <row r="116" spans="1:4" ht="14.4">
+    <row r="116" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A116" s="10" t="s">
         <v>369</v>
       </c>
@@ -4284,7 +4290,7 @@
       </c>
       <c r="D116"/>
     </row>
-    <row r="117" spans="1:4" ht="14.4">
+    <row r="117" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A117" s="10" t="s">
         <v>370</v>
       </c>
@@ -4293,7 +4299,7 @@
       </c>
       <c r="D117"/>
     </row>
-    <row r="118" spans="1:4" ht="14.4">
+    <row r="118" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A118" s="10" t="s">
         <v>371</v>
       </c>
@@ -4302,7 +4308,7 @@
       </c>
       <c r="D118"/>
     </row>
-    <row r="119" spans="1:4" ht="14.4">
+    <row r="119" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A119" s="10" t="s">
         <v>372</v>
       </c>
@@ -4311,7 +4317,7 @@
       </c>
       <c r="D119"/>
     </row>
-    <row r="120" spans="1:4" ht="14.4">
+    <row r="120" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A120" s="10" t="s">
         <v>373</v>
       </c>
@@ -4320,7 +4326,7 @@
       </c>
       <c r="D120"/>
     </row>
-    <row r="121" spans="1:4" ht="14.4">
+    <row r="121" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A121" s="10" t="s">
         <v>374</v>
       </c>
@@ -4329,7 +4335,7 @@
       </c>
       <c r="D121"/>
     </row>
-    <row r="122" spans="1:4" ht="14.4">
+    <row r="122" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A122" s="10" t="s">
         <v>257</v>
       </c>
@@ -4338,423 +4344,806 @@
       </c>
       <c r="D122"/>
     </row>
-    <row r="123" spans="1:4">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B123"/>
       <c r="D123"/>
     </row>
-    <row r="124" spans="1:4">
-      <c r="B124"/>
+    <row r="124" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A124" s="15" t="s">
+        <v>750</v>
+      </c>
+      <c r="B124" s="17" t="s">
+        <v>888</v>
+      </c>
       <c r="D124"/>
     </row>
-    <row r="125" spans="1:4">
-      <c r="B125"/>
+    <row r="125" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A125" s="16" t="s">
+        <v>751</v>
+      </c>
+      <c r="B125" s="17" t="s">
+        <v>888</v>
+      </c>
       <c r="D125"/>
     </row>
-    <row r="126" spans="1:4">
-      <c r="B126"/>
+    <row r="126" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A126" s="16" t="s">
+        <v>752</v>
+      </c>
+      <c r="B126" s="17" t="s">
+        <v>888</v>
+      </c>
       <c r="D126"/>
     </row>
-    <row r="127" spans="1:4">
-      <c r="B127"/>
+    <row r="127" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A127" s="16" t="s">
+        <v>753</v>
+      </c>
+      <c r="B127" s="17" t="s">
+        <v>888</v>
+      </c>
       <c r="D127"/>
     </row>
-    <row r="128" spans="1:4">
-      <c r="B128"/>
+    <row r="128" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A128" s="16" t="s">
+        <v>754</v>
+      </c>
+      <c r="B128" s="17" t="s">
+        <v>888</v>
+      </c>
       <c r="D128"/>
     </row>
-    <row r="130" spans="1:1" ht="14.4">
-      <c r="A130" s="7"/>
-    </row>
-    <row r="131" spans="1:1" ht="14.4">
-      <c r="A131" s="8"/>
-    </row>
-    <row r="132" spans="1:1" ht="14.4">
-      <c r="A132" s="7"/>
-    </row>
-    <row r="133" spans="1:1" ht="14.4">
-      <c r="A133" s="7"/>
-    </row>
-    <row r="134" spans="1:1" ht="14.4">
-      <c r="A134" s="7"/>
-    </row>
-    <row r="135" spans="1:1" ht="14.4">
-      <c r="A135" s="7"/>
-    </row>
-    <row r="136" spans="1:1" ht="14.4">
-      <c r="A136" s="8"/>
-    </row>
-    <row r="137" spans="1:1" ht="14.4">
-      <c r="A137" s="7"/>
-    </row>
-    <row r="138" spans="1:1" ht="14.4">
-      <c r="A138" s="7"/>
-    </row>
-    <row r="139" spans="1:1" ht="14.4">
-      <c r="A139" s="7"/>
-    </row>
-    <row r="140" spans="1:1" ht="14.4">
-      <c r="A140" s="8"/>
-    </row>
-    <row r="141" spans="1:1" ht="14.4">
-      <c r="A141" s="7"/>
-    </row>
-    <row r="142" spans="1:1" ht="14.4">
-      <c r="A142" s="7"/>
-    </row>
-    <row r="143" spans="1:1" ht="14.4">
-      <c r="A143" s="7"/>
-    </row>
-    <row r="144" spans="1:1" ht="14.4">
-      <c r="A144" s="7"/>
-    </row>
-    <row r="145" spans="1:1" ht="14.4">
-      <c r="A145" s="7"/>
-    </row>
-    <row r="146" spans="1:1" ht="14.4">
-      <c r="A146" s="7"/>
-    </row>
-    <row r="147" spans="1:1" ht="14.4">
-      <c r="A147" s="7"/>
-    </row>
-    <row r="148" spans="1:1" ht="14.4">
-      <c r="A148" s="7"/>
-    </row>
-    <row r="149" spans="1:1" ht="14.4">
-      <c r="A149" s="8"/>
-    </row>
-    <row r="150" spans="1:1" ht="14.4">
-      <c r="A150" s="8"/>
-    </row>
-    <row r="151" spans="1:1" ht="14.4">
-      <c r="A151" s="7"/>
-    </row>
-    <row r="152" spans="1:1" ht="14.4">
-      <c r="A152" s="7"/>
-    </row>
-    <row r="153" spans="1:1" ht="14.4">
-      <c r="A153" s="8"/>
-    </row>
-    <row r="154" spans="1:1" ht="14.4">
-      <c r="A154" s="7"/>
-    </row>
-    <row r="155" spans="1:1" ht="14.4">
-      <c r="A155" s="7"/>
-    </row>
-    <row r="156" spans="1:1" ht="14.4">
-      <c r="A156" s="7"/>
-    </row>
-    <row r="157" spans="1:1" ht="14.4">
-      <c r="A157" s="8"/>
-    </row>
-    <row r="158" spans="1:1" ht="14.4">
-      <c r="A158" s="8"/>
-    </row>
-    <row r="159" spans="1:1" ht="14.4">
-      <c r="A159" s="7"/>
-    </row>
-    <row r="160" spans="1:1" ht="14.4">
-      <c r="A160" s="8"/>
-    </row>
-    <row r="161" spans="1:1" ht="14.4">
-      <c r="A161" s="8"/>
-    </row>
-    <row r="162" spans="1:1" ht="14.4">
-      <c r="A162" s="8"/>
-    </row>
-    <row r="163" spans="1:1" ht="14.4">
-      <c r="A163" s="7"/>
-    </row>
-    <row r="164" spans="1:1" ht="14.4">
-      <c r="A164" s="8"/>
-    </row>
-    <row r="165" spans="1:1" ht="14.4">
-      <c r="A165" s="7"/>
-    </row>
-    <row r="166" spans="1:1" ht="14.4">
-      <c r="A166" s="7"/>
-    </row>
-    <row r="167" spans="1:1" ht="14.4">
-      <c r="A167" s="7"/>
-    </row>
-    <row r="168" spans="1:1" ht="14.4">
-      <c r="A168" s="7"/>
-    </row>
-    <row r="169" spans="1:1" ht="14.4">
-      <c r="A169" s="7"/>
-    </row>
-    <row r="170" spans="1:1" ht="14.4">
-      <c r="A170" s="8"/>
-    </row>
-    <row r="171" spans="1:1" ht="14.4">
-      <c r="A171" s="7"/>
-    </row>
-    <row r="172" spans="1:1" ht="14.4">
-      <c r="A172" s="8"/>
-    </row>
-    <row r="173" spans="1:1" ht="14.4">
-      <c r="A173" s="7"/>
-    </row>
-    <row r="174" spans="1:1" ht="14.4">
-      <c r="A174" s="8"/>
-    </row>
-    <row r="175" spans="1:1" ht="14.4">
-      <c r="A175" s="7"/>
-    </row>
-    <row r="176" spans="1:1" ht="14.4">
-      <c r="A176" s="7"/>
-    </row>
-    <row r="177" spans="1:1" ht="14.4">
-      <c r="A177" s="7"/>
-    </row>
-    <row r="178" spans="1:1" ht="14.4">
-      <c r="A178" s="7"/>
-    </row>
-    <row r="179" spans="1:1" ht="14.4">
-      <c r="A179" s="8"/>
-    </row>
-    <row r="180" spans="1:1" ht="14.4">
-      <c r="A180" s="7"/>
-    </row>
-    <row r="181" spans="1:1" ht="14.4">
-      <c r="A181" s="8"/>
-    </row>
-    <row r="182" spans="1:1" ht="14.4">
-      <c r="A182" s="8"/>
-    </row>
-    <row r="183" spans="1:1" ht="14.4">
-      <c r="A183" s="8"/>
-    </row>
-    <row r="184" spans="1:1" ht="14.4">
-      <c r="A184" s="7"/>
-    </row>
-    <row r="185" spans="1:1" ht="14.4">
-      <c r="A185" s="7"/>
-    </row>
-    <row r="186" spans="1:1" ht="14.4">
-      <c r="A186" s="7"/>
-    </row>
-    <row r="187" spans="1:1" ht="14.4">
-      <c r="A187" s="7"/>
-    </row>
-    <row r="188" spans="1:1" ht="14.4">
-      <c r="A188" s="8"/>
-    </row>
-    <row r="189" spans="1:1" ht="14.4">
-      <c r="A189" s="8"/>
-    </row>
-    <row r="190" spans="1:1" ht="14.4">
-      <c r="A190" s="7"/>
-    </row>
-    <row r="191" spans="1:1" ht="14.4">
-      <c r="A191" s="7"/>
-    </row>
-    <row r="192" spans="1:1" ht="14.4">
-      <c r="A192" s="7"/>
-    </row>
-    <row r="193" spans="1:1" ht="14.4">
-      <c r="A193" s="8"/>
-    </row>
-    <row r="194" spans="1:1" ht="14.4">
-      <c r="A194" s="7"/>
-    </row>
-    <row r="195" spans="1:1" ht="14.4">
-      <c r="A195" s="8"/>
-    </row>
-    <row r="196" spans="1:1" ht="14.4">
-      <c r="A196" s="7"/>
-    </row>
-    <row r="197" spans="1:1" ht="14.4">
-      <c r="A197" s="7"/>
-    </row>
-    <row r="198" spans="1:1" ht="14.4">
-      <c r="A198" s="7"/>
-    </row>
-    <row r="199" spans="1:1" ht="14.4">
-      <c r="A199" s="7"/>
-    </row>
-    <row r="200" spans="1:1" ht="14.4">
+    <row r="129" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A129" s="16" t="s">
+        <v>755</v>
+      </c>
+      <c r="B129" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A130" s="16" t="s">
+        <v>756</v>
+      </c>
+      <c r="B130" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A131" s="15" t="s">
+        <v>757</v>
+      </c>
+      <c r="B131" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A132" s="16" t="s">
+        <v>758</v>
+      </c>
+      <c r="B132" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A133" s="16" t="s">
+        <v>759</v>
+      </c>
+      <c r="B133" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A134" s="16" t="s">
+        <v>760</v>
+      </c>
+      <c r="B134" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A135" s="15" t="s">
+        <v>761</v>
+      </c>
+      <c r="B135" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A136" s="16" t="s">
+        <v>762</v>
+      </c>
+      <c r="B136" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A137" s="16" t="s">
+        <v>763</v>
+      </c>
+      <c r="B137" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A138" s="16" t="s">
+        <v>764</v>
+      </c>
+      <c r="B138" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A139" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="B139" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A140" s="16" t="s">
+        <v>766</v>
+      </c>
+      <c r="B140" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A141" s="16" t="s">
+        <v>767</v>
+      </c>
+      <c r="B141" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A142" s="16" t="s">
+        <v>768</v>
+      </c>
+      <c r="B142" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A143" s="16" t="s">
+        <v>769</v>
+      </c>
+      <c r="B143" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A144" s="16" t="s">
+        <v>769</v>
+      </c>
+      <c r="B144" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A145" s="16" t="s">
+        <v>770</v>
+      </c>
+      <c r="B145" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A146" s="16" t="s">
+        <v>771</v>
+      </c>
+      <c r="B146" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A147" s="15" t="s">
+        <v>772</v>
+      </c>
+      <c r="B147" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A148" s="15" t="s">
+        <v>773</v>
+      </c>
+      <c r="B148" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A149" s="16" t="s">
+        <v>774</v>
+      </c>
+      <c r="B149" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A150" s="16" t="s">
+        <v>775</v>
+      </c>
+      <c r="B150" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A151" s="16" t="s">
+        <v>776</v>
+      </c>
+      <c r="B151" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A152" s="15" t="s">
+        <v>777</v>
+      </c>
+      <c r="B152" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A153" s="16" t="s">
+        <v>778</v>
+      </c>
+      <c r="B153" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A154" s="16" t="s">
+        <v>779</v>
+      </c>
+      <c r="B154" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A155" s="16" t="s">
+        <v>780</v>
+      </c>
+      <c r="B155" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A156" s="16" t="s">
+        <v>781</v>
+      </c>
+      <c r="B156" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A157" s="16" t="s">
+        <v>782</v>
+      </c>
+      <c r="B157" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A158" s="15" t="s">
+        <v>783</v>
+      </c>
+      <c r="B158" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A159" s="15" t="s">
+        <v>784</v>
+      </c>
+      <c r="B159" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A160" s="15" t="s">
+        <v>785</v>
+      </c>
+      <c r="B160" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A161" s="16" t="s">
+        <v>786</v>
+      </c>
+      <c r="B161" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A162" s="16" t="s">
+        <v>787</v>
+      </c>
+      <c r="B162" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A163" s="16" t="s">
+        <v>788</v>
+      </c>
+      <c r="B163" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A164" s="16" t="s">
+        <v>789</v>
+      </c>
+      <c r="B164" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A165" s="15" t="s">
+        <v>790</v>
+      </c>
+      <c r="B165" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A166" s="16" t="s">
+        <v>791</v>
+      </c>
+      <c r="B166" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A167" s="15" t="s">
+        <v>792</v>
+      </c>
+      <c r="B167" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A168" s="15" t="s">
+        <v>793</v>
+      </c>
+      <c r="B168" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A169" s="15" t="s">
+        <v>794</v>
+      </c>
+      <c r="B169" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A170" s="16" t="s">
+        <v>795</v>
+      </c>
+      <c r="B170" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A171" s="16" t="s">
+        <v>796</v>
+      </c>
+      <c r="B171" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A172" s="16" t="s">
+        <v>797</v>
+      </c>
+      <c r="B172" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A173" s="15" t="s">
+        <v>798</v>
+      </c>
+      <c r="B173" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A174" s="16" t="s">
+        <v>799</v>
+      </c>
+      <c r="B174" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A175" s="16" t="s">
+        <v>800</v>
+      </c>
+      <c r="B175" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A176" s="16" t="s">
+        <v>801</v>
+      </c>
+      <c r="B176" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A177" s="16" t="s">
+        <v>802</v>
+      </c>
+      <c r="B177" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A178" s="16" t="s">
+        <v>803</v>
+      </c>
+      <c r="B178" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A179" s="15" t="s">
+        <v>804</v>
+      </c>
+      <c r="B179" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A180" s="16" t="s">
+        <v>805</v>
+      </c>
+      <c r="B180" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A181" s="16" t="s">
+        <v>806</v>
+      </c>
+      <c r="B181" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A182" s="16" t="s">
+        <v>807</v>
+      </c>
+      <c r="B182" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A183" s="15" t="s">
+        <v>808</v>
+      </c>
+      <c r="B183" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A184" s="16" t="s">
+        <v>809</v>
+      </c>
+      <c r="B184" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A185" s="15" t="s">
+        <v>810</v>
+      </c>
+      <c r="B185" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A186" s="16" t="s">
+        <v>811</v>
+      </c>
+      <c r="B186" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A187" s="16" t="s">
+        <v>812</v>
+      </c>
+      <c r="B187" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A188" s="15" t="s">
+        <v>813</v>
+      </c>
+      <c r="B188" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A189" s="15" t="s">
+        <v>814</v>
+      </c>
+      <c r="B189" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A190" s="16" t="s">
+        <v>815</v>
+      </c>
+      <c r="B190" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A191" s="16" t="s">
+        <v>816</v>
+      </c>
+      <c r="B191" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A192" s="15" t="s">
+        <v>817</v>
+      </c>
+      <c r="B192" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A193" s="15" t="s">
+        <v>818</v>
+      </c>
+      <c r="B193" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A194" s="16" t="s">
+        <v>819</v>
+      </c>
+      <c r="B194" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A195" s="16" t="s">
+        <v>820</v>
+      </c>
+      <c r="B195" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A196" s="15" t="s">
+        <v>821</v>
+      </c>
+      <c r="B196" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A197" s="15" t="s">
+        <v>750</v>
+      </c>
+      <c r="B197" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A198" s="16" t="s">
+        <v>822</v>
+      </c>
+      <c r="B198" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A199" s="16" t="s">
+        <v>823</v>
+      </c>
+      <c r="B199" s="17" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A200" s="7"/>
     </row>
-    <row r="201" spans="1:1" ht="14.4">
+    <row r="201" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A201" s="7"/>
     </row>
-    <row r="202" spans="1:1" ht="14.4">
+    <row r="202" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A202" s="7"/>
     </row>
-    <row r="203" spans="1:1" ht="14.4">
+    <row r="203" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A203" s="8"/>
     </row>
-    <row r="204" spans="1:1" ht="14.4">
+    <row r="204" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A204" s="7"/>
     </row>
-    <row r="205" spans="1:1" ht="14.4">
+    <row r="205" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A205" s="7"/>
     </row>
-    <row r="206" spans="1:1" ht="14.4">
+    <row r="206" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A206" s="7"/>
     </row>
-    <row r="207" spans="1:1" ht="14.4">
+    <row r="207" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A207" s="8"/>
     </row>
-    <row r="208" spans="1:1" ht="14.4">
+    <row r="208" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A208" s="7"/>
     </row>
-    <row r="209" spans="1:1" ht="14.4">
+    <row r="209" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A209" s="7"/>
     </row>
-    <row r="210" spans="1:1" ht="14.4">
+    <row r="210" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A210" s="7"/>
     </row>
-    <row r="211" spans="1:1" ht="14.4">
+    <row r="211" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A211" s="6"/>
     </row>
-    <row r="212" spans="1:1" ht="14.4">
+    <row r="212" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A212" s="3"/>
     </row>
-    <row r="213" spans="1:1" ht="14.4">
+    <row r="213" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A213" s="3"/>
     </row>
-    <row r="214" spans="1:1" ht="14.4">
+    <row r="214" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A214" s="3"/>
     </row>
-    <row r="215" spans="1:1" ht="14.4">
+    <row r="215" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A215" s="5"/>
     </row>
-    <row r="216" spans="1:1" ht="14.4">
+    <row r="216" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A216" s="3"/>
     </row>
-    <row r="217" spans="1:1" ht="14.4">
+    <row r="217" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A217" s="5"/>
     </row>
-    <row r="218" spans="1:1" ht="14.4">
+    <row r="218" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A218" s="5"/>
     </row>
-    <row r="219" spans="1:1" ht="14.4">
+    <row r="219" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A219" s="3"/>
     </row>
-    <row r="220" spans="1:1" ht="14.4">
+    <row r="220" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A220" s="3"/>
     </row>
-    <row r="221" spans="1:1" ht="14.4">
+    <row r="221" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A221" s="3"/>
     </row>
-    <row r="222" spans="1:1" ht="14.4">
+    <row r="222" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A222" s="5"/>
     </row>
-    <row r="223" spans="1:1" ht="14.4">
+    <row r="223" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A223" s="5"/>
     </row>
-    <row r="224" spans="1:1" ht="14.4">
+    <row r="224" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A224" s="5"/>
     </row>
-    <row r="225" spans="1:1" ht="14.4">
+    <row r="225" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A225" s="3"/>
     </row>
-    <row r="226" spans="1:1" ht="14.4">
+    <row r="226" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A226" s="5"/>
     </row>
-    <row r="227" spans="1:1" ht="14.4">
+    <row r="227" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A227" s="3"/>
     </row>
-    <row r="228" spans="1:1" ht="14.4">
+    <row r="228" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A228" s="3"/>
     </row>
-    <row r="229" spans="1:1" ht="14.4">
+    <row r="229" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A229" s="3"/>
     </row>
-    <row r="230" spans="1:1" ht="14.4">
+    <row r="230" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A230" s="3"/>
     </row>
-    <row r="231" spans="1:1" ht="14.4">
+    <row r="231" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A231" s="5"/>
     </row>
-    <row r="232" spans="1:1" ht="14.4">
+    <row r="232" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A232" s="10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:1" ht="14.4">
+    <row r="233" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A233" s="3"/>
     </row>
-    <row r="234" spans="1:1" ht="14.4">
+    <row r="234" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A234" s="3"/>
     </row>
-    <row r="235" spans="1:1" ht="14.4">
+    <row r="235" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A235" s="3"/>
     </row>
-    <row r="236" spans="1:1" ht="14.4">
+    <row r="236" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A236" s="3"/>
     </row>
-    <row r="237" spans="1:1" ht="14.4">
+    <row r="237" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A237" s="5"/>
     </row>
-    <row r="238" spans="1:1" ht="14.4">
+    <row r="238" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A238" s="5"/>
     </row>
-    <row r="239" spans="1:1" ht="14.4">
+    <row r="239" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A239" s="5"/>
     </row>
-    <row r="240" spans="1:1" ht="14.4">
+    <row r="240" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A240" s="3"/>
     </row>
-    <row r="241" spans="1:1" ht="14.4">
+    <row r="241" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A241" s="3"/>
     </row>
-    <row r="242" spans="1:1" ht="14.4">
+    <row r="242" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A242" s="5"/>
     </row>
-    <row r="243" spans="1:1" ht="14.4">
+    <row r="243" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A243" s="5"/>
     </row>
-    <row r="244" spans="1:1" ht="14.4">
+    <row r="244" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A244" s="3"/>
     </row>
-    <row r="245" spans="1:1" ht="14.4">
+    <row r="245" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A245" s="3"/>
     </row>
-    <row r="246" spans="1:1" ht="14.4">
+    <row r="246" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A246" s="3"/>
     </row>
-    <row r="247" spans="1:1" ht="14.4">
+    <row r="247" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A247" s="3"/>
     </row>
-    <row r="248" spans="1:1" ht="14.4">
+    <row r="248" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A248" s="3"/>
     </row>
-    <row r="249" spans="1:1" ht="14.4">
+    <row r="249" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A249" s="3"/>
     </row>
-    <row r="250" spans="1:1" ht="14.4">
+    <row r="250" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A250" s="3"/>
     </row>
-    <row r="251" spans="1:1" ht="14.4">
+    <row r="251" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A251" s="3"/>
     </row>
-    <row r="252" spans="1:1" ht="14.4">
+    <row r="252" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A252" s="3"/>
     </row>
-    <row r="253" spans="1:1" ht="14.4">
+    <row r="253" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A253" s="3"/>
     </row>
-    <row r="254" spans="1:1" ht="14.4">
+    <row r="254" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A254" s="3"/>
     </row>
-    <row r="255" spans="1:1" ht="14.4">
+    <row r="255" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A255" s="5"/>
     </row>
-    <row r="256" spans="1:1" ht="14.4">
+    <row r="256" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A256" s="3"/>
     </row>
-    <row r="257" spans="1:1" ht="14.4">
+    <row r="257" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A257" s="4"/>
     </row>
-    <row r="258" spans="1:1" ht="14.4">
+    <row r="258" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A258" s="3"/>
     </row>
-    <row r="259" spans="1:1" ht="14.4">
+    <row r="259" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A259" s="3"/>
     </row>
-    <row r="436" spans="1:2" ht="14.4">
+    <row r="436" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A436" s="10" t="s">
         <v>2</v>
       </c>
@@ -4762,7 +5151,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="437" spans="1:2" ht="14.4">
+    <row r="437" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A437" s="9" t="s">
         <v>3</v>
       </c>
@@ -4770,7 +5159,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="438" spans="1:2" ht="14.4">
+    <row r="438" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A438" s="9" t="s">
         <v>4</v>
       </c>
@@ -4778,7 +5167,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="439" spans="1:2" ht="14.4">
+    <row r="439" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A439" s="9" t="s">
         <v>5</v>
       </c>
@@ -4786,7 +5175,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="440" spans="1:2" ht="14.4">
+    <row r="440" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A440" s="10" t="s">
         <v>6</v>
       </c>
@@ -4794,7 +5183,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="441" spans="1:2" ht="14.4">
+    <row r="441" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A441" s="10" t="s">
         <v>7</v>
       </c>
@@ -4802,7 +5191,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="442" spans="1:2" ht="14.4">
+    <row r="442" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A442" s="10" t="s">
         <v>8</v>
       </c>
@@ -4810,7 +5199,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="443" spans="1:2" ht="14.4">
+    <row r="443" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A443" s="10" t="s">
         <v>9</v>
       </c>
@@ -4818,7 +5207,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="444" spans="1:2" ht="14.4">
+    <row r="444" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A444" s="10" t="s">
         <v>6</v>
       </c>
@@ -4826,7 +5215,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="445" spans="1:2" ht="14.4">
+    <row r="445" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A445" s="10" t="s">
         <v>10</v>
       </c>
@@ -4834,7 +5223,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="446" spans="1:2" ht="14.4">
+    <row r="446" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A446" s="9" t="s">
         <v>11</v>
       </c>
@@ -4842,7 +5231,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="447" spans="1:2" ht="14.4">
+    <row r="447" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A447" s="10" t="s">
         <v>12</v>
       </c>
@@ -4850,7 +5239,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="448" spans="1:2" ht="14.4">
+    <row r="448" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A448" s="10" t="s">
         <v>12</v>
       </c>
@@ -4858,7 +5247,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="449" spans="1:2" ht="14.4">
+    <row r="449" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A449" s="10" t="s">
         <v>13</v>
       </c>
@@ -4866,7 +5255,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="450" spans="1:2" ht="14.4">
+    <row r="450" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A450" s="10" t="s">
         <v>14</v>
       </c>
@@ -4874,7 +5263,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="451" spans="1:2" ht="14.4">
+    <row r="451" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A451" s="10" t="s">
         <v>15</v>
       </c>
@@ -4882,7 +5271,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="452" spans="1:2" ht="14.4">
+    <row r="452" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A452" s="9" t="s">
         <v>16</v>
       </c>
@@ -4890,7 +5279,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="453" spans="1:2" ht="14.4">
+    <row r="453" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A453" s="10" t="s">
         <v>17</v>
       </c>
@@ -4898,7 +5287,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="454" spans="1:2" ht="14.4">
+    <row r="454" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A454" s="9" t="s">
         <v>18</v>
       </c>
@@ -4906,7 +5295,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="455" spans="1:2" ht="14.4">
+    <row r="455" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A455" s="9" t="s">
         <v>19</v>
       </c>
@@ -4914,7 +5303,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="456" spans="1:2" ht="14.4">
+    <row r="456" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A456" s="10" t="s">
         <v>20</v>
       </c>
@@ -4922,7 +5311,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="457" spans="1:2" ht="14.4">
+    <row r="457" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A457" s="10" t="s">
         <v>21</v>
       </c>
@@ -4930,7 +5319,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="458" spans="1:2" ht="14.4">
+    <row r="458" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A458" s="9" t="s">
         <v>22</v>
       </c>
@@ -4938,7 +5327,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="459" spans="1:2" ht="14.4">
+    <row r="459" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A459" s="9" t="s">
         <v>23</v>
       </c>
@@ -4946,7 +5335,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="460" spans="1:2" ht="14.4">
+    <row r="460" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A460" s="10" t="s">
         <v>24</v>
       </c>
@@ -4954,7 +5343,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="461" spans="1:2" ht="14.4">
+    <row r="461" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A461" s="9" t="s">
         <v>25</v>
       </c>
@@ -4962,7 +5351,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="462" spans="1:2" ht="14.4">
+    <row r="462" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A462" s="9" t="s">
         <v>26</v>
       </c>
@@ -4970,7 +5359,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="463" spans="1:2" ht="14.4">
+    <row r="463" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A463" s="9" t="s">
         <v>27</v>
       </c>
@@ -4978,7 +5367,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="464" spans="1:2" ht="14.4">
+    <row r="464" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A464" s="9" t="s">
         <v>28</v>
       </c>
@@ -4986,7 +5375,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="465" spans="1:2" ht="14.4">
+    <row r="465" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A465" s="10" t="s">
         <v>29</v>
       </c>
@@ -4994,7 +5383,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="466" spans="1:2" ht="14.4">
+    <row r="466" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A466" s="9" t="s">
         <v>30</v>
       </c>
@@ -5002,7 +5391,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="467" spans="1:2" ht="14.4">
+    <row r="467" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A467" s="10" t="s">
         <v>31</v>
       </c>
@@ -5010,7 +5399,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="468" spans="1:2" ht="14.4">
+    <row r="468" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A468" s="10" t="s">
         <v>32</v>
       </c>
@@ -5018,7 +5407,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="469" spans="1:2" ht="14.4">
+    <row r="469" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A469" s="10" t="s">
         <v>33</v>
       </c>
@@ -5026,7 +5415,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="470" spans="1:2" ht="14.4">
+    <row r="470" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A470" s="10" t="s">
         <v>34</v>
       </c>
@@ -5034,7 +5423,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="471" spans="1:2" ht="14.4">
+    <row r="471" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A471" s="10" t="s">
         <v>35</v>
       </c>
@@ -5042,7 +5431,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="472" spans="1:2" ht="14.4">
+    <row r="472" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A472" s="10" t="s">
         <v>36</v>
       </c>
@@ -5050,7 +5439,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="473" spans="1:2" ht="14.4">
+    <row r="473" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A473" s="10" t="s">
         <v>37</v>
       </c>
@@ -5058,7 +5447,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="474" spans="1:2" ht="14.4">
+    <row r="474" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A474" s="10" t="s">
         <v>38</v>
       </c>
@@ -5066,7 +5455,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="475" spans="1:2" ht="14.4">
+    <row r="475" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A475" s="10" t="s">
         <v>39</v>
       </c>
@@ -5074,7 +5463,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="476" spans="1:2" ht="14.4">
+    <row r="476" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A476" s="10" t="s">
         <v>40</v>
       </c>
@@ -5082,7 +5471,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="477" spans="1:2" ht="14.4">
+    <row r="477" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A477" s="10" t="s">
         <v>41</v>
       </c>
@@ -5090,7 +5479,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="478" spans="1:2" ht="14.4">
+    <row r="478" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A478" s="10" t="s">
         <v>42</v>
       </c>
@@ -5098,7 +5487,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="479" spans="1:2" ht="14.4">
+    <row r="479" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A479" s="10" t="s">
         <v>43</v>
       </c>
@@ -5106,7 +5495,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="480" spans="1:2" ht="14.4">
+    <row r="480" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A480" s="10" t="s">
         <v>44</v>
       </c>
@@ -5114,7 +5503,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="481" spans="1:2" ht="14.4">
+    <row r="481" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A481" s="10" t="s">
         <v>45</v>
       </c>
@@ -5122,7 +5511,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="482" spans="1:2" ht="14.4">
+    <row r="482" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A482" s="10" t="s">
         <v>46</v>
       </c>
@@ -5130,7 +5519,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="483" spans="1:2" ht="14.4">
+    <row r="483" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A483" s="10" t="s">
         <v>47</v>
       </c>
@@ -5138,7 +5527,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="484" spans="1:2" ht="14.4">
+    <row r="484" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A484" s="9" t="s">
         <v>48</v>
       </c>
@@ -5146,7 +5535,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="485" spans="1:2" ht="14.4">
+    <row r="485" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A485" s="9" t="s">
         <v>49</v>
       </c>
@@ -5154,7 +5543,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="486" spans="1:2" ht="14.4">
+    <row r="486" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A486" s="10" t="s">
         <v>50</v>
       </c>
@@ -5162,7 +5551,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="487" spans="1:2" ht="14.4">
+    <row r="487" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A487" s="10" t="s">
         <v>51</v>
       </c>
@@ -5170,7 +5559,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="488" spans="1:2" ht="14.4">
+    <row r="488" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A488" s="9" t="s">
         <v>52</v>
       </c>
@@ -5178,7 +5567,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="489" spans="1:2" ht="14.4">
+    <row r="489" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A489" s="10" t="s">
         <v>53</v>
       </c>
@@ -5186,7 +5575,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="490" spans="1:2" ht="14.4">
+    <row r="490" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A490" s="9" t="s">
         <v>54</v>
       </c>
@@ -5194,7 +5583,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="491" spans="1:2" ht="14.4">
+    <row r="491" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A491" s="9" t="s">
         <v>55</v>
       </c>
@@ -5202,7 +5591,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="492" spans="1:2" ht="14.4">
+    <row r="492" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A492" s="10" t="s">
         <v>56</v>
       </c>
@@ -5210,7 +5599,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="493" spans="1:2" ht="14.4">
+    <row r="493" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A493" s="9" t="s">
         <v>57</v>
       </c>
@@ -5218,7 +5607,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="494" spans="1:2" ht="14.4">
+    <row r="494" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A494" s="10" t="s">
         <v>58</v>
       </c>
@@ -5226,7 +5615,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="495" spans="1:2" ht="14.4">
+    <row r="495" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A495" s="9" t="s">
         <v>59</v>
       </c>
@@ -5234,7 +5623,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="496" spans="1:2" ht="14.4">
+    <row r="496" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A496" s="9" t="s">
         <v>60</v>
       </c>
@@ -5242,7 +5631,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="497" spans="1:2" ht="14.4">
+    <row r="497" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A497" s="9" t="s">
         <v>61</v>
       </c>
@@ -5250,7 +5639,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="498" spans="1:2" ht="14.4">
+    <row r="498" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A498" s="9" t="s">
         <v>62</v>
       </c>
@@ -5258,7 +5647,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="499" spans="1:2" ht="14.4">
+    <row r="499" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A499" s="10" t="s">
         <v>63</v>
       </c>
@@ -5266,7 +5655,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="500" spans="1:2" ht="14.4">
+    <row r="500" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A500" s="9" t="s">
         <v>64</v>
       </c>
@@ -5274,7 +5663,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="501" spans="1:2" ht="14.4">
+    <row r="501" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A501" s="10" t="s">
         <v>65</v>
       </c>
@@ -5282,7 +5671,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="502" spans="1:2" ht="14.4">
+    <row r="502" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A502" s="10" t="s">
         <v>66</v>
       </c>
@@ -5290,7 +5679,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="503" spans="1:2" ht="14.4">
+    <row r="503" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A503" s="10" t="s">
         <v>67</v>
       </c>
@@ -5298,7 +5687,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="504" spans="1:2" ht="14.4">
+    <row r="504" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A504" s="10" t="s">
         <v>68</v>
       </c>
@@ -5306,7 +5695,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="505" spans="1:2" ht="14.4">
+    <row r="505" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A505" s="10" t="s">
         <v>69</v>
       </c>
@@ -5314,7 +5703,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="506" spans="1:2" ht="14.4">
+    <row r="506" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A506" s="10" t="s">
         <v>70</v>
       </c>
@@ -5322,7 +5711,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="507" spans="1:2" ht="14.4">
+    <row r="507" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A507" s="10" t="s">
         <v>71</v>
       </c>
@@ -5330,7 +5719,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="508" spans="1:2" ht="14.4">
+    <row r="508" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A508" s="10" t="s">
         <v>72</v>
       </c>
@@ -5338,7 +5727,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="509" spans="1:2" ht="14.4">
+    <row r="509" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A509" s="10" t="s">
         <v>73</v>
       </c>
@@ -5346,7 +5735,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="510" spans="1:2" ht="14.4">
+    <row r="510" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A510" s="9" t="s">
         <v>74</v>
       </c>
@@ -5354,7 +5743,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="511" spans="1:2" ht="14.4">
+    <row r="511" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A511" s="10" t="s">
         <v>75</v>
       </c>
@@ -5362,7 +5751,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="512" spans="1:2" ht="14.4">
+    <row r="512" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A512" s="10" t="s">
         <v>76</v>
       </c>
@@ -5370,7 +5759,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="513" spans="1:2" ht="14.4">
+    <row r="513" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A513" s="10" t="s">
         <v>29</v>
       </c>
@@ -5378,7 +5767,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="515" spans="1:2" ht="14.4">
+    <row r="515" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A515" s="10" t="s">
         <v>599</v>
       </c>
@@ -5386,7 +5775,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="516" spans="1:2" ht="14.4">
+    <row r="516" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A516" s="9" t="s">
         <v>598</v>
       </c>
@@ -5394,7 +5783,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="517" spans="1:2" ht="14.4">
+    <row r="517" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A517" s="9" t="s">
         <v>597</v>
       </c>
@@ -5402,7 +5791,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="518" spans="1:2" ht="14.4">
+    <row r="518" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A518" s="10" t="s">
         <v>596</v>
       </c>
@@ -5410,7 +5799,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="519" spans="1:2" ht="14.4">
+    <row r="519" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A519" s="9" t="s">
         <v>595</v>
       </c>
@@ -5418,7 +5807,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="520" spans="1:2" ht="14.4">
+    <row r="520" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A520" s="10" t="s">
         <v>594</v>
       </c>
@@ -5426,7 +5815,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="521" spans="1:2" ht="14.4">
+    <row r="521" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A521" s="10" t="s">
         <v>593</v>
       </c>
@@ -5434,7 +5823,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="522" spans="1:2" ht="14.4">
+    <row r="522" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A522" s="10" t="s">
         <v>592</v>
       </c>
@@ -5442,7 +5831,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="523" spans="1:2" ht="14.4">
+    <row r="523" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A523" s="9" t="s">
         <v>591</v>
       </c>
@@ -5450,7 +5839,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="524" spans="1:2" ht="14.4">
+    <row r="524" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A524" s="9" t="s">
         <v>590</v>
       </c>
@@ -5458,7 +5847,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="525" spans="1:2" ht="14.4">
+    <row r="525" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A525" s="10" t="s">
         <v>589</v>
       </c>
@@ -5466,7 +5855,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="526" spans="1:2" ht="14.4">
+    <row r="526" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A526" s="10" t="s">
         <v>588</v>
       </c>
@@ -5474,7 +5863,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="527" spans="1:2" ht="14.4">
+    <row r="527" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A527" s="10" t="s">
         <v>587</v>
       </c>
@@ -5482,7 +5871,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="528" spans="1:2" ht="14.4">
+    <row r="528" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A528" s="10" t="s">
         <v>586</v>
       </c>
@@ -5490,7 +5879,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="529" spans="1:2" ht="14.4">
+    <row r="529" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A529" s="10" t="s">
         <v>585</v>
       </c>
@@ -5498,7 +5887,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="530" spans="1:2" ht="14.4">
+    <row r="530" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A530" s="9" t="s">
         <v>584</v>
       </c>
@@ -5506,7 +5895,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="531" spans="1:2" ht="14.4">
+    <row r="531" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A531" s="10" t="s">
         <v>583</v>
       </c>
@@ -5514,7 +5903,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="532" spans="1:2" ht="14.4">
+    <row r="532" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A532" s="10" t="s">
         <v>582</v>
       </c>
@@ -5522,7 +5911,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="533" spans="1:2" ht="14.4">
+    <row r="533" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A533" s="10" t="s">
         <v>581</v>
       </c>
@@ -5530,7 +5919,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="534" spans="1:2" ht="14.4">
+    <row r="534" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A534" s="10" t="s">
         <v>580</v>
       </c>
@@ -5538,7 +5927,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="535" spans="1:2" ht="14.4">
+    <row r="535" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A535" s="9" t="s">
         <v>579</v>
       </c>
@@ -5546,7 +5935,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="536" spans="1:2" ht="14.4">
+    <row r="536" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A536" s="9" t="s">
         <v>578</v>
       </c>
@@ -5554,7 +5943,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="537" spans="1:2" ht="14.4">
+    <row r="537" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A537" s="10" t="s">
         <v>577</v>
       </c>
@@ -5562,7 +5951,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="538" spans="1:2" ht="14.4">
+    <row r="538" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A538" s="9" t="s">
         <v>576</v>
       </c>
@@ -5570,7 +5959,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="539" spans="1:2" ht="14.4">
+    <row r="539" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A539" s="9" t="s">
         <v>575</v>
       </c>
@@ -5578,7 +5967,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="540" spans="1:2" ht="14.4">
+    <row r="540" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A540" s="9" t="s">
         <v>574</v>
       </c>
@@ -5586,7 +5975,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="541" spans="1:2" ht="14.4">
+    <row r="541" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A541" s="9" t="s">
         <v>573</v>
       </c>
@@ -5594,7 +5983,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="542" spans="1:2" ht="14.4">
+    <row r="542" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A542" s="10" t="s">
         <v>572</v>
       </c>
@@ -5602,7 +5991,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="543" spans="1:2" ht="14.4">
+    <row r="543" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A543" s="10" t="s">
         <v>571</v>
       </c>
@@ -5610,7 +5999,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="544" spans="1:2" ht="14.4">
+    <row r="544" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A544" s="9" t="s">
         <v>570</v>
       </c>
@@ -5618,7 +6007,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="545" spans="1:2" ht="14.4">
+    <row r="545" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A545" s="10" t="s">
         <v>569</v>
       </c>
@@ -5626,7 +6015,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="546" spans="1:2" ht="14.4">
+    <row r="546" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A546" s="10" t="s">
         <v>568</v>
       </c>
@@ -5634,7 +6023,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="547" spans="1:2" ht="14.4">
+    <row r="547" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A547" s="9" t="s">
         <v>543</v>
       </c>
@@ -5642,7 +6031,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="548" spans="1:2" ht="14.4">
+    <row r="548" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A548" s="9" t="s">
         <v>567</v>
       </c>
@@ -5650,7 +6039,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="549" spans="1:2" ht="14.4">
+    <row r="549" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A549" s="10" t="s">
         <v>566</v>
       </c>
@@ -5658,7 +6047,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="550" spans="1:2" ht="14.4">
+    <row r="550" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A550" s="9" t="s">
         <v>565</v>
       </c>
@@ -5666,7 +6055,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="551" spans="1:2" ht="14.4">
+    <row r="551" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A551" s="10" t="s">
         <v>564</v>
       </c>
@@ -5674,7 +6063,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="552" spans="1:2" ht="14.4">
+    <row r="552" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A552" s="9" t="s">
         <v>563</v>
       </c>
@@ -5682,7 +6071,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="553" spans="1:2" ht="14.4">
+    <row r="553" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A553" s="9" t="s">
         <v>562</v>
       </c>
@@ -5690,7 +6079,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="554" spans="1:2" ht="14.4">
+    <row r="554" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A554" s="10" t="s">
         <v>561</v>
       </c>
@@ -5698,7 +6087,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="555" spans="1:2" ht="14.4">
+    <row r="555" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A555" s="9" t="s">
         <v>560</v>
       </c>
@@ -5706,7 +6095,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="556" spans="1:2" ht="14.4">
+    <row r="556" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A556" s="10" t="s">
         <v>559</v>
       </c>
@@ -5714,7 +6103,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="557" spans="1:2" ht="14.4">
+    <row r="557" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A557" s="10" t="s">
         <v>558</v>
       </c>
@@ -5722,7 +6111,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="558" spans="1:2" ht="14.4">
+    <row r="558" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A558" s="9" t="s">
         <v>557</v>
       </c>
@@ -5730,7 +6119,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="559" spans="1:2" ht="14.4">
+    <row r="559" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A559" s="9" t="s">
         <v>556</v>
       </c>
@@ -5738,7 +6127,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="560" spans="1:2" ht="14.4">
+    <row r="560" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A560" s="9" t="s">
         <v>555</v>
       </c>
@@ -5746,7 +6135,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="561" spans="1:2" ht="14.4">
+    <row r="561" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A561" s="10" t="s">
         <v>554</v>
       </c>
@@ -5754,7 +6143,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="562" spans="1:2" ht="14.4">
+    <row r="562" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A562" s="9" t="s">
         <v>553</v>
       </c>
@@ -5762,7 +6151,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="563" spans="1:2" ht="14.4">
+    <row r="563" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A563" s="9" t="s">
         <v>552</v>
       </c>
@@ -5770,7 +6159,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="564" spans="1:2" ht="14.4">
+    <row r="564" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A564" s="9" t="s">
         <v>551</v>
       </c>
@@ -5778,7 +6167,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="565" spans="1:2" ht="14.4">
+    <row r="565" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A565" s="9" t="s">
         <v>550</v>
       </c>
@@ -5786,7 +6175,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="566" spans="1:2" ht="14.4">
+    <row r="566" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A566" s="10" t="s">
         <v>549</v>
       </c>
@@ -5794,7 +6183,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="567" spans="1:2" ht="14.4">
+    <row r="567" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A567" s="10" t="s">
         <v>548</v>
       </c>
@@ -5802,7 +6191,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="568" spans="1:2" ht="14.4">
+    <row r="568" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A568" s="10" t="s">
         <v>547</v>
       </c>
@@ -5810,7 +6199,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="569" spans="1:2" ht="14.4">
+    <row r="569" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A569" s="10" t="s">
         <v>546</v>
       </c>
@@ -5818,7 +6207,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="570" spans="1:2" ht="14.4">
+    <row r="570" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A570" s="9" t="s">
         <v>545</v>
       </c>
@@ -5826,7 +6215,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="571" spans="1:2" ht="14.4">
+    <row r="571" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A571" s="10" t="s">
         <v>544</v>
       </c>
@@ -5834,7 +6223,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="572" spans="1:2" ht="14.4">
+    <row r="572" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A572" s="9" t="s">
         <v>543</v>
       </c>
@@ -5842,7 +6231,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="573" spans="1:2" ht="14.4">
+    <row r="573" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A573" s="10" t="s">
         <v>542</v>
       </c>
@@ -5850,7 +6239,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="574" spans="1:2" ht="14.4">
+    <row r="574" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A574" s="10" t="s">
         <v>541</v>
       </c>
@@ -5858,7 +6247,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="575" spans="1:2" ht="14.4">
+    <row r="575" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A575" s="10" t="s">
         <v>540</v>
       </c>
@@ -5866,7 +6255,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="576" spans="1:2" ht="14.4">
+    <row r="576" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A576" s="9" t="s">
         <v>539</v>
       </c>
@@ -5874,7 +6263,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="577" spans="1:2" ht="14.4">
+    <row r="577" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A577" s="10" t="s">
         <v>538</v>
       </c>
@@ -5882,7 +6271,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="578" spans="1:2" ht="14.4">
+    <row r="578" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A578" s="9" t="s">
         <v>537</v>
       </c>
@@ -5890,7 +6279,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="579" spans="1:2" ht="14.4">
+    <row r="579" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A579" s="10" t="s">
         <v>536</v>
       </c>
@@ -5898,7 +6287,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="580" spans="1:2" ht="14.4">
+    <row r="580" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A580" s="10" t="s">
         <v>535</v>
       </c>
@@ -5906,7 +6295,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="581" spans="1:2" ht="14.4">
+    <row r="581" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A581" s="10" t="s">
         <v>534</v>
       </c>
@@ -5914,7 +6303,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="582" spans="1:2" ht="14.4">
+    <row r="582" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A582" s="9" t="s">
         <v>533</v>
       </c>
@@ -5922,7 +6311,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="583" spans="1:2" ht="14.4">
+    <row r="583" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A583" s="10" t="s">
         <v>532</v>
       </c>
@@ -5930,7 +6319,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="584" spans="1:2" ht="14.4">
+    <row r="584" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A584" s="10" t="s">
         <v>531</v>
       </c>
@@ -5938,7 +6327,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="585" spans="1:2" ht="14.4">
+    <row r="585" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A585" s="10" t="s">
         <v>530</v>
       </c>
@@ -5946,7 +6335,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="586" spans="1:2" ht="14.4">
+    <row r="586" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A586" s="10" t="s">
         <v>529</v>
       </c>
@@ -5954,7 +6343,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="587" spans="1:2" ht="14.4">
+    <row r="587" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A587" s="10" t="s">
         <v>528</v>
       </c>
@@ -5962,7 +6351,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="588" spans="1:2" ht="14.4">
+    <row r="588" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A588" s="9" t="s">
         <v>527</v>
       </c>
@@ -5970,7 +6359,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="589" spans="1:2" ht="14.4">
+    <row r="589" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A589" s="10" t="s">
         <v>526</v>
       </c>
@@ -5978,16 +6367,16 @@
         <v>600</v>
       </c>
     </row>
-    <row r="590" spans="1:2" ht="14.4">
+    <row r="590" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A590" s="10"/>
     </row>
-    <row r="591" spans="1:2" ht="14.4">
+    <row r="591" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A591" s="10"/>
     </row>
-    <row r="592" spans="1:2" ht="14.4">
+    <row r="592" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A592" s="10"/>
     </row>
-    <row r="593" spans="1:2" ht="14.4">
+    <row r="593" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A593" s="10" t="s">
         <v>254</v>
       </c>
@@ -5995,7 +6384,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="594" spans="1:2" ht="14.4">
+    <row r="594" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A594" s="10" t="s">
         <v>253</v>
       </c>
@@ -6003,7 +6392,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="595" spans="1:2" ht="14.4">
+    <row r="595" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A595" s="9" t="s">
         <v>252</v>
       </c>
@@ -6011,7 +6400,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="596" spans="1:2" ht="14.4">
+    <row r="596" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A596" s="10" t="s">
         <v>251</v>
       </c>
@@ -6019,7 +6408,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="597" spans="1:2" ht="14.4">
+    <row r="597" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A597" s="10" t="s">
         <v>250</v>
       </c>
@@ -6027,7 +6416,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="598" spans="1:2" ht="14.4">
+    <row r="598" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A598" s="10" t="s">
         <v>249</v>
       </c>
@@ -6035,7 +6424,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="599" spans="1:2" ht="14.4">
+    <row r="599" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A599" s="9" t="s">
         <v>248</v>
       </c>
@@ -6043,7 +6432,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="600" spans="1:2" ht="14.4">
+    <row r="600" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A600" s="10" t="s">
         <v>247</v>
       </c>
@@ -6051,7 +6440,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="601" spans="1:2" ht="14.4">
+    <row r="601" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A601" s="10" t="s">
         <v>246</v>
       </c>
@@ -6059,7 +6448,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="602" spans="1:2" ht="14.4">
+    <row r="602" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A602" s="10" t="s">
         <v>245</v>
       </c>
@@ -6067,7 +6456,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="603" spans="1:2" ht="14.4">
+    <row r="603" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A603" s="9" t="s">
         <v>244</v>
       </c>
@@ -6075,7 +6464,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="604" spans="1:2" ht="14.4">
+    <row r="604" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A604" s="10" t="s">
         <v>243</v>
       </c>
@@ -6083,7 +6472,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="605" spans="1:2" ht="14.4">
+    <row r="605" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A605" s="10" t="s">
         <v>242</v>
       </c>
@@ -6091,7 +6480,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="606" spans="1:2" ht="14.4">
+    <row r="606" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A606" s="10" t="s">
         <v>241</v>
       </c>
@@ -6099,7 +6488,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="607" spans="1:2" ht="14.4">
+    <row r="607" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A607" s="10" t="s">
         <v>240</v>
       </c>
@@ -6107,7 +6496,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="608" spans="1:2" ht="14.4">
+    <row r="608" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A608" s="10" t="s">
         <v>239</v>
       </c>
@@ -6115,7 +6504,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="609" spans="1:2" ht="14.4">
+    <row r="609" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A609" s="10" t="s">
         <v>238</v>
       </c>
@@ -6123,7 +6512,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="610" spans="1:2" ht="14.4">
+    <row r="610" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A610" s="10" t="s">
         <v>237</v>
       </c>
@@ -6131,7 +6520,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="611" spans="1:2" ht="14.4">
+    <row r="611" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A611" s="9" t="s">
         <v>236</v>
       </c>
@@ -6139,7 +6528,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="612" spans="1:2" ht="14.4">
+    <row r="612" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A612" s="10" t="s">
         <v>235</v>
       </c>
@@ -6147,7 +6536,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="613" spans="1:2" ht="14.4">
+    <row r="613" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A613" s="10" t="s">
         <v>234</v>
       </c>
@@ -6155,7 +6544,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="614" spans="1:2" ht="14.4">
+    <row r="614" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A614" s="9" t="s">
         <v>233</v>
       </c>
@@ -6163,7 +6552,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="615" spans="1:2" ht="14.4">
+    <row r="615" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A615" s="10" t="s">
         <v>232</v>
       </c>
@@ -6171,7 +6560,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="616" spans="1:2" ht="14.4">
+    <row r="616" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A616" s="10" t="s">
         <v>231</v>
       </c>
@@ -6179,7 +6568,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="617" spans="1:2" ht="14.4">
+    <row r="617" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A617" s="9" t="s">
         <v>230</v>
       </c>
@@ -6187,7 +6576,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="618" spans="1:2" ht="14.4">
+    <row r="618" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A618" s="9" t="s">
         <v>229</v>
       </c>
@@ -6195,7 +6584,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="619" spans="1:2" ht="14.4">
+    <row r="619" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A619" s="10" t="s">
         <v>228</v>
       </c>
@@ -6203,7 +6592,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="620" spans="1:2" ht="14.4">
+    <row r="620" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A620" s="10" t="s">
         <v>227</v>
       </c>
@@ -6211,7 +6600,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="621" spans="1:2" ht="14.4">
+    <row r="621" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A621" s="9" t="s">
         <v>226</v>
       </c>
@@ -6219,7 +6608,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="622" spans="1:2" ht="14.4">
+    <row r="622" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A622" s="10" t="s">
         <v>225</v>
       </c>
@@ -6227,7 +6616,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="623" spans="1:2" ht="14.4">
+    <row r="623" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A623" s="10" t="s">
         <v>224</v>
       </c>
@@ -6235,7 +6624,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="624" spans="1:2" ht="14.4">
+    <row r="624" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A624" s="10" t="s">
         <v>223</v>
       </c>
@@ -6243,7 +6632,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="625" spans="1:2" ht="14.4">
+    <row r="625" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A625" s="10" t="s">
         <v>222</v>
       </c>
@@ -6251,7 +6640,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="626" spans="1:2" ht="14.4">
+    <row r="626" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A626" s="9" t="s">
         <v>221</v>
       </c>
@@ -6259,7 +6648,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="627" spans="1:2" ht="14.4">
+    <row r="627" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A627" s="10" t="s">
         <v>220</v>
       </c>
@@ -6267,7 +6656,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="628" spans="1:2" ht="14.4">
+    <row r="628" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A628" s="9" t="s">
         <v>219</v>
       </c>
@@ -6275,7 +6664,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="629" spans="1:2" ht="14.4">
+    <row r="629" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A629" s="10" t="s">
         <v>218</v>
       </c>
@@ -6283,7 +6672,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="630" spans="1:2" ht="14.4">
+    <row r="630" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A630" s="10" t="s">
         <v>217</v>
       </c>
@@ -6291,7 +6680,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="631" spans="1:2" ht="14.4">
+    <row r="631" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A631" s="9" t="s">
         <v>216</v>
       </c>
@@ -6299,7 +6688,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="632" spans="1:2" ht="14.4">
+    <row r="632" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A632" s="10" t="s">
         <v>215</v>
       </c>
@@ -6307,7 +6696,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="633" spans="1:2" ht="14.4">
+    <row r="633" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A633" s="10" t="s">
         <v>214</v>
       </c>
@@ -6315,7 +6704,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="634" spans="1:2" ht="14.4">
+    <row r="634" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A634" s="10" t="s">
         <v>213</v>
       </c>
@@ -6323,7 +6712,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="635" spans="1:2" ht="14.4">
+    <row r="635" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A635" s="10" t="s">
         <v>212</v>
       </c>
@@ -6331,7 +6720,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="636" spans="1:2" ht="14.4">
+    <row r="636" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A636" s="10" t="s">
         <v>211</v>
       </c>
@@ -6339,7 +6728,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="637" spans="1:2" ht="14.4">
+    <row r="637" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A637" s="9" t="s">
         <v>210</v>
       </c>
@@ -6347,7 +6736,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="638" spans="1:2" ht="14.4">
+    <row r="638" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A638" s="10" t="s">
         <v>209</v>
       </c>
@@ -6355,7 +6744,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="639" spans="1:2" ht="14.4">
+    <row r="639" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A639" s="10" t="s">
         <v>208</v>
       </c>
@@ -6363,7 +6752,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="640" spans="1:2" ht="14.4">
+    <row r="640" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A640" s="9" t="s">
         <v>207</v>
       </c>
@@ -6371,7 +6760,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="641" spans="1:2" ht="14.4">
+    <row r="641" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A641" s="9" t="s">
         <v>206</v>
       </c>
@@ -6379,7 +6768,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="642" spans="1:2" ht="14.4">
+    <row r="642" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A642" s="10" t="s">
         <v>205</v>
       </c>
@@ -6387,7 +6776,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="643" spans="1:2" ht="14.4">
+    <row r="643" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A643" s="10" t="s">
         <v>204</v>
       </c>
@@ -6395,7 +6784,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="644" spans="1:2" ht="14.4">
+    <row r="644" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A644" s="9" t="s">
         <v>203</v>
       </c>
@@ -6403,7 +6792,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="645" spans="1:2" ht="14.4">
+    <row r="645" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A645" s="9" t="s">
         <v>202</v>
       </c>
@@ -6411,7 +6800,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="646" spans="1:2" ht="14.4">
+    <row r="646" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A646" s="10" t="s">
         <v>201</v>
       </c>
@@ -6419,7 +6808,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="647" spans="1:2" ht="14.4">
+    <row r="647" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A647" s="9" t="s">
         <v>200</v>
       </c>
@@ -6427,7 +6816,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="648" spans="1:2" ht="14.4">
+    <row r="648" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A648" s="10" t="s">
         <v>199</v>
       </c>
@@ -6435,7 +6824,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="649" spans="1:2" ht="14.4">
+    <row r="649" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A649" s="9" t="s">
         <v>198</v>
       </c>
@@ -6443,7 +6832,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="650" spans="1:2" ht="14.4">
+    <row r="650" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A650" s="10" t="s">
         <v>197</v>
       </c>
@@ -6451,7 +6840,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="651" spans="1:2" ht="14.4">
+    <row r="651" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A651" s="10" t="s">
         <v>196</v>
       </c>
@@ -6459,7 +6848,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="652" spans="1:2" ht="14.4">
+    <row r="652" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A652" s="10" t="s">
         <v>195</v>
       </c>
@@ -6467,7 +6856,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="653" spans="1:2" ht="14.4">
+    <row r="653" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A653" s="9" t="s">
         <v>194</v>
       </c>
@@ -6475,7 +6864,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="654" spans="1:2" ht="14.4">
+    <row r="654" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A654" s="10" t="s">
         <v>193</v>
       </c>
@@ -6483,7 +6872,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="655" spans="1:2" ht="14.4">
+    <row r="655" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A655" s="10" t="s">
         <v>192</v>
       </c>
@@ -6491,7 +6880,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="656" spans="1:2" ht="14.4">
+    <row r="656" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A656" s="10" t="s">
         <v>191</v>
       </c>
@@ -6499,7 +6888,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="657" spans="1:2" ht="14.4">
+    <row r="657" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A657" s="9" t="s">
         <v>190</v>
       </c>
@@ -6507,7 +6896,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="658" spans="1:2" ht="14.4">
+    <row r="658" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A658" s="9" t="s">
         <v>189</v>
       </c>
@@ -6515,7 +6904,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="659" spans="1:2" ht="14.4">
+    <row r="659" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A659" s="10" t="s">
         <v>188</v>
       </c>
@@ -6523,7 +6912,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="660" spans="1:2" ht="14.4">
+    <row r="660" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A660" s="10" t="s">
         <v>187</v>
       </c>
@@ -6531,7 +6920,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="661" spans="1:2" ht="14.4">
+    <row r="661" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A661" s="10" t="s">
         <v>186</v>
       </c>
@@ -6539,7 +6928,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="662" spans="1:2" ht="14.4">
+    <row r="662" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A662" s="10" t="s">
         <v>185</v>
       </c>
@@ -6547,7 +6936,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="663" spans="1:2" ht="14.4">
+    <row r="663" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A663" s="10" t="s">
         <v>184</v>
       </c>
@@ -6555,7 +6944,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="664" spans="1:2" ht="14.4">
+    <row r="664" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A664" s="9" t="s">
         <v>183</v>
       </c>
@@ -6563,7 +6952,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="665" spans="1:2" ht="14.4">
+    <row r="665" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A665" s="10" t="s">
         <v>182</v>
       </c>
@@ -6571,7 +6960,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="666" spans="1:2" ht="14.4">
+    <row r="666" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A666" s="10" t="s">
         <v>181</v>
       </c>
@@ -6579,7 +6968,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="667" spans="1:2" ht="14.4">
+    <row r="667" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A667" s="10" t="s">
         <v>180</v>
       </c>
@@ -6587,7 +6976,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="668" spans="1:2" ht="14.4">
+    <row r="668" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A668" s="9" t="s">
         <v>179</v>
       </c>
@@ -6595,10 +6984,10 @@
         <v>523</v>
       </c>
     </row>
-    <row r="669" spans="1:2" ht="14.4">
+    <row r="669" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A669" s="9"/>
     </row>
-    <row r="670" spans="1:2" ht="14.4">
+    <row r="670" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A670" s="10" t="s">
         <v>77</v>
       </c>
@@ -6606,7 +6995,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="671" spans="1:2" ht="14.4">
+    <row r="671" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A671" s="10" t="s">
         <v>145</v>
       </c>
@@ -6614,7 +7003,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="672" spans="1:2" ht="14.4">
+    <row r="672" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A672" s="10" t="s">
         <v>178</v>
       </c>
@@ -6622,7 +7011,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="673" spans="1:2" ht="14.4">
+    <row r="673" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A673" s="9" t="s">
         <v>177</v>
       </c>
@@ -6630,7 +7019,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="674" spans="1:2" ht="14.4">
+    <row r="674" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A674" s="9" t="s">
         <v>176</v>
       </c>
@@ -6638,7 +7027,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="675" spans="1:2" ht="14.4">
+    <row r="675" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A675" s="10" t="s">
         <v>175</v>
       </c>
@@ -6646,7 +7035,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="676" spans="1:2" ht="14.4">
+    <row r="676" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A676" s="10" t="s">
         <v>174</v>
       </c>
@@ -6654,7 +7043,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="677" spans="1:2" ht="14.4">
+    <row r="677" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A677" s="9" t="s">
         <v>173</v>
       </c>
@@ -6662,7 +7051,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="678" spans="1:2" ht="14.4">
+    <row r="678" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A678" s="10" t="s">
         <v>172</v>
       </c>
@@ -6670,7 +7059,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="679" spans="1:2" ht="14.4">
+    <row r="679" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A679" s="10" t="s">
         <v>171</v>
       </c>
@@ -6678,7 +7067,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="680" spans="1:2" ht="14.4">
+    <row r="680" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A680" s="10" t="s">
         <v>170</v>
       </c>
@@ -6686,7 +7075,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="681" spans="1:2" ht="14.4">
+    <row r="681" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A681" s="10" t="s">
         <v>169</v>
       </c>
@@ -6694,7 +7083,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="682" spans="1:2" ht="14.4">
+    <row r="682" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A682" s="10" t="s">
         <v>168</v>
       </c>
@@ -6702,7 +7091,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="683" spans="1:2" ht="14.4">
+    <row r="683" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A683" s="9" t="s">
         <v>167</v>
       </c>
@@ -6710,7 +7099,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="684" spans="1:2" ht="14.4">
+    <row r="684" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A684" s="9" t="s">
         <v>166</v>
       </c>
@@ -6718,7 +7107,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="685" spans="1:2" ht="14.4">
+    <row r="685" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A685" s="9" t="s">
         <v>165</v>
       </c>
@@ -6726,7 +7115,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="686" spans="1:2" ht="14.4">
+    <row r="686" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A686" s="9" t="s">
         <v>164</v>
       </c>
@@ -6734,7 +7123,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="687" spans="1:2" ht="14.4">
+    <row r="687" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A687" s="9" t="s">
         <v>163</v>
       </c>
@@ -6742,7 +7131,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="688" spans="1:2" ht="14.4">
+    <row r="688" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A688" s="9" t="s">
         <v>162</v>
       </c>
@@ -6750,7 +7139,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="689" spans="1:2" ht="14.4">
+    <row r="689" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A689" s="10" t="s">
         <v>161</v>
       </c>
@@ -6758,7 +7147,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="690" spans="1:2" ht="14.4">
+    <row r="690" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A690" s="10" t="s">
         <v>160</v>
       </c>
@@ -6766,7 +7155,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="691" spans="1:2" ht="14.4">
+    <row r="691" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A691" s="9" t="s">
         <v>159</v>
       </c>
@@ -6774,7 +7163,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="692" spans="1:2" ht="14.4">
+    <row r="692" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A692" s="9" t="s">
         <v>158</v>
       </c>
@@ -6782,7 +7171,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="693" spans="1:2" ht="14.4">
+    <row r="693" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A693" s="9" t="s">
         <v>157</v>
       </c>
@@ -6790,7 +7179,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="694" spans="1:2" ht="14.4">
+    <row r="694" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A694" s="10" t="s">
         <v>156</v>
       </c>
@@ -6798,7 +7187,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="695" spans="1:2" ht="14.4">
+    <row r="695" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A695" s="10" t="s">
         <v>155</v>
       </c>
@@ -6806,7 +7195,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="696" spans="1:2" ht="14.4">
+    <row r="696" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A696" s="9" t="s">
         <v>154</v>
       </c>
@@ -6814,7 +7203,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="697" spans="1:2" ht="14.4">
+    <row r="697" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A697" s="10" t="s">
         <v>153</v>
       </c>
@@ -6822,7 +7211,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="698" spans="1:2" ht="14.4">
+    <row r="698" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A698" s="10" t="s">
         <v>152</v>
       </c>
@@ -6830,7 +7219,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="699" spans="1:2" ht="14.4">
+    <row r="699" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A699" s="9" t="s">
         <v>151</v>
       </c>
@@ -6838,7 +7227,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="700" spans="1:2" ht="14.4">
+    <row r="700" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A700" s="10" t="s">
         <v>150</v>
       </c>
@@ -6846,7 +7235,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="701" spans="1:2" ht="14.4">
+    <row r="701" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A701" s="10" t="s">
         <v>149</v>
       </c>
@@ -6854,7 +7243,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="702" spans="1:2" ht="14.4">
+    <row r="702" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A702" s="10" t="s">
         <v>148</v>
       </c>
@@ -6862,7 +7251,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="703" spans="1:2" ht="14.4">
+    <row r="703" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A703" s="9" t="s">
         <v>147</v>
       </c>
@@ -6870,7 +7259,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="704" spans="1:2" ht="14.4">
+    <row r="704" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A704" s="9" t="s">
         <v>146</v>
       </c>
@@ -6878,7 +7267,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="705" spans="1:2" ht="14.4">
+    <row r="705" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A705" s="10" t="s">
         <v>145</v>
       </c>
@@ -6886,7 +7275,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="706" spans="1:2" ht="14.4">
+    <row r="706" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A706" s="10" t="s">
         <v>144</v>
       </c>
@@ -6894,7 +7283,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="707" spans="1:2" ht="14.4">
+    <row r="707" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A707" s="9" t="s">
         <v>143</v>
       </c>
@@ -6902,7 +7291,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="708" spans="1:2" ht="14.4">
+    <row r="708" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A708" s="10" t="s">
         <v>142</v>
       </c>
@@ -6910,7 +7299,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="709" spans="1:2" ht="14.4">
+    <row r="709" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A709" s="10" t="s">
         <v>141</v>
       </c>
@@ -6918,7 +7307,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="710" spans="1:2" ht="14.4">
+    <row r="710" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A710" s="10" t="s">
         <v>140</v>
       </c>
@@ -6926,7 +7315,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="711" spans="1:2" ht="14.4">
+    <row r="711" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A711" s="10" t="s">
         <v>139</v>
       </c>
@@ -6934,7 +7323,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="712" spans="1:2" ht="14.4">
+    <row r="712" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A712" s="10" t="s">
         <v>138</v>
       </c>
@@ -6942,7 +7331,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="713" spans="1:2" ht="14.4">
+    <row r="713" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A713" s="10" t="s">
         <v>137</v>
       </c>
@@ -6950,7 +7339,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="714" spans="1:2" ht="14.4">
+    <row r="714" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A714" s="9" t="s">
         <v>136</v>
       </c>
@@ -6958,7 +7347,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="715" spans="1:2" ht="14.4">
+    <row r="715" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A715" s="10" t="s">
         <v>135</v>
       </c>
@@ -6966,7 +7355,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="716" spans="1:2" ht="14.4">
+    <row r="716" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A716" s="9" t="s">
         <v>134</v>
       </c>
@@ -6974,7 +7363,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="717" spans="1:2" ht="14.4">
+    <row r="717" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A717" s="9" t="s">
         <v>133</v>
       </c>
@@ -6982,7 +7371,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="718" spans="1:2" ht="14.4">
+    <row r="718" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A718" s="10" t="s">
         <v>132</v>
       </c>
@@ -6990,7 +7379,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="719" spans="1:2" ht="14.4">
+    <row r="719" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A719" s="9" t="s">
         <v>131</v>
       </c>
@@ -6998,7 +7387,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="720" spans="1:2" ht="14.4">
+    <row r="720" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A720" s="10" t="s">
         <v>130</v>
       </c>
@@ -7006,7 +7395,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="721" spans="1:2" ht="14.4">
+    <row r="721" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A721" s="10" t="s">
         <v>129</v>
       </c>
@@ -7014,7 +7403,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="722" spans="1:2" ht="14.4">
+    <row r="722" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A722" s="10" t="s">
         <v>128</v>
       </c>
@@ -7022,7 +7411,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="723" spans="1:2" ht="14.4">
+    <row r="723" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A723" s="10" t="s">
         <v>127</v>
       </c>
@@ -7030,7 +7419,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="724" spans="1:2" ht="14.4">
+    <row r="724" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A724" s="10" t="s">
         <v>126</v>
       </c>
@@ -7038,7 +7427,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="725" spans="1:2" ht="14.4">
+    <row r="725" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A725" s="10" t="s">
         <v>125</v>
       </c>
@@ -7046,7 +7435,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="726" spans="1:2" ht="14.4">
+    <row r="726" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A726" s="10" t="s">
         <v>124</v>
       </c>
@@ -7054,7 +7443,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="727" spans="1:2" ht="14.4">
+    <row r="727" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A727" s="10" t="s">
         <v>123</v>
       </c>
@@ -7062,7 +7451,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="728" spans="1:2" ht="14.4">
+    <row r="728" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A728" s="10" t="s">
         <v>122</v>
       </c>
@@ -7070,7 +7459,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="729" spans="1:2" ht="14.4">
+    <row r="729" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A729" s="10" t="s">
         <v>121</v>
       </c>
@@ -7078,7 +7467,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="730" spans="1:2" ht="14.4">
+    <row r="730" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A730" s="9" t="s">
         <v>120</v>
       </c>
@@ -7086,7 +7475,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="731" spans="1:2" ht="14.4">
+    <row r="731" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A731" s="10" t="s">
         <v>119</v>
       </c>
@@ -7094,7 +7483,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="732" spans="1:2" ht="14.4">
+    <row r="732" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A732" s="10" t="s">
         <v>118</v>
       </c>
@@ -7102,7 +7491,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="733" spans="1:2" ht="14.4">
+    <row r="733" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A733" s="10" t="s">
         <v>117</v>
       </c>
@@ -7110,7 +7499,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="734" spans="1:2" ht="14.4">
+    <row r="734" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A734" s="10" t="s">
         <v>116</v>
       </c>
@@ -7118,7 +7507,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="735" spans="1:2" ht="14.4">
+    <row r="735" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A735" s="9" t="s">
         <v>115</v>
       </c>
@@ -7126,7 +7515,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="736" spans="1:2" ht="14.4">
+    <row r="736" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A736" s="10" t="s">
         <v>114</v>
       </c>
@@ -7134,7 +7523,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="737" spans="1:2" ht="14.4">
+    <row r="737" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A737" s="9" t="s">
         <v>113</v>
       </c>
@@ -7142,7 +7531,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="738" spans="1:2" ht="14.4">
+    <row r="738" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A738" s="9" t="s">
         <v>112</v>
       </c>
@@ -7150,7 +7539,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="739" spans="1:2" ht="14.4">
+    <row r="739" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A739" s="10" t="s">
         <v>111</v>
       </c>
@@ -7158,7 +7547,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="740" spans="1:2" ht="14.4">
+    <row r="740" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A740" s="9" t="s">
         <v>110</v>
       </c>
@@ -7166,7 +7555,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="741" spans="1:2" ht="14.4">
+    <row r="741" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A741" s="9" t="s">
         <v>109</v>
       </c>
@@ -7174,7 +7563,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="742" spans="1:2" ht="14.4">
+    <row r="742" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A742" s="10" t="s">
         <v>108</v>
       </c>
@@ -7182,7 +7571,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="743" spans="1:2" ht="14.4">
+    <row r="743" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A743" s="10" t="s">
         <v>107</v>
       </c>
@@ -7190,7 +7579,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="744" spans="1:2" ht="14.4">
+    <row r="744" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A744" s="9" t="s">
         <v>106</v>
       </c>
@@ -7198,7 +7587,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="745" spans="1:2" ht="14.4">
+    <row r="745" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A745" s="9" t="s">
         <v>105</v>
       </c>
@@ -7206,7 +7595,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="746" spans="1:2" ht="14.4">
+    <row r="746" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A746" s="10" t="s">
         <v>104</v>
       </c>
@@ -7214,7 +7603,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="747" spans="1:2" ht="14.4">
+    <row r="747" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A747" s="10" t="s">
         <v>103</v>
       </c>
@@ -7222,7 +7611,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="748" spans="1:2" ht="14.4">
+    <row r="748" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A748" s="10" t="s">
         <v>102</v>
       </c>
@@ -7230,7 +7619,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="749" spans="1:2" ht="14.4">
+    <row r="749" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A749" s="10" t="s">
         <v>101</v>
       </c>
@@ -7238,7 +7627,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="750" spans="1:2" ht="14.4">
+    <row r="750" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A750" s="10" t="s">
         <v>100</v>
       </c>
@@ -7246,7 +7635,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="751" spans="1:2" ht="14.4">
+    <row r="751" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A751" s="10" t="s">
         <v>99</v>
       </c>
@@ -7254,7 +7643,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="752" spans="1:2" ht="14.4">
+    <row r="752" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A752" s="9" t="s">
         <v>98</v>
       </c>
@@ -7262,7 +7651,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="753" spans="1:2" ht="14.4">
+    <row r="753" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A753" s="10" t="s">
         <v>97</v>
       </c>
@@ -7270,7 +7659,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="754" spans="1:2" ht="14.4">
+    <row r="754" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A754" s="10" t="s">
         <v>96</v>
       </c>
@@ -7278,7 +7667,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="755" spans="1:2" ht="14.4">
+    <row r="755" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A755" s="10" t="s">
         <v>95</v>
       </c>
@@ -7286,7 +7675,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="756" spans="1:2" ht="14.4">
+    <row r="756" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A756" s="10" t="s">
         <v>94</v>
       </c>
@@ -7294,7 +7683,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="757" spans="1:2" ht="14.4">
+    <row r="757" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A757" s="10" t="s">
         <v>93</v>
       </c>
@@ -7302,7 +7691,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="758" spans="1:2" ht="14.4">
+    <row r="758" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A758" s="9" t="s">
         <v>92</v>
       </c>
@@ -7310,7 +7699,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="759" spans="1:2" ht="14.4">
+    <row r="759" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A759" s="9" t="s">
         <v>91</v>
       </c>
@@ -7318,7 +7707,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="760" spans="1:2" ht="14.4">
+    <row r="760" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A760" s="9" t="s">
         <v>90</v>
       </c>
@@ -7326,7 +7715,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="761" spans="1:2" ht="14.4">
+    <row r="761" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A761" s="10" t="s">
         <v>89</v>
       </c>
@@ -7334,7 +7723,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="762" spans="1:2" ht="14.4">
+    <row r="762" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A762" s="10" t="s">
         <v>88</v>
       </c>
@@ -7342,7 +7731,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="763" spans="1:2" ht="14.4">
+    <row r="763" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A763" s="10" t="s">
         <v>87</v>
       </c>
@@ -7350,7 +7739,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="764" spans="1:2" ht="14.4">
+    <row r="764" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A764" s="10" t="s">
         <v>86</v>
       </c>
@@ -7358,7 +7747,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="765" spans="1:2" ht="14.4">
+    <row r="765" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A765" s="9" t="s">
         <v>85</v>
       </c>
@@ -7366,7 +7755,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="766" spans="1:2" ht="14.4">
+    <row r="766" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A766" s="9" t="s">
         <v>84</v>
       </c>
@@ -7374,7 +7763,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="767" spans="1:2" ht="14.4">
+    <row r="767" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A767" s="10" t="s">
         <v>83</v>
       </c>
@@ -7382,7 +7771,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="768" spans="1:2" ht="14.4">
+    <row r="768" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A768" s="10" t="s">
         <v>82</v>
       </c>
@@ -7390,7 +7779,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="769" spans="1:2" ht="14.4">
+    <row r="769" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A769" s="10" t="s">
         <v>81</v>
       </c>
@@ -7398,7 +7787,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="770" spans="1:2" ht="14.4">
+    <row r="770" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A770" s="10" t="s">
         <v>80</v>
       </c>
@@ -7406,7 +7795,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="771" spans="1:2" ht="14.4">
+    <row r="771" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A771" s="10" t="s">
         <v>79</v>
       </c>
@@ -7414,7 +7803,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="772" spans="1:2" ht="14.4">
+    <row r="772" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A772" s="10" t="s">
         <v>78</v>
       </c>
@@ -7422,7 +7811,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="773" spans="1:2" ht="14.4">
+    <row r="773" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A773" s="10" t="s">
         <v>77</v>
       </c>
@@ -7430,7 +7819,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="775" spans="1:2" ht="14.4">
+    <row r="775" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A775" s="10">
         <v>777425546939086</v>
       </c>
@@ -7438,7 +7827,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="776" spans="1:2" ht="14.4">
+    <row r="776" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A776" s="10" t="s">
         <v>411</v>
       </c>
@@ -7446,7 +7835,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="777" spans="1:2" ht="14.4">
+    <row r="777" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A777" s="9" t="s">
         <v>410</v>
       </c>
@@ -7454,7 +7843,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="778" spans="1:2" ht="14.4">
+    <row r="778" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A778" s="10" t="s">
         <v>409</v>
       </c>
@@ -7462,7 +7851,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="779" spans="1:2" ht="14.4">
+    <row r="779" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A779" s="10" t="s">
         <v>408</v>
       </c>
@@ -7470,7 +7859,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="780" spans="1:2" ht="14.4">
+    <row r="780" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A780" s="9" t="s">
         <v>407</v>
       </c>
@@ -7478,7 +7867,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="781" spans="1:2" ht="14.4">
+    <row r="781" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A781" s="10" t="s">
         <v>406</v>
       </c>
@@ -7486,7 +7875,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="782" spans="1:2" ht="14.4">
+    <row r="782" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A782" s="10" t="s">
         <v>405</v>
       </c>
@@ -7494,7 +7883,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="783" spans="1:2" ht="14.4">
+    <row r="783" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A783" s="10" t="s">
         <v>404</v>
       </c>
@@ -7502,7 +7891,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="784" spans="1:2" ht="14.4">
+    <row r="784" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A784" s="10" t="s">
         <v>403</v>
       </c>
@@ -7510,7 +7899,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="785" spans="1:2" ht="14.4">
+    <row r="785" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A785" s="10" t="s">
         <v>402</v>
       </c>
@@ -7518,7 +7907,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="786" spans="1:2" ht="14.4">
+    <row r="786" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A786" s="10" t="s">
         <v>401</v>
       </c>
@@ -7526,7 +7915,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="787" spans="1:2" ht="14.4">
+    <row r="787" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A787" s="10" t="s">
         <v>400</v>
       </c>
@@ -7534,7 +7923,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="788" spans="1:2" ht="14.4">
+    <row r="788" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A788" s="10" t="s">
         <v>399</v>
       </c>
@@ -7542,7 +7931,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="789" spans="1:2" ht="14.4">
+    <row r="789" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A789" s="9" t="s">
         <v>398</v>
       </c>
@@ -7550,7 +7939,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="790" spans="1:2" ht="14.4">
+    <row r="790" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A790" s="10" t="s">
         <v>397</v>
       </c>
@@ -7558,7 +7947,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="791" spans="1:2" ht="14.4">
+    <row r="791" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A791" s="10" t="s">
         <v>396</v>
       </c>
@@ -7566,7 +7955,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="792" spans="1:2" ht="14.4">
+    <row r="792" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A792" s="10" t="s">
         <v>395</v>
       </c>
@@ -7574,7 +7963,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="793" spans="1:2" ht="14.4">
+    <row r="793" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A793" s="10" t="s">
         <v>394</v>
       </c>
@@ -7582,7 +7971,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="794" spans="1:2" ht="14.4">
+    <row r="794" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A794" s="10" t="s">
         <v>393</v>
       </c>
@@ -7590,7 +7979,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="795" spans="1:2" ht="14.4">
+    <row r="795" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A795" s="9" t="s">
         <v>392</v>
       </c>
@@ -7598,7 +7987,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="796" spans="1:2" ht="14.4">
+    <row r="796" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A796" s="10" t="s">
         <v>391</v>
       </c>
@@ -7606,7 +7995,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="797" spans="1:2" ht="14.4">
+    <row r="797" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A797" s="9" t="s">
         <v>390</v>
       </c>
@@ -7614,7 +8003,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="798" spans="1:2" ht="14.4">
+    <row r="798" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A798" s="10" t="s">
         <v>389</v>
       </c>
@@ -7622,7 +8011,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="799" spans="1:2" ht="14.4">
+    <row r="799" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A799" s="10" t="s">
         <v>388</v>
       </c>
@@ -7630,7 +8019,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="800" spans="1:2" ht="14.4">
+    <row r="800" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A800" s="10" t="s">
         <v>387</v>
       </c>
@@ -7638,7 +8027,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="801" spans="1:2" ht="14.4">
+    <row r="801" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A801" s="10" t="s">
         <v>386</v>
       </c>
@@ -7646,7 +8035,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="802" spans="1:2" ht="14.4">
+    <row r="802" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A802" s="10" t="s">
         <v>385</v>
       </c>
@@ -7654,7 +8043,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="803" spans="1:2" ht="14.4">
+    <row r="803" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A803" s="9" t="s">
         <v>384</v>
       </c>
@@ -7662,7 +8051,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="804" spans="1:2" ht="14.4">
+    <row r="804" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A804" s="10" t="s">
         <v>383</v>
       </c>
@@ -7670,7 +8059,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="805" spans="1:2" ht="14.4">
+    <row r="805" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A805" s="10" t="s">
         <v>382</v>
       </c>
@@ -7678,7 +8067,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="806" spans="1:2" ht="14.4">
+    <row r="806" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A806" s="10" t="s">
         <v>381</v>
       </c>
@@ -7686,7 +8075,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="807" spans="1:2" ht="14.4">
+    <row r="807" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A807" s="10" t="s">
         <v>380</v>
       </c>
@@ -7694,7 +8083,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="808" spans="1:2" ht="14.4">
+    <row r="808" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A808" s="9" t="s">
         <v>379</v>
       </c>
@@ -7702,7 +8091,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="809" spans="1:2" ht="14.4">
+    <row r="809" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A809" s="10" t="s">
         <v>378</v>
       </c>
@@ -7710,7 +8099,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="810" spans="1:2" ht="14.4">
+    <row r="810" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A810" s="10" t="s">
         <v>377</v>
       </c>
@@ -7718,7 +8107,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="811" spans="1:2" ht="14.4">
+    <row r="811" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A811" s="9" t="s">
         <v>376</v>
       </c>
@@ -7726,7 +8115,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="812" spans="1:2" ht="14.4">
+    <row r="812" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A812" s="9" t="s">
         <v>375</v>
       </c>
@@ -7734,7 +8123,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="814" spans="1:2" ht="14.4">
+    <row r="814" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A814" s="10" t="s">
         <v>519</v>
       </c>
@@ -7742,7 +8131,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="815" spans="1:2" ht="14.4">
+    <row r="815" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A815" s="10" t="s">
         <v>518</v>
       </c>
@@ -7750,7 +8139,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="816" spans="1:2" ht="14.4">
+    <row r="816" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A816" s="9" t="s">
         <v>517</v>
       </c>
@@ -7758,7 +8147,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="817" spans="1:2" ht="14.4">
+    <row r="817" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A817" s="10" t="s">
         <v>516</v>
       </c>
@@ -7766,7 +8155,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="818" spans="1:2" ht="14.4">
+    <row r="818" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A818" s="9" t="s">
         <v>515</v>
       </c>
@@ -7774,7 +8163,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="819" spans="1:2" ht="14.4">
+    <row r="819" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A819" s="10" t="s">
         <v>514</v>
       </c>
@@ -7782,7 +8171,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="820" spans="1:2" ht="14.4">
+    <row r="820" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A820" s="10" t="s">
         <v>513</v>
       </c>
@@ -7790,7 +8179,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="821" spans="1:2" ht="14.4">
+    <row r="821" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A821" s="9" t="s">
         <v>439</v>
       </c>
@@ -7798,7 +8187,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="822" spans="1:2" ht="14.4">
+    <row r="822" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A822" s="9" t="s">
         <v>512</v>
       </c>
@@ -7806,7 +8195,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="823" spans="1:2" ht="14.4">
+    <row r="823" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A823" s="10" t="s">
         <v>511</v>
       </c>
@@ -7814,7 +8203,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="824" spans="1:2" ht="14.4">
+    <row r="824" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A824" s="10" t="s">
         <v>510</v>
       </c>
@@ -7822,7 +8211,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="825" spans="1:2" ht="14.4">
+    <row r="825" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A825" s="10" t="s">
         <v>509</v>
       </c>
@@ -7830,7 +8219,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="826" spans="1:2" ht="14.4">
+    <row r="826" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A826" s="9" t="s">
         <v>508</v>
       </c>
@@ -7838,7 +8227,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="827" spans="1:2" ht="14.4">
+    <row r="827" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A827" s="10" t="s">
         <v>507</v>
       </c>
@@ -7846,7 +8235,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="828" spans="1:2" ht="14.4">
+    <row r="828" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A828" s="10" t="s">
         <v>506</v>
       </c>
@@ -7854,7 +8243,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="829" spans="1:2" ht="14.4">
+    <row r="829" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A829" s="9" t="s">
         <v>505</v>
       </c>
@@ -7862,7 +8251,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="830" spans="1:2" ht="14.4">
+    <row r="830" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A830" s="10" t="s">
         <v>504</v>
       </c>
@@ -7870,7 +8259,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="831" spans="1:2" ht="14.4">
+    <row r="831" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A831" s="9" t="s">
         <v>503</v>
       </c>
@@ -7878,7 +8267,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="832" spans="1:2" ht="14.4">
+    <row r="832" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A832" s="10" t="s">
         <v>502</v>
       </c>
@@ -7886,7 +8275,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="833" spans="1:2" ht="14.4">
+    <row r="833" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A833" s="10" t="s">
         <v>501</v>
       </c>
@@ -7894,7 +8283,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="834" spans="1:2" ht="14.4">
+    <row r="834" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A834" s="10" t="s">
         <v>500</v>
       </c>
@@ -7902,7 +8291,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="835" spans="1:2" ht="14.4">
+    <row r="835" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A835" s="10" t="s">
         <v>499</v>
       </c>
@@ -7910,7 +8299,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="836" spans="1:2" ht="14.4">
+    <row r="836" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A836" s="10" t="s">
         <v>498</v>
       </c>
@@ -7918,7 +8307,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="837" spans="1:2" ht="14.4">
+    <row r="837" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A837" s="9" t="s">
         <v>497</v>
       </c>
@@ -7926,7 +8315,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="838" spans="1:2" ht="14.4">
+    <row r="838" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A838" s="10" t="s">
         <v>496</v>
       </c>
@@ -7934,7 +8323,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="839" spans="1:2" ht="14.4">
+    <row r="839" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A839" s="9" t="s">
         <v>495</v>
       </c>
@@ -7942,7 +8331,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="840" spans="1:2" ht="14.4">
+    <row r="840" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A840" s="9" t="s">
         <v>494</v>
       </c>
@@ -7950,7 +8339,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="841" spans="1:2" ht="14.4">
+    <row r="841" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A841" s="10" t="s">
         <v>493</v>
       </c>
@@ -7958,7 +8347,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="842" spans="1:2" ht="14.4">
+    <row r="842" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A842" s="10" t="s">
         <v>492</v>
       </c>
@@ -7966,7 +8355,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="843" spans="1:2" ht="14.4">
+    <row r="843" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A843" s="10" t="s">
         <v>491</v>
       </c>
@@ -7974,7 +8363,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="844" spans="1:2" ht="14.4">
+    <row r="844" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A844" s="9" t="s">
         <v>490</v>
       </c>
@@ -7982,7 +8371,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="845" spans="1:2" ht="14.4">
+    <row r="845" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A845" s="9" t="s">
         <v>489</v>
       </c>
@@ -7990,7 +8379,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="846" spans="1:2" ht="14.4">
+    <row r="846" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A846" s="10" t="s">
         <v>488</v>
       </c>
@@ -7998,7 +8387,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="847" spans="1:2" ht="14.4">
+    <row r="847" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A847" s="10" t="s">
         <v>487</v>
       </c>
@@ -8006,7 +8395,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="848" spans="1:2" ht="14.4">
+    <row r="848" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A848" s="9" t="s">
         <v>486</v>
       </c>
@@ -8014,7 +8403,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="849" spans="1:2" ht="14.4">
+    <row r="849" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A849" s="10" t="s">
         <v>485</v>
       </c>
@@ -8022,7 +8411,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="850" spans="1:2" ht="14.4">
+    <row r="850" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A850" s="9" t="s">
         <v>484</v>
       </c>
@@ -8030,7 +8419,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="851" spans="1:2" ht="14.4">
+    <row r="851" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A851" s="9" t="s">
         <v>483</v>
       </c>
@@ -8038,7 +8427,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="852" spans="1:2" ht="14.4">
+    <row r="852" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A852" s="9" t="s">
         <v>482</v>
       </c>
@@ -8046,7 +8435,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="853" spans="1:2" ht="14.4">
+    <row r="853" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A853" s="10" t="s">
         <v>481</v>
       </c>
@@ -8054,7 +8443,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="854" spans="1:2" ht="14.4">
+    <row r="854" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A854" s="9" t="s">
         <v>480</v>
       </c>
@@ -8062,7 +8451,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="855" spans="1:2" ht="14.4">
+    <row r="855" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A855" s="10" t="s">
         <v>479</v>
       </c>
@@ -8070,7 +8459,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="856" spans="1:2" ht="14.4">
+    <row r="856" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A856" s="10" t="s">
         <v>478</v>
       </c>
@@ -8078,7 +8467,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="857" spans="1:2" ht="14.4">
+    <row r="857" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A857" s="9" t="s">
         <v>477</v>
       </c>
@@ -8086,7 +8475,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="858" spans="1:2" ht="14.4">
+    <row r="858" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A858" s="9" t="s">
         <v>476</v>
       </c>
@@ -8094,7 +8483,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="859" spans="1:2" ht="14.4">
+    <row r="859" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A859" s="9" t="s">
         <v>475</v>
       </c>
@@ -8102,7 +8491,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="860" spans="1:2" ht="14.4">
+    <row r="860" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A860" s="10" t="s">
         <v>474</v>
       </c>
@@ -8110,7 +8499,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="861" spans="1:2" ht="14.4">
+    <row r="861" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A861" s="10" t="s">
         <v>473</v>
       </c>
@@ -8118,7 +8507,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="862" spans="1:2" ht="14.4">
+    <row r="862" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A862" s="10" t="s">
         <v>472</v>
       </c>
@@ -8126,7 +8515,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="863" spans="1:2" ht="14.4">
+    <row r="863" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A863" s="9" t="s">
         <v>471</v>
       </c>
@@ -8134,7 +8523,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="864" spans="1:2" ht="14.4">
+    <row r="864" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A864" s="9" t="s">
         <v>470</v>
       </c>
@@ -8142,7 +8531,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="865" spans="1:2" ht="14.4">
+    <row r="865" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A865" s="10" t="s">
         <v>469</v>
       </c>
@@ -8150,7 +8539,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="866" spans="1:2" ht="14.4">
+    <row r="866" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A866" s="9" t="s">
         <v>468</v>
       </c>
@@ -8158,7 +8547,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="867" spans="1:2" ht="14.4">
+    <row r="867" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A867" s="10" t="s">
         <v>467</v>
       </c>
@@ -8166,7 +8555,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="868" spans="1:2" ht="14.4">
+    <row r="868" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A868" s="10" t="s">
         <v>466</v>
       </c>
@@ -8174,7 +8563,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="869" spans="1:2" ht="14.4">
+    <row r="869" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A869" s="9" t="s">
         <v>465</v>
       </c>
@@ -8182,7 +8571,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="870" spans="1:2" ht="14.4">
+    <row r="870" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A870" s="10" t="s">
         <v>464</v>
       </c>
@@ -8190,7 +8579,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="871" spans="1:2" ht="14.4">
+    <row r="871" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A871" s="10" t="s">
         <v>463</v>
       </c>
@@ -8198,7 +8587,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="872" spans="1:2" ht="14.4">
+    <row r="872" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A872" s="9" t="s">
         <v>462</v>
       </c>
@@ -8206,7 +8595,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="873" spans="1:2" ht="14.4">
+    <row r="873" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A873" s="9" t="s">
         <v>461</v>
       </c>
@@ -8214,7 +8603,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="874" spans="1:2" ht="14.4">
+    <row r="874" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A874" s="9" t="s">
         <v>460</v>
       </c>
@@ -8222,7 +8611,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="875" spans="1:2" ht="14.4">
+    <row r="875" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A875" s="10" t="s">
         <v>459</v>
       </c>
@@ -8230,7 +8619,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="876" spans="1:2" ht="14.4">
+    <row r="876" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A876" s="10" t="s">
         <v>458</v>
       </c>
@@ -8238,7 +8627,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="877" spans="1:2" ht="14.4">
+    <row r="877" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A877" s="10" t="s">
         <v>457</v>
       </c>
@@ -8246,7 +8635,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="878" spans="1:2" ht="14.4">
+    <row r="878" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A878" s="10" t="s">
         <v>456</v>
       </c>
@@ -8254,7 +8643,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="879" spans="1:2" ht="14.4">
+    <row r="879" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A879" s="9" t="s">
         <v>455</v>
       </c>
@@ -8262,7 +8651,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="880" spans="1:2" ht="14.4">
+    <row r="880" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A880" s="10" t="s">
         <v>454</v>
       </c>
@@ -8270,7 +8659,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="881" spans="1:2" ht="14.4">
+    <row r="881" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A881" s="10" t="s">
         <v>453</v>
       </c>
@@ -8278,7 +8667,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="882" spans="1:2" ht="14.4">
+    <row r="882" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A882" s="9" t="s">
         <v>452</v>
       </c>
@@ -8286,7 +8675,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="883" spans="1:2" ht="14.4">
+    <row r="883" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A883" s="10" t="s">
         <v>451</v>
       </c>
@@ -8294,7 +8683,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="884" spans="1:2" ht="14.4">
+    <row r="884" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A884" s="10" t="s">
         <v>450</v>
       </c>
@@ -8302,7 +8691,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="885" spans="1:2" ht="14.4">
+    <row r="885" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A885" s="10" t="s">
         <v>449</v>
       </c>
@@ -8310,7 +8699,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="886" spans="1:2" ht="14.4">
+    <row r="886" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A886" s="10" t="s">
         <v>448</v>
       </c>
@@ -8318,7 +8707,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="887" spans="1:2" ht="14.4">
+    <row r="887" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A887" s="10" t="s">
         <v>436</v>
       </c>
@@ -8326,7 +8715,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="888" spans="1:2" ht="14.4">
+    <row r="888" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A888" s="10" t="s">
         <v>447</v>
       </c>
@@ -8334,7 +8723,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="889" spans="1:2" ht="14.4">
+    <row r="889" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A889" s="9" t="s">
         <v>446</v>
       </c>
@@ -8342,7 +8731,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="890" spans="1:2" ht="14.4">
+    <row r="890" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A890" s="9" t="s">
         <v>445</v>
       </c>
@@ -8350,7 +8739,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="891" spans="1:2" ht="14.4">
+    <row r="891" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A891" s="10" t="s">
         <v>444</v>
       </c>
@@ -8358,7 +8747,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="892" spans="1:2" ht="14.4">
+    <row r="892" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A892" s="10" t="s">
         <v>443</v>
       </c>
@@ -8366,7 +8755,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="893" spans="1:2" ht="14.4">
+    <row r="893" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A893" s="10" t="s">
         <v>442</v>
       </c>
@@ -8374,7 +8763,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="894" spans="1:2" ht="14.4">
+    <row r="894" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A894" s="9" t="s">
         <v>441</v>
       </c>
@@ -8382,7 +8771,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="895" spans="1:2" ht="14.4">
+    <row r="895" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A895" s="10" t="s">
         <v>437</v>
       </c>
@@ -8390,7 +8779,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="896" spans="1:2" ht="14.4">
+    <row r="896" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A896" s="10" t="s">
         <v>440</v>
       </c>
@@ -8398,7 +8787,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="897" spans="1:2" ht="14.4">
+    <row r="897" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A897" s="9" t="s">
         <v>439</v>
       </c>
@@ -8406,7 +8795,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="898" spans="1:2" ht="14.4">
+    <row r="898" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A898" s="9" t="s">
         <v>438</v>
       </c>
@@ -8414,7 +8803,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="899" spans="1:2" ht="14.4">
+    <row r="899" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A899" s="10" t="s">
         <v>437</v>
       </c>
@@ -8422,7 +8811,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="900" spans="1:2" ht="14.4">
+    <row r="900" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A900" s="10" t="s">
         <v>436</v>
       </c>
@@ -8430,7 +8819,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="901" spans="1:2" ht="14.4">
+    <row r="901" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A901" s="10" t="s">
         <v>435</v>
       </c>
@@ -8438,7 +8827,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="902" spans="1:2" ht="14.4">
+    <row r="902" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A902" s="10" t="s">
         <v>434</v>
       </c>
@@ -8446,7 +8835,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="903" spans="1:2" ht="14.4">
+    <row r="903" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A903" s="10" t="s">
         <v>433</v>
       </c>
@@ -8454,7 +8843,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="904" spans="1:2" ht="14.4">
+    <row r="904" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A904" s="9" t="s">
         <v>432</v>
       </c>
@@ -8462,7 +8851,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="905" spans="1:2" ht="14.4">
+    <row r="905" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A905" s="9" t="s">
         <v>431</v>
       </c>
@@ -8470,7 +8859,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="906" spans="1:2" ht="14.4">
+    <row r="906" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A906" s="10" t="s">
         <v>430</v>
       </c>
@@ -8478,7 +8867,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="907" spans="1:2" ht="14.4">
+    <row r="907" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A907" s="10" t="s">
         <v>429</v>
       </c>
@@ -8486,7 +8875,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="908" spans="1:2" ht="14.4">
+    <row r="908" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A908" s="10" t="s">
         <v>428</v>
       </c>
@@ -8494,7 +8883,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="909" spans="1:2" ht="14.4">
+    <row r="909" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A909" s="9" t="s">
         <v>427</v>
       </c>
@@ -8502,7 +8891,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="910" spans="1:2" ht="14.4">
+    <row r="910" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A910" s="10" t="s">
         <v>426</v>
       </c>
@@ -8510,7 +8899,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="911" spans="1:2" ht="14.4">
+    <row r="911" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A911" s="10" t="s">
         <v>425</v>
       </c>
@@ -8518,7 +8907,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="912" spans="1:2" ht="14.4">
+    <row r="912" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A912" s="10" t="s">
         <v>424</v>
       </c>
@@ -8526,7 +8915,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="913" spans="1:2" ht="14.4">
+    <row r="913" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A913" s="10" t="s">
         <v>423</v>
       </c>
@@ -8534,7 +8923,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="914" spans="1:2" ht="14.4">
+    <row r="914" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A914" s="9" t="s">
         <v>422</v>
       </c>
@@ -8542,7 +8931,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="915" spans="1:2" ht="14.4">
+    <row r="915" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A915" s="10" t="s">
         <v>421</v>
       </c>
@@ -8550,7 +8939,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="916" spans="1:2" ht="14.4">
+    <row r="916" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A916" s="10" t="s">
         <v>420</v>
       </c>
@@ -8558,7 +8947,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="917" spans="1:2" ht="14.4">
+    <row r="917" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A917" s="10" t="s">
         <v>419</v>
       </c>
@@ -8566,7 +8955,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="918" spans="1:2" ht="14.4">
+    <row r="918" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A918" s="9" t="s">
         <v>418</v>
       </c>
@@ -8574,7 +8963,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="919" spans="1:2" ht="14.4">
+    <row r="919" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A919" s="10" t="s">
         <v>417</v>
       </c>
@@ -8582,7 +8971,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="920" spans="1:2" ht="14.4">
+    <row r="920" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A920" s="9" t="s">
         <v>416</v>
       </c>
@@ -8590,7 +8979,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="921" spans="1:2" ht="14.4">
+    <row r="921" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A921" s="9" t="s">
         <v>415</v>
       </c>
@@ -8598,7 +8987,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="922" spans="1:2" ht="14.4">
+    <row r="922" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A922" s="9" t="s">
         <v>414</v>
       </c>
@@ -8606,7 +8995,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="923" spans="1:2" ht="14.4">
+    <row r="923" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A923" s="10" t="s">
         <v>413</v>
       </c>
@@ -8614,7 +9003,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="925" spans="1:2" ht="14.4">
+    <row r="925" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A925" s="10" t="s">
         <v>659</v>
       </c>
@@ -8622,7 +9011,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="926" spans="1:2" ht="14.4">
+    <row r="926" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A926" s="9" t="s">
         <v>658</v>
       </c>
@@ -8630,7 +9019,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="927" spans="1:2" ht="14.4">
+    <row r="927" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A927" s="10" t="s">
         <v>657</v>
       </c>
@@ -8638,7 +9027,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="928" spans="1:2" ht="14.4">
+    <row r="928" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A928" s="9" t="s">
         <v>656</v>
       </c>
@@ -8646,7 +9035,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="929" spans="1:2" ht="14.4">
+    <row r="929" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A929" s="9" t="s">
         <v>655</v>
       </c>
@@ -8654,7 +9043,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="930" spans="1:2" ht="14.4">
+    <row r="930" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A930" s="10" t="s">
         <v>654</v>
       </c>
@@ -8662,7 +9051,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="931" spans="1:2" ht="14.4">
+    <row r="931" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A931" s="10" t="s">
         <v>653</v>
       </c>
@@ -8670,7 +9059,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="932" spans="1:2" ht="14.4">
+    <row r="932" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A932" s="9" t="s">
         <v>652</v>
       </c>
@@ -8678,7 +9067,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="933" spans="1:2" ht="14.4">
+    <row r="933" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A933" s="10" t="s">
         <v>651</v>
       </c>
@@ -8686,7 +9075,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="934" spans="1:2" ht="14.4">
+    <row r="934" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A934" s="10" t="s">
         <v>650</v>
       </c>
@@ -8694,7 +9083,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="935" spans="1:2" ht="14.4">
+    <row r="935" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A935" s="9" t="s">
         <v>649</v>
       </c>
@@ -8702,7 +9091,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="936" spans="1:2" ht="14.4">
+    <row r="936" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A936" s="10" t="s">
         <v>648</v>
       </c>
@@ -8710,7 +9099,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="937" spans="1:2" ht="14.4">
+    <row r="937" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A937" s="10" t="s">
         <v>647</v>
       </c>
@@ -8718,7 +9107,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="938" spans="1:2" ht="14.4">
+    <row r="938" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A938" s="10" t="s">
         <v>646</v>
       </c>
@@ -8726,7 +9115,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="939" spans="1:2" ht="14.4">
+    <row r="939" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A939" s="10" t="s">
         <v>645</v>
       </c>
@@ -8734,7 +9123,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="940" spans="1:2" ht="14.4">
+    <row r="940" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A940" s="10" t="s">
         <v>644</v>
       </c>
@@ -8742,7 +9131,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="941" spans="1:2" ht="14.4">
+    <row r="941" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A941" s="9" t="s">
         <v>643</v>
       </c>
@@ -8750,7 +9139,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="942" spans="1:2" ht="14.4">
+    <row r="942" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A942" s="9" t="s">
         <v>642</v>
       </c>
@@ -8758,7 +9147,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="943" spans="1:2" ht="14.4">
+    <row r="943" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A943" s="10" t="s">
         <v>641</v>
       </c>
@@ -8766,7 +9155,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="944" spans="1:2" ht="14.4">
+    <row r="944" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A944" s="10" t="s">
         <v>640</v>
       </c>
@@ -8774,7 +9163,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="945" spans="1:2" ht="14.4">
+    <row r="945" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A945" s="10" t="s">
         <v>639</v>
       </c>
@@ -8782,7 +9171,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="946" spans="1:2" ht="14.4">
+    <row r="946" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A946" s="10" t="s">
         <v>638</v>
       </c>
@@ -8790,7 +9179,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="947" spans="1:2" ht="14.4">
+    <row r="947" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A947" s="9" t="s">
         <v>637</v>
       </c>
@@ -8798,7 +9187,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="948" spans="1:2" ht="14.4">
+    <row r="948" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A948" s="10" t="s">
         <v>636</v>
       </c>
@@ -8806,7 +9195,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="949" spans="1:2" ht="14.4">
+    <row r="949" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A949" s="10" t="s">
         <v>635</v>
       </c>
@@ -8814,7 +9203,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="950" spans="1:2" ht="14.4">
+    <row r="950" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A950" s="10" t="s">
         <v>634</v>
       </c>
@@ -8822,7 +9211,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="951" spans="1:2" ht="14.4">
+    <row r="951" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A951" s="9" t="s">
         <v>633</v>
       </c>
@@ -8830,7 +9219,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="952" spans="1:2" ht="14.4">
+    <row r="952" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A952" s="10" t="s">
         <v>632</v>
       </c>
@@ -8838,7 +9227,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="953" spans="1:2" ht="14.4">
+    <row r="953" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A953" s="10" t="s">
         <v>631</v>
       </c>
@@ -8846,7 +9235,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="954" spans="1:2" ht="14.4">
+    <row r="954" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A954" s="10" t="s">
         <v>630</v>
       </c>
@@ -8854,7 +9243,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="955" spans="1:2" ht="14.4">
+    <row r="955" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A955" s="10" t="s">
         <v>629</v>
       </c>
@@ -8862,7 +9251,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="956" spans="1:2" ht="14.4">
+    <row r="956" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A956" s="10" t="s">
         <v>628</v>
       </c>
@@ -8870,7 +9259,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="957" spans="1:2" ht="14.4">
+    <row r="957" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A957" s="9" t="s">
         <v>627</v>
       </c>
@@ -8878,7 +9267,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="958" spans="1:2" ht="14.4">
+    <row r="958" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A958" s="10" t="s">
         <v>626</v>
       </c>
@@ -8886,7 +9275,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="959" spans="1:2" ht="14.4">
+    <row r="959" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A959" s="10" t="s">
         <v>625</v>
       </c>
@@ -8894,7 +9283,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="960" spans="1:2" ht="14.4">
+    <row r="960" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A960" s="10" t="s">
         <v>624</v>
       </c>
@@ -8902,7 +9291,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="961" spans="1:2" ht="14.4">
+    <row r="961" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A961" s="10" t="s">
         <v>623</v>
       </c>
@@ -8910,7 +9299,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="962" spans="1:2" ht="14.4">
+    <row r="962" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A962" s="10" t="s">
         <v>622</v>
       </c>
@@ -8918,7 +9307,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="963" spans="1:2" ht="14.4">
+    <row r="963" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A963" s="10" t="s">
         <v>621</v>
       </c>
@@ -8926,7 +9315,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="964" spans="1:2" ht="14.4">
+    <row r="964" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A964" s="10" t="s">
         <v>620</v>
       </c>
@@ -8934,7 +9323,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="965" spans="1:2" ht="14.4">
+    <row r="965" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A965" s="10" t="s">
         <v>619</v>
       </c>
@@ -8942,7 +9331,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="966" spans="1:2" ht="14.4">
+    <row r="966" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A966" s="10" t="s">
         <v>618</v>
       </c>
@@ -8950,7 +9339,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="967" spans="1:2" ht="14.4">
+    <row r="967" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A967" s="10" t="s">
         <v>617</v>
       </c>
@@ -8958,7 +9347,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="968" spans="1:2" ht="14.4">
+    <row r="968" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A968" s="10" t="s">
         <v>616</v>
       </c>
@@ -8966,7 +9355,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="969" spans="1:2" ht="14.4">
+    <row r="969" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A969" s="10" t="s">
         <v>615</v>
       </c>
@@ -8974,7 +9363,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="970" spans="1:2" ht="14.4">
+    <row r="970" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A970" s="10" t="s">
         <v>614</v>
       </c>
@@ -8982,7 +9371,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="971" spans="1:2" ht="14.4">
+    <row r="971" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A971" s="10" t="s">
         <v>613</v>
       </c>
@@ -8990,7 +9379,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="972" spans="1:2" ht="14.4">
+    <row r="972" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A972" s="10" t="s">
         <v>612</v>
       </c>
@@ -8998,7 +9387,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="973" spans="1:2" ht="14.4">
+    <row r="973" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A973" s="10" t="s">
         <v>611</v>
       </c>
@@ -9006,7 +9395,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="974" spans="1:2" ht="14.4">
+    <row r="974" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A974" s="10" t="s">
         <v>610</v>
       </c>
@@ -9014,7 +9403,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="975" spans="1:2" ht="14.4">
+    <row r="975" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A975" s="9" t="s">
         <v>609</v>
       </c>
@@ -9022,7 +9411,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="976" spans="1:2" ht="14.4">
+    <row r="976" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A976" s="10" t="s">
         <v>608</v>
       </c>
@@ -9030,7 +9419,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="977" spans="1:4" ht="14.4">
+    <row r="977" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A977" s="10" t="s">
         <v>607</v>
       </c>
@@ -9038,7 +9427,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="978" spans="1:4" ht="14.4">
+    <row r="978" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A978" s="10" t="s">
         <v>606</v>
       </c>
@@ -9049,7 +9438,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="979" spans="1:4" ht="14.4">
+    <row r="979" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A979" s="10" t="s">
         <v>605</v>
       </c>
@@ -9057,7 +9446,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="980" spans="1:4" ht="14.4">
+    <row r="980" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A980" s="10" t="s">
         <v>604</v>
       </c>
@@ -9065,7 +9454,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="981" spans="1:4" ht="14.4">
+    <row r="981" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A981" s="10" t="s">
         <v>603</v>
       </c>
@@ -9073,7 +9462,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="982" spans="1:4" ht="14.4">
+    <row r="982" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A982" s="10" t="s">
         <v>602</v>
       </c>
@@ -9081,7 +9470,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="983" spans="1:4" ht="14.4">
+    <row r="983" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A983" s="10" t="s">
         <v>601</v>
       </c>
@@ -9089,7 +9478,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="985" spans="1:4" ht="14.4">
+    <row r="985" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A985" s="11" t="s">
         <v>662</v>
       </c>
@@ -9097,7 +9486,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="986" spans="1:4" ht="14.4">
+    <row r="986" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A986" s="11" t="s">
         <v>663</v>
       </c>
@@ -9105,7 +9494,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="987" spans="1:4" ht="14.4">
+    <row r="987" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A987" s="12" t="s">
         <v>664</v>
       </c>
@@ -9113,7 +9502,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="988" spans="1:4" ht="14.4">
+    <row r="988" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A988" s="11" t="s">
         <v>665</v>
       </c>
@@ -9121,7 +9510,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="989" spans="1:4" ht="14.4">
+    <row r="989" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A989" s="11" t="s">
         <v>666</v>
       </c>
@@ -9129,7 +9518,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="990" spans="1:4" ht="14.4">
+    <row r="990" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A990" s="12" t="s">
         <v>667</v>
       </c>
@@ -9137,7 +9526,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="991" spans="1:4" ht="14.4">
+    <row r="991" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A991" s="12" t="s">
         <v>668</v>
       </c>
@@ -9145,7 +9534,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="992" spans="1:4" ht="14.4">
+    <row r="992" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A992" s="11" t="s">
         <v>669</v>
       </c>
@@ -9153,7 +9542,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="993" spans="1:2" ht="14.4">
+    <row r="993" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A993" s="12" t="s">
         <v>670</v>
       </c>
@@ -9161,7 +9550,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="994" spans="1:2" ht="14.4">
+    <row r="994" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A994" s="12" t="s">
         <v>671</v>
       </c>
@@ -9169,7 +9558,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="995" spans="1:2" ht="14.4">
+    <row r="995" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A995" s="12" t="s">
         <v>672</v>
       </c>
@@ -9177,7 +9566,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="996" spans="1:2" ht="14.4">
+    <row r="996" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A996" s="11" t="s">
         <v>673</v>
       </c>
@@ -9185,7 +9574,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="997" spans="1:2" ht="14.4">
+    <row r="997" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A997" s="12" t="s">
         <v>674</v>
       </c>
@@ -9193,7 +9582,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="998" spans="1:2" ht="14.4">
+    <row r="998" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A998" s="11" t="s">
         <v>675</v>
       </c>
@@ -9201,7 +9590,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="999" spans="1:2" ht="14.4">
+    <row r="999" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A999" s="11" t="s">
         <v>676</v>
       </c>
@@ -9209,7 +9598,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1000" spans="1:2" ht="14.4">
+    <row r="1000" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1000" s="11" t="s">
         <v>677</v>
       </c>
@@ -9217,7 +9606,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1001" spans="1:2" ht="14.4">
+    <row r="1001" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1001" s="12" t="s">
         <v>678</v>
       </c>
@@ -9225,7 +9614,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1002" spans="1:2" ht="14.4">
+    <row r="1002" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1002" s="11" t="s">
         <v>679</v>
       </c>
@@ -9233,7 +9622,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1003" spans="1:2" ht="14.4">
+    <row r="1003" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1003" s="12" t="s">
         <v>680</v>
       </c>
@@ -9241,7 +9630,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1004" spans="1:2" ht="14.4">
+    <row r="1004" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1004" s="11" t="s">
         <v>681</v>
       </c>
@@ -9249,7 +9638,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1005" spans="1:2" ht="14.4">
+    <row r="1005" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1005" s="12" t="s">
         <v>682</v>
       </c>
@@ -9257,7 +9646,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1006" spans="1:2" ht="14.4">
+    <row r="1006" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1006" s="12" t="s">
         <v>683</v>
       </c>
@@ -9265,7 +9654,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1007" spans="1:2" ht="14.4">
+    <row r="1007" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1007" s="12" t="s">
         <v>684</v>
       </c>
@@ -9273,7 +9662,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1008" spans="1:2" ht="14.4">
+    <row r="1008" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1008" s="11" t="s">
         <v>685</v>
       </c>
@@ -9281,7 +9670,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1009" spans="1:2" ht="14.4">
+    <row r="1009" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1009" s="12" t="s">
         <v>686</v>
       </c>
@@ -9289,7 +9678,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1010" spans="1:2" ht="14.4">
+    <row r="1010" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1010" s="11" t="s">
         <v>687</v>
       </c>
@@ -9297,7 +9686,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1011" spans="1:2" ht="14.4">
+    <row r="1011" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1011" s="12" t="s">
         <v>688</v>
       </c>
@@ -9305,7 +9694,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1012" spans="1:2" ht="14.4">
+    <row r="1012" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1012" s="11" t="s">
         <v>689</v>
       </c>
@@ -9313,7 +9702,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1013" spans="1:2" ht="14.4">
+    <row r="1013" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1013" s="12" t="s">
         <v>690</v>
       </c>
@@ -9321,7 +9710,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1014" spans="1:2" ht="14.4">
+    <row r="1014" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1014" s="12" t="s">
         <v>691</v>
       </c>
@@ -9329,7 +9718,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1015" spans="1:2" ht="14.4">
+    <row r="1015" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1015" s="12" t="s">
         <v>692</v>
       </c>
@@ -9337,7 +9726,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1016" spans="1:2" ht="14.4">
+    <row r="1016" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1016" s="11" t="s">
         <v>693</v>
       </c>
@@ -9345,7 +9734,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1017" spans="1:2" ht="14.4">
+    <row r="1017" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1017" s="12" t="s">
         <v>694</v>
       </c>
@@ -9353,7 +9742,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1018" spans="1:2" ht="14.4">
+    <row r="1018" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1018" s="12" t="s">
         <v>695</v>
       </c>
@@ -9361,7 +9750,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1019" spans="1:2" ht="14.4">
+    <row r="1019" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1019" s="11" t="s">
         <v>696</v>
       </c>
@@ -9369,7 +9758,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1020" spans="1:2" ht="14.4">
+    <row r="1020" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1020" s="11" t="s">
         <v>697</v>
       </c>
@@ -9377,7 +9766,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1021" spans="1:2" ht="14.4">
+    <row r="1021" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1021" s="12" t="s">
         <v>698</v>
       </c>
@@ -9385,7 +9774,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1022" spans="1:2" ht="14.4">
+    <row r="1022" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1022" s="12" t="s">
         <v>699</v>
       </c>
@@ -9393,7 +9782,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1023" spans="1:2" ht="14.4">
+    <row r="1023" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1023" s="11" t="s">
         <v>700</v>
       </c>
@@ -9401,7 +9790,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1024" spans="1:2" ht="14.4">
+    <row r="1024" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1024" s="11" t="s">
         <v>701</v>
       </c>
@@ -9409,7 +9798,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1025" spans="1:2" ht="14.4">
+    <row r="1025" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1025" s="12" t="s">
         <v>702</v>
       </c>
@@ -9417,7 +9806,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1026" spans="1:2" ht="14.4">
+    <row r="1026" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1026" s="12" t="s">
         <v>703</v>
       </c>
@@ -9425,7 +9814,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1027" spans="1:2" ht="14.4">
+    <row r="1027" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1027" s="11" t="s">
         <v>704</v>
       </c>
@@ -9433,7 +9822,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1028" spans="1:2" ht="14.4">
+    <row r="1028" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1028" s="12" t="s">
         <v>705</v>
       </c>
@@ -9441,7 +9830,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1029" spans="1:2" ht="14.4">
+    <row r="1029" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1029" s="12" t="s">
         <v>706</v>
       </c>
@@ -9449,7 +9838,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1030" spans="1:2" ht="14.4">
+    <row r="1030" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1030" s="12" t="s">
         <v>707</v>
       </c>
@@ -9457,7 +9846,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1031" spans="1:2" ht="14.4">
+    <row r="1031" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1031" s="12" t="s">
         <v>708</v>
       </c>
@@ -9465,7 +9854,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1032" spans="1:2" ht="14.4">
+    <row r="1032" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1032" s="12" t="s">
         <v>709</v>
       </c>
@@ -9473,7 +9862,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1033" spans="1:2" ht="14.4">
+    <row r="1033" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1033" s="12" t="s">
         <v>710</v>
       </c>
@@ -9481,7 +9870,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1034" spans="1:2" ht="14.4">
+    <row r="1034" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1034" s="12" t="s">
         <v>711</v>
       </c>
@@ -9489,7 +9878,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1035" spans="1:2" ht="14.4">
+    <row r="1035" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1035" s="12" t="s">
         <v>712</v>
       </c>
@@ -9497,7 +9886,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1036" spans="1:2" ht="14.4">
+    <row r="1036" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1036" s="12" t="s">
         <v>713</v>
       </c>
@@ -9505,7 +9894,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1037" spans="1:2" ht="14.4">
+    <row r="1037" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1037" s="12" t="s">
         <v>714</v>
       </c>
@@ -9513,7 +9902,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1038" spans="1:2" ht="14.4">
+    <row r="1038" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1038" s="11" t="s">
         <v>715</v>
       </c>
@@ -9521,7 +9910,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1039" spans="1:2" ht="14.4">
+    <row r="1039" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1039" s="11" t="s">
         <v>716</v>
       </c>
@@ -9529,7 +9918,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1040" spans="1:2" ht="14.4">
+    <row r="1040" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1040" s="12" t="s">
         <v>717</v>
       </c>
@@ -9537,7 +9926,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1041" spans="1:2" ht="14.4">
+    <row r="1041" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1041" s="12" t="s">
         <v>718</v>
       </c>
@@ -9545,7 +9934,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1042" spans="1:2" ht="14.4">
+    <row r="1042" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1042" s="12" t="s">
         <v>719</v>
       </c>
@@ -9553,7 +9942,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1043" spans="1:2" ht="14.4">
+    <row r="1043" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1043" s="12" t="s">
         <v>720</v>
       </c>
@@ -9561,7 +9950,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1044" spans="1:2" ht="14.4">
+    <row r="1044" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1044" s="12" t="s">
         <v>720</v>
       </c>
@@ -9569,7 +9958,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1045" spans="1:2" ht="14.4">
+    <row r="1045" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1045" s="12" t="s">
         <v>721</v>
       </c>
@@ -9577,7 +9966,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1046" spans="1:2" ht="14.4">
+    <row r="1046" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1046" s="11" t="s">
         <v>722</v>
       </c>
@@ -9585,7 +9974,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1047" spans="1:2" ht="14.4">
+    <row r="1047" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1047" s="12" t="s">
         <v>723</v>
       </c>
@@ -9593,7 +9982,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1048" spans="1:2" ht="14.4">
+    <row r="1048" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1048" s="12" t="s">
         <v>724</v>
       </c>
@@ -9601,7 +9990,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1049" spans="1:2" ht="14.4">
+    <row r="1049" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1049" s="12" t="s">
         <v>725</v>
       </c>
@@ -9609,7 +9998,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1050" spans="1:2" ht="14.4">
+    <row r="1050" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1050" s="12" t="s">
         <v>726</v>
       </c>
@@ -9617,7 +10006,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1051" spans="1:2" ht="14.4">
+    <row r="1051" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1051" s="12" t="s">
         <v>727</v>
       </c>
@@ -9625,7 +10014,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1052" spans="1:2" ht="14.4">
+    <row r="1052" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1052" s="11" t="s">
         <v>728</v>
       </c>
@@ -9633,7 +10022,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1053" spans="1:2" ht="14.4">
+    <row r="1053" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1053" s="12" t="s">
         <v>729</v>
       </c>
@@ -9641,7 +10030,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1054" spans="1:2" ht="14.4">
+    <row r="1054" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1054" s="11" t="s">
         <v>730</v>
       </c>
@@ -9649,7 +10038,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1055" spans="1:2" ht="14.4">
+    <row r="1055" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1055" s="12" t="s">
         <v>731</v>
       </c>
@@ -9657,7 +10046,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1056" spans="1:2" ht="14.4">
+    <row r="1056" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1056" s="12" t="s">
         <v>732</v>
       </c>
@@ -9665,7 +10054,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1057" spans="1:2" ht="14.4">
+    <row r="1057" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1057" s="11" t="s">
         <v>733</v>
       </c>
@@ -9673,7 +10062,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1058" spans="1:2" ht="14.4">
+    <row r="1058" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1058" s="11" t="s">
         <v>734</v>
       </c>
@@ -9681,7 +10070,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1059" spans="1:2" ht="14.4">
+    <row r="1059" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1059" s="12" t="s">
         <v>735</v>
       </c>
@@ -9689,7 +10078,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1060" spans="1:2" ht="14.4">
+    <row r="1060" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1060" s="12" t="s">
         <v>736</v>
       </c>
@@ -9697,7 +10086,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1061" spans="1:2" ht="14.4">
+    <row r="1061" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1061" s="12" t="s">
         <v>737</v>
       </c>
@@ -9705,7 +10094,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1062" spans="1:2" ht="14.4">
+    <row r="1062" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1062" s="11" t="s">
         <v>738</v>
       </c>
@@ -9713,7 +10102,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1063" spans="1:2" ht="14.4">
+    <row r="1063" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1063" s="12" t="s">
         <v>739</v>
       </c>
@@ -9721,7 +10110,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1064" spans="1:2" ht="14.4">
+    <row r="1064" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1064" s="12" t="s">
         <v>740</v>
       </c>
@@ -9729,7 +10118,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1065" spans="1:2" ht="14.4">
+    <row r="1065" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1065" s="11" t="s">
         <v>741</v>
       </c>
@@ -9737,7 +10126,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1066" spans="1:2" ht="14.4">
+    <row r="1066" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1066" s="12" t="s">
         <v>742</v>
       </c>
@@ -9745,7 +10134,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1067" spans="1:2" ht="14.4">
+    <row r="1067" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1067" s="11" t="s">
         <v>743</v>
       </c>
@@ -9753,7 +10142,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1068" spans="1:2" ht="14.4">
+    <row r="1068" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1068" s="11" t="s">
         <v>744</v>
       </c>
@@ -9761,7 +10150,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1069" spans="1:2" ht="14.4">
+    <row r="1069" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1069" s="11" t="s">
         <v>745</v>
       </c>
@@ -9769,7 +10158,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1070" spans="1:2" ht="14.4">
+    <row r="1070" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1070" s="11" t="s">
         <v>746</v>
       </c>
@@ -9777,7 +10166,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1071" spans="1:2" ht="14.4">
+    <row r="1071" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1071" s="11" t="s">
         <v>747</v>
       </c>
@@ -9785,7 +10174,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1072" spans="1:2" ht="14.4">
+    <row r="1072" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1072" s="12" t="s">
         <v>748</v>
       </c>
@@ -9793,7 +10182,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1073" spans="1:2" ht="14.4">
+    <row r="1073" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1073" s="12" t="s">
         <v>708</v>
       </c>
@@ -9801,7 +10190,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="1075" spans="1:2" ht="14.4">
+    <row r="1075" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1075" s="13" t="s">
         <v>750</v>
       </c>
@@ -9809,7 +10198,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1076" spans="1:2" ht="14.4">
+    <row r="1076" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1076" s="14" t="s">
         <v>751</v>
       </c>
@@ -9817,7 +10206,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1077" spans="1:2" ht="14.4">
+    <row r="1077" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1077" s="14" t="s">
         <v>752</v>
       </c>
@@ -9825,7 +10214,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1078" spans="1:2" ht="14.4">
+    <row r="1078" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1078" s="14" t="s">
         <v>753</v>
       </c>
@@ -9833,7 +10222,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1079" spans="1:2" ht="14.4">
+    <row r="1079" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1079" s="14" t="s">
         <v>754</v>
       </c>
@@ -9841,7 +10230,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1080" spans="1:2" ht="14.4">
+    <row r="1080" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1080" s="14" t="s">
         <v>755</v>
       </c>
@@ -9849,7 +10238,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1081" spans="1:2" ht="14.4">
+    <row r="1081" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1081" s="14" t="s">
         <v>756</v>
       </c>
@@ -9857,7 +10246,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1082" spans="1:2" ht="14.4">
+    <row r="1082" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1082" s="13" t="s">
         <v>757</v>
       </c>
@@ -9865,7 +10254,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1083" spans="1:2" ht="14.4">
+    <row r="1083" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1083" s="14" t="s">
         <v>758</v>
       </c>
@@ -9873,7 +10262,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1084" spans="1:2" ht="14.4">
+    <row r="1084" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1084" s="14" t="s">
         <v>759</v>
       </c>
@@ -9881,7 +10270,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1085" spans="1:2" ht="14.4">
+    <row r="1085" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1085" s="14" t="s">
         <v>760</v>
       </c>
@@ -9889,7 +10278,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1086" spans="1:2" ht="14.4">
+    <row r="1086" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1086" s="13" t="s">
         <v>761</v>
       </c>
@@ -9897,7 +10286,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1087" spans="1:2" ht="14.4">
+    <row r="1087" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1087" s="14" t="s">
         <v>762</v>
       </c>
@@ -9905,7 +10294,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1088" spans="1:2" ht="14.4">
+    <row r="1088" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1088" s="14" t="s">
         <v>763</v>
       </c>
@@ -9913,7 +10302,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1089" spans="1:2" ht="14.4">
+    <row r="1089" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1089" s="14" t="s">
         <v>764</v>
       </c>
@@ -9921,7 +10310,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1090" spans="1:2" ht="14.4">
+    <row r="1090" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1090" s="13" t="s">
         <v>765</v>
       </c>
@@ -9929,7 +10318,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1091" spans="1:2" ht="14.4">
+    <row r="1091" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1091" s="14" t="s">
         <v>766</v>
       </c>
@@ -9937,7 +10326,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1092" spans="1:2" ht="14.4">
+    <row r="1092" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1092" s="14" t="s">
         <v>767</v>
       </c>
@@ -9945,7 +10334,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1093" spans="1:2" ht="14.4">
+    <row r="1093" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1093" s="14" t="s">
         <v>768</v>
       </c>
@@ -9953,7 +10342,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1094" spans="1:2" ht="14.4">
+    <row r="1094" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1094" s="14" t="s">
         <v>769</v>
       </c>
@@ -9961,7 +10350,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1095" spans="1:2" ht="14.4">
+    <row r="1095" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1095" s="14" t="s">
         <v>769</v>
       </c>
@@ -9969,7 +10358,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1096" spans="1:2" ht="14.4">
+    <row r="1096" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1096" s="14" t="s">
         <v>770</v>
       </c>
@@ -9977,7 +10366,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1097" spans="1:2" ht="14.4">
+    <row r="1097" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1097" s="14" t="s">
         <v>771</v>
       </c>
@@ -9985,7 +10374,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1098" spans="1:2" ht="14.4">
+    <row r="1098" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1098" s="13" t="s">
         <v>772</v>
       </c>
@@ -9993,7 +10382,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1099" spans="1:2" ht="14.4">
+    <row r="1099" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1099" s="13" t="s">
         <v>773</v>
       </c>
@@ -10001,7 +10390,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1100" spans="1:2" ht="14.4">
+    <row r="1100" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1100" s="14" t="s">
         <v>774</v>
       </c>
@@ -10009,7 +10398,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1101" spans="1:2" ht="14.4">
+    <row r="1101" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1101" s="14" t="s">
         <v>775</v>
       </c>
@@ -10017,7 +10406,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1102" spans="1:2" ht="14.4">
+    <row r="1102" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1102" s="14" t="s">
         <v>776</v>
       </c>
@@ -10025,7 +10414,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1103" spans="1:2" ht="14.4">
+    <row r="1103" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1103" s="13" t="s">
         <v>777</v>
       </c>
@@ -10033,7 +10422,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1104" spans="1:2" ht="14.4">
+    <row r="1104" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1104" s="14" t="s">
         <v>778</v>
       </c>
@@ -10041,7 +10430,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1105" spans="1:2" ht="14.4">
+    <row r="1105" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1105" s="14" t="s">
         <v>779</v>
       </c>
@@ -10049,7 +10438,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1106" spans="1:2" ht="14.4">
+    <row r="1106" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1106" s="14" t="s">
         <v>780</v>
       </c>
@@ -10057,7 +10446,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1107" spans="1:2" ht="14.4">
+    <row r="1107" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1107" s="14" t="s">
         <v>781</v>
       </c>
@@ -10065,7 +10454,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1108" spans="1:2" ht="14.4">
+    <row r="1108" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1108" s="14" t="s">
         <v>782</v>
       </c>
@@ -10073,7 +10462,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1109" spans="1:2" ht="14.4">
+    <row r="1109" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1109" s="13" t="s">
         <v>783</v>
       </c>
@@ -10081,7 +10470,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1110" spans="1:2" ht="14.4">
+    <row r="1110" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1110" s="13" t="s">
         <v>784</v>
       </c>
@@ -10089,7 +10478,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1111" spans="1:2" ht="14.4">
+    <row r="1111" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1111" s="13" t="s">
         <v>785</v>
       </c>
@@ -10097,7 +10486,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1112" spans="1:2" ht="14.4">
+    <row r="1112" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1112" s="14" t="s">
         <v>786</v>
       </c>
@@ -10105,7 +10494,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1113" spans="1:2" ht="14.4">
+    <row r="1113" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1113" s="14" t="s">
         <v>787</v>
       </c>
@@ -10113,7 +10502,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1114" spans="1:2" ht="14.4">
+    <row r="1114" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1114" s="14" t="s">
         <v>788</v>
       </c>
@@ -10121,7 +10510,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1115" spans="1:2" ht="14.4">
+    <row r="1115" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1115" s="14" t="s">
         <v>789</v>
       </c>
@@ -10129,7 +10518,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1116" spans="1:2" ht="14.4">
+    <row r="1116" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1116" s="13" t="s">
         <v>790</v>
       </c>
@@ -10137,7 +10526,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1117" spans="1:2" ht="14.4">
+    <row r="1117" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1117" s="14" t="s">
         <v>791</v>
       </c>
@@ -10145,7 +10534,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1118" spans="1:2" ht="14.4">
+    <row r="1118" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1118" s="13" t="s">
         <v>792</v>
       </c>
@@ -10153,7 +10542,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1119" spans="1:2" ht="14.4">
+    <row r="1119" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1119" s="13" t="s">
         <v>793</v>
       </c>
@@ -10161,7 +10550,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1120" spans="1:2" ht="14.4">
+    <row r="1120" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1120" s="13" t="s">
         <v>794</v>
       </c>
@@ -10169,7 +10558,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1121" spans="1:2" ht="14.4">
+    <row r="1121" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1121" s="14" t="s">
         <v>795</v>
       </c>
@@ -10177,7 +10566,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1122" spans="1:2" ht="14.4">
+    <row r="1122" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1122" s="14" t="s">
         <v>796</v>
       </c>
@@ -10185,7 +10574,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1123" spans="1:2" ht="14.4">
+    <row r="1123" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1123" s="14" t="s">
         <v>797</v>
       </c>
@@ -10193,7 +10582,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1124" spans="1:2" ht="14.4">
+    <row r="1124" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1124" s="13" t="s">
         <v>798</v>
       </c>
@@ -10201,7 +10590,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1125" spans="1:2" ht="14.4">
+    <row r="1125" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1125" s="14" t="s">
         <v>799</v>
       </c>
@@ -10209,7 +10598,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1126" spans="1:2" ht="14.4">
+    <row r="1126" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1126" s="14" t="s">
         <v>800</v>
       </c>
@@ -10217,7 +10606,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1127" spans="1:2" ht="14.4">
+    <row r="1127" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1127" s="14" t="s">
         <v>801</v>
       </c>
@@ -10225,7 +10614,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1128" spans="1:2" ht="14.4">
+    <row r="1128" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1128" s="14" t="s">
         <v>802</v>
       </c>
@@ -10233,7 +10622,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1129" spans="1:2" ht="14.4">
+    <row r="1129" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1129" s="14" t="s">
         <v>803</v>
       </c>
@@ -10241,7 +10630,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1130" spans="1:2" ht="14.4">
+    <row r="1130" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1130" s="13" t="s">
         <v>804</v>
       </c>
@@ -10249,7 +10638,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1131" spans="1:2" ht="14.4">
+    <row r="1131" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1131" s="14" t="s">
         <v>805</v>
       </c>
@@ -10257,7 +10646,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1132" spans="1:2" ht="14.4">
+    <row r="1132" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1132" s="14" t="s">
         <v>806</v>
       </c>
@@ -10265,7 +10654,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1133" spans="1:2" ht="14.4">
+    <row r="1133" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1133" s="14" t="s">
         <v>807</v>
       </c>
@@ -10273,7 +10662,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1134" spans="1:2" ht="14.4">
+    <row r="1134" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1134" s="13" t="s">
         <v>808</v>
       </c>
@@ -10281,7 +10670,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1135" spans="1:2" ht="14.4">
+    <row r="1135" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1135" s="14" t="s">
         <v>809</v>
       </c>
@@ -10289,7 +10678,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1136" spans="1:2" ht="14.4">
+    <row r="1136" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1136" s="13" t="s">
         <v>810</v>
       </c>
@@ -10297,7 +10686,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1137" spans="1:2" ht="14.4">
+    <row r="1137" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1137" s="14" t="s">
         <v>811</v>
       </c>
@@ -10305,7 +10694,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1138" spans="1:2" ht="14.4">
+    <row r="1138" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1138" s="14" t="s">
         <v>812</v>
       </c>
@@ -10313,7 +10702,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1139" spans="1:2" ht="14.4">
+    <row r="1139" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1139" s="13" t="s">
         <v>813</v>
       </c>
@@ -10321,7 +10710,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1140" spans="1:2" ht="14.4">
+    <row r="1140" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1140" s="13" t="s">
         <v>814</v>
       </c>
@@ -10329,7 +10718,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1141" spans="1:2" ht="14.4">
+    <row r="1141" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1141" s="14" t="s">
         <v>815</v>
       </c>
@@ -10337,7 +10726,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1142" spans="1:2" ht="14.4">
+    <row r="1142" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1142" s="14" t="s">
         <v>816</v>
       </c>
@@ -10345,7 +10734,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1143" spans="1:2" ht="14.4">
+    <row r="1143" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1143" s="13" t="s">
         <v>817</v>
       </c>
@@ -10353,7 +10742,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1144" spans="1:2" ht="14.4">
+    <row r="1144" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1144" s="13" t="s">
         <v>818</v>
       </c>
@@ -10361,7 +10750,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1145" spans="1:2" ht="14.4">
+    <row r="1145" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1145" s="14" t="s">
         <v>819</v>
       </c>
@@ -10369,7 +10758,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1146" spans="1:2" ht="14.4">
+    <row r="1146" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1146" s="14" t="s">
         <v>820</v>
       </c>
@@ -10377,7 +10766,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1147" spans="1:2" ht="14.4">
+    <row r="1147" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1147" s="13" t="s">
         <v>821</v>
       </c>
@@ -10385,7 +10774,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1148" spans="1:2" ht="14.4">
+    <row r="1148" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1148" s="13" t="s">
         <v>750</v>
       </c>
@@ -10393,7 +10782,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1149" spans="1:2" ht="14.4">
+    <row r="1149" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1149" s="14" t="s">
         <v>822</v>
       </c>
@@ -10401,7 +10790,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1150" spans="1:2" ht="14.4">
+    <row r="1150" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1150" s="14" t="s">
         <v>823</v>
       </c>
@@ -10409,7 +10798,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="1152" spans="1:2" ht="14.4">
+    <row r="1152" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1152" s="16" t="s">
         <v>825</v>
       </c>
@@ -10417,7 +10806,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1153" spans="1:2" ht="14.4">
+    <row r="1153" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1153" s="16" t="s">
         <v>826</v>
       </c>
@@ -10425,7 +10814,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1154" spans="1:2" ht="14.4">
+    <row r="1154" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1154" s="16" t="s">
         <v>827</v>
       </c>
@@ -10433,7 +10822,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1155" spans="1:2" ht="14.4">
+    <row r="1155" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1155" s="16" t="s">
         <v>828</v>
       </c>
@@ -10441,7 +10830,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1156" spans="1:2" ht="14.4">
+    <row r="1156" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1156" s="16" t="s">
         <v>829</v>
       </c>
@@ -10449,7 +10838,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1157" spans="1:2" ht="14.4">
+    <row r="1157" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1157" s="16" t="s">
         <v>830</v>
       </c>
@@ -10457,7 +10846,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1158" spans="1:2" ht="14.4">
+    <row r="1158" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1158" s="16" t="s">
         <v>831</v>
       </c>
@@ -10465,7 +10854,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1159" spans="1:2" ht="14.4">
+    <row r="1159" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1159" s="15" t="s">
         <v>832</v>
       </c>
@@ -10473,7 +10862,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1160" spans="1:2" ht="14.4">
+    <row r="1160" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1160" s="16" t="s">
         <v>833</v>
       </c>
@@ -10481,7 +10870,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1161" spans="1:2" ht="14.4">
+    <row r="1161" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1161" s="16" t="s">
         <v>834</v>
       </c>
@@ -10489,7 +10878,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1162" spans="1:2" ht="14.4">
+    <row r="1162" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1162" s="16" t="s">
         <v>835</v>
       </c>
@@ -10497,7 +10886,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1163" spans="1:2" ht="14.4">
+    <row r="1163" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1163" s="16" t="s">
         <v>836</v>
       </c>
@@ -10505,7 +10894,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1164" spans="1:2" ht="14.4">
+    <row r="1164" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1164" s="16" t="s">
         <v>837</v>
       </c>
@@ -10513,7 +10902,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1165" spans="1:2" ht="14.4">
+    <row r="1165" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1165" s="16" t="s">
         <v>838</v>
       </c>
@@ -10521,7 +10910,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1166" spans="1:2" ht="14.4">
+    <row r="1166" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1166" s="16" t="s">
         <v>839</v>
       </c>
@@ -10529,7 +10918,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1167" spans="1:2" ht="14.4">
+    <row r="1167" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1167" s="16" t="s">
         <v>840</v>
       </c>
@@ -10537,7 +10926,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1168" spans="1:2" ht="14.4">
+    <row r="1168" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1168" s="16" t="s">
         <v>841</v>
       </c>
@@ -10545,7 +10934,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1169" spans="1:2" ht="14.4">
+    <row r="1169" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1169" s="16" t="s">
         <v>842</v>
       </c>
@@ -10553,7 +10942,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1170" spans="1:2" ht="14.4">
+    <row r="1170" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1170" s="15" t="s">
         <v>843</v>
       </c>
@@ -10561,7 +10950,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1171" spans="1:2" ht="14.4">
+    <row r="1171" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1171" s="15" t="s">
         <v>844</v>
       </c>
@@ -10569,7 +10958,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1172" spans="1:2" ht="14.4">
+    <row r="1172" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1172" s="16" t="s">
         <v>845</v>
       </c>
@@ -10577,7 +10966,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1173" spans="1:2" ht="14.4">
+    <row r="1173" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1173" s="16" t="s">
         <v>846</v>
       </c>
@@ -10585,7 +10974,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1174" spans="1:2" ht="14.4">
+    <row r="1174" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1174" s="15" t="s">
         <v>847</v>
       </c>
@@ -10593,7 +10982,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1175" spans="1:2" ht="14.4">
+    <row r="1175" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1175" s="16" t="s">
         <v>848</v>
       </c>
@@ -10601,7 +10990,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1176" spans="1:2" ht="14.4">
+    <row r="1176" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1176" s="16" t="s">
         <v>849</v>
       </c>
@@ -10609,7 +10998,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1177" spans="1:2" ht="14.4">
+    <row r="1177" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1177" s="16" t="s">
         <v>850</v>
       </c>
@@ -10617,7 +11006,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1178" spans="1:2" ht="14.4">
+    <row r="1178" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1178" s="15" t="s">
         <v>851</v>
       </c>
@@ -10625,7 +11014,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1179" spans="1:2" ht="14.4">
+    <row r="1179" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1179" s="15" t="s">
         <v>852</v>
       </c>
@@ -10633,7 +11022,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1180" spans="1:2" ht="14.4">
+    <row r="1180" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1180" s="16" t="s">
         <v>853</v>
       </c>
@@ -10641,7 +11030,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1181" spans="1:2" ht="14.4">
+    <row r="1181" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1181" s="16" t="s">
         <v>854</v>
       </c>
@@ -10649,7 +11038,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1182" spans="1:2" ht="14.4">
+    <row r="1182" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1182" s="16" t="s">
         <v>855</v>
       </c>
@@ -10657,7 +11046,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1183" spans="1:2" ht="14.4">
+    <row r="1183" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1183" s="16" t="s">
         <v>856</v>
       </c>
@@ -10665,7 +11054,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1184" spans="1:2" ht="14.4">
+    <row r="1184" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1184" s="15" t="s">
         <v>857</v>
       </c>
@@ -10673,7 +11062,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1185" spans="1:2" ht="14.4">
+    <row r="1185" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1185" s="15" t="s">
         <v>858</v>
       </c>
@@ -10681,7 +11070,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1186" spans="1:2" ht="14.4">
+    <row r="1186" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1186" s="15" t="s">
         <v>859</v>
       </c>
@@ -10689,7 +11078,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1187" spans="1:2" ht="14.4">
+    <row r="1187" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1187" s="16" t="s">
         <v>860</v>
       </c>
@@ -10697,7 +11086,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1188" spans="1:2" ht="14.4">
+    <row r="1188" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1188" s="15" t="s">
         <v>861</v>
       </c>
@@ -10705,7 +11094,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1189" spans="1:2" ht="14.4">
+    <row r="1189" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1189" s="15" t="s">
         <v>862</v>
       </c>
@@ -10713,7 +11102,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1190" spans="1:2" ht="14.4">
+    <row r="1190" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1190" s="16" t="s">
         <v>863</v>
       </c>
@@ -10721,7 +11110,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1191" spans="1:2" ht="14.4">
+    <row r="1191" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1191" s="15" t="s">
         <v>864</v>
       </c>
@@ -10729,7 +11118,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1192" spans="1:2" ht="14.4">
+    <row r="1192" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1192" s="16" t="s">
         <v>865</v>
       </c>
@@ -10737,7 +11126,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1193" spans="1:2" ht="14.4">
+    <row r="1193" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1193" s="15" t="s">
         <v>866</v>
       </c>
@@ -10745,7 +11134,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1194" spans="1:2" ht="14.4">
+    <row r="1194" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1194" s="15" t="s">
         <v>867</v>
       </c>
@@ -10753,7 +11142,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1195" spans="1:2" ht="14.4">
+    <row r="1195" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1195" s="16" t="s">
         <v>868</v>
       </c>
@@ -10761,7 +11150,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1196" spans="1:2" ht="14.4">
+    <row r="1196" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1196" s="16" t="s">
         <v>869</v>
       </c>
@@ -10769,7 +11158,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1197" spans="1:2" ht="14.4">
+    <row r="1197" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1197" s="16" t="s">
         <v>870</v>
       </c>
@@ -10777,7 +11166,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1198" spans="1:2" ht="14.4">
+    <row r="1198" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1198" s="16" t="s">
         <v>871</v>
       </c>
@@ -10785,7 +11174,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1199" spans="1:2" ht="14.4">
+    <row r="1199" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1199" s="16" t="s">
         <v>872</v>
       </c>
@@ -10793,7 +11182,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1200" spans="1:2" ht="14.4">
+    <row r="1200" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1200" s="16" t="s">
         <v>873</v>
       </c>
@@ -10801,7 +11190,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1201" spans="1:2" ht="14.4">
+    <row r="1201" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1201" s="16" t="s">
         <v>874</v>
       </c>
@@ -10809,7 +11198,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1202" spans="1:2" ht="14.4">
+    <row r="1202" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1202" s="15" t="s">
         <v>875</v>
       </c>
@@ -10817,7 +11206,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1203" spans="1:2" ht="14.4">
+    <row r="1203" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1203" s="15" t="s">
         <v>876</v>
       </c>
@@ -10825,7 +11214,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1204" spans="1:2" ht="14.4">
+    <row r="1204" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1204" s="16" t="s">
         <v>877</v>
       </c>
@@ -10833,7 +11222,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1205" spans="1:2" ht="14.4">
+    <row r="1205" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1205" s="15" t="s">
         <v>878</v>
       </c>
@@ -10841,7 +11230,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1206" spans="1:2" ht="14.4">
+    <row r="1206" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1206" s="16" t="s">
         <v>879</v>
       </c>
@@ -10849,7 +11238,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1207" spans="1:2" ht="14.4">
+    <row r="1207" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1207" s="16" t="s">
         <v>880</v>
       </c>
@@ -10857,7 +11246,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1208" spans="1:2" ht="14.4">
+    <row r="1208" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1208" s="15" t="s">
         <v>881</v>
       </c>
@@ -10865,7 +11254,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1209" spans="1:2" ht="14.4">
+    <row r="1209" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1209" s="15" t="s">
         <v>882</v>
       </c>
@@ -10873,7 +11262,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1210" spans="1:2" ht="14.4">
+    <row r="1210" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1210" s="16" t="s">
         <v>883</v>
       </c>
@@ -10881,7 +11270,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1211" spans="1:2" ht="14.4">
+    <row r="1211" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1211" s="15" t="s">
         <v>884</v>
       </c>
@@ -10889,7 +11278,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1212" spans="1:2" ht="14.4">
+    <row r="1212" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1212" s="16" t="s">
         <v>885</v>
       </c>
@@ -10897,7 +11286,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1213" spans="1:2" ht="14.4">
+    <row r="1213" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1213" s="15" t="s">
         <v>886</v>
       </c>
@@ -10905,7 +11294,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="1214" spans="1:2" ht="14.4">
+    <row r="1214" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1214" s="16" t="s">
         <v>825</v>
       </c>
@@ -10922,7 +11311,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10931,7 +11320,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/on_the_way.xlsx
+++ b/on_the_way.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1933" uniqueCount="889">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1625" uniqueCount="736">
   <si>
     <t>Track</t>
   </si>
@@ -24,231 +24,6 @@
     <t>465448988108738</t>
   </si>
   <si>
-    <t>79118257588609</t>
-  </si>
-  <si>
-    <t>YT888971825187</t>
-  </si>
-  <si>
-    <t>ＪＤＡＰ０３13258422</t>
-  </si>
-  <si>
-    <t>JDAP0313258422</t>
-  </si>
-  <si>
-    <t>79118367875866</t>
-  </si>
-  <si>
-    <t>777420282036519</t>
-  </si>
-  <si>
-    <t>79118276902896</t>
-  </si>
-  <si>
-    <t>79015519961480</t>
-  </si>
-  <si>
-    <t>79118373286841</t>
-  </si>
-  <si>
-    <t>JT550099745629</t>
-  </si>
-  <si>
-    <t>465474899950488</t>
-  </si>
-  <si>
-    <t>777422956038345</t>
-  </si>
-  <si>
-    <t>9817751764072</t>
-  </si>
-  <si>
-    <t>79118817209091</t>
-  </si>
-  <si>
-    <t>JT550478769131</t>
-  </si>
-  <si>
-    <t>79118138983288</t>
-  </si>
-  <si>
-    <t>ＹＴ８８８812345532</t>
-  </si>
-  <si>
-    <t>YT888812345532</t>
-  </si>
-  <si>
-    <t>79118656662606</t>
-  </si>
-  <si>
-    <t>777423388035728</t>
-  </si>
-  <si>
-    <t>ＹＴ８８８579129738</t>
-  </si>
-  <si>
-    <t>YT888579129738</t>
-  </si>
-  <si>
-    <t>9817758621431</t>
-  </si>
-  <si>
-    <t>YT8883068430782</t>
-  </si>
-  <si>
-    <t>YT888728725446</t>
-  </si>
-  <si>
-    <t>YT8882728725446</t>
-  </si>
-  <si>
-    <t>JT5500919745629</t>
-  </si>
-  <si>
-    <t>79015421313659</t>
-  </si>
-  <si>
-    <t>YT8883016778119</t>
-  </si>
-  <si>
-    <t>777422811535476</t>
-  </si>
-  <si>
-    <t>9817676881239</t>
-  </si>
-  <si>
-    <t>79118554290183</t>
-  </si>
-  <si>
-    <t>777423080271777</t>
-  </si>
-  <si>
-    <t>777422831741276</t>
-  </si>
-  <si>
-    <t>79118644923859</t>
-  </si>
-  <si>
-    <t>79118717367067</t>
-  </si>
-  <si>
-    <t>9817659220150</t>
-  </si>
-  <si>
-    <t>777423193264153</t>
-  </si>
-  <si>
-    <t>79118615476461</t>
-  </si>
-  <si>
-    <t>777423262190233</t>
-  </si>
-  <si>
-    <t>465463953627717</t>
-  </si>
-  <si>
-    <t>79118522980734</t>
-  </si>
-  <si>
-    <t>79118579258190</t>
-  </si>
-  <si>
-    <t>465459643712698</t>
-  </si>
-  <si>
-    <t>465466976923906</t>
-  </si>
-  <si>
-    <t>9817751470985</t>
-  </si>
-  <si>
-    <t>JT3168752156470</t>
-  </si>
-  <si>
-    <t>YT8881866116899</t>
-  </si>
-  <si>
-    <t>79118432746656</t>
-  </si>
-  <si>
-    <t>465468421375906</t>
-  </si>
-  <si>
-    <t>YT8883165794725</t>
-  </si>
-  <si>
-    <t>465467345765080</t>
-  </si>
-  <si>
-    <t>JT5500938255508</t>
-  </si>
-  <si>
-    <t>JT5500670686464</t>
-  </si>
-  <si>
-    <t>465475987318740</t>
-  </si>
-  <si>
-    <t>YT8881966666733</t>
-  </si>
-  <si>
-    <t>777422847337625</t>
-  </si>
-  <si>
-    <t>YT8882001189556</t>
-  </si>
-  <si>
-    <t>JT5500848779222</t>
-  </si>
-  <si>
-    <t>YT8882076042439</t>
-  </si>
-  <si>
-    <t>YT8881950927855</t>
-  </si>
-  <si>
-    <t>777423349497530</t>
-  </si>
-  <si>
-    <t>YT8882024475728</t>
-  </si>
-  <si>
-    <t>79118247028763</t>
-  </si>
-  <si>
-    <t>9817650895696</t>
-  </si>
-  <si>
-    <t>79118249168211</t>
-  </si>
-  <si>
-    <t>465466346707418</t>
-  </si>
-  <si>
-    <t>465467113069181</t>
-  </si>
-  <si>
-    <t>777423445904215</t>
-  </si>
-  <si>
-    <t>9817714904846</t>
-  </si>
-  <si>
-    <t>9817688850817</t>
-  </si>
-  <si>
-    <t>79118141365896</t>
-  </si>
-  <si>
-    <t>JT5501195769597</t>
-  </si>
-  <si>
-    <t>777423146909811</t>
-  </si>
-  <si>
-    <t>777423269005541</t>
-  </si>
-  <si>
     <t>777424220162412</t>
   </si>
   <si>
@@ -555,234 +330,6 @@
     <t>465478836046637</t>
   </si>
   <si>
-    <t>YT8883595470376</t>
-  </si>
-  <si>
-    <t>465475481375138</t>
-  </si>
-  <si>
-    <t>777423955269542</t>
-  </si>
-  <si>
-    <t>79118705036709</t>
-  </si>
-  <si>
-    <t>YT8883410575516</t>
-  </si>
-  <si>
-    <t>9817726965432</t>
-  </si>
-  <si>
-    <t>79119122374228</t>
-  </si>
-  <si>
-    <t>79119161828030</t>
-  </si>
-  <si>
-    <t>777423648422955</t>
-  </si>
-  <si>
-    <t>777423009363641</t>
-  </si>
-  <si>
-    <t>JT5501372942277</t>
-  </si>
-  <si>
-    <t>JT5501532764591</t>
-  </si>
-  <si>
-    <t>777423677128532</t>
-  </si>
-  <si>
-    <t>465472391693106</t>
-  </si>
-  <si>
-    <t>777422996731755</t>
-  </si>
-  <si>
-    <t>JT5501532535801</t>
-  </si>
-  <si>
-    <t>777423745466795</t>
-  </si>
-  <si>
-    <t>777423767375582</t>
-  </si>
-  <si>
-    <t>465472002832188</t>
-  </si>
-  <si>
-    <t>YT8883674598074</t>
-  </si>
-  <si>
-    <t>465471732331470</t>
-  </si>
-  <si>
-    <t>YT8882580605650</t>
-  </si>
-  <si>
-    <t>465472312616126</t>
-  </si>
-  <si>
-    <t>YT8883239639732</t>
-  </si>
-  <si>
-    <t>JT5501302513659</t>
-  </si>
-  <si>
-    <t>777422837209675</t>
-  </si>
-  <si>
-    <t>777424099932425</t>
-  </si>
-  <si>
-    <t>YT8882970307102</t>
-  </si>
-  <si>
-    <t>JT5501077523127</t>
-  </si>
-  <si>
-    <t>9817736381529</t>
-  </si>
-  <si>
-    <t>777423571387306</t>
-  </si>
-  <si>
-    <t>YT8882892016005</t>
-  </si>
-  <si>
-    <t>777424007430464</t>
-  </si>
-  <si>
-    <t>777423875081346</t>
-  </si>
-  <si>
-    <t>465473412612728</t>
-  </si>
-  <si>
-    <t>777423532876975</t>
-  </si>
-  <si>
-    <t>777424092833669</t>
-  </si>
-  <si>
-    <t>YT8883742931987</t>
-  </si>
-  <si>
-    <t>79119299656526</t>
-  </si>
-  <si>
-    <t>9817780091264</t>
-  </si>
-  <si>
-    <t>YT8883626255907</t>
-  </si>
-  <si>
-    <t>465475448112441</t>
-  </si>
-  <si>
-    <t>JT5501299359983</t>
-  </si>
-  <si>
-    <t>79119137632359</t>
-  </si>
-  <si>
-    <t>777424114810896</t>
-  </si>
-  <si>
-    <t>9817653521677</t>
-  </si>
-  <si>
-    <t>777424572515165</t>
-  </si>
-  <si>
-    <t>JT5502597241614</t>
-  </si>
-  <si>
-    <t>79118979425089</t>
-  </si>
-  <si>
-    <t>79118833080186</t>
-  </si>
-  <si>
-    <t>YT8882874480068</t>
-  </si>
-  <si>
-    <t>JT5501535601748</t>
-  </si>
-  <si>
-    <t>9817769911867</t>
-  </si>
-  <si>
-    <t>9817753460786</t>
-  </si>
-  <si>
-    <t>YT8883849849679</t>
-  </si>
-  <si>
-    <t>9817784576370</t>
-  </si>
-  <si>
-    <t>9817605081138</t>
-  </si>
-  <si>
-    <t>YT8883723028714</t>
-  </si>
-  <si>
-    <t>79119050833173</t>
-  </si>
-  <si>
-    <t>79119471430708</t>
-  </si>
-  <si>
-    <t>9817751874305</t>
-  </si>
-  <si>
-    <t>79119089277103</t>
-  </si>
-  <si>
-    <t>9817718946799</t>
-  </si>
-  <si>
-    <t>79119327158321</t>
-  </si>
-  <si>
-    <t>79119040950183</t>
-  </si>
-  <si>
-    <t>YT8883182286722</t>
-  </si>
-  <si>
-    <t>79118908516350</t>
-  </si>
-  <si>
-    <t>465475730266001</t>
-  </si>
-  <si>
-    <t>79119115957783</t>
-  </si>
-  <si>
-    <t>YT8883049444988</t>
-  </si>
-  <si>
-    <t>465460557466698</t>
-  </si>
-  <si>
-    <t>777423791434285</t>
-  </si>
-  <si>
-    <t>777423766456070</t>
-  </si>
-  <si>
-    <t>JT5501371556169</t>
-  </si>
-  <si>
-    <t>465472981439634</t>
-  </si>
-  <si>
-    <t>79118824420191</t>
-  </si>
-  <si>
     <t>YT8884755194668</t>
   </si>
   <si>
@@ -1582,12 +1129,6 @@
   </si>
   <si>
     <t>Date</t>
-  </si>
-  <si>
-    <t>06.07.26</t>
-  </si>
-  <si>
-    <t>08.07.26</t>
   </si>
   <si>
     <t>11.07.26</t>
@@ -3333,1014 +2874,1014 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>521</v>
+        <v>370</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>255</v>
+        <v>104</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>256</v>
+        <v>105</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>257</v>
+        <v>106</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>258</v>
+        <v>107</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>259</v>
+        <v>108</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
-        <v>260</v>
+        <v>109</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
-        <v>261</v>
+        <v>110</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>262</v>
+        <v>111</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
-        <v>263</v>
+        <v>112</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>264</v>
+        <v>113</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>265</v>
+        <v>114</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
-        <v>266</v>
+        <v>115</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
-        <v>267</v>
+        <v>116</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
-        <v>268</v>
+        <v>117</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
-        <v>269</v>
+        <v>118</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
-        <v>270</v>
+        <v>119</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>271</v>
+        <v>120</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
-        <v>272</v>
+        <v>121</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
-        <v>273</v>
+        <v>122</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>274</v>
+        <v>123</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
-        <v>275</v>
+        <v>124</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
-        <v>276</v>
+        <v>125</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="10" t="s">
-        <v>277</v>
+        <v>126</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
-        <v>278</v>
+        <v>127</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
-        <v>279</v>
+        <v>128</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
-        <v>280</v>
+        <v>129</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
-        <v>281</v>
+        <v>130</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
-        <v>282</v>
+        <v>131</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
-        <v>283</v>
+        <v>132</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
-        <v>284</v>
+        <v>133</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
-        <v>285</v>
+        <v>134</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
-        <v>286</v>
+        <v>135</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
-        <v>287</v>
+        <v>136</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
-        <v>288</v>
+        <v>137</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
-        <v>289</v>
+        <v>138</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
-        <v>290</v>
+        <v>139</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
-        <v>291</v>
+        <v>140</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
-        <v>292</v>
+        <v>141</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="10" t="s">
-        <v>293</v>
+        <v>142</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="10" t="s">
-        <v>294</v>
+        <v>143</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="10" t="s">
-        <v>295</v>
+        <v>144</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
-        <v>296</v>
+        <v>145</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
-        <v>297</v>
+        <v>146</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
-        <v>298</v>
+        <v>147</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="10" t="s">
-        <v>299</v>
+        <v>148</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
-        <v>300</v>
+        <v>149</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="10" t="s">
-        <v>301</v>
+        <v>150</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="9" t="s">
-        <v>302</v>
+        <v>151</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="10" t="s">
-        <v>303</v>
+        <v>152</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
-        <v>304</v>
+        <v>153</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="10" t="s">
-        <v>305</v>
+        <v>154</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
-        <v>306</v>
+        <v>155</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="10" t="s">
-        <v>307</v>
+        <v>156</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
-        <v>308</v>
+        <v>157</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
-        <v>309</v>
+        <v>158</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
-        <v>310</v>
+        <v>159</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="10" t="s">
-        <v>311</v>
+        <v>160</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
-        <v>312</v>
+        <v>161</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="10" t="s">
-        <v>313</v>
+        <v>162</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="10" t="s">
-        <v>314</v>
+        <v>163</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="10" t="s">
-        <v>315</v>
+        <v>164</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="63" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="10" t="s">
-        <v>316</v>
+        <v>165</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="64" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
-        <v>317</v>
+        <v>166</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="9" t="s">
-        <v>318</v>
+        <v>167</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="9" t="s">
-        <v>319</v>
+        <v>168</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="67" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="10" t="s">
-        <v>320</v>
+        <v>169</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="9" t="s">
-        <v>321</v>
+        <v>170</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="10" t="s">
-        <v>322</v>
+        <v>171</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="10" t="s">
-        <v>323</v>
+        <v>172</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="10" t="s">
-        <v>324</v>
+        <v>173</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="72" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="9" t="s">
-        <v>325</v>
+        <v>174</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="73" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73" s="9" t="s">
-        <v>326</v>
+        <v>175</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="74" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="9" t="s">
-        <v>327</v>
+        <v>176</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="75" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" s="10" t="s">
-        <v>328</v>
+        <v>177</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76" s="9" t="s">
-        <v>329</v>
+        <v>178</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="9" t="s">
-        <v>330</v>
+        <v>179</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="78" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="10" t="s">
-        <v>331</v>
+        <v>180</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="79" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" s="10" t="s">
-        <v>332</v>
+        <v>181</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="80" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" s="10" t="s">
-        <v>333</v>
+        <v>182</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A81" s="9" t="s">
-        <v>334</v>
+        <v>183</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A82" s="10" t="s">
-        <v>335</v>
+        <v>184</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A83" s="10" t="s">
-        <v>336</v>
+        <v>185</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D83"/>
     </row>
     <row r="84" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A84" s="10" t="s">
-        <v>337</v>
+        <v>186</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D84"/>
     </row>
     <row r="85" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A85" s="10" t="s">
-        <v>338</v>
+        <v>187</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D85"/>
     </row>
     <row r="86" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" s="9" t="s">
-        <v>339</v>
+        <v>188</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D86"/>
     </row>
     <row r="87" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A87" s="9" t="s">
-        <v>340</v>
+        <v>189</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D87"/>
     </row>
     <row r="88" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A88" s="10" t="s">
-        <v>341</v>
+        <v>190</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D88"/>
     </row>
     <row r="89" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A89" s="9" t="s">
-        <v>342</v>
+        <v>191</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D89"/>
     </row>
     <row r="90" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A90" s="10" t="s">
-        <v>343</v>
+        <v>192</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D90"/>
     </row>
     <row r="91" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A91" s="10" t="s">
-        <v>344</v>
+        <v>193</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D91"/>
     </row>
     <row r="92" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A92" s="10" t="s">
-        <v>345</v>
+        <v>194</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D92"/>
     </row>
     <row r="93" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A93" s="10" t="s">
-        <v>346</v>
+        <v>195</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D93"/>
     </row>
     <row r="94" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A94" s="10" t="s">
-        <v>347</v>
+        <v>196</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D94"/>
     </row>
     <row r="95" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A95" s="10" t="s">
-        <v>348</v>
+        <v>197</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D95"/>
     </row>
     <row r="96" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A96" s="10" t="s">
-        <v>349</v>
+        <v>198</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D96"/>
     </row>
     <row r="97" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A97" s="9" t="s">
-        <v>350</v>
+        <v>199</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D97"/>
     </row>
     <row r="98" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A98" s="10" t="s">
-        <v>351</v>
+        <v>200</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D98"/>
     </row>
     <row r="99" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A99" s="10" t="s">
-        <v>352</v>
+        <v>201</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D99"/>
     </row>
     <row r="100" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A100" s="10" t="s">
-        <v>353</v>
+        <v>202</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D100"/>
     </row>
     <row r="101" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A101" s="10" t="s">
-        <v>354</v>
+        <v>203</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D101"/>
     </row>
     <row r="102" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A102" s="10" t="s">
-        <v>355</v>
+        <v>204</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D102"/>
     </row>
     <row r="103" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A103" s="10" t="s">
-        <v>356</v>
+        <v>205</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D103"/>
     </row>
     <row r="104" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A104" s="9" t="s">
-        <v>357</v>
+        <v>206</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D104"/>
     </row>
     <row r="105" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A105" s="10" t="s">
-        <v>358</v>
+        <v>207</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D105"/>
     </row>
     <row r="106" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A106" s="10" t="s">
-        <v>359</v>
+        <v>208</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D106"/>
     </row>
     <row r="107" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A107" s="10" t="s">
-        <v>360</v>
+        <v>209</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D107"/>
     </row>
     <row r="108" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A108" s="10" t="s">
-        <v>361</v>
+        <v>210</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D108"/>
     </row>
     <row r="109" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A109" s="10" t="s">
-        <v>362</v>
+        <v>211</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D109"/>
     </row>
     <row r="110" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A110" s="10" t="s">
-        <v>363</v>
+        <v>212</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D110"/>
     </row>
     <row r="111" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A111" s="9" t="s">
-        <v>364</v>
+        <v>213</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D111"/>
     </row>
     <row r="112" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A112" s="10" t="s">
-        <v>365</v>
+        <v>214</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D112"/>
     </row>
     <row r="113" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A113" s="10" t="s">
-        <v>366</v>
+        <v>215</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D113"/>
     </row>
     <row r="114" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A114" s="10" t="s">
-        <v>367</v>
+        <v>216</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D114"/>
     </row>
     <row r="115" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A115" s="10" t="s">
-        <v>368</v>
+        <v>217</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D115"/>
     </row>
     <row r="116" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A116" s="10" t="s">
-        <v>369</v>
+        <v>218</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D116"/>
     </row>
     <row r="117" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A117" s="10" t="s">
-        <v>370</v>
+        <v>219</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D117"/>
     </row>
     <row r="118" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A118" s="10" t="s">
-        <v>371</v>
+        <v>220</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D118"/>
     </row>
     <row r="119" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A119" s="10" t="s">
-        <v>372</v>
+        <v>221</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D119"/>
     </row>
     <row r="120" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A120" s="10" t="s">
-        <v>373</v>
+        <v>222</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D120"/>
     </row>
     <row r="121" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A121" s="10" t="s">
-        <v>374</v>
+        <v>223</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D121"/>
     </row>
     <row r="122" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A122" s="10" t="s">
-        <v>257</v>
+        <v>106</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>520</v>
+        <v>369</v>
       </c>
       <c r="D122"/>
     </row>
@@ -4350,615 +3891,615 @@
     </row>
     <row r="124" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A124" s="15" t="s">
-        <v>750</v>
+        <v>597</v>
       </c>
       <c r="B124" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
       <c r="D124"/>
     </row>
     <row r="125" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A125" s="16" t="s">
-        <v>751</v>
+        <v>598</v>
       </c>
       <c r="B125" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
       <c r="D125"/>
     </row>
     <row r="126" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A126" s="16" t="s">
-        <v>752</v>
+        <v>599</v>
       </c>
       <c r="B126" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
       <c r="D126"/>
     </row>
     <row r="127" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A127" s="16" t="s">
-        <v>753</v>
+        <v>600</v>
       </c>
       <c r="B127" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
       <c r="D127"/>
     </row>
     <row r="128" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A128" s="16" t="s">
-        <v>754</v>
+        <v>601</v>
       </c>
       <c r="B128" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
       <c r="D128"/>
     </row>
     <row r="129" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A129" s="16" t="s">
-        <v>755</v>
+        <v>602</v>
       </c>
       <c r="B129" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="130" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A130" s="16" t="s">
-        <v>756</v>
+        <v>603</v>
       </c>
       <c r="B130" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="131" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A131" s="15" t="s">
-        <v>757</v>
+        <v>604</v>
       </c>
       <c r="B131" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="132" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A132" s="16" t="s">
-        <v>758</v>
+        <v>605</v>
       </c>
       <c r="B132" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="133" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A133" s="16" t="s">
-        <v>759</v>
+        <v>606</v>
       </c>
       <c r="B133" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="134" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A134" s="16" t="s">
-        <v>760</v>
+        <v>607</v>
       </c>
       <c r="B134" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="135" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A135" s="15" t="s">
-        <v>761</v>
+        <v>608</v>
       </c>
       <c r="B135" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="136" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A136" s="16" t="s">
-        <v>762</v>
+        <v>609</v>
       </c>
       <c r="B136" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="137" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A137" s="16" t="s">
-        <v>763</v>
+        <v>610</v>
       </c>
       <c r="B137" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="138" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A138" s="16" t="s">
-        <v>764</v>
+        <v>611</v>
       </c>
       <c r="B138" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="139" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A139" s="15" t="s">
-        <v>765</v>
+        <v>612</v>
       </c>
       <c r="B139" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="140" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A140" s="16" t="s">
-        <v>766</v>
+        <v>613</v>
       </c>
       <c r="B140" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="141" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A141" s="16" t="s">
-        <v>767</v>
+        <v>614</v>
       </c>
       <c r="B141" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="142" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A142" s="16" t="s">
-        <v>768</v>
+        <v>615</v>
       </c>
       <c r="B142" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="143" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A143" s="16" t="s">
-        <v>769</v>
+        <v>616</v>
       </c>
       <c r="B143" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="144" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A144" s="16" t="s">
-        <v>769</v>
+        <v>616</v>
       </c>
       <c r="B144" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="145" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A145" s="16" t="s">
-        <v>770</v>
+        <v>617</v>
       </c>
       <c r="B145" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="146" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A146" s="16" t="s">
-        <v>771</v>
+        <v>618</v>
       </c>
       <c r="B146" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="147" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A147" s="15" t="s">
-        <v>772</v>
+        <v>619</v>
       </c>
       <c r="B147" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="148" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A148" s="15" t="s">
-        <v>773</v>
+        <v>620</v>
       </c>
       <c r="B148" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="149" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A149" s="16" t="s">
-        <v>774</v>
+        <v>621</v>
       </c>
       <c r="B149" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="150" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A150" s="16" t="s">
-        <v>775</v>
+        <v>622</v>
       </c>
       <c r="B150" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="151" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A151" s="16" t="s">
-        <v>776</v>
+        <v>623</v>
       </c>
       <c r="B151" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="152" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A152" s="15" t="s">
-        <v>777</v>
+        <v>624</v>
       </c>
       <c r="B152" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="153" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A153" s="16" t="s">
-        <v>778</v>
+        <v>625</v>
       </c>
       <c r="B153" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="154" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A154" s="16" t="s">
-        <v>779</v>
+        <v>626</v>
       </c>
       <c r="B154" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="155" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A155" s="16" t="s">
-        <v>780</v>
+        <v>627</v>
       </c>
       <c r="B155" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="156" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A156" s="16" t="s">
-        <v>781</v>
+        <v>628</v>
       </c>
       <c r="B156" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="157" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A157" s="16" t="s">
-        <v>782</v>
+        <v>629</v>
       </c>
       <c r="B157" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="158" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A158" s="15" t="s">
-        <v>783</v>
+        <v>630</v>
       </c>
       <c r="B158" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="159" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A159" s="15" t="s">
-        <v>784</v>
+        <v>631</v>
       </c>
       <c r="B159" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="160" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A160" s="15" t="s">
-        <v>785</v>
+        <v>632</v>
       </c>
       <c r="B160" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="161" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A161" s="16" t="s">
-        <v>786</v>
+        <v>633</v>
       </c>
       <c r="B161" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="162" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A162" s="16" t="s">
-        <v>787</v>
+        <v>634</v>
       </c>
       <c r="B162" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="163" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A163" s="16" t="s">
-        <v>788</v>
+        <v>635</v>
       </c>
       <c r="B163" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="164" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A164" s="16" t="s">
-        <v>789</v>
+        <v>636</v>
       </c>
       <c r="B164" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="165" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A165" s="15" t="s">
-        <v>790</v>
+        <v>637</v>
       </c>
       <c r="B165" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="166" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A166" s="16" t="s">
-        <v>791</v>
+        <v>638</v>
       </c>
       <c r="B166" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="167" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A167" s="15" t="s">
-        <v>792</v>
+        <v>639</v>
       </c>
       <c r="B167" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="168" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A168" s="15" t="s">
-        <v>793</v>
+        <v>640</v>
       </c>
       <c r="B168" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="169" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A169" s="15" t="s">
-        <v>794</v>
+        <v>641</v>
       </c>
       <c r="B169" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="170" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A170" s="16" t="s">
-        <v>795</v>
+        <v>642</v>
       </c>
       <c r="B170" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="171" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A171" s="16" t="s">
-        <v>796</v>
+        <v>643</v>
       </c>
       <c r="B171" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="172" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A172" s="16" t="s">
-        <v>797</v>
+        <v>644</v>
       </c>
       <c r="B172" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="173" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A173" s="15" t="s">
-        <v>798</v>
+        <v>645</v>
       </c>
       <c r="B173" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="174" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A174" s="16" t="s">
-        <v>799</v>
+        <v>646</v>
       </c>
       <c r="B174" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="175" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A175" s="16" t="s">
-        <v>800</v>
+        <v>647</v>
       </c>
       <c r="B175" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="176" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A176" s="16" t="s">
-        <v>801</v>
+        <v>648</v>
       </c>
       <c r="B176" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="177" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A177" s="16" t="s">
-        <v>802</v>
+        <v>649</v>
       </c>
       <c r="B177" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="178" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A178" s="16" t="s">
-        <v>803</v>
+        <v>650</v>
       </c>
       <c r="B178" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="179" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A179" s="15" t="s">
-        <v>804</v>
+        <v>651</v>
       </c>
       <c r="B179" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="180" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A180" s="16" t="s">
-        <v>805</v>
+        <v>652</v>
       </c>
       <c r="B180" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="181" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A181" s="16" t="s">
-        <v>806</v>
+        <v>653</v>
       </c>
       <c r="B181" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="182" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A182" s="16" t="s">
-        <v>807</v>
+        <v>654</v>
       </c>
       <c r="B182" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="183" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A183" s="15" t="s">
-        <v>808</v>
+        <v>655</v>
       </c>
       <c r="B183" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="184" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A184" s="16" t="s">
-        <v>809</v>
+        <v>656</v>
       </c>
       <c r="B184" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="185" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A185" s="15" t="s">
-        <v>810</v>
+        <v>657</v>
       </c>
       <c r="B185" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="186" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A186" s="16" t="s">
-        <v>811</v>
+        <v>658</v>
       </c>
       <c r="B186" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="187" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A187" s="16" t="s">
-        <v>812</v>
+        <v>659</v>
       </c>
       <c r="B187" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="188" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A188" s="15" t="s">
-        <v>813</v>
+        <v>660</v>
       </c>
       <c r="B188" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="189" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A189" s="15" t="s">
-        <v>814</v>
+        <v>661</v>
       </c>
       <c r="B189" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="190" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A190" s="16" t="s">
-        <v>815</v>
+        <v>662</v>
       </c>
       <c r="B190" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="191" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A191" s="16" t="s">
-        <v>816</v>
+        <v>663</v>
       </c>
       <c r="B191" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="192" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A192" s="15" t="s">
-        <v>817</v>
+        <v>664</v>
       </c>
       <c r="B192" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="193" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A193" s="15" t="s">
-        <v>818</v>
+        <v>665</v>
       </c>
       <c r="B193" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="194" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A194" s="16" t="s">
-        <v>819</v>
+        <v>666</v>
       </c>
       <c r="B194" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="195" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A195" s="16" t="s">
-        <v>820</v>
+        <v>667</v>
       </c>
       <c r="B195" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="196" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A196" s="15" t="s">
-        <v>821</v>
+        <v>668</v>
       </c>
       <c r="B196" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="197" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A197" s="15" t="s">
-        <v>750</v>
+        <v>597</v>
       </c>
       <c r="B197" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="198" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A198" s="16" t="s">
-        <v>822</v>
+        <v>669</v>
       </c>
       <c r="B198" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="199" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A199" s="16" t="s">
-        <v>823</v>
+        <v>670</v>
       </c>
       <c r="B199" s="17" t="s">
-        <v>888</v>
+        <v>735</v>
       </c>
     </row>
     <row r="200" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
@@ -5143,1228 +4684,604 @@
     <row r="259" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A259" s="3"/>
     </row>
-    <row r="436" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A436" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="B436" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="437" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A437" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B437" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="438" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A438" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B438" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="439" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A439" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B439" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="440" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A440" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B440" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="441" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A441" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B441" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="442" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A442" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B442" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="443" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A443" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B443" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="444" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A444" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B444" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="445" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A445" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B445" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="446" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A446" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B446" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="447" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A447" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B447" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="448" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A448" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B448" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="449" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A449" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B449" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="450" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A450" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B450" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="451" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A451" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B451" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="452" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A452" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B452" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="453" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A453" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B453" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="454" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A454" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B454" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="455" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A455" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B455" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="456" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A456" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B456" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="457" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A457" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B457" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="458" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A458" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B458" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="459" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A459" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B459" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="460" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A460" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B460" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="461" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A461" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B461" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="462" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A462" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B462" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="463" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A463" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B463" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="464" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A464" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B464" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="465" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A465" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B465" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="466" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A466" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B466" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="467" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A467" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B467" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="468" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A468" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B468" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="469" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A469" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B469" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="470" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A470" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B470" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="471" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A471" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B471" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="472" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A472" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B472" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="473" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A473" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B473" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="474" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A474" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B474" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="475" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A475" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B475" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="476" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A476" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B476" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="477" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A477" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B477" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="478" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A478" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="B478" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="479" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A479" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="B479" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="480" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A480" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B480" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="481" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A481" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B481" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="482" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A482" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B482" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="483" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A483" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="B483" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="484" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A484" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B484" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="485" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A485" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B485" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="486" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A486" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="B486" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="487" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A487" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="B487" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="488" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A488" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B488" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="489" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A489" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="B489" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="490" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A490" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="B490" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="491" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A491" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B491" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="492" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A492" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="B492" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="493" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A493" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B493" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="494" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A494" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="B494" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="495" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A495" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B495" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="496" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A496" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="B496" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="497" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A497" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B497" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="498" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A498" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B498" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="499" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A499" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="B499" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="500" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A500" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B500" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="501" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A501" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B501" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="502" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A502" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="B502" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="503" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A503" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="B503" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="504" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A504" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="B504" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="505" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A505" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="B505" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="506" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A506" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B506" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="507" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A507" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="B507" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="508" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A508" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="B508" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="509" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A509" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="B509" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="510" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A510" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="B510" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="511" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A511" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="B511" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="512" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A512" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="B512" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="513" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A513" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B513" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
     <row r="515" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A515" s="10" t="s">
-        <v>599</v>
+        <v>446</v>
       </c>
       <c r="B515" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="516" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A516" s="9" t="s">
-        <v>598</v>
+        <v>445</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="517" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A517" s="9" t="s">
-        <v>597</v>
+        <v>444</v>
       </c>
       <c r="B517" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="518" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A518" s="10" t="s">
-        <v>596</v>
+        <v>443</v>
       </c>
       <c r="B518" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="519" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A519" s="9" t="s">
-        <v>595</v>
+        <v>442</v>
       </c>
       <c r="B519" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="520" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A520" s="10" t="s">
-        <v>594</v>
+        <v>441</v>
       </c>
       <c r="B520" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="521" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A521" s="10" t="s">
-        <v>593</v>
+        <v>440</v>
       </c>
       <c r="B521" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="522" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A522" s="10" t="s">
-        <v>592</v>
+        <v>439</v>
       </c>
       <c r="B522" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="523" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A523" s="9" t="s">
-        <v>591</v>
+        <v>438</v>
       </c>
       <c r="B523" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="524" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A524" s="9" t="s">
-        <v>590</v>
+        <v>437</v>
       </c>
       <c r="B524" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="525" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A525" s="10" t="s">
-        <v>589</v>
+        <v>436</v>
       </c>
       <c r="B525" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="526" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A526" s="10" t="s">
-        <v>588</v>
+        <v>435</v>
       </c>
       <c r="B526" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="527" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A527" s="10" t="s">
-        <v>587</v>
+        <v>434</v>
       </c>
       <c r="B527" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="528" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A528" s="10" t="s">
-        <v>586</v>
+        <v>433</v>
       </c>
       <c r="B528" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="529" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A529" s="10" t="s">
-        <v>585</v>
+        <v>432</v>
       </c>
       <c r="B529" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="530" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A530" s="9" t="s">
-        <v>584</v>
+        <v>431</v>
       </c>
       <c r="B530" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="531" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A531" s="10" t="s">
-        <v>583</v>
+        <v>430</v>
       </c>
       <c r="B531" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="532" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A532" s="10" t="s">
-        <v>582</v>
+        <v>429</v>
       </c>
       <c r="B532" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="533" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A533" s="10" t="s">
-        <v>581</v>
+        <v>428</v>
       </c>
       <c r="B533" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="534" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A534" s="10" t="s">
-        <v>580</v>
+        <v>427</v>
       </c>
       <c r="B534" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="535" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A535" s="9" t="s">
-        <v>579</v>
+        <v>426</v>
       </c>
       <c r="B535" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="536" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A536" s="9" t="s">
-        <v>578</v>
+        <v>425</v>
       </c>
       <c r="B536" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="537" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A537" s="10" t="s">
-        <v>577</v>
+        <v>424</v>
       </c>
       <c r="B537" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="538" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A538" s="9" t="s">
-        <v>576</v>
+        <v>423</v>
       </c>
       <c r="B538" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="539" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A539" s="9" t="s">
-        <v>575</v>
+        <v>422</v>
       </c>
       <c r="B539" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="540" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A540" s="9" t="s">
-        <v>574</v>
+        <v>421</v>
       </c>
       <c r="B540" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="541" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A541" s="9" t="s">
-        <v>573</v>
+        <v>420</v>
       </c>
       <c r="B541" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="542" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A542" s="10" t="s">
-        <v>572</v>
+        <v>419</v>
       </c>
       <c r="B542" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="543" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A543" s="10" t="s">
-        <v>571</v>
+        <v>418</v>
       </c>
       <c r="B543" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="544" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A544" s="9" t="s">
-        <v>570</v>
+        <v>417</v>
       </c>
       <c r="B544" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="545" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A545" s="10" t="s">
-        <v>569</v>
+        <v>416</v>
       </c>
       <c r="B545" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="546" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A546" s="10" t="s">
-        <v>568</v>
+        <v>415</v>
       </c>
       <c r="B546" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="547" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A547" s="9" t="s">
-        <v>543</v>
+        <v>390</v>
       </c>
       <c r="B547" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="548" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A548" s="9" t="s">
-        <v>567</v>
+        <v>414</v>
       </c>
       <c r="B548" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="549" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A549" s="10" t="s">
-        <v>566</v>
+        <v>413</v>
       </c>
       <c r="B549" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="550" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A550" s="9" t="s">
-        <v>565</v>
+        <v>412</v>
       </c>
       <c r="B550" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="551" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A551" s="10" t="s">
-        <v>564</v>
+        <v>411</v>
       </c>
       <c r="B551" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="552" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A552" s="9" t="s">
-        <v>563</v>
+        <v>410</v>
       </c>
       <c r="B552" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="553" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A553" s="9" t="s">
-        <v>562</v>
+        <v>409</v>
       </c>
       <c r="B553" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="554" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A554" s="10" t="s">
-        <v>561</v>
+        <v>408</v>
       </c>
       <c r="B554" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="555" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A555" s="9" t="s">
-        <v>560</v>
+        <v>407</v>
       </c>
       <c r="B555" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="556" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A556" s="10" t="s">
-        <v>559</v>
+        <v>406</v>
       </c>
       <c r="B556" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="557" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A557" s="10" t="s">
-        <v>558</v>
+        <v>405</v>
       </c>
       <c r="B557" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="558" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A558" s="9" t="s">
-        <v>557</v>
+        <v>404</v>
       </c>
       <c r="B558" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="559" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A559" s="9" t="s">
-        <v>556</v>
+        <v>403</v>
       </c>
       <c r="B559" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="560" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A560" s="9" t="s">
-        <v>555</v>
+        <v>402</v>
       </c>
       <c r="B560" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="561" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A561" s="10" t="s">
-        <v>554</v>
+        <v>401</v>
       </c>
       <c r="B561" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="562" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A562" s="9" t="s">
-        <v>553</v>
+        <v>400</v>
       </c>
       <c r="B562" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="563" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A563" s="9" t="s">
-        <v>552</v>
+        <v>399</v>
       </c>
       <c r="B563" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="564" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A564" s="9" t="s">
-        <v>551</v>
+        <v>398</v>
       </c>
       <c r="B564" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="565" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A565" s="9" t="s">
-        <v>550</v>
+        <v>397</v>
       </c>
       <c r="B565" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="566" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A566" s="10" t="s">
-        <v>549</v>
+        <v>396</v>
       </c>
       <c r="B566" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="567" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A567" s="10" t="s">
-        <v>548</v>
+        <v>395</v>
       </c>
       <c r="B567" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="568" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A568" s="10" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="B568" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="569" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A569" s="10" t="s">
-        <v>546</v>
+        <v>393</v>
       </c>
       <c r="B569" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="570" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A570" s="9" t="s">
-        <v>545</v>
+        <v>392</v>
       </c>
       <c r="B570" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="571" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A571" s="10" t="s">
-        <v>544</v>
+        <v>391</v>
       </c>
       <c r="B571" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="572" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A572" s="9" t="s">
-        <v>543</v>
+        <v>390</v>
       </c>
       <c r="B572" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="573" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A573" s="10" t="s">
-        <v>542</v>
+        <v>389</v>
       </c>
       <c r="B573" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="574" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A574" s="10" t="s">
-        <v>541</v>
+        <v>388</v>
       </c>
       <c r="B574" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="575" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A575" s="10" t="s">
-        <v>540</v>
+        <v>387</v>
       </c>
       <c r="B575" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="576" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A576" s="9" t="s">
-        <v>539</v>
+        <v>386</v>
       </c>
       <c r="B576" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="577" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A577" s="10" t="s">
-        <v>538</v>
+        <v>385</v>
       </c>
       <c r="B577" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="578" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A578" s="9" t="s">
-        <v>537</v>
+        <v>384</v>
       </c>
       <c r="B578" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="579" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A579" s="10" t="s">
-        <v>536</v>
+        <v>383</v>
       </c>
       <c r="B579" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="580" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A580" s="10" t="s">
-        <v>535</v>
+        <v>382</v>
       </c>
       <c r="B580" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="581" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A581" s="10" t="s">
-        <v>534</v>
+        <v>381</v>
       </c>
       <c r="B581" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="582" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A582" s="9" t="s">
-        <v>533</v>
+        <v>380</v>
       </c>
       <c r="B582" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="583" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A583" s="10" t="s">
-        <v>532</v>
+        <v>379</v>
       </c>
       <c r="B583" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="584" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A584" s="10" t="s">
-        <v>531</v>
+        <v>378</v>
       </c>
       <c r="B584" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="585" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A585" s="10" t="s">
-        <v>530</v>
+        <v>377</v>
       </c>
       <c r="B585" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="586" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A586" s="10" t="s">
-        <v>529</v>
+        <v>376</v>
       </c>
       <c r="B586" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="587" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A587" s="10" t="s">
-        <v>528</v>
+        <v>375</v>
       </c>
       <c r="B587" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="588" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A588" s="9" t="s">
-        <v>527</v>
+        <v>374</v>
       </c>
       <c r="B588" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="589" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A589" s="10" t="s">
-        <v>526</v>
+        <v>373</v>
       </c>
       <c r="B589" s="1" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="590" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
@@ -6376,1447 +5293,839 @@
     <row r="592" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A592" s="10"/>
     </row>
-    <row r="593" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A593" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="B593" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="594" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A594" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="B594" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="595" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A595" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="B595" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="596" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A596" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="B596" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="597" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A597" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="B597" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="598" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A598" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="B598" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="599" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A599" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="B599" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="600" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A600" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="B600" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="601" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A601" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="B601" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="602" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A602" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="B602" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="603" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A603" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="B603" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="604" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A604" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="B604" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="605" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A605" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="B605" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="606" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A606" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="B606" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="607" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A607" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="B607" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="608" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A608" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="B608" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="609" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A609" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="B609" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="610" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A610" s="10" t="s">
-        <v>237</v>
-      </c>
-      <c r="B610" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="611" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A611" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="B611" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="612" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A612" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="B612" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="613" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A613" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="B613" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="614" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A614" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="B614" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="615" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A615" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="B615" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="616" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A616" s="10" t="s">
-        <v>231</v>
-      </c>
-      <c r="B616" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="617" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A617" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="B617" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="618" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A618" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="B618" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="619" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A619" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="B619" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="620" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A620" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="B620" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="621" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A621" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="B621" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="622" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A622" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="B622" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="623" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A623" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="B623" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="624" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A624" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="B624" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="625" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A625" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="B625" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="626" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A626" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="B626" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="627" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A627" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="B627" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="628" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A628" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B628" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="629" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A629" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="B629" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="630" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A630" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="B630" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="631" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A631" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="B631" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="632" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A632" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="B632" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="633" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A633" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="B633" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="634" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A634" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="B634" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="635" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A635" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="B635" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="636" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A636" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="B636" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="637" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A637" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="B637" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="638" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A638" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="B638" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="639" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A639" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="B639" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="640" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A640" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="B640" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="641" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A641" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="B641" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="642" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A642" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="B642" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="643" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A643" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="B643" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="644" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A644" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="B644" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="645" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A645" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="B645" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="646" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A646" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="B646" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="647" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A647" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="B647" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="648" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A648" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="B648" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="649" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A649" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="B649" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="650" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A650" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="B650" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="651" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A651" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="B651" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="652" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A652" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="B652" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="653" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A653" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="B653" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="654" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A654" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="B654" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="655" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A655" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="B655" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="656" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A656" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="B656" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="657" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A657" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="B657" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="658" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A658" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="B658" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="659" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A659" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="B659" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="660" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A660" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="B660" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="661" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A661" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="B661" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="662" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A662" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="B662" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="663" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A663" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="B663" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="664" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A664" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="B664" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="665" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A665" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="B665" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="666" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A666" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="B666" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="667" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A667" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="B667" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="668" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A668" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="B668" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
     <row r="669" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A669" s="9"/>
     </row>
     <row r="670" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A670" s="10" t="s">
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="B670" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="671" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A671" s="10" t="s">
-        <v>145</v>
+        <v>70</v>
       </c>
       <c r="B671" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="672" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A672" s="10" t="s">
-        <v>178</v>
+        <v>103</v>
       </c>
       <c r="B672" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="673" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A673" s="9" t="s">
-        <v>177</v>
+        <v>102</v>
       </c>
       <c r="B673" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="674" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A674" s="9" t="s">
-        <v>176</v>
+        <v>101</v>
       </c>
       <c r="B674" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="675" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A675" s="10" t="s">
-        <v>175</v>
+        <v>100</v>
       </c>
       <c r="B675" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="676" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A676" s="10" t="s">
-        <v>174</v>
+        <v>99</v>
       </c>
       <c r="B676" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="677" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A677" s="9" t="s">
-        <v>173</v>
+        <v>98</v>
       </c>
       <c r="B677" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="678" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A678" s="10" t="s">
-        <v>172</v>
+        <v>97</v>
       </c>
       <c r="B678" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="679" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A679" s="10" t="s">
-        <v>171</v>
+        <v>96</v>
       </c>
       <c r="B679" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="680" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A680" s="10" t="s">
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="B680" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="681" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A681" s="10" t="s">
-        <v>169</v>
+        <v>94</v>
       </c>
       <c r="B681" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="682" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A682" s="10" t="s">
-        <v>168</v>
+        <v>93</v>
       </c>
       <c r="B682" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="683" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A683" s="9" t="s">
-        <v>167</v>
+        <v>92</v>
       </c>
       <c r="B683" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="684" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A684" s="9" t="s">
-        <v>166</v>
+        <v>91</v>
       </c>
       <c r="B684" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="685" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A685" s="9" t="s">
-        <v>165</v>
+        <v>90</v>
       </c>
       <c r="B685" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="686" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A686" s="9" t="s">
-        <v>164</v>
+        <v>89</v>
       </c>
       <c r="B686" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="687" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A687" s="9" t="s">
-        <v>163</v>
+        <v>88</v>
       </c>
       <c r="B687" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="688" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A688" s="9" t="s">
-        <v>162</v>
+        <v>87</v>
       </c>
       <c r="B688" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="689" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A689" s="10" t="s">
-        <v>161</v>
+        <v>86</v>
       </c>
       <c r="B689" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="690" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A690" s="10" t="s">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="B690" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="691" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A691" s="9" t="s">
-        <v>159</v>
+        <v>84</v>
       </c>
       <c r="B691" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="692" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A692" s="9" t="s">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="B692" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="693" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A693" s="9" t="s">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="B693" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="694" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A694" s="10" t="s">
-        <v>156</v>
+        <v>81</v>
       </c>
       <c r="B694" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="695" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A695" s="10" t="s">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="B695" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="696" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A696" s="9" t="s">
-        <v>154</v>
+        <v>79</v>
       </c>
       <c r="B696" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="697" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A697" s="10" t="s">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="B697" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="698" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A698" s="10" t="s">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="B698" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="699" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A699" s="9" t="s">
-        <v>151</v>
+        <v>76</v>
       </c>
       <c r="B699" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="700" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A700" s="10" t="s">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="B700" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="701" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A701" s="10" t="s">
-        <v>149</v>
+        <v>74</v>
       </c>
       <c r="B701" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="702" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A702" s="10" t="s">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="B702" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="703" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A703" s="9" t="s">
-        <v>147</v>
+        <v>72</v>
       </c>
       <c r="B703" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="704" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A704" s="9" t="s">
-        <v>146</v>
+        <v>71</v>
       </c>
       <c r="B704" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="705" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A705" s="10" t="s">
-        <v>145</v>
+        <v>70</v>
       </c>
       <c r="B705" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="706" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A706" s="10" t="s">
-        <v>144</v>
+        <v>69</v>
       </c>
       <c r="B706" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="707" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A707" s="9" t="s">
-        <v>143</v>
+        <v>68</v>
       </c>
       <c r="B707" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="708" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A708" s="10" t="s">
-        <v>142</v>
+        <v>67</v>
       </c>
       <c r="B708" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="709" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A709" s="10" t="s">
-        <v>141</v>
+        <v>66</v>
       </c>
       <c r="B709" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="710" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A710" s="10" t="s">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="B710" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="711" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A711" s="10" t="s">
-        <v>139</v>
+        <v>64</v>
       </c>
       <c r="B711" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="712" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A712" s="10" t="s">
-        <v>138</v>
+        <v>63</v>
       </c>
       <c r="B712" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="713" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A713" s="10" t="s">
-        <v>137</v>
+        <v>62</v>
       </c>
       <c r="B713" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="714" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A714" s="9" t="s">
-        <v>136</v>
+        <v>61</v>
       </c>
       <c r="B714" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="715" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A715" s="10" t="s">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="B715" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="716" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A716" s="9" t="s">
-        <v>134</v>
+        <v>59</v>
       </c>
       <c r="B716" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="717" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A717" s="9" t="s">
-        <v>133</v>
+        <v>58</v>
       </c>
       <c r="B717" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="718" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A718" s="10" t="s">
-        <v>132</v>
+        <v>57</v>
       </c>
       <c r="B718" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="719" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A719" s="9" t="s">
-        <v>131</v>
+        <v>56</v>
       </c>
       <c r="B719" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="720" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A720" s="10" t="s">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="B720" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="721" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A721" s="10" t="s">
-        <v>129</v>
+        <v>54</v>
       </c>
       <c r="B721" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="722" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A722" s="10" t="s">
-        <v>128</v>
+        <v>53</v>
       </c>
       <c r="B722" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="723" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A723" s="10" t="s">
-        <v>127</v>
+        <v>52</v>
       </c>
       <c r="B723" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="724" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A724" s="10" t="s">
-        <v>126</v>
+        <v>51</v>
       </c>
       <c r="B724" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="725" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A725" s="10" t="s">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="B725" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="726" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A726" s="10" t="s">
-        <v>124</v>
+        <v>49</v>
       </c>
       <c r="B726" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="727" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A727" s="10" t="s">
-        <v>123</v>
+        <v>48</v>
       </c>
       <c r="B727" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="728" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A728" s="10" t="s">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="B728" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="729" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A729" s="10" t="s">
-        <v>121</v>
+        <v>46</v>
       </c>
       <c r="B729" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="730" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A730" s="9" t="s">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="B730" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="731" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A731" s="10" t="s">
-        <v>119</v>
+        <v>44</v>
       </c>
       <c r="B731" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="732" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A732" s="10" t="s">
-        <v>118</v>
+        <v>43</v>
       </c>
       <c r="B732" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="733" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A733" s="10" t="s">
-        <v>117</v>
+        <v>42</v>
       </c>
       <c r="B733" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="734" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A734" s="10" t="s">
-        <v>116</v>
+        <v>41</v>
       </c>
       <c r="B734" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="735" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A735" s="9" t="s">
-        <v>115</v>
+        <v>40</v>
       </c>
       <c r="B735" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="736" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A736" s="10" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
       <c r="B736" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="737" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A737" s="9" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="B737" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="738" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A738" s="9" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="B738" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="739" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A739" s="10" t="s">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="B739" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="740" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A740" s="9" t="s">
-        <v>110</v>
+        <v>35</v>
       </c>
       <c r="B740" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="741" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A741" s="9" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
       <c r="B741" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="742" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A742" s="10" t="s">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="B742" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="743" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A743" s="10" t="s">
-        <v>107</v>
+        <v>32</v>
       </c>
       <c r="B743" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="744" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A744" s="9" t="s">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="B744" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="745" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A745" s="9" t="s">
-        <v>105</v>
+        <v>30</v>
       </c>
       <c r="B745" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="746" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A746" s="10" t="s">
-        <v>104</v>
+        <v>29</v>
       </c>
       <c r="B746" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="747" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A747" s="10" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="B747" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="748" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A748" s="10" t="s">
-        <v>102</v>
+        <v>27</v>
       </c>
       <c r="B748" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="749" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A749" s="10" t="s">
-        <v>101</v>
+        <v>26</v>
       </c>
       <c r="B749" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="750" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A750" s="10" t="s">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="B750" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="751" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A751" s="10" t="s">
-        <v>99</v>
+        <v>24</v>
       </c>
       <c r="B751" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="752" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A752" s="9" t="s">
-        <v>98</v>
+        <v>23</v>
       </c>
       <c r="B752" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="753" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A753" s="10" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="B753" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="754" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A754" s="10" t="s">
-        <v>96</v>
+        <v>21</v>
       </c>
       <c r="B754" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="755" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A755" s="10" t="s">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="B755" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="756" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A756" s="10" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="B756" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="757" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A757" s="10" t="s">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="B757" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="758" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A758" s="9" t="s">
-        <v>92</v>
+        <v>17</v>
       </c>
       <c r="B758" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="759" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A759" s="9" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="B759" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="760" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A760" s="9" t="s">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="B760" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="761" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A761" s="10" t="s">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="B761" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="762" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A762" s="10" t="s">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="B762" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="763" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A763" s="10" t="s">
-        <v>87</v>
+        <v>12</v>
       </c>
       <c r="B763" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="764" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A764" s="10" t="s">
-        <v>86</v>
+        <v>11</v>
       </c>
       <c r="B764" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="765" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A765" s="9" t="s">
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="B765" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="766" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A766" s="9" t="s">
-        <v>84</v>
+        <v>9</v>
       </c>
       <c r="B766" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="767" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A767" s="10" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="B767" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="768" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A768" s="10" t="s">
-        <v>82</v>
+        <v>7</v>
       </c>
       <c r="B768" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="769" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A769" s="10" t="s">
-        <v>81</v>
+        <v>6</v>
       </c>
       <c r="B769" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="770" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A770" s="10" t="s">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="B770" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="771" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A771" s="10" t="s">
-        <v>79</v>
+        <v>4</v>
       </c>
       <c r="B771" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="772" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A772" s="10" t="s">
-        <v>78</v>
+        <v>3</v>
       </c>
       <c r="B772" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="773" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A773" s="10" t="s">
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="B773" s="1" t="s">
-        <v>524</v>
+        <v>371</v>
       </c>
     </row>
     <row r="775" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
@@ -7824,3482 +6133,3482 @@
         <v>777425546939086</v>
       </c>
       <c r="B775" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="776" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A776" s="10" t="s">
-        <v>411</v>
+        <v>260</v>
       </c>
       <c r="B776" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="777" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A777" s="9" t="s">
-        <v>410</v>
+        <v>259</v>
       </c>
       <c r="B777" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="778" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A778" s="10" t="s">
-        <v>409</v>
+        <v>258</v>
       </c>
       <c r="B778" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="779" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A779" s="10" t="s">
-        <v>408</v>
+        <v>257</v>
       </c>
       <c r="B779" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="780" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A780" s="9" t="s">
-        <v>407</v>
+        <v>256</v>
       </c>
       <c r="B780" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="781" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A781" s="10" t="s">
-        <v>406</v>
+        <v>255</v>
       </c>
       <c r="B781" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="782" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A782" s="10" t="s">
-        <v>405</v>
+        <v>254</v>
       </c>
       <c r="B782" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="783" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A783" s="10" t="s">
-        <v>404</v>
+        <v>253</v>
       </c>
       <c r="B783" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="784" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A784" s="10" t="s">
-        <v>403</v>
+        <v>252</v>
       </c>
       <c r="B784" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="785" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A785" s="10" t="s">
-        <v>402</v>
+        <v>251</v>
       </c>
       <c r="B785" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="786" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A786" s="10" t="s">
-        <v>401</v>
+        <v>250</v>
       </c>
       <c r="B786" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="787" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A787" s="10" t="s">
-        <v>400</v>
+        <v>249</v>
       </c>
       <c r="B787" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="788" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A788" s="10" t="s">
-        <v>399</v>
+        <v>248</v>
       </c>
       <c r="B788" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="789" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A789" s="9" t="s">
-        <v>398</v>
+        <v>247</v>
       </c>
       <c r="B789" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="790" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A790" s="10" t="s">
-        <v>397</v>
+        <v>246</v>
       </c>
       <c r="B790" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="791" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A791" s="10" t="s">
-        <v>396</v>
+        <v>245</v>
       </c>
       <c r="B791" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="792" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A792" s="10" t="s">
-        <v>395</v>
+        <v>244</v>
       </c>
       <c r="B792" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="793" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A793" s="10" t="s">
-        <v>394</v>
+        <v>243</v>
       </c>
       <c r="B793" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="794" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A794" s="10" t="s">
-        <v>393</v>
+        <v>242</v>
       </c>
       <c r="B794" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="795" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A795" s="9" t="s">
-        <v>392</v>
+        <v>241</v>
       </c>
       <c r="B795" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="796" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A796" s="10" t="s">
-        <v>391</v>
+        <v>240</v>
       </c>
       <c r="B796" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="797" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A797" s="9" t="s">
-        <v>390</v>
+        <v>239</v>
       </c>
       <c r="B797" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="798" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A798" s="10" t="s">
-        <v>389</v>
+        <v>238</v>
       </c>
       <c r="B798" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="799" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A799" s="10" t="s">
-        <v>388</v>
+        <v>237</v>
       </c>
       <c r="B799" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="800" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A800" s="10" t="s">
-        <v>387</v>
+        <v>236</v>
       </c>
       <c r="B800" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="801" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A801" s="10" t="s">
-        <v>386</v>
+        <v>235</v>
       </c>
       <c r="B801" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="802" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A802" s="10" t="s">
-        <v>385</v>
+        <v>234</v>
       </c>
       <c r="B802" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="803" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A803" s="9" t="s">
-        <v>384</v>
+        <v>233</v>
       </c>
       <c r="B803" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="804" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A804" s="10" t="s">
-        <v>383</v>
+        <v>232</v>
       </c>
       <c r="B804" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="805" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A805" s="10" t="s">
-        <v>382</v>
+        <v>231</v>
       </c>
       <c r="B805" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="806" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A806" s="10" t="s">
-        <v>381</v>
+        <v>230</v>
       </c>
       <c r="B806" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="807" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A807" s="10" t="s">
-        <v>380</v>
+        <v>229</v>
       </c>
       <c r="B807" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="808" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A808" s="9" t="s">
-        <v>379</v>
+        <v>228</v>
       </c>
       <c r="B808" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="809" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A809" s="10" t="s">
-        <v>378</v>
+        <v>227</v>
       </c>
       <c r="B809" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="810" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A810" s="10" t="s">
-        <v>377</v>
+        <v>226</v>
       </c>
       <c r="B810" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="811" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A811" s="9" t="s">
-        <v>376</v>
+        <v>225</v>
       </c>
       <c r="B811" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="812" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A812" s="9" t="s">
-        <v>375</v>
+        <v>224</v>
       </c>
       <c r="B812" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
     </row>
     <row r="814" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A814" s="10" t="s">
-        <v>519</v>
+        <v>368</v>
       </c>
       <c r="B814" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="815" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A815" s="10" t="s">
-        <v>518</v>
+        <v>367</v>
       </c>
       <c r="B815" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="816" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A816" s="9" t="s">
-        <v>517</v>
+        <v>366</v>
       </c>
       <c r="B816" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="817" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A817" s="10" t="s">
-        <v>516</v>
+        <v>365</v>
       </c>
       <c r="B817" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="818" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A818" s="9" t="s">
-        <v>515</v>
+        <v>364</v>
       </c>
       <c r="B818" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="819" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A819" s="10" t="s">
-        <v>514</v>
+        <v>363</v>
       </c>
       <c r="B819" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="820" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A820" s="10" t="s">
-        <v>513</v>
+        <v>362</v>
       </c>
       <c r="B820" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="821" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A821" s="9" t="s">
-        <v>439</v>
+        <v>288</v>
       </c>
       <c r="B821" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="822" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A822" s="9" t="s">
-        <v>512</v>
+        <v>361</v>
       </c>
       <c r="B822" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="823" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A823" s="10" t="s">
-        <v>511</v>
+        <v>360</v>
       </c>
       <c r="B823" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="824" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A824" s="10" t="s">
-        <v>510</v>
+        <v>359</v>
       </c>
       <c r="B824" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="825" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A825" s="10" t="s">
-        <v>509</v>
+        <v>358</v>
       </c>
       <c r="B825" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="826" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A826" s="9" t="s">
-        <v>508</v>
+        <v>357</v>
       </c>
       <c r="B826" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="827" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A827" s="10" t="s">
-        <v>507</v>
+        <v>356</v>
       </c>
       <c r="B827" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="828" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A828" s="10" t="s">
-        <v>506</v>
+        <v>355</v>
       </c>
       <c r="B828" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="829" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A829" s="9" t="s">
-        <v>505</v>
+        <v>354</v>
       </c>
       <c r="B829" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="830" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A830" s="10" t="s">
-        <v>504</v>
+        <v>353</v>
       </c>
       <c r="B830" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="831" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A831" s="9" t="s">
-        <v>503</v>
+        <v>352</v>
       </c>
       <c r="B831" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="832" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A832" s="10" t="s">
-        <v>502</v>
+        <v>351</v>
       </c>
       <c r="B832" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="833" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A833" s="10" t="s">
-        <v>501</v>
+        <v>350</v>
       </c>
       <c r="B833" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="834" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A834" s="10" t="s">
-        <v>500</v>
+        <v>349</v>
       </c>
       <c r="B834" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="835" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A835" s="10" t="s">
-        <v>499</v>
+        <v>348</v>
       </c>
       <c r="B835" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="836" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A836" s="10" t="s">
-        <v>498</v>
+        <v>347</v>
       </c>
       <c r="B836" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="837" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A837" s="9" t="s">
-        <v>497</v>
+        <v>346</v>
       </c>
       <c r="B837" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="838" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A838" s="10" t="s">
-        <v>496</v>
+        <v>345</v>
       </c>
       <c r="B838" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="839" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A839" s="9" t="s">
-        <v>495</v>
+        <v>344</v>
       </c>
       <c r="B839" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="840" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A840" s="9" t="s">
-        <v>494</v>
+        <v>343</v>
       </c>
       <c r="B840" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="841" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A841" s="10" t="s">
-        <v>493</v>
+        <v>342</v>
       </c>
       <c r="B841" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="842" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A842" s="10" t="s">
-        <v>492</v>
+        <v>341</v>
       </c>
       <c r="B842" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="843" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A843" s="10" t="s">
-        <v>491</v>
+        <v>340</v>
       </c>
       <c r="B843" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="844" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A844" s="9" t="s">
-        <v>490</v>
+        <v>339</v>
       </c>
       <c r="B844" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="845" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A845" s="9" t="s">
-        <v>489</v>
+        <v>338</v>
       </c>
       <c r="B845" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="846" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A846" s="10" t="s">
-        <v>488</v>
+        <v>337</v>
       </c>
       <c r="B846" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="847" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A847" s="10" t="s">
-        <v>487</v>
+        <v>336</v>
       </c>
       <c r="B847" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="848" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A848" s="9" t="s">
-        <v>486</v>
+        <v>335</v>
       </c>
       <c r="B848" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="849" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A849" s="10" t="s">
-        <v>485</v>
+        <v>334</v>
       </c>
       <c r="B849" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="850" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A850" s="9" t="s">
-        <v>484</v>
+        <v>333</v>
       </c>
       <c r="B850" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="851" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A851" s="9" t="s">
-        <v>483</v>
+        <v>332</v>
       </c>
       <c r="B851" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="852" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A852" s="9" t="s">
-        <v>482</v>
+        <v>331</v>
       </c>
       <c r="B852" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="853" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A853" s="10" t="s">
-        <v>481</v>
+        <v>330</v>
       </c>
       <c r="B853" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="854" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A854" s="9" t="s">
-        <v>480</v>
+        <v>329</v>
       </c>
       <c r="B854" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="855" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A855" s="10" t="s">
-        <v>479</v>
+        <v>328</v>
       </c>
       <c r="B855" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="856" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A856" s="10" t="s">
-        <v>478</v>
+        <v>327</v>
       </c>
       <c r="B856" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="857" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A857" s="9" t="s">
-        <v>477</v>
+        <v>326</v>
       </c>
       <c r="B857" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="858" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A858" s="9" t="s">
-        <v>476</v>
+        <v>325</v>
       </c>
       <c r="B858" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="859" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A859" s="9" t="s">
-        <v>475</v>
+        <v>324</v>
       </c>
       <c r="B859" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="860" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A860" s="10" t="s">
-        <v>474</v>
+        <v>323</v>
       </c>
       <c r="B860" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="861" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A861" s="10" t="s">
-        <v>473</v>
+        <v>322</v>
       </c>
       <c r="B861" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="862" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A862" s="10" t="s">
-        <v>472</v>
+        <v>321</v>
       </c>
       <c r="B862" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="863" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A863" s="9" t="s">
-        <v>471</v>
+        <v>320</v>
       </c>
       <c r="B863" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="864" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A864" s="9" t="s">
-        <v>470</v>
+        <v>319</v>
       </c>
       <c r="B864" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="865" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A865" s="10" t="s">
-        <v>469</v>
+        <v>318</v>
       </c>
       <c r="B865" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="866" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A866" s="9" t="s">
-        <v>468</v>
+        <v>317</v>
       </c>
       <c r="B866" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="867" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A867" s="10" t="s">
-        <v>467</v>
+        <v>316</v>
       </c>
       <c r="B867" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="868" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A868" s="10" t="s">
-        <v>466</v>
+        <v>315</v>
       </c>
       <c r="B868" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="869" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A869" s="9" t="s">
-        <v>465</v>
+        <v>314</v>
       </c>
       <c r="B869" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="870" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A870" s="10" t="s">
-        <v>464</v>
+        <v>313</v>
       </c>
       <c r="B870" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="871" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A871" s="10" t="s">
-        <v>463</v>
+        <v>312</v>
       </c>
       <c r="B871" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="872" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A872" s="9" t="s">
-        <v>462</v>
+        <v>311</v>
       </c>
       <c r="B872" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="873" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A873" s="9" t="s">
-        <v>461</v>
+        <v>310</v>
       </c>
       <c r="B873" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="874" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A874" s="9" t="s">
-        <v>460</v>
+        <v>309</v>
       </c>
       <c r="B874" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="875" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A875" s="10" t="s">
-        <v>459</v>
+        <v>308</v>
       </c>
       <c r="B875" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="876" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A876" s="10" t="s">
-        <v>458</v>
+        <v>307</v>
       </c>
       <c r="B876" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="877" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A877" s="10" t="s">
-        <v>457</v>
+        <v>306</v>
       </c>
       <c r="B877" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="878" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A878" s="10" t="s">
-        <v>456</v>
+        <v>305</v>
       </c>
       <c r="B878" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="879" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A879" s="9" t="s">
-        <v>455</v>
+        <v>304</v>
       </c>
       <c r="B879" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="880" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A880" s="10" t="s">
-        <v>454</v>
+        <v>303</v>
       </c>
       <c r="B880" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="881" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A881" s="10" t="s">
-        <v>453</v>
+        <v>302</v>
       </c>
       <c r="B881" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="882" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A882" s="9" t="s">
-        <v>452</v>
+        <v>301</v>
       </c>
       <c r="B882" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="883" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A883" s="10" t="s">
-        <v>451</v>
+        <v>300</v>
       </c>
       <c r="B883" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="884" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A884" s="10" t="s">
-        <v>450</v>
+        <v>299</v>
       </c>
       <c r="B884" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="885" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A885" s="10" t="s">
-        <v>449</v>
+        <v>298</v>
       </c>
       <c r="B885" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="886" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A886" s="10" t="s">
-        <v>448</v>
+        <v>297</v>
       </c>
       <c r="B886" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="887" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A887" s="10" t="s">
-        <v>436</v>
+        <v>285</v>
       </c>
       <c r="B887" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="888" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A888" s="10" t="s">
-        <v>447</v>
+        <v>296</v>
       </c>
       <c r="B888" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="889" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A889" s="9" t="s">
-        <v>446</v>
+        <v>295</v>
       </c>
       <c r="B889" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="890" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A890" s="9" t="s">
-        <v>445</v>
+        <v>294</v>
       </c>
       <c r="B890" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="891" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A891" s="10" t="s">
-        <v>444</v>
+        <v>293</v>
       </c>
       <c r="B891" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="892" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A892" s="10" t="s">
-        <v>443</v>
+        <v>292</v>
       </c>
       <c r="B892" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="893" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A893" s="10" t="s">
-        <v>442</v>
+        <v>291</v>
       </c>
       <c r="B893" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="894" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A894" s="9" t="s">
-        <v>441</v>
+        <v>290</v>
       </c>
       <c r="B894" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="895" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A895" s="10" t="s">
-        <v>437</v>
+        <v>286</v>
       </c>
       <c r="B895" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="896" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A896" s="10" t="s">
-        <v>440</v>
+        <v>289</v>
       </c>
       <c r="B896" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="897" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A897" s="9" t="s">
-        <v>439</v>
+        <v>288</v>
       </c>
       <c r="B897" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="898" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A898" s="9" t="s">
-        <v>438</v>
+        <v>287</v>
       </c>
       <c r="B898" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="899" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A899" s="10" t="s">
-        <v>437</v>
+        <v>286</v>
       </c>
       <c r="B899" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="900" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A900" s="10" t="s">
-        <v>436</v>
+        <v>285</v>
       </c>
       <c r="B900" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="901" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A901" s="10" t="s">
-        <v>435</v>
+        <v>284</v>
       </c>
       <c r="B901" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="902" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A902" s="10" t="s">
-        <v>434</v>
+        <v>283</v>
       </c>
       <c r="B902" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="903" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A903" s="10" t="s">
-        <v>433</v>
+        <v>282</v>
       </c>
       <c r="B903" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="904" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A904" s="9" t="s">
-        <v>432</v>
+        <v>281</v>
       </c>
       <c r="B904" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="905" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A905" s="9" t="s">
-        <v>431</v>
+        <v>280</v>
       </c>
       <c r="B905" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="906" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A906" s="10" t="s">
-        <v>430</v>
+        <v>279</v>
       </c>
       <c r="B906" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="907" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A907" s="10" t="s">
-        <v>429</v>
+        <v>278</v>
       </c>
       <c r="B907" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="908" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A908" s="10" t="s">
-        <v>428</v>
+        <v>277</v>
       </c>
       <c r="B908" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="909" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A909" s="9" t="s">
-        <v>427</v>
+        <v>276</v>
       </c>
       <c r="B909" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="910" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A910" s="10" t="s">
-        <v>426</v>
+        <v>275</v>
       </c>
       <c r="B910" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="911" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A911" s="10" t="s">
-        <v>425</v>
+        <v>274</v>
       </c>
       <c r="B911" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="912" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A912" s="10" t="s">
-        <v>424</v>
+        <v>273</v>
       </c>
       <c r="B912" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="913" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A913" s="10" t="s">
-        <v>423</v>
+        <v>272</v>
       </c>
       <c r="B913" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="914" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A914" s="9" t="s">
-        <v>422</v>
+        <v>271</v>
       </c>
       <c r="B914" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="915" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A915" s="10" t="s">
-        <v>421</v>
+        <v>270</v>
       </c>
       <c r="B915" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="916" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A916" s="10" t="s">
-        <v>420</v>
+        <v>269</v>
       </c>
       <c r="B916" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="917" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A917" s="10" t="s">
-        <v>419</v>
+        <v>268</v>
       </c>
       <c r="B917" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="918" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A918" s="9" t="s">
-        <v>418</v>
+        <v>267</v>
       </c>
       <c r="B918" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="919" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A919" s="10" t="s">
-        <v>417</v>
+        <v>266</v>
       </c>
       <c r="B919" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="920" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A920" s="9" t="s">
-        <v>416</v>
+        <v>265</v>
       </c>
       <c r="B920" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="921" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A921" s="9" t="s">
-        <v>415</v>
+        <v>264</v>
       </c>
       <c r="B921" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="922" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A922" s="9" t="s">
-        <v>414</v>
+        <v>263</v>
       </c>
       <c r="B922" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="923" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A923" s="10" t="s">
-        <v>413</v>
+        <v>262</v>
       </c>
       <c r="B923" s="1" t="s">
-        <v>525</v>
+        <v>372</v>
       </c>
     </row>
     <row r="925" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A925" s="10" t="s">
-        <v>659</v>
+        <v>506</v>
       </c>
       <c r="B925" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="926" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A926" s="9" t="s">
-        <v>658</v>
+        <v>505</v>
       </c>
       <c r="B926" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="927" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A927" s="10" t="s">
-        <v>657</v>
+        <v>504</v>
       </c>
       <c r="B927" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="928" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A928" s="9" t="s">
-        <v>656</v>
+        <v>503</v>
       </c>
       <c r="B928" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="929" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A929" s="9" t="s">
-        <v>655</v>
+        <v>502</v>
       </c>
       <c r="B929" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="930" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A930" s="10" t="s">
-        <v>654</v>
+        <v>501</v>
       </c>
       <c r="B930" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="931" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A931" s="10" t="s">
-        <v>653</v>
+        <v>500</v>
       </c>
       <c r="B931" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="932" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A932" s="9" t="s">
-        <v>652</v>
+        <v>499</v>
       </c>
       <c r="B932" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="933" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A933" s="10" t="s">
-        <v>651</v>
+        <v>498</v>
       </c>
       <c r="B933" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="934" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A934" s="10" t="s">
-        <v>650</v>
+        <v>497</v>
       </c>
       <c r="B934" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="935" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A935" s="9" t="s">
-        <v>649</v>
+        <v>496</v>
       </c>
       <c r="B935" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="936" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A936" s="10" t="s">
-        <v>648</v>
+        <v>495</v>
       </c>
       <c r="B936" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="937" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A937" s="10" t="s">
-        <v>647</v>
+        <v>494</v>
       </c>
       <c r="B937" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="938" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A938" s="10" t="s">
-        <v>646</v>
+        <v>493</v>
       </c>
       <c r="B938" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="939" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A939" s="10" t="s">
-        <v>645</v>
+        <v>492</v>
       </c>
       <c r="B939" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="940" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A940" s="10" t="s">
-        <v>644</v>
+        <v>491</v>
       </c>
       <c r="B940" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="941" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A941" s="9" t="s">
-        <v>643</v>
+        <v>490</v>
       </c>
       <c r="B941" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="942" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A942" s="9" t="s">
-        <v>642</v>
+        <v>489</v>
       </c>
       <c r="B942" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="943" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A943" s="10" t="s">
-        <v>641</v>
+        <v>488</v>
       </c>
       <c r="B943" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="944" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A944" s="10" t="s">
-        <v>640</v>
+        <v>487</v>
       </c>
       <c r="B944" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="945" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A945" s="10" t="s">
-        <v>639</v>
+        <v>486</v>
       </c>
       <c r="B945" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="946" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A946" s="10" t="s">
-        <v>638</v>
+        <v>485</v>
       </c>
       <c r="B946" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="947" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A947" s="9" t="s">
-        <v>637</v>
+        <v>484</v>
       </c>
       <c r="B947" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="948" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A948" s="10" t="s">
-        <v>636</v>
+        <v>483</v>
       </c>
       <c r="B948" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="949" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A949" s="10" t="s">
-        <v>635</v>
+        <v>482</v>
       </c>
       <c r="B949" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="950" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A950" s="10" t="s">
-        <v>634</v>
+        <v>481</v>
       </c>
       <c r="B950" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="951" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A951" s="9" t="s">
-        <v>633</v>
+        <v>480</v>
       </c>
       <c r="B951" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="952" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A952" s="10" t="s">
-        <v>632</v>
+        <v>479</v>
       </c>
       <c r="B952" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="953" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A953" s="10" t="s">
-        <v>631</v>
+        <v>478</v>
       </c>
       <c r="B953" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="954" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A954" s="10" t="s">
-        <v>630</v>
+        <v>477</v>
       </c>
       <c r="B954" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="955" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A955" s="10" t="s">
-        <v>629</v>
+        <v>476</v>
       </c>
       <c r="B955" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="956" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A956" s="10" t="s">
-        <v>628</v>
+        <v>475</v>
       </c>
       <c r="B956" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="957" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A957" s="9" t="s">
-        <v>627</v>
+        <v>474</v>
       </c>
       <c r="B957" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="958" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A958" s="10" t="s">
-        <v>626</v>
+        <v>473</v>
       </c>
       <c r="B958" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="959" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A959" s="10" t="s">
-        <v>625</v>
+        <v>472</v>
       </c>
       <c r="B959" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="960" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A960" s="10" t="s">
-        <v>624</v>
+        <v>471</v>
       </c>
       <c r="B960" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="961" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A961" s="10" t="s">
-        <v>623</v>
+        <v>470</v>
       </c>
       <c r="B961" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="962" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A962" s="10" t="s">
-        <v>622</v>
+        <v>469</v>
       </c>
       <c r="B962" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="963" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A963" s="10" t="s">
-        <v>621</v>
+        <v>468</v>
       </c>
       <c r="B963" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="964" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A964" s="10" t="s">
-        <v>620</v>
+        <v>467</v>
       </c>
       <c r="B964" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="965" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A965" s="10" t="s">
-        <v>619</v>
+        <v>466</v>
       </c>
       <c r="B965" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="966" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A966" s="10" t="s">
-        <v>618</v>
+        <v>465</v>
       </c>
       <c r="B966" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="967" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A967" s="10" t="s">
-        <v>617</v>
+        <v>464</v>
       </c>
       <c r="B967" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="968" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A968" s="10" t="s">
-        <v>616</v>
+        <v>463</v>
       </c>
       <c r="B968" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="969" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A969" s="10" t="s">
-        <v>615</v>
+        <v>462</v>
       </c>
       <c r="B969" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="970" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A970" s="10" t="s">
-        <v>614</v>
+        <v>461</v>
       </c>
       <c r="B970" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="971" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A971" s="10" t="s">
-        <v>613</v>
+        <v>460</v>
       </c>
       <c r="B971" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="972" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A972" s="10" t="s">
-        <v>612</v>
+        <v>459</v>
       </c>
       <c r="B972" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="973" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A973" s="10" t="s">
-        <v>611</v>
+        <v>458</v>
       </c>
       <c r="B973" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="974" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A974" s="10" t="s">
-        <v>610</v>
+        <v>457</v>
       </c>
       <c r="B974" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="975" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A975" s="9" t="s">
-        <v>609</v>
+        <v>456</v>
       </c>
       <c r="B975" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="976" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A976" s="10" t="s">
-        <v>608</v>
+        <v>455</v>
       </c>
       <c r="B976" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="977" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A977" s="10" t="s">
-        <v>607</v>
+        <v>454</v>
       </c>
       <c r="B977" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="978" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A978" s="10" t="s">
-        <v>606</v>
+        <v>453</v>
       </c>
       <c r="B978" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
       <c r="D978" s="1" t="s">
-        <v>661</v>
+        <v>508</v>
       </c>
     </row>
     <row r="979" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A979" s="10" t="s">
-        <v>605</v>
+        <v>452</v>
       </c>
       <c r="B979" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="980" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A980" s="10" t="s">
-        <v>604</v>
+        <v>451</v>
       </c>
       <c r="B980" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="981" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A981" s="10" t="s">
-        <v>603</v>
+        <v>450</v>
       </c>
       <c r="B981" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="982" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A982" s="10" t="s">
-        <v>602</v>
+        <v>449</v>
       </c>
       <c r="B982" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="983" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A983" s="10" t="s">
-        <v>601</v>
+        <v>448</v>
       </c>
       <c r="B983" s="1" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="985" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A985" s="11" t="s">
-        <v>662</v>
+        <v>509</v>
       </c>
       <c r="B985" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="986" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A986" s="11" t="s">
-        <v>663</v>
+        <v>510</v>
       </c>
       <c r="B986" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="987" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A987" s="12" t="s">
-        <v>664</v>
+        <v>511</v>
       </c>
       <c r="B987" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="988" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A988" s="11" t="s">
-        <v>665</v>
+        <v>512</v>
       </c>
       <c r="B988" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="989" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A989" s="11" t="s">
-        <v>666</v>
+        <v>513</v>
       </c>
       <c r="B989" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="990" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A990" s="12" t="s">
-        <v>667</v>
+        <v>514</v>
       </c>
       <c r="B990" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="991" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A991" s="12" t="s">
-        <v>668</v>
+        <v>515</v>
       </c>
       <c r="B991" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="992" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A992" s="11" t="s">
-        <v>669</v>
+        <v>516</v>
       </c>
       <c r="B992" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="993" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A993" s="12" t="s">
-        <v>670</v>
+        <v>517</v>
       </c>
       <c r="B993" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="994" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A994" s="12" t="s">
-        <v>671</v>
+        <v>518</v>
       </c>
       <c r="B994" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="995" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A995" s="12" t="s">
-        <v>672</v>
+        <v>519</v>
       </c>
       <c r="B995" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="996" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A996" s="11" t="s">
-        <v>673</v>
+        <v>520</v>
       </c>
       <c r="B996" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="997" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A997" s="12" t="s">
-        <v>674</v>
+        <v>521</v>
       </c>
       <c r="B997" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="998" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A998" s="11" t="s">
-        <v>675</v>
+        <v>522</v>
       </c>
       <c r="B998" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="999" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A999" s="11" t="s">
-        <v>676</v>
+        <v>523</v>
       </c>
       <c r="B999" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1000" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1000" s="11" t="s">
-        <v>677</v>
+        <v>524</v>
       </c>
       <c r="B1000" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1001" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1001" s="12" t="s">
-        <v>678</v>
+        <v>525</v>
       </c>
       <c r="B1001" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1002" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1002" s="11" t="s">
-        <v>679</v>
+        <v>526</v>
       </c>
       <c r="B1002" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1003" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1003" s="12" t="s">
-        <v>680</v>
+        <v>527</v>
       </c>
       <c r="B1003" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1004" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1004" s="11" t="s">
-        <v>681</v>
+        <v>528</v>
       </c>
       <c r="B1004" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1005" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1005" s="12" t="s">
-        <v>682</v>
+        <v>529</v>
       </c>
       <c r="B1005" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1006" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1006" s="12" t="s">
-        <v>683</v>
+        <v>530</v>
       </c>
       <c r="B1006" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1007" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1007" s="12" t="s">
-        <v>684</v>
+        <v>531</v>
       </c>
       <c r="B1007" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1008" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1008" s="11" t="s">
-        <v>685</v>
+        <v>532</v>
       </c>
       <c r="B1008" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1009" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1009" s="12" t="s">
-        <v>686</v>
+        <v>533</v>
       </c>
       <c r="B1009" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1010" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1010" s="11" t="s">
-        <v>687</v>
+        <v>534</v>
       </c>
       <c r="B1010" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1011" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1011" s="12" t="s">
-        <v>688</v>
+        <v>535</v>
       </c>
       <c r="B1011" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1012" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1012" s="11" t="s">
-        <v>689</v>
+        <v>536</v>
       </c>
       <c r="B1012" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1013" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1013" s="12" t="s">
-        <v>690</v>
+        <v>537</v>
       </c>
       <c r="B1013" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1014" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1014" s="12" t="s">
-        <v>691</v>
+        <v>538</v>
       </c>
       <c r="B1014" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1015" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1015" s="12" t="s">
-        <v>692</v>
+        <v>539</v>
       </c>
       <c r="B1015" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1016" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1016" s="11" t="s">
-        <v>693</v>
+        <v>540</v>
       </c>
       <c r="B1016" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1017" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1017" s="12" t="s">
-        <v>694</v>
+        <v>541</v>
       </c>
       <c r="B1017" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1018" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1018" s="12" t="s">
-        <v>695</v>
+        <v>542</v>
       </c>
       <c r="B1018" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1019" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1019" s="11" t="s">
-        <v>696</v>
+        <v>543</v>
       </c>
       <c r="B1019" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1020" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1020" s="11" t="s">
-        <v>697</v>
+        <v>544</v>
       </c>
       <c r="B1020" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1021" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1021" s="12" t="s">
-        <v>698</v>
+        <v>545</v>
       </c>
       <c r="B1021" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1022" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1022" s="12" t="s">
-        <v>699</v>
+        <v>546</v>
       </c>
       <c r="B1022" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1023" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1023" s="11" t="s">
-        <v>700</v>
+        <v>547</v>
       </c>
       <c r="B1023" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1024" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1024" s="11" t="s">
-        <v>701</v>
+        <v>548</v>
       </c>
       <c r="B1024" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1025" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1025" s="12" t="s">
-        <v>702</v>
+        <v>549</v>
       </c>
       <c r="B1025" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1026" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1026" s="12" t="s">
-        <v>703</v>
+        <v>550</v>
       </c>
       <c r="B1026" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1027" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1027" s="11" t="s">
-        <v>704</v>
+        <v>551</v>
       </c>
       <c r="B1027" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1028" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1028" s="12" t="s">
-        <v>705</v>
+        <v>552</v>
       </c>
       <c r="B1028" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1029" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1029" s="12" t="s">
-        <v>706</v>
+        <v>553</v>
       </c>
       <c r="B1029" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1030" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1030" s="12" t="s">
-        <v>707</v>
+        <v>554</v>
       </c>
       <c r="B1030" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1031" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1031" s="12" t="s">
-        <v>708</v>
+        <v>555</v>
       </c>
       <c r="B1031" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1032" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1032" s="12" t="s">
-        <v>709</v>
+        <v>556</v>
       </c>
       <c r="B1032" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1033" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1033" s="12" t="s">
-        <v>710</v>
+        <v>557</v>
       </c>
       <c r="B1033" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1034" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1034" s="12" t="s">
-        <v>711</v>
+        <v>558</v>
       </c>
       <c r="B1034" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1035" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1035" s="12" t="s">
-        <v>712</v>
+        <v>559</v>
       </c>
       <c r="B1035" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1036" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1036" s="12" t="s">
-        <v>713</v>
+        <v>560</v>
       </c>
       <c r="B1036" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1037" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1037" s="12" t="s">
-        <v>714</v>
+        <v>561</v>
       </c>
       <c r="B1037" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1038" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1038" s="11" t="s">
-        <v>715</v>
+        <v>562</v>
       </c>
       <c r="B1038" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1039" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1039" s="11" t="s">
-        <v>716</v>
+        <v>563</v>
       </c>
       <c r="B1039" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1040" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1040" s="12" t="s">
-        <v>717</v>
+        <v>564</v>
       </c>
       <c r="B1040" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1041" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1041" s="12" t="s">
-        <v>718</v>
+        <v>565</v>
       </c>
       <c r="B1041" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1042" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1042" s="12" t="s">
-        <v>719</v>
+        <v>566</v>
       </c>
       <c r="B1042" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1043" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1043" s="12" t="s">
-        <v>720</v>
+        <v>567</v>
       </c>
       <c r="B1043" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1044" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1044" s="12" t="s">
-        <v>720</v>
+        <v>567</v>
       </c>
       <c r="B1044" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1045" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1045" s="12" t="s">
-        <v>721</v>
+        <v>568</v>
       </c>
       <c r="B1045" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1046" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1046" s="11" t="s">
-        <v>722</v>
+        <v>569</v>
       </c>
       <c r="B1046" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1047" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1047" s="12" t="s">
-        <v>723</v>
+        <v>570</v>
       </c>
       <c r="B1047" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1048" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1048" s="12" t="s">
-        <v>724</v>
+        <v>571</v>
       </c>
       <c r="B1048" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1049" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1049" s="12" t="s">
-        <v>725</v>
+        <v>572</v>
       </c>
       <c r="B1049" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1050" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1050" s="12" t="s">
-        <v>726</v>
+        <v>573</v>
       </c>
       <c r="B1050" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1051" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1051" s="12" t="s">
-        <v>727</v>
+        <v>574</v>
       </c>
       <c r="B1051" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1052" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1052" s="11" t="s">
-        <v>728</v>
+        <v>575</v>
       </c>
       <c r="B1052" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1053" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1053" s="12" t="s">
-        <v>729</v>
+        <v>576</v>
       </c>
       <c r="B1053" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1054" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1054" s="11" t="s">
-        <v>730</v>
+        <v>577</v>
       </c>
       <c r="B1054" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1055" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1055" s="12" t="s">
-        <v>731</v>
+        <v>578</v>
       </c>
       <c r="B1055" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1056" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1056" s="12" t="s">
-        <v>732</v>
+        <v>579</v>
       </c>
       <c r="B1056" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1057" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1057" s="11" t="s">
-        <v>733</v>
+        <v>580</v>
       </c>
       <c r="B1057" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1058" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1058" s="11" t="s">
-        <v>734</v>
+        <v>581</v>
       </c>
       <c r="B1058" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1059" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1059" s="12" t="s">
-        <v>735</v>
+        <v>582</v>
       </c>
       <c r="B1059" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1060" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1060" s="12" t="s">
-        <v>736</v>
+        <v>583</v>
       </c>
       <c r="B1060" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1061" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1061" s="12" t="s">
-        <v>737</v>
+        <v>584</v>
       </c>
       <c r="B1061" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1062" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1062" s="11" t="s">
-        <v>738</v>
+        <v>585</v>
       </c>
       <c r="B1062" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1063" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1063" s="12" t="s">
-        <v>739</v>
+        <v>586</v>
       </c>
       <c r="B1063" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1064" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1064" s="12" t="s">
-        <v>740</v>
+        <v>587</v>
       </c>
       <c r="B1064" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1065" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1065" s="11" t="s">
-        <v>741</v>
+        <v>588</v>
       </c>
       <c r="B1065" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1066" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1066" s="12" t="s">
-        <v>742</v>
+        <v>589</v>
       </c>
       <c r="B1066" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1067" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1067" s="11" t="s">
-        <v>743</v>
+        <v>590</v>
       </c>
       <c r="B1067" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1068" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1068" s="11" t="s">
-        <v>744</v>
+        <v>591</v>
       </c>
       <c r="B1068" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1069" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1069" s="11" t="s">
-        <v>745</v>
+        <v>592</v>
       </c>
       <c r="B1069" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1070" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1070" s="11" t="s">
-        <v>746</v>
+        <v>593</v>
       </c>
       <c r="B1070" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1071" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1071" s="11" t="s">
-        <v>747</v>
+        <v>594</v>
       </c>
       <c r="B1071" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1072" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1072" s="12" t="s">
-        <v>748</v>
+        <v>595</v>
       </c>
       <c r="B1072" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1073" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1073" s="12" t="s">
-        <v>708</v>
+        <v>555</v>
       </c>
       <c r="B1073" s="1" t="s">
-        <v>749</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1075" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1075" s="13" t="s">
-        <v>750</v>
+        <v>597</v>
       </c>
       <c r="B1075" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1076" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1076" s="14" t="s">
-        <v>751</v>
+        <v>598</v>
       </c>
       <c r="B1076" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1077" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1077" s="14" t="s">
-        <v>752</v>
+        <v>599</v>
       </c>
       <c r="B1077" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1078" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1078" s="14" t="s">
-        <v>753</v>
+        <v>600</v>
       </c>
       <c r="B1078" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1079" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1079" s="14" t="s">
-        <v>754</v>
+        <v>601</v>
       </c>
       <c r="B1079" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1080" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1080" s="14" t="s">
-        <v>755</v>
+        <v>602</v>
       </c>
       <c r="B1080" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1081" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1081" s="14" t="s">
-        <v>756</v>
+        <v>603</v>
       </c>
       <c r="B1081" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1082" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1082" s="13" t="s">
-        <v>757</v>
+        <v>604</v>
       </c>
       <c r="B1082" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1083" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1083" s="14" t="s">
-        <v>758</v>
+        <v>605</v>
       </c>
       <c r="B1083" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1084" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1084" s="14" t="s">
-        <v>759</v>
+        <v>606</v>
       </c>
       <c r="B1084" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1085" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1085" s="14" t="s">
-        <v>760</v>
+        <v>607</v>
       </c>
       <c r="B1085" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1086" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1086" s="13" t="s">
-        <v>761</v>
+        <v>608</v>
       </c>
       <c r="B1086" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1087" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1087" s="14" t="s">
-        <v>762</v>
+        <v>609</v>
       </c>
       <c r="B1087" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1088" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1088" s="14" t="s">
-        <v>763</v>
+        <v>610</v>
       </c>
       <c r="B1088" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1089" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1089" s="14" t="s">
-        <v>764</v>
+        <v>611</v>
       </c>
       <c r="B1089" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1090" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1090" s="13" t="s">
-        <v>765</v>
+        <v>612</v>
       </c>
       <c r="B1090" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1091" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1091" s="14" t="s">
-        <v>766</v>
+        <v>613</v>
       </c>
       <c r="B1091" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1092" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1092" s="14" t="s">
-        <v>767</v>
+        <v>614</v>
       </c>
       <c r="B1092" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1093" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1093" s="14" t="s">
-        <v>768</v>
+        <v>615</v>
       </c>
       <c r="B1093" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1094" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1094" s="14" t="s">
-        <v>769</v>
+        <v>616</v>
       </c>
       <c r="B1094" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1095" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1095" s="14" t="s">
-        <v>769</v>
+        <v>616</v>
       </c>
       <c r="B1095" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1096" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1096" s="14" t="s">
-        <v>770</v>
+        <v>617</v>
       </c>
       <c r="B1096" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1097" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1097" s="14" t="s">
-        <v>771</v>
+        <v>618</v>
       </c>
       <c r="B1097" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1098" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1098" s="13" t="s">
-        <v>772</v>
+        <v>619</v>
       </c>
       <c r="B1098" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1099" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1099" s="13" t="s">
-        <v>773</v>
+        <v>620</v>
       </c>
       <c r="B1099" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1100" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1100" s="14" t="s">
-        <v>774</v>
+        <v>621</v>
       </c>
       <c r="B1100" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1101" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1101" s="14" t="s">
-        <v>775</v>
+        <v>622</v>
       </c>
       <c r="B1101" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1102" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1102" s="14" t="s">
-        <v>776</v>
+        <v>623</v>
       </c>
       <c r="B1102" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1103" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1103" s="13" t="s">
-        <v>777</v>
+        <v>624</v>
       </c>
       <c r="B1103" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1104" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1104" s="14" t="s">
-        <v>778</v>
+        <v>625</v>
       </c>
       <c r="B1104" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1105" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1105" s="14" t="s">
-        <v>779</v>
+        <v>626</v>
       </c>
       <c r="B1105" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1106" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1106" s="14" t="s">
-        <v>780</v>
+        <v>627</v>
       </c>
       <c r="B1106" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1107" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1107" s="14" t="s">
-        <v>781</v>
+        <v>628</v>
       </c>
       <c r="B1107" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1108" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1108" s="14" t="s">
-        <v>782</v>
+        <v>629</v>
       </c>
       <c r="B1108" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1109" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1109" s="13" t="s">
-        <v>783</v>
+        <v>630</v>
       </c>
       <c r="B1109" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1110" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1110" s="13" t="s">
-        <v>784</v>
+        <v>631</v>
       </c>
       <c r="B1110" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1111" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1111" s="13" t="s">
-        <v>785</v>
+        <v>632</v>
       </c>
       <c r="B1111" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1112" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1112" s="14" t="s">
-        <v>786</v>
+        <v>633</v>
       </c>
       <c r="B1112" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1113" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1113" s="14" t="s">
-        <v>787</v>
+        <v>634</v>
       </c>
       <c r="B1113" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1114" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1114" s="14" t="s">
-        <v>788</v>
+        <v>635</v>
       </c>
       <c r="B1114" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1115" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1115" s="14" t="s">
-        <v>789</v>
+        <v>636</v>
       </c>
       <c r="B1115" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1116" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1116" s="13" t="s">
-        <v>790</v>
+        <v>637</v>
       </c>
       <c r="B1116" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1117" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1117" s="14" t="s">
-        <v>791</v>
+        <v>638</v>
       </c>
       <c r="B1117" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1118" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1118" s="13" t="s">
-        <v>792</v>
+        <v>639</v>
       </c>
       <c r="B1118" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1119" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1119" s="13" t="s">
-        <v>793</v>
+        <v>640</v>
       </c>
       <c r="B1119" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1120" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1120" s="13" t="s">
-        <v>794</v>
+        <v>641</v>
       </c>
       <c r="B1120" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1121" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1121" s="14" t="s">
-        <v>795</v>
+        <v>642</v>
       </c>
       <c r="B1121" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1122" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1122" s="14" t="s">
-        <v>796</v>
+        <v>643</v>
       </c>
       <c r="B1122" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1123" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1123" s="14" t="s">
-        <v>797</v>
+        <v>644</v>
       </c>
       <c r="B1123" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1124" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1124" s="13" t="s">
-        <v>798</v>
+        <v>645</v>
       </c>
       <c r="B1124" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1125" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1125" s="14" t="s">
-        <v>799</v>
+        <v>646</v>
       </c>
       <c r="B1125" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1126" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1126" s="14" t="s">
-        <v>800</v>
+        <v>647</v>
       </c>
       <c r="B1126" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1127" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1127" s="14" t="s">
-        <v>801</v>
+        <v>648</v>
       </c>
       <c r="B1127" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1128" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1128" s="14" t="s">
-        <v>802</v>
+        <v>649</v>
       </c>
       <c r="B1128" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1129" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1129" s="14" t="s">
-        <v>803</v>
+        <v>650</v>
       </c>
       <c r="B1129" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1130" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1130" s="13" t="s">
-        <v>804</v>
+        <v>651</v>
       </c>
       <c r="B1130" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1131" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1131" s="14" t="s">
-        <v>805</v>
+        <v>652</v>
       </c>
       <c r="B1131" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1132" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1132" s="14" t="s">
-        <v>806</v>
+        <v>653</v>
       </c>
       <c r="B1132" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1133" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1133" s="14" t="s">
-        <v>807</v>
+        <v>654</v>
       </c>
       <c r="B1133" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1134" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1134" s="13" t="s">
-        <v>808</v>
+        <v>655</v>
       </c>
       <c r="B1134" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1135" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1135" s="14" t="s">
-        <v>809</v>
+        <v>656</v>
       </c>
       <c r="B1135" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1136" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1136" s="13" t="s">
-        <v>810</v>
+        <v>657</v>
       </c>
       <c r="B1136" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1137" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1137" s="14" t="s">
-        <v>811</v>
+        <v>658</v>
       </c>
       <c r="B1137" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1138" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1138" s="14" t="s">
-        <v>812</v>
+        <v>659</v>
       </c>
       <c r="B1138" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1139" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1139" s="13" t="s">
-        <v>813</v>
+        <v>660</v>
       </c>
       <c r="B1139" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1140" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1140" s="13" t="s">
-        <v>814</v>
+        <v>661</v>
       </c>
       <c r="B1140" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1141" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1141" s="14" t="s">
-        <v>815</v>
+        <v>662</v>
       </c>
       <c r="B1141" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1142" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1142" s="14" t="s">
-        <v>816</v>
+        <v>663</v>
       </c>
       <c r="B1142" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1143" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1143" s="13" t="s">
-        <v>817</v>
+        <v>664</v>
       </c>
       <c r="B1143" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1144" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1144" s="13" t="s">
-        <v>818</v>
+        <v>665</v>
       </c>
       <c r="B1144" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1145" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1145" s="14" t="s">
-        <v>819</v>
+        <v>666</v>
       </c>
       <c r="B1145" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1146" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1146" s="14" t="s">
-        <v>820</v>
+        <v>667</v>
       </c>
       <c r="B1146" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1147" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1147" s="13" t="s">
-        <v>821</v>
+        <v>668</v>
       </c>
       <c r="B1147" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1148" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1148" s="13" t="s">
-        <v>750</v>
+        <v>597</v>
       </c>
       <c r="B1148" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1149" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1149" s="14" t="s">
-        <v>822</v>
+        <v>669</v>
       </c>
       <c r="B1149" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1150" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1150" s="14" t="s">
-        <v>823</v>
+        <v>670</v>
       </c>
       <c r="B1150" s="1" t="s">
-        <v>824</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1152" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1152" s="16" t="s">
-        <v>825</v>
+        <v>672</v>
       </c>
       <c r="B1152" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1153" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1153" s="16" t="s">
-        <v>826</v>
+        <v>673</v>
       </c>
       <c r="B1153" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1154" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1154" s="16" t="s">
-        <v>827</v>
+        <v>674</v>
       </c>
       <c r="B1154" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1155" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1155" s="16" t="s">
-        <v>828</v>
+        <v>675</v>
       </c>
       <c r="B1155" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1156" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1156" s="16" t="s">
-        <v>829</v>
+        <v>676</v>
       </c>
       <c r="B1156" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1157" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1157" s="16" t="s">
-        <v>830</v>
+        <v>677</v>
       </c>
       <c r="B1157" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1158" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1158" s="16" t="s">
-        <v>831</v>
+        <v>678</v>
       </c>
       <c r="B1158" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1159" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1159" s="15" t="s">
-        <v>832</v>
+        <v>679</v>
       </c>
       <c r="B1159" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1160" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1160" s="16" t="s">
-        <v>833</v>
+        <v>680</v>
       </c>
       <c r="B1160" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1161" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1161" s="16" t="s">
-        <v>834</v>
+        <v>681</v>
       </c>
       <c r="B1161" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1162" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1162" s="16" t="s">
-        <v>835</v>
+        <v>682</v>
       </c>
       <c r="B1162" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1163" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1163" s="16" t="s">
-        <v>836</v>
+        <v>683</v>
       </c>
       <c r="B1163" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1164" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1164" s="16" t="s">
-        <v>837</v>
+        <v>684</v>
       </c>
       <c r="B1164" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1165" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1165" s="16" t="s">
-        <v>838</v>
+        <v>685</v>
       </c>
       <c r="B1165" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1166" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1166" s="16" t="s">
-        <v>839</v>
+        <v>686</v>
       </c>
       <c r="B1166" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1167" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1167" s="16" t="s">
-        <v>840</v>
+        <v>687</v>
       </c>
       <c r="B1167" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1168" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1168" s="16" t="s">
-        <v>841</v>
+        <v>688</v>
       </c>
       <c r="B1168" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1169" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1169" s="16" t="s">
-        <v>842</v>
+        <v>689</v>
       </c>
       <c r="B1169" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1170" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1170" s="15" t="s">
-        <v>843</v>
+        <v>690</v>
       </c>
       <c r="B1170" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1171" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1171" s="15" t="s">
-        <v>844</v>
+        <v>691</v>
       </c>
       <c r="B1171" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1172" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1172" s="16" t="s">
-        <v>845</v>
+        <v>692</v>
       </c>
       <c r="B1172" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1173" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1173" s="16" t="s">
-        <v>846</v>
+        <v>693</v>
       </c>
       <c r="B1173" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1174" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1174" s="15" t="s">
-        <v>847</v>
+        <v>694</v>
       </c>
       <c r="B1174" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1175" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1175" s="16" t="s">
-        <v>848</v>
+        <v>695</v>
       </c>
       <c r="B1175" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1176" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1176" s="16" t="s">
-        <v>849</v>
+        <v>696</v>
       </c>
       <c r="B1176" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1177" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1177" s="16" t="s">
-        <v>850</v>
+        <v>697</v>
       </c>
       <c r="B1177" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1178" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1178" s="15" t="s">
-        <v>851</v>
+        <v>698</v>
       </c>
       <c r="B1178" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1179" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1179" s="15" t="s">
-        <v>852</v>
+        <v>699</v>
       </c>
       <c r="B1179" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1180" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1180" s="16" t="s">
-        <v>853</v>
+        <v>700</v>
       </c>
       <c r="B1180" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1181" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1181" s="16" t="s">
-        <v>854</v>
+        <v>701</v>
       </c>
       <c r="B1181" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1182" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1182" s="16" t="s">
-        <v>855</v>
+        <v>702</v>
       </c>
       <c r="B1182" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1183" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1183" s="16" t="s">
-        <v>856</v>
+        <v>703</v>
       </c>
       <c r="B1183" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1184" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1184" s="15" t="s">
-        <v>857</v>
+        <v>704</v>
       </c>
       <c r="B1184" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1185" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1185" s="15" t="s">
-        <v>858</v>
+        <v>705</v>
       </c>
       <c r="B1185" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1186" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1186" s="15" t="s">
-        <v>859</v>
+        <v>706</v>
       </c>
       <c r="B1186" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1187" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1187" s="16" t="s">
-        <v>860</v>
+        <v>707</v>
       </c>
       <c r="B1187" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1188" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1188" s="15" t="s">
-        <v>861</v>
+        <v>708</v>
       </c>
       <c r="B1188" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1189" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1189" s="15" t="s">
-        <v>862</v>
+        <v>709</v>
       </c>
       <c r="B1189" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1190" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1190" s="16" t="s">
-        <v>863</v>
+        <v>710</v>
       </c>
       <c r="B1190" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1191" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1191" s="15" t="s">
-        <v>864</v>
+        <v>711</v>
       </c>
       <c r="B1191" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1192" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1192" s="16" t="s">
-        <v>865</v>
+        <v>712</v>
       </c>
       <c r="B1192" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1193" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1193" s="15" t="s">
-        <v>866</v>
+        <v>713</v>
       </c>
       <c r="B1193" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1194" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1194" s="15" t="s">
-        <v>867</v>
+        <v>714</v>
       </c>
       <c r="B1194" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1195" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1195" s="16" t="s">
-        <v>868</v>
+        <v>715</v>
       </c>
       <c r="B1195" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1196" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1196" s="16" t="s">
-        <v>869</v>
+        <v>716</v>
       </c>
       <c r="B1196" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1197" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1197" s="16" t="s">
-        <v>870</v>
+        <v>717</v>
       </c>
       <c r="B1197" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1198" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1198" s="16" t="s">
-        <v>871</v>
+        <v>718</v>
       </c>
       <c r="B1198" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1199" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1199" s="16" t="s">
-        <v>872</v>
+        <v>719</v>
       </c>
       <c r="B1199" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1200" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1200" s="16" t="s">
-        <v>873</v>
+        <v>720</v>
       </c>
       <c r="B1200" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1201" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1201" s="16" t="s">
-        <v>874</v>
+        <v>721</v>
       </c>
       <c r="B1201" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1202" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1202" s="15" t="s">
-        <v>875</v>
+        <v>722</v>
       </c>
       <c r="B1202" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1203" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1203" s="15" t="s">
-        <v>876</v>
+        <v>723</v>
       </c>
       <c r="B1203" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1204" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1204" s="16" t="s">
-        <v>877</v>
+        <v>724</v>
       </c>
       <c r="B1204" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1205" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1205" s="15" t="s">
-        <v>878</v>
+        <v>725</v>
       </c>
       <c r="B1205" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1206" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1206" s="16" t="s">
-        <v>879</v>
+        <v>726</v>
       </c>
       <c r="B1206" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1207" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1207" s="16" t="s">
-        <v>880</v>
+        <v>727</v>
       </c>
       <c r="B1207" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1208" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1208" s="15" t="s">
-        <v>881</v>
+        <v>728</v>
       </c>
       <c r="B1208" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1209" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1209" s="15" t="s">
-        <v>882</v>
+        <v>729</v>
       </c>
       <c r="B1209" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1210" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1210" s="16" t="s">
-        <v>883</v>
+        <v>730</v>
       </c>
       <c r="B1210" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1211" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1211" s="15" t="s">
-        <v>884</v>
+        <v>731</v>
       </c>
       <c r="B1211" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1212" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1212" s="16" t="s">
-        <v>885</v>
+        <v>732</v>
       </c>
       <c r="B1212" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1213" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1213" s="15" t="s">
-        <v>886</v>
+        <v>733</v>
       </c>
       <c r="B1213" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
     <row r="1214" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1214" s="16" t="s">
-        <v>825</v>
+        <v>672</v>
       </c>
       <c r="B1214" s="1" t="s">
-        <v>887</v>
+        <v>734</v>
       </c>
     </row>
   </sheetData>

--- a/on_the_way.xlsx
+++ b/on_the_way.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1625" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="828">
   <si>
     <t>Track</t>
   </si>
@@ -2224,6 +2224,282 @@
   </si>
   <si>
     <t>28.07.26</t>
+  </si>
+  <si>
+    <t>9818442599394</t>
+  </si>
+  <si>
+    <t>465549081115766</t>
+  </si>
+  <si>
+    <t>JT5511185882148</t>
+  </si>
+  <si>
+    <t>465548548886001</t>
+  </si>
+  <si>
+    <t>777432063211602</t>
+  </si>
+  <si>
+    <t>JT5510355734148</t>
+  </si>
+  <si>
+    <t>465548552468967</t>
+  </si>
+  <si>
+    <t>YT8891325773525</t>
+  </si>
+  <si>
+    <t>465549042589756</t>
+  </si>
+  <si>
+    <t>JT5510132982176</t>
+  </si>
+  <si>
+    <t>777432158518297</t>
+  </si>
+  <si>
+    <t>JT5510061906537</t>
+  </si>
+  <si>
+    <t>9818387087110</t>
+  </si>
+  <si>
+    <t>JT5510140227778</t>
+  </si>
+  <si>
+    <t>YT8891880478978</t>
+  </si>
+  <si>
+    <t>JT5510649920333</t>
+  </si>
+  <si>
+    <t>9818387096840</t>
+  </si>
+  <si>
+    <t>YT8890992018243</t>
+  </si>
+  <si>
+    <t>YT8891767150454</t>
+  </si>
+  <si>
+    <t>777430903351626</t>
+  </si>
+  <si>
+    <t>YT8891881900904</t>
+  </si>
+  <si>
+    <t>777432059013391</t>
+  </si>
+  <si>
+    <t>9818446077705</t>
+  </si>
+  <si>
+    <t>79126284650210</t>
+  </si>
+  <si>
+    <t>777432088183502</t>
+  </si>
+  <si>
+    <t>YT8891278714105</t>
+  </si>
+  <si>
+    <t>JT5510135579978</t>
+  </si>
+  <si>
+    <t>YT8891795116590</t>
+  </si>
+  <si>
+    <t>777430920982555</t>
+  </si>
+  <si>
+    <t>465546740549273</t>
+  </si>
+  <si>
+    <t>YT8891580846420</t>
+  </si>
+  <si>
+    <t>JT5511184366216</t>
+  </si>
+  <si>
+    <t>465548264826153</t>
+  </si>
+  <si>
+    <t>JT5510597159096</t>
+  </si>
+  <si>
+    <t>777431960209962</t>
+  </si>
+  <si>
+    <t>9818361400289</t>
+  </si>
+  <si>
+    <t>79126749253511</t>
+  </si>
+  <si>
+    <t>9818383563980</t>
+  </si>
+  <si>
+    <t>YT8891506440392</t>
+  </si>
+  <si>
+    <t>465547146132090</t>
+  </si>
+  <si>
+    <t>777430868980561</t>
+  </si>
+  <si>
+    <t>465549582038706</t>
+  </si>
+  <si>
+    <t>777431385521296</t>
+  </si>
+  <si>
+    <t>YT8891831940365</t>
+  </si>
+  <si>
+    <t>79124757791321</t>
+  </si>
+  <si>
+    <t>79126478668925</t>
+  </si>
+  <si>
+    <t>79126520553614</t>
+  </si>
+  <si>
+    <t>79020619222184</t>
+  </si>
+  <si>
+    <t>9818447906456</t>
+  </si>
+  <si>
+    <t>9818373142201</t>
+  </si>
+  <si>
+    <t>777432167222781</t>
+  </si>
+  <si>
+    <t>79126606315278</t>
+  </si>
+  <si>
+    <t>9818377794315</t>
+  </si>
+  <si>
+    <t>465543566777196</t>
+  </si>
+  <si>
+    <t>9818380085725</t>
+  </si>
+  <si>
+    <t>79126201907033</t>
+  </si>
+  <si>
+    <t>79126384928607</t>
+  </si>
+  <si>
+    <t>9818336689278</t>
+  </si>
+  <si>
+    <t>YT8891909119176</t>
+  </si>
+  <si>
+    <t>79126562991215</t>
+  </si>
+  <si>
+    <t>79126625094930</t>
+  </si>
+  <si>
+    <t>9818326022938</t>
+  </si>
+  <si>
+    <t>9818382717349</t>
+  </si>
+  <si>
+    <t>9818341208609</t>
+  </si>
+  <si>
+    <t>79126622450624</t>
+  </si>
+  <si>
+    <t>9818387986149</t>
+  </si>
+  <si>
+    <t>79126250681329</t>
+  </si>
+  <si>
+    <t>79126709533161</t>
+  </si>
+  <si>
+    <t>9818368763844</t>
+  </si>
+  <si>
+    <t>9818345684947</t>
+  </si>
+  <si>
+    <t>79126334420888</t>
+  </si>
+  <si>
+    <t>9818355457295</t>
+  </si>
+  <si>
+    <t>79126665761106</t>
+  </si>
+  <si>
+    <t>9818385955633</t>
+  </si>
+  <si>
+    <t>777432125697657</t>
+  </si>
+  <si>
+    <t>9818357476853</t>
+  </si>
+  <si>
+    <t>777431127882333</t>
+  </si>
+  <si>
+    <t>465546553155218</t>
+  </si>
+  <si>
+    <t>79126700521951</t>
+  </si>
+  <si>
+    <t>9818382806860</t>
+  </si>
+  <si>
+    <t>79126824946485</t>
+  </si>
+  <si>
+    <t>79125662919124</t>
+  </si>
+  <si>
+    <t>79126657805236</t>
+  </si>
+  <si>
+    <t>79126896512999</t>
+  </si>
+  <si>
+    <t>79125661408398</t>
+  </si>
+  <si>
+    <t>79126995864544</t>
+  </si>
+  <si>
+    <t>79022353735996</t>
+  </si>
+  <si>
+    <t>79126562788491</t>
+  </si>
+  <si>
+    <t>79127010733647</t>
+  </si>
+  <si>
+    <t>777432092100584</t>
+  </si>
+  <si>
+    <t>YT8891897134557</t>
+  </si>
+  <si>
+    <t>03.08.26</t>
   </si>
 </sst>
 </file>
@@ -2285,13 +2561,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyBorder="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyBorder="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2301,9 +2580,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -2344,10 +2620,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" quotePrefix="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 3" xfId="2"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
@@ -2878,7 +3161,7 @@
       </c>
     </row>
     <row r="2" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>104</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -2886,7 +3169,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>105</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -2894,7 +3177,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="9" t="s">
         <v>106</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -2902,7 +3185,7 @@
       </c>
     </row>
     <row r="5" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="9" t="s">
         <v>107</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -2910,7 +3193,7 @@
       </c>
     </row>
     <row r="6" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="9" t="s">
         <v>108</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -2918,7 +3201,7 @@
       </c>
     </row>
     <row r="7" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="9" t="s">
         <v>109</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -2926,7 +3209,7 @@
       </c>
     </row>
     <row r="8" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="9" t="s">
         <v>110</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -2934,7 +3217,7 @@
       </c>
     </row>
     <row r="9" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="8" t="s">
         <v>111</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -2942,7 +3225,7 @@
       </c>
     </row>
     <row r="10" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="9" t="s">
         <v>112</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -2950,7 +3233,7 @@
       </c>
     </row>
     <row r="11" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="8" t="s">
         <v>113</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -2958,7 +3241,7 @@
       </c>
     </row>
     <row r="12" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="8" t="s">
         <v>114</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -2966,7 +3249,7 @@
       </c>
     </row>
     <row r="13" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="9" t="s">
         <v>115</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -2974,7 +3257,7 @@
       </c>
     </row>
     <row r="14" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="9" t="s">
         <v>116</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -2982,7 +3265,7 @@
       </c>
     </row>
     <row r="15" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="9" t="s">
         <v>117</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -2990,7 +3273,7 @@
       </c>
     </row>
     <row r="16" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="9" t="s">
         <v>118</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -2998,7 +3281,7 @@
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="9" t="s">
         <v>119</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -3006,7 +3289,7 @@
       </c>
     </row>
     <row r="18" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="8" t="s">
         <v>120</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -3014,7 +3297,7 @@
       </c>
     </row>
     <row r="19" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="9" t="s">
         <v>121</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -3022,7 +3305,7 @@
       </c>
     </row>
     <row r="20" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="9" t="s">
         <v>122</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -3030,7 +3313,7 @@
       </c>
     </row>
     <row r="21" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="8" t="s">
         <v>123</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -3038,7 +3321,7 @@
       </c>
     </row>
     <row r="22" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="9" t="s">
         <v>124</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -3046,7 +3329,7 @@
       </c>
     </row>
     <row r="23" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="9" t="s">
         <v>125</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -3054,7 +3337,7 @@
       </c>
     </row>
     <row r="24" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="9" t="s">
         <v>126</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -3062,7 +3345,7 @@
       </c>
     </row>
     <row r="25" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="8" t="s">
         <v>127</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -3070,7 +3353,7 @@
       </c>
     </row>
     <row r="26" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="9" t="s">
         <v>128</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -3078,7 +3361,7 @@
       </c>
     </row>
     <row r="27" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="8" t="s">
         <v>129</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -3086,7 +3369,7 @@
       </c>
     </row>
     <row r="28" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="8" t="s">
         <v>130</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -3094,7 +3377,7 @@
       </c>
     </row>
     <row r="29" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="8" t="s">
         <v>131</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -3102,7 +3385,7 @@
       </c>
     </row>
     <row r="30" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="9" t="s">
         <v>132</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -3110,7 +3393,7 @@
       </c>
     </row>
     <row r="31" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A31" s="9" t="s">
+      <c r="A31" s="8" t="s">
         <v>133</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -3118,7 +3401,7 @@
       </c>
     </row>
     <row r="32" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A32" s="9" t="s">
+      <c r="A32" s="8" t="s">
         <v>134</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -3126,7 +3409,7 @@
       </c>
     </row>
     <row r="33" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A33" s="9" t="s">
+      <c r="A33" s="8" t="s">
         <v>135</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -3134,7 +3417,7 @@
       </c>
     </row>
     <row r="34" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A34" s="10" t="s">
+      <c r="A34" s="9" t="s">
         <v>136</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -3142,7 +3425,7 @@
       </c>
     </row>
     <row r="35" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A35" s="9" t="s">
+      <c r="A35" s="8" t="s">
         <v>137</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -3150,7 +3433,7 @@
       </c>
     </row>
     <row r="36" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A36" s="9" t="s">
+      <c r="A36" s="8" t="s">
         <v>138</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -3158,7 +3441,7 @@
       </c>
     </row>
     <row r="37" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="9" t="s">
         <v>139</v>
       </c>
       <c r="B37" s="1" t="s">
@@ -3166,7 +3449,7 @@
       </c>
     </row>
     <row r="38" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A38" s="9" t="s">
+      <c r="A38" s="8" t="s">
         <v>140</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -3174,7 +3457,7 @@
       </c>
     </row>
     <row r="39" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A39" s="9" t="s">
+      <c r="A39" s="8" t="s">
         <v>141</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -3182,7 +3465,7 @@
       </c>
     </row>
     <row r="40" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A40" s="10" t="s">
+      <c r="A40" s="9" t="s">
         <v>142</v>
       </c>
       <c r="B40" s="1" t="s">
@@ -3190,7 +3473,7 @@
       </c>
     </row>
     <row r="41" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A41" s="10" t="s">
+      <c r="A41" s="9" t="s">
         <v>143</v>
       </c>
       <c r="B41" s="1" t="s">
@@ -3198,7 +3481,7 @@
       </c>
     </row>
     <row r="42" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A42" s="10" t="s">
+      <c r="A42" s="9" t="s">
         <v>144</v>
       </c>
       <c r="B42" s="1" t="s">
@@ -3206,7 +3489,7 @@
       </c>
     </row>
     <row r="43" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A43" s="9" t="s">
+      <c r="A43" s="8" t="s">
         <v>145</v>
       </c>
       <c r="B43" s="1" t="s">
@@ -3214,7 +3497,7 @@
       </c>
     </row>
     <row r="44" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A44" s="9" t="s">
+      <c r="A44" s="8" t="s">
         <v>146</v>
       </c>
       <c r="B44" s="1" t="s">
@@ -3222,7 +3505,7 @@
       </c>
     </row>
     <row r="45" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A45" s="9" t="s">
+      <c r="A45" s="8" t="s">
         <v>147</v>
       </c>
       <c r="B45" s="1" t="s">
@@ -3230,7 +3513,7 @@
       </c>
     </row>
     <row r="46" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A46" s="10" t="s">
+      <c r="A46" s="9" t="s">
         <v>148</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -3238,7 +3521,7 @@
       </c>
     </row>
     <row r="47" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A47" s="10" t="s">
+      <c r="A47" s="9" t="s">
         <v>149</v>
       </c>
       <c r="B47" s="1" t="s">
@@ -3246,7 +3529,7 @@
       </c>
     </row>
     <row r="48" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A48" s="10" t="s">
+      <c r="A48" s="9" t="s">
         <v>150</v>
       </c>
       <c r="B48" s="1" t="s">
@@ -3254,7 +3537,7 @@
       </c>
     </row>
     <row r="49" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A49" s="9" t="s">
+      <c r="A49" s="8" t="s">
         <v>151</v>
       </c>
       <c r="B49" s="1" t="s">
@@ -3262,7 +3545,7 @@
       </c>
     </row>
     <row r="50" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A50" s="10" t="s">
+      <c r="A50" s="9" t="s">
         <v>152</v>
       </c>
       <c r="B50" s="1" t="s">
@@ -3270,7 +3553,7 @@
       </c>
     </row>
     <row r="51" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A51" s="10" t="s">
+      <c r="A51" s="9" t="s">
         <v>153</v>
       </c>
       <c r="B51" s="1" t="s">
@@ -3278,7 +3561,7 @@
       </c>
     </row>
     <row r="52" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A52" s="10" t="s">
+      <c r="A52" s="9" t="s">
         <v>154</v>
       </c>
       <c r="B52" s="1" t="s">
@@ -3286,7 +3569,7 @@
       </c>
     </row>
     <row r="53" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A53" s="10" t="s">
+      <c r="A53" s="9" t="s">
         <v>155</v>
       </c>
       <c r="B53" s="1" t="s">
@@ -3294,7 +3577,7 @@
       </c>
     </row>
     <row r="54" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A54" s="10" t="s">
+      <c r="A54" s="9" t="s">
         <v>156</v>
       </c>
       <c r="B54" s="1" t="s">
@@ -3302,7 +3585,7 @@
       </c>
     </row>
     <row r="55" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A55" s="10" t="s">
+      <c r="A55" s="9" t="s">
         <v>157</v>
       </c>
       <c r="B55" s="1" t="s">
@@ -3310,7 +3593,7 @@
       </c>
     </row>
     <row r="56" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A56" s="9" t="s">
+      <c r="A56" s="8" t="s">
         <v>158</v>
       </c>
       <c r="B56" s="1" t="s">
@@ -3318,7 +3601,7 @@
       </c>
     </row>
     <row r="57" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A57" s="9" t="s">
+      <c r="A57" s="8" t="s">
         <v>159</v>
       </c>
       <c r="B57" s="1" t="s">
@@ -3326,7 +3609,7 @@
       </c>
     </row>
     <row r="58" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A58" s="10" t="s">
+      <c r="A58" s="9" t="s">
         <v>160</v>
       </c>
       <c r="B58" s="1" t="s">
@@ -3334,7 +3617,7 @@
       </c>
     </row>
     <row r="59" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A59" s="9" t="s">
+      <c r="A59" s="8" t="s">
         <v>161</v>
       </c>
       <c r="B59" s="1" t="s">
@@ -3342,7 +3625,7 @@
       </c>
     </row>
     <row r="60" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A60" s="10" t="s">
+      <c r="A60" s="9" t="s">
         <v>162</v>
       </c>
       <c r="B60" s="1" t="s">
@@ -3350,7 +3633,7 @@
       </c>
     </row>
     <row r="61" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A61" s="10" t="s">
+      <c r="A61" s="9" t="s">
         <v>163</v>
       </c>
       <c r="B61" s="1" t="s">
@@ -3358,7 +3641,7 @@
       </c>
     </row>
     <row r="62" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A62" s="10" t="s">
+      <c r="A62" s="9" t="s">
         <v>164</v>
       </c>
       <c r="B62" s="1" t="s">
@@ -3366,7 +3649,7 @@
       </c>
     </row>
     <row r="63" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A63" s="10" t="s">
+      <c r="A63" s="9" t="s">
         <v>165</v>
       </c>
       <c r="B63" s="1" t="s">
@@ -3374,7 +3657,7 @@
       </c>
     </row>
     <row r="64" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A64" s="9" t="s">
+      <c r="A64" s="8" t="s">
         <v>166</v>
       </c>
       <c r="B64" s="1" t="s">
@@ -3382,7 +3665,7 @@
       </c>
     </row>
     <row r="65" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A65" s="9" t="s">
+      <c r="A65" s="8" t="s">
         <v>167</v>
       </c>
       <c r="B65" s="1" t="s">
@@ -3390,7 +3673,7 @@
       </c>
     </row>
     <row r="66" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A66" s="9" t="s">
+      <c r="A66" s="8" t="s">
         <v>168</v>
       </c>
       <c r="B66" s="1" t="s">
@@ -3398,7 +3681,7 @@
       </c>
     </row>
     <row r="67" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A67" s="10" t="s">
+      <c r="A67" s="9" t="s">
         <v>169</v>
       </c>
       <c r="B67" s="1" t="s">
@@ -3406,7 +3689,7 @@
       </c>
     </row>
     <row r="68" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A68" s="9" t="s">
+      <c r="A68" s="8" t="s">
         <v>170</v>
       </c>
       <c r="B68" s="1" t="s">
@@ -3414,7 +3697,7 @@
       </c>
     </row>
     <row r="69" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A69" s="10" t="s">
+      <c r="A69" s="9" t="s">
         <v>171</v>
       </c>
       <c r="B69" s="1" t="s">
@@ -3422,7 +3705,7 @@
       </c>
     </row>
     <row r="70" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A70" s="10" t="s">
+      <c r="A70" s="9" t="s">
         <v>172</v>
       </c>
       <c r="B70" s="1" t="s">
@@ -3430,7 +3713,7 @@
       </c>
     </row>
     <row r="71" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A71" s="10" t="s">
+      <c r="A71" s="9" t="s">
         <v>173</v>
       </c>
       <c r="B71" s="1" t="s">
@@ -3438,7 +3721,7 @@
       </c>
     </row>
     <row r="72" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A72" s="9" t="s">
+      <c r="A72" s="8" t="s">
         <v>174</v>
       </c>
       <c r="B72" s="1" t="s">
@@ -3446,7 +3729,7 @@
       </c>
     </row>
     <row r="73" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A73" s="9" t="s">
+      <c r="A73" s="8" t="s">
         <v>175</v>
       </c>
       <c r="B73" s="1" t="s">
@@ -3454,7 +3737,7 @@
       </c>
     </row>
     <row r="74" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A74" s="9" t="s">
+      <c r="A74" s="8" t="s">
         <v>176</v>
       </c>
       <c r="B74" s="1" t="s">
@@ -3462,7 +3745,7 @@
       </c>
     </row>
     <row r="75" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A75" s="10" t="s">
+      <c r="A75" s="9" t="s">
         <v>177</v>
       </c>
       <c r="B75" s="1" t="s">
@@ -3470,7 +3753,7 @@
       </c>
     </row>
     <row r="76" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A76" s="9" t="s">
+      <c r="A76" s="8" t="s">
         <v>178</v>
       </c>
       <c r="B76" s="1" t="s">
@@ -3478,7 +3761,7 @@
       </c>
     </row>
     <row r="77" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A77" s="9" t="s">
+      <c r="A77" s="8" t="s">
         <v>179</v>
       </c>
       <c r="B77" s="1" t="s">
@@ -3486,7 +3769,7 @@
       </c>
     </row>
     <row r="78" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A78" s="10" t="s">
+      <c r="A78" s="9" t="s">
         <v>180</v>
       </c>
       <c r="B78" s="1" t="s">
@@ -3494,7 +3777,7 @@
       </c>
     </row>
     <row r="79" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A79" s="10" t="s">
+      <c r="A79" s="9" t="s">
         <v>181</v>
       </c>
       <c r="B79" s="1" t="s">
@@ -3502,7 +3785,7 @@
       </c>
     </row>
     <row r="80" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A80" s="10" t="s">
+      <c r="A80" s="9" t="s">
         <v>182</v>
       </c>
       <c r="B80" s="1" t="s">
@@ -3510,7 +3793,7 @@
       </c>
     </row>
     <row r="81" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A81" s="9" t="s">
+      <c r="A81" s="8" t="s">
         <v>183</v>
       </c>
       <c r="B81" s="1" t="s">
@@ -3518,7 +3801,7 @@
       </c>
     </row>
     <row r="82" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A82" s="10" t="s">
+      <c r="A82" s="9" t="s">
         <v>184</v>
       </c>
       <c r="B82" s="1" t="s">
@@ -3526,7 +3809,7 @@
       </c>
     </row>
     <row r="83" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A83" s="10" t="s">
+      <c r="A83" s="9" t="s">
         <v>185</v>
       </c>
       <c r="B83" s="1" t="s">
@@ -3535,7 +3818,7 @@
       <c r="D83"/>
     </row>
     <row r="84" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A84" s="10" t="s">
+      <c r="A84" s="9" t="s">
         <v>186</v>
       </c>
       <c r="B84" s="1" t="s">
@@ -3544,7 +3827,7 @@
       <c r="D84"/>
     </row>
     <row r="85" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A85" s="10" t="s">
+      <c r="A85" s="9" t="s">
         <v>187</v>
       </c>
       <c r="B85" s="1" t="s">
@@ -3553,7 +3836,7 @@
       <c r="D85"/>
     </row>
     <row r="86" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A86" s="9" t="s">
+      <c r="A86" s="8" t="s">
         <v>188</v>
       </c>
       <c r="B86" s="1" t="s">
@@ -3562,7 +3845,7 @@
       <c r="D86"/>
     </row>
     <row r="87" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A87" s="9" t="s">
+      <c r="A87" s="8" t="s">
         <v>189</v>
       </c>
       <c r="B87" s="1" t="s">
@@ -3571,7 +3854,7 @@
       <c r="D87"/>
     </row>
     <row r="88" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A88" s="10" t="s">
+      <c r="A88" s="9" t="s">
         <v>190</v>
       </c>
       <c r="B88" s="1" t="s">
@@ -3580,7 +3863,7 @@
       <c r="D88"/>
     </row>
     <row r="89" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A89" s="9" t="s">
+      <c r="A89" s="8" t="s">
         <v>191</v>
       </c>
       <c r="B89" s="1" t="s">
@@ -3589,7 +3872,7 @@
       <c r="D89"/>
     </row>
     <row r="90" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A90" s="10" t="s">
+      <c r="A90" s="9" t="s">
         <v>192</v>
       </c>
       <c r="B90" s="1" t="s">
@@ -3598,7 +3881,7 @@
       <c r="D90"/>
     </row>
     <row r="91" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A91" s="10" t="s">
+      <c r="A91" s="9" t="s">
         <v>193</v>
       </c>
       <c r="B91" s="1" t="s">
@@ -3607,7 +3890,7 @@
       <c r="D91"/>
     </row>
     <row r="92" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A92" s="10" t="s">
+      <c r="A92" s="9" t="s">
         <v>194</v>
       </c>
       <c r="B92" s="1" t="s">
@@ -3616,7 +3899,7 @@
       <c r="D92"/>
     </row>
     <row r="93" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A93" s="10" t="s">
+      <c r="A93" s="9" t="s">
         <v>195</v>
       </c>
       <c r="B93" s="1" t="s">
@@ -3625,7 +3908,7 @@
       <c r="D93"/>
     </row>
     <row r="94" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A94" s="10" t="s">
+      <c r="A94" s="9" t="s">
         <v>196</v>
       </c>
       <c r="B94" s="1" t="s">
@@ -3634,7 +3917,7 @@
       <c r="D94"/>
     </row>
     <row r="95" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A95" s="10" t="s">
+      <c r="A95" s="9" t="s">
         <v>197</v>
       </c>
       <c r="B95" s="1" t="s">
@@ -3643,7 +3926,7 @@
       <c r="D95"/>
     </row>
     <row r="96" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A96" s="10" t="s">
+      <c r="A96" s="9" t="s">
         <v>198</v>
       </c>
       <c r="B96" s="1" t="s">
@@ -3652,7 +3935,7 @@
       <c r="D96"/>
     </row>
     <row r="97" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A97" s="9" t="s">
+      <c r="A97" s="8" t="s">
         <v>199</v>
       </c>
       <c r="B97" s="1" t="s">
@@ -3661,7 +3944,7 @@
       <c r="D97"/>
     </row>
     <row r="98" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A98" s="10" t="s">
+      <c r="A98" s="9" t="s">
         <v>200</v>
       </c>
       <c r="B98" s="1" t="s">
@@ -3670,7 +3953,7 @@
       <c r="D98"/>
     </row>
     <row r="99" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A99" s="10" t="s">
+      <c r="A99" s="9" t="s">
         <v>201</v>
       </c>
       <c r="B99" s="1" t="s">
@@ -3679,7 +3962,7 @@
       <c r="D99"/>
     </row>
     <row r="100" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A100" s="10" t="s">
+      <c r="A100" s="9" t="s">
         <v>202</v>
       </c>
       <c r="B100" s="1" t="s">
@@ -3688,7 +3971,7 @@
       <c r="D100"/>
     </row>
     <row r="101" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A101" s="10" t="s">
+      <c r="A101" s="9" t="s">
         <v>203</v>
       </c>
       <c r="B101" s="1" t="s">
@@ -3697,7 +3980,7 @@
       <c r="D101"/>
     </row>
     <row r="102" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A102" s="10" t="s">
+      <c r="A102" s="9" t="s">
         <v>204</v>
       </c>
       <c r="B102" s="1" t="s">
@@ -3706,7 +3989,7 @@
       <c r="D102"/>
     </row>
     <row r="103" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A103" s="10" t="s">
+      <c r="A103" s="9" t="s">
         <v>205</v>
       </c>
       <c r="B103" s="1" t="s">
@@ -3715,7 +3998,7 @@
       <c r="D103"/>
     </row>
     <row r="104" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A104" s="9" t="s">
+      <c r="A104" s="8" t="s">
         <v>206</v>
       </c>
       <c r="B104" s="1" t="s">
@@ -3724,7 +4007,7 @@
       <c r="D104"/>
     </row>
     <row r="105" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A105" s="10" t="s">
+      <c r="A105" s="9" t="s">
         <v>207</v>
       </c>
       <c r="B105" s="1" t="s">
@@ -3733,7 +4016,7 @@
       <c r="D105"/>
     </row>
     <row r="106" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A106" s="10" t="s">
+      <c r="A106" s="9" t="s">
         <v>208</v>
       </c>
       <c r="B106" s="1" t="s">
@@ -3742,7 +4025,7 @@
       <c r="D106"/>
     </row>
     <row r="107" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A107" s="10" t="s">
+      <c r="A107" s="9" t="s">
         <v>209</v>
       </c>
       <c r="B107" s="1" t="s">
@@ -3751,7 +4034,7 @@
       <c r="D107"/>
     </row>
     <row r="108" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A108" s="10" t="s">
+      <c r="A108" s="9" t="s">
         <v>210</v>
       </c>
       <c r="B108" s="1" t="s">
@@ -3760,7 +4043,7 @@
       <c r="D108"/>
     </row>
     <row r="109" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A109" s="10" t="s">
+      <c r="A109" s="9" t="s">
         <v>211</v>
       </c>
       <c r="B109" s="1" t="s">
@@ -3769,7 +4052,7 @@
       <c r="D109"/>
     </row>
     <row r="110" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A110" s="10" t="s">
+      <c r="A110" s="9" t="s">
         <v>212</v>
       </c>
       <c r="B110" s="1" t="s">
@@ -3778,7 +4061,7 @@
       <c r="D110"/>
     </row>
     <row r="111" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A111" s="9" t="s">
+      <c r="A111" s="8" t="s">
         <v>213</v>
       </c>
       <c r="B111" s="1" t="s">
@@ -3787,7 +4070,7 @@
       <c r="D111"/>
     </row>
     <row r="112" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A112" s="10" t="s">
+      <c r="A112" s="9" t="s">
         <v>214</v>
       </c>
       <c r="B112" s="1" t="s">
@@ -3796,7 +4079,7 @@
       <c r="D112"/>
     </row>
     <row r="113" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A113" s="10" t="s">
+      <c r="A113" s="9" t="s">
         <v>215</v>
       </c>
       <c r="B113" s="1" t="s">
@@ -3805,7 +4088,7 @@
       <c r="D113"/>
     </row>
     <row r="114" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A114" s="10" t="s">
+      <c r="A114" s="9" t="s">
         <v>216</v>
       </c>
       <c r="B114" s="1" t="s">
@@ -3814,7 +4097,7 @@
       <c r="D114"/>
     </row>
     <row r="115" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A115" s="10" t="s">
+      <c r="A115" s="9" t="s">
         <v>217</v>
       </c>
       <c r="B115" s="1" t="s">
@@ -3823,7 +4106,7 @@
       <c r="D115"/>
     </row>
     <row r="116" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A116" s="10" t="s">
+      <c r="A116" s="9" t="s">
         <v>218</v>
       </c>
       <c r="B116" s="1" t="s">
@@ -3832,7 +4115,7 @@
       <c r="D116"/>
     </row>
     <row r="117" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A117" s="10" t="s">
+      <c r="A117" s="9" t="s">
         <v>219</v>
       </c>
       <c r="B117" s="1" t="s">
@@ -3841,7 +4124,7 @@
       <c r="D117"/>
     </row>
     <row r="118" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A118" s="10" t="s">
+      <c r="A118" s="9" t="s">
         <v>220</v>
       </c>
       <c r="B118" s="1" t="s">
@@ -3850,7 +4133,7 @@
       <c r="D118"/>
     </row>
     <row r="119" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A119" s="10" t="s">
+      <c r="A119" s="9" t="s">
         <v>221</v>
       </c>
       <c r="B119" s="1" t="s">
@@ -3859,7 +4142,7 @@
       <c r="D119"/>
     </row>
     <row r="120" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A120" s="10" t="s">
+      <c r="A120" s="9" t="s">
         <v>222</v>
       </c>
       <c r="B120" s="1" t="s">
@@ -3868,7 +4151,7 @@
       <c r="D120"/>
     </row>
     <row r="121" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A121" s="10" t="s">
+      <c r="A121" s="9" t="s">
         <v>223</v>
       </c>
       <c r="B121" s="1" t="s">
@@ -3877,7 +4160,7 @@
       <c r="D121"/>
     </row>
     <row r="122" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A122" s="10" t="s">
+      <c r="A122" s="9" t="s">
         <v>106</v>
       </c>
       <c r="B122" s="1" t="s">
@@ -3890,653 +4173,653 @@
       <c r="D123"/>
     </row>
     <row r="124" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A124" s="15" t="s">
+      <c r="A124" s="14" t="s">
         <v>597</v>
       </c>
-      <c r="B124" s="17" t="s">
+      <c r="B124" s="16" t="s">
         <v>735</v>
       </c>
       <c r="D124"/>
     </row>
     <row r="125" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A125" s="16" t="s">
+      <c r="A125" s="15" t="s">
         <v>598</v>
       </c>
-      <c r="B125" s="17" t="s">
+      <c r="B125" s="16" t="s">
         <v>735</v>
       </c>
       <c r="D125"/>
     </row>
     <row r="126" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A126" s="16" t="s">
+      <c r="A126" s="15" t="s">
         <v>599</v>
       </c>
-      <c r="B126" s="17" t="s">
+      <c r="B126" s="16" t="s">
         <v>735</v>
       </c>
       <c r="D126"/>
     </row>
     <row r="127" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A127" s="16" t="s">
+      <c r="A127" s="15" t="s">
         <v>600</v>
       </c>
-      <c r="B127" s="17" t="s">
+      <c r="B127" s="16" t="s">
         <v>735</v>
       </c>
       <c r="D127"/>
     </row>
     <row r="128" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A128" s="16" t="s">
+      <c r="A128" s="15" t="s">
         <v>601</v>
       </c>
-      <c r="B128" s="17" t="s">
+      <c r="B128" s="16" t="s">
         <v>735</v>
       </c>
       <c r="D128"/>
     </row>
     <row r="129" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A129" s="16" t="s">
+      <c r="A129" s="15" t="s">
         <v>602</v>
       </c>
-      <c r="B129" s="17" t="s">
+      <c r="B129" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="130" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A130" s="16" t="s">
+      <c r="A130" s="15" t="s">
         <v>603</v>
       </c>
-      <c r="B130" s="17" t="s">
+      <c r="B130" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="131" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A131" s="15" t="s">
+      <c r="A131" s="14" t="s">
         <v>604</v>
       </c>
-      <c r="B131" s="17" t="s">
+      <c r="B131" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="132" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A132" s="16" t="s">
+      <c r="A132" s="15" t="s">
         <v>605</v>
       </c>
-      <c r="B132" s="17" t="s">
+      <c r="B132" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="133" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A133" s="16" t="s">
+      <c r="A133" s="15" t="s">
         <v>606</v>
       </c>
-      <c r="B133" s="17" t="s">
+      <c r="B133" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="134" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A134" s="16" t="s">
+      <c r="A134" s="15" t="s">
         <v>607</v>
       </c>
-      <c r="B134" s="17" t="s">
+      <c r="B134" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="135" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A135" s="15" t="s">
+      <c r="A135" s="14" t="s">
         <v>608</v>
       </c>
-      <c r="B135" s="17" t="s">
+      <c r="B135" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="136" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A136" s="16" t="s">
+      <c r="A136" s="15" t="s">
         <v>609</v>
       </c>
-      <c r="B136" s="17" t="s">
+      <c r="B136" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="137" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A137" s="16" t="s">
+      <c r="A137" s="15" t="s">
         <v>610</v>
       </c>
-      <c r="B137" s="17" t="s">
+      <c r="B137" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="138" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A138" s="16" t="s">
+      <c r="A138" s="15" t="s">
         <v>611</v>
       </c>
-      <c r="B138" s="17" t="s">
+      <c r="B138" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="139" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A139" s="15" t="s">
+      <c r="A139" s="14" t="s">
         <v>612</v>
       </c>
-      <c r="B139" s="17" t="s">
+      <c r="B139" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="140" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A140" s="16" t="s">
+      <c r="A140" s="15" t="s">
         <v>613</v>
       </c>
-      <c r="B140" s="17" t="s">
+      <c r="B140" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="141" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A141" s="16" t="s">
+      <c r="A141" s="15" t="s">
         <v>614</v>
       </c>
-      <c r="B141" s="17" t="s">
+      <c r="B141" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="142" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A142" s="16" t="s">
+      <c r="A142" s="15" t="s">
         <v>615</v>
       </c>
-      <c r="B142" s="17" t="s">
+      <c r="B142" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="143" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A143" s="16" t="s">
+      <c r="A143" s="15" t="s">
         <v>616</v>
       </c>
-      <c r="B143" s="17" t="s">
+      <c r="B143" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="144" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A144" s="16" t="s">
+      <c r="A144" s="15" t="s">
         <v>616</v>
       </c>
-      <c r="B144" s="17" t="s">
+      <c r="B144" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="145" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A145" s="16" t="s">
+      <c r="A145" s="15" t="s">
         <v>617</v>
       </c>
-      <c r="B145" s="17" t="s">
+      <c r="B145" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="146" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A146" s="16" t="s">
+      <c r="A146" s="15" t="s">
         <v>618</v>
       </c>
-      <c r="B146" s="17" t="s">
+      <c r="B146" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="147" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A147" s="15" t="s">
+      <c r="A147" s="14" t="s">
         <v>619</v>
       </c>
-      <c r="B147" s="17" t="s">
+      <c r="B147" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="148" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A148" s="15" t="s">
+      <c r="A148" s="14" t="s">
         <v>620</v>
       </c>
-      <c r="B148" s="17" t="s">
+      <c r="B148" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="149" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A149" s="16" t="s">
+      <c r="A149" s="15" t="s">
         <v>621</v>
       </c>
-      <c r="B149" s="17" t="s">
+      <c r="B149" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="150" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A150" s="16" t="s">
+      <c r="A150" s="15" t="s">
         <v>622</v>
       </c>
-      <c r="B150" s="17" t="s">
+      <c r="B150" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="151" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A151" s="16" t="s">
+      <c r="A151" s="15" t="s">
         <v>623</v>
       </c>
-      <c r="B151" s="17" t="s">
+      <c r="B151" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="152" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A152" s="15" t="s">
+      <c r="A152" s="14" t="s">
         <v>624</v>
       </c>
-      <c r="B152" s="17" t="s">
+      <c r="B152" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="153" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A153" s="16" t="s">
+      <c r="A153" s="15" t="s">
         <v>625</v>
       </c>
-      <c r="B153" s="17" t="s">
+      <c r="B153" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="154" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A154" s="16" t="s">
+      <c r="A154" s="15" t="s">
         <v>626</v>
       </c>
-      <c r="B154" s="17" t="s">
+      <c r="B154" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="155" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A155" s="16" t="s">
+      <c r="A155" s="15" t="s">
         <v>627</v>
       </c>
-      <c r="B155" s="17" t="s">
+      <c r="B155" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="156" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A156" s="16" t="s">
+      <c r="A156" s="15" t="s">
         <v>628</v>
       </c>
-      <c r="B156" s="17" t="s">
+      <c r="B156" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="157" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A157" s="16" t="s">
+      <c r="A157" s="15" t="s">
         <v>629</v>
       </c>
-      <c r="B157" s="17" t="s">
+      <c r="B157" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="158" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A158" s="15" t="s">
+      <c r="A158" s="14" t="s">
         <v>630</v>
       </c>
-      <c r="B158" s="17" t="s">
+      <c r="B158" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="159" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A159" s="15" t="s">
+      <c r="A159" s="14" t="s">
         <v>631</v>
       </c>
-      <c r="B159" s="17" t="s">
+      <c r="B159" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="160" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A160" s="15" t="s">
+      <c r="A160" s="14" t="s">
         <v>632</v>
       </c>
-      <c r="B160" s="17" t="s">
+      <c r="B160" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="161" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A161" s="16" t="s">
+      <c r="A161" s="15" t="s">
         <v>633</v>
       </c>
-      <c r="B161" s="17" t="s">
+      <c r="B161" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="162" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A162" s="16" t="s">
+      <c r="A162" s="15" t="s">
         <v>634</v>
       </c>
-      <c r="B162" s="17" t="s">
+      <c r="B162" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="163" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A163" s="16" t="s">
+      <c r="A163" s="15" t="s">
         <v>635</v>
       </c>
-      <c r="B163" s="17" t="s">
+      <c r="B163" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="164" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A164" s="16" t="s">
+      <c r="A164" s="15" t="s">
         <v>636</v>
       </c>
-      <c r="B164" s="17" t="s">
+      <c r="B164" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="165" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A165" s="15" t="s">
+      <c r="A165" s="14" t="s">
         <v>637</v>
       </c>
-      <c r="B165" s="17" t="s">
+      <c r="B165" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="166" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A166" s="16" t="s">
+      <c r="A166" s="15" t="s">
         <v>638</v>
       </c>
-      <c r="B166" s="17" t="s">
+      <c r="B166" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="167" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A167" s="15" t="s">
+      <c r="A167" s="14" t="s">
         <v>639</v>
       </c>
-      <c r="B167" s="17" t="s">
+      <c r="B167" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="168" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A168" s="15" t="s">
+      <c r="A168" s="14" t="s">
         <v>640</v>
       </c>
-      <c r="B168" s="17" t="s">
+      <c r="B168" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="169" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A169" s="15" t="s">
+      <c r="A169" s="14" t="s">
         <v>641</v>
       </c>
-      <c r="B169" s="17" t="s">
+      <c r="B169" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="170" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A170" s="16" t="s">
+      <c r="A170" s="15" t="s">
         <v>642</v>
       </c>
-      <c r="B170" s="17" t="s">
+      <c r="B170" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="171" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A171" s="16" t="s">
+      <c r="A171" s="15" t="s">
         <v>643</v>
       </c>
-      <c r="B171" s="17" t="s">
+      <c r="B171" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="172" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A172" s="16" t="s">
+      <c r="A172" s="15" t="s">
         <v>644</v>
       </c>
-      <c r="B172" s="17" t="s">
+      <c r="B172" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="173" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A173" s="15" t="s">
+      <c r="A173" s="14" t="s">
         <v>645</v>
       </c>
-      <c r="B173" s="17" t="s">
+      <c r="B173" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="174" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A174" s="16" t="s">
+      <c r="A174" s="15" t="s">
         <v>646</v>
       </c>
-      <c r="B174" s="17" t="s">
+      <c r="B174" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="175" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A175" s="16" t="s">
+      <c r="A175" s="15" t="s">
         <v>647</v>
       </c>
-      <c r="B175" s="17" t="s">
+      <c r="B175" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="176" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A176" s="16" t="s">
+      <c r="A176" s="15" t="s">
         <v>648</v>
       </c>
-      <c r="B176" s="17" t="s">
+      <c r="B176" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="177" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A177" s="16" t="s">
+      <c r="A177" s="15" t="s">
         <v>649</v>
       </c>
-      <c r="B177" s="17" t="s">
+      <c r="B177" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="178" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A178" s="16" t="s">
+      <c r="A178" s="15" t="s">
         <v>650</v>
       </c>
-      <c r="B178" s="17" t="s">
+      <c r="B178" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="179" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A179" s="15" t="s">
+      <c r="A179" s="14" t="s">
         <v>651</v>
       </c>
-      <c r="B179" s="17" t="s">
+      <c r="B179" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="180" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A180" s="16" t="s">
+      <c r="A180" s="15" t="s">
         <v>652</v>
       </c>
-      <c r="B180" s="17" t="s">
+      <c r="B180" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="181" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A181" s="16" t="s">
+      <c r="A181" s="15" t="s">
         <v>653</v>
       </c>
-      <c r="B181" s="17" t="s">
+      <c r="B181" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="182" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A182" s="16" t="s">
+      <c r="A182" s="15" t="s">
         <v>654</v>
       </c>
-      <c r="B182" s="17" t="s">
+      <c r="B182" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="183" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A183" s="15" t="s">
+      <c r="A183" s="14" t="s">
         <v>655</v>
       </c>
-      <c r="B183" s="17" t="s">
+      <c r="B183" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="184" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A184" s="16" t="s">
+      <c r="A184" s="15" t="s">
         <v>656</v>
       </c>
-      <c r="B184" s="17" t="s">
+      <c r="B184" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="185" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A185" s="15" t="s">
+      <c r="A185" s="14" t="s">
         <v>657</v>
       </c>
-      <c r="B185" s="17" t="s">
+      <c r="B185" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="186" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A186" s="16" t="s">
+      <c r="A186" s="15" t="s">
         <v>658</v>
       </c>
-      <c r="B186" s="17" t="s">
+      <c r="B186" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="187" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A187" s="16" t="s">
+      <c r="A187" s="15" t="s">
         <v>659</v>
       </c>
-      <c r="B187" s="17" t="s">
+      <c r="B187" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="188" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A188" s="15" t="s">
+      <c r="A188" s="14" t="s">
         <v>660</v>
       </c>
-      <c r="B188" s="17" t="s">
+      <c r="B188" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="189" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A189" s="15" t="s">
+      <c r="A189" s="14" t="s">
         <v>661</v>
       </c>
-      <c r="B189" s="17" t="s">
+      <c r="B189" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="190" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A190" s="16" t="s">
+      <c r="A190" s="15" t="s">
         <v>662</v>
       </c>
-      <c r="B190" s="17" t="s">
+      <c r="B190" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="191" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A191" s="16" t="s">
+      <c r="A191" s="15" t="s">
         <v>663</v>
       </c>
-      <c r="B191" s="17" t="s">
+      <c r="B191" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="192" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A192" s="15" t="s">
+      <c r="A192" s="14" t="s">
         <v>664</v>
       </c>
-      <c r="B192" s="17" t="s">
+      <c r="B192" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="193" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A193" s="15" t="s">
+      <c r="A193" s="14" t="s">
         <v>665</v>
       </c>
-      <c r="B193" s="17" t="s">
+      <c r="B193" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="194" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A194" s="16" t="s">
+      <c r="A194" s="15" t="s">
         <v>666</v>
       </c>
-      <c r="B194" s="17" t="s">
+      <c r="B194" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="195" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A195" s="16" t="s">
+      <c r="A195" s="15" t="s">
         <v>667</v>
       </c>
-      <c r="B195" s="17" t="s">
+      <c r="B195" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="196" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A196" s="15" t="s">
+      <c r="A196" s="14" t="s">
         <v>668</v>
       </c>
-      <c r="B196" s="17" t="s">
+      <c r="B196" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="197" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A197" s="15" t="s">
+      <c r="A197" s="14" t="s">
         <v>597</v>
       </c>
-      <c r="B197" s="17" t="s">
+      <c r="B197" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="198" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A198" s="16" t="s">
+      <c r="A198" s="15" t="s">
         <v>669</v>
       </c>
-      <c r="B198" s="17" t="s">
+      <c r="B198" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="199" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A199" s="16" t="s">
+      <c r="A199" s="15" t="s">
         <v>670</v>
       </c>
-      <c r="B199" s="17" t="s">
+      <c r="B199" s="16" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="200" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A200" s="7"/>
+      <c r="A200" s="6"/>
     </row>
     <row r="201" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A201" s="7"/>
+      <c r="A201" s="6"/>
     </row>
     <row r="202" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A202" s="7"/>
+      <c r="A202" s="6"/>
     </row>
     <row r="203" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A203" s="8"/>
+      <c r="A203" s="7"/>
     </row>
     <row r="204" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A204" s="7"/>
+      <c r="A204" s="6"/>
     </row>
     <row r="205" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A205" s="7"/>
+      <c r="A205" s="6"/>
     </row>
     <row r="206" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A206" s="7"/>
+      <c r="A206" s="6"/>
     </row>
     <row r="207" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A207" s="8"/>
+      <c r="A207" s="7"/>
     </row>
     <row r="208" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A208" s="7"/>
+      <c r="A208" s="6"/>
     </row>
     <row r="209" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A209" s="7"/>
+      <c r="A209" s="6"/>
     </row>
     <row r="210" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A210" s="7"/>
+      <c r="A210" s="6"/>
     </row>
     <row r="211" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A211" s="6"/>
+      <c r="A211" s="5"/>
     </row>
     <row r="212" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A212" s="3"/>
@@ -4548,16 +4831,16 @@
       <c r="A214" s="3"/>
     </row>
     <row r="215" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A215" s="5"/>
+      <c r="A215" s="4"/>
     </row>
     <row r="216" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A216" s="3"/>
     </row>
     <row r="217" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A217" s="5"/>
+      <c r="A217" s="4"/>
     </row>
     <row r="218" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A218" s="5"/>
+      <c r="A218" s="4"/>
     </row>
     <row r="219" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A219" s="3"/>
@@ -4569,123 +4852,784 @@
       <c r="A221" s="3"/>
     </row>
     <row r="222" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A222" s="5"/>
+      <c r="A222" s="4"/>
     </row>
     <row r="223" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A223" s="5"/>
+      <c r="A223" s="4"/>
     </row>
     <row r="224" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A224" s="5"/>
-    </row>
-    <row r="225" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A224" s="4"/>
+    </row>
+    <row r="225" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A225" s="3"/>
     </row>
-    <row r="226" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A226" s="5"/>
-    </row>
-    <row r="227" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A226" s="4"/>
+    </row>
+    <row r="227" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A227" s="3"/>
     </row>
-    <row r="228" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A228" s="3"/>
     </row>
-    <row r="229" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A229" s="3"/>
     </row>
-    <row r="230" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A230" s="3"/>
     </row>
-    <row r="231" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A231" s="5"/>
-    </row>
-    <row r="232" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A232" s="10" t="s">
+    <row r="231" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A231" s="4"/>
+    </row>
+    <row r="232" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A232" s="9" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A233" s="3"/>
     </row>
-    <row r="234" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A234" s="3"/>
     </row>
-    <row r="235" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A235" s="3"/>
-    </row>
-    <row r="236" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A236" s="3"/>
-    </row>
-    <row r="237" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A237" s="5"/>
-    </row>
-    <row r="238" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A238" s="5"/>
-    </row>
-    <row r="239" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A239" s="5"/>
-    </row>
-    <row r="240" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A240" s="3"/>
-    </row>
-    <row r="241" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A241" s="3"/>
-    </row>
-    <row r="242" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A242" s="5"/>
-    </row>
-    <row r="243" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A243" s="5"/>
-    </row>
-    <row r="244" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A244" s="3"/>
-    </row>
-    <row r="245" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A245" s="3"/>
-    </row>
-    <row r="246" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A246" s="3"/>
-    </row>
-    <row r="247" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A247" s="3"/>
-    </row>
-    <row r="248" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A248" s="3"/>
-    </row>
-    <row r="249" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A249" s="3"/>
-    </row>
-    <row r="250" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A250" s="3"/>
-    </row>
-    <row r="251" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A251" s="3"/>
-    </row>
-    <row r="252" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A252" s="3"/>
-    </row>
-    <row r="253" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A253" s="3"/>
-    </row>
-    <row r="254" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A254" s="3"/>
-    </row>
-    <row r="255" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A255" s="5"/>
-    </row>
-    <row r="256" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A256" s="3"/>
-    </row>
-    <row r="257" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A257" s="4"/>
-    </row>
-    <row r="258" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A258" s="3"/>
-    </row>
-    <row r="259" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A259" s="3"/>
+    <row r="235" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A235" s="18" t="s">
+        <v>826</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A236" s="17" t="s">
+        <v>825</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A237" s="17" t="s">
+        <v>824</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A238" s="17" t="s">
+        <v>823</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A239" s="17" t="s">
+        <v>822</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A240" s="17" t="s">
+        <v>821</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A241" s="17" t="s">
+        <v>820</v>
+      </c>
+      <c r="B241" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A242" s="17" t="s">
+        <v>819</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A243" s="17" t="s">
+        <v>818</v>
+      </c>
+      <c r="B243" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A244" s="17" t="s">
+        <v>817</v>
+      </c>
+      <c r="B244" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A245" s="17" t="s">
+        <v>816</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A246" s="17" t="s">
+        <v>815</v>
+      </c>
+      <c r="B246" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A247" s="17" t="s">
+        <v>814</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A248" s="17" t="s">
+        <v>813</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A249" s="17" t="s">
+        <v>812</v>
+      </c>
+      <c r="B249" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A250" s="17" t="s">
+        <v>811</v>
+      </c>
+      <c r="B250" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A251" s="17" t="s">
+        <v>810</v>
+      </c>
+      <c r="B251" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A252" s="17" t="s">
+        <v>809</v>
+      </c>
+      <c r="B252" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A253" s="17" t="s">
+        <v>808</v>
+      </c>
+      <c r="B253" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A254" s="17" t="s">
+        <v>807</v>
+      </c>
+      <c r="B254" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A255" s="17" t="s">
+        <v>806</v>
+      </c>
+      <c r="B255" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A256" s="17" t="s">
+        <v>805</v>
+      </c>
+      <c r="B256" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A257" s="17" t="s">
+        <v>804</v>
+      </c>
+      <c r="B257" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A258" s="17" t="s">
+        <v>803</v>
+      </c>
+      <c r="B258" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A259" s="17" t="s">
+        <v>802</v>
+      </c>
+      <c r="B259" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A260" s="17" t="s">
+        <v>801</v>
+      </c>
+      <c r="B260" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A261" s="17" t="s">
+        <v>800</v>
+      </c>
+      <c r="B261" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A262" s="17" t="s">
+        <v>799</v>
+      </c>
+      <c r="B262" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A263" s="17" t="s">
+        <v>798</v>
+      </c>
+      <c r="B263" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A264" s="17" t="s">
+        <v>797</v>
+      </c>
+      <c r="B264" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A265" s="17" t="s">
+        <v>796</v>
+      </c>
+      <c r="B265" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A266" s="17" t="s">
+        <v>795</v>
+      </c>
+      <c r="B266" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A267" s="18" t="s">
+        <v>794</v>
+      </c>
+      <c r="B267" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A268" s="17" t="s">
+        <v>793</v>
+      </c>
+      <c r="B268" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A269" s="17" t="s">
+        <v>792</v>
+      </c>
+      <c r="B269" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A270" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="B270" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A271" s="17" t="s">
+        <v>790</v>
+      </c>
+      <c r="B271" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A272" s="17" t="s">
+        <v>789</v>
+      </c>
+      <c r="B272" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A273" s="17" t="s">
+        <v>788</v>
+      </c>
+      <c r="B273" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A274" s="17" t="s">
+        <v>787</v>
+      </c>
+      <c r="B274" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A275" s="17" t="s">
+        <v>786</v>
+      </c>
+      <c r="B275" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A276" s="17" t="s">
+        <v>785</v>
+      </c>
+      <c r="B276" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A277" s="17" t="s">
+        <v>784</v>
+      </c>
+      <c r="B277" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A278" s="17" t="s">
+        <v>783</v>
+      </c>
+      <c r="B278" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A279" s="17" t="s">
+        <v>782</v>
+      </c>
+      <c r="B279" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A280" s="17" t="s">
+        <v>781</v>
+      </c>
+      <c r="B280" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A281" s="17" t="s">
+        <v>780</v>
+      </c>
+      <c r="B281" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A282" s="18" t="s">
+        <v>779</v>
+      </c>
+      <c r="B282" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A283" s="17" t="s">
+        <v>778</v>
+      </c>
+      <c r="B283" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A284" s="17" t="s">
+        <v>777</v>
+      </c>
+      <c r="B284" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A285" s="17" t="s">
+        <v>776</v>
+      </c>
+      <c r="B285" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A286" s="17" t="s">
+        <v>775</v>
+      </c>
+      <c r="B286" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A287" s="18" t="s">
+        <v>774</v>
+      </c>
+      <c r="B287" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A288" s="17" t="s">
+        <v>773</v>
+      </c>
+      <c r="B288" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A289" s="17" t="s">
+        <v>772</v>
+      </c>
+      <c r="B289" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A290" s="17" t="s">
+        <v>771</v>
+      </c>
+      <c r="B290" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A291" s="17" t="s">
+        <v>770</v>
+      </c>
+      <c r="B291" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A292" s="18" t="s">
+        <v>769</v>
+      </c>
+      <c r="B292" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A293" s="17" t="s">
+        <v>768</v>
+      </c>
+      <c r="B293" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A294" s="18" t="s">
+        <v>767</v>
+      </c>
+      <c r="B294" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A295" s="18" t="s">
+        <v>766</v>
+      </c>
+      <c r="B295" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A296" s="17" t="s">
+        <v>765</v>
+      </c>
+      <c r="B296" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A297" s="17" t="s">
+        <v>764</v>
+      </c>
+      <c r="B297" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A298" s="18" t="s">
+        <v>763</v>
+      </c>
+      <c r="B298" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A299" s="18" t="s">
+        <v>762</v>
+      </c>
+      <c r="B299" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A300" s="18" t="s">
+        <v>761</v>
+      </c>
+      <c r="B300" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A301" s="18" t="s">
+        <v>756</v>
+      </c>
+      <c r="B301" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A302" s="17" t="s">
+        <v>760</v>
+      </c>
+      <c r="B302" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A303" s="17" t="s">
+        <v>759</v>
+      </c>
+      <c r="B303" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A304" s="17" t="s">
+        <v>758</v>
+      </c>
+      <c r="B304" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A305" s="17" t="s">
+        <v>757</v>
+      </c>
+      <c r="B305" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A306" s="18" t="s">
+        <v>756</v>
+      </c>
+      <c r="B306" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A307" s="17" t="s">
+        <v>755</v>
+      </c>
+      <c r="B307" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A308" s="18" t="s">
+        <v>754</v>
+      </c>
+      <c r="B308" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A309" s="18" t="s">
+        <v>753</v>
+      </c>
+      <c r="B309" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A310" s="17" t="s">
+        <v>752</v>
+      </c>
+      <c r="B310" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A311" s="18" t="s">
+        <v>751</v>
+      </c>
+      <c r="B311" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A312" s="18" t="s">
+        <v>750</v>
+      </c>
+      <c r="B312" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A313" s="18" t="s">
+        <v>749</v>
+      </c>
+      <c r="B313" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A314" s="17" t="s">
+        <v>748</v>
+      </c>
+      <c r="B314" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A315" s="18" t="s">
+        <v>747</v>
+      </c>
+      <c r="B315" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A316" s="17" t="s">
+        <v>746</v>
+      </c>
+      <c r="B316" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A317" s="18" t="s">
+        <v>745</v>
+      </c>
+      <c r="B317" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A318" s="17" t="s">
+        <v>744</v>
+      </c>
+      <c r="B318" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A319" s="18" t="s">
+        <v>743</v>
+      </c>
+      <c r="B319" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A320" s="17" t="s">
+        <v>742</v>
+      </c>
+      <c r="B320" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A321" s="18" t="s">
+        <v>741</v>
+      </c>
+      <c r="B321" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A322" s="17" t="s">
+        <v>740</v>
+      </c>
+      <c r="B322" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A323" s="17" t="s">
+        <v>739</v>
+      </c>
+      <c r="B323" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A324" s="18" t="s">
+        <v>738</v>
+      </c>
+      <c r="B324" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A325" s="17" t="s">
+        <v>737</v>
+      </c>
+      <c r="B325" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A326" s="17" t="s">
+        <v>736</v>
+      </c>
+      <c r="B326" s="1" t="s">
+        <v>827</v>
+      </c>
     </row>
     <row r="515" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A515" s="10" t="s">
+      <c r="A515" s="9" t="s">
         <v>446</v>
       </c>
       <c r="B515" s="1" t="s">
@@ -4693,7 +5637,7 @@
       </c>
     </row>
     <row r="516" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A516" s="9" t="s">
+      <c r="A516" s="8" t="s">
         <v>445</v>
       </c>
       <c r="B516" s="1" t="s">
@@ -4701,7 +5645,7 @@
       </c>
     </row>
     <row r="517" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A517" s="9" t="s">
+      <c r="A517" s="8" t="s">
         <v>444</v>
       </c>
       <c r="B517" s="1" t="s">
@@ -4709,7 +5653,7 @@
       </c>
     </row>
     <row r="518" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A518" s="10" t="s">
+      <c r="A518" s="9" t="s">
         <v>443</v>
       </c>
       <c r="B518" s="1" t="s">
@@ -4717,7 +5661,7 @@
       </c>
     </row>
     <row r="519" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A519" s="9" t="s">
+      <c r="A519" s="8" t="s">
         <v>442</v>
       </c>
       <c r="B519" s="1" t="s">
@@ -4725,7 +5669,7 @@
       </c>
     </row>
     <row r="520" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A520" s="10" t="s">
+      <c r="A520" s="9" t="s">
         <v>441</v>
       </c>
       <c r="B520" s="1" t="s">
@@ -4733,7 +5677,7 @@
       </c>
     </row>
     <row r="521" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A521" s="10" t="s">
+      <c r="A521" s="9" t="s">
         <v>440</v>
       </c>
       <c r="B521" s="1" t="s">
@@ -4741,7 +5685,7 @@
       </c>
     </row>
     <row r="522" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A522" s="10" t="s">
+      <c r="A522" s="9" t="s">
         <v>439</v>
       </c>
       <c r="B522" s="1" t="s">
@@ -4749,7 +5693,7 @@
       </c>
     </row>
     <row r="523" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A523" s="9" t="s">
+      <c r="A523" s="8" t="s">
         <v>438</v>
       </c>
       <c r="B523" s="1" t="s">
@@ -4757,7 +5701,7 @@
       </c>
     </row>
     <row r="524" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A524" s="9" t="s">
+      <c r="A524" s="8" t="s">
         <v>437</v>
       </c>
       <c r="B524" s="1" t="s">
@@ -4765,7 +5709,7 @@
       </c>
     </row>
     <row r="525" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A525" s="10" t="s">
+      <c r="A525" s="9" t="s">
         <v>436</v>
       </c>
       <c r="B525" s="1" t="s">
@@ -4773,7 +5717,7 @@
       </c>
     </row>
     <row r="526" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A526" s="10" t="s">
+      <c r="A526" s="9" t="s">
         <v>435</v>
       </c>
       <c r="B526" s="1" t="s">
@@ -4781,7 +5725,7 @@
       </c>
     </row>
     <row r="527" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A527" s="10" t="s">
+      <c r="A527" s="9" t="s">
         <v>434</v>
       </c>
       <c r="B527" s="1" t="s">
@@ -4789,7 +5733,7 @@
       </c>
     </row>
     <row r="528" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A528" s="10" t="s">
+      <c r="A528" s="9" t="s">
         <v>433</v>
       </c>
       <c r="B528" s="1" t="s">
@@ -4797,7 +5741,7 @@
       </c>
     </row>
     <row r="529" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A529" s="10" t="s">
+      <c r="A529" s="9" t="s">
         <v>432</v>
       </c>
       <c r="B529" s="1" t="s">
@@ -4805,7 +5749,7 @@
       </c>
     </row>
     <row r="530" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A530" s="9" t="s">
+      <c r="A530" s="8" t="s">
         <v>431</v>
       </c>
       <c r="B530" s="1" t="s">
@@ -4813,7 +5757,7 @@
       </c>
     </row>
     <row r="531" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A531" s="10" t="s">
+      <c r="A531" s="9" t="s">
         <v>430</v>
       </c>
       <c r="B531" s="1" t="s">
@@ -4821,7 +5765,7 @@
       </c>
     </row>
     <row r="532" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A532" s="10" t="s">
+      <c r="A532" s="9" t="s">
         <v>429</v>
       </c>
       <c r="B532" s="1" t="s">
@@ -4829,7 +5773,7 @@
       </c>
     </row>
     <row r="533" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A533" s="10" t="s">
+      <c r="A533" s="9" t="s">
         <v>428</v>
       </c>
       <c r="B533" s="1" t="s">
@@ -4837,7 +5781,7 @@
       </c>
     </row>
     <row r="534" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A534" s="10" t="s">
+      <c r="A534" s="9" t="s">
         <v>427</v>
       </c>
       <c r="B534" s="1" t="s">
@@ -4845,7 +5789,7 @@
       </c>
     </row>
     <row r="535" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A535" s="9" t="s">
+      <c r="A535" s="8" t="s">
         <v>426</v>
       </c>
       <c r="B535" s="1" t="s">
@@ -4853,7 +5797,7 @@
       </c>
     </row>
     <row r="536" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A536" s="9" t="s">
+      <c r="A536" s="8" t="s">
         <v>425</v>
       </c>
       <c r="B536" s="1" t="s">
@@ -4861,7 +5805,7 @@
       </c>
     </row>
     <row r="537" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A537" s="10" t="s">
+      <c r="A537" s="9" t="s">
         <v>424</v>
       </c>
       <c r="B537" s="1" t="s">
@@ -4869,7 +5813,7 @@
       </c>
     </row>
     <row r="538" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A538" s="9" t="s">
+      <c r="A538" s="8" t="s">
         <v>423</v>
       </c>
       <c r="B538" s="1" t="s">
@@ -4877,7 +5821,7 @@
       </c>
     </row>
     <row r="539" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A539" s="9" t="s">
+      <c r="A539" s="8" t="s">
         <v>422</v>
       </c>
       <c r="B539" s="1" t="s">
@@ -4885,7 +5829,7 @@
       </c>
     </row>
     <row r="540" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A540" s="9" t="s">
+      <c r="A540" s="8" t="s">
         <v>421</v>
       </c>
       <c r="B540" s="1" t="s">
@@ -4893,7 +5837,7 @@
       </c>
     </row>
     <row r="541" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A541" s="9" t="s">
+      <c r="A541" s="8" t="s">
         <v>420</v>
       </c>
       <c r="B541" s="1" t="s">
@@ -4901,7 +5845,7 @@
       </c>
     </row>
     <row r="542" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A542" s="10" t="s">
+      <c r="A542" s="9" t="s">
         <v>419</v>
       </c>
       <c r="B542" s="1" t="s">
@@ -4909,7 +5853,7 @@
       </c>
     </row>
     <row r="543" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A543" s="10" t="s">
+      <c r="A543" s="9" t="s">
         <v>418</v>
       </c>
       <c r="B543" s="1" t="s">
@@ -4917,7 +5861,7 @@
       </c>
     </row>
     <row r="544" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A544" s="9" t="s">
+      <c r="A544" s="8" t="s">
         <v>417</v>
       </c>
       <c r="B544" s="1" t="s">
@@ -4925,7 +5869,7 @@
       </c>
     </row>
     <row r="545" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A545" s="10" t="s">
+      <c r="A545" s="9" t="s">
         <v>416</v>
       </c>
       <c r="B545" s="1" t="s">
@@ -4933,7 +5877,7 @@
       </c>
     </row>
     <row r="546" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A546" s="10" t="s">
+      <c r="A546" s="9" t="s">
         <v>415</v>
       </c>
       <c r="B546" s="1" t="s">
@@ -4941,7 +5885,7 @@
       </c>
     </row>
     <row r="547" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A547" s="9" t="s">
+      <c r="A547" s="8" t="s">
         <v>390</v>
       </c>
       <c r="B547" s="1" t="s">
@@ -4949,7 +5893,7 @@
       </c>
     </row>
     <row r="548" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A548" s="9" t="s">
+      <c r="A548" s="8" t="s">
         <v>414</v>
       </c>
       <c r="B548" s="1" t="s">
@@ -4957,7 +5901,7 @@
       </c>
     </row>
     <row r="549" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A549" s="10" t="s">
+      <c r="A549" s="9" t="s">
         <v>413</v>
       </c>
       <c r="B549" s="1" t="s">
@@ -4965,7 +5909,7 @@
       </c>
     </row>
     <row r="550" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A550" s="9" t="s">
+      <c r="A550" s="8" t="s">
         <v>412</v>
       </c>
       <c r="B550" s="1" t="s">
@@ -4973,7 +5917,7 @@
       </c>
     </row>
     <row r="551" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A551" s="10" t="s">
+      <c r="A551" s="9" t="s">
         <v>411</v>
       </c>
       <c r="B551" s="1" t="s">
@@ -4981,7 +5925,7 @@
       </c>
     </row>
     <row r="552" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A552" s="9" t="s">
+      <c r="A552" s="8" t="s">
         <v>410</v>
       </c>
       <c r="B552" s="1" t="s">
@@ -4989,7 +5933,7 @@
       </c>
     </row>
     <row r="553" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A553" s="9" t="s">
+      <c r="A553" s="8" t="s">
         <v>409</v>
       </c>
       <c r="B553" s="1" t="s">
@@ -4997,7 +5941,7 @@
       </c>
     </row>
     <row r="554" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A554" s="10" t="s">
+      <c r="A554" s="9" t="s">
         <v>408</v>
       </c>
       <c r="B554" s="1" t="s">
@@ -5005,7 +5949,7 @@
       </c>
     </row>
     <row r="555" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A555" s="9" t="s">
+      <c r="A555" s="8" t="s">
         <v>407</v>
       </c>
       <c r="B555" s="1" t="s">
@@ -5013,7 +5957,7 @@
       </c>
     </row>
     <row r="556" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A556" s="10" t="s">
+      <c r="A556" s="9" t="s">
         <v>406</v>
       </c>
       <c r="B556" s="1" t="s">
@@ -5021,7 +5965,7 @@
       </c>
     </row>
     <row r="557" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A557" s="10" t="s">
+      <c r="A557" s="9" t="s">
         <v>405</v>
       </c>
       <c r="B557" s="1" t="s">
@@ -5029,7 +5973,7 @@
       </c>
     </row>
     <row r="558" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A558" s="9" t="s">
+      <c r="A558" s="8" t="s">
         <v>404</v>
       </c>
       <c r="B558" s="1" t="s">
@@ -5037,7 +5981,7 @@
       </c>
     </row>
     <row r="559" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A559" s="9" t="s">
+      <c r="A559" s="8" t="s">
         <v>403</v>
       </c>
       <c r="B559" s="1" t="s">
@@ -5045,7 +5989,7 @@
       </c>
     </row>
     <row r="560" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A560" s="9" t="s">
+      <c r="A560" s="8" t="s">
         <v>402</v>
       </c>
       <c r="B560" s="1" t="s">
@@ -5053,7 +5997,7 @@
       </c>
     </row>
     <row r="561" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A561" s="10" t="s">
+      <c r="A561" s="9" t="s">
         <v>401</v>
       </c>
       <c r="B561" s="1" t="s">
@@ -5061,7 +6005,7 @@
       </c>
     </row>
     <row r="562" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A562" s="9" t="s">
+      <c r="A562" s="8" t="s">
         <v>400</v>
       </c>
       <c r="B562" s="1" t="s">
@@ -5069,7 +6013,7 @@
       </c>
     </row>
     <row r="563" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A563" s="9" t="s">
+      <c r="A563" s="8" t="s">
         <v>399</v>
       </c>
       <c r="B563" s="1" t="s">
@@ -5077,7 +6021,7 @@
       </c>
     </row>
     <row r="564" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A564" s="9" t="s">
+      <c r="A564" s="8" t="s">
         <v>398</v>
       </c>
       <c r="B564" s="1" t="s">
@@ -5085,7 +6029,7 @@
       </c>
     </row>
     <row r="565" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A565" s="9" t="s">
+      <c r="A565" s="8" t="s">
         <v>397</v>
       </c>
       <c r="B565" s="1" t="s">
@@ -5093,7 +6037,7 @@
       </c>
     </row>
     <row r="566" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A566" s="10" t="s">
+      <c r="A566" s="9" t="s">
         <v>396</v>
       </c>
       <c r="B566" s="1" t="s">
@@ -5101,7 +6045,7 @@
       </c>
     </row>
     <row r="567" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A567" s="10" t="s">
+      <c r="A567" s="9" t="s">
         <v>395</v>
       </c>
       <c r="B567" s="1" t="s">
@@ -5109,7 +6053,7 @@
       </c>
     </row>
     <row r="568" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A568" s="10" t="s">
+      <c r="A568" s="9" t="s">
         <v>394</v>
       </c>
       <c r="B568" s="1" t="s">
@@ -5117,7 +6061,7 @@
       </c>
     </row>
     <row r="569" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A569" s="10" t="s">
+      <c r="A569" s="9" t="s">
         <v>393</v>
       </c>
       <c r="B569" s="1" t="s">
@@ -5125,7 +6069,7 @@
       </c>
     </row>
     <row r="570" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A570" s="9" t="s">
+      <c r="A570" s="8" t="s">
         <v>392</v>
       </c>
       <c r="B570" s="1" t="s">
@@ -5133,7 +6077,7 @@
       </c>
     </row>
     <row r="571" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A571" s="10" t="s">
+      <c r="A571" s="9" t="s">
         <v>391</v>
       </c>
       <c r="B571" s="1" t="s">
@@ -5141,7 +6085,7 @@
       </c>
     </row>
     <row r="572" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A572" s="9" t="s">
+      <c r="A572" s="8" t="s">
         <v>390</v>
       </c>
       <c r="B572" s="1" t="s">
@@ -5149,7 +6093,7 @@
       </c>
     </row>
     <row r="573" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A573" s="10" t="s">
+      <c r="A573" s="9" t="s">
         <v>389</v>
       </c>
       <c r="B573" s="1" t="s">
@@ -5157,7 +6101,7 @@
       </c>
     </row>
     <row r="574" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A574" s="10" t="s">
+      <c r="A574" s="9" t="s">
         <v>388</v>
       </c>
       <c r="B574" s="1" t="s">
@@ -5165,7 +6109,7 @@
       </c>
     </row>
     <row r="575" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A575" s="10" t="s">
+      <c r="A575" s="9" t="s">
         <v>387</v>
       </c>
       <c r="B575" s="1" t="s">
@@ -5173,7 +6117,7 @@
       </c>
     </row>
     <row r="576" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A576" s="9" t="s">
+      <c r="A576" s="8" t="s">
         <v>386</v>
       </c>
       <c r="B576" s="1" t="s">
@@ -5181,7 +6125,7 @@
       </c>
     </row>
     <row r="577" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A577" s="10" t="s">
+      <c r="A577" s="9" t="s">
         <v>385</v>
       </c>
       <c r="B577" s="1" t="s">
@@ -5189,7 +6133,7 @@
       </c>
     </row>
     <row r="578" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A578" s="9" t="s">
+      <c r="A578" s="8" t="s">
         <v>384</v>
       </c>
       <c r="B578" s="1" t="s">
@@ -5197,7 +6141,7 @@
       </c>
     </row>
     <row r="579" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A579" s="10" t="s">
+      <c r="A579" s="9" t="s">
         <v>383</v>
       </c>
       <c r="B579" s="1" t="s">
@@ -5205,7 +6149,7 @@
       </c>
     </row>
     <row r="580" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A580" s="10" t="s">
+      <c r="A580" s="9" t="s">
         <v>382</v>
       </c>
       <c r="B580" s="1" t="s">
@@ -5213,7 +6157,7 @@
       </c>
     </row>
     <row r="581" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A581" s="10" t="s">
+      <c r="A581" s="9" t="s">
         <v>381</v>
       </c>
       <c r="B581" s="1" t="s">
@@ -5221,7 +6165,7 @@
       </c>
     </row>
     <row r="582" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A582" s="9" t="s">
+      <c r="A582" s="8" t="s">
         <v>380</v>
       </c>
       <c r="B582" s="1" t="s">
@@ -5229,7 +6173,7 @@
       </c>
     </row>
     <row r="583" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A583" s="10" t="s">
+      <c r="A583" s="9" t="s">
         <v>379</v>
       </c>
       <c r="B583" s="1" t="s">
@@ -5237,7 +6181,7 @@
       </c>
     </row>
     <row r="584" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A584" s="10" t="s">
+      <c r="A584" s="9" t="s">
         <v>378</v>
       </c>
       <c r="B584" s="1" t="s">
@@ -5245,7 +6189,7 @@
       </c>
     </row>
     <row r="585" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A585" s="10" t="s">
+      <c r="A585" s="9" t="s">
         <v>377</v>
       </c>
       <c r="B585" s="1" t="s">
@@ -5253,7 +6197,7 @@
       </c>
     </row>
     <row r="586" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A586" s="10" t="s">
+      <c r="A586" s="9" t="s">
         <v>376</v>
       </c>
       <c r="B586" s="1" t="s">
@@ -5261,7 +6205,7 @@
       </c>
     </row>
     <row r="587" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A587" s="10" t="s">
+      <c r="A587" s="9" t="s">
         <v>375</v>
       </c>
       <c r="B587" s="1" t="s">
@@ -5269,7 +6213,7 @@
       </c>
     </row>
     <row r="588" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A588" s="9" t="s">
+      <c r="A588" s="8" t="s">
         <v>374</v>
       </c>
       <c r="B588" s="1" t="s">
@@ -5277,7 +6221,7 @@
       </c>
     </row>
     <row r="589" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A589" s="10" t="s">
+      <c r="A589" s="9" t="s">
         <v>373</v>
       </c>
       <c r="B589" s="1" t="s">
@@ -5285,19 +6229,19 @@
       </c>
     </row>
     <row r="590" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A590" s="10"/>
+      <c r="A590" s="9"/>
     </row>
     <row r="591" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A591" s="10"/>
+      <c r="A591" s="9"/>
     </row>
     <row r="592" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A592" s="10"/>
+      <c r="A592" s="9"/>
     </row>
     <row r="669" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A669" s="9"/>
+      <c r="A669" s="8"/>
     </row>
     <row r="670" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A670" s="10" t="s">
+      <c r="A670" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B670" s="1" t="s">
@@ -5305,7 +6249,7 @@
       </c>
     </row>
     <row r="671" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A671" s="10" t="s">
+      <c r="A671" s="9" t="s">
         <v>70</v>
       </c>
       <c r="B671" s="1" t="s">
@@ -5313,7 +6257,7 @@
       </c>
     </row>
     <row r="672" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A672" s="10" t="s">
+      <c r="A672" s="9" t="s">
         <v>103</v>
       </c>
       <c r="B672" s="1" t="s">
@@ -5321,7 +6265,7 @@
       </c>
     </row>
     <row r="673" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A673" s="9" t="s">
+      <c r="A673" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B673" s="1" t="s">
@@ -5329,7 +6273,7 @@
       </c>
     </row>
     <row r="674" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A674" s="9" t="s">
+      <c r="A674" s="8" t="s">
         <v>101</v>
       </c>
       <c r="B674" s="1" t="s">
@@ -5337,7 +6281,7 @@
       </c>
     </row>
     <row r="675" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A675" s="10" t="s">
+      <c r="A675" s="9" t="s">
         <v>100</v>
       </c>
       <c r="B675" s="1" t="s">
@@ -5345,7 +6289,7 @@
       </c>
     </row>
     <row r="676" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A676" s="10" t="s">
+      <c r="A676" s="9" t="s">
         <v>99</v>
       </c>
       <c r="B676" s="1" t="s">
@@ -5353,7 +6297,7 @@
       </c>
     </row>
     <row r="677" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A677" s="9" t="s">
+      <c r="A677" s="8" t="s">
         <v>98</v>
       </c>
       <c r="B677" s="1" t="s">
@@ -5361,7 +6305,7 @@
       </c>
     </row>
     <row r="678" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A678" s="10" t="s">
+      <c r="A678" s="9" t="s">
         <v>97</v>
       </c>
       <c r="B678" s="1" t="s">
@@ -5369,7 +6313,7 @@
       </c>
     </row>
     <row r="679" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A679" s="10" t="s">
+      <c r="A679" s="9" t="s">
         <v>96</v>
       </c>
       <c r="B679" s="1" t="s">
@@ -5377,7 +6321,7 @@
       </c>
     </row>
     <row r="680" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A680" s="10" t="s">
+      <c r="A680" s="9" t="s">
         <v>95</v>
       </c>
       <c r="B680" s="1" t="s">
@@ -5385,7 +6329,7 @@
       </c>
     </row>
     <row r="681" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A681" s="10" t="s">
+      <c r="A681" s="9" t="s">
         <v>94</v>
       </c>
       <c r="B681" s="1" t="s">
@@ -5393,7 +6337,7 @@
       </c>
     </row>
     <row r="682" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A682" s="10" t="s">
+      <c r="A682" s="9" t="s">
         <v>93</v>
       </c>
       <c r="B682" s="1" t="s">
@@ -5401,7 +6345,7 @@
       </c>
     </row>
     <row r="683" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A683" s="9" t="s">
+      <c r="A683" s="8" t="s">
         <v>92</v>
       </c>
       <c r="B683" s="1" t="s">
@@ -5409,7 +6353,7 @@
       </c>
     </row>
     <row r="684" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A684" s="9" t="s">
+      <c r="A684" s="8" t="s">
         <v>91</v>
       </c>
       <c r="B684" s="1" t="s">
@@ -5417,7 +6361,7 @@
       </c>
     </row>
     <row r="685" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A685" s="9" t="s">
+      <c r="A685" s="8" t="s">
         <v>90</v>
       </c>
       <c r="B685" s="1" t="s">
@@ -5425,7 +6369,7 @@
       </c>
     </row>
     <row r="686" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A686" s="9" t="s">
+      <c r="A686" s="8" t="s">
         <v>89</v>
       </c>
       <c r="B686" s="1" t="s">
@@ -5433,7 +6377,7 @@
       </c>
     </row>
     <row r="687" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A687" s="9" t="s">
+      <c r="A687" s="8" t="s">
         <v>88</v>
       </c>
       <c r="B687" s="1" t="s">
@@ -5441,7 +6385,7 @@
       </c>
     </row>
     <row r="688" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A688" s="9" t="s">
+      <c r="A688" s="8" t="s">
         <v>87</v>
       </c>
       <c r="B688" s="1" t="s">
@@ -5449,7 +6393,7 @@
       </c>
     </row>
     <row r="689" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A689" s="10" t="s">
+      <c r="A689" s="9" t="s">
         <v>86</v>
       </c>
       <c r="B689" s="1" t="s">
@@ -5457,7 +6401,7 @@
       </c>
     </row>
     <row r="690" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A690" s="10" t="s">
+      <c r="A690" s="9" t="s">
         <v>85</v>
       </c>
       <c r="B690" s="1" t="s">
@@ -5465,7 +6409,7 @@
       </c>
     </row>
     <row r="691" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A691" s="9" t="s">
+      <c r="A691" s="8" t="s">
         <v>84</v>
       </c>
       <c r="B691" s="1" t="s">
@@ -5473,7 +6417,7 @@
       </c>
     </row>
     <row r="692" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A692" s="9" t="s">
+      <c r="A692" s="8" t="s">
         <v>83</v>
       </c>
       <c r="B692" s="1" t="s">
@@ -5481,7 +6425,7 @@
       </c>
     </row>
     <row r="693" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A693" s="9" t="s">
+      <c r="A693" s="8" t="s">
         <v>82</v>
       </c>
       <c r="B693" s="1" t="s">
@@ -5489,7 +6433,7 @@
       </c>
     </row>
     <row r="694" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A694" s="10" t="s">
+      <c r="A694" s="9" t="s">
         <v>81</v>
       </c>
       <c r="B694" s="1" t="s">
@@ -5497,7 +6441,7 @@
       </c>
     </row>
     <row r="695" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A695" s="10" t="s">
+      <c r="A695" s="9" t="s">
         <v>80</v>
       </c>
       <c r="B695" s="1" t="s">
@@ -5505,7 +6449,7 @@
       </c>
     </row>
     <row r="696" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A696" s="9" t="s">
+      <c r="A696" s="8" t="s">
         <v>79</v>
       </c>
       <c r="B696" s="1" t="s">
@@ -5513,7 +6457,7 @@
       </c>
     </row>
     <row r="697" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A697" s="10" t="s">
+      <c r="A697" s="9" t="s">
         <v>78</v>
       </c>
       <c r="B697" s="1" t="s">
@@ -5521,7 +6465,7 @@
       </c>
     </row>
     <row r="698" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A698" s="10" t="s">
+      <c r="A698" s="9" t="s">
         <v>77</v>
       </c>
       <c r="B698" s="1" t="s">
@@ -5529,7 +6473,7 @@
       </c>
     </row>
     <row r="699" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A699" s="9" t="s">
+      <c r="A699" s="8" t="s">
         <v>76</v>
       </c>
       <c r="B699" s="1" t="s">
@@ -5537,7 +6481,7 @@
       </c>
     </row>
     <row r="700" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A700" s="10" t="s">
+      <c r="A700" s="9" t="s">
         <v>75</v>
       </c>
       <c r="B700" s="1" t="s">
@@ -5545,7 +6489,7 @@
       </c>
     </row>
     <row r="701" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A701" s="10" t="s">
+      <c r="A701" s="9" t="s">
         <v>74</v>
       </c>
       <c r="B701" s="1" t="s">
@@ -5553,7 +6497,7 @@
       </c>
     </row>
     <row r="702" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A702" s="10" t="s">
+      <c r="A702" s="9" t="s">
         <v>73</v>
       </c>
       <c r="B702" s="1" t="s">
@@ -5561,7 +6505,7 @@
       </c>
     </row>
     <row r="703" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A703" s="9" t="s">
+      <c r="A703" s="8" t="s">
         <v>72</v>
       </c>
       <c r="B703" s="1" t="s">
@@ -5569,7 +6513,7 @@
       </c>
     </row>
     <row r="704" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A704" s="9" t="s">
+      <c r="A704" s="8" t="s">
         <v>71</v>
       </c>
       <c r="B704" s="1" t="s">
@@ -5577,7 +6521,7 @@
       </c>
     </row>
     <row r="705" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A705" s="10" t="s">
+      <c r="A705" s="9" t="s">
         <v>70</v>
       </c>
       <c r="B705" s="1" t="s">
@@ -5585,7 +6529,7 @@
       </c>
     </row>
     <row r="706" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A706" s="10" t="s">
+      <c r="A706" s="9" t="s">
         <v>69</v>
       </c>
       <c r="B706" s="1" t="s">
@@ -5593,7 +6537,7 @@
       </c>
     </row>
     <row r="707" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A707" s="9" t="s">
+      <c r="A707" s="8" t="s">
         <v>68</v>
       </c>
       <c r="B707" s="1" t="s">
@@ -5601,7 +6545,7 @@
       </c>
     </row>
     <row r="708" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A708" s="10" t="s">
+      <c r="A708" s="9" t="s">
         <v>67</v>
       </c>
       <c r="B708" s="1" t="s">
@@ -5609,7 +6553,7 @@
       </c>
     </row>
     <row r="709" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A709" s="10" t="s">
+      <c r="A709" s="9" t="s">
         <v>66</v>
       </c>
       <c r="B709" s="1" t="s">
@@ -5617,7 +6561,7 @@
       </c>
     </row>
     <row r="710" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A710" s="10" t="s">
+      <c r="A710" s="9" t="s">
         <v>65</v>
       </c>
       <c r="B710" s="1" t="s">
@@ -5625,7 +6569,7 @@
       </c>
     </row>
     <row r="711" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A711" s="10" t="s">
+      <c r="A711" s="9" t="s">
         <v>64</v>
       </c>
       <c r="B711" s="1" t="s">
@@ -5633,7 +6577,7 @@
       </c>
     </row>
     <row r="712" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A712" s="10" t="s">
+      <c r="A712" s="9" t="s">
         <v>63</v>
       </c>
       <c r="B712" s="1" t="s">
@@ -5641,7 +6585,7 @@
       </c>
     </row>
     <row r="713" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A713" s="10" t="s">
+      <c r="A713" s="9" t="s">
         <v>62</v>
       </c>
       <c r="B713" s="1" t="s">
@@ -5649,7 +6593,7 @@
       </c>
     </row>
     <row r="714" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A714" s="9" t="s">
+      <c r="A714" s="8" t="s">
         <v>61</v>
       </c>
       <c r="B714" s="1" t="s">
@@ -5657,7 +6601,7 @@
       </c>
     </row>
     <row r="715" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A715" s="10" t="s">
+      <c r="A715" s="9" t="s">
         <v>60</v>
       </c>
       <c r="B715" s="1" t="s">
@@ -5665,7 +6609,7 @@
       </c>
     </row>
     <row r="716" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A716" s="9" t="s">
+      <c r="A716" s="8" t="s">
         <v>59</v>
       </c>
       <c r="B716" s="1" t="s">
@@ -5673,7 +6617,7 @@
       </c>
     </row>
     <row r="717" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A717" s="9" t="s">
+      <c r="A717" s="8" t="s">
         <v>58</v>
       </c>
       <c r="B717" s="1" t="s">
@@ -5681,7 +6625,7 @@
       </c>
     </row>
     <row r="718" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A718" s="10" t="s">
+      <c r="A718" s="9" t="s">
         <v>57</v>
       </c>
       <c r="B718" s="1" t="s">
@@ -5689,7 +6633,7 @@
       </c>
     </row>
     <row r="719" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A719" s="9" t="s">
+      <c r="A719" s="8" t="s">
         <v>56</v>
       </c>
       <c r="B719" s="1" t="s">
@@ -5697,7 +6641,7 @@
       </c>
     </row>
     <row r="720" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A720" s="10" t="s">
+      <c r="A720" s="9" t="s">
         <v>55</v>
       </c>
       <c r="B720" s="1" t="s">
@@ -5705,7 +6649,7 @@
       </c>
     </row>
     <row r="721" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A721" s="10" t="s">
+      <c r="A721" s="9" t="s">
         <v>54</v>
       </c>
       <c r="B721" s="1" t="s">
@@ -5713,7 +6657,7 @@
       </c>
     </row>
     <row r="722" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A722" s="10" t="s">
+      <c r="A722" s="9" t="s">
         <v>53</v>
       </c>
       <c r="B722" s="1" t="s">
@@ -5721,7 +6665,7 @@
       </c>
     </row>
     <row r="723" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A723" s="10" t="s">
+      <c r="A723" s="9" t="s">
         <v>52</v>
       </c>
       <c r="B723" s="1" t="s">
@@ -5729,7 +6673,7 @@
       </c>
     </row>
     <row r="724" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A724" s="10" t="s">
+      <c r="A724" s="9" t="s">
         <v>51</v>
       </c>
       <c r="B724" s="1" t="s">
@@ -5737,7 +6681,7 @@
       </c>
     </row>
     <row r="725" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A725" s="10" t="s">
+      <c r="A725" s="9" t="s">
         <v>50</v>
       </c>
       <c r="B725" s="1" t="s">
@@ -5745,7 +6689,7 @@
       </c>
     </row>
     <row r="726" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A726" s="10" t="s">
+      <c r="A726" s="9" t="s">
         <v>49</v>
       </c>
       <c r="B726" s="1" t="s">
@@ -5753,7 +6697,7 @@
       </c>
     </row>
     <row r="727" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A727" s="10" t="s">
+      <c r="A727" s="9" t="s">
         <v>48</v>
       </c>
       <c r="B727" s="1" t="s">
@@ -5761,7 +6705,7 @@
       </c>
     </row>
     <row r="728" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A728" s="10" t="s">
+      <c r="A728" s="9" t="s">
         <v>47</v>
       </c>
       <c r="B728" s="1" t="s">
@@ -5769,7 +6713,7 @@
       </c>
     </row>
     <row r="729" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A729" s="10" t="s">
+      <c r="A729" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B729" s="1" t="s">
@@ -5777,7 +6721,7 @@
       </c>
     </row>
     <row r="730" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A730" s="9" t="s">
+      <c r="A730" s="8" t="s">
         <v>45</v>
       </c>
       <c r="B730" s="1" t="s">
@@ -5785,7 +6729,7 @@
       </c>
     </row>
     <row r="731" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A731" s="10" t="s">
+      <c r="A731" s="9" t="s">
         <v>44</v>
       </c>
       <c r="B731" s="1" t="s">
@@ -5793,7 +6737,7 @@
       </c>
     </row>
     <row r="732" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A732" s="10" t="s">
+      <c r="A732" s="9" t="s">
         <v>43</v>
       </c>
       <c r="B732" s="1" t="s">
@@ -5801,7 +6745,7 @@
       </c>
     </row>
     <row r="733" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A733" s="10" t="s">
+      <c r="A733" s="9" t="s">
         <v>42</v>
       </c>
       <c r="B733" s="1" t="s">
@@ -5809,7 +6753,7 @@
       </c>
     </row>
     <row r="734" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A734" s="10" t="s">
+      <c r="A734" s="9" t="s">
         <v>41</v>
       </c>
       <c r="B734" s="1" t="s">
@@ -5817,7 +6761,7 @@
       </c>
     </row>
     <row r="735" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A735" s="9" t="s">
+      <c r="A735" s="8" t="s">
         <v>40</v>
       </c>
       <c r="B735" s="1" t="s">
@@ -5825,7 +6769,7 @@
       </c>
     </row>
     <row r="736" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A736" s="10" t="s">
+      <c r="A736" s="9" t="s">
         <v>39</v>
       </c>
       <c r="B736" s="1" t="s">
@@ -5833,7 +6777,7 @@
       </c>
     </row>
     <row r="737" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A737" s="9" t="s">
+      <c r="A737" s="8" t="s">
         <v>38</v>
       </c>
       <c r="B737" s="1" t="s">
@@ -5841,7 +6785,7 @@
       </c>
     </row>
     <row r="738" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A738" s="9" t="s">
+      <c r="A738" s="8" t="s">
         <v>37</v>
       </c>
       <c r="B738" s="1" t="s">
@@ -5849,7 +6793,7 @@
       </c>
     </row>
     <row r="739" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A739" s="10" t="s">
+      <c r="A739" s="9" t="s">
         <v>36</v>
       </c>
       <c r="B739" s="1" t="s">
@@ -5857,7 +6801,7 @@
       </c>
     </row>
     <row r="740" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A740" s="9" t="s">
+      <c r="A740" s="8" t="s">
         <v>35</v>
       </c>
       <c r="B740" s="1" t="s">
@@ -5865,7 +6809,7 @@
       </c>
     </row>
     <row r="741" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A741" s="9" t="s">
+      <c r="A741" s="8" t="s">
         <v>34</v>
       </c>
       <c r="B741" s="1" t="s">
@@ -5873,7 +6817,7 @@
       </c>
     </row>
     <row r="742" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A742" s="10" t="s">
+      <c r="A742" s="9" t="s">
         <v>33</v>
       </c>
       <c r="B742" s="1" t="s">
@@ -5881,7 +6825,7 @@
       </c>
     </row>
     <row r="743" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A743" s="10" t="s">
+      <c r="A743" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B743" s="1" t="s">
@@ -5889,7 +6833,7 @@
       </c>
     </row>
     <row r="744" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A744" s="9" t="s">
+      <c r="A744" s="8" t="s">
         <v>31</v>
       </c>
       <c r="B744" s="1" t="s">
@@ -5897,7 +6841,7 @@
       </c>
     </row>
     <row r="745" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A745" s="9" t="s">
+      <c r="A745" s="8" t="s">
         <v>30</v>
       </c>
       <c r="B745" s="1" t="s">
@@ -5905,7 +6849,7 @@
       </c>
     </row>
     <row r="746" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A746" s="10" t="s">
+      <c r="A746" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B746" s="1" t="s">
@@ -5913,7 +6857,7 @@
       </c>
     </row>
     <row r="747" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A747" s="10" t="s">
+      <c r="A747" s="9" t="s">
         <v>28</v>
       </c>
       <c r="B747" s="1" t="s">
@@ -5921,7 +6865,7 @@
       </c>
     </row>
     <row r="748" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A748" s="10" t="s">
+      <c r="A748" s="9" t="s">
         <v>27</v>
       </c>
       <c r="B748" s="1" t="s">
@@ -5929,7 +6873,7 @@
       </c>
     </row>
     <row r="749" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A749" s="10" t="s">
+      <c r="A749" s="9" t="s">
         <v>26</v>
       </c>
       <c r="B749" s="1" t="s">
@@ -5937,7 +6881,7 @@
       </c>
     </row>
     <row r="750" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A750" s="10" t="s">
+      <c r="A750" s="9" t="s">
         <v>25</v>
       </c>
       <c r="B750" s="1" t="s">
@@ -5945,7 +6889,7 @@
       </c>
     </row>
     <row r="751" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A751" s="10" t="s">
+      <c r="A751" s="9" t="s">
         <v>24</v>
       </c>
       <c r="B751" s="1" t="s">
@@ -5953,7 +6897,7 @@
       </c>
     </row>
     <row r="752" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A752" s="9" t="s">
+      <c r="A752" s="8" t="s">
         <v>23</v>
       </c>
       <c r="B752" s="1" t="s">
@@ -5961,7 +6905,7 @@
       </c>
     </row>
     <row r="753" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A753" s="10" t="s">
+      <c r="A753" s="9" t="s">
         <v>22</v>
       </c>
       <c r="B753" s="1" t="s">
@@ -5969,7 +6913,7 @@
       </c>
     </row>
     <row r="754" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A754" s="10" t="s">
+      <c r="A754" s="9" t="s">
         <v>21</v>
       </c>
       <c r="B754" s="1" t="s">
@@ -5977,7 +6921,7 @@
       </c>
     </row>
     <row r="755" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A755" s="10" t="s">
+      <c r="A755" s="9" t="s">
         <v>20</v>
       </c>
       <c r="B755" s="1" t="s">
@@ -5985,7 +6929,7 @@
       </c>
     </row>
     <row r="756" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A756" s="10" t="s">
+      <c r="A756" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B756" s="1" t="s">
@@ -5993,7 +6937,7 @@
       </c>
     </row>
     <row r="757" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A757" s="10" t="s">
+      <c r="A757" s="9" t="s">
         <v>18</v>
       </c>
       <c r="B757" s="1" t="s">
@@ -6001,7 +6945,7 @@
       </c>
     </row>
     <row r="758" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A758" s="9" t="s">
+      <c r="A758" s="8" t="s">
         <v>17</v>
       </c>
       <c r="B758" s="1" t="s">
@@ -6009,7 +6953,7 @@
       </c>
     </row>
     <row r="759" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A759" s="9" t="s">
+      <c r="A759" s="8" t="s">
         <v>16</v>
       </c>
       <c r="B759" s="1" t="s">
@@ -6017,7 +6961,7 @@
       </c>
     </row>
     <row r="760" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A760" s="9" t="s">
+      <c r="A760" s="8" t="s">
         <v>15</v>
       </c>
       <c r="B760" s="1" t="s">
@@ -6025,7 +6969,7 @@
       </c>
     </row>
     <row r="761" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A761" s="10" t="s">
+      <c r="A761" s="9" t="s">
         <v>14</v>
       </c>
       <c r="B761" s="1" t="s">
@@ -6033,7 +6977,7 @@
       </c>
     </row>
     <row r="762" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A762" s="10" t="s">
+      <c r="A762" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B762" s="1" t="s">
@@ -6041,7 +6985,7 @@
       </c>
     </row>
     <row r="763" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A763" s="10" t="s">
+      <c r="A763" s="9" t="s">
         <v>12</v>
       </c>
       <c r="B763" s="1" t="s">
@@ -6049,7 +6993,7 @@
       </c>
     </row>
     <row r="764" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A764" s="10" t="s">
+      <c r="A764" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B764" s="1" t="s">
@@ -6057,7 +7001,7 @@
       </c>
     </row>
     <row r="765" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A765" s="9" t="s">
+      <c r="A765" s="8" t="s">
         <v>10</v>
       </c>
       <c r="B765" s="1" t="s">
@@ -6065,7 +7009,7 @@
       </c>
     </row>
     <row r="766" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A766" s="9" t="s">
+      <c r="A766" s="8" t="s">
         <v>9</v>
       </c>
       <c r="B766" s="1" t="s">
@@ -6073,7 +7017,7 @@
       </c>
     </row>
     <row r="767" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A767" s="10" t="s">
+      <c r="A767" s="9" t="s">
         <v>8</v>
       </c>
       <c r="B767" s="1" t="s">
@@ -6081,7 +7025,7 @@
       </c>
     </row>
     <row r="768" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A768" s="10" t="s">
+      <c r="A768" s="9" t="s">
         <v>7</v>
       </c>
       <c r="B768" s="1" t="s">
@@ -6089,7 +7033,7 @@
       </c>
     </row>
     <row r="769" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A769" s="10" t="s">
+      <c r="A769" s="9" t="s">
         <v>6</v>
       </c>
       <c r="B769" s="1" t="s">
@@ -6097,7 +7041,7 @@
       </c>
     </row>
     <row r="770" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A770" s="10" t="s">
+      <c r="A770" s="9" t="s">
         <v>5</v>
       </c>
       <c r="B770" s="1" t="s">
@@ -6105,7 +7049,7 @@
       </c>
     </row>
     <row r="771" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A771" s="10" t="s">
+      <c r="A771" s="9" t="s">
         <v>4</v>
       </c>
       <c r="B771" s="1" t="s">
@@ -6113,7 +7057,7 @@
       </c>
     </row>
     <row r="772" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A772" s="10" t="s">
+      <c r="A772" s="9" t="s">
         <v>3</v>
       </c>
       <c r="B772" s="1" t="s">
@@ -6121,7 +7065,7 @@
       </c>
     </row>
     <row r="773" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A773" s="10" t="s">
+      <c r="A773" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B773" s="1" t="s">
@@ -6129,7 +7073,7 @@
       </c>
     </row>
     <row r="775" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A775" s="10">
+      <c r="A775" s="9">
         <v>777425546939086</v>
       </c>
       <c r="B775" s="1" t="s">
@@ -6137,7 +7081,7 @@
       </c>
     </row>
     <row r="776" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A776" s="10" t="s">
+      <c r="A776" s="9" t="s">
         <v>260</v>
       </c>
       <c r="B776" s="1" t="s">
@@ -6145,7 +7089,7 @@
       </c>
     </row>
     <row r="777" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A777" s="9" t="s">
+      <c r="A777" s="8" t="s">
         <v>259</v>
       </c>
       <c r="B777" s="1" t="s">
@@ -6153,7 +7097,7 @@
       </c>
     </row>
     <row r="778" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A778" s="10" t="s">
+      <c r="A778" s="9" t="s">
         <v>258</v>
       </c>
       <c r="B778" s="1" t="s">
@@ -6161,7 +7105,7 @@
       </c>
     </row>
     <row r="779" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A779" s="10" t="s">
+      <c r="A779" s="9" t="s">
         <v>257</v>
       </c>
       <c r="B779" s="1" t="s">
@@ -6169,7 +7113,7 @@
       </c>
     </row>
     <row r="780" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A780" s="9" t="s">
+      <c r="A780" s="8" t="s">
         <v>256</v>
       </c>
       <c r="B780" s="1" t="s">
@@ -6177,7 +7121,7 @@
       </c>
     </row>
     <row r="781" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A781" s="10" t="s">
+      <c r="A781" s="9" t="s">
         <v>255</v>
       </c>
       <c r="B781" s="1" t="s">
@@ -6185,7 +7129,7 @@
       </c>
     </row>
     <row r="782" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A782" s="10" t="s">
+      <c r="A782" s="9" t="s">
         <v>254</v>
       </c>
       <c r="B782" s="1" t="s">
@@ -6193,7 +7137,7 @@
       </c>
     </row>
     <row r="783" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A783" s="10" t="s">
+      <c r="A783" s="9" t="s">
         <v>253</v>
       </c>
       <c r="B783" s="1" t="s">
@@ -6201,7 +7145,7 @@
       </c>
     </row>
     <row r="784" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A784" s="10" t="s">
+      <c r="A784" s="9" t="s">
         <v>252</v>
       </c>
       <c r="B784" s="1" t="s">
@@ -6209,7 +7153,7 @@
       </c>
     </row>
     <row r="785" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A785" s="10" t="s">
+      <c r="A785" s="9" t="s">
         <v>251</v>
       </c>
       <c r="B785" s="1" t="s">
@@ -6217,7 +7161,7 @@
       </c>
     </row>
     <row r="786" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A786" s="10" t="s">
+      <c r="A786" s="9" t="s">
         <v>250</v>
       </c>
       <c r="B786" s="1" t="s">
@@ -6225,7 +7169,7 @@
       </c>
     </row>
     <row r="787" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A787" s="10" t="s">
+      <c r="A787" s="9" t="s">
         <v>249</v>
       </c>
       <c r="B787" s="1" t="s">
@@ -6233,7 +7177,7 @@
       </c>
     </row>
     <row r="788" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A788" s="10" t="s">
+      <c r="A788" s="9" t="s">
         <v>248</v>
       </c>
       <c r="B788" s="1" t="s">
@@ -6241,7 +7185,7 @@
       </c>
     </row>
     <row r="789" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A789" s="9" t="s">
+      <c r="A789" s="8" t="s">
         <v>247</v>
       </c>
       <c r="B789" s="1" t="s">
@@ -6249,7 +7193,7 @@
       </c>
     </row>
     <row r="790" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A790" s="10" t="s">
+      <c r="A790" s="9" t="s">
         <v>246</v>
       </c>
       <c r="B790" s="1" t="s">
@@ -6257,7 +7201,7 @@
       </c>
     </row>
     <row r="791" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A791" s="10" t="s">
+      <c r="A791" s="9" t="s">
         <v>245</v>
       </c>
       <c r="B791" s="1" t="s">
@@ -6265,7 +7209,7 @@
       </c>
     </row>
     <row r="792" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A792" s="10" t="s">
+      <c r="A792" s="9" t="s">
         <v>244</v>
       </c>
       <c r="B792" s="1" t="s">
@@ -6273,7 +7217,7 @@
       </c>
     </row>
     <row r="793" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A793" s="10" t="s">
+      <c r="A793" s="9" t="s">
         <v>243</v>
       </c>
       <c r="B793" s="1" t="s">
@@ -6281,7 +7225,7 @@
       </c>
     </row>
     <row r="794" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A794" s="10" t="s">
+      <c r="A794" s="9" t="s">
         <v>242</v>
       </c>
       <c r="B794" s="1" t="s">
@@ -6289,7 +7233,7 @@
       </c>
     </row>
     <row r="795" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A795" s="9" t="s">
+      <c r="A795" s="8" t="s">
         <v>241</v>
       </c>
       <c r="B795" s="1" t="s">
@@ -6297,7 +7241,7 @@
       </c>
     </row>
     <row r="796" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A796" s="10" t="s">
+      <c r="A796" s="9" t="s">
         <v>240</v>
       </c>
       <c r="B796" s="1" t="s">
@@ -6305,7 +7249,7 @@
       </c>
     </row>
     <row r="797" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A797" s="9" t="s">
+      <c r="A797" s="8" t="s">
         <v>239</v>
       </c>
       <c r="B797" s="1" t="s">
@@ -6313,7 +7257,7 @@
       </c>
     </row>
     <row r="798" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A798" s="10" t="s">
+      <c r="A798" s="9" t="s">
         <v>238</v>
       </c>
       <c r="B798" s="1" t="s">
@@ -6321,7 +7265,7 @@
       </c>
     </row>
     <row r="799" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A799" s="10" t="s">
+      <c r="A799" s="9" t="s">
         <v>237</v>
       </c>
       <c r="B799" s="1" t="s">
@@ -6329,7 +7273,7 @@
       </c>
     </row>
     <row r="800" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A800" s="10" t="s">
+      <c r="A800" s="9" t="s">
         <v>236</v>
       </c>
       <c r="B800" s="1" t="s">
@@ -6337,7 +7281,7 @@
       </c>
     </row>
     <row r="801" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A801" s="10" t="s">
+      <c r="A801" s="9" t="s">
         <v>235</v>
       </c>
       <c r="B801" s="1" t="s">
@@ -6345,7 +7289,7 @@
       </c>
     </row>
     <row r="802" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A802" s="10" t="s">
+      <c r="A802" s="9" t="s">
         <v>234</v>
       </c>
       <c r="B802" s="1" t="s">
@@ -6353,7 +7297,7 @@
       </c>
     </row>
     <row r="803" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A803" s="9" t="s">
+      <c r="A803" s="8" t="s">
         <v>233</v>
       </c>
       <c r="B803" s="1" t="s">
@@ -6361,7 +7305,7 @@
       </c>
     </row>
     <row r="804" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A804" s="10" t="s">
+      <c r="A804" s="9" t="s">
         <v>232</v>
       </c>
       <c r="B804" s="1" t="s">
@@ -6369,7 +7313,7 @@
       </c>
     </row>
     <row r="805" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A805" s="10" t="s">
+      <c r="A805" s="9" t="s">
         <v>231</v>
       </c>
       <c r="B805" s="1" t="s">
@@ -6377,7 +7321,7 @@
       </c>
     </row>
     <row r="806" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A806" s="10" t="s">
+      <c r="A806" s="9" t="s">
         <v>230</v>
       </c>
       <c r="B806" s="1" t="s">
@@ -6385,7 +7329,7 @@
       </c>
     </row>
     <row r="807" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A807" s="10" t="s">
+      <c r="A807" s="9" t="s">
         <v>229</v>
       </c>
       <c r="B807" s="1" t="s">
@@ -6393,7 +7337,7 @@
       </c>
     </row>
     <row r="808" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A808" s="9" t="s">
+      <c r="A808" s="8" t="s">
         <v>228</v>
       </c>
       <c r="B808" s="1" t="s">
@@ -6401,7 +7345,7 @@
       </c>
     </row>
     <row r="809" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A809" s="10" t="s">
+      <c r="A809" s="9" t="s">
         <v>227</v>
       </c>
       <c r="B809" s="1" t="s">
@@ -6409,7 +7353,7 @@
       </c>
     </row>
     <row r="810" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A810" s="10" t="s">
+      <c r="A810" s="9" t="s">
         <v>226</v>
       </c>
       <c r="B810" s="1" t="s">
@@ -6417,7 +7361,7 @@
       </c>
     </row>
     <row r="811" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A811" s="9" t="s">
+      <c r="A811" s="8" t="s">
         <v>225</v>
       </c>
       <c r="B811" s="1" t="s">
@@ -6425,7 +7369,7 @@
       </c>
     </row>
     <row r="812" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A812" s="9" t="s">
+      <c r="A812" s="8" t="s">
         <v>224</v>
       </c>
       <c r="B812" s="1" t="s">
@@ -6433,7 +7377,7 @@
       </c>
     </row>
     <row r="814" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A814" s="10" t="s">
+      <c r="A814" s="9" t="s">
         <v>368</v>
       </c>
       <c r="B814" s="1" t="s">
@@ -6441,7 +7385,7 @@
       </c>
     </row>
     <row r="815" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A815" s="10" t="s">
+      <c r="A815" s="9" t="s">
         <v>367</v>
       </c>
       <c r="B815" s="1" t="s">
@@ -6449,7 +7393,7 @@
       </c>
     </row>
     <row r="816" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A816" s="9" t="s">
+      <c r="A816" s="8" t="s">
         <v>366</v>
       </c>
       <c r="B816" s="1" t="s">
@@ -6457,7 +7401,7 @@
       </c>
     </row>
     <row r="817" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A817" s="10" t="s">
+      <c r="A817" s="9" t="s">
         <v>365</v>
       </c>
       <c r="B817" s="1" t="s">
@@ -6465,7 +7409,7 @@
       </c>
     </row>
     <row r="818" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A818" s="9" t="s">
+      <c r="A818" s="8" t="s">
         <v>364</v>
       </c>
       <c r="B818" s="1" t="s">
@@ -6473,7 +7417,7 @@
       </c>
     </row>
     <row r="819" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A819" s="10" t="s">
+      <c r="A819" s="9" t="s">
         <v>363</v>
       </c>
       <c r="B819" s="1" t="s">
@@ -6481,7 +7425,7 @@
       </c>
     </row>
     <row r="820" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A820" s="10" t="s">
+      <c r="A820" s="9" t="s">
         <v>362</v>
       </c>
       <c r="B820" s="1" t="s">
@@ -6489,7 +7433,7 @@
       </c>
     </row>
     <row r="821" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A821" s="9" t="s">
+      <c r="A821" s="8" t="s">
         <v>288</v>
       </c>
       <c r="B821" s="1" t="s">
@@ -6497,7 +7441,7 @@
       </c>
     </row>
     <row r="822" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A822" s="9" t="s">
+      <c r="A822" s="8" t="s">
         <v>361</v>
       </c>
       <c r="B822" s="1" t="s">
@@ -6505,7 +7449,7 @@
       </c>
     </row>
     <row r="823" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A823" s="10" t="s">
+      <c r="A823" s="9" t="s">
         <v>360</v>
       </c>
       <c r="B823" s="1" t="s">
@@ -6513,7 +7457,7 @@
       </c>
     </row>
     <row r="824" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A824" s="10" t="s">
+      <c r="A824" s="9" t="s">
         <v>359</v>
       </c>
       <c r="B824" s="1" t="s">
@@ -6521,7 +7465,7 @@
       </c>
     </row>
     <row r="825" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A825" s="10" t="s">
+      <c r="A825" s="9" t="s">
         <v>358</v>
       </c>
       <c r="B825" s="1" t="s">
@@ -6529,7 +7473,7 @@
       </c>
     </row>
     <row r="826" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A826" s="9" t="s">
+      <c r="A826" s="8" t="s">
         <v>357</v>
       </c>
       <c r="B826" s="1" t="s">
@@ -6537,7 +7481,7 @@
       </c>
     </row>
     <row r="827" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A827" s="10" t="s">
+      <c r="A827" s="9" t="s">
         <v>356</v>
       </c>
       <c r="B827" s="1" t="s">
@@ -6545,7 +7489,7 @@
       </c>
     </row>
     <row r="828" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A828" s="10" t="s">
+      <c r="A828" s="9" t="s">
         <v>355</v>
       </c>
       <c r="B828" s="1" t="s">
@@ -6553,7 +7497,7 @@
       </c>
     </row>
     <row r="829" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A829" s="9" t="s">
+      <c r="A829" s="8" t="s">
         <v>354</v>
       </c>
       <c r="B829" s="1" t="s">
@@ -6561,7 +7505,7 @@
       </c>
     </row>
     <row r="830" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A830" s="10" t="s">
+      <c r="A830" s="9" t="s">
         <v>353</v>
       </c>
       <c r="B830" s="1" t="s">
@@ -6569,7 +7513,7 @@
       </c>
     </row>
     <row r="831" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A831" s="9" t="s">
+      <c r="A831" s="8" t="s">
         <v>352</v>
       </c>
       <c r="B831" s="1" t="s">
@@ -6577,7 +7521,7 @@
       </c>
     </row>
     <row r="832" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A832" s="10" t="s">
+      <c r="A832" s="9" t="s">
         <v>351</v>
       </c>
       <c r="B832" s="1" t="s">
@@ -6585,7 +7529,7 @@
       </c>
     </row>
     <row r="833" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A833" s="10" t="s">
+      <c r="A833" s="9" t="s">
         <v>350</v>
       </c>
       <c r="B833" s="1" t="s">
@@ -6593,7 +7537,7 @@
       </c>
     </row>
     <row r="834" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A834" s="10" t="s">
+      <c r="A834" s="9" t="s">
         <v>349</v>
       </c>
       <c r="B834" s="1" t="s">
@@ -6601,7 +7545,7 @@
       </c>
     </row>
     <row r="835" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A835" s="10" t="s">
+      <c r="A835" s="9" t="s">
         <v>348</v>
       </c>
       <c r="B835" s="1" t="s">
@@ -6609,7 +7553,7 @@
       </c>
     </row>
     <row r="836" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A836" s="10" t="s">
+      <c r="A836" s="9" t="s">
         <v>347</v>
       </c>
       <c r="B836" s="1" t="s">
@@ -6617,7 +7561,7 @@
       </c>
     </row>
     <row r="837" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A837" s="9" t="s">
+      <c r="A837" s="8" t="s">
         <v>346</v>
       </c>
       <c r="B837" s="1" t="s">
@@ -6625,7 +7569,7 @@
       </c>
     </row>
     <row r="838" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A838" s="10" t="s">
+      <c r="A838" s="9" t="s">
         <v>345</v>
       </c>
       <c r="B838" s="1" t="s">
@@ -6633,7 +7577,7 @@
       </c>
     </row>
     <row r="839" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A839" s="9" t="s">
+      <c r="A839" s="8" t="s">
         <v>344</v>
       </c>
       <c r="B839" s="1" t="s">
@@ -6641,7 +7585,7 @@
       </c>
     </row>
     <row r="840" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A840" s="9" t="s">
+      <c r="A840" s="8" t="s">
         <v>343</v>
       </c>
       <c r="B840" s="1" t="s">
@@ -6649,7 +7593,7 @@
       </c>
     </row>
     <row r="841" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A841" s="10" t="s">
+      <c r="A841" s="9" t="s">
         <v>342</v>
       </c>
       <c r="B841" s="1" t="s">
@@ -6657,7 +7601,7 @@
       </c>
     </row>
     <row r="842" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A842" s="10" t="s">
+      <c r="A842" s="9" t="s">
         <v>341</v>
       </c>
       <c r="B842" s="1" t="s">
@@ -6665,7 +7609,7 @@
       </c>
     </row>
     <row r="843" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A843" s="10" t="s">
+      <c r="A843" s="9" t="s">
         <v>340</v>
       </c>
       <c r="B843" s="1" t="s">
@@ -6673,7 +7617,7 @@
       </c>
     </row>
     <row r="844" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A844" s="9" t="s">
+      <c r="A844" s="8" t="s">
         <v>339</v>
       </c>
       <c r="B844" s="1" t="s">
@@ -6681,7 +7625,7 @@
       </c>
     </row>
     <row r="845" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A845" s="9" t="s">
+      <c r="A845" s="8" t="s">
         <v>338</v>
       </c>
       <c r="B845" s="1" t="s">
@@ -6689,7 +7633,7 @@
       </c>
     </row>
     <row r="846" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A846" s="10" t="s">
+      <c r="A846" s="9" t="s">
         <v>337</v>
       </c>
       <c r="B846" s="1" t="s">
@@ -6697,7 +7641,7 @@
       </c>
     </row>
     <row r="847" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A847" s="10" t="s">
+      <c r="A847" s="9" t="s">
         <v>336</v>
       </c>
       <c r="B847" s="1" t="s">
@@ -6705,7 +7649,7 @@
       </c>
     </row>
     <row r="848" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A848" s="9" t="s">
+      <c r="A848" s="8" t="s">
         <v>335</v>
       </c>
       <c r="B848" s="1" t="s">
@@ -6713,7 +7657,7 @@
       </c>
     </row>
     <row r="849" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A849" s="10" t="s">
+      <c r="A849" s="9" t="s">
         <v>334</v>
       </c>
       <c r="B849" s="1" t="s">
@@ -6721,7 +7665,7 @@
       </c>
     </row>
     <row r="850" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A850" s="9" t="s">
+      <c r="A850" s="8" t="s">
         <v>333</v>
       </c>
       <c r="B850" s="1" t="s">
@@ -6729,7 +7673,7 @@
       </c>
     </row>
     <row r="851" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A851" s="9" t="s">
+      <c r="A851" s="8" t="s">
         <v>332</v>
       </c>
       <c r="B851" s="1" t="s">
@@ -6737,7 +7681,7 @@
       </c>
     </row>
     <row r="852" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A852" s="9" t="s">
+      <c r="A852" s="8" t="s">
         <v>331</v>
       </c>
       <c r="B852" s="1" t="s">
@@ -6745,7 +7689,7 @@
       </c>
     </row>
     <row r="853" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A853" s="10" t="s">
+      <c r="A853" s="9" t="s">
         <v>330</v>
       </c>
       <c r="B853" s="1" t="s">
@@ -6753,7 +7697,7 @@
       </c>
     </row>
     <row r="854" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A854" s="9" t="s">
+      <c r="A854" s="8" t="s">
         <v>329</v>
       </c>
       <c r="B854" s="1" t="s">
@@ -6761,7 +7705,7 @@
       </c>
     </row>
     <row r="855" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A855" s="10" t="s">
+      <c r="A855" s="9" t="s">
         <v>328</v>
       </c>
       <c r="B855" s="1" t="s">
@@ -6769,7 +7713,7 @@
       </c>
     </row>
     <row r="856" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A856" s="10" t="s">
+      <c r="A856" s="9" t="s">
         <v>327</v>
       </c>
       <c r="B856" s="1" t="s">
@@ -6777,7 +7721,7 @@
       </c>
     </row>
     <row r="857" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A857" s="9" t="s">
+      <c r="A857" s="8" t="s">
         <v>326</v>
       </c>
       <c r="B857" s="1" t="s">
@@ -6785,7 +7729,7 @@
       </c>
     </row>
     <row r="858" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A858" s="9" t="s">
+      <c r="A858" s="8" t="s">
         <v>325</v>
       </c>
       <c r="B858" s="1" t="s">
@@ -6793,7 +7737,7 @@
       </c>
     </row>
     <row r="859" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A859" s="9" t="s">
+      <c r="A859" s="8" t="s">
         <v>324</v>
       </c>
       <c r="B859" s="1" t="s">
@@ -6801,7 +7745,7 @@
       </c>
     </row>
     <row r="860" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A860" s="10" t="s">
+      <c r="A860" s="9" t="s">
         <v>323</v>
       </c>
       <c r="B860" s="1" t="s">
@@ -6809,7 +7753,7 @@
       </c>
     </row>
     <row r="861" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A861" s="10" t="s">
+      <c r="A861" s="9" t="s">
         <v>322</v>
       </c>
       <c r="B861" s="1" t="s">
@@ -6817,7 +7761,7 @@
       </c>
     </row>
     <row r="862" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A862" s="10" t="s">
+      <c r="A862" s="9" t="s">
         <v>321</v>
       </c>
       <c r="B862" s="1" t="s">
@@ -6825,7 +7769,7 @@
       </c>
     </row>
     <row r="863" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A863" s="9" t="s">
+      <c r="A863" s="8" t="s">
         <v>320</v>
       </c>
       <c r="B863" s="1" t="s">
@@ -6833,7 +7777,7 @@
       </c>
     </row>
     <row r="864" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A864" s="9" t="s">
+      <c r="A864" s="8" t="s">
         <v>319</v>
       </c>
       <c r="B864" s="1" t="s">
@@ -6841,7 +7785,7 @@
       </c>
     </row>
     <row r="865" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A865" s="10" t="s">
+      <c r="A865" s="9" t="s">
         <v>318</v>
       </c>
       <c r="B865" s="1" t="s">
@@ -6849,7 +7793,7 @@
       </c>
     </row>
     <row r="866" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A866" s="9" t="s">
+      <c r="A866" s="8" t="s">
         <v>317</v>
       </c>
       <c r="B866" s="1" t="s">
@@ -6857,7 +7801,7 @@
       </c>
     </row>
     <row r="867" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A867" s="10" t="s">
+      <c r="A867" s="9" t="s">
         <v>316</v>
       </c>
       <c r="B867" s="1" t="s">
@@ -6865,7 +7809,7 @@
       </c>
     </row>
     <row r="868" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A868" s="10" t="s">
+      <c r="A868" s="9" t="s">
         <v>315</v>
       </c>
       <c r="B868" s="1" t="s">
@@ -6873,7 +7817,7 @@
       </c>
     </row>
     <row r="869" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A869" s="9" t="s">
+      <c r="A869" s="8" t="s">
         <v>314</v>
       </c>
       <c r="B869" s="1" t="s">
@@ -6881,7 +7825,7 @@
       </c>
     </row>
     <row r="870" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A870" s="10" t="s">
+      <c r="A870" s="9" t="s">
         <v>313</v>
       </c>
       <c r="B870" s="1" t="s">
@@ -6889,7 +7833,7 @@
       </c>
     </row>
     <row r="871" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A871" s="10" t="s">
+      <c r="A871" s="9" t="s">
         <v>312</v>
       </c>
       <c r="B871" s="1" t="s">
@@ -6897,7 +7841,7 @@
       </c>
     </row>
     <row r="872" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A872" s="9" t="s">
+      <c r="A872" s="8" t="s">
         <v>311</v>
       </c>
       <c r="B872" s="1" t="s">
@@ -6905,7 +7849,7 @@
       </c>
     </row>
     <row r="873" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A873" s="9" t="s">
+      <c r="A873" s="8" t="s">
         <v>310</v>
       </c>
       <c r="B873" s="1" t="s">
@@ -6913,7 +7857,7 @@
       </c>
     </row>
     <row r="874" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A874" s="9" t="s">
+      <c r="A874" s="8" t="s">
         <v>309</v>
       </c>
       <c r="B874" s="1" t="s">
@@ -6921,7 +7865,7 @@
       </c>
     </row>
     <row r="875" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A875" s="10" t="s">
+      <c r="A875" s="9" t="s">
         <v>308</v>
       </c>
       <c r="B875" s="1" t="s">
@@ -6929,7 +7873,7 @@
       </c>
     </row>
     <row r="876" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A876" s="10" t="s">
+      <c r="A876" s="9" t="s">
         <v>307</v>
       </c>
       <c r="B876" s="1" t="s">
@@ -6937,7 +7881,7 @@
       </c>
     </row>
     <row r="877" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A877" s="10" t="s">
+      <c r="A877" s="9" t="s">
         <v>306</v>
       </c>
       <c r="B877" s="1" t="s">
@@ -6945,7 +7889,7 @@
       </c>
     </row>
     <row r="878" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A878" s="10" t="s">
+      <c r="A878" s="9" t="s">
         <v>305</v>
       </c>
       <c r="B878" s="1" t="s">
@@ -6953,7 +7897,7 @@
       </c>
     </row>
     <row r="879" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A879" s="9" t="s">
+      <c r="A879" s="8" t="s">
         <v>304</v>
       </c>
       <c r="B879" s="1" t="s">
@@ -6961,7 +7905,7 @@
       </c>
     </row>
     <row r="880" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A880" s="10" t="s">
+      <c r="A880" s="9" t="s">
         <v>303</v>
       </c>
       <c r="B880" s="1" t="s">
@@ -6969,7 +7913,7 @@
       </c>
     </row>
     <row r="881" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A881" s="10" t="s">
+      <c r="A881" s="9" t="s">
         <v>302</v>
       </c>
       <c r="B881" s="1" t="s">
@@ -6977,7 +7921,7 @@
       </c>
     </row>
     <row r="882" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A882" s="9" t="s">
+      <c r="A882" s="8" t="s">
         <v>301</v>
       </c>
       <c r="B882" s="1" t="s">
@@ -6985,7 +7929,7 @@
       </c>
     </row>
     <row r="883" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A883" s="10" t="s">
+      <c r="A883" s="9" t="s">
         <v>300</v>
       </c>
       <c r="B883" s="1" t="s">
@@ -6993,7 +7937,7 @@
       </c>
     </row>
     <row r="884" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A884" s="10" t="s">
+      <c r="A884" s="9" t="s">
         <v>299</v>
       </c>
       <c r="B884" s="1" t="s">
@@ -7001,7 +7945,7 @@
       </c>
     </row>
     <row r="885" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A885" s="10" t="s">
+      <c r="A885" s="9" t="s">
         <v>298</v>
       </c>
       <c r="B885" s="1" t="s">
@@ -7009,7 +7953,7 @@
       </c>
     </row>
     <row r="886" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A886" s="10" t="s">
+      <c r="A886" s="9" t="s">
         <v>297</v>
       </c>
       <c r="B886" s="1" t="s">
@@ -7017,7 +7961,7 @@
       </c>
     </row>
     <row r="887" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A887" s="10" t="s">
+      <c r="A887" s="9" t="s">
         <v>285</v>
       </c>
       <c r="B887" s="1" t="s">
@@ -7025,7 +7969,7 @@
       </c>
     </row>
     <row r="888" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A888" s="10" t="s">
+      <c r="A888" s="9" t="s">
         <v>296</v>
       </c>
       <c r="B888" s="1" t="s">
@@ -7033,7 +7977,7 @@
       </c>
     </row>
     <row r="889" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A889" s="9" t="s">
+      <c r="A889" s="8" t="s">
         <v>295</v>
       </c>
       <c r="B889" s="1" t="s">
@@ -7041,7 +7985,7 @@
       </c>
     </row>
     <row r="890" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A890" s="9" t="s">
+      <c r="A890" s="8" t="s">
         <v>294</v>
       </c>
       <c r="B890" s="1" t="s">
@@ -7049,7 +7993,7 @@
       </c>
     </row>
     <row r="891" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A891" s="10" t="s">
+      <c r="A891" s="9" t="s">
         <v>293</v>
       </c>
       <c r="B891" s="1" t="s">
@@ -7057,7 +8001,7 @@
       </c>
     </row>
     <row r="892" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A892" s="10" t="s">
+      <c r="A892" s="9" t="s">
         <v>292</v>
       </c>
       <c r="B892" s="1" t="s">
@@ -7065,7 +8009,7 @@
       </c>
     </row>
     <row r="893" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A893" s="10" t="s">
+      <c r="A893" s="9" t="s">
         <v>291</v>
       </c>
       <c r="B893" s="1" t="s">
@@ -7073,7 +8017,7 @@
       </c>
     </row>
     <row r="894" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A894" s="9" t="s">
+      <c r="A894" s="8" t="s">
         <v>290</v>
       </c>
       <c r="B894" s="1" t="s">
@@ -7081,7 +8025,7 @@
       </c>
     </row>
     <row r="895" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A895" s="10" t="s">
+      <c r="A895" s="9" t="s">
         <v>286</v>
       </c>
       <c r="B895" s="1" t="s">
@@ -7089,7 +8033,7 @@
       </c>
     </row>
     <row r="896" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A896" s="10" t="s">
+      <c r="A896" s="9" t="s">
         <v>289</v>
       </c>
       <c r="B896" s="1" t="s">
@@ -7097,7 +8041,7 @@
       </c>
     </row>
     <row r="897" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A897" s="9" t="s">
+      <c r="A897" s="8" t="s">
         <v>288</v>
       </c>
       <c r="B897" s="1" t="s">
@@ -7105,7 +8049,7 @@
       </c>
     </row>
     <row r="898" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A898" s="9" t="s">
+      <c r="A898" s="8" t="s">
         <v>287</v>
       </c>
       <c r="B898" s="1" t="s">
@@ -7113,7 +8057,7 @@
       </c>
     </row>
     <row r="899" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A899" s="10" t="s">
+      <c r="A899" s="9" t="s">
         <v>286</v>
       </c>
       <c r="B899" s="1" t="s">
@@ -7121,7 +8065,7 @@
       </c>
     </row>
     <row r="900" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A900" s="10" t="s">
+      <c r="A900" s="9" t="s">
         <v>285</v>
       </c>
       <c r="B900" s="1" t="s">
@@ -7129,7 +8073,7 @@
       </c>
     </row>
     <row r="901" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A901" s="10" t="s">
+      <c r="A901" s="9" t="s">
         <v>284</v>
       </c>
       <c r="B901" s="1" t="s">
@@ -7137,7 +8081,7 @@
       </c>
     </row>
     <row r="902" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A902" s="10" t="s">
+      <c r="A902" s="9" t="s">
         <v>283</v>
       </c>
       <c r="B902" s="1" t="s">
@@ -7145,7 +8089,7 @@
       </c>
     </row>
     <row r="903" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A903" s="10" t="s">
+      <c r="A903" s="9" t="s">
         <v>282</v>
       </c>
       <c r="B903" s="1" t="s">
@@ -7153,7 +8097,7 @@
       </c>
     </row>
     <row r="904" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A904" s="9" t="s">
+      <c r="A904" s="8" t="s">
         <v>281</v>
       </c>
       <c r="B904" s="1" t="s">
@@ -7161,7 +8105,7 @@
       </c>
     </row>
     <row r="905" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A905" s="9" t="s">
+      <c r="A905" s="8" t="s">
         <v>280</v>
       </c>
       <c r="B905" s="1" t="s">
@@ -7169,7 +8113,7 @@
       </c>
     </row>
     <row r="906" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A906" s="10" t="s">
+      <c r="A906" s="9" t="s">
         <v>279</v>
       </c>
       <c r="B906" s="1" t="s">
@@ -7177,7 +8121,7 @@
       </c>
     </row>
     <row r="907" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A907" s="10" t="s">
+      <c r="A907" s="9" t="s">
         <v>278</v>
       </c>
       <c r="B907" s="1" t="s">
@@ -7185,7 +8129,7 @@
       </c>
     </row>
     <row r="908" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A908" s="10" t="s">
+      <c r="A908" s="9" t="s">
         <v>277</v>
       </c>
       <c r="B908" s="1" t="s">
@@ -7193,7 +8137,7 @@
       </c>
     </row>
     <row r="909" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A909" s="9" t="s">
+      <c r="A909" s="8" t="s">
         <v>276</v>
       </c>
       <c r="B909" s="1" t="s">
@@ -7201,7 +8145,7 @@
       </c>
     </row>
     <row r="910" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A910" s="10" t="s">
+      <c r="A910" s="9" t="s">
         <v>275</v>
       </c>
       <c r="B910" s="1" t="s">
@@ -7209,7 +8153,7 @@
       </c>
     </row>
     <row r="911" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A911" s="10" t="s">
+      <c r="A911" s="9" t="s">
         <v>274</v>
       </c>
       <c r="B911" s="1" t="s">
@@ -7217,7 +8161,7 @@
       </c>
     </row>
     <row r="912" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A912" s="10" t="s">
+      <c r="A912" s="9" t="s">
         <v>273</v>
       </c>
       <c r="B912" s="1" t="s">
@@ -7225,7 +8169,7 @@
       </c>
     </row>
     <row r="913" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A913" s="10" t="s">
+      <c r="A913" s="9" t="s">
         <v>272</v>
       </c>
       <c r="B913" s="1" t="s">
@@ -7233,7 +8177,7 @@
       </c>
     </row>
     <row r="914" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A914" s="9" t="s">
+      <c r="A914" s="8" t="s">
         <v>271</v>
       </c>
       <c r="B914" s="1" t="s">
@@ -7241,7 +8185,7 @@
       </c>
     </row>
     <row r="915" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A915" s="10" t="s">
+      <c r="A915" s="9" t="s">
         <v>270</v>
       </c>
       <c r="B915" s="1" t="s">
@@ -7249,7 +8193,7 @@
       </c>
     </row>
     <row r="916" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A916" s="10" t="s">
+      <c r="A916" s="9" t="s">
         <v>269</v>
       </c>
       <c r="B916" s="1" t="s">
@@ -7257,7 +8201,7 @@
       </c>
     </row>
     <row r="917" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A917" s="10" t="s">
+      <c r="A917" s="9" t="s">
         <v>268</v>
       </c>
       <c r="B917" s="1" t="s">
@@ -7265,7 +8209,7 @@
       </c>
     </row>
     <row r="918" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A918" s="9" t="s">
+      <c r="A918" s="8" t="s">
         <v>267</v>
       </c>
       <c r="B918" s="1" t="s">
@@ -7273,7 +8217,7 @@
       </c>
     </row>
     <row r="919" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A919" s="10" t="s">
+      <c r="A919" s="9" t="s">
         <v>266</v>
       </c>
       <c r="B919" s="1" t="s">
@@ -7281,7 +8225,7 @@
       </c>
     </row>
     <row r="920" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A920" s="9" t="s">
+      <c r="A920" s="8" t="s">
         <v>265</v>
       </c>
       <c r="B920" s="1" t="s">
@@ -7289,7 +8233,7 @@
       </c>
     </row>
     <row r="921" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A921" s="9" t="s">
+      <c r="A921" s="8" t="s">
         <v>264</v>
       </c>
       <c r="B921" s="1" t="s">
@@ -7297,7 +8241,7 @@
       </c>
     </row>
     <row r="922" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A922" s="9" t="s">
+      <c r="A922" s="8" t="s">
         <v>263</v>
       </c>
       <c r="B922" s="1" t="s">
@@ -7305,7 +8249,7 @@
       </c>
     </row>
     <row r="923" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A923" s="10" t="s">
+      <c r="A923" s="9" t="s">
         <v>262</v>
       </c>
       <c r="B923" s="1" t="s">
@@ -7313,7 +8257,7 @@
       </c>
     </row>
     <row r="925" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A925" s="10" t="s">
+      <c r="A925" s="9" t="s">
         <v>506</v>
       </c>
       <c r="B925" s="1" t="s">
@@ -7321,7 +8265,7 @@
       </c>
     </row>
     <row r="926" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A926" s="9" t="s">
+      <c r="A926" s="8" t="s">
         <v>505</v>
       </c>
       <c r="B926" s="1" t="s">
@@ -7329,7 +8273,7 @@
       </c>
     </row>
     <row r="927" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A927" s="10" t="s">
+      <c r="A927" s="9" t="s">
         <v>504</v>
       </c>
       <c r="B927" s="1" t="s">
@@ -7337,7 +8281,7 @@
       </c>
     </row>
     <row r="928" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A928" s="9" t="s">
+      <c r="A928" s="8" t="s">
         <v>503</v>
       </c>
       <c r="B928" s="1" t="s">
@@ -7345,7 +8289,7 @@
       </c>
     </row>
     <row r="929" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A929" s="9" t="s">
+      <c r="A929" s="8" t="s">
         <v>502</v>
       </c>
       <c r="B929" s="1" t="s">
@@ -7353,7 +8297,7 @@
       </c>
     </row>
     <row r="930" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A930" s="10" t="s">
+      <c r="A930" s="9" t="s">
         <v>501</v>
       </c>
       <c r="B930" s="1" t="s">
@@ -7361,7 +8305,7 @@
       </c>
     </row>
     <row r="931" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A931" s="10" t="s">
+      <c r="A931" s="9" t="s">
         <v>500</v>
       </c>
       <c r="B931" s="1" t="s">
@@ -7369,7 +8313,7 @@
       </c>
     </row>
     <row r="932" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A932" s="9" t="s">
+      <c r="A932" s="8" t="s">
         <v>499</v>
       </c>
       <c r="B932" s="1" t="s">
@@ -7377,7 +8321,7 @@
       </c>
     </row>
     <row r="933" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A933" s="10" t="s">
+      <c r="A933" s="9" t="s">
         <v>498</v>
       </c>
       <c r="B933" s="1" t="s">
@@ -7385,7 +8329,7 @@
       </c>
     </row>
     <row r="934" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A934" s="10" t="s">
+      <c r="A934" s="9" t="s">
         <v>497</v>
       </c>
       <c r="B934" s="1" t="s">
@@ -7393,7 +8337,7 @@
       </c>
     </row>
     <row r="935" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A935" s="9" t="s">
+      <c r="A935" s="8" t="s">
         <v>496</v>
       </c>
       <c r="B935" s="1" t="s">
@@ -7401,7 +8345,7 @@
       </c>
     </row>
     <row r="936" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A936" s="10" t="s">
+      <c r="A936" s="9" t="s">
         <v>495</v>
       </c>
       <c r="B936" s="1" t="s">
@@ -7409,7 +8353,7 @@
       </c>
     </row>
     <row r="937" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A937" s="10" t="s">
+      <c r="A937" s="9" t="s">
         <v>494</v>
       </c>
       <c r="B937" s="1" t="s">
@@ -7417,7 +8361,7 @@
       </c>
     </row>
     <row r="938" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A938" s="10" t="s">
+      <c r="A938" s="9" t="s">
         <v>493</v>
       </c>
       <c r="B938" s="1" t="s">
@@ -7425,7 +8369,7 @@
       </c>
     </row>
     <row r="939" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A939" s="10" t="s">
+      <c r="A939" s="9" t="s">
         <v>492</v>
       </c>
       <c r="B939" s="1" t="s">
@@ -7433,7 +8377,7 @@
       </c>
     </row>
     <row r="940" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A940" s="10" t="s">
+      <c r="A940" s="9" t="s">
         <v>491</v>
       </c>
       <c r="B940" s="1" t="s">
@@ -7441,7 +8385,7 @@
       </c>
     </row>
     <row r="941" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A941" s="9" t="s">
+      <c r="A941" s="8" t="s">
         <v>490</v>
       </c>
       <c r="B941" s="1" t="s">
@@ -7449,7 +8393,7 @@
       </c>
     </row>
     <row r="942" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A942" s="9" t="s">
+      <c r="A942" s="8" t="s">
         <v>489</v>
       </c>
       <c r="B942" s="1" t="s">
@@ -7457,7 +8401,7 @@
       </c>
     </row>
     <row r="943" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A943" s="10" t="s">
+      <c r="A943" s="9" t="s">
         <v>488</v>
       </c>
       <c r="B943" s="1" t="s">
@@ -7465,7 +8409,7 @@
       </c>
     </row>
     <row r="944" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A944" s="10" t="s">
+      <c r="A944" s="9" t="s">
         <v>487</v>
       </c>
       <c r="B944" s="1" t="s">
@@ -7473,7 +8417,7 @@
       </c>
     </row>
     <row r="945" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A945" s="10" t="s">
+      <c r="A945" s="9" t="s">
         <v>486</v>
       </c>
       <c r="B945" s="1" t="s">
@@ -7481,7 +8425,7 @@
       </c>
     </row>
     <row r="946" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A946" s="10" t="s">
+      <c r="A946" s="9" t="s">
         <v>485</v>
       </c>
       <c r="B946" s="1" t="s">
@@ -7489,7 +8433,7 @@
       </c>
     </row>
     <row r="947" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A947" s="9" t="s">
+      <c r="A947" s="8" t="s">
         <v>484</v>
       </c>
       <c r="B947" s="1" t="s">
@@ -7497,7 +8441,7 @@
       </c>
     </row>
     <row r="948" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A948" s="10" t="s">
+      <c r="A948" s="9" t="s">
         <v>483</v>
       </c>
       <c r="B948" s="1" t="s">
@@ -7505,7 +8449,7 @@
       </c>
     </row>
     <row r="949" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A949" s="10" t="s">
+      <c r="A949" s="9" t="s">
         <v>482</v>
       </c>
       <c r="B949" s="1" t="s">
@@ -7513,7 +8457,7 @@
       </c>
     </row>
     <row r="950" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A950" s="10" t="s">
+      <c r="A950" s="9" t="s">
         <v>481</v>
       </c>
       <c r="B950" s="1" t="s">
@@ -7521,7 +8465,7 @@
       </c>
     </row>
     <row r="951" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A951" s="9" t="s">
+      <c r="A951" s="8" t="s">
         <v>480</v>
       </c>
       <c r="B951" s="1" t="s">
@@ -7529,7 +8473,7 @@
       </c>
     </row>
     <row r="952" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A952" s="10" t="s">
+      <c r="A952" s="9" t="s">
         <v>479</v>
       </c>
       <c r="B952" s="1" t="s">
@@ -7537,7 +8481,7 @@
       </c>
     </row>
     <row r="953" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A953" s="10" t="s">
+      <c r="A953" s="9" t="s">
         <v>478</v>
       </c>
       <c r="B953" s="1" t="s">
@@ -7545,7 +8489,7 @@
       </c>
     </row>
     <row r="954" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A954" s="10" t="s">
+      <c r="A954" s="9" t="s">
         <v>477</v>
       </c>
       <c r="B954" s="1" t="s">
@@ -7553,7 +8497,7 @@
       </c>
     </row>
     <row r="955" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A955" s="10" t="s">
+      <c r="A955" s="9" t="s">
         <v>476</v>
       </c>
       <c r="B955" s="1" t="s">
@@ -7561,7 +8505,7 @@
       </c>
     </row>
     <row r="956" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A956" s="10" t="s">
+      <c r="A956" s="9" t="s">
         <v>475</v>
       </c>
       <c r="B956" s="1" t="s">
@@ -7569,7 +8513,7 @@
       </c>
     </row>
     <row r="957" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A957" s="9" t="s">
+      <c r="A957" s="8" t="s">
         <v>474</v>
       </c>
       <c r="B957" s="1" t="s">
@@ -7577,7 +8521,7 @@
       </c>
     </row>
     <row r="958" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A958" s="10" t="s">
+      <c r="A958" s="9" t="s">
         <v>473</v>
       </c>
       <c r="B958" s="1" t="s">
@@ -7585,7 +8529,7 @@
       </c>
     </row>
     <row r="959" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A959" s="10" t="s">
+      <c r="A959" s="9" t="s">
         <v>472</v>
       </c>
       <c r="B959" s="1" t="s">
@@ -7593,7 +8537,7 @@
       </c>
     </row>
     <row r="960" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A960" s="10" t="s">
+      <c r="A960" s="9" t="s">
         <v>471</v>
       </c>
       <c r="B960" s="1" t="s">
@@ -7601,7 +8545,7 @@
       </c>
     </row>
     <row r="961" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A961" s="10" t="s">
+      <c r="A961" s="9" t="s">
         <v>470</v>
       </c>
       <c r="B961" s="1" t="s">
@@ -7609,7 +8553,7 @@
       </c>
     </row>
     <row r="962" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A962" s="10" t="s">
+      <c r="A962" s="9" t="s">
         <v>469</v>
       </c>
       <c r="B962" s="1" t="s">
@@ -7617,7 +8561,7 @@
       </c>
     </row>
     <row r="963" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A963" s="10" t="s">
+      <c r="A963" s="9" t="s">
         <v>468</v>
       </c>
       <c r="B963" s="1" t="s">
@@ -7625,7 +8569,7 @@
       </c>
     </row>
     <row r="964" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A964" s="10" t="s">
+      <c r="A964" s="9" t="s">
         <v>467</v>
       </c>
       <c r="B964" s="1" t="s">
@@ -7633,7 +8577,7 @@
       </c>
     </row>
     <row r="965" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A965" s="10" t="s">
+      <c r="A965" s="9" t="s">
         <v>466</v>
       </c>
       <c r="B965" s="1" t="s">
@@ -7641,7 +8585,7 @@
       </c>
     </row>
     <row r="966" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A966" s="10" t="s">
+      <c r="A966" s="9" t="s">
         <v>465</v>
       </c>
       <c r="B966" s="1" t="s">
@@ -7649,7 +8593,7 @@
       </c>
     </row>
     <row r="967" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A967" s="10" t="s">
+      <c r="A967" s="9" t="s">
         <v>464</v>
       </c>
       <c r="B967" s="1" t="s">
@@ -7657,7 +8601,7 @@
       </c>
     </row>
     <row r="968" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A968" s="10" t="s">
+      <c r="A968" s="9" t="s">
         <v>463</v>
       </c>
       <c r="B968" s="1" t="s">
@@ -7665,7 +8609,7 @@
       </c>
     </row>
     <row r="969" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A969" s="10" t="s">
+      <c r="A969" s="9" t="s">
         <v>462</v>
       </c>
       <c r="B969" s="1" t="s">
@@ -7673,7 +8617,7 @@
       </c>
     </row>
     <row r="970" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A970" s="10" t="s">
+      <c r="A970" s="9" t="s">
         <v>461</v>
       </c>
       <c r="B970" s="1" t="s">
@@ -7681,7 +8625,7 @@
       </c>
     </row>
     <row r="971" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A971" s="10" t="s">
+      <c r="A971" s="9" t="s">
         <v>460</v>
       </c>
       <c r="B971" s="1" t="s">
@@ -7689,7 +8633,7 @@
       </c>
     </row>
     <row r="972" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A972" s="10" t="s">
+      <c r="A972" s="9" t="s">
         <v>459</v>
       </c>
       <c r="B972" s="1" t="s">
@@ -7697,7 +8641,7 @@
       </c>
     </row>
     <row r="973" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A973" s="10" t="s">
+      <c r="A973" s="9" t="s">
         <v>458</v>
       </c>
       <c r="B973" s="1" t="s">
@@ -7705,7 +8649,7 @@
       </c>
     </row>
     <row r="974" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A974" s="10" t="s">
+      <c r="A974" s="9" t="s">
         <v>457</v>
       </c>
       <c r="B974" s="1" t="s">
@@ -7713,7 +8657,7 @@
       </c>
     </row>
     <row r="975" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A975" s="9" t="s">
+      <c r="A975" s="8" t="s">
         <v>456</v>
       </c>
       <c r="B975" s="1" t="s">
@@ -7721,7 +8665,7 @@
       </c>
     </row>
     <row r="976" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A976" s="10" t="s">
+      <c r="A976" s="9" t="s">
         <v>455</v>
       </c>
       <c r="B976" s="1" t="s">
@@ -7729,7 +8673,7 @@
       </c>
     </row>
     <row r="977" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A977" s="10" t="s">
+      <c r="A977" s="9" t="s">
         <v>454</v>
       </c>
       <c r="B977" s="1" t="s">
@@ -7737,7 +8681,7 @@
       </c>
     </row>
     <row r="978" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A978" s="10" t="s">
+      <c r="A978" s="9" t="s">
         <v>453</v>
       </c>
       <c r="B978" s="1" t="s">
@@ -7748,7 +8692,7 @@
       </c>
     </row>
     <row r="979" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A979" s="10" t="s">
+      <c r="A979" s="9" t="s">
         <v>452</v>
       </c>
       <c r="B979" s="1" t="s">
@@ -7756,7 +8700,7 @@
       </c>
     </row>
     <row r="980" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A980" s="10" t="s">
+      <c r="A980" s="9" t="s">
         <v>451</v>
       </c>
       <c r="B980" s="1" t="s">
@@ -7764,7 +8708,7 @@
       </c>
     </row>
     <row r="981" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A981" s="10" t="s">
+      <c r="A981" s="9" t="s">
         <v>450</v>
       </c>
       <c r="B981" s="1" t="s">
@@ -7772,7 +8716,7 @@
       </c>
     </row>
     <row r="982" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A982" s="10" t="s">
+      <c r="A982" s="9" t="s">
         <v>449</v>
       </c>
       <c r="B982" s="1" t="s">
@@ -7780,7 +8724,7 @@
       </c>
     </row>
     <row r="983" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A983" s="10" t="s">
+      <c r="A983" s="9" t="s">
         <v>448</v>
       </c>
       <c r="B983" s="1" t="s">
@@ -7788,7 +8732,7 @@
       </c>
     </row>
     <row r="985" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A985" s="11" t="s">
+      <c r="A985" s="10" t="s">
         <v>509</v>
       </c>
       <c r="B985" s="1" t="s">
@@ -7796,7 +8740,7 @@
       </c>
     </row>
     <row r="986" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A986" s="11" t="s">
+      <c r="A986" s="10" t="s">
         <v>510</v>
       </c>
       <c r="B986" s="1" t="s">
@@ -7804,7 +8748,7 @@
       </c>
     </row>
     <row r="987" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A987" s="12" t="s">
+      <c r="A987" s="11" t="s">
         <v>511</v>
       </c>
       <c r="B987" s="1" t="s">
@@ -7812,7 +8756,7 @@
       </c>
     </row>
     <row r="988" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A988" s="11" t="s">
+      <c r="A988" s="10" t="s">
         <v>512</v>
       </c>
       <c r="B988" s="1" t="s">
@@ -7820,7 +8764,7 @@
       </c>
     </row>
     <row r="989" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A989" s="11" t="s">
+      <c r="A989" s="10" t="s">
         <v>513</v>
       </c>
       <c r="B989" s="1" t="s">
@@ -7828,7 +8772,7 @@
       </c>
     </row>
     <row r="990" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A990" s="12" t="s">
+      <c r="A990" s="11" t="s">
         <v>514</v>
       </c>
       <c r="B990" s="1" t="s">
@@ -7836,7 +8780,7 @@
       </c>
     </row>
     <row r="991" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A991" s="12" t="s">
+      <c r="A991" s="11" t="s">
         <v>515</v>
       </c>
       <c r="B991" s="1" t="s">
@@ -7844,7 +8788,7 @@
       </c>
     </row>
     <row r="992" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A992" s="11" t="s">
+      <c r="A992" s="10" t="s">
         <v>516</v>
       </c>
       <c r="B992" s="1" t="s">
@@ -7852,7 +8796,7 @@
       </c>
     </row>
     <row r="993" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A993" s="12" t="s">
+      <c r="A993" s="11" t="s">
         <v>517</v>
       </c>
       <c r="B993" s="1" t="s">
@@ -7860,7 +8804,7 @@
       </c>
     </row>
     <row r="994" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A994" s="12" t="s">
+      <c r="A994" s="11" t="s">
         <v>518</v>
       </c>
       <c r="B994" s="1" t="s">
@@ -7868,7 +8812,7 @@
       </c>
     </row>
     <row r="995" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A995" s="12" t="s">
+      <c r="A995" s="11" t="s">
         <v>519</v>
       </c>
       <c r="B995" s="1" t="s">
@@ -7876,7 +8820,7 @@
       </c>
     </row>
     <row r="996" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A996" s="11" t="s">
+      <c r="A996" s="10" t="s">
         <v>520</v>
       </c>
       <c r="B996" s="1" t="s">
@@ -7884,7 +8828,7 @@
       </c>
     </row>
     <row r="997" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A997" s="12" t="s">
+      <c r="A997" s="11" t="s">
         <v>521</v>
       </c>
       <c r="B997" s="1" t="s">
@@ -7892,7 +8836,7 @@
       </c>
     </row>
     <row r="998" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A998" s="11" t="s">
+      <c r="A998" s="10" t="s">
         <v>522</v>
       </c>
       <c r="B998" s="1" t="s">
@@ -7900,7 +8844,7 @@
       </c>
     </row>
     <row r="999" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A999" s="11" t="s">
+      <c r="A999" s="10" t="s">
         <v>523</v>
       </c>
       <c r="B999" s="1" t="s">
@@ -7908,7 +8852,7 @@
       </c>
     </row>
     <row r="1000" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1000" s="11" t="s">
+      <c r="A1000" s="10" t="s">
         <v>524</v>
       </c>
       <c r="B1000" s="1" t="s">
@@ -7916,7 +8860,7 @@
       </c>
     </row>
     <row r="1001" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1001" s="12" t="s">
+      <c r="A1001" s="11" t="s">
         <v>525</v>
       </c>
       <c r="B1001" s="1" t="s">
@@ -7924,7 +8868,7 @@
       </c>
     </row>
     <row r="1002" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1002" s="11" t="s">
+      <c r="A1002" s="10" t="s">
         <v>526</v>
       </c>
       <c r="B1002" s="1" t="s">
@@ -7932,7 +8876,7 @@
       </c>
     </row>
     <row r="1003" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1003" s="12" t="s">
+      <c r="A1003" s="11" t="s">
         <v>527</v>
       </c>
       <c r="B1003" s="1" t="s">
@@ -7940,7 +8884,7 @@
       </c>
     </row>
     <row r="1004" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1004" s="11" t="s">
+      <c r="A1004" s="10" t="s">
         <v>528</v>
       </c>
       <c r="B1004" s="1" t="s">
@@ -7948,7 +8892,7 @@
       </c>
     </row>
     <row r="1005" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1005" s="12" t="s">
+      <c r="A1005" s="11" t="s">
         <v>529</v>
       </c>
       <c r="B1005" s="1" t="s">
@@ -7956,7 +8900,7 @@
       </c>
     </row>
     <row r="1006" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1006" s="12" t="s">
+      <c r="A1006" s="11" t="s">
         <v>530</v>
       </c>
       <c r="B1006" s="1" t="s">
@@ -7964,7 +8908,7 @@
       </c>
     </row>
     <row r="1007" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1007" s="12" t="s">
+      <c r="A1007" s="11" t="s">
         <v>531</v>
       </c>
       <c r="B1007" s="1" t="s">
@@ -7972,7 +8916,7 @@
       </c>
     </row>
     <row r="1008" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1008" s="11" t="s">
+      <c r="A1008" s="10" t="s">
         <v>532</v>
       </c>
       <c r="B1008" s="1" t="s">
@@ -7980,7 +8924,7 @@
       </c>
     </row>
     <row r="1009" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1009" s="12" t="s">
+      <c r="A1009" s="11" t="s">
         <v>533</v>
       </c>
       <c r="B1009" s="1" t="s">
@@ -7988,7 +8932,7 @@
       </c>
     </row>
     <row r="1010" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1010" s="11" t="s">
+      <c r="A1010" s="10" t="s">
         <v>534</v>
       </c>
       <c r="B1010" s="1" t="s">
@@ -7996,7 +8940,7 @@
       </c>
     </row>
     <row r="1011" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1011" s="12" t="s">
+      <c r="A1011" s="11" t="s">
         <v>535</v>
       </c>
       <c r="B1011" s="1" t="s">
@@ -8004,7 +8948,7 @@
       </c>
     </row>
     <row r="1012" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1012" s="11" t="s">
+      <c r="A1012" s="10" t="s">
         <v>536</v>
       </c>
       <c r="B1012" s="1" t="s">
@@ -8012,7 +8956,7 @@
       </c>
     </row>
     <row r="1013" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1013" s="12" t="s">
+      <c r="A1013" s="11" t="s">
         <v>537</v>
       </c>
       <c r="B1013" s="1" t="s">
@@ -8020,7 +8964,7 @@
       </c>
     </row>
     <row r="1014" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1014" s="12" t="s">
+      <c r="A1014" s="11" t="s">
         <v>538</v>
       </c>
       <c r="B1014" s="1" t="s">
@@ -8028,7 +8972,7 @@
       </c>
     </row>
     <row r="1015" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1015" s="12" t="s">
+      <c r="A1015" s="11" t="s">
         <v>539</v>
       </c>
       <c r="B1015" s="1" t="s">
@@ -8036,7 +8980,7 @@
       </c>
     </row>
     <row r="1016" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1016" s="11" t="s">
+      <c r="A1016" s="10" t="s">
         <v>540</v>
       </c>
       <c r="B1016" s="1" t="s">
@@ -8044,7 +8988,7 @@
       </c>
     </row>
     <row r="1017" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1017" s="12" t="s">
+      <c r="A1017" s="11" t="s">
         <v>541</v>
       </c>
       <c r="B1017" s="1" t="s">
@@ -8052,7 +8996,7 @@
       </c>
     </row>
     <row r="1018" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1018" s="12" t="s">
+      <c r="A1018" s="11" t="s">
         <v>542</v>
       </c>
       <c r="B1018" s="1" t="s">
@@ -8060,7 +9004,7 @@
       </c>
     </row>
     <row r="1019" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1019" s="11" t="s">
+      <c r="A1019" s="10" t="s">
         <v>543</v>
       </c>
       <c r="B1019" s="1" t="s">
@@ -8068,7 +9012,7 @@
       </c>
     </row>
     <row r="1020" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1020" s="11" t="s">
+      <c r="A1020" s="10" t="s">
         <v>544</v>
       </c>
       <c r="B1020" s="1" t="s">
@@ -8076,7 +9020,7 @@
       </c>
     </row>
     <row r="1021" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1021" s="12" t="s">
+      <c r="A1021" s="11" t="s">
         <v>545</v>
       </c>
       <c r="B1021" s="1" t="s">
@@ -8084,7 +9028,7 @@
       </c>
     </row>
     <row r="1022" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1022" s="12" t="s">
+      <c r="A1022" s="11" t="s">
         <v>546</v>
       </c>
       <c r="B1022" s="1" t="s">
@@ -8092,7 +9036,7 @@
       </c>
     </row>
     <row r="1023" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1023" s="11" t="s">
+      <c r="A1023" s="10" t="s">
         <v>547</v>
       </c>
       <c r="B1023" s="1" t="s">
@@ -8100,7 +9044,7 @@
       </c>
     </row>
     <row r="1024" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1024" s="11" t="s">
+      <c r="A1024" s="10" t="s">
         <v>548</v>
       </c>
       <c r="B1024" s="1" t="s">
@@ -8108,7 +9052,7 @@
       </c>
     </row>
     <row r="1025" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1025" s="12" t="s">
+      <c r="A1025" s="11" t="s">
         <v>549</v>
       </c>
       <c r="B1025" s="1" t="s">
@@ -8116,7 +9060,7 @@
       </c>
     </row>
     <row r="1026" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1026" s="12" t="s">
+      <c r="A1026" s="11" t="s">
         <v>550</v>
       </c>
       <c r="B1026" s="1" t="s">
@@ -8124,7 +9068,7 @@
       </c>
     </row>
     <row r="1027" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1027" s="11" t="s">
+      <c r="A1027" s="10" t="s">
         <v>551</v>
       </c>
       <c r="B1027" s="1" t="s">
@@ -8132,7 +9076,7 @@
       </c>
     </row>
     <row r="1028" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1028" s="12" t="s">
+      <c r="A1028" s="11" t="s">
         <v>552</v>
       </c>
       <c r="B1028" s="1" t="s">
@@ -8140,7 +9084,7 @@
       </c>
     </row>
     <row r="1029" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1029" s="12" t="s">
+      <c r="A1029" s="11" t="s">
         <v>553</v>
       </c>
       <c r="B1029" s="1" t="s">
@@ -8148,7 +9092,7 @@
       </c>
     </row>
     <row r="1030" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1030" s="12" t="s">
+      <c r="A1030" s="11" t="s">
         <v>554</v>
       </c>
       <c r="B1030" s="1" t="s">
@@ -8156,7 +9100,7 @@
       </c>
     </row>
     <row r="1031" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1031" s="12" t="s">
+      <c r="A1031" s="11" t="s">
         <v>555</v>
       </c>
       <c r="B1031" s="1" t="s">
@@ -8164,7 +9108,7 @@
       </c>
     </row>
     <row r="1032" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1032" s="12" t="s">
+      <c r="A1032" s="11" t="s">
         <v>556</v>
       </c>
       <c r="B1032" s="1" t="s">
@@ -8172,7 +9116,7 @@
       </c>
     </row>
     <row r="1033" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1033" s="12" t="s">
+      <c r="A1033" s="11" t="s">
         <v>557</v>
       </c>
       <c r="B1033" s="1" t="s">
@@ -8180,7 +9124,7 @@
       </c>
     </row>
     <row r="1034" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1034" s="12" t="s">
+      <c r="A1034" s="11" t="s">
         <v>558</v>
       </c>
       <c r="B1034" s="1" t="s">
@@ -8188,7 +9132,7 @@
       </c>
     </row>
     <row r="1035" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1035" s="12" t="s">
+      <c r="A1035" s="11" t="s">
         <v>559</v>
       </c>
       <c r="B1035" s="1" t="s">
@@ -8196,7 +9140,7 @@
       </c>
     </row>
     <row r="1036" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1036" s="12" t="s">
+      <c r="A1036" s="11" t="s">
         <v>560</v>
       </c>
       <c r="B1036" s="1" t="s">
@@ -8204,7 +9148,7 @@
       </c>
     </row>
     <row r="1037" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1037" s="12" t="s">
+      <c r="A1037" s="11" t="s">
         <v>561</v>
       </c>
       <c r="B1037" s="1" t="s">
@@ -8212,7 +9156,7 @@
       </c>
     </row>
     <row r="1038" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1038" s="11" t="s">
+      <c r="A1038" s="10" t="s">
         <v>562</v>
       </c>
       <c r="B1038" s="1" t="s">
@@ -8220,7 +9164,7 @@
       </c>
     </row>
     <row r="1039" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1039" s="11" t="s">
+      <c r="A1039" s="10" t="s">
         <v>563</v>
       </c>
       <c r="B1039" s="1" t="s">
@@ -8228,7 +9172,7 @@
       </c>
     </row>
     <row r="1040" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1040" s="12" t="s">
+      <c r="A1040" s="11" t="s">
         <v>564</v>
       </c>
       <c r="B1040" s="1" t="s">
@@ -8236,7 +9180,7 @@
       </c>
     </row>
     <row r="1041" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1041" s="12" t="s">
+      <c r="A1041" s="11" t="s">
         <v>565</v>
       </c>
       <c r="B1041" s="1" t="s">
@@ -8244,7 +9188,7 @@
       </c>
     </row>
     <row r="1042" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1042" s="12" t="s">
+      <c r="A1042" s="11" t="s">
         <v>566</v>
       </c>
       <c r="B1042" s="1" t="s">
@@ -8252,7 +9196,7 @@
       </c>
     </row>
     <row r="1043" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1043" s="12" t="s">
+      <c r="A1043" s="11" t="s">
         <v>567</v>
       </c>
       <c r="B1043" s="1" t="s">
@@ -8260,7 +9204,7 @@
       </c>
     </row>
     <row r="1044" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1044" s="12" t="s">
+      <c r="A1044" s="11" t="s">
         <v>567</v>
       </c>
       <c r="B1044" s="1" t="s">
@@ -8268,7 +9212,7 @@
       </c>
     </row>
     <row r="1045" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1045" s="12" t="s">
+      <c r="A1045" s="11" t="s">
         <v>568</v>
       </c>
       <c r="B1045" s="1" t="s">
@@ -8276,7 +9220,7 @@
       </c>
     </row>
     <row r="1046" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1046" s="11" t="s">
+      <c r="A1046" s="10" t="s">
         <v>569</v>
       </c>
       <c r="B1046" s="1" t="s">
@@ -8284,7 +9228,7 @@
       </c>
     </row>
     <row r="1047" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1047" s="12" t="s">
+      <c r="A1047" s="11" t="s">
         <v>570</v>
       </c>
       <c r="B1047" s="1" t="s">
@@ -8292,7 +9236,7 @@
       </c>
     </row>
     <row r="1048" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1048" s="12" t="s">
+      <c r="A1048" s="11" t="s">
         <v>571</v>
       </c>
       <c r="B1048" s="1" t="s">
@@ -8300,7 +9244,7 @@
       </c>
     </row>
     <row r="1049" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1049" s="12" t="s">
+      <c r="A1049" s="11" t="s">
         <v>572</v>
       </c>
       <c r="B1049" s="1" t="s">
@@ -8308,7 +9252,7 @@
       </c>
     </row>
     <row r="1050" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1050" s="12" t="s">
+      <c r="A1050" s="11" t="s">
         <v>573</v>
       </c>
       <c r="B1050" s="1" t="s">
@@ -8316,7 +9260,7 @@
       </c>
     </row>
     <row r="1051" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1051" s="12" t="s">
+      <c r="A1051" s="11" t="s">
         <v>574</v>
       </c>
       <c r="B1051" s="1" t="s">
@@ -8324,7 +9268,7 @@
       </c>
     </row>
     <row r="1052" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1052" s="11" t="s">
+      <c r="A1052" s="10" t="s">
         <v>575</v>
       </c>
       <c r="B1052" s="1" t="s">
@@ -8332,7 +9276,7 @@
       </c>
     </row>
     <row r="1053" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1053" s="12" t="s">
+      <c r="A1053" s="11" t="s">
         <v>576</v>
       </c>
       <c r="B1053" s="1" t="s">
@@ -8340,7 +9284,7 @@
       </c>
     </row>
     <row r="1054" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1054" s="11" t="s">
+      <c r="A1054" s="10" t="s">
         <v>577</v>
       </c>
       <c r="B1054" s="1" t="s">
@@ -8348,7 +9292,7 @@
       </c>
     </row>
     <row r="1055" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1055" s="12" t="s">
+      <c r="A1055" s="11" t="s">
         <v>578</v>
       </c>
       <c r="B1055" s="1" t="s">
@@ -8356,7 +9300,7 @@
       </c>
     </row>
     <row r="1056" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1056" s="12" t="s">
+      <c r="A1056" s="11" t="s">
         <v>579</v>
       </c>
       <c r="B1056" s="1" t="s">
@@ -8364,7 +9308,7 @@
       </c>
     </row>
     <row r="1057" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1057" s="11" t="s">
+      <c r="A1057" s="10" t="s">
         <v>580</v>
       </c>
       <c r="B1057" s="1" t="s">
@@ -8372,7 +9316,7 @@
       </c>
     </row>
     <row r="1058" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1058" s="11" t="s">
+      <c r="A1058" s="10" t="s">
         <v>581</v>
       </c>
       <c r="B1058" s="1" t="s">
@@ -8380,7 +9324,7 @@
       </c>
     </row>
     <row r="1059" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1059" s="12" t="s">
+      <c r="A1059" s="11" t="s">
         <v>582</v>
       </c>
       <c r="B1059" s="1" t="s">
@@ -8388,7 +9332,7 @@
       </c>
     </row>
     <row r="1060" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1060" s="12" t="s">
+      <c r="A1060" s="11" t="s">
         <v>583</v>
       </c>
       <c r="B1060" s="1" t="s">
@@ -8396,7 +9340,7 @@
       </c>
     </row>
     <row r="1061" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1061" s="12" t="s">
+      <c r="A1061" s="11" t="s">
         <v>584</v>
       </c>
       <c r="B1061" s="1" t="s">
@@ -8404,7 +9348,7 @@
       </c>
     </row>
     <row r="1062" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1062" s="11" t="s">
+      <c r="A1062" s="10" t="s">
         <v>585</v>
       </c>
       <c r="B1062" s="1" t="s">
@@ -8412,7 +9356,7 @@
       </c>
     </row>
     <row r="1063" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1063" s="12" t="s">
+      <c r="A1063" s="11" t="s">
         <v>586</v>
       </c>
       <c r="B1063" s="1" t="s">
@@ -8420,7 +9364,7 @@
       </c>
     </row>
     <row r="1064" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1064" s="12" t="s">
+      <c r="A1064" s="11" t="s">
         <v>587</v>
       </c>
       <c r="B1064" s="1" t="s">
@@ -8428,7 +9372,7 @@
       </c>
     </row>
     <row r="1065" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1065" s="11" t="s">
+      <c r="A1065" s="10" t="s">
         <v>588</v>
       </c>
       <c r="B1065" s="1" t="s">
@@ -8436,7 +9380,7 @@
       </c>
     </row>
     <row r="1066" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1066" s="12" t="s">
+      <c r="A1066" s="11" t="s">
         <v>589</v>
       </c>
       <c r="B1066" s="1" t="s">
@@ -8444,7 +9388,7 @@
       </c>
     </row>
     <row r="1067" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1067" s="11" t="s">
+      <c r="A1067" s="10" t="s">
         <v>590</v>
       </c>
       <c r="B1067" s="1" t="s">
@@ -8452,7 +9396,7 @@
       </c>
     </row>
     <row r="1068" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1068" s="11" t="s">
+      <c r="A1068" s="10" t="s">
         <v>591</v>
       </c>
       <c r="B1068" s="1" t="s">
@@ -8460,7 +9404,7 @@
       </c>
     </row>
     <row r="1069" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1069" s="11" t="s">
+      <c r="A1069" s="10" t="s">
         <v>592</v>
       </c>
       <c r="B1069" s="1" t="s">
@@ -8468,7 +9412,7 @@
       </c>
     </row>
     <row r="1070" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1070" s="11" t="s">
+      <c r="A1070" s="10" t="s">
         <v>593</v>
       </c>
       <c r="B1070" s="1" t="s">
@@ -8476,7 +9420,7 @@
       </c>
     </row>
     <row r="1071" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1071" s="11" t="s">
+      <c r="A1071" s="10" t="s">
         <v>594</v>
       </c>
       <c r="B1071" s="1" t="s">
@@ -8484,7 +9428,7 @@
       </c>
     </row>
     <row r="1072" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1072" s="12" t="s">
+      <c r="A1072" s="11" t="s">
         <v>595</v>
       </c>
       <c r="B1072" s="1" t="s">
@@ -8492,7 +9436,7 @@
       </c>
     </row>
     <row r="1073" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1073" s="12" t="s">
+      <c r="A1073" s="11" t="s">
         <v>555</v>
       </c>
       <c r="B1073" s="1" t="s">
@@ -8500,7 +9444,7 @@
       </c>
     </row>
     <row r="1075" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1075" s="13" t="s">
+      <c r="A1075" s="12" t="s">
         <v>597</v>
       </c>
       <c r="B1075" s="1" t="s">
@@ -8508,7 +9452,7 @@
       </c>
     </row>
     <row r="1076" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1076" s="14" t="s">
+      <c r="A1076" s="13" t="s">
         <v>598</v>
       </c>
       <c r="B1076" s="1" t="s">
@@ -8516,7 +9460,7 @@
       </c>
     </row>
     <row r="1077" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1077" s="14" t="s">
+      <c r="A1077" s="13" t="s">
         <v>599</v>
       </c>
       <c r="B1077" s="1" t="s">
@@ -8524,7 +9468,7 @@
       </c>
     </row>
     <row r="1078" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1078" s="14" t="s">
+      <c r="A1078" s="13" t="s">
         <v>600</v>
       </c>
       <c r="B1078" s="1" t="s">
@@ -8532,7 +9476,7 @@
       </c>
     </row>
     <row r="1079" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1079" s="14" t="s">
+      <c r="A1079" s="13" t="s">
         <v>601</v>
       </c>
       <c r="B1079" s="1" t="s">
@@ -8540,7 +9484,7 @@
       </c>
     </row>
     <row r="1080" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1080" s="14" t="s">
+      <c r="A1080" s="13" t="s">
         <v>602</v>
       </c>
       <c r="B1080" s="1" t="s">
@@ -8548,7 +9492,7 @@
       </c>
     </row>
     <row r="1081" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1081" s="14" t="s">
+      <c r="A1081" s="13" t="s">
         <v>603</v>
       </c>
       <c r="B1081" s="1" t="s">
@@ -8556,7 +9500,7 @@
       </c>
     </row>
     <row r="1082" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1082" s="13" t="s">
+      <c r="A1082" s="12" t="s">
         <v>604</v>
       </c>
       <c r="B1082" s="1" t="s">
@@ -8564,7 +9508,7 @@
       </c>
     </row>
     <row r="1083" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1083" s="14" t="s">
+      <c r="A1083" s="13" t="s">
         <v>605</v>
       </c>
       <c r="B1083" s="1" t="s">
@@ -8572,7 +9516,7 @@
       </c>
     </row>
     <row r="1084" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1084" s="14" t="s">
+      <c r="A1084" s="13" t="s">
         <v>606</v>
       </c>
       <c r="B1084" s="1" t="s">
@@ -8580,7 +9524,7 @@
       </c>
     </row>
     <row r="1085" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1085" s="14" t="s">
+      <c r="A1085" s="13" t="s">
         <v>607</v>
       </c>
       <c r="B1085" s="1" t="s">
@@ -8588,7 +9532,7 @@
       </c>
     </row>
     <row r="1086" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1086" s="13" t="s">
+      <c r="A1086" s="12" t="s">
         <v>608</v>
       </c>
       <c r="B1086" s="1" t="s">
@@ -8596,7 +9540,7 @@
       </c>
     </row>
     <row r="1087" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1087" s="14" t="s">
+      <c r="A1087" s="13" t="s">
         <v>609</v>
       </c>
       <c r="B1087" s="1" t="s">
@@ -8604,7 +9548,7 @@
       </c>
     </row>
     <row r="1088" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1088" s="14" t="s">
+      <c r="A1088" s="13" t="s">
         <v>610</v>
       </c>
       <c r="B1088" s="1" t="s">
@@ -8612,7 +9556,7 @@
       </c>
     </row>
     <row r="1089" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1089" s="14" t="s">
+      <c r="A1089" s="13" t="s">
         <v>611</v>
       </c>
       <c r="B1089" s="1" t="s">
@@ -8620,7 +9564,7 @@
       </c>
     </row>
     <row r="1090" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1090" s="13" t="s">
+      <c r="A1090" s="12" t="s">
         <v>612</v>
       </c>
       <c r="B1090" s="1" t="s">
@@ -8628,7 +9572,7 @@
       </c>
     </row>
     <row r="1091" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1091" s="14" t="s">
+      <c r="A1091" s="13" t="s">
         <v>613</v>
       </c>
       <c r="B1091" s="1" t="s">
@@ -8636,7 +9580,7 @@
       </c>
     </row>
     <row r="1092" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1092" s="14" t="s">
+      <c r="A1092" s="13" t="s">
         <v>614</v>
       </c>
       <c r="B1092" s="1" t="s">
@@ -8644,7 +9588,7 @@
       </c>
     </row>
     <row r="1093" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1093" s="14" t="s">
+      <c r="A1093" s="13" t="s">
         <v>615</v>
       </c>
       <c r="B1093" s="1" t="s">
@@ -8652,7 +9596,7 @@
       </c>
     </row>
     <row r="1094" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1094" s="14" t="s">
+      <c r="A1094" s="13" t="s">
         <v>616</v>
       </c>
       <c r="B1094" s="1" t="s">
@@ -8660,7 +9604,7 @@
       </c>
     </row>
     <row r="1095" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1095" s="14" t="s">
+      <c r="A1095" s="13" t="s">
         <v>616</v>
       </c>
       <c r="B1095" s="1" t="s">
@@ -8668,7 +9612,7 @@
       </c>
     </row>
     <row r="1096" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1096" s="14" t="s">
+      <c r="A1096" s="13" t="s">
         <v>617</v>
       </c>
       <c r="B1096" s="1" t="s">
@@ -8676,7 +9620,7 @@
       </c>
     </row>
     <row r="1097" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1097" s="14" t="s">
+      <c r="A1097" s="13" t="s">
         <v>618</v>
       </c>
       <c r="B1097" s="1" t="s">
@@ -8684,7 +9628,7 @@
       </c>
     </row>
     <row r="1098" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1098" s="13" t="s">
+      <c r="A1098" s="12" t="s">
         <v>619</v>
       </c>
       <c r="B1098" s="1" t="s">
@@ -8692,7 +9636,7 @@
       </c>
     </row>
     <row r="1099" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1099" s="13" t="s">
+      <c r="A1099" s="12" t="s">
         <v>620</v>
       </c>
       <c r="B1099" s="1" t="s">
@@ -8700,7 +9644,7 @@
       </c>
     </row>
     <row r="1100" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1100" s="14" t="s">
+      <c r="A1100" s="13" t="s">
         <v>621</v>
       </c>
       <c r="B1100" s="1" t="s">
@@ -8708,7 +9652,7 @@
       </c>
     </row>
     <row r="1101" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1101" s="14" t="s">
+      <c r="A1101" s="13" t="s">
         <v>622</v>
       </c>
       <c r="B1101" s="1" t="s">
@@ -8716,7 +9660,7 @@
       </c>
     </row>
     <row r="1102" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1102" s="14" t="s">
+      <c r="A1102" s="13" t="s">
         <v>623</v>
       </c>
       <c r="B1102" s="1" t="s">
@@ -8724,7 +9668,7 @@
       </c>
     </row>
     <row r="1103" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1103" s="13" t="s">
+      <c r="A1103" s="12" t="s">
         <v>624</v>
       </c>
       <c r="B1103" s="1" t="s">
@@ -8732,7 +9676,7 @@
       </c>
     </row>
     <row r="1104" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1104" s="14" t="s">
+      <c r="A1104" s="13" t="s">
         <v>625</v>
       </c>
       <c r="B1104" s="1" t="s">
@@ -8740,7 +9684,7 @@
       </c>
     </row>
     <row r="1105" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1105" s="14" t="s">
+      <c r="A1105" s="13" t="s">
         <v>626</v>
       </c>
       <c r="B1105" s="1" t="s">
@@ -8748,7 +9692,7 @@
       </c>
     </row>
     <row r="1106" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1106" s="14" t="s">
+      <c r="A1106" s="13" t="s">
         <v>627</v>
       </c>
       <c r="B1106" s="1" t="s">
@@ -8756,7 +9700,7 @@
       </c>
     </row>
     <row r="1107" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1107" s="14" t="s">
+      <c r="A1107" s="13" t="s">
         <v>628</v>
       </c>
       <c r="B1107" s="1" t="s">
@@ -8764,7 +9708,7 @@
       </c>
     </row>
     <row r="1108" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1108" s="14" t="s">
+      <c r="A1108" s="13" t="s">
         <v>629</v>
       </c>
       <c r="B1108" s="1" t="s">
@@ -8772,7 +9716,7 @@
       </c>
     </row>
     <row r="1109" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1109" s="13" t="s">
+      <c r="A1109" s="12" t="s">
         <v>630</v>
       </c>
       <c r="B1109" s="1" t="s">
@@ -8780,7 +9724,7 @@
       </c>
     </row>
     <row r="1110" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1110" s="13" t="s">
+      <c r="A1110" s="12" t="s">
         <v>631</v>
       </c>
       <c r="B1110" s="1" t="s">
@@ -8788,7 +9732,7 @@
       </c>
     </row>
     <row r="1111" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1111" s="13" t="s">
+      <c r="A1111" s="12" t="s">
         <v>632</v>
       </c>
       <c r="B1111" s="1" t="s">
@@ -8796,7 +9740,7 @@
       </c>
     </row>
     <row r="1112" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1112" s="14" t="s">
+      <c r="A1112" s="13" t="s">
         <v>633</v>
       </c>
       <c r="B1112" s="1" t="s">
@@ -8804,7 +9748,7 @@
       </c>
     </row>
     <row r="1113" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1113" s="14" t="s">
+      <c r="A1113" s="13" t="s">
         <v>634</v>
       </c>
       <c r="B1113" s="1" t="s">
@@ -8812,7 +9756,7 @@
       </c>
     </row>
     <row r="1114" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1114" s="14" t="s">
+      <c r="A1114" s="13" t="s">
         <v>635</v>
       </c>
       <c r="B1114" s="1" t="s">
@@ -8820,7 +9764,7 @@
       </c>
     </row>
     <row r="1115" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1115" s="14" t="s">
+      <c r="A1115" s="13" t="s">
         <v>636</v>
       </c>
       <c r="B1115" s="1" t="s">
@@ -8828,7 +9772,7 @@
       </c>
     </row>
     <row r="1116" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1116" s="13" t="s">
+      <c r="A1116" s="12" t="s">
         <v>637</v>
       </c>
       <c r="B1116" s="1" t="s">
@@ -8836,7 +9780,7 @@
       </c>
     </row>
     <row r="1117" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1117" s="14" t="s">
+      <c r="A1117" s="13" t="s">
         <v>638</v>
       </c>
       <c r="B1117" s="1" t="s">
@@ -8844,7 +9788,7 @@
       </c>
     </row>
     <row r="1118" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1118" s="13" t="s">
+      <c r="A1118" s="12" t="s">
         <v>639</v>
       </c>
       <c r="B1118" s="1" t="s">
@@ -8852,7 +9796,7 @@
       </c>
     </row>
     <row r="1119" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1119" s="13" t="s">
+      <c r="A1119" s="12" t="s">
         <v>640</v>
       </c>
       <c r="B1119" s="1" t="s">
@@ -8860,7 +9804,7 @@
       </c>
     </row>
     <row r="1120" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1120" s="13" t="s">
+      <c r="A1120" s="12" t="s">
         <v>641</v>
       </c>
       <c r="B1120" s="1" t="s">
@@ -8868,7 +9812,7 @@
       </c>
     </row>
     <row r="1121" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1121" s="14" t="s">
+      <c r="A1121" s="13" t="s">
         <v>642</v>
       </c>
       <c r="B1121" s="1" t="s">
@@ -8876,7 +9820,7 @@
       </c>
     </row>
     <row r="1122" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1122" s="14" t="s">
+      <c r="A1122" s="13" t="s">
         <v>643</v>
       </c>
       <c r="B1122" s="1" t="s">
@@ -8884,7 +9828,7 @@
       </c>
     </row>
     <row r="1123" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1123" s="14" t="s">
+      <c r="A1123" s="13" t="s">
         <v>644</v>
       </c>
       <c r="B1123" s="1" t="s">
@@ -8892,7 +9836,7 @@
       </c>
     </row>
     <row r="1124" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1124" s="13" t="s">
+      <c r="A1124" s="12" t="s">
         <v>645</v>
       </c>
       <c r="B1124" s="1" t="s">
@@ -8900,7 +9844,7 @@
       </c>
     </row>
     <row r="1125" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1125" s="14" t="s">
+      <c r="A1125" s="13" t="s">
         <v>646</v>
       </c>
       <c r="B1125" s="1" t="s">
@@ -8908,7 +9852,7 @@
       </c>
     </row>
     <row r="1126" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1126" s="14" t="s">
+      <c r="A1126" s="13" t="s">
         <v>647</v>
       </c>
       <c r="B1126" s="1" t="s">
@@ -8916,7 +9860,7 @@
       </c>
     </row>
     <row r="1127" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1127" s="14" t="s">
+      <c r="A1127" s="13" t="s">
         <v>648</v>
       </c>
       <c r="B1127" s="1" t="s">
@@ -8924,7 +9868,7 @@
       </c>
     </row>
     <row r="1128" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1128" s="14" t="s">
+      <c r="A1128" s="13" t="s">
         <v>649</v>
       </c>
       <c r="B1128" s="1" t="s">
@@ -8932,7 +9876,7 @@
       </c>
     </row>
     <row r="1129" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1129" s="14" t="s">
+      <c r="A1129" s="13" t="s">
         <v>650</v>
       </c>
       <c r="B1129" s="1" t="s">
@@ -8940,7 +9884,7 @@
       </c>
     </row>
     <row r="1130" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1130" s="13" t="s">
+      <c r="A1130" s="12" t="s">
         <v>651</v>
       </c>
       <c r="B1130" s="1" t="s">
@@ -8948,7 +9892,7 @@
       </c>
     </row>
     <row r="1131" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1131" s="14" t="s">
+      <c r="A1131" s="13" t="s">
         <v>652</v>
       </c>
       <c r="B1131" s="1" t="s">
@@ -8956,7 +9900,7 @@
       </c>
     </row>
     <row r="1132" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1132" s="14" t="s">
+      <c r="A1132" s="13" t="s">
         <v>653</v>
       </c>
       <c r="B1132" s="1" t="s">
@@ -8964,7 +9908,7 @@
       </c>
     </row>
     <row r="1133" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1133" s="14" t="s">
+      <c r="A1133" s="13" t="s">
         <v>654</v>
       </c>
       <c r="B1133" s="1" t="s">
@@ -8972,7 +9916,7 @@
       </c>
     </row>
     <row r="1134" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1134" s="13" t="s">
+      <c r="A1134" s="12" t="s">
         <v>655</v>
       </c>
       <c r="B1134" s="1" t="s">
@@ -8980,7 +9924,7 @@
       </c>
     </row>
     <row r="1135" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1135" s="14" t="s">
+      <c r="A1135" s="13" t="s">
         <v>656</v>
       </c>
       <c r="B1135" s="1" t="s">
@@ -8988,7 +9932,7 @@
       </c>
     </row>
     <row r="1136" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1136" s="13" t="s">
+      <c r="A1136" s="12" t="s">
         <v>657</v>
       </c>
       <c r="B1136" s="1" t="s">
@@ -8996,7 +9940,7 @@
       </c>
     </row>
     <row r="1137" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1137" s="14" t="s">
+      <c r="A1137" s="13" t="s">
         <v>658</v>
       </c>
       <c r="B1137" s="1" t="s">
@@ -9004,7 +9948,7 @@
       </c>
     </row>
     <row r="1138" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1138" s="14" t="s">
+      <c r="A1138" s="13" t="s">
         <v>659</v>
       </c>
       <c r="B1138" s="1" t="s">
@@ -9012,7 +9956,7 @@
       </c>
     </row>
     <row r="1139" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1139" s="13" t="s">
+      <c r="A1139" s="12" t="s">
         <v>660</v>
       </c>
       <c r="B1139" s="1" t="s">
@@ -9020,7 +9964,7 @@
       </c>
     </row>
     <row r="1140" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1140" s="13" t="s">
+      <c r="A1140" s="12" t="s">
         <v>661</v>
       </c>
       <c r="B1140" s="1" t="s">
@@ -9028,7 +9972,7 @@
       </c>
     </row>
     <row r="1141" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1141" s="14" t="s">
+      <c r="A1141" s="13" t="s">
         <v>662</v>
       </c>
       <c r="B1141" s="1" t="s">
@@ -9036,7 +9980,7 @@
       </c>
     </row>
     <row r="1142" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1142" s="14" t="s">
+      <c r="A1142" s="13" t="s">
         <v>663</v>
       </c>
       <c r="B1142" s="1" t="s">
@@ -9044,7 +9988,7 @@
       </c>
     </row>
     <row r="1143" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1143" s="13" t="s">
+      <c r="A1143" s="12" t="s">
         <v>664</v>
       </c>
       <c r="B1143" s="1" t="s">
@@ -9052,7 +9996,7 @@
       </c>
     </row>
     <row r="1144" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1144" s="13" t="s">
+      <c r="A1144" s="12" t="s">
         <v>665</v>
       </c>
       <c r="B1144" s="1" t="s">
@@ -9060,7 +10004,7 @@
       </c>
     </row>
     <row r="1145" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1145" s="14" t="s">
+      <c r="A1145" s="13" t="s">
         <v>666</v>
       </c>
       <c r="B1145" s="1" t="s">
@@ -9068,7 +10012,7 @@
       </c>
     </row>
     <row r="1146" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1146" s="14" t="s">
+      <c r="A1146" s="13" t="s">
         <v>667</v>
       </c>
       <c r="B1146" s="1" t="s">
@@ -9076,7 +10020,7 @@
       </c>
     </row>
     <row r="1147" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1147" s="13" t="s">
+      <c r="A1147" s="12" t="s">
         <v>668</v>
       </c>
       <c r="B1147" s="1" t="s">
@@ -9084,7 +10028,7 @@
       </c>
     </row>
     <row r="1148" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1148" s="13" t="s">
+      <c r="A1148" s="12" t="s">
         <v>597</v>
       </c>
       <c r="B1148" s="1" t="s">
@@ -9092,7 +10036,7 @@
       </c>
     </row>
     <row r="1149" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1149" s="14" t="s">
+      <c r="A1149" s="13" t="s">
         <v>669</v>
       </c>
       <c r="B1149" s="1" t="s">
@@ -9100,7 +10044,7 @@
       </c>
     </row>
     <row r="1150" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1150" s="14" t="s">
+      <c r="A1150" s="13" t="s">
         <v>670</v>
       </c>
       <c r="B1150" s="1" t="s">
@@ -9108,7 +10052,7 @@
       </c>
     </row>
     <row r="1152" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1152" s="16" t="s">
+      <c r="A1152" s="15" t="s">
         <v>672</v>
       </c>
       <c r="B1152" s="1" t="s">
@@ -9116,7 +10060,7 @@
       </c>
     </row>
     <row r="1153" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1153" s="16" t="s">
+      <c r="A1153" s="15" t="s">
         <v>673</v>
       </c>
       <c r="B1153" s="1" t="s">
@@ -9124,7 +10068,7 @@
       </c>
     </row>
     <row r="1154" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1154" s="16" t="s">
+      <c r="A1154" s="15" t="s">
         <v>674</v>
       </c>
       <c r="B1154" s="1" t="s">
@@ -9132,7 +10076,7 @@
       </c>
     </row>
     <row r="1155" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1155" s="16" t="s">
+      <c r="A1155" s="15" t="s">
         <v>675</v>
       </c>
       <c r="B1155" s="1" t="s">
@@ -9140,7 +10084,7 @@
       </c>
     </row>
     <row r="1156" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1156" s="16" t="s">
+      <c r="A1156" s="15" t="s">
         <v>676</v>
       </c>
       <c r="B1156" s="1" t="s">
@@ -9148,7 +10092,7 @@
       </c>
     </row>
     <row r="1157" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1157" s="16" t="s">
+      <c r="A1157" s="15" t="s">
         <v>677</v>
       </c>
       <c r="B1157" s="1" t="s">
@@ -9156,7 +10100,7 @@
       </c>
     </row>
     <row r="1158" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1158" s="16" t="s">
+      <c r="A1158" s="15" t="s">
         <v>678</v>
       </c>
       <c r="B1158" s="1" t="s">
@@ -9164,7 +10108,7 @@
       </c>
     </row>
     <row r="1159" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1159" s="15" t="s">
+      <c r="A1159" s="14" t="s">
         <v>679</v>
       </c>
       <c r="B1159" s="1" t="s">
@@ -9172,7 +10116,7 @@
       </c>
     </row>
     <row r="1160" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1160" s="16" t="s">
+      <c r="A1160" s="15" t="s">
         <v>680</v>
       </c>
       <c r="B1160" s="1" t="s">
@@ -9180,7 +10124,7 @@
       </c>
     </row>
     <row r="1161" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1161" s="16" t="s">
+      <c r="A1161" s="15" t="s">
         <v>681</v>
       </c>
       <c r="B1161" s="1" t="s">
@@ -9188,7 +10132,7 @@
       </c>
     </row>
     <row r="1162" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1162" s="16" t="s">
+      <c r="A1162" s="15" t="s">
         <v>682</v>
       </c>
       <c r="B1162" s="1" t="s">
@@ -9196,7 +10140,7 @@
       </c>
     </row>
     <row r="1163" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1163" s="16" t="s">
+      <c r="A1163" s="15" t="s">
         <v>683</v>
       </c>
       <c r="B1163" s="1" t="s">
@@ -9204,7 +10148,7 @@
       </c>
     </row>
     <row r="1164" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1164" s="16" t="s">
+      <c r="A1164" s="15" t="s">
         <v>684</v>
       </c>
       <c r="B1164" s="1" t="s">
@@ -9212,7 +10156,7 @@
       </c>
     </row>
     <row r="1165" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1165" s="16" t="s">
+      <c r="A1165" s="15" t="s">
         <v>685</v>
       </c>
       <c r="B1165" s="1" t="s">
@@ -9220,7 +10164,7 @@
       </c>
     </row>
     <row r="1166" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1166" s="16" t="s">
+      <c r="A1166" s="15" t="s">
         <v>686</v>
       </c>
       <c r="B1166" s="1" t="s">
@@ -9228,7 +10172,7 @@
       </c>
     </row>
     <row r="1167" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1167" s="16" t="s">
+      <c r="A1167" s="15" t="s">
         <v>687</v>
       </c>
       <c r="B1167" s="1" t="s">
@@ -9236,7 +10180,7 @@
       </c>
     </row>
     <row r="1168" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1168" s="16" t="s">
+      <c r="A1168" s="15" t="s">
         <v>688</v>
       </c>
       <c r="B1168" s="1" t="s">
@@ -9244,7 +10188,7 @@
       </c>
     </row>
     <row r="1169" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1169" s="16" t="s">
+      <c r="A1169" s="15" t="s">
         <v>689</v>
       </c>
       <c r="B1169" s="1" t="s">
@@ -9252,7 +10196,7 @@
       </c>
     </row>
     <row r="1170" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1170" s="15" t="s">
+      <c r="A1170" s="14" t="s">
         <v>690</v>
       </c>
       <c r="B1170" s="1" t="s">
@@ -9260,7 +10204,7 @@
       </c>
     </row>
     <row r="1171" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1171" s="15" t="s">
+      <c r="A1171" s="14" t="s">
         <v>691</v>
       </c>
       <c r="B1171" s="1" t="s">
@@ -9268,7 +10212,7 @@
       </c>
     </row>
     <row r="1172" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1172" s="16" t="s">
+      <c r="A1172" s="15" t="s">
         <v>692</v>
       </c>
       <c r="B1172" s="1" t="s">
@@ -9276,7 +10220,7 @@
       </c>
     </row>
     <row r="1173" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1173" s="16" t="s">
+      <c r="A1173" s="15" t="s">
         <v>693</v>
       </c>
       <c r="B1173" s="1" t="s">
@@ -9284,7 +10228,7 @@
       </c>
     </row>
     <row r="1174" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1174" s="15" t="s">
+      <c r="A1174" s="14" t="s">
         <v>694</v>
       </c>
       <c r="B1174" s="1" t="s">
@@ -9292,7 +10236,7 @@
       </c>
     </row>
     <row r="1175" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1175" s="16" t="s">
+      <c r="A1175" s="15" t="s">
         <v>695</v>
       </c>
       <c r="B1175" s="1" t="s">
@@ -9300,7 +10244,7 @@
       </c>
     </row>
     <row r="1176" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1176" s="16" t="s">
+      <c r="A1176" s="15" t="s">
         <v>696</v>
       </c>
       <c r="B1176" s="1" t="s">
@@ -9308,7 +10252,7 @@
       </c>
     </row>
     <row r="1177" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1177" s="16" t="s">
+      <c r="A1177" s="15" t="s">
         <v>697</v>
       </c>
       <c r="B1177" s="1" t="s">
@@ -9316,7 +10260,7 @@
       </c>
     </row>
     <row r="1178" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1178" s="15" t="s">
+      <c r="A1178" s="14" t="s">
         <v>698</v>
       </c>
       <c r="B1178" s="1" t="s">
@@ -9324,7 +10268,7 @@
       </c>
     </row>
     <row r="1179" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1179" s="15" t="s">
+      <c r="A1179" s="14" t="s">
         <v>699</v>
       </c>
       <c r="B1179" s="1" t="s">
@@ -9332,7 +10276,7 @@
       </c>
     </row>
     <row r="1180" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1180" s="16" t="s">
+      <c r="A1180" s="15" t="s">
         <v>700</v>
       </c>
       <c r="B1180" s="1" t="s">
@@ -9340,7 +10284,7 @@
       </c>
     </row>
     <row r="1181" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1181" s="16" t="s">
+      <c r="A1181" s="15" t="s">
         <v>701</v>
       </c>
       <c r="B1181" s="1" t="s">
@@ -9348,7 +10292,7 @@
       </c>
     </row>
     <row r="1182" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1182" s="16" t="s">
+      <c r="A1182" s="15" t="s">
         <v>702</v>
       </c>
       <c r="B1182" s="1" t="s">
@@ -9356,7 +10300,7 @@
       </c>
     </row>
     <row r="1183" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1183" s="16" t="s">
+      <c r="A1183" s="15" t="s">
         <v>703</v>
       </c>
       <c r="B1183" s="1" t="s">
@@ -9364,7 +10308,7 @@
       </c>
     </row>
     <row r="1184" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1184" s="15" t="s">
+      <c r="A1184" s="14" t="s">
         <v>704</v>
       </c>
       <c r="B1184" s="1" t="s">
@@ -9372,7 +10316,7 @@
       </c>
     </row>
     <row r="1185" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1185" s="15" t="s">
+      <c r="A1185" s="14" t="s">
         <v>705</v>
       </c>
       <c r="B1185" s="1" t="s">
@@ -9380,7 +10324,7 @@
       </c>
     </row>
     <row r="1186" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1186" s="15" t="s">
+      <c r="A1186" s="14" t="s">
         <v>706</v>
       </c>
       <c r="B1186" s="1" t="s">
@@ -9388,7 +10332,7 @@
       </c>
     </row>
     <row r="1187" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1187" s="16" t="s">
+      <c r="A1187" s="15" t="s">
         <v>707</v>
       </c>
       <c r="B1187" s="1" t="s">
@@ -9396,7 +10340,7 @@
       </c>
     </row>
     <row r="1188" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1188" s="15" t="s">
+      <c r="A1188" s="14" t="s">
         <v>708</v>
       </c>
       <c r="B1188" s="1" t="s">
@@ -9404,7 +10348,7 @@
       </c>
     </row>
     <row r="1189" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1189" s="15" t="s">
+      <c r="A1189" s="14" t="s">
         <v>709</v>
       </c>
       <c r="B1189" s="1" t="s">
@@ -9412,7 +10356,7 @@
       </c>
     </row>
     <row r="1190" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1190" s="16" t="s">
+      <c r="A1190" s="15" t="s">
         <v>710</v>
       </c>
       <c r="B1190" s="1" t="s">
@@ -9420,7 +10364,7 @@
       </c>
     </row>
     <row r="1191" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1191" s="15" t="s">
+      <c r="A1191" s="14" t="s">
         <v>711</v>
       </c>
       <c r="B1191" s="1" t="s">
@@ -9428,7 +10372,7 @@
       </c>
     </row>
     <row r="1192" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1192" s="16" t="s">
+      <c r="A1192" s="15" t="s">
         <v>712</v>
       </c>
       <c r="B1192" s="1" t="s">
@@ -9436,7 +10380,7 @@
       </c>
     </row>
     <row r="1193" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1193" s="15" t="s">
+      <c r="A1193" s="14" t="s">
         <v>713</v>
       </c>
       <c r="B1193" s="1" t="s">
@@ -9444,7 +10388,7 @@
       </c>
     </row>
     <row r="1194" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1194" s="15" t="s">
+      <c r="A1194" s="14" t="s">
         <v>714</v>
       </c>
       <c r="B1194" s="1" t="s">
@@ -9452,7 +10396,7 @@
       </c>
     </row>
     <row r="1195" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1195" s="16" t="s">
+      <c r="A1195" s="15" t="s">
         <v>715</v>
       </c>
       <c r="B1195" s="1" t="s">
@@ -9460,7 +10404,7 @@
       </c>
     </row>
     <row r="1196" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1196" s="16" t="s">
+      <c r="A1196" s="15" t="s">
         <v>716</v>
       </c>
       <c r="B1196" s="1" t="s">
@@ -9468,7 +10412,7 @@
       </c>
     </row>
     <row r="1197" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1197" s="16" t="s">
+      <c r="A1197" s="15" t="s">
         <v>717</v>
       </c>
       <c r="B1197" s="1" t="s">
@@ -9476,7 +10420,7 @@
       </c>
     </row>
     <row r="1198" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1198" s="16" t="s">
+      <c r="A1198" s="15" t="s">
         <v>718</v>
       </c>
       <c r="B1198" s="1" t="s">
@@ -9484,7 +10428,7 @@
       </c>
     </row>
     <row r="1199" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1199" s="16" t="s">
+      <c r="A1199" s="15" t="s">
         <v>719</v>
       </c>
       <c r="B1199" s="1" t="s">
@@ -9492,7 +10436,7 @@
       </c>
     </row>
     <row r="1200" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1200" s="16" t="s">
+      <c r="A1200" s="15" t="s">
         <v>720</v>
       </c>
       <c r="B1200" s="1" t="s">
@@ -9500,7 +10444,7 @@
       </c>
     </row>
     <row r="1201" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1201" s="16" t="s">
+      <c r="A1201" s="15" t="s">
         <v>721</v>
       </c>
       <c r="B1201" s="1" t="s">
@@ -9508,7 +10452,7 @@
       </c>
     </row>
     <row r="1202" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1202" s="15" t="s">
+      <c r="A1202" s="14" t="s">
         <v>722</v>
       </c>
       <c r="B1202" s="1" t="s">
@@ -9516,7 +10460,7 @@
       </c>
     </row>
     <row r="1203" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1203" s="15" t="s">
+      <c r="A1203" s="14" t="s">
         <v>723</v>
       </c>
       <c r="B1203" s="1" t="s">
@@ -9524,7 +10468,7 @@
       </c>
     </row>
     <row r="1204" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1204" s="16" t="s">
+      <c r="A1204" s="15" t="s">
         <v>724</v>
       </c>
       <c r="B1204" s="1" t="s">
@@ -9532,7 +10476,7 @@
       </c>
     </row>
     <row r="1205" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1205" s="15" t="s">
+      <c r="A1205" s="14" t="s">
         <v>725</v>
       </c>
       <c r="B1205" s="1" t="s">
@@ -9540,7 +10484,7 @@
       </c>
     </row>
     <row r="1206" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1206" s="16" t="s">
+      <c r="A1206" s="15" t="s">
         <v>726</v>
       </c>
       <c r="B1206" s="1" t="s">
@@ -9548,7 +10492,7 @@
       </c>
     </row>
     <row r="1207" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1207" s="16" t="s">
+      <c r="A1207" s="15" t="s">
         <v>727</v>
       </c>
       <c r="B1207" s="1" t="s">
@@ -9556,7 +10500,7 @@
       </c>
     </row>
     <row r="1208" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1208" s="15" t="s">
+      <c r="A1208" s="14" t="s">
         <v>728</v>
       </c>
       <c r="B1208" s="1" t="s">
@@ -9564,7 +10508,7 @@
       </c>
     </row>
     <row r="1209" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1209" s="15" t="s">
+      <c r="A1209" s="14" t="s">
         <v>729</v>
       </c>
       <c r="B1209" s="1" t="s">
@@ -9572,7 +10516,7 @@
       </c>
     </row>
     <row r="1210" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1210" s="16" t="s">
+      <c r="A1210" s="15" t="s">
         <v>730</v>
       </c>
       <c r="B1210" s="1" t="s">
@@ -9580,7 +10524,7 @@
       </c>
     </row>
     <row r="1211" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1211" s="15" t="s">
+      <c r="A1211" s="14" t="s">
         <v>731</v>
       </c>
       <c r="B1211" s="1" t="s">
@@ -9588,7 +10532,7 @@
       </c>
     </row>
     <row r="1212" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1212" s="16" t="s">
+      <c r="A1212" s="15" t="s">
         <v>732</v>
       </c>
       <c r="B1212" s="1" t="s">
@@ -9596,7 +10540,7 @@
       </c>
     </row>
     <row r="1213" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1213" s="15" t="s">
+      <c r="A1213" s="14" t="s">
         <v>733</v>
       </c>
       <c r="B1213" s="1" t="s">
@@ -9604,7 +10548,7 @@
       </c>
     </row>
     <row r="1214" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1214" s="16" t="s">
+      <c r="A1214" s="15" t="s">
         <v>672</v>
       </c>
       <c r="B1214" s="1" t="s">

--- a/on_the_way.xlsx
+++ b/on_the_way.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1687" uniqueCount="765">
   <si>
     <t>Track</t>
   </si>
@@ -2026,6 +2026,291 @@
   </si>
   <si>
     <t>05.08.26</t>
+  </si>
+  <si>
+    <t>JT5511973202283</t>
+  </si>
+  <si>
+    <t>JT5511973153680</t>
+  </si>
+  <si>
+    <t>YT8892595504448</t>
+  </si>
+  <si>
+    <t>JT5510751101070</t>
+  </si>
+  <si>
+    <t>465553370173853</t>
+  </si>
+  <si>
+    <t>JT5510949500563</t>
+  </si>
+  <si>
+    <t>YT0700600264066</t>
+  </si>
+  <si>
+    <t>YT8892361595988</t>
+  </si>
+  <si>
+    <t>465558909221993</t>
+  </si>
+  <si>
+    <t>YT8892351647709</t>
+  </si>
+  <si>
+    <t>777432678439867</t>
+  </si>
+  <si>
+    <t>777432279361848</t>
+  </si>
+  <si>
+    <t>JT5511973902656</t>
+  </si>
+  <si>
+    <t>777432214675708</t>
+  </si>
+  <si>
+    <t>JT5510762925121</t>
+  </si>
+  <si>
+    <t>777432240513929</t>
+  </si>
+  <si>
+    <t>465551672943085</t>
+  </si>
+  <si>
+    <t>772074120654568</t>
+  </si>
+  <si>
+    <t>465551581548192</t>
+  </si>
+  <si>
+    <t>465551470001808</t>
+  </si>
+  <si>
+    <t>777432263500258</t>
+  </si>
+  <si>
+    <t>777432246140664</t>
+  </si>
+  <si>
+    <t>465550458587016</t>
+  </si>
+  <si>
+    <t>YT0700336055592</t>
+  </si>
+  <si>
+    <t>465558592879946</t>
+  </si>
+  <si>
+    <t>JT5511907726353</t>
+  </si>
+  <si>
+    <t>465551842614031</t>
+  </si>
+  <si>
+    <t>JT5511728205740</t>
+  </si>
+  <si>
+    <t>YT8892186939080</t>
+  </si>
+  <si>
+    <t>465551743051717</t>
+  </si>
+  <si>
+    <t>465557629034254</t>
+  </si>
+  <si>
+    <t>777432185033186</t>
+  </si>
+  <si>
+    <t>79127714461538</t>
+  </si>
+  <si>
+    <t>777432658497305</t>
+  </si>
+  <si>
+    <t>313076959715943</t>
+  </si>
+  <si>
+    <t>JT5510881627338</t>
+  </si>
+  <si>
+    <t>YT0700616152270</t>
+  </si>
+  <si>
+    <t>YT0700597569647</t>
+  </si>
+  <si>
+    <t>465558694397552</t>
+  </si>
+  <si>
+    <t>773434720557336</t>
+  </si>
+  <si>
+    <t>YT8892426122009</t>
+  </si>
+  <si>
+    <t>777432446417598</t>
+  </si>
+  <si>
+    <t>JT5511907159189</t>
+  </si>
+  <si>
+    <t>JT5511748199726</t>
+  </si>
+  <si>
+    <t>YT8892362101364</t>
+  </si>
+  <si>
+    <t>777432285504366</t>
+  </si>
+  <si>
+    <t>777432680249682</t>
+  </si>
+  <si>
+    <t>465551614318475</t>
+  </si>
+  <si>
+    <t>JT5511729139154</t>
+  </si>
+  <si>
+    <t>777431653134158</t>
+  </si>
+  <si>
+    <t>777432355607831</t>
+  </si>
+  <si>
+    <t>JT5511735288630</t>
+  </si>
+  <si>
+    <t>465556047210629</t>
+  </si>
+  <si>
+    <t>YT0700020043612</t>
+  </si>
+  <si>
+    <t>YT8892560147218</t>
+  </si>
+  <si>
+    <t>465552096769480</t>
+  </si>
+  <si>
+    <t>465558765931389</t>
+  </si>
+  <si>
+    <t>777429492292130</t>
+  </si>
+  <si>
+    <t>777432466543501</t>
+  </si>
+  <si>
+    <t>JT5511891191583</t>
+  </si>
+  <si>
+    <t>JT5512024904547</t>
+  </si>
+  <si>
+    <t>777432663036500</t>
+  </si>
+  <si>
+    <t>777432477122243</t>
+  </si>
+  <si>
+    <t>777431676072240</t>
+  </si>
+  <si>
+    <t>YT0700369824068</t>
+  </si>
+  <si>
+    <t>465553583088242</t>
+  </si>
+  <si>
+    <t>YT0700117383700</t>
+  </si>
+  <si>
+    <t>YT8892362552036</t>
+  </si>
+  <si>
+    <t>YT0700368351174</t>
+  </si>
+  <si>
+    <t>465550137059361</t>
+  </si>
+  <si>
+    <t>JT5510914728341</t>
+  </si>
+  <si>
+    <t>777432391504005</t>
+  </si>
+  <si>
+    <t>YT0700577599440</t>
+  </si>
+  <si>
+    <t>777432184056112</t>
+  </si>
+  <si>
+    <t>777432408169779</t>
+  </si>
+  <si>
+    <t>777432221794253</t>
+  </si>
+  <si>
+    <t>777432270160105</t>
+  </si>
+  <si>
+    <t>777431660785017</t>
+  </si>
+  <si>
+    <t>YT0700560157226</t>
+  </si>
+  <si>
+    <t>777432250208460</t>
+  </si>
+  <si>
+    <t>777431648147834</t>
+  </si>
+  <si>
+    <t>JT5511912987930</t>
+  </si>
+  <si>
+    <t>YT0700649807824</t>
+  </si>
+  <si>
+    <t>JT5510917714135</t>
+  </si>
+  <si>
+    <t>YT7636081852193</t>
+  </si>
+  <si>
+    <t>JT5510702699570</t>
+  </si>
+  <si>
+    <t>YT0700033639613</t>
+  </si>
+  <si>
+    <t>777432470862713</t>
+  </si>
+  <si>
+    <t>YT0700560949247</t>
+  </si>
+  <si>
+    <t>465551248621930</t>
+  </si>
+  <si>
+    <t>313075838295836</t>
+  </si>
+  <si>
+    <t>777432481130011</t>
+  </si>
+  <si>
+    <t>777432378881342</t>
+  </si>
+  <si>
+    <t>465555652660380</t>
+  </si>
+  <si>
+    <t>07.08.26</t>
   </si>
 </sst>
 </file>
@@ -2087,7 +2372,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyBorder="0">
       <alignment vertical="center"/>
@@ -2098,8 +2383,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyBorder="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyBorder="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2152,12 +2440,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="4" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1"/>
     <cellStyle name="Normal 3" xfId="2"/>
     <cellStyle name="Normal 4" xfId="3"/>
+    <cellStyle name="Normal 5" xfId="4"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
@@ -2669,7 +2964,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D759"/>
+  <dimension ref="A1:D856"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.44140625" style="2" customWidth="1"/>
@@ -8674,6 +8969,774 @@
       </c>
       <c r="B759" s="1" t="s">
         <v>669</v>
+      </c>
+    </row>
+    <row r="761" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A761" s="19" t="s">
+        <v>763</v>
+      </c>
+      <c r="B761" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="762" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A762" s="19" t="s">
+        <v>762</v>
+      </c>
+      <c r="B762" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="763" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A763" s="19" t="s">
+        <v>761</v>
+      </c>
+      <c r="B763" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="764" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A764" s="19" t="s">
+        <v>760</v>
+      </c>
+      <c r="B764" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="765" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A765" s="19" t="s">
+        <v>759</v>
+      </c>
+      <c r="B765" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="766" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A766" s="18" t="s">
+        <v>758</v>
+      </c>
+      <c r="B766" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="767" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A767" s="19" t="s">
+        <v>757</v>
+      </c>
+      <c r="B767" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="768" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A768" s="18" t="s">
+        <v>756</v>
+      </c>
+      <c r="B768" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="769" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A769" s="18" t="s">
+        <v>755</v>
+      </c>
+      <c r="B769" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="770" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A770" s="18" t="s">
+        <v>671</v>
+      </c>
+      <c r="B770" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="771" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A771" s="18" t="s">
+        <v>754</v>
+      </c>
+      <c r="B771" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="772" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A772" s="18" t="s">
+        <v>753</v>
+      </c>
+      <c r="B772" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="773" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A773" s="18" t="s">
+        <v>752</v>
+      </c>
+      <c r="B773" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="774" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A774" s="18" t="s">
+        <v>751</v>
+      </c>
+      <c r="B774" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="775" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A775" s="19" t="s">
+        <v>750</v>
+      </c>
+      <c r="B775" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="776" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A776" s="19" t="s">
+        <v>749</v>
+      </c>
+      <c r="B776" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="777" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A777" s="18" t="s">
+        <v>748</v>
+      </c>
+      <c r="B777" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="778" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A778" s="19" t="s">
+        <v>747</v>
+      </c>
+      <c r="B778" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="779" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A779" s="19" t="s">
+        <v>746</v>
+      </c>
+      <c r="B779" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="780" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A780" s="19" t="s">
+        <v>745</v>
+      </c>
+      <c r="B780" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="781" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A781" s="19" t="s">
+        <v>744</v>
+      </c>
+      <c r="B781" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="782" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A782" s="19" t="s">
+        <v>743</v>
+      </c>
+      <c r="B782" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="783" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A783" s="18" t="s">
+        <v>742</v>
+      </c>
+      <c r="B783" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="784" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A784" s="19" t="s">
+        <v>741</v>
+      </c>
+      <c r="B784" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="785" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A785" s="18" t="s">
+        <v>740</v>
+      </c>
+      <c r="B785" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="786" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A786" s="19" t="s">
+        <v>739</v>
+      </c>
+      <c r="B786" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="787" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A787" s="18" t="s">
+        <v>738</v>
+      </c>
+      <c r="B787" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="788" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A788" s="18" t="s">
+        <v>737</v>
+      </c>
+      <c r="B788" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="789" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A789" s="18" t="s">
+        <v>736</v>
+      </c>
+      <c r="B789" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="790" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A790" s="19" t="s">
+        <v>735</v>
+      </c>
+      <c r="B790" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="791" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A791" s="18" t="s">
+        <v>734</v>
+      </c>
+      <c r="B791" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="792" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A792" s="19" t="s">
+        <v>733</v>
+      </c>
+      <c r="B792" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="793" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A793" s="19" t="s">
+        <v>732</v>
+      </c>
+      <c r="B793" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="794" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A794" s="19" t="s">
+        <v>731</v>
+      </c>
+      <c r="B794" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="795" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A795" s="18" t="s">
+        <v>730</v>
+      </c>
+      <c r="B795" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="796" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A796" s="18" t="s">
+        <v>729</v>
+      </c>
+      <c r="B796" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="797" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A797" s="19" t="s">
+        <v>728</v>
+      </c>
+      <c r="B797" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="798" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A798" s="19" t="s">
+        <v>727</v>
+      </c>
+      <c r="B798" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="799" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A799" s="19" t="s">
+        <v>726</v>
+      </c>
+      <c r="B799" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="800" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A800" s="19" t="s">
+        <v>725</v>
+      </c>
+      <c r="B800" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="801" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A801" s="18" t="s">
+        <v>724</v>
+      </c>
+      <c r="B801" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="802" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A802" s="18" t="s">
+        <v>723</v>
+      </c>
+      <c r="B802" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="803" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A803" s="19" t="s">
+        <v>722</v>
+      </c>
+      <c r="B803" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="804" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A804" s="18" t="s">
+        <v>721</v>
+      </c>
+      <c r="B804" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="805" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A805" s="19" t="s">
+        <v>720</v>
+      </c>
+      <c r="B805" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="806" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A806" s="19" t="s">
+        <v>719</v>
+      </c>
+      <c r="B806" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="807" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A807" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="B807" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="808" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A808" s="19" t="s">
+        <v>717</v>
+      </c>
+      <c r="B808" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="809" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A809" s="19" t="s">
+        <v>716</v>
+      </c>
+      <c r="B809" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="810" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A810" s="19" t="s">
+        <v>715</v>
+      </c>
+      <c r="B810" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="811" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A811" s="18" t="s">
+        <v>714</v>
+      </c>
+      <c r="B811" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="812" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A812" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="B812" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="813" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A813" s="18" t="s">
+        <v>712</v>
+      </c>
+      <c r="B813" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="814" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A814" s="19" t="s">
+        <v>711</v>
+      </c>
+      <c r="B814" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="815" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A815" s="18" t="s">
+        <v>710</v>
+      </c>
+      <c r="B815" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="816" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A816" s="19" t="s">
+        <v>709</v>
+      </c>
+      <c r="B816" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="817" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A817" s="19" t="s">
+        <v>708</v>
+      </c>
+      <c r="B817" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="818" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A818" s="18" t="s">
+        <v>707</v>
+      </c>
+      <c r="B818" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="819" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A819" s="18" t="s">
+        <v>706</v>
+      </c>
+      <c r="B819" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="820" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A820" s="18" t="s">
+        <v>705</v>
+      </c>
+      <c r="B820" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="821" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A821" s="19" t="s">
+        <v>704</v>
+      </c>
+      <c r="B821" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="822" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A822" s="19" t="s">
+        <v>703</v>
+      </c>
+      <c r="B822" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="823" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A823" s="19" t="s">
+        <v>702</v>
+      </c>
+      <c r="B823" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="824" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A824" s="19" t="s">
+        <v>701</v>
+      </c>
+      <c r="B824" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="825" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A825" s="19" t="s">
+        <v>700</v>
+      </c>
+      <c r="B825" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="826" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A826" s="19" t="s">
+        <v>699</v>
+      </c>
+      <c r="B826" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="827" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A827" s="18" t="s">
+        <v>698</v>
+      </c>
+      <c r="B827" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="828" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A828" s="18" t="s">
+        <v>697</v>
+      </c>
+      <c r="B828" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="829" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A829" s="19" t="s">
+        <v>696</v>
+      </c>
+      <c r="B829" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="830" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A830" s="18" t="s">
+        <v>695</v>
+      </c>
+      <c r="B830" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="831" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A831" s="19" t="s">
+        <v>694</v>
+      </c>
+      <c r="B831" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="832" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A832" s="18" t="s">
+        <v>693</v>
+      </c>
+      <c r="B832" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="833" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A833" s="19" t="s">
+        <v>692</v>
+      </c>
+      <c r="B833" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="834" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A834" s="19" t="s">
+        <v>691</v>
+      </c>
+      <c r="B834" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="835" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A835" s="19" t="s">
+        <v>690</v>
+      </c>
+      <c r="B835" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="836" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A836" s="19" t="s">
+        <v>689</v>
+      </c>
+      <c r="B836" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="837" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A837" s="19" t="s">
+        <v>688</v>
+      </c>
+      <c r="B837" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="838" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A838" s="18" t="s">
+        <v>672</v>
+      </c>
+      <c r="B838" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="839" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A839" s="19" t="s">
+        <v>687</v>
+      </c>
+      <c r="B839" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="840" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A840" s="19" t="s">
+        <v>686</v>
+      </c>
+      <c r="B840" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="841" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A841" s="19" t="s">
+        <v>685</v>
+      </c>
+      <c r="B841" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="842" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A842" s="18" t="s">
+        <v>684</v>
+      </c>
+      <c r="B842" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="843" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A843" s="19" t="s">
+        <v>683</v>
+      </c>
+      <c r="B843" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="844" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A844" s="18" t="s">
+        <v>682</v>
+      </c>
+      <c r="B844" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="845" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A845" s="19" t="s">
+        <v>681</v>
+      </c>
+      <c r="B845" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="846" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A846" s="19" t="s">
+        <v>680</v>
+      </c>
+      <c r="B846" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="847" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A847" s="18" t="s">
+        <v>679</v>
+      </c>
+      <c r="B847" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="848" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A848" s="19" t="s">
+        <v>678</v>
+      </c>
+      <c r="B848" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="849" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A849" s="18" t="s">
+        <v>677</v>
+      </c>
+      <c r="B849" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="850" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A850" s="18" t="s">
+        <v>676</v>
+      </c>
+      <c r="B850" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="851" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A851" s="18" t="s">
+        <v>675</v>
+      </c>
+      <c r="B851" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="852" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A852" s="19" t="s">
+        <v>674</v>
+      </c>
+      <c r="B852" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="853" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A853" s="18" t="s">
+        <v>673</v>
+      </c>
+      <c r="B853" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="854" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A854" s="18" t="s">
+        <v>672</v>
+      </c>
+      <c r="B854" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="855" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A855" s="18" t="s">
+        <v>671</v>
+      </c>
+      <c r="B855" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="856" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A856" s="18" t="s">
+        <v>670</v>
+      </c>
+      <c r="B856" s="1" t="s">
+        <v>764</v>
       </c>
     </row>
   </sheetData>

--- a/on_the_way.xlsx
+++ b/on_the_way.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2191" uniqueCount="991">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2385" uniqueCount="1086">
   <si>
     <t>Track</t>
   </si>
@@ -2989,6 +2989,291 @@
   </si>
   <si>
     <t>465536522184988</t>
+  </si>
+  <si>
+    <t>777434090393020</t>
+  </si>
+  <si>
+    <t>465566169789464</t>
+  </si>
+  <si>
+    <t>JT5513045238314</t>
+  </si>
+  <si>
+    <t>777433662475158</t>
+  </si>
+  <si>
+    <t>9818559892636</t>
+  </si>
+  <si>
+    <t>YT8893094760881</t>
+  </si>
+  <si>
+    <t>777434073315054</t>
+  </si>
+  <si>
+    <t>9818578550531</t>
+  </si>
+  <si>
+    <t>79128460260058</t>
+  </si>
+  <si>
+    <t>9818576706061</t>
+  </si>
+  <si>
+    <t>465564992037113</t>
+  </si>
+  <si>
+    <t>9818577037004</t>
+  </si>
+  <si>
+    <t>9840060133744</t>
+  </si>
+  <si>
+    <t>79128826754930</t>
+  </si>
+  <si>
+    <t>79129179322763</t>
+  </si>
+  <si>
+    <t>9840038387928</t>
+  </si>
+  <si>
+    <t>SF5111574911471</t>
+  </si>
+  <si>
+    <t>777433527468973</t>
+  </si>
+  <si>
+    <t>YT7637068719807</t>
+  </si>
+  <si>
+    <t>JT5513707504339</t>
+  </si>
+  <si>
+    <t>79129156123281</t>
+  </si>
+  <si>
+    <t>79128853693826</t>
+  </si>
+  <si>
+    <t>YT7637058244955</t>
+  </si>
+  <si>
+    <t>465566092886770</t>
+  </si>
+  <si>
+    <t>777434050892814</t>
+  </si>
+  <si>
+    <t>465574634283285</t>
+  </si>
+  <si>
+    <t>465563664573725</t>
+  </si>
+  <si>
+    <t>465566406174921</t>
+  </si>
+  <si>
+    <t>79129044047956</t>
+  </si>
+  <si>
+    <t>YT8892994401272</t>
+  </si>
+  <si>
+    <t>JT9002655758778</t>
+  </si>
+  <si>
+    <t>YT8893257692341</t>
+  </si>
+  <si>
+    <t>JT5513626163572</t>
+  </si>
+  <si>
+    <t>9818561987580</t>
+  </si>
+  <si>
+    <t>YT8892979283930</t>
+  </si>
+  <si>
+    <t>9818586683596</t>
+  </si>
+  <si>
+    <t>9818530207013</t>
+  </si>
+  <si>
+    <t>79129222778231</t>
+  </si>
+  <si>
+    <t>79129205750236</t>
+  </si>
+  <si>
+    <t>79129141494256</t>
+  </si>
+  <si>
+    <t>79129230309146</t>
+  </si>
+  <si>
+    <t>9818584360819</t>
+  </si>
+  <si>
+    <t>9818581111963</t>
+  </si>
+  <si>
+    <t>JT5512664136523</t>
+  </si>
+  <si>
+    <t>465566995872448</t>
+  </si>
+  <si>
+    <t>465566321766962</t>
+  </si>
+  <si>
+    <t>JT5512724538526</t>
+  </si>
+  <si>
+    <t>777433874590537</t>
+  </si>
+  <si>
+    <t>465565875662049</t>
+  </si>
+  <si>
+    <t>777433711450355</t>
+  </si>
+  <si>
+    <t>YT0701294554686</t>
+  </si>
+  <si>
+    <t>79129230300670</t>
+  </si>
+  <si>
+    <t>79128857545559</t>
+  </si>
+  <si>
+    <t>79128814029756</t>
+  </si>
+  <si>
+    <t>JT5513675093398</t>
+  </si>
+  <si>
+    <t>9818561019674</t>
+  </si>
+  <si>
+    <t>JT5513193877406</t>
+  </si>
+  <si>
+    <t>JT5513237468484</t>
+  </si>
+  <si>
+    <t>YT0701283811255</t>
+  </si>
+  <si>
+    <t>YT8892827580624</t>
+  </si>
+  <si>
+    <t>79129038752092</t>
+  </si>
+  <si>
+    <t>465564043205290</t>
+  </si>
+  <si>
+    <t>9818552381440</t>
+  </si>
+  <si>
+    <t>YT0701214758048</t>
+  </si>
+  <si>
+    <t>9840050663402</t>
+  </si>
+  <si>
+    <t>YT0701245500313</t>
+  </si>
+  <si>
+    <t>777433786111597</t>
+  </si>
+  <si>
+    <t>465567207526059</t>
+  </si>
+  <si>
+    <t>YT0701023018171</t>
+  </si>
+  <si>
+    <t>777433007904358</t>
+  </si>
+  <si>
+    <t>9818562435993</t>
+  </si>
+  <si>
+    <t>YT0701238200936</t>
+  </si>
+  <si>
+    <t>9840056909746</t>
+  </si>
+  <si>
+    <t>JT5512929435504</t>
+  </si>
+  <si>
+    <t>777433732351786</t>
+  </si>
+  <si>
+    <t>YT0701254688563</t>
+  </si>
+  <si>
+    <t>777433699389874</t>
+  </si>
+  <si>
+    <t>465567736767087</t>
+  </si>
+  <si>
+    <t>777434050976170</t>
+  </si>
+  <si>
+    <t>YT0701158861813</t>
+  </si>
+  <si>
+    <t>YT8893144142577</t>
+  </si>
+  <si>
+    <t>YT8893268926457</t>
+  </si>
+  <si>
+    <t>YT0701159825618</t>
+  </si>
+  <si>
+    <t>YT0700970389303</t>
+  </si>
+  <si>
+    <t>701314495076</t>
+  </si>
+  <si>
+    <t>777433671745217</t>
+  </si>
+  <si>
+    <t>465569411936239</t>
+  </si>
+  <si>
+    <t>465549252290332</t>
+  </si>
+  <si>
+    <t>777433841170338</t>
+  </si>
+  <si>
+    <t>YT0701314352454</t>
+  </si>
+  <si>
+    <t>YT0700887517882</t>
+  </si>
+  <si>
+    <t>777433739476901</t>
+  </si>
+  <si>
+    <t>777433856563195</t>
+  </si>
+  <si>
+    <t>JT0025066115699</t>
+  </si>
+  <si>
+    <t>10.08.26</t>
   </si>
 </sst>
 </file>
@@ -3081,7 +3366,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3156,6 +3441,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="7" quotePrefix="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3679,7 +3970,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1139"/>
+  <dimension ref="A1:D1237"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="27.44140625" style="2" customWidth="1"/>
@@ -12688,6 +12979,782 @@
       </c>
       <c r="B1139" s="1" t="s">
         <v>364</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:2" ht="14.4">
+      <c r="A1141" s="27" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B1141" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:2" ht="14.4">
+      <c r="A1142" s="26" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B1142" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:2" ht="14.4">
+      <c r="A1143" s="26" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B1143" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:2" ht="14.4">
+      <c r="A1144" s="27" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B1144" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:2" ht="14.4">
+      <c r="A1145" s="27" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B1145" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:2" ht="14.4">
+      <c r="A1146" s="26" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B1146" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:2" ht="14.4">
+      <c r="A1147" s="26" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B1147" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:2" ht="14.4">
+      <c r="A1148" s="26" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B1148" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:2" ht="14.4">
+      <c r="A1149" s="26" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B1149" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:2" ht="14.4">
+      <c r="A1150" s="26" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B1150" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:2" ht="14.4">
+      <c r="A1151" s="27" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B1151" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:2" ht="14.4">
+      <c r="A1152" s="27" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B1152" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:2" ht="14.4">
+      <c r="A1153" s="27" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B1153" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:2" ht="14.4">
+      <c r="A1154" s="27" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B1154" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:2" ht="14.4">
+      <c r="A1155" s="27" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B1155" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:2" ht="14.4">
+      <c r="A1156" s="26" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B1156" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:2" ht="14.4">
+      <c r="A1157" s="26" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B1157" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:2" ht="14.4">
+      <c r="A1158" s="26" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B1158" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:2" ht="14.4">
+      <c r="A1159" s="27" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B1159" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:2" ht="14.4">
+      <c r="A1160" s="26" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B1160" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:2" ht="14.4">
+      <c r="A1161" s="27" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B1161" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:2" ht="14.4">
+      <c r="A1162" s="26" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B1162" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:2" ht="14.4">
+      <c r="A1163" s="27" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B1163" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:2" ht="14.4">
+      <c r="A1164" s="26" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B1164" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:2" ht="14.4">
+      <c r="A1165" s="26" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B1165" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:2" ht="14.4">
+      <c r="A1166" s="27" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B1166" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:2" ht="14.4">
+      <c r="A1167" s="26" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B1167" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:2" ht="14.4">
+      <c r="A1168" s="26" t="s">
+        <v>992</v>
+      </c>
+      <c r="B1168" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:2" ht="14.4">
+      <c r="A1169" s="26" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B1169" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:2" ht="14.4">
+      <c r="A1170" s="27" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B1170" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:2" ht="14.4">
+      <c r="A1171" s="26" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B1171" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:2" ht="14.4">
+      <c r="A1172" s="27" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B1172" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:2" ht="14.4">
+      <c r="A1173" s="26" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B1173" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:2" ht="14.4">
+      <c r="A1174" s="26" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B1174" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:2" ht="14.4">
+      <c r="A1175" s="26" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B1175" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:2" ht="14.4">
+      <c r="A1176" s="27" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B1176" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:2" ht="14.4">
+      <c r="A1177" s="27" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B1177" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:2" ht="14.4">
+      <c r="A1178" s="27" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B1178" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:2" ht="14.4">
+      <c r="A1179" s="27" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B1179" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:2" ht="14.4">
+      <c r="A1180" s="26" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B1180" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:2" ht="14.4">
+      <c r="A1181" s="27" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B1181" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:2" ht="14.4">
+      <c r="A1182" s="26" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B1182" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:2" ht="14.4">
+      <c r="A1183" s="26" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B1183" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:2" ht="14.4">
+      <c r="A1184" s="26" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B1184" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:2" ht="14.4">
+      <c r="A1185" s="26" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1185" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:2" ht="14.4">
+      <c r="A1186" s="27" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B1186" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:2" ht="14.4">
+      <c r="A1187" s="26" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B1187" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:2" ht="14.4">
+      <c r="A1188" s="26" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B1188" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:2" ht="14.4">
+      <c r="A1189" s="26" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B1189" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:2" ht="14.4">
+      <c r="A1190" s="27" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B1190" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:2" ht="14.4">
+      <c r="A1191" s="26" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B1191" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:2" ht="14.4">
+      <c r="A1192" s="26" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B1192" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:2" ht="14.4">
+      <c r="A1193" s="26" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B1193" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:2" ht="14.4">
+      <c r="A1194" s="27" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B1194" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:2" ht="14.4">
+      <c r="A1195" s="26" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B1195" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:2" ht="14.4">
+      <c r="A1196" s="26" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B1196" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:2" ht="14.4">
+      <c r="A1197" s="26" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B1197" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:2" ht="14.4">
+      <c r="A1198" s="26" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B1198" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:2" ht="14.4">
+      <c r="A1199" s="26" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B1199" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:2" ht="14.4">
+      <c r="A1200" s="26" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B1200" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:2" ht="14.4">
+      <c r="A1201" s="26" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B1201" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:2" ht="14.4">
+      <c r="A1202" s="26" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B1202" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:2" ht="14.4">
+      <c r="A1203" s="27" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B1203" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:2" ht="14.4">
+      <c r="A1204" s="26" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B1204" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:2" ht="14.4">
+      <c r="A1205" s="27" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B1205" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:2" ht="14.4">
+      <c r="A1206" s="27" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B1206" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:2" ht="14.4">
+      <c r="A1207" s="27" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B1207" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:2" ht="14.4">
+      <c r="A1208" s="27" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B1208" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:2" ht="14.4">
+      <c r="A1209" s="26" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B1209" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:2" ht="14.4">
+      <c r="A1210" s="26" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B1210" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:2" ht="14.4">
+      <c r="A1211" s="26" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B1211" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:2" ht="14.4">
+      <c r="A1212" s="26" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B1212" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:2" ht="14.4">
+      <c r="A1213" s="26" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B1213" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:2" ht="14.4">
+      <c r="A1214" s="26" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B1214" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:2" ht="14.4">
+      <c r="A1215" s="27" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B1215" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:2" ht="14.4">
+      <c r="A1216" s="26" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B1216" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:2" ht="14.4">
+      <c r="A1217" s="26" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B1217" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:2" ht="14.4">
+      <c r="A1218" s="27" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B1218" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:2" ht="14.4">
+      <c r="A1219" s="27" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B1219" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:2" ht="14.4">
+      <c r="A1220" s="26" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B1220" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:2" ht="14.4">
+      <c r="A1221" s="27" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B1221" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:2" ht="14.4">
+      <c r="A1222" s="26" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B1222" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:2" ht="14.4">
+      <c r="A1223" s="26" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B1223" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:2" ht="14.4">
+      <c r="A1224" s="26" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B1224" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:2" ht="14.4">
+      <c r="A1225" s="26" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B1225" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:2" ht="14.4">
+      <c r="A1226" s="26" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B1226" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:2" ht="14.4">
+      <c r="A1227" s="26" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B1227" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:2" ht="14.4">
+      <c r="A1228" s="26" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B1228" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:2" ht="14.4">
+      <c r="A1229" s="26" t="s">
+        <v>999</v>
+      </c>
+      <c r="B1229" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:2" ht="14.4">
+      <c r="A1230" s="26" t="s">
+        <v>998</v>
+      </c>
+      <c r="B1230" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:2" ht="14.4">
+      <c r="A1231" s="26" t="s">
+        <v>997</v>
+      </c>
+      <c r="B1231" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:2" ht="14.4">
+      <c r="A1232" s="27" t="s">
+        <v>996</v>
+      </c>
+      <c r="B1232" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:2" ht="14.4">
+      <c r="A1233" s="26" t="s">
+        <v>995</v>
+      </c>
+      <c r="B1233" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:2" ht="14.4">
+      <c r="A1234" s="26" t="s">
+        <v>994</v>
+      </c>
+      <c r="B1234" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:2" ht="14.4">
+      <c r="A1235" s="27" t="s">
+        <v>993</v>
+      </c>
+      <c r="B1235" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:2" ht="14.4">
+      <c r="A1236" s="26" t="s">
+        <v>992</v>
+      </c>
+      <c r="B1236" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:2" ht="14.4">
+      <c r="A1237" s="26" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1237" s="1" t="s">
+        <v>1085</v>
       </c>
     </row>
   </sheetData>

--- a/on_the_way.xlsx
+++ b/on_the_way.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30DF60C6-41DF-4E6E-B927-EDC4E7075643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB775BB1-F6B4-4E29-BC67-C05C412AB3B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2751" uniqueCount="1174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2983" uniqueCount="1235">
   <si>
     <t>Track</t>
   </si>
@@ -3552,13 +3552,196 @@
   </si>
   <si>
     <t>02.08.26</t>
+  </si>
+  <si>
+    <t>JT5514369771159</t>
+  </si>
+  <si>
+    <t>JT5514222047724</t>
+  </si>
+  <si>
+    <t>JT5514191133250</t>
+  </si>
+  <si>
+    <t>JT5514387160969</t>
+  </si>
+  <si>
+    <t>JT5515333619926</t>
+  </si>
+  <si>
+    <t>JT5514273420118</t>
+  </si>
+  <si>
+    <t>JT5514772403108</t>
+  </si>
+  <si>
+    <t>YT8893663683449</t>
+  </si>
+  <si>
+    <t>YT8893606621372</t>
+  </si>
+  <si>
+    <t>JT5514331870580</t>
+  </si>
+  <si>
+    <t>JT5514318815720</t>
+  </si>
+  <si>
+    <t>JT5515382703484</t>
+  </si>
+  <si>
+    <t>JT5514154028743</t>
+  </si>
+  <si>
+    <t>YT8893609315751</t>
+  </si>
+  <si>
+    <t>YT8893659852668</t>
+  </si>
+  <si>
+    <t>YT0702581563916</t>
+  </si>
+  <si>
+    <t>YT8893437760297</t>
+  </si>
+  <si>
+    <t>YT0702471925297</t>
+  </si>
+  <si>
+    <t>YT8893707568215</t>
+  </si>
+  <si>
+    <t>YT8893459036910</t>
+  </si>
+  <si>
+    <t>YT8893735361495</t>
+  </si>
+  <si>
+    <t>YT0702550991045</t>
+  </si>
+  <si>
+    <t>YT8893529184215</t>
+  </si>
+  <si>
+    <t>JT5515325105649</t>
+  </si>
+  <si>
+    <t>JT5515013775852</t>
+  </si>
+  <si>
+    <t>YT8893553629908</t>
+  </si>
+  <si>
+    <t>YT8893568735430</t>
+  </si>
+  <si>
+    <t>JT5514806504489</t>
+  </si>
+  <si>
+    <t>YT8893573902391</t>
+  </si>
+  <si>
+    <t>YT8893328872674</t>
+  </si>
+  <si>
+    <t>DPK317147298462</t>
+  </si>
+  <si>
+    <t>JT5513864452084</t>
+  </si>
+  <si>
+    <t>JT5514366380148</t>
+  </si>
+  <si>
+    <t>JT5515103455832</t>
+  </si>
+  <si>
+    <t>JT5514251343504</t>
+  </si>
+  <si>
+    <t>YT8893753537049</t>
+  </si>
+  <si>
+    <t>YT8893603345556</t>
+  </si>
+  <si>
+    <t>YT0701417973666</t>
+  </si>
+  <si>
+    <t>YT0701511065027</t>
+  </si>
+  <si>
+    <t>YT8893927297359</t>
+  </si>
+  <si>
+    <t>JT5514113897521</t>
+  </si>
+  <si>
+    <t>JT5513870972023</t>
+  </si>
+  <si>
+    <t>JT9002630635983</t>
+  </si>
+  <si>
+    <t>JT5513851297687</t>
+  </si>
+  <si>
+    <t>YT8893729572461</t>
+  </si>
+  <si>
+    <t>JT5514530389324</t>
+  </si>
+  <si>
+    <t>JT5514476194551</t>
+  </si>
+  <si>
+    <t>JT5514432508668</t>
+  </si>
+  <si>
+    <t>YT0701917026688</t>
+  </si>
+  <si>
+    <t>YT8893564258412</t>
+  </si>
+  <si>
+    <t>JT5513724742314</t>
+  </si>
+  <si>
+    <t>YT8893640396748</t>
+  </si>
+  <si>
+    <t>YT8893873599659</t>
+  </si>
+  <si>
+    <t>JT5514212072439</t>
+  </si>
+  <si>
+    <t>JT5514251573866</t>
+  </si>
+  <si>
+    <t>JT5514205469407</t>
+  </si>
+  <si>
+    <t>JT5513737705831</t>
+  </si>
+  <si>
+    <t>JT5514136170830</t>
+  </si>
+  <si>
+    <t>JT5514695832192</t>
+  </si>
+  <si>
+    <t>14.08.26</t>
+  </si>
+  <si>
+    <t>16.08.26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3585,6 +3768,12 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -4236,7 +4425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1421"/>
+  <dimension ref="A1:D1595"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="27.44140625" style="2" customWidth="1"/>
@@ -15489,7 +15678,1387 @@
         <v>1173</v>
       </c>
     </row>
+    <row r="1423" spans="1:2" ht="14.4">
+      <c r="A1423">
+        <v>8200443693521</v>
+      </c>
+      <c r="B1423" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:2" ht="14.4">
+      <c r="A1424" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B1424" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:2" ht="14.4">
+      <c r="A1425">
+        <v>9818636146318</v>
+      </c>
+      <c r="B1425" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:2" ht="14.4">
+      <c r="A1426" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B1426" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:2" ht="14.4">
+      <c r="A1427" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B1427" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:2" ht="14.4">
+      <c r="A1428">
+        <v>465580401727419</v>
+      </c>
+      <c r="B1428" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:2" ht="14.4">
+      <c r="A1429">
+        <v>777435018724159</v>
+      </c>
+      <c r="B1429" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:2" ht="14.4">
+      <c r="A1430" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B1430" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:2" ht="14.4">
+      <c r="A1431" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B1431" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:2" ht="14.4">
+      <c r="A1432" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B1432" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:2" ht="14.4">
+      <c r="A1433">
+        <v>465583330213192</v>
+      </c>
+      <c r="B1433" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:2" ht="14.4">
+      <c r="A1434" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B1434" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:2" ht="14.4">
+      <c r="A1435" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B1435" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:2" ht="14.4">
+      <c r="A1436" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B1436" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:2" ht="14.4">
+      <c r="A1437">
+        <v>777435343890019</v>
+      </c>
+      <c r="B1437" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:2" ht="14.4">
+      <c r="A1438" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B1438" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:2" ht="14.4">
+      <c r="A1439">
+        <v>9818645079994</v>
+      </c>
+      <c r="B1439" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:2" ht="14.4">
+      <c r="A1440">
+        <v>9818590707776</v>
+      </c>
+      <c r="B1440" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:2" ht="14.4">
+      <c r="A1441">
+        <v>79130375055265</v>
+      </c>
+      <c r="B1441" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:2" ht="14.4">
+      <c r="A1442">
+        <v>9818591328486</v>
+      </c>
+      <c r="B1442" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:2" ht="14.4">
+      <c r="A1443">
+        <v>777435164554151</v>
+      </c>
+      <c r="B1443" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:2" ht="14.4">
+      <c r="A1444" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B1444" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:2" ht="14.4">
+      <c r="A1445">
+        <v>777434990462240</v>
+      </c>
+      <c r="B1445" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:2" ht="14.4">
+      <c r="A1446" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B1446" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:2" ht="14.4">
+      <c r="A1447">
+        <v>465578424722236</v>
+      </c>
+      <c r="B1447" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:2" ht="14.4">
+      <c r="A1448" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B1448" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:2" ht="14.4">
+      <c r="A1449" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B1449" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:2" ht="14.4">
+      <c r="A1450">
+        <v>9818642414455</v>
+      </c>
+      <c r="B1450" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:2" ht="14.4">
+      <c r="A1451">
+        <v>777434351560656</v>
+      </c>
+      <c r="B1451" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:2" ht="14.4">
+      <c r="A1452">
+        <v>79130274448824</v>
+      </c>
+      <c r="B1452" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:2" ht="14.4">
+      <c r="A1453" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B1453" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:2" ht="14.4">
+      <c r="A1454">
+        <v>465578311147993</v>
+      </c>
+      <c r="B1454" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:2" ht="14.4">
+      <c r="A1455">
+        <v>9818644951424</v>
+      </c>
+      <c r="B1455" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:2" ht="14.4">
+      <c r="A1456">
+        <v>465580826023570</v>
+      </c>
+      <c r="B1456" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:2" ht="14.4">
+      <c r="A1457">
+        <v>9818631639538</v>
+      </c>
+      <c r="B1457" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:2" ht="14.4">
+      <c r="A1458">
+        <v>9840030374709</v>
+      </c>
+      <c r="B1458" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:2" ht="14.4">
+      <c r="A1459">
+        <v>9818600175463</v>
+      </c>
+      <c r="B1459" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:2" ht="14.4">
+      <c r="A1460">
+        <v>777434506666952</v>
+      </c>
+      <c r="B1460" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:2" ht="14.4">
+      <c r="A1461">
+        <v>777435351332185</v>
+      </c>
+      <c r="B1461" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:2" ht="14.4">
+      <c r="A1462" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B1462" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:2" ht="14.4">
+      <c r="A1463">
+        <v>777435035694786</v>
+      </c>
+      <c r="B1463" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:2" ht="14.4">
+      <c r="A1464" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B1464" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:2" ht="14.4">
+      <c r="A1465" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B1465" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:2" ht="14.4">
+      <c r="A1466">
+        <v>79130143110425</v>
+      </c>
+      <c r="B1466" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:2" ht="14.4">
+      <c r="A1467">
+        <v>9840004280016</v>
+      </c>
+      <c r="B1467" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:2" ht="14.4">
+      <c r="A1468">
+        <v>79130322188117</v>
+      </c>
+      <c r="B1468" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:2" ht="14.4">
+      <c r="A1469">
+        <v>777434456545990</v>
+      </c>
+      <c r="B1469" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:2" ht="14.4">
+      <c r="A1470" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B1470" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:2" ht="14.4">
+      <c r="A1471" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B1471" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:2" ht="14.4">
+      <c r="A1472">
+        <v>9818593453144</v>
+      </c>
+      <c r="B1472" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:2" ht="14.4">
+      <c r="A1473">
+        <v>9818654424503</v>
+      </c>
+      <c r="B1473" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:2" ht="14.4">
+      <c r="A1474">
+        <v>9818643788381</v>
+      </c>
+      <c r="B1474" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:2" ht="14.4">
+      <c r="A1475">
+        <v>777434280772084</v>
+      </c>
+      <c r="B1475" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:2" ht="14.4">
+      <c r="A1476">
+        <v>9840006010501</v>
+      </c>
+      <c r="B1476" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:2" ht="14.4">
+      <c r="A1477">
+        <v>9818629818882</v>
+      </c>
+      <c r="B1477" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:2" ht="14.4">
+      <c r="A1478">
+        <v>465578051542107</v>
+      </c>
+      <c r="B1478" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:2" ht="14.4">
+      <c r="A1479">
+        <v>9818627138675</v>
+      </c>
+      <c r="B1479" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:2" ht="14.4">
+      <c r="A1480">
+        <v>777435025666846</v>
+      </c>
+      <c r="B1480" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:2" ht="14.4">
+      <c r="A1481">
+        <v>465570902374412</v>
+      </c>
+      <c r="B1481" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:2" ht="14.4">
+      <c r="A1482">
+        <v>777434390270214</v>
+      </c>
+      <c r="B1482" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:2" ht="14.4">
+      <c r="A1483">
+        <v>465579140601896</v>
+      </c>
+      <c r="B1483" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:2" ht="14.4">
+      <c r="A1484" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B1484" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:2" ht="14.4">
+      <c r="A1485">
+        <v>777434297610954</v>
+      </c>
+      <c r="B1485" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:2" ht="14.4">
+      <c r="A1486" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B1486" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:2" ht="14.4">
+      <c r="A1487">
+        <v>777434295567852</v>
+      </c>
+      <c r="B1487" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:2" ht="14.4">
+      <c r="A1488">
+        <v>773435854529975</v>
+      </c>
+      <c r="B1488" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:2" ht="14.4">
+      <c r="A1489">
+        <v>465579400399077</v>
+      </c>
+      <c r="B1489" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:2" ht="14.4">
+      <c r="A1490">
+        <v>465571656078034</v>
+      </c>
+      <c r="B1490" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:2" ht="14.4">
+      <c r="A1491">
+        <v>465571656078034</v>
+      </c>
+      <c r="B1491" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:2" ht="14.4">
+      <c r="A1492" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B1492" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:2" ht="14.4">
+      <c r="A1493">
+        <v>465579119943647</v>
+      </c>
+      <c r="B1493" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:2" ht="14.4">
+      <c r="A1494" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B1494" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:2" ht="14.4">
+      <c r="A1495">
+        <v>465582471070146</v>
+      </c>
+      <c r="B1495" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:2" ht="14.4">
+      <c r="A1496">
+        <v>777434233604218</v>
+      </c>
+      <c r="B1496" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:2" ht="14.4">
+      <c r="A1497">
+        <v>777434884882435</v>
+      </c>
+      <c r="B1497" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:2" ht="14.4">
+      <c r="A1498">
+        <v>777434299301964</v>
+      </c>
+      <c r="B1498" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:2" ht="14.4">
+      <c r="A1499">
+        <v>313082691804394</v>
+      </c>
+      <c r="B1499" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:2" ht="14.4">
+      <c r="A1500">
+        <v>777434946844488</v>
+      </c>
+      <c r="B1500" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:2" ht="14.4">
+      <c r="A1501">
+        <v>777434884881930</v>
+      </c>
+      <c r="B1501" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:2" ht="14.4">
+      <c r="A1502">
+        <v>435307032391454</v>
+      </c>
+      <c r="B1502" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:2" ht="14.4">
+      <c r="A1503">
+        <v>79130494504955</v>
+      </c>
+      <c r="B1503" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:2" ht="14.4">
+      <c r="A1504">
+        <v>465582327633731</v>
+      </c>
+      <c r="B1504" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:2" ht="14.4">
+      <c r="A1505" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B1505" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:2" ht="14.4">
+      <c r="A1506" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B1506" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:2" ht="14.4">
+      <c r="A1507">
+        <v>79129480026947</v>
+      </c>
+      <c r="B1507" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:2" ht="14.4">
+      <c r="A1508">
+        <v>79129956787218</v>
+      </c>
+      <c r="B1508" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:2" ht="14.4">
+      <c r="A1509">
+        <v>79130449704992</v>
+      </c>
+      <c r="B1509" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:2" ht="14.4">
+      <c r="A1510">
+        <v>79130656900441</v>
+      </c>
+      <c r="B1510" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:2" ht="14.4">
+      <c r="A1511">
+        <v>79130533639222</v>
+      </c>
+      <c r="B1511" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:2" ht="14.4">
+      <c r="A1512" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B1512" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:2" ht="14.4">
+      <c r="A1513" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B1513" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:2" ht="14.4">
+      <c r="A1514">
+        <v>79130458508416</v>
+      </c>
+      <c r="B1514" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:2" ht="14.4">
+      <c r="A1515" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B1515" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:2" ht="14.4">
+      <c r="A1516">
+        <v>9818636146318</v>
+      </c>
+      <c r="B1516" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:2" ht="14.4">
+      <c r="A1517" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B1517" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:2" ht="14.4">
+      <c r="A1518" s="1"/>
+    </row>
+    <row r="1519" spans="1:2" ht="14.4">
+      <c r="A1519">
+        <v>777435353876275</v>
+      </c>
+      <c r="B1519" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:2" ht="14.4">
+      <c r="A1520">
+        <v>465580835799057</v>
+      </c>
+      <c r="B1520" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:2" ht="14.4">
+      <c r="A1521">
+        <v>9818617018947</v>
+      </c>
+      <c r="B1521" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:2" ht="14.4">
+      <c r="A1522">
+        <v>465578912722442</v>
+      </c>
+      <c r="B1522" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:2" ht="14.4">
+      <c r="A1523" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B1523" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:2" ht="14.4">
+      <c r="A1524">
+        <v>777435252663232</v>
+      </c>
+      <c r="B1524" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:2" ht="14.4">
+      <c r="A1525" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B1525" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:2" ht="14.4">
+      <c r="A1526" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B1526" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:2" ht="14.4">
+      <c r="A1527">
+        <v>9818601514151</v>
+      </c>
+      <c r="B1527" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:2" ht="14.4">
+      <c r="A1528">
+        <v>9818610359642</v>
+      </c>
+      <c r="B1528" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:2" ht="14.4">
+      <c r="A1529">
+        <v>9818613092601</v>
+      </c>
+      <c r="B1529" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:2" ht="14.4">
+      <c r="A1530" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B1530" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:2" ht="14.4">
+      <c r="A1531">
+        <v>465582936597633</v>
+      </c>
+      <c r="B1531" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:2" ht="14.4">
+      <c r="A1532">
+        <v>777436034549323</v>
+      </c>
+      <c r="B1532" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:2" ht="14.4">
+      <c r="A1533" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B1533" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:2" ht="14.4">
+      <c r="A1534" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B1534" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:2" ht="14.4">
+      <c r="A1535" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B1535" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:2" ht="14.4">
+      <c r="A1536" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B1536" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:2" ht="14.4">
+      <c r="A1537" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B1537" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:2" ht="14.4">
+      <c r="A1538" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B1538" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:2" ht="14.4">
+      <c r="A1539">
+        <v>777435457067840</v>
+      </c>
+      <c r="B1539" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:2" ht="14.4">
+      <c r="A1540">
+        <v>777435490412564</v>
+      </c>
+      <c r="B1540" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:2" ht="14.4">
+      <c r="A1541">
+        <v>773436555560374</v>
+      </c>
+      <c r="B1541" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:2" ht="14.4">
+      <c r="A1542" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B1542" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:2" ht="14.4">
+      <c r="A1543" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B1543" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:2" ht="14.4">
+      <c r="A1544" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B1544" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:2" ht="14.4">
+      <c r="A1545">
+        <v>777435391763316</v>
+      </c>
+      <c r="B1545" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:2" ht="14.4">
+      <c r="A1546">
+        <v>79130364270671</v>
+      </c>
+      <c r="B1546" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:2" ht="14.4">
+      <c r="A1547" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B1547" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:2" ht="14.4">
+      <c r="A1548">
+        <v>465581814789127</v>
+      </c>
+      <c r="B1548" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:2" ht="14.4">
+      <c r="A1549" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B1549" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:2" ht="14.4">
+      <c r="A1550">
+        <v>777435921603737</v>
+      </c>
+      <c r="B1550" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:2" ht="14.4">
+      <c r="A1551">
+        <v>465588881652713</v>
+      </c>
+      <c r="B1551" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1552" spans="1:2" ht="14.4">
+      <c r="A1552">
+        <v>465588489250632</v>
+      </c>
+      <c r="B1552" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:2" ht="14.4">
+      <c r="A1553">
+        <v>465580490864093</v>
+      </c>
+      <c r="B1553" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:2" ht="14.4">
+      <c r="A1554">
+        <v>777435424905540</v>
+      </c>
+      <c r="B1554" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:2" ht="14.4">
+      <c r="A1555" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B1555" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:2" ht="14.4">
+      <c r="A1556">
+        <v>465581312531999</v>
+      </c>
+      <c r="B1556" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:2" ht="14.4">
+      <c r="A1557">
+        <v>777435223838178</v>
+      </c>
+      <c r="B1557" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:2" ht="14.4">
+      <c r="A1558">
+        <v>777435877234853</v>
+      </c>
+      <c r="B1558" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:2" ht="14.4">
+      <c r="A1559">
+        <v>773436470982899</v>
+      </c>
+      <c r="B1559" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:2" ht="14.4">
+      <c r="A1560" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B1560" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:2" ht="14.4">
+      <c r="A1561">
+        <v>465582279909107</v>
+      </c>
+      <c r="B1561" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:2" ht="14.4">
+      <c r="A1562">
+        <v>777435252517930</v>
+      </c>
+      <c r="B1562" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:2" ht="14.4">
+      <c r="A1563">
+        <v>9818688573287</v>
+      </c>
+      <c r="B1563" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:2" ht="14.4">
+      <c r="A1564" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B1564" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:2" ht="14.4">
+      <c r="A1565" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B1565" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:2" ht="14.4">
+      <c r="A1566" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B1566" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:2" ht="14.4">
+      <c r="A1567" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B1567" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:2" ht="14.4">
+      <c r="A1568" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B1568" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:2" ht="14.4">
+      <c r="A1569">
+        <v>9818617576374</v>
+      </c>
+      <c r="B1569" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:2" ht="14.4">
+      <c r="A1570" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B1570" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:2" ht="14.4">
+      <c r="A1571">
+        <v>79130707695017</v>
+      </c>
+      <c r="B1571" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:2" ht="14.4">
+      <c r="A1572">
+        <v>9818654269552</v>
+      </c>
+      <c r="B1572" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:2" ht="14.4">
+      <c r="A1573" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B1573" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:2" ht="14.4">
+      <c r="A1574">
+        <v>777435226494580</v>
+      </c>
+      <c r="B1574" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:2" ht="14.4">
+      <c r="A1575" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B1575" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:2" ht="14.4">
+      <c r="A1576">
+        <v>9818644786454</v>
+      </c>
+      <c r="B1576" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:2" ht="14.4">
+      <c r="A1577">
+        <v>79131026087503</v>
+      </c>
+      <c r="B1577" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:2" ht="14.4">
+      <c r="A1578">
+        <v>79130421641222</v>
+      </c>
+      <c r="B1578" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:2" ht="14.4">
+      <c r="A1579" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B1579" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:2" ht="14.4">
+      <c r="A1580" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B1580" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:2" ht="14.4">
+      <c r="A1581">
+        <v>465582217151986</v>
+      </c>
+      <c r="B1581" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:2" ht="14.4">
+      <c r="A1582">
+        <v>9818655262041</v>
+      </c>
+      <c r="B1582" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:2" ht="14.4">
+      <c r="A1583">
+        <v>79130706635294</v>
+      </c>
+      <c r="B1583" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:2" ht="14.4">
+      <c r="A1584" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B1584" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:2" ht="14.4">
+      <c r="A1585">
+        <v>79131225335597</v>
+      </c>
+      <c r="B1585" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:2" ht="14.4">
+      <c r="A1586">
+        <v>9818650608648</v>
+      </c>
+      <c r="B1586" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:2" ht="14.4">
+      <c r="A1587">
+        <v>79130611869731</v>
+      </c>
+      <c r="B1587" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:2" ht="14.4">
+      <c r="A1588">
+        <v>8216193224121</v>
+      </c>
+      <c r="B1588" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:2" ht="14.4">
+      <c r="A1589">
+        <v>79130603998795</v>
+      </c>
+      <c r="B1589" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:2" ht="14.4">
+      <c r="A1590">
+        <v>79130567443930</v>
+      </c>
+      <c r="B1590" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:2" ht="14.4">
+      <c r="A1591">
+        <v>79130479184776</v>
+      </c>
+      <c r="B1591" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:2" ht="14.4">
+      <c r="A1592">
+        <v>79025184696373</v>
+      </c>
+      <c r="B1592" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:2" ht="14.4">
+      <c r="A1593" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B1593" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:2" ht="14.4">
+      <c r="A1594">
+        <v>8201623748621</v>
+      </c>
+      <c r="B1594" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:2" ht="14.4">
+      <c r="A1595" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B1595" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
